--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -3,15 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zkJIpBtB4AkNuWB2yILnwV6giu8Vz9ZSJTBZi+xvUCc="/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -147,6 +152,48 @@
   <si>
     <t>Hp</t>
   </si>
+  <si>
+    <t>Item_Test_LargeRuby</t>
+  </si>
+  <si>
+    <t>큰 루비</t>
+  </si>
+  <si>
+    <t>Item_Test_HeavyJewel</t>
+  </si>
+  <si>
+    <t>무거운 보석</t>
+  </si>
+  <si>
+    <t>가방 중량 테스트용</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Item_Test_LargeDiamond</t>
+  </si>
+  <si>
+    <t>큰 다이아몬드</t>
+  </si>
+  <si>
+    <t>크고 비싸다</t>
+  </si>
+  <si>
+    <t>Item_Test_SmallRuby</t>
+  </si>
+  <si>
+    <t>루비</t>
+  </si>
+  <si>
+    <t>작고 소중하다</t>
+  </si>
+  <si>
+    <t>Item_Test_SmallSappire</t>
+  </si>
+  <si>
+    <t>사파이어</t>
+  </si>
 </sst>
 </file>
 
@@ -220,7 +267,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -233,23 +280,20 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
     <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -261,10 +305,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -469,7 +509,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.38"/>
+    <col customWidth="1" min="1" max="1" width="20.13"/>
     <col customWidth="1" min="2" max="2" width="17.13"/>
     <col customWidth="1" min="3" max="3" width="44.38"/>
     <col customWidth="1" min="4" max="4" width="17.75"/>
@@ -513,16 +553,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3"/>
@@ -567,16 +607,16 @@
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N2" s="3"/>
@@ -594,79 +634,79 @@
       <c r="Z2" s="3"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>1.0</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4" s="3">
         <v>100.0</v>
       </c>
       <c r="H4" s="3"/>
@@ -690,30 +730,30 @@
       <c r="Z4" s="3"/>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="3">
         <v>10.0</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5" s="3">
         <v>30.0</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="4">
+      <c r="J5" s="3">
         <v>100.0</v>
       </c>
       <c r="K5" s="3"/>
@@ -734,37 +774,37 @@
       <c r="Z5" s="3"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <v>2.0</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6" s="3">
         <v>20.0</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="4">
+      <c r="L6" s="3">
         <v>50.0</v>
       </c>
-      <c r="M6" s="4">
+      <c r="M6" s="3">
         <v>0.0</v>
       </c>
       <c r="N6" s="3"/>
@@ -782,13 +822,27 @@
       <c r="Z6" s="3"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
+      <c r="A7" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="8">
+        <v>15.0</v>
+      </c>
+      <c r="G7" s="8">
+        <v>100.0</v>
+      </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
@@ -810,13 +864,27 @@
       <c r="Z7" s="3"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
+      <c r="A8" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="8">
+        <v>9999.0</v>
+      </c>
+      <c r="G8" s="8">
+        <v>10.0</v>
+      </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3"/>
       <c r="J8" s="3"/>
@@ -838,13 +906,27 @@
       <c r="Z8" s="3"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
+      <c r="A9" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="8">
+        <v>20.0</v>
+      </c>
+      <c r="G9" s="8">
+        <v>150.0</v>
+      </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
@@ -866,13 +948,27 @@
       <c r="Z9" s="3"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
+      <c r="A10" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="G10" s="8">
+        <v>15.0</v>
+      </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
@@ -894,13 +990,27 @@
       <c r="Z10" s="3"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="8">
+        <v>2.0</v>
+      </c>
+      <c r="G11" s="8">
+        <v>15.0</v>
+      </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,12 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId5"/>
+    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -151,41 +167,203 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="25">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -199,9 +377,201 @@
         <bgColor rgb="FFD2F2DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -215,60 +585,545 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -458,34 +1313,35 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:Z1000"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.38"/>
-    <col customWidth="1" min="2" max="2" width="17.13"/>
-    <col customWidth="1" min="3" max="3" width="44.38"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="5" width="19.75"/>
-    <col customWidth="1" min="6" max="6" width="13.25"/>
-    <col customWidth="1" min="7" max="7" width="11.0"/>
-    <col customWidth="1" min="8" max="8" width="27.13"/>
-    <col customWidth="1" min="9" max="9" width="28.25"/>
-    <col customWidth="1" min="10" max="10" width="14.63"/>
-    <col customWidth="1" min="11" max="11" width="12.88"/>
-    <col customWidth="1" min="12" max="12" width="11.0"/>
-    <col customWidth="1" min="13" max="13" width="17.38"/>
-    <col customWidth="1" min="14" max="26" width="11.0"/>
+    <col min="1" max="1" width="19.3796296296296" customWidth="1"/>
+    <col min="2" max="2" width="17.1296296296296" customWidth="1"/>
+    <col min="3" max="3" width="44.3796296296296" customWidth="1"/>
+    <col min="4" max="4" width="17.75" customWidth="1"/>
+    <col min="5" max="5" width="19.75" customWidth="1"/>
+    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="27.1296296296296" customWidth="1"/>
+    <col min="9" max="9" width="28.25" customWidth="1"/>
+    <col min="10" max="10" width="14.6296296296296" customWidth="1"/>
+    <col min="11" max="11" width="12.8796296296296" customWidth="1"/>
+    <col min="12" max="12" width="11" customWidth="1"/>
+    <col min="13" max="13" width="17.3796296296296" customWidth="1"/>
+    <col min="14" max="26" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1" spans="1:26">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -513,16 +1369,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3"/>
@@ -539,7 +1395,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2">
+    <row r="2" ht="13.2" spans="1:26">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -567,16 +1423,16 @@
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>16</v>
       </c>
       <c r="N2" s="3"/>
@@ -593,81 +1449,81 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="8" t="s">
+      <c r="N3" s="5"/>
+      <c r="O3" s="5"/>
+      <c r="P3" s="5"/>
+      <c r="Q3" s="5"/>
+      <c r="R3" s="5"/>
+      <c r="S3" s="5"/>
+      <c r="T3" s="5"/>
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="B4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="9">
-        <v>1.0</v>
+      <c r="F4" s="6">
+        <v>1</v>
       </c>
-      <c r="G4" s="4">
-        <v>100.0</v>
+      <c r="G4" s="3">
+        <v>100</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -689,32 +1545,32 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="8" t="s">
+    <row r="5" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="4">
-        <v>10.0</v>
+      <c r="F5" s="3">
+        <v>10</v>
       </c>
-      <c r="G5" s="4">
-        <v>30.0</v>
+      <c r="G5" s="3">
+        <v>30</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="4">
-        <v>100.0</v>
+      <c r="J5" s="3">
+        <v>100</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -733,39 +1589,39 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="8" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:26">
+      <c r="A6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="8" t="s">
+      <c r="B6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="4">
-        <v>2.0</v>
+      <c r="F6" s="3">
+        <v>2</v>
       </c>
-      <c r="G6" s="4">
-        <v>20.0</v>
+      <c r="G6" s="3">
+        <v>20</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="4">
-        <v>50.0</v>
+      <c r="L6" s="3">
+        <v>50</v>
       </c>
-      <c r="M6" s="4">
-        <v>0.0</v>
+      <c r="M6" s="3">
+        <v>0</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -781,7 +1637,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.75" customHeight="1" spans="1:26">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -809,7 +1665,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1" spans="1:26">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -837,7 +1693,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1" spans="1:26">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -865,7 +1721,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1" spans="1:26">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -893,7 +1749,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1" spans="1:26">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -921,7 +1777,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1" spans="1:26">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -949,7 +1805,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
+    <row r="13" ht="15.75" customHeight="1" spans="1:26">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -977,7 +1833,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
+    <row r="14" ht="15.75" customHeight="1" spans="1:26">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1005,7 +1861,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
+    <row r="15" ht="15.75" customHeight="1" spans="1:26">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1033,7 +1889,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
+    <row r="16" ht="15.75" customHeight="1" spans="1:26">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1061,7 +1917,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
+    <row r="17" ht="15.75" customHeight="1" spans="1:26">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1089,7 +1945,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1" spans="1:26">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1117,7 +1973,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.75" customHeight="1" spans="1:26">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1145,7 +2001,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1" spans="1:26">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1173,7 +2029,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1" spans="1:26">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1201,7 +2057,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1" spans="1:26">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1229,7 +2085,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1" spans="1:26">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1257,7 +2113,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1" spans="1:26">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1285,7 +2141,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1" spans="1:26">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -1313,7 +2169,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1" spans="1:26">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -1341,7 +2197,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1" spans="1:26">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -1369,7 +2225,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1" spans="1:26">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -1397,7 +2253,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1" spans="1:26">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -1425,7 +2281,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1" spans="1:26">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -1453,7 +2309,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1" spans="1:26">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -1481,7 +2337,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1" spans="1:26">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -1509,7 +2365,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1" spans="1:26">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -1537,7 +2393,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1" spans="1:26">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -1565,7 +2421,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1" spans="1:26">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1593,7 +2449,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1" spans="1:26">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1621,7 +2477,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1" spans="1:26">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1649,7 +2505,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1" spans="1:26">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1677,7 +2533,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1" spans="1:26">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1705,7 +2561,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1" spans="1:26">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1733,7 +2589,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1" spans="1:26">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1761,7 +2617,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1" spans="1:26">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1789,7 +2645,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="1:26">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1817,7 +2673,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1" spans="1:26">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1845,7 +2701,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1" spans="1:26">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1873,7 +2729,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1" spans="1:26">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1901,7 +2757,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1" spans="1:26">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1929,7 +2785,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1" spans="1:26">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -1957,7 +2813,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1" spans="1:26">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -1985,7 +2841,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1" spans="1:26">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2013,7 +2869,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1" spans="1:26">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2041,7 +2897,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1" spans="1:26">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2069,7 +2925,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1" spans="1:26">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2097,7 +2953,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1" spans="1:26">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2125,7 +2981,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1" spans="1:26">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2153,7 +3009,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1" spans="1:26">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2181,7 +3037,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1" spans="1:26">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2209,7 +3065,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1" spans="1:26">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2237,7 +3093,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1" spans="1:26">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2265,7 +3121,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1" spans="1:26">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2293,7 +3149,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1" spans="1:26">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2321,7 +3177,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1" spans="1:26">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2349,7 +3205,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1" spans="1:26">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2377,7 +3233,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1" spans="1:26">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2405,7 +3261,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1" spans="1:26">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2433,7 +3289,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1" spans="1:26">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2461,7 +3317,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1" spans="1:26">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2489,7 +3345,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1" spans="1:26">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2517,7 +3373,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1" spans="1:26">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2545,7 +3401,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1" spans="1:26">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2573,7 +3429,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1" spans="1:26">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2601,7 +3457,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1" spans="1:26">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2629,7 +3485,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1" spans="1:26">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2657,7 +3513,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1" spans="1:26">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2685,7 +3541,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1" spans="1:26">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2713,7 +3569,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1" spans="1:26">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2741,7 +3597,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1" spans="1:26">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2769,7 +3625,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1" spans="1:26">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2797,7 +3653,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1" spans="1:26">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2825,7 +3681,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1" spans="1:26">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2853,7 +3709,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1" spans="1:26">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2881,7 +3737,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1" spans="1:26">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2909,7 +3765,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1" spans="1:26">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2937,7 +3793,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1" spans="1:26">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2965,7 +3821,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1" spans="1:26">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2993,7 +3849,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1" spans="1:26">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3021,7 +3877,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1" spans="1:26">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3049,7 +3905,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1" spans="1:26">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3077,7 +3933,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1" spans="1:26">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3105,7 +3961,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1" spans="1:26">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3133,7 +3989,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1" spans="1:26">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -3161,7 +4017,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1" spans="1:26">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -3189,7 +4045,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1" spans="1:26">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -3217,7 +4073,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1" spans="1:26">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -3245,7 +4101,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1" spans="1:26">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -3273,7 +4129,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1" spans="1:26">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -3301,7 +4157,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1" spans="1:26">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -3329,7 +4185,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1" spans="1:26">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -3357,7 +4213,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1" spans="1:26">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -3385,7 +4241,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1" spans="1:26">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3413,7 +4269,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1" spans="1:26">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3441,7 +4297,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1" spans="1:26">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -3469,7 +4325,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1" spans="1:26">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -3497,7 +4353,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1" spans="1:26">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -3525,7 +4381,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1" spans="1:26">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -3553,7 +4409,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1" spans="1:26">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3581,7 +4437,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1" spans="1:26">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -3609,7 +4465,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1" spans="1:26">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -3637,7 +4493,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1" spans="1:26">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3665,7 +4521,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1" spans="1:26">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3693,7 +4549,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1" spans="1:26">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -3721,7 +4577,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1" spans="1:26">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -3749,7 +4605,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1" spans="1:26">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -3777,7 +4633,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1" spans="1:26">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -3805,7 +4661,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1" spans="1:26">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -3833,7 +4689,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1" spans="1:26">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -3861,7 +4717,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1" spans="1:26">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -3889,7 +4745,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1" spans="1:26">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3917,7 +4773,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1" spans="1:26">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -3945,7 +4801,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1" spans="1:26">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -3973,7 +4829,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1" spans="1:26">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4001,7 +4857,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1" spans="1:26">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4029,7 +4885,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1" spans="1:26">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4057,7 +4913,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1" spans="1:26">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4085,7 +4941,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1" spans="1:26">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4113,7 +4969,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1" spans="1:26">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4141,7 +4997,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1" spans="1:26">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -4169,7 +5025,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1" spans="1:26">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -4197,7 +5053,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1" spans="1:26">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4225,7 +5081,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1" spans="1:26">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -4253,7 +5109,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1" spans="1:26">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -4281,7 +5137,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1" spans="1:26">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -4309,7 +5165,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1" spans="1:26">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -4337,7 +5193,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1" spans="1:26">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -4365,7 +5221,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1" spans="1:26">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -4393,7 +5249,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1" spans="1:26">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -4421,7 +5277,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1" spans="1:26">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -4449,7 +5305,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1" spans="1:26">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -4477,7 +5333,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.75" customHeight="1" spans="1:26">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -4505,7 +5361,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1" spans="1:26">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -4533,7 +5389,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1" spans="1:26">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -4561,7 +5417,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1" spans="1:26">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -4589,7 +5445,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1" spans="1:26">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -4617,7 +5473,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1" spans="1:26">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -4645,7 +5501,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1" spans="1:26">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -4673,7 +5529,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1" spans="1:26">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -4701,7 +5557,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1" spans="1:26">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -4729,7 +5585,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1" spans="1:26">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -4757,7 +5613,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1" spans="1:26">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -4785,7 +5641,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1" spans="1:26">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -4813,7 +5669,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1" spans="1:26">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -4841,7 +5697,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1" spans="1:26">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -4869,7 +5725,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1" spans="1:26">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -4897,7 +5753,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1" spans="1:26">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -4925,7 +5781,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1" spans="1:26">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -4953,7 +5809,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1" spans="1:26">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4981,7 +5837,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1" spans="1:26">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5009,7 +5865,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1" spans="1:26">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5037,7 +5893,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1" spans="1:26">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5065,7 +5921,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1" spans="1:26">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5093,7 +5949,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1" spans="1:26">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5121,7 +5977,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1" spans="1:26">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5149,7 +6005,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1" spans="1:26">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -5177,7 +6033,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1" spans="1:26">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -5205,7 +6061,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1" spans="1:26">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -5233,7 +6089,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1" spans="1:26">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -5261,7 +6117,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1" spans="1:26">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -5289,7 +6145,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1" spans="1:26">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -5317,7 +6173,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1" spans="1:26">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -5345,7 +6201,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1" spans="1:26">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -5373,7 +6229,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1" spans="1:26">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -5401,7 +6257,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1" spans="1:26">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -5429,7 +6285,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1" spans="1:26">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -5457,7 +6313,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1" spans="1:26">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -5485,7 +6341,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1" spans="1:26">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -5513,7 +6369,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1" spans="1:26">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -5541,7 +6397,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1" spans="1:26">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -5569,7 +6425,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1" spans="1:26">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -5597,7 +6453,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1" spans="1:26">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -5625,7 +6481,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1" spans="1:26">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -5653,7 +6509,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1" spans="1:26">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -5681,7 +6537,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1" spans="1:26">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -5709,7 +6565,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1" spans="1:26">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -5737,7 +6593,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1" spans="1:26">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -5765,7 +6621,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1" spans="1:26">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -5793,7 +6649,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1" spans="1:26">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -5821,7 +6677,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1" spans="1:26">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -5849,7 +6705,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1" spans="1:26">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -5877,7 +6733,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1" spans="1:26">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -5905,7 +6761,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1" spans="1:26">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -5933,7 +6789,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1" spans="1:26">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -5961,7 +6817,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1" spans="1:26">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -5989,7 +6845,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1" spans="1:26">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6017,7 +6873,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1" spans="1:26">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6045,7 +6901,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1" spans="1:26">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6073,7 +6929,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1" spans="1:26">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6101,7 +6957,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1" spans="1:26">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6129,7 +6985,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1" spans="1:26">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -6157,7 +7013,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1" spans="1:26">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -6185,7 +7041,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1" spans="1:26">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -6213,7 +7069,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1" spans="1:26">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -6241,7 +7097,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1" spans="1:26">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -6269,7 +7125,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1" spans="1:26">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -6297,7 +7153,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1" spans="1:26">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -6325,7 +7181,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1" spans="1:26">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -6353,7 +7209,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1" spans="1:26">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -6381,7 +7237,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1" spans="1:26">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -6409,7 +7265,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1" spans="1:26">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -6437,7 +7293,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1" spans="1:26">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -6465,7 +7321,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1" spans="1:26">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -6493,7 +7349,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1" spans="1:26">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -6521,7 +7377,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1" spans="1:26">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -6549,7 +7405,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1" spans="1:26">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -6577,7 +7433,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1" spans="1:26">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -6605,7 +7461,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1" spans="1:26">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -6633,7 +7489,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1" spans="1:26">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -6661,7 +7517,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1" spans="1:26">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -6689,7 +7545,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1" spans="1:26">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -6717,7 +7573,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1" spans="1:26">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -6745,7 +7601,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1" spans="1:26">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7554,9 +8410,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>
+  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,22 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CE695B3-5EDF-4202-9CE3-059B9221085D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-432" yWindow="768" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId4"/>
+    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="zkJIpBtB4AkNuWB2yILnwV6giu8Vz9ZSJTBZi+xvUCc="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1vHpoHAi14pJrWCrnqynttxKRttNcSH5KaN2SCCJsnE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="67">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -30,9 +39,6 @@
     <t>아이템 종류</t>
   </si>
   <si>
-    <t>아이템 등급</t>
-  </si>
-  <si>
     <t>아이템 무게</t>
   </si>
   <si>
@@ -42,19 +48,7 @@
     <t>아이템 아이콘 경로</t>
   </si>
   <si>
-    <t>아이템 프리팹 경로</t>
-  </si>
-  <si>
-    <t>내구도(Tool)</t>
-  </si>
-  <si>
-    <t>버프종류(Potion)</t>
-  </si>
-  <si>
-    <t>버프량(Potion)</t>
-  </si>
-  <si>
-    <t>버프지속시간(Potion)</t>
+    <t>사용 횟수( -1: 무제한)</t>
   </si>
   <si>
     <t>string</t>
@@ -63,18 +57,12 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>ItemGrade</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>BuffType</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -84,12 +72,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CurrentItemType</t>
-  </si>
-  <si>
-    <t>CurrentItemGrade</t>
-  </si>
-  <si>
     <t>Weight</t>
   </si>
   <si>
@@ -99,132 +81,236 @@
     <t>IconPath</t>
   </si>
   <si>
-    <t>PrefabPath</t>
-  </si>
-  <si>
-    <t>Durability</t>
-  </si>
-  <si>
-    <t>CurrentBuffType</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
-    <t>Item_Jewel_Diamond</t>
+    <t>ChargeCount</t>
+  </si>
+  <si>
+    <t>MaterialPaths</t>
+  </si>
+  <si>
+    <t>Item_Tool_MasterKey</t>
+  </si>
+  <si>
+    <t>만능 열쇠</t>
+  </si>
+  <si>
+    <t>잠겨있는 무언가를 열 수 있다.
+여러 번 사용할 수 있다.</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Item_Tool_Key</t>
+  </si>
+  <si>
+    <t>열쇠</t>
+  </si>
+  <si>
+    <t>잠겨있는 무언가를 열 수 있다.
+한 번만 사용 할 수 있다.</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>MeshPath</t>
+  </si>
+  <si>
+    <t>Husks</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ToolObject</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Jewel__Diamond</t>
   </si>
   <si>
     <t>다이아몬드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemType</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>Jewel</t>
-  </si>
-  <si>
-    <t>Legendary</t>
-  </si>
-  <si>
-    <t>Item_Tool_Bat</t>
-  </si>
-  <si>
-    <t>방망이</t>
-  </si>
-  <si>
-    <t>Tool</t>
-  </si>
-  <si>
-    <t>Epic</t>
-  </si>
-  <si>
-    <t>Item_Potion_HealPotion</t>
-  </si>
-  <si>
-    <t>체력 포션</t>
-  </si>
-  <si>
-    <t>Potion</t>
-  </si>
-  <si>
-    <t>Rare</t>
-  </si>
-  <si>
-    <t>Hp</t>
-  </si>
-  <si>
-    <t>Item_Test_LargeRuby</t>
-  </si>
-  <si>
-    <t>큰 루비</t>
-  </si>
-  <si>
-    <t>Item_Test_HeavyJewel</t>
-  </si>
-  <si>
-    <t>무거운 보석</t>
-  </si>
-  <si>
-    <t>가방 중량 테스트용</t>
-  </si>
-  <si>
-    <t>Common</t>
-  </si>
-  <si>
-    <t>Item_Test_LargeDiamond</t>
-  </si>
-  <si>
-    <t>큰 다이아몬드</t>
-  </si>
-  <si>
-    <t>크고 비싸다</t>
-  </si>
-  <si>
-    <t>Item_Test_SmallRuby</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Diamond,Lit</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Jewel_Cone[Cone]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>JewelObject</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Amethyst</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Amethyst</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자수정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Jewel_Aquamarine</t>
+  </si>
+  <si>
+    <t>아쿠아마린</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쿠아마린이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자수정이다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>다이아몬드다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Aquamarine</t>
+  </si>
+  <si>
+    <t>에메랄드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>에메랄드다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Emerald</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Ruby</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Jewel_Emerald</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>루비</t>
-  </si>
-  <si>
-    <t>작고 소중하다</t>
-  </si>
-  <si>
-    <t>Item_Test_SmallSappire</t>
-  </si>
-  <si>
-    <t>사파이어</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>루비다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Ruby</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>Item_Jewel_Sapphire</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사피이어</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사파이어다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Sapphire</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Topaz</t>
+  </si>
+  <si>
+    <t>토파즈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>토파즈다.</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>M_Gemstone_Topaz</t>
+  </si>
+  <si>
+    <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="7">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -232,7 +318,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -248,7 +334,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -262,53 +354,57 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="left" vertical="bottom"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -498,38 +594,37 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:T1000"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.13"/>
-    <col customWidth="1" min="2" max="2" width="17.13"/>
-    <col customWidth="1" min="3" max="3" width="44.38"/>
-    <col customWidth="1" min="4" max="4" width="17.75"/>
-    <col customWidth="1" min="5" max="5" width="19.75"/>
-    <col customWidth="1" min="6" max="6" width="13.25"/>
-    <col customWidth="1" min="7" max="7" width="11.0"/>
-    <col customWidth="1" min="8" max="8" width="27.13"/>
-    <col customWidth="1" min="9" max="9" width="28.25"/>
-    <col customWidth="1" min="10" max="10" width="14.63"/>
-    <col customWidth="1" min="11" max="11" width="12.88"/>
-    <col customWidth="1" min="12" max="12" width="11.0"/>
-    <col customWidth="1" min="13" max="13" width="17.38"/>
-    <col customWidth="1" min="14" max="26" width="11.0"/>
+    <col min="1" max="1" width="20.109375" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.109375" style="9" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.77734375" customWidth="1"/>
+    <col min="5" max="5" width="13.21875" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="7" max="7" width="27.109375" customWidth="1"/>
+    <col min="8" max="8" width="16.109375" customWidth="1"/>
+    <col min="9" max="9" width="24.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="31.21875" bestFit="1" customWidth="1"/>
+    <col min="11" max="20" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -538,7 +633,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -550,21 +645,11 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -572,53 +657,43 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
+    </row>
+    <row r="2" spans="1:20" ht="13.8">
+      <c r="A2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -626,53 +701,43 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="4" t="s">
+    </row>
+    <row r="3" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>27</v>
-      </c>
       <c r="J3" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>31</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -680,39 +745,39 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:20" ht="15" customHeight="1">
+      <c r="A4" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100000</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>-1</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1.0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -722,41 +787,39 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>37</v>
+    </row>
+    <row r="5" spans="1:20" ht="15" customHeight="1">
+      <c r="A5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>23</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1</v>
       </c>
       <c r="F5" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>100.0</v>
-      </c>
-      <c r="K5" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>33</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -766,47 +829,39 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="3">
-        <v>50.0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -814,39 +869,37 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="8">
-        <v>15.0</v>
-      </c>
-      <c r="G7" s="8">
-        <v>100.0</v>
-      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8</v>
+      </c>
+      <c r="F7" s="3">
+        <v>800</v>
+      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -856,39 +909,37 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="7" t="s">
+    </row>
+    <row r="8" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A8" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3">
+        <v>700</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="8">
-        <v>9999.0</v>
-      </c>
-      <c r="G8" s="8">
-        <v>10.0</v>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="J8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -898,39 +949,37 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="7" t="s">
+    </row>
+    <row r="9" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6</v>
+      </c>
+      <c r="F9" s="3">
+        <v>600</v>
+      </c>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="8">
-        <v>20.0</v>
-      </c>
-      <c r="G9" s="8">
-        <v>150.0</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="J9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -940,39 +989,37 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B10" s="7" t="s">
+    </row>
+    <row r="10" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A10" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F10" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G10" s="8">
-        <v>15.0</v>
-      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500</v>
+      </c>
+      <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -982,39 +1029,37 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="B11" s="7" t="s">
+    </row>
+    <row r="11" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F11" s="8">
-        <v>2.0</v>
-      </c>
-      <c r="G11" s="8">
-        <v>15.0</v>
-      </c>
+      <c r="B11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4</v>
+      </c>
+      <c r="F11" s="3">
+        <v>400</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1024,25 +1069,37 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+    </row>
+    <row r="12" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A12" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3</v>
+      </c>
+      <c r="F12" s="3">
+        <v>300</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -1052,16 +1109,10 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+    </row>
+    <row r="13" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
       <c r="C13" s="1"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -1080,16 +1131,10 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+    </row>
+    <row r="14" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A14" s="6"/>
+      <c r="B14" s="6"/>
       <c r="C14" s="1"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -1108,16 +1153,10 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+    </row>
+    <row r="15" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A15" s="6"/>
+      <c r="B15" s="6"/>
       <c r="C15" s="1"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -1125,7 +1164,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="J15" s="10"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
@@ -1136,16 +1175,10 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+    </row>
+    <row r="16" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -1164,16 +1197,10 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
+    </row>
+    <row r="17" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -1192,16 +1219,10 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
+    </row>
+    <row r="18" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -1220,16 +1241,10 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
+    </row>
+    <row r="19" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -1248,16 +1263,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
+    </row>
+    <row r="20" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A20" s="8"/>
+      <c r="B20" s="8"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1276,16 +1285,10 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
+    </row>
+    <row r="21" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A21" s="8"/>
+      <c r="B21" s="8"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -1304,16 +1307,10 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
+    </row>
+    <row r="22" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A22" s="8"/>
+      <c r="B22" s="8"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1332,16 +1329,10 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
+    </row>
+    <row r="23" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A23" s="8"/>
+      <c r="B23" s="8"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -1360,16 +1351,10 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
+    </row>
+    <row r="24" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A24" s="8"/>
+      <c r="B24" s="8"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -1388,16 +1373,10 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+    </row>
+    <row r="25" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A25" s="8"/>
+      <c r="B25" s="8"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -1416,16 +1395,10 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+    </row>
+    <row r="26" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -1444,16 +1417,10 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+    </row>
+    <row r="27" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1472,16 +1439,10 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
+    </row>
+    <row r="28" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A28" s="8"/>
+      <c r="B28" s="8"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -1500,16 +1461,10 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+    </row>
+    <row r="29" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A29" s="8"/>
+      <c r="B29" s="8"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -1528,16 +1483,10 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
+    </row>
+    <row r="30" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -1556,16 +1505,10 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
+    </row>
+    <row r="31" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A31" s="8"/>
+      <c r="B31" s="8"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -1584,16 +1527,10 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
+    </row>
+    <row r="32" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A32" s="8"/>
+      <c r="B32" s="8"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -1612,16 +1549,10 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
+    </row>
+    <row r="33" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -1640,16 +1571,10 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
+    </row>
+    <row r="34" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A34" s="8"/>
+      <c r="B34" s="8"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -1668,16 +1593,10 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
+    </row>
+    <row r="35" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -1696,16 +1615,10 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
+    </row>
+    <row r="36" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A36" s="8"/>
+      <c r="B36" s="8"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -1724,16 +1637,10 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
+    </row>
+    <row r="37" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A37" s="8"/>
+      <c r="B37" s="8"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -1752,16 +1659,10 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
+    </row>
+    <row r="38" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A38" s="8"/>
+      <c r="B38" s="8"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -1780,16 +1681,10 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
+    </row>
+    <row r="39" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A39" s="8"/>
+      <c r="B39" s="8"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -1808,16 +1703,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
+    </row>
+    <row r="40" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A40" s="8"/>
+      <c r="B40" s="8"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -1836,16 +1725,10 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
+    </row>
+    <row r="41" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A41" s="8"/>
+      <c r="B41" s="8"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -1864,16 +1747,10 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
+    </row>
+    <row r="42" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A42" s="8"/>
+      <c r="B42" s="8"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -1892,16 +1769,10 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
+    </row>
+    <row r="43" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A43" s="8"/>
+      <c r="B43" s="8"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -1920,16 +1791,10 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
+    </row>
+    <row r="44" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A44" s="8"/>
+      <c r="B44" s="8"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -1948,16 +1813,10 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
+    </row>
+    <row r="45" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -1976,16 +1835,10 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
+    </row>
+    <row r="46" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -2004,16 +1857,10 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+    </row>
+    <row r="47" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A47" s="8"/>
+      <c r="B47" s="8"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -2032,16 +1879,10 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
+    </row>
+    <row r="48" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A48" s="8"/>
+      <c r="B48" s="8"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -2060,16 +1901,10 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
+    </row>
+    <row r="49" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A49" s="8"/>
+      <c r="B49" s="8"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -2088,16 +1923,10 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
+    </row>
+    <row r="50" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A50" s="8"/>
+      <c r="B50" s="8"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -2116,16 +1945,10 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
+    </row>
+    <row r="51" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A51" s="8"/>
+      <c r="B51" s="8"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -2144,16 +1967,10 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
+    </row>
+    <row r="52" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A52" s="8"/>
+      <c r="B52" s="8"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -2172,16 +1989,10 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
+    </row>
+    <row r="53" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -2200,16 +2011,10 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
+    </row>
+    <row r="54" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A54" s="8"/>
+      <c r="B54" s="8"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -2228,16 +2033,10 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
+    </row>
+    <row r="55" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A55" s="8"/>
+      <c r="B55" s="8"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -2256,16 +2055,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
+    </row>
+    <row r="56" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A56" s="8"/>
+      <c r="B56" s="8"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -2284,16 +2077,10 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
+    </row>
+    <row r="57" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A57" s="8"/>
+      <c r="B57" s="8"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -2312,16 +2099,10 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
+    </row>
+    <row r="58" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A58" s="8"/>
+      <c r="B58" s="8"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -2340,16 +2121,10 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
+    </row>
+    <row r="59" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A59" s="8"/>
+      <c r="B59" s="8"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -2368,16 +2143,10 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
+    </row>
+    <row r="60" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A60" s="8"/>
+      <c r="B60" s="8"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -2396,16 +2165,10 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
+    </row>
+    <row r="61" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A61" s="8"/>
+      <c r="B61" s="8"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -2424,16 +2187,10 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
+    </row>
+    <row r="62" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A62" s="8"/>
+      <c r="B62" s="8"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -2452,16 +2209,10 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
+    </row>
+    <row r="63" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -2480,16 +2231,10 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
+    </row>
+    <row r="64" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A64" s="8"/>
+      <c r="B64" s="8"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -2508,16 +2253,10 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
+    </row>
+    <row r="65" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A65" s="8"/>
+      <c r="B65" s="8"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -2536,16 +2275,10 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
+    </row>
+    <row r="66" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A66" s="8"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -2564,16 +2297,10 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
+    </row>
+    <row r="67" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A67" s="8"/>
+      <c r="B67" s="8"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -2592,16 +2319,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
+    </row>
+    <row r="68" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A68" s="8"/>
+      <c r="B68" s="8"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -2620,16 +2341,10 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
+    </row>
+    <row r="69" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A69" s="8"/>
+      <c r="B69" s="8"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -2648,16 +2363,10 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
+    </row>
+    <row r="70" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A70" s="8"/>
+      <c r="B70" s="8"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -2676,16 +2385,10 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
+    </row>
+    <row r="71" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A71" s="8"/>
+      <c r="B71" s="8"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -2704,16 +2407,10 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
+    </row>
+    <row r="72" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A72" s="8"/>
+      <c r="B72" s="8"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -2732,16 +2429,10 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
+    </row>
+    <row r="73" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A73" s="8"/>
+      <c r="B73" s="8"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -2760,16 +2451,10 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
+    </row>
+    <row r="74" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A74" s="8"/>
+      <c r="B74" s="8"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -2788,16 +2473,10 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="3"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
+    </row>
+    <row r="75" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A75" s="8"/>
+      <c r="B75" s="8"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -2816,16 +2495,10 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="3"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
+    </row>
+    <row r="76" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A76" s="8"/>
+      <c r="B76" s="8"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -2844,16 +2517,10 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="3"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
+    </row>
+    <row r="77" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A77" s="8"/>
+      <c r="B77" s="8"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -2872,16 +2539,10 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="3"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
+    </row>
+    <row r="78" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A78" s="8"/>
+      <c r="B78" s="8"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -2900,16 +2561,10 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
-      <c r="U78" s="3"/>
-      <c r="V78" s="3"/>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="3"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
+    </row>
+    <row r="79" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A79" s="8"/>
+      <c r="B79" s="8"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -2928,16 +2583,10 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="3"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
+    </row>
+    <row r="80" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A80" s="8"/>
+      <c r="B80" s="8"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -2956,16 +2605,10 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
-      <c r="U80" s="3"/>
-      <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
-      <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="3"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
+    </row>
+    <row r="81" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A81" s="8"/>
+      <c r="B81" s="8"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -2984,16 +2627,10 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="3"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
+    </row>
+    <row r="82" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A82" s="8"/>
+      <c r="B82" s="8"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -3012,16 +2649,10 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="3"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
+    </row>
+    <row r="83" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A83" s="8"/>
+      <c r="B83" s="8"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -3040,16 +2671,10 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="3"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
+    </row>
+    <row r="84" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A84" s="8"/>
+      <c r="B84" s="8"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -3068,16 +2693,10 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
+    </row>
+    <row r="85" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A85" s="8"/>
+      <c r="B85" s="8"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -3096,16 +2715,10 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="3"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
+    </row>
+    <row r="86" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A86" s="8"/>
+      <c r="B86" s="8"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -3124,16 +2737,10 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
-      <c r="U86" s="3"/>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="3"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
+    </row>
+    <row r="87" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A87" s="8"/>
+      <c r="B87" s="8"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -3152,16 +2759,10 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="3"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
+    </row>
+    <row r="88" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A88" s="8"/>
+      <c r="B88" s="8"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -3180,16 +2781,10 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
-      <c r="V88" s="3"/>
-      <c r="W88" s="3"/>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="3"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
+    </row>
+    <row r="89" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A89" s="8"/>
+      <c r="B89" s="8"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -3208,16 +2803,10 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="3"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
+    </row>
+    <row r="90" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A90" s="8"/>
+      <c r="B90" s="8"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -3236,16 +2825,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="3"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
+    </row>
+    <row r="91" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A91" s="8"/>
+      <c r="B91" s="8"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -3264,16 +2847,10 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
+    </row>
+    <row r="92" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A92" s="8"/>
+      <c r="B92" s="8"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -3292,16 +2869,10 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
-      <c r="U92" s="3"/>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="3"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
+    </row>
+    <row r="93" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A93" s="8"/>
+      <c r="B93" s="8"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -3320,16 +2891,10 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="3"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
+    </row>
+    <row r="94" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A94" s="8"/>
+      <c r="B94" s="8"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -3348,16 +2913,10 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
+    </row>
+    <row r="95" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A95" s="8"/>
+      <c r="B95" s="8"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -3376,16 +2935,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="3"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
+    </row>
+    <row r="96" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A96" s="8"/>
+      <c r="B96" s="8"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -3404,16 +2957,10 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
+    </row>
+    <row r="97" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A97" s="8"/>
+      <c r="B97" s="8"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -3432,16 +2979,10 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="3"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
+    </row>
+    <row r="98" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A98" s="8"/>
+      <c r="B98" s="8"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -3460,16 +3001,10 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
-      <c r="U98" s="3"/>
-      <c r="V98" s="3"/>
-      <c r="W98" s="3"/>
-      <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="3"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
+    </row>
+    <row r="99" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A99" s="8"/>
+      <c r="B99" s="8"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -3488,16 +3023,10 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
-      <c r="U99" s="3"/>
-      <c r="V99" s="3"/>
-      <c r="W99" s="3"/>
-      <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="3"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
+    </row>
+    <row r="100" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A100" s="8"/>
+      <c r="B100" s="8"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -3516,16 +3045,10 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
-      <c r="U100" s="3"/>
-      <c r="V100" s="3"/>
-      <c r="W100" s="3"/>
-      <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="3"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
+    </row>
+    <row r="101" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A101" s="8"/>
+      <c r="B101" s="8"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -3544,16 +3067,10 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
-      <c r="U101" s="3"/>
-      <c r="V101" s="3"/>
-      <c r="W101" s="3"/>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="3"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
+    </row>
+    <row r="102" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A102" s="8"/>
+      <c r="B102" s="8"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -3572,16 +3089,10 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
-      <c r="U102" s="3"/>
-      <c r="V102" s="3"/>
-      <c r="W102" s="3"/>
-      <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="3"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
+    </row>
+    <row r="103" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -3600,16 +3111,10 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
-      <c r="U103" s="3"/>
-      <c r="V103" s="3"/>
-      <c r="W103" s="3"/>
-      <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="3"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
+    </row>
+    <row r="104" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A104" s="8"/>
+      <c r="B104" s="8"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -3628,16 +3133,10 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
-      <c r="U104" s="3"/>
-      <c r="V104" s="3"/>
-      <c r="W104" s="3"/>
-      <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
-      <c r="Z104" s="3"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
+    </row>
+    <row r="105" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A105" s="8"/>
+      <c r="B105" s="8"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -3656,16 +3155,10 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
-      <c r="U105" s="3"/>
-      <c r="V105" s="3"/>
-      <c r="W105" s="3"/>
-      <c r="X105" s="3"/>
-      <c r="Y105" s="3"/>
-      <c r="Z105" s="3"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
+    </row>
+    <row r="106" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A106" s="8"/>
+      <c r="B106" s="8"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -3684,16 +3177,10 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
-      <c r="U106" s="3"/>
-      <c r="V106" s="3"/>
-      <c r="W106" s="3"/>
-      <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="3"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
+    </row>
+    <row r="107" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A107" s="8"/>
+      <c r="B107" s="8"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -3712,16 +3199,10 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
-      <c r="U107" s="3"/>
-      <c r="V107" s="3"/>
-      <c r="W107" s="3"/>
-      <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
-      <c r="Z107" s="3"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
+    </row>
+    <row r="108" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A108" s="8"/>
+      <c r="B108" s="8"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -3740,16 +3221,10 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
-      <c r="U108" s="3"/>
-      <c r="V108" s="3"/>
-      <c r="W108" s="3"/>
-      <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
-      <c r="Z108" s="3"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
+    </row>
+    <row r="109" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A109" s="8"/>
+      <c r="B109" s="8"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -3768,16 +3243,10 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
-      <c r="U109" s="3"/>
-      <c r="V109" s="3"/>
-      <c r="W109" s="3"/>
-      <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
-      <c r="Z109" s="3"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
+    </row>
+    <row r="110" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A110" s="8"/>
+      <c r="B110" s="8"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -3796,16 +3265,10 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
-      <c r="U110" s="3"/>
-      <c r="V110" s="3"/>
-      <c r="W110" s="3"/>
-      <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
-      <c r="Z110" s="3"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
+    </row>
+    <row r="111" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A111" s="8"/>
+      <c r="B111" s="8"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -3824,16 +3287,10 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
-      <c r="U111" s="3"/>
-      <c r="V111" s="3"/>
-      <c r="W111" s="3"/>
-      <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
-      <c r="Z111" s="3"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
+    </row>
+    <row r="112" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A112" s="8"/>
+      <c r="B112" s="8"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -3852,16 +3309,10 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
-      <c r="U112" s="3"/>
-      <c r="V112" s="3"/>
-      <c r="W112" s="3"/>
-      <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="3"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
+    </row>
+    <row r="113" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A113" s="8"/>
+      <c r="B113" s="8"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -3880,16 +3331,10 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
-      <c r="U113" s="3"/>
-      <c r="V113" s="3"/>
-      <c r="W113" s="3"/>
-      <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
-      <c r="Z113" s="3"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
+    </row>
+    <row r="114" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A114" s="8"/>
+      <c r="B114" s="8"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -3908,16 +3353,10 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
-      <c r="U114" s="3"/>
-      <c r="V114" s="3"/>
-      <c r="W114" s="3"/>
-      <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
-      <c r="Z114" s="3"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
+    </row>
+    <row r="115" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A115" s="8"/>
+      <c r="B115" s="8"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -3936,16 +3375,10 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
-      <c r="U115" s="3"/>
-      <c r="V115" s="3"/>
-      <c r="W115" s="3"/>
-      <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
-      <c r="Z115" s="3"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
+    </row>
+    <row r="116" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A116" s="8"/>
+      <c r="B116" s="8"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -3964,16 +3397,10 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
-      <c r="U116" s="3"/>
-      <c r="V116" s="3"/>
-      <c r="W116" s="3"/>
-      <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
-      <c r="Z116" s="3"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
+    </row>
+    <row r="117" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A117" s="8"/>
+      <c r="B117" s="8"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -3992,16 +3419,10 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
-      <c r="U117" s="3"/>
-      <c r="V117" s="3"/>
-      <c r="W117" s="3"/>
-      <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
-      <c r="Z117" s="3"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
+    </row>
+    <row r="118" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A118" s="8"/>
+      <c r="B118" s="8"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -4020,16 +3441,10 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
-      <c r="U118" s="3"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="3"/>
-      <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
-      <c r="Z118" s="3"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
+    </row>
+    <row r="119" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A119" s="8"/>
+      <c r="B119" s="8"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -4048,16 +3463,10 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
-      <c r="U119" s="3"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
-      <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
-      <c r="Z119" s="3"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
+    </row>
+    <row r="120" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A120" s="8"/>
+      <c r="B120" s="8"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -4076,16 +3485,10 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
-      <c r="U120" s="3"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="3"/>
-      <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
-      <c r="Z120" s="3"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
+    </row>
+    <row r="121" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A121" s="8"/>
+      <c r="B121" s="8"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -4104,16 +3507,10 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
-      <c r="U121" s="3"/>
-      <c r="V121" s="3"/>
-      <c r="W121" s="3"/>
-      <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
-      <c r="Z121" s="3"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
+    </row>
+    <row r="122" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A122" s="8"/>
+      <c r="B122" s="8"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -4132,16 +3529,10 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
-      <c r="U122" s="3"/>
-      <c r="V122" s="3"/>
-      <c r="W122" s="3"/>
-      <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
-      <c r="Z122" s="3"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
+    </row>
+    <row r="123" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A123" s="8"/>
+      <c r="B123" s="8"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -4160,16 +3551,10 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
-      <c r="U123" s="3"/>
-      <c r="V123" s="3"/>
-      <c r="W123" s="3"/>
-      <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
-      <c r="Z123" s="3"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
+    </row>
+    <row r="124" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A124" s="8"/>
+      <c r="B124" s="8"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -4188,16 +3573,10 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
-      <c r="U124" s="3"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="3"/>
-      <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
-      <c r="Z124" s="3"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
+    </row>
+    <row r="125" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A125" s="8"/>
+      <c r="B125" s="8"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -4216,16 +3595,10 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
-      <c r="U125" s="3"/>
-      <c r="V125" s="3"/>
-      <c r="W125" s="3"/>
-      <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
-      <c r="Z125" s="3"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
+    </row>
+    <row r="126" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A126" s="8"/>
+      <c r="B126" s="8"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -4244,16 +3617,10 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
-      <c r="U126" s="3"/>
-      <c r="V126" s="3"/>
-      <c r="W126" s="3"/>
-      <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
-      <c r="Z126" s="3"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
+    </row>
+    <row r="127" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A127" s="8"/>
+      <c r="B127" s="8"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -4272,16 +3639,10 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
-      <c r="U127" s="3"/>
-      <c r="V127" s="3"/>
-      <c r="W127" s="3"/>
-      <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
-      <c r="Z127" s="3"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
+    </row>
+    <row r="128" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A128" s="8"/>
+      <c r="B128" s="8"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -4300,16 +3661,10 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
-      <c r="U128" s="3"/>
-      <c r="V128" s="3"/>
-      <c r="W128" s="3"/>
-      <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
-      <c r="Z128" s="3"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
+    </row>
+    <row r="129" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A129" s="8"/>
+      <c r="B129" s="8"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -4328,16 +3683,10 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
-      <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="3"/>
-      <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-      <c r="Z129" s="3"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
+    </row>
+    <row r="130" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A130" s="8"/>
+      <c r="B130" s="8"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -4356,16 +3705,10 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
-      <c r="U130" s="3"/>
-      <c r="V130" s="3"/>
-      <c r="W130" s="3"/>
-      <c r="X130" s="3"/>
-      <c r="Y130" s="3"/>
-      <c r="Z130" s="3"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
+    </row>
+    <row r="131" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A131" s="8"/>
+      <c r="B131" s="8"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -4384,16 +3727,10 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
-      <c r="U131" s="3"/>
-      <c r="V131" s="3"/>
-      <c r="W131" s="3"/>
-      <c r="X131" s="3"/>
-      <c r="Y131" s="3"/>
-      <c r="Z131" s="3"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
+    </row>
+    <row r="132" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A132" s="8"/>
+      <c r="B132" s="8"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -4412,16 +3749,10 @@
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
-      <c r="U132" s="3"/>
-      <c r="V132" s="3"/>
-      <c r="W132" s="3"/>
-      <c r="X132" s="3"/>
-      <c r="Y132" s="3"/>
-      <c r="Z132" s="3"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
+    </row>
+    <row r="133" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A133" s="8"/>
+      <c r="B133" s="8"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -4440,16 +3771,10 @@
       <c r="R133" s="3"/>
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
-      <c r="U133" s="3"/>
-      <c r="V133" s="3"/>
-      <c r="W133" s="3"/>
-      <c r="X133" s="3"/>
-      <c r="Y133" s="3"/>
-      <c r="Z133" s="3"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
+    </row>
+    <row r="134" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A134" s="8"/>
+      <c r="B134" s="8"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -4468,16 +3793,10 @@
       <c r="R134" s="3"/>
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
-      <c r="U134" s="3"/>
-      <c r="V134" s="3"/>
-      <c r="W134" s="3"/>
-      <c r="X134" s="3"/>
-      <c r="Y134" s="3"/>
-      <c r="Z134" s="3"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
+    </row>
+    <row r="135" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A135" s="8"/>
+      <c r="B135" s="8"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -4496,16 +3815,10 @@
       <c r="R135" s="3"/>
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
-      <c r="U135" s="3"/>
-      <c r="V135" s="3"/>
-      <c r="W135" s="3"/>
-      <c r="X135" s="3"/>
-      <c r="Y135" s="3"/>
-      <c r="Z135" s="3"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
+    </row>
+    <row r="136" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A136" s="8"/>
+      <c r="B136" s="8"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -4524,16 +3837,10 @@
       <c r="R136" s="3"/>
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
-      <c r="U136" s="3"/>
-      <c r="V136" s="3"/>
-      <c r="W136" s="3"/>
-      <c r="X136" s="3"/>
-      <c r="Y136" s="3"/>
-      <c r="Z136" s="3"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
+    </row>
+    <row r="137" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A137" s="8"/>
+      <c r="B137" s="8"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -4552,16 +3859,10 @@
       <c r="R137" s="3"/>
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
-      <c r="U137" s="3"/>
-      <c r="V137" s="3"/>
-      <c r="W137" s="3"/>
-      <c r="X137" s="3"/>
-      <c r="Y137" s="3"/>
-      <c r="Z137" s="3"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
+    </row>
+    <row r="138" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A138" s="8"/>
+      <c r="B138" s="8"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -4580,16 +3881,10 @@
       <c r="R138" s="3"/>
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
-      <c r="U138" s="3"/>
-      <c r="V138" s="3"/>
-      <c r="W138" s="3"/>
-      <c r="X138" s="3"/>
-      <c r="Y138" s="3"/>
-      <c r="Z138" s="3"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
+    </row>
+    <row r="139" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A139" s="8"/>
+      <c r="B139" s="8"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -4608,16 +3903,10 @@
       <c r="R139" s="3"/>
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
-      <c r="U139" s="3"/>
-      <c r="V139" s="3"/>
-      <c r="W139" s="3"/>
-      <c r="X139" s="3"/>
-      <c r="Y139" s="3"/>
-      <c r="Z139" s="3"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
+    </row>
+    <row r="140" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A140" s="8"/>
+      <c r="B140" s="8"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -4636,16 +3925,10 @@
       <c r="R140" s="3"/>
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
-      <c r="U140" s="3"/>
-      <c r="V140" s="3"/>
-      <c r="W140" s="3"/>
-      <c r="X140" s="3"/>
-      <c r="Y140" s="3"/>
-      <c r="Z140" s="3"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
+    </row>
+    <row r="141" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A141" s="8"/>
+      <c r="B141" s="8"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -4664,16 +3947,10 @@
       <c r="R141" s="3"/>
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
-      <c r="U141" s="3"/>
-      <c r="V141" s="3"/>
-      <c r="W141" s="3"/>
-      <c r="X141" s="3"/>
-      <c r="Y141" s="3"/>
-      <c r="Z141" s="3"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
+    </row>
+    <row r="142" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A142" s="8"/>
+      <c r="B142" s="8"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -4692,16 +3969,10 @@
       <c r="R142" s="3"/>
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
-      <c r="U142" s="3"/>
-      <c r="V142" s="3"/>
-      <c r="W142" s="3"/>
-      <c r="X142" s="3"/>
-      <c r="Y142" s="3"/>
-      <c r="Z142" s="3"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
+    </row>
+    <row r="143" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A143" s="8"/>
+      <c r="B143" s="8"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -4720,16 +3991,10 @@
       <c r="R143" s="3"/>
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
-      <c r="U143" s="3"/>
-      <c r="V143" s="3"/>
-      <c r="W143" s="3"/>
-      <c r="X143" s="3"/>
-      <c r="Y143" s="3"/>
-      <c r="Z143" s="3"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
+    </row>
+    <row r="144" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A144" s="8"/>
+      <c r="B144" s="8"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -4748,16 +4013,10 @@
       <c r="R144" s="3"/>
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
-      <c r="U144" s="3"/>
-      <c r="V144" s="3"/>
-      <c r="W144" s="3"/>
-      <c r="X144" s="3"/>
-      <c r="Y144" s="3"/>
-      <c r="Z144" s="3"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
+    </row>
+    <row r="145" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A145" s="8"/>
+      <c r="B145" s="8"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -4776,16 +4035,10 @@
       <c r="R145" s="3"/>
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
-      <c r="U145" s="3"/>
-      <c r="V145" s="3"/>
-      <c r="W145" s="3"/>
-      <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
-      <c r="Z145" s="3"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
+    </row>
+    <row r="146" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A146" s="8"/>
+      <c r="B146" s="8"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -4804,16 +4057,10 @@
       <c r="R146" s="3"/>
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
-      <c r="U146" s="3"/>
-      <c r="V146" s="3"/>
-      <c r="W146" s="3"/>
-      <c r="X146" s="3"/>
-      <c r="Y146" s="3"/>
-      <c r="Z146" s="3"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
+    </row>
+    <row r="147" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A147" s="8"/>
+      <c r="B147" s="8"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -4832,16 +4079,10 @@
       <c r="R147" s="3"/>
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
-      <c r="U147" s="3"/>
-      <c r="V147" s="3"/>
-      <c r="W147" s="3"/>
-      <c r="X147" s="3"/>
-      <c r="Y147" s="3"/>
-      <c r="Z147" s="3"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
+    </row>
+    <row r="148" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A148" s="8"/>
+      <c r="B148" s="8"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -4860,16 +4101,10 @@
       <c r="R148" s="3"/>
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
-      <c r="U148" s="3"/>
-      <c r="V148" s="3"/>
-      <c r="W148" s="3"/>
-      <c r="X148" s="3"/>
-      <c r="Y148" s="3"/>
-      <c r="Z148" s="3"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
+    </row>
+    <row r="149" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A149" s="8"/>
+      <c r="B149" s="8"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -4888,16 +4123,10 @@
       <c r="R149" s="3"/>
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
-      <c r="U149" s="3"/>
-      <c r="V149" s="3"/>
-      <c r="W149" s="3"/>
-      <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
-      <c r="Z149" s="3"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
+    </row>
+    <row r="150" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A150" s="8"/>
+      <c r="B150" s="8"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -4916,16 +4145,10 @@
       <c r="R150" s="3"/>
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
-      <c r="U150" s="3"/>
-      <c r="V150" s="3"/>
-      <c r="W150" s="3"/>
-      <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
-      <c r="Z150" s="3"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
+    </row>
+    <row r="151" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A151" s="8"/>
+      <c r="B151" s="8"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -4944,16 +4167,10 @@
       <c r="R151" s="3"/>
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
-      <c r="U151" s="3"/>
-      <c r="V151" s="3"/>
-      <c r="W151" s="3"/>
-      <c r="X151" s="3"/>
-      <c r="Y151" s="3"/>
-      <c r="Z151" s="3"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
+    </row>
+    <row r="152" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A152" s="8"/>
+      <c r="B152" s="8"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -4972,16 +4189,10 @@
       <c r="R152" s="3"/>
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
-      <c r="U152" s="3"/>
-      <c r="V152" s="3"/>
-      <c r="W152" s="3"/>
-      <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
-      <c r="Z152" s="3"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
+    </row>
+    <row r="153" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A153" s="8"/>
+      <c r="B153" s="8"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -5000,16 +4211,10 @@
       <c r="R153" s="3"/>
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
-      <c r="U153" s="3"/>
-      <c r="V153" s="3"/>
-      <c r="W153" s="3"/>
-      <c r="X153" s="3"/>
-      <c r="Y153" s="3"/>
-      <c r="Z153" s="3"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
+    </row>
+    <row r="154" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A154" s="8"/>
+      <c r="B154" s="8"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -5028,16 +4233,10 @@
       <c r="R154" s="3"/>
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
-      <c r="U154" s="3"/>
-      <c r="V154" s="3"/>
-      <c r="W154" s="3"/>
-      <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
-      <c r="Z154" s="3"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
+    </row>
+    <row r="155" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A155" s="8"/>
+      <c r="B155" s="8"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -5056,16 +4255,10 @@
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
-      <c r="U155" s="3"/>
-      <c r="V155" s="3"/>
-      <c r="W155" s="3"/>
-      <c r="X155" s="3"/>
-      <c r="Y155" s="3"/>
-      <c r="Z155" s="3"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
+    </row>
+    <row r="156" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A156" s="8"/>
+      <c r="B156" s="8"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -5084,16 +4277,10 @@
       <c r="R156" s="3"/>
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
-      <c r="U156" s="3"/>
-      <c r="V156" s="3"/>
-      <c r="W156" s="3"/>
-      <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
-      <c r="Z156" s="3"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
+    </row>
+    <row r="157" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A157" s="8"/>
+      <c r="B157" s="8"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -5112,16 +4299,10 @@
       <c r="R157" s="3"/>
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
-      <c r="U157" s="3"/>
-      <c r="V157" s="3"/>
-      <c r="W157" s="3"/>
-      <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
-      <c r="Z157" s="3"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
+    </row>
+    <row r="158" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A158" s="8"/>
+      <c r="B158" s="8"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -5140,16 +4321,10 @@
       <c r="R158" s="3"/>
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
-      <c r="U158" s="3"/>
-      <c r="V158" s="3"/>
-      <c r="W158" s="3"/>
-      <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
-      <c r="Z158" s="3"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
+    </row>
+    <row r="159" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A159" s="8"/>
+      <c r="B159" s="8"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -5168,16 +4343,10 @@
       <c r="R159" s="3"/>
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
-      <c r="U159" s="3"/>
-      <c r="V159" s="3"/>
-      <c r="W159" s="3"/>
-      <c r="X159" s="3"/>
-      <c r="Y159" s="3"/>
-      <c r="Z159" s="3"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
+    </row>
+    <row r="160" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A160" s="8"/>
+      <c r="B160" s="8"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -5196,16 +4365,10 @@
       <c r="R160" s="3"/>
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
-      <c r="U160" s="3"/>
-      <c r="V160" s="3"/>
-      <c r="W160" s="3"/>
-      <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
-      <c r="Z160" s="3"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
+    </row>
+    <row r="161" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A161" s="8"/>
+      <c r="B161" s="8"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -5224,16 +4387,10 @@
       <c r="R161" s="3"/>
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
-      <c r="U161" s="3"/>
-      <c r="V161" s="3"/>
-      <c r="W161" s="3"/>
-      <c r="X161" s="3"/>
-      <c r="Y161" s="3"/>
-      <c r="Z161" s="3"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
+    </row>
+    <row r="162" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A162" s="8"/>
+      <c r="B162" s="8"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -5252,16 +4409,10 @@
       <c r="R162" s="3"/>
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
-      <c r="U162" s="3"/>
-      <c r="V162" s="3"/>
-      <c r="W162" s="3"/>
-      <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
-      <c r="Z162" s="3"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
+    </row>
+    <row r="163" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A163" s="8"/>
+      <c r="B163" s="8"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -5280,16 +4431,10 @@
       <c r="R163" s="3"/>
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
-      <c r="U163" s="3"/>
-      <c r="V163" s="3"/>
-      <c r="W163" s="3"/>
-      <c r="X163" s="3"/>
-      <c r="Y163" s="3"/>
-      <c r="Z163" s="3"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
+    </row>
+    <row r="164" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A164" s="8"/>
+      <c r="B164" s="8"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -5308,16 +4453,10 @@
       <c r="R164" s="3"/>
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
-      <c r="U164" s="3"/>
-      <c r="V164" s="3"/>
-      <c r="W164" s="3"/>
-      <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
-      <c r="Z164" s="3"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
+    </row>
+    <row r="165" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A165" s="8"/>
+      <c r="B165" s="8"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -5336,16 +4475,10 @@
       <c r="R165" s="3"/>
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
-      <c r="U165" s="3"/>
-      <c r="V165" s="3"/>
-      <c r="W165" s="3"/>
-      <c r="X165" s="3"/>
-      <c r="Y165" s="3"/>
-      <c r="Z165" s="3"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
+    </row>
+    <row r="166" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A166" s="8"/>
+      <c r="B166" s="8"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -5364,16 +4497,10 @@
       <c r="R166" s="3"/>
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
-      <c r="U166" s="3"/>
-      <c r="V166" s="3"/>
-      <c r="W166" s="3"/>
-      <c r="X166" s="3"/>
-      <c r="Y166" s="3"/>
-      <c r="Z166" s="3"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
+    </row>
+    <row r="167" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A167" s="8"/>
+      <c r="B167" s="8"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -5392,16 +4519,10 @@
       <c r="R167" s="3"/>
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
-      <c r="U167" s="3"/>
-      <c r="V167" s="3"/>
-      <c r="W167" s="3"/>
-      <c r="X167" s="3"/>
-      <c r="Y167" s="3"/>
-      <c r="Z167" s="3"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
+    </row>
+    <row r="168" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A168" s="8"/>
+      <c r="B168" s="8"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -5420,16 +4541,10 @@
       <c r="R168" s="3"/>
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
-      <c r="U168" s="3"/>
-      <c r="V168" s="3"/>
-      <c r="W168" s="3"/>
-      <c r="X168" s="3"/>
-      <c r="Y168" s="3"/>
-      <c r="Z168" s="3"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
+    </row>
+    <row r="169" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A169" s="8"/>
+      <c r="B169" s="8"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -5448,16 +4563,10 @@
       <c r="R169" s="3"/>
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
-      <c r="U169" s="3"/>
-      <c r="V169" s="3"/>
-      <c r="W169" s="3"/>
-      <c r="X169" s="3"/>
-      <c r="Y169" s="3"/>
-      <c r="Z169" s="3"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
+    </row>
+    <row r="170" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A170" s="8"/>
+      <c r="B170" s="8"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -5476,16 +4585,10 @@
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
-      <c r="U170" s="3"/>
-      <c r="V170" s="3"/>
-      <c r="W170" s="3"/>
-      <c r="X170" s="3"/>
-      <c r="Y170" s="3"/>
-      <c r="Z170" s="3"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
+    </row>
+    <row r="171" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A171" s="8"/>
+      <c r="B171" s="8"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -5504,16 +4607,10 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
-      <c r="U171" s="3"/>
-      <c r="V171" s="3"/>
-      <c r="W171" s="3"/>
-      <c r="X171" s="3"/>
-      <c r="Y171" s="3"/>
-      <c r="Z171" s="3"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
+    </row>
+    <row r="172" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A172" s="8"/>
+      <c r="B172" s="8"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -5532,16 +4629,10 @@
       <c r="R172" s="3"/>
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
-      <c r="U172" s="3"/>
-      <c r="V172" s="3"/>
-      <c r="W172" s="3"/>
-      <c r="X172" s="3"/>
-      <c r="Y172" s="3"/>
-      <c r="Z172" s="3"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
+    </row>
+    <row r="173" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A173" s="8"/>
+      <c r="B173" s="8"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -5560,16 +4651,10 @@
       <c r="R173" s="3"/>
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
-      <c r="U173" s="3"/>
-      <c r="V173" s="3"/>
-      <c r="W173" s="3"/>
-      <c r="X173" s="3"/>
-      <c r="Y173" s="3"/>
-      <c r="Z173" s="3"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
+    </row>
+    <row r="174" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A174" s="8"/>
+      <c r="B174" s="8"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -5588,16 +4673,10 @@
       <c r="R174" s="3"/>
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
-      <c r="U174" s="3"/>
-      <c r="V174" s="3"/>
-      <c r="W174" s="3"/>
-      <c r="X174" s="3"/>
-      <c r="Y174" s="3"/>
-      <c r="Z174" s="3"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
+    </row>
+    <row r="175" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A175" s="8"/>
+      <c r="B175" s="8"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -5616,16 +4695,10 @@
       <c r="R175" s="3"/>
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
-      <c r="U175" s="3"/>
-      <c r="V175" s="3"/>
-      <c r="W175" s="3"/>
-      <c r="X175" s="3"/>
-      <c r="Y175" s="3"/>
-      <c r="Z175" s="3"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
+    </row>
+    <row r="176" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A176" s="8"/>
+      <c r="B176" s="8"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -5644,16 +4717,10 @@
       <c r="R176" s="3"/>
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
-      <c r="U176" s="3"/>
-      <c r="V176" s="3"/>
-      <c r="W176" s="3"/>
-      <c r="X176" s="3"/>
-      <c r="Y176" s="3"/>
-      <c r="Z176" s="3"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
+    </row>
+    <row r="177" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A177" s="8"/>
+      <c r="B177" s="8"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -5672,16 +4739,10 @@
       <c r="R177" s="3"/>
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
-      <c r="U177" s="3"/>
-      <c r="V177" s="3"/>
-      <c r="W177" s="3"/>
-      <c r="X177" s="3"/>
-      <c r="Y177" s="3"/>
-      <c r="Z177" s="3"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
+    </row>
+    <row r="178" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A178" s="8"/>
+      <c r="B178" s="8"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -5700,16 +4761,10 @@
       <c r="R178" s="3"/>
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
-      <c r="U178" s="3"/>
-      <c r="V178" s="3"/>
-      <c r="W178" s="3"/>
-      <c r="X178" s="3"/>
-      <c r="Y178" s="3"/>
-      <c r="Z178" s="3"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
+    </row>
+    <row r="179" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A179" s="8"/>
+      <c r="B179" s="8"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -5728,16 +4783,10 @@
       <c r="R179" s="3"/>
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
-      <c r="U179" s="3"/>
-      <c r="V179" s="3"/>
-      <c r="W179" s="3"/>
-      <c r="X179" s="3"/>
-      <c r="Y179" s="3"/>
-      <c r="Z179" s="3"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
+    </row>
+    <row r="180" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A180" s="8"/>
+      <c r="B180" s="8"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -5756,16 +4805,10 @@
       <c r="R180" s="3"/>
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
-      <c r="U180" s="3"/>
-      <c r="V180" s="3"/>
-      <c r="W180" s="3"/>
-      <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
-      <c r="Z180" s="3"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
+    </row>
+    <row r="181" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A181" s="8"/>
+      <c r="B181" s="8"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -5784,16 +4827,10 @@
       <c r="R181" s="3"/>
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
-      <c r="U181" s="3"/>
-      <c r="V181" s="3"/>
-      <c r="W181" s="3"/>
-      <c r="X181" s="3"/>
-      <c r="Y181" s="3"/>
-      <c r="Z181" s="3"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
+    </row>
+    <row r="182" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A182" s="8"/>
+      <c r="B182" s="8"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -5812,16 +4849,10 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
-      <c r="U182" s="3"/>
-      <c r="V182" s="3"/>
-      <c r="W182" s="3"/>
-      <c r="X182" s="3"/>
-      <c r="Y182" s="3"/>
-      <c r="Z182" s="3"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
+    </row>
+    <row r="183" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A183" s="8"/>
+      <c r="B183" s="8"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -5840,16 +4871,10 @@
       <c r="R183" s="3"/>
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
-      <c r="U183" s="3"/>
-      <c r="V183" s="3"/>
-      <c r="W183" s="3"/>
-      <c r="X183" s="3"/>
-      <c r="Y183" s="3"/>
-      <c r="Z183" s="3"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
+    </row>
+    <row r="184" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A184" s="8"/>
+      <c r="B184" s="8"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -5868,16 +4893,10 @@
       <c r="R184" s="3"/>
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
-      <c r="U184" s="3"/>
-      <c r="V184" s="3"/>
-      <c r="W184" s="3"/>
-      <c r="X184" s="3"/>
-      <c r="Y184" s="3"/>
-      <c r="Z184" s="3"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
+    </row>
+    <row r="185" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A185" s="8"/>
+      <c r="B185" s="8"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -5896,16 +4915,10 @@
       <c r="R185" s="3"/>
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
-      <c r="U185" s="3"/>
-      <c r="V185" s="3"/>
-      <c r="W185" s="3"/>
-      <c r="X185" s="3"/>
-      <c r="Y185" s="3"/>
-      <c r="Z185" s="3"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
+    </row>
+    <row r="186" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A186" s="8"/>
+      <c r="B186" s="8"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -5924,16 +4937,10 @@
       <c r="R186" s="3"/>
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
-      <c r="U186" s="3"/>
-      <c r="V186" s="3"/>
-      <c r="W186" s="3"/>
-      <c r="X186" s="3"/>
-      <c r="Y186" s="3"/>
-      <c r="Z186" s="3"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
+    </row>
+    <row r="187" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A187" s="8"/>
+      <c r="B187" s="8"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -5952,16 +4959,10 @@
       <c r="R187" s="3"/>
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
-      <c r="U187" s="3"/>
-      <c r="V187" s="3"/>
-      <c r="W187" s="3"/>
-      <c r="X187" s="3"/>
-      <c r="Y187" s="3"/>
-      <c r="Z187" s="3"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
+    </row>
+    <row r="188" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A188" s="8"/>
+      <c r="B188" s="8"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -5980,16 +4981,10 @@
       <c r="R188" s="3"/>
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
-      <c r="U188" s="3"/>
-      <c r="V188" s="3"/>
-      <c r="W188" s="3"/>
-      <c r="X188" s="3"/>
-      <c r="Y188" s="3"/>
-      <c r="Z188" s="3"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
+    </row>
+    <row r="189" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A189" s="8"/>
+      <c r="B189" s="8"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -6008,16 +5003,10 @@
       <c r="R189" s="3"/>
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
-      <c r="U189" s="3"/>
-      <c r="V189" s="3"/>
-      <c r="W189" s="3"/>
-      <c r="X189" s="3"/>
-      <c r="Y189" s="3"/>
-      <c r="Z189" s="3"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
+    </row>
+    <row r="190" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A190" s="8"/>
+      <c r="B190" s="8"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -6036,16 +5025,10 @@
       <c r="R190" s="3"/>
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
-      <c r="U190" s="3"/>
-      <c r="V190" s="3"/>
-      <c r="W190" s="3"/>
-      <c r="X190" s="3"/>
-      <c r="Y190" s="3"/>
-      <c r="Z190" s="3"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
+    </row>
+    <row r="191" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A191" s="8"/>
+      <c r="B191" s="8"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -6064,16 +5047,10 @@
       <c r="R191" s="3"/>
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
-      <c r="U191" s="3"/>
-      <c r="V191" s="3"/>
-      <c r="W191" s="3"/>
-      <c r="X191" s="3"/>
-      <c r="Y191" s="3"/>
-      <c r="Z191" s="3"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
+    </row>
+    <row r="192" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A192" s="8"/>
+      <c r="B192" s="8"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -6092,16 +5069,10 @@
       <c r="R192" s="3"/>
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
-      <c r="U192" s="3"/>
-      <c r="V192" s="3"/>
-      <c r="W192" s="3"/>
-      <c r="X192" s="3"/>
-      <c r="Y192" s="3"/>
-      <c r="Z192" s="3"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
+    </row>
+    <row r="193" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A193" s="8"/>
+      <c r="B193" s="8"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -6120,16 +5091,10 @@
       <c r="R193" s="3"/>
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
-      <c r="U193" s="3"/>
-      <c r="V193" s="3"/>
-      <c r="W193" s="3"/>
-      <c r="X193" s="3"/>
-      <c r="Y193" s="3"/>
-      <c r="Z193" s="3"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
+    </row>
+    <row r="194" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A194" s="8"/>
+      <c r="B194" s="8"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -6148,16 +5113,10 @@
       <c r="R194" s="3"/>
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
-      <c r="U194" s="3"/>
-      <c r="V194" s="3"/>
-      <c r="W194" s="3"/>
-      <c r="X194" s="3"/>
-      <c r="Y194" s="3"/>
-      <c r="Z194" s="3"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
+    </row>
+    <row r="195" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A195" s="8"/>
+      <c r="B195" s="8"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -6176,16 +5135,10 @@
       <c r="R195" s="3"/>
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
-      <c r="U195" s="3"/>
-      <c r="V195" s="3"/>
-      <c r="W195" s="3"/>
-      <c r="X195" s="3"/>
-      <c r="Y195" s="3"/>
-      <c r="Z195" s="3"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
+    </row>
+    <row r="196" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A196" s="8"/>
+      <c r="B196" s="8"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -6204,16 +5157,10 @@
       <c r="R196" s="3"/>
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
-      <c r="U196" s="3"/>
-      <c r="V196" s="3"/>
-      <c r="W196" s="3"/>
-      <c r="X196" s="3"/>
-      <c r="Y196" s="3"/>
-      <c r="Z196" s="3"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="3"/>
-      <c r="B197" s="3"/>
+    </row>
+    <row r="197" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A197" s="8"/>
+      <c r="B197" s="8"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -6232,16 +5179,10 @@
       <c r="R197" s="3"/>
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
-      <c r="U197" s="3"/>
-      <c r="V197" s="3"/>
-      <c r="W197" s="3"/>
-      <c r="X197" s="3"/>
-      <c r="Y197" s="3"/>
-      <c r="Z197" s="3"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
+    </row>
+    <row r="198" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A198" s="8"/>
+      <c r="B198" s="8"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -6260,16 +5201,10 @@
       <c r="R198" s="3"/>
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
-      <c r="U198" s="3"/>
-      <c r="V198" s="3"/>
-      <c r="W198" s="3"/>
-      <c r="X198" s="3"/>
-      <c r="Y198" s="3"/>
-      <c r="Z198" s="3"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
+    </row>
+    <row r="199" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A199" s="8"/>
+      <c r="B199" s="8"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -6288,16 +5223,10 @@
       <c r="R199" s="3"/>
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
-      <c r="U199" s="3"/>
-      <c r="V199" s="3"/>
-      <c r="W199" s="3"/>
-      <c r="X199" s="3"/>
-      <c r="Y199" s="3"/>
-      <c r="Z199" s="3"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
+    </row>
+    <row r="200" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A200" s="8"/>
+      <c r="B200" s="8"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -6316,16 +5245,10 @@
       <c r="R200" s="3"/>
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
-      <c r="U200" s="3"/>
-      <c r="V200" s="3"/>
-      <c r="W200" s="3"/>
-      <c r="X200" s="3"/>
-      <c r="Y200" s="3"/>
-      <c r="Z200" s="3"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="3"/>
-      <c r="B201" s="3"/>
+    </row>
+    <row r="201" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A201" s="8"/>
+      <c r="B201" s="8"/>
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -6344,16 +5267,10 @@
       <c r="R201" s="3"/>
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
-      <c r="U201" s="3"/>
-      <c r="V201" s="3"/>
-      <c r="W201" s="3"/>
-      <c r="X201" s="3"/>
-      <c r="Y201" s="3"/>
-      <c r="Z201" s="3"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="3"/>
-      <c r="B202" s="3"/>
+    </row>
+    <row r="202" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A202" s="8"/>
+      <c r="B202" s="8"/>
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -6372,16 +5289,10 @@
       <c r="R202" s="3"/>
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
-      <c r="U202" s="3"/>
-      <c r="V202" s="3"/>
-      <c r="W202" s="3"/>
-      <c r="X202" s="3"/>
-      <c r="Y202" s="3"/>
-      <c r="Z202" s="3"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="3"/>
-      <c r="B203" s="3"/>
+    </row>
+    <row r="203" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A203" s="8"/>
+      <c r="B203" s="8"/>
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -6400,16 +5311,10 @@
       <c r="R203" s="3"/>
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
-      <c r="U203" s="3"/>
-      <c r="V203" s="3"/>
-      <c r="W203" s="3"/>
-      <c r="X203" s="3"/>
-      <c r="Y203" s="3"/>
-      <c r="Z203" s="3"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="3"/>
-      <c r="B204" s="3"/>
+    </row>
+    <row r="204" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A204" s="8"/>
+      <c r="B204" s="8"/>
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -6428,16 +5333,10 @@
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
-      <c r="U204" s="3"/>
-      <c r="V204" s="3"/>
-      <c r="W204" s="3"/>
-      <c r="X204" s="3"/>
-      <c r="Y204" s="3"/>
-      <c r="Z204" s="3"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="3"/>
-      <c r="B205" s="3"/>
+    </row>
+    <row r="205" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A205" s="8"/>
+      <c r="B205" s="8"/>
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -6456,16 +5355,10 @@
       <c r="R205" s="3"/>
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
-      <c r="U205" s="3"/>
-      <c r="V205" s="3"/>
-      <c r="W205" s="3"/>
-      <c r="X205" s="3"/>
-      <c r="Y205" s="3"/>
-      <c r="Z205" s="3"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="3"/>
-      <c r="B206" s="3"/>
+    </row>
+    <row r="206" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A206" s="8"/>
+      <c r="B206" s="8"/>
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -6484,16 +5377,10 @@
       <c r="R206" s="3"/>
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
-      <c r="U206" s="3"/>
-      <c r="V206" s="3"/>
-      <c r="W206" s="3"/>
-      <c r="X206" s="3"/>
-      <c r="Y206" s="3"/>
-      <c r="Z206" s="3"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="3"/>
-      <c r="B207" s="3"/>
+    </row>
+    <row r="207" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A207" s="8"/>
+      <c r="B207" s="8"/>
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -6512,16 +5399,10 @@
       <c r="R207" s="3"/>
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
-      <c r="U207" s="3"/>
-      <c r="V207" s="3"/>
-      <c r="W207" s="3"/>
-      <c r="X207" s="3"/>
-      <c r="Y207" s="3"/>
-      <c r="Z207" s="3"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="3"/>
-      <c r="B208" s="3"/>
+    </row>
+    <row r="208" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A208" s="8"/>
+      <c r="B208" s="8"/>
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -6540,16 +5421,10 @@
       <c r="R208" s="3"/>
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
-      <c r="U208" s="3"/>
-      <c r="V208" s="3"/>
-      <c r="W208" s="3"/>
-      <c r="X208" s="3"/>
-      <c r="Y208" s="3"/>
-      <c r="Z208" s="3"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="3"/>
-      <c r="B209" s="3"/>
+    </row>
+    <row r="209" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A209" s="8"/>
+      <c r="B209" s="8"/>
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -6568,16 +5443,10 @@
       <c r="R209" s="3"/>
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
-      <c r="U209" s="3"/>
-      <c r="V209" s="3"/>
-      <c r="W209" s="3"/>
-      <c r="X209" s="3"/>
-      <c r="Y209" s="3"/>
-      <c r="Z209" s="3"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="3"/>
-      <c r="B210" s="3"/>
+    </row>
+    <row r="210" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A210" s="8"/>
+      <c r="B210" s="8"/>
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -6596,16 +5465,10 @@
       <c r="R210" s="3"/>
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
-      <c r="U210" s="3"/>
-      <c r="V210" s="3"/>
-      <c r="W210" s="3"/>
-      <c r="X210" s="3"/>
-      <c r="Y210" s="3"/>
-      <c r="Z210" s="3"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="3"/>
-      <c r="B211" s="3"/>
+    </row>
+    <row r="211" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A211" s="8"/>
+      <c r="B211" s="8"/>
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -6624,16 +5487,10 @@
       <c r="R211" s="3"/>
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
-      <c r="U211" s="3"/>
-      <c r="V211" s="3"/>
-      <c r="W211" s="3"/>
-      <c r="X211" s="3"/>
-      <c r="Y211" s="3"/>
-      <c r="Z211" s="3"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="3"/>
-      <c r="B212" s="3"/>
+    </row>
+    <row r="212" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A212" s="8"/>
+      <c r="B212" s="8"/>
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -6652,16 +5509,10 @@
       <c r="R212" s="3"/>
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
-      <c r="U212" s="3"/>
-      <c r="V212" s="3"/>
-      <c r="W212" s="3"/>
-      <c r="X212" s="3"/>
-      <c r="Y212" s="3"/>
-      <c r="Z212" s="3"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="3"/>
-      <c r="B213" s="3"/>
+    </row>
+    <row r="213" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A213" s="8"/>
+      <c r="B213" s="8"/>
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -6680,16 +5531,10 @@
       <c r="R213" s="3"/>
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
-      <c r="U213" s="3"/>
-      <c r="V213" s="3"/>
-      <c r="W213" s="3"/>
-      <c r="X213" s="3"/>
-      <c r="Y213" s="3"/>
-      <c r="Z213" s="3"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="3"/>
-      <c r="B214" s="3"/>
+    </row>
+    <row r="214" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A214" s="8"/>
+      <c r="B214" s="8"/>
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -6708,16 +5553,10 @@
       <c r="R214" s="3"/>
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
-      <c r="U214" s="3"/>
-      <c r="V214" s="3"/>
-      <c r="W214" s="3"/>
-      <c r="X214" s="3"/>
-      <c r="Y214" s="3"/>
-      <c r="Z214" s="3"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="3"/>
-      <c r="B215" s="3"/>
+    </row>
+    <row r="215" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A215" s="8"/>
+      <c r="B215" s="8"/>
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -6736,16 +5575,10 @@
       <c r="R215" s="3"/>
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
-      <c r="U215" s="3"/>
-      <c r="V215" s="3"/>
-      <c r="W215" s="3"/>
-      <c r="X215" s="3"/>
-      <c r="Y215" s="3"/>
-      <c r="Z215" s="3"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="3"/>
-      <c r="B216" s="3"/>
+    </row>
+    <row r="216" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A216" s="8"/>
+      <c r="B216" s="8"/>
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -6764,16 +5597,10 @@
       <c r="R216" s="3"/>
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
-      <c r="U216" s="3"/>
-      <c r="V216" s="3"/>
-      <c r="W216" s="3"/>
-      <c r="X216" s="3"/>
-      <c r="Y216" s="3"/>
-      <c r="Z216" s="3"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="3"/>
-      <c r="B217" s="3"/>
+    </row>
+    <row r="217" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A217" s="8"/>
+      <c r="B217" s="8"/>
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -6792,16 +5619,10 @@
       <c r="R217" s="3"/>
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
-      <c r="U217" s="3"/>
-      <c r="V217" s="3"/>
-      <c r="W217" s="3"/>
-      <c r="X217" s="3"/>
-      <c r="Y217" s="3"/>
-      <c r="Z217" s="3"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="3"/>
-      <c r="B218" s="3"/>
+    </row>
+    <row r="218" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A218" s="8"/>
+      <c r="B218" s="8"/>
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -6820,16 +5641,10 @@
       <c r="R218" s="3"/>
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
-      <c r="U218" s="3"/>
-      <c r="V218" s="3"/>
-      <c r="W218" s="3"/>
-      <c r="X218" s="3"/>
-      <c r="Y218" s="3"/>
-      <c r="Z218" s="3"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
+    </row>
+    <row r="219" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A219" s="8"/>
+      <c r="B219" s="8"/>
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -6848,16 +5663,10 @@
       <c r="R219" s="3"/>
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
-      <c r="U219" s="3"/>
-      <c r="V219" s="3"/>
-      <c r="W219" s="3"/>
-      <c r="X219" s="3"/>
-      <c r="Y219" s="3"/>
-      <c r="Z219" s="3"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="3"/>
-      <c r="B220" s="3"/>
+    </row>
+    <row r="220" spans="1:20" ht="15.75" customHeight="1">
+      <c r="A220" s="8"/>
+      <c r="B220" s="8"/>
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -6876,17 +5685,11 @@
       <c r="R220" s="3"/>
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
-      <c r="U220" s="3"/>
-      <c r="V220" s="3"/>
-      <c r="W220" s="3"/>
-      <c r="X220" s="3"/>
-      <c r="Y220" s="3"/>
-      <c r="Z220" s="3"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="221" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="222" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="223" spans="1:20" ht="15.75" customHeight="1"/>
+    <row r="224" spans="1:20" ht="15.75" customHeight="1"/>
     <row r="225" ht="15.75" customHeight="1"/>
     <row r="226" ht="15.75" customHeight="1"/>
     <row r="227" ht="15.75" customHeight="1"/>
@@ -7664,9 +6467,8 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>
+  <phoneticPr fontId="5" type="noConversion"/>
+  <pageMargins left="0.69999998807907104" right="0.69999998807907104" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,28 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
   <sheets>
-    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr/>
 </workbook>
 </file>
 
@@ -167,203 +151,41 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -377,201 +199,9 @@
         <bgColor rgb="FFD2F2DB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -585,545 +215,60 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="10">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1313,35 +458,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.3796296296296" customWidth="1"/>
-    <col min="2" max="2" width="17.1296296296296" customWidth="1"/>
-    <col min="3" max="3" width="44.3796296296296" customWidth="1"/>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="27.1296296296296" customWidth="1"/>
-    <col min="9" max="9" width="28.25" customWidth="1"/>
-    <col min="10" max="10" width="14.6296296296296" customWidth="1"/>
-    <col min="11" max="11" width="12.8796296296296" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="17.3796296296296" customWidth="1"/>
-    <col min="14" max="26" width="11" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="19.38"/>
+    <col customWidth="1" min="2" max="2" width="17.13"/>
+    <col customWidth="1" min="3" max="3" width="44.38"/>
+    <col customWidth="1" min="4" max="4" width="17.75"/>
+    <col customWidth="1" min="5" max="5" width="19.75"/>
+    <col customWidth="1" min="6" max="6" width="13.25"/>
+    <col customWidth="1" min="7" max="7" width="11.0"/>
+    <col customWidth="1" min="8" max="8" width="27.13"/>
+    <col customWidth="1" min="9" max="9" width="28.25"/>
+    <col customWidth="1" min="10" max="10" width="14.63"/>
+    <col customWidth="1" min="11" max="11" width="12.88"/>
+    <col customWidth="1" min="12" max="12" width="11.0"/>
+    <col customWidth="1" min="13" max="13" width="17.38"/>
+    <col customWidth="1" min="14" max="26" width="11.0"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:26">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1369,16 +513,16 @@
       <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="N1" s="3"/>
@@ -1395,7 +539,7 @@
       <c r="Y1" s="3"/>
       <c r="Z1" s="3"/>
     </row>
-    <row r="2" ht="13.2" spans="1:26">
+    <row r="2">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -1423,16 +567,16 @@
       <c r="I2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="K2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="M2" s="4" t="s">
         <v>16</v>
       </c>
       <c r="N2" s="3"/>
@@ -1449,81 +593,81 @@
       <c r="Y2" s="3"/>
       <c r="Z2" s="3"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="15.75" customHeight="1">
+      <c r="A3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="5" t="s">
+      <c r="M3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A4" s="1" t="s">
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1">
+      <c r="A4" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="6">
-        <v>1</v>
+      <c r="F4" s="9">
+        <v>1.0</v>
       </c>
-      <c r="G4" s="3">
-        <v>100</v>
+      <c r="G4" s="4">
+        <v>100.0</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
@@ -1545,32 +689,32 @@
       <c r="Y4" s="3"/>
       <c r="Z4" s="3"/>
     </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="15.75" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="3">
-        <v>10</v>
+      <c r="F5" s="4">
+        <v>10.0</v>
       </c>
-      <c r="G5" s="3">
-        <v>30</v>
+      <c r="G5" s="4">
+        <v>30.0</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>100</v>
+      <c r="J5" s="4">
+        <v>100.0</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
@@ -1589,39 +733,39 @@
       <c r="Y5" s="3"/>
       <c r="Z5" s="3"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="3">
-        <v>2</v>
+      <c r="F6" s="4">
+        <v>2.0</v>
       </c>
-      <c r="G6" s="3">
-        <v>20</v>
+      <c r="G6" s="4">
+        <v>20.0</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
+      <c r="K6" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="L6" s="3">
-        <v>50</v>
+      <c r="L6" s="4">
+        <v>50.0</v>
       </c>
-      <c r="M6" s="3">
-        <v>0</v>
+      <c r="M6" s="4">
+        <v>0.0</v>
       </c>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1637,7 +781,7 @@
       <c r="Y6" s="3"/>
       <c r="Z6" s="3"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:26">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1665,7 +809,7 @@
       <c r="Y7" s="3"/>
       <c r="Z7" s="3"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:26">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1693,7 +837,7 @@
       <c r="Y8" s="3"/>
       <c r="Z8" s="3"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:26">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1721,7 +865,7 @@
       <c r="Y9" s="3"/>
       <c r="Z9" s="3"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:26">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1749,7 +893,7 @@
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:26">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1777,7 +921,7 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:26">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1805,7 +949,7 @@
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:26">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1833,7 +977,7 @@
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:26">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1861,7 +1005,7 @@
       <c r="Y14" s="3"/>
       <c r="Z14" s="3"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:26">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1889,7 +1033,7 @@
       <c r="Y15" s="3"/>
       <c r="Z15" s="3"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:26">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1917,7 +1061,7 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:26">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1945,7 +1089,7 @@
       <c r="Y17" s="3"/>
       <c r="Z17" s="3"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:26">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1973,7 +1117,7 @@
       <c r="Y18" s="3"/>
       <c r="Z18" s="3"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:26">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -2001,7 +1145,7 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:26">
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2029,7 +1173,7 @@
       <c r="Y20" s="3"/>
       <c r="Z20" s="3"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:26">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2057,7 +1201,7 @@
       <c r="Y21" s="3"/>
       <c r="Z21" s="3"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:26">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2085,7 +1229,7 @@
       <c r="Y22" s="3"/>
       <c r="Z22" s="3"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:26">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2113,7 +1257,7 @@
       <c r="Y23" s="3"/>
       <c r="Z23" s="3"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:26">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2141,7 +1285,7 @@
       <c r="Y24" s="3"/>
       <c r="Z24" s="3"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:26">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2169,7 +1313,7 @@
       <c r="Y25" s="3"/>
       <c r="Z25" s="3"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:26">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2197,7 +1341,7 @@
       <c r="Y26" s="3"/>
       <c r="Z26" s="3"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:26">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2225,7 +1369,7 @@
       <c r="Y27" s="3"/>
       <c r="Z27" s="3"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:26">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2253,7 +1397,7 @@
       <c r="Y28" s="3"/>
       <c r="Z28" s="3"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:26">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2281,7 +1425,7 @@
       <c r="Y29" s="3"/>
       <c r="Z29" s="3"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:26">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2309,7 +1453,7 @@
       <c r="Y30" s="3"/>
       <c r="Z30" s="3"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:26">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2337,7 +1481,7 @@
       <c r="Y31" s="3"/>
       <c r="Z31" s="3"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:26">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2365,7 +1509,7 @@
       <c r="Y32" s="3"/>
       <c r="Z32" s="3"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:26">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2393,7 +1537,7 @@
       <c r="Y33" s="3"/>
       <c r="Z33" s="3"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:26">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2421,7 +1565,7 @@
       <c r="Y34" s="3"/>
       <c r="Z34" s="3"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:26">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2449,7 +1593,7 @@
       <c r="Y35" s="3"/>
       <c r="Z35" s="3"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:26">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2477,7 +1621,7 @@
       <c r="Y36" s="3"/>
       <c r="Z36" s="3"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:26">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2505,7 +1649,7 @@
       <c r="Y37" s="3"/>
       <c r="Z37" s="3"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:26">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2533,7 +1677,7 @@
       <c r="Y38" s="3"/>
       <c r="Z38" s="3"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:26">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2561,7 +1705,7 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:26">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2589,7 +1733,7 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:26">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2617,7 +1761,7 @@
       <c r="Y41" s="3"/>
       <c r="Z41" s="3"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:26">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2645,7 +1789,7 @@
       <c r="Y42" s="3"/>
       <c r="Z42" s="3"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:26">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2673,7 +1817,7 @@
       <c r="Y43" s="3"/>
       <c r="Z43" s="3"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:26">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2701,7 +1845,7 @@
       <c r="Y44" s="3"/>
       <c r="Z44" s="3"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:26">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2729,7 +1873,7 @@
       <c r="Y45" s="3"/>
       <c r="Z45" s="3"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:26">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2757,7 +1901,7 @@
       <c r="Y46" s="3"/>
       <c r="Z46" s="3"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:26">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2785,7 +1929,7 @@
       <c r="Y47" s="3"/>
       <c r="Z47" s="3"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:26">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2813,7 +1957,7 @@
       <c r="Y48" s="3"/>
       <c r="Z48" s="3"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:26">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2841,7 +1985,7 @@
       <c r="Y49" s="3"/>
       <c r="Z49" s="3"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:26">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2869,7 +2013,7 @@
       <c r="Y50" s="3"/>
       <c r="Z50" s="3"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:26">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2897,7 +2041,7 @@
       <c r="Y51" s="3"/>
       <c r="Z51" s="3"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:26">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2925,7 +2069,7 @@
       <c r="Y52" s="3"/>
       <c r="Z52" s="3"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:26">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2953,7 +2097,7 @@
       <c r="Y53" s="3"/>
       <c r="Z53" s="3"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:26">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2981,7 +2125,7 @@
       <c r="Y54" s="3"/>
       <c r="Z54" s="3"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:26">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3009,7 +2153,7 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:26">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3037,7 +2181,7 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:26">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3065,7 +2209,7 @@
       <c r="Y57" s="3"/>
       <c r="Z57" s="3"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:26">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3093,7 +2237,7 @@
       <c r="Y58" s="3"/>
       <c r="Z58" s="3"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:26">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3121,7 +2265,7 @@
       <c r="Y59" s="3"/>
       <c r="Z59" s="3"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:26">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3149,7 +2293,7 @@
       <c r="Y60" s="3"/>
       <c r="Z60" s="3"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:26">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3177,7 +2321,7 @@
       <c r="Y61" s="3"/>
       <c r="Z61" s="3"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:26">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3205,7 +2349,7 @@
       <c r="Y62" s="3"/>
       <c r="Z62" s="3"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:26">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3233,7 +2377,7 @@
       <c r="Y63" s="3"/>
       <c r="Z63" s="3"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:26">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3261,7 +2405,7 @@
       <c r="Y64" s="3"/>
       <c r="Z64" s="3"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:26">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3289,7 +2433,7 @@
       <c r="Y65" s="3"/>
       <c r="Z65" s="3"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:26">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3317,7 +2461,7 @@
       <c r="Y66" s="3"/>
       <c r="Z66" s="3"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:26">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3345,7 +2489,7 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:26">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3373,7 +2517,7 @@
       <c r="Y68" s="3"/>
       <c r="Z68" s="3"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:26">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3401,7 +2545,7 @@
       <c r="Y69" s="3"/>
       <c r="Z69" s="3"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:26">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3429,7 +2573,7 @@
       <c r="Y70" s="3"/>
       <c r="Z70" s="3"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:26">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3457,7 +2601,7 @@
       <c r="Y71" s="3"/>
       <c r="Z71" s="3"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:26">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3485,7 +2629,7 @@
       <c r="Y72" s="3"/>
       <c r="Z72" s="3"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:26">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3513,7 +2657,7 @@
       <c r="Y73" s="3"/>
       <c r="Z73" s="3"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1" spans="1:26">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3541,7 +2685,7 @@
       <c r="Y74" s="3"/>
       <c r="Z74" s="3"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1" spans="1:26">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3569,7 +2713,7 @@
       <c r="Y75" s="3"/>
       <c r="Z75" s="3"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1" spans="1:26">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3597,7 +2741,7 @@
       <c r="Y76" s="3"/>
       <c r="Z76" s="3"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1" spans="1:26">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3625,7 +2769,7 @@
       <c r="Y77" s="3"/>
       <c r="Z77" s="3"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1" spans="1:26">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3653,7 +2797,7 @@
       <c r="Y78" s="3"/>
       <c r="Z78" s="3"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:26">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3681,7 +2825,7 @@
       <c r="Y79" s="3"/>
       <c r="Z79" s="3"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1" spans="1:26">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3709,7 +2853,7 @@
       <c r="Y80" s="3"/>
       <c r="Z80" s="3"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1" spans="1:26">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3737,7 +2881,7 @@
       <c r="Y81" s="3"/>
       <c r="Z81" s="3"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1" spans="1:26">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3765,7 +2909,7 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" spans="1:26">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -3793,7 +2937,7 @@
       <c r="Y83" s="3"/>
       <c r="Z83" s="3"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1" spans="1:26">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3821,7 +2965,7 @@
       <c r="Y84" s="3"/>
       <c r="Z84" s="3"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1" spans="1:26">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3849,7 +2993,7 @@
       <c r="Y85" s="3"/>
       <c r="Z85" s="3"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1" spans="1:26">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3877,7 +3021,7 @@
       <c r="Y86" s="3"/>
       <c r="Z86" s="3"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1" spans="1:26">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3905,7 +3049,7 @@
       <c r="Y87" s="3"/>
       <c r="Z87" s="3"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1" spans="1:26">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3933,7 +3077,7 @@
       <c r="Y88" s="3"/>
       <c r="Z88" s="3"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:26">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3961,7 +3105,7 @@
       <c r="Y89" s="3"/>
       <c r="Z89" s="3"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:26">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3989,7 +3133,7 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1" spans="1:26">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -4017,7 +3161,7 @@
       <c r="Y91" s="3"/>
       <c r="Z91" s="3"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1" spans="1:26">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4045,7 +3189,7 @@
       <c r="Y92" s="3"/>
       <c r="Z92" s="3"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:26">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -4073,7 +3217,7 @@
       <c r="Y93" s="3"/>
       <c r="Z93" s="3"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:26">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -4101,7 +3245,7 @@
       <c r="Y94" s="3"/>
       <c r="Z94" s="3"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1" spans="1:26">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -4129,7 +3273,7 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1" spans="1:26">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -4157,7 +3301,7 @@
       <c r="Y96" s="3"/>
       <c r="Z96" s="3"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:26">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -4185,7 +3329,7 @@
       <c r="Y97" s="3"/>
       <c r="Z97" s="3"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1" spans="1:26">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -4213,7 +3357,7 @@
       <c r="Y98" s="3"/>
       <c r="Z98" s="3"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:26">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -4241,7 +3385,7 @@
       <c r="Y99" s="3"/>
       <c r="Z99" s="3"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1" spans="1:26">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4269,7 +3413,7 @@
       <c r="Y100" s="3"/>
       <c r="Z100" s="3"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1" spans="1:26">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4297,7 +3441,7 @@
       <c r="Y101" s="3"/>
       <c r="Z101" s="3"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1" spans="1:26">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4325,7 +3469,7 @@
       <c r="Y102" s="3"/>
       <c r="Z102" s="3"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1" spans="1:26">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4353,7 +3497,7 @@
       <c r="Y103" s="3"/>
       <c r="Z103" s="3"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1" spans="1:26">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4381,7 +3525,7 @@
       <c r="Y104" s="3"/>
       <c r="Z104" s="3"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1" spans="1:26">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4409,7 +3553,7 @@
       <c r="Y105" s="3"/>
       <c r="Z105" s="3"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1" spans="1:26">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4437,7 +3581,7 @@
       <c r="Y106" s="3"/>
       <c r="Z106" s="3"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1" spans="1:26">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4465,7 +3609,7 @@
       <c r="Y107" s="3"/>
       <c r="Z107" s="3"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:26">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4493,7 +3637,7 @@
       <c r="Y108" s="3"/>
       <c r="Z108" s="3"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1" spans="1:26">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4521,7 +3665,7 @@
       <c r="Y109" s="3"/>
       <c r="Z109" s="3"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1" spans="1:26">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4549,7 +3693,7 @@
       <c r="Y110" s="3"/>
       <c r="Z110" s="3"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1" spans="1:26">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4577,7 +3721,7 @@
       <c r="Y111" s="3"/>
       <c r="Z111" s="3"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1" spans="1:26">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4605,7 +3749,7 @@
       <c r="Y112" s="3"/>
       <c r="Z112" s="3"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1" spans="1:26">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4633,7 +3777,7 @@
       <c r="Y113" s="3"/>
       <c r="Z113" s="3"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1" spans="1:26">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4661,7 +3805,7 @@
       <c r="Y114" s="3"/>
       <c r="Z114" s="3"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1" spans="1:26">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4689,7 +3833,7 @@
       <c r="Y115" s="3"/>
       <c r="Z115" s="3"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1" spans="1:26">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4717,7 +3861,7 @@
       <c r="Y116" s="3"/>
       <c r="Z116" s="3"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1" spans="1:26">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4745,7 +3889,7 @@
       <c r="Y117" s="3"/>
       <c r="Z117" s="3"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1" spans="1:26">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4773,7 +3917,7 @@
       <c r="Y118" s="3"/>
       <c r="Z118" s="3"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1" spans="1:26">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4801,7 +3945,7 @@
       <c r="Y119" s="3"/>
       <c r="Z119" s="3"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:26">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4829,7 +3973,7 @@
       <c r="Y120" s="3"/>
       <c r="Z120" s="3"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:26">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4857,7 +4001,7 @@
       <c r="Y121" s="3"/>
       <c r="Z121" s="3"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1" spans="1:26">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4885,7 +4029,7 @@
       <c r="Y122" s="3"/>
       <c r="Z122" s="3"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:26">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4913,7 +4057,7 @@
       <c r="Y123" s="3"/>
       <c r="Z123" s="3"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1" spans="1:26">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4941,7 +4085,7 @@
       <c r="Y124" s="3"/>
       <c r="Z124" s="3"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:26">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4969,7 +4113,7 @@
       <c r="Y125" s="3"/>
       <c r="Z125" s="3"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1" spans="1:26">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4997,7 +4141,7 @@
       <c r="Y126" s="3"/>
       <c r="Z126" s="3"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1" spans="1:26">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5025,7 +4169,7 @@
       <c r="Y127" s="3"/>
       <c r="Z127" s="3"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1" spans="1:26">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5053,7 +4197,7 @@
       <c r="Y128" s="3"/>
       <c r="Z128" s="3"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1" spans="1:26">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5081,7 +4225,7 @@
       <c r="Y129" s="3"/>
       <c r="Z129" s="3"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1" spans="1:26">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5109,7 +4253,7 @@
       <c r="Y130" s="3"/>
       <c r="Z130" s="3"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1" spans="1:26">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5137,7 +4281,7 @@
       <c r="Y131" s="3"/>
       <c r="Z131" s="3"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1" spans="1:26">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -5165,7 +4309,7 @@
       <c r="Y132" s="3"/>
       <c r="Z132" s="3"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1" spans="1:26">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5193,7 +4337,7 @@
       <c r="Y133" s="3"/>
       <c r="Z133" s="3"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1" spans="1:26">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5221,7 +4365,7 @@
       <c r="Y134" s="3"/>
       <c r="Z134" s="3"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1" spans="1:26">
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5249,7 +4393,7 @@
       <c r="Y135" s="3"/>
       <c r="Z135" s="3"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1" spans="1:26">
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5277,7 +4421,7 @@
       <c r="Y136" s="3"/>
       <c r="Z136" s="3"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1" spans="1:26">
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5305,7 +4449,7 @@
       <c r="Y137" s="3"/>
       <c r="Z137" s="3"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1" spans="1:26">
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5333,7 +4477,7 @@
       <c r="Y138" s="3"/>
       <c r="Z138" s="3"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1" spans="1:26">
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5361,7 +4505,7 @@
       <c r="Y139" s="3"/>
       <c r="Z139" s="3"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1" spans="1:26">
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5389,7 +4533,7 @@
       <c r="Y140" s="3"/>
       <c r="Z140" s="3"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1" spans="1:26">
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5417,7 +4561,7 @@
       <c r="Y141" s="3"/>
       <c r="Z141" s="3"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1" spans="1:26">
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5445,7 +4589,7 @@
       <c r="Y142" s="3"/>
       <c r="Z142" s="3"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1" spans="1:26">
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5473,7 +4617,7 @@
       <c r="Y143" s="3"/>
       <c r="Z143" s="3"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1" spans="1:26">
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5501,7 +4645,7 @@
       <c r="Y144" s="3"/>
       <c r="Z144" s="3"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1" spans="1:26">
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5529,7 +4673,7 @@
       <c r="Y145" s="3"/>
       <c r="Z145" s="3"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1" spans="1:26">
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5557,7 +4701,7 @@
       <c r="Y146" s="3"/>
       <c r="Z146" s="3"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1" spans="1:26">
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5585,7 +4729,7 @@
       <c r="Y147" s="3"/>
       <c r="Z147" s="3"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1" spans="1:26">
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5613,7 +4757,7 @@
       <c r="Y148" s="3"/>
       <c r="Z148" s="3"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1" spans="1:26">
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5641,7 +4785,7 @@
       <c r="Y149" s="3"/>
       <c r="Z149" s="3"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1" spans="1:26">
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5669,7 +4813,7 @@
       <c r="Y150" s="3"/>
       <c r="Z150" s="3"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1" spans="1:26">
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5697,7 +4841,7 @@
       <c r="Y151" s="3"/>
       <c r="Z151" s="3"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:26">
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5725,7 +4869,7 @@
       <c r="Y152" s="3"/>
       <c r="Z152" s="3"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:26">
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5753,7 +4897,7 @@
       <c r="Y153" s="3"/>
       <c r="Z153" s="3"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:26">
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5781,7 +4925,7 @@
       <c r="Y154" s="3"/>
       <c r="Z154" s="3"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1" spans="1:26">
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5809,7 +4953,7 @@
       <c r="Y155" s="3"/>
       <c r="Z155" s="3"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1" spans="1:26">
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5837,7 +4981,7 @@
       <c r="Y156" s="3"/>
       <c r="Z156" s="3"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1" spans="1:26">
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5865,7 +5009,7 @@
       <c r="Y157" s="3"/>
       <c r="Z157" s="3"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:26">
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5893,7 +5037,7 @@
       <c r="Y158" s="3"/>
       <c r="Z158" s="3"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1" spans="1:26">
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5921,7 +5065,7 @@
       <c r="Y159" s="3"/>
       <c r="Z159" s="3"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:26">
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5949,7 +5093,7 @@
       <c r="Y160" s="3"/>
       <c r="Z160" s="3"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1" spans="1:26">
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5977,7 +5121,7 @@
       <c r="Y161" s="3"/>
       <c r="Z161" s="3"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:26">
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -6005,7 +5149,7 @@
       <c r="Y162" s="3"/>
       <c r="Z162" s="3"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1" spans="1:26">
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -6033,7 +5177,7 @@
       <c r="Y163" s="3"/>
       <c r="Z163" s="3"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1" spans="1:26">
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -6061,7 +5205,7 @@
       <c r="Y164" s="3"/>
       <c r="Z164" s="3"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1" spans="1:26">
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -6089,7 +5233,7 @@
       <c r="Y165" s="3"/>
       <c r="Z165" s="3"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1" spans="1:26">
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -6117,7 +5261,7 @@
       <c r="Y166" s="3"/>
       <c r="Z166" s="3"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1" spans="1:26">
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -6145,7 +5289,7 @@
       <c r="Y167" s="3"/>
       <c r="Z167" s="3"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1" spans="1:26">
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -6173,7 +5317,7 @@
       <c r="Y168" s="3"/>
       <c r="Z168" s="3"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1" spans="1:26">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6201,7 +5345,7 @@
       <c r="Y169" s="3"/>
       <c r="Z169" s="3"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1" spans="1:26">
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6229,7 +5373,7 @@
       <c r="Y170" s="3"/>
       <c r="Z170" s="3"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1" spans="1:26">
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6257,7 +5401,7 @@
       <c r="Y171" s="3"/>
       <c r="Z171" s="3"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1" spans="1:26">
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6285,7 +5429,7 @@
       <c r="Y172" s="3"/>
       <c r="Z172" s="3"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1" spans="1:26">
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6313,7 +5457,7 @@
       <c r="Y173" s="3"/>
       <c r="Z173" s="3"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1" spans="1:26">
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6341,7 +5485,7 @@
       <c r="Y174" s="3"/>
       <c r="Z174" s="3"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1" spans="1:26">
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6369,7 +5513,7 @@
       <c r="Y175" s="3"/>
       <c r="Z175" s="3"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1" spans="1:26">
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6397,7 +5541,7 @@
       <c r="Y176" s="3"/>
       <c r="Z176" s="3"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:26">
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6425,7 +5569,7 @@
       <c r="Y177" s="3"/>
       <c r="Z177" s="3"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1" spans="1:26">
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6453,7 +5597,7 @@
       <c r="Y178" s="3"/>
       <c r="Z178" s="3"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:26">
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6481,7 +5625,7 @@
       <c r="Y179" s="3"/>
       <c r="Z179" s="3"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1" spans="1:26">
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6509,7 +5653,7 @@
       <c r="Y180" s="3"/>
       <c r="Z180" s="3"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1" spans="1:26">
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6537,7 +5681,7 @@
       <c r="Y181" s="3"/>
       <c r="Z181" s="3"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1" spans="1:26">
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6565,7 +5709,7 @@
       <c r="Y182" s="3"/>
       <c r="Z182" s="3"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1" spans="1:26">
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6593,7 +5737,7 @@
       <c r="Y183" s="3"/>
       <c r="Z183" s="3"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1" spans="1:26">
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6621,7 +5765,7 @@
       <c r="Y184" s="3"/>
       <c r="Z184" s="3"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:26">
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6649,7 +5793,7 @@
       <c r="Y185" s="3"/>
       <c r="Z185" s="3"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1" spans="1:26">
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6677,7 +5821,7 @@
       <c r="Y186" s="3"/>
       <c r="Z186" s="3"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:26">
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6705,7 +5849,7 @@
       <c r="Y187" s="3"/>
       <c r="Z187" s="3"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1" spans="1:26">
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6733,7 +5877,7 @@
       <c r="Y188" s="3"/>
       <c r="Z188" s="3"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1" spans="1:26">
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6761,7 +5905,7 @@
       <c r="Y189" s="3"/>
       <c r="Z189" s="3"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1" spans="1:26">
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6789,7 +5933,7 @@
       <c r="Y190" s="3"/>
       <c r="Z190" s="3"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1" spans="1:26">
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6817,7 +5961,7 @@
       <c r="Y191" s="3"/>
       <c r="Z191" s="3"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1" spans="1:26">
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6845,7 +5989,7 @@
       <c r="Y192" s="3"/>
       <c r="Z192" s="3"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1" spans="1:26">
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6873,7 +6017,7 @@
       <c r="Y193" s="3"/>
       <c r="Z193" s="3"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1" spans="1:26">
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6901,7 +6045,7 @@
       <c r="Y194" s="3"/>
       <c r="Z194" s="3"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1" spans="1:26">
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6929,7 +6073,7 @@
       <c r="Y195" s="3"/>
       <c r="Z195" s="3"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1" spans="1:26">
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6957,7 +6101,7 @@
       <c r="Y196" s="3"/>
       <c r="Z196" s="3"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1" spans="1:26">
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6985,7 +6129,7 @@
       <c r="Y197" s="3"/>
       <c r="Z197" s="3"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1" spans="1:26">
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -7013,7 +6157,7 @@
       <c r="Y198" s="3"/>
       <c r="Z198" s="3"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1" spans="1:26">
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -7041,7 +6185,7 @@
       <c r="Y199" s="3"/>
       <c r="Z199" s="3"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1" spans="1:26">
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7069,7 +6213,7 @@
       <c r="Y200" s="3"/>
       <c r="Z200" s="3"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1" spans="1:26">
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -7097,7 +6241,7 @@
       <c r="Y201" s="3"/>
       <c r="Z201" s="3"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:26">
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -7125,7 +6269,7 @@
       <c r="Y202" s="3"/>
       <c r="Z202" s="3"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1" spans="1:26">
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7153,7 +6297,7 @@
       <c r="Y203" s="3"/>
       <c r="Z203" s="3"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1" spans="1:26">
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7181,7 +6325,7 @@
       <c r="Y204" s="3"/>
       <c r="Z204" s="3"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1" spans="1:26">
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7209,7 +6353,7 @@
       <c r="Y205" s="3"/>
       <c r="Z205" s="3"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1" spans="1:26">
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7237,7 +6381,7 @@
       <c r="Y206" s="3"/>
       <c r="Z206" s="3"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1" spans="1:26">
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7265,7 +6409,7 @@
       <c r="Y207" s="3"/>
       <c r="Z207" s="3"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1" spans="1:26">
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7293,7 +6437,7 @@
       <c r="Y208" s="3"/>
       <c r="Z208" s="3"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1" spans="1:26">
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7321,7 +6465,7 @@
       <c r="Y209" s="3"/>
       <c r="Z209" s="3"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1" spans="1:26">
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7349,7 +6493,7 @@
       <c r="Y210" s="3"/>
       <c r="Z210" s="3"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1" spans="1:26">
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7377,7 +6521,7 @@
       <c r="Y211" s="3"/>
       <c r="Z211" s="3"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1" spans="1:26">
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7405,7 +6549,7 @@
       <c r="Y212" s="3"/>
       <c r="Z212" s="3"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1" spans="1:26">
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7433,7 +6577,7 @@
       <c r="Y213" s="3"/>
       <c r="Z213" s="3"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1" spans="1:26">
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7461,7 +6605,7 @@
       <c r="Y214" s="3"/>
       <c r="Z214" s="3"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1" spans="1:26">
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7489,7 +6633,7 @@
       <c r="Y215" s="3"/>
       <c r="Z215" s="3"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1" spans="1:26">
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7517,7 +6661,7 @@
       <c r="Y216" s="3"/>
       <c r="Z216" s="3"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1" spans="1:26">
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7545,7 +6689,7 @@
       <c r="Y217" s="3"/>
       <c r="Z217" s="3"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1" spans="1:26">
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7573,7 +6717,7 @@
       <c r="Y218" s="3"/>
       <c r="Z218" s="3"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1" spans="1:26">
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7601,7 +6745,7 @@
       <c r="Y219" s="3"/>
       <c r="Z219" s="3"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1" spans="1:26">
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -8410,8 +7554,9 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
-  </bookViews>
   <sheets>
-    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
+    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <definedNames/>
+  <calcPr/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext uri="GoogleSheetsCustomDataVersion2">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1vHpoHAi14pJrWCrnqynttxKRttNcSH5KaN2SCCJsnE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="65">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -41,9 +30,6 @@
     <t>아이템 종류</t>
   </si>
   <si>
-    <t>아이템 등급</t>
-  </si>
-  <si>
     <t>아이템 무게</t>
   </si>
   <si>
@@ -53,19 +39,7 @@
     <t>아이템 아이콘 경로</t>
   </si>
   <si>
-    <t>아이템 프리팹 경로</t>
-  </si>
-  <si>
-    <t>내구도(Tool)</t>
-  </si>
-  <si>
-    <t>버프종류(Potion)</t>
-  </si>
-  <si>
-    <t>버프량(Potion)</t>
-  </si>
-  <si>
-    <t>버프지속시간(Potion)</t>
+    <t>사용 횟수( -1: 무제한)</t>
   </si>
   <si>
     <t>string</t>
@@ -74,16 +48,13 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>ItemGrade</t>
-  </si>
-  <si>
     <t>float</t>
   </si>
   <si>
     <t>int</t>
   </si>
   <si>
-    <t>BuffType</t>
+    <t>string[]</t>
   </si>
   <si>
     <t>Id</t>
@@ -95,12 +66,6 @@
     <t>Description</t>
   </si>
   <si>
-    <t>CurrentItemType</t>
-  </si>
-  <si>
-    <t>CurrentItemGrade</t>
-  </si>
-  <si>
     <t>Weight</t>
   </si>
   <si>
@@ -110,19 +75,51 @@
     <t>IconPath</t>
   </si>
   <si>
-    <t>PrefabPath</t>
+    <t>ChargeCount</t>
   </si>
   <si>
-    <t>Durability</t>
+    <t>MaterialPaths</t>
   </si>
   <si>
-    <t>CurrentBuffType</t>
+    <t>MeshPath</t>
   </si>
   <si>
-    <t>Value</t>
+    <t>Husks</t>
   </si>
   <si>
-    <t>Duration</t>
+    <t>Item_Tool_MasterKey</t>
+  </si>
+  <si>
+    <t>만능 열쇠</t>
+  </si>
+  <si>
+    <t>잠겨있는 무언가를 열 수 있다.
+여러 번 사용할 수 있다.</t>
+  </si>
+  <si>
+    <t>Tool</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
+  </si>
+  <si>
+    <t>ToolObject</t>
+  </si>
+  <si>
+    <t>Item_Tool_Key</t>
+  </si>
+  <si>
+    <t>열쇠</t>
+  </si>
+  <si>
+    <t>잠겨있는 무언가를 열 수 있다.
+한 번만 사용 할 수 있다.</t>
+  </si>
+  <si>
+    <t>Black</t>
   </si>
   <si>
     <t>Item_Jewel_Diamond</t>
@@ -131,239 +128,131 @@
     <t>다이아몬드</t>
   </si>
   <si>
+    <t>다이아몬드다.</t>
+  </si>
+  <si>
     <t>Jewel</t>
   </si>
   <si>
-    <t>Legendary</t>
+    <t>M_Gemstone_Diamond,Lit</t>
   </si>
   <si>
-    <t>Item_Tool_Bat</t>
+    <t>Jewel_Cone[Cone]</t>
   </si>
   <si>
-    <t>방망이</t>
+    <t>JewelObject</t>
   </si>
   <si>
-    <t>Tool</t>
+    <t>Item_Jewel_Amethyst</t>
   </si>
   <si>
-    <t>Epic</t>
+    <t>자수정</t>
   </si>
   <si>
-    <t>Item_Potion_HealPotion</t>
+    <t>자수정이다.</t>
   </si>
   <si>
-    <t>체력 포션</t>
+    <t>M_Gemstone_Amethyst</t>
   </si>
   <si>
-    <t>Potion</t>
+    <t>Item_Jewel_Aquamarine</t>
   </si>
   <si>
-    <t>Rare</t>
+    <t>아쿠아마린</t>
   </si>
   <si>
-    <t>Hp</t>
+    <t>아쿠아마린이다.</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Aquamarine</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Emerald</t>
+  </si>
+  <si>
+    <t>에메랄드</t>
+  </si>
+  <si>
+    <t>에메랄드다.</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Emerald</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Ruby</t>
+  </si>
+  <si>
+    <t>루비</t>
+  </si>
+  <si>
+    <t>루비다.</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Ruby</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Sapphire</t>
+  </si>
+  <si>
+    <t>사피이어</t>
+  </si>
+  <si>
+    <t>사파이어다.</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Sapphire</t>
+  </si>
+  <si>
+    <t>Item_Jewel_Topaz</t>
+  </si>
+  <si>
+    <t>토파즈</t>
+  </si>
+  <si>
+    <t>토파즈다.</t>
+  </si>
+  <si>
+    <t>M_Gemstone_Topaz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="25">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <fonts count="5">
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="10.0"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="11.0"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="gray125"/>
+      <patternFill patternType="lightGray"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -377,201 +266,9 @@
         <bgColor rgb="FFD2F2DB"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+  <borders count="2">
+    <border/>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -585,545 +282,42 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+  <cellStyleXfs count="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-  </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
-    </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
-    </tableStyle>
-  </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <dxfs count="0"/>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1313,35 +507,31 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1000"/>
-  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.3796296296296" customWidth="1"/>
-    <col min="2" max="2" width="17.1296296296296" customWidth="1"/>
-    <col min="3" max="3" width="44.3796296296296" customWidth="1"/>
-    <col min="4" max="4" width="17.75" customWidth="1"/>
-    <col min="5" max="5" width="19.75" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="27.1296296296296" customWidth="1"/>
-    <col min="9" max="9" width="28.25" customWidth="1"/>
-    <col min="10" max="10" width="14.6296296296296" customWidth="1"/>
-    <col min="11" max="11" width="12.8796296296296" customWidth="1"/>
-    <col min="12" max="12" width="11" customWidth="1"/>
-    <col min="13" max="13" width="17.3796296296296" customWidth="1"/>
-    <col min="14" max="26" width="11" customWidth="1"/>
+    <col customWidth="1" min="1" max="1" width="17.63"/>
+    <col customWidth="1" min="2" max="2" width="15.0"/>
+    <col customWidth="1" min="3" max="3" width="24.25"/>
+    <col customWidth="1" min="4" max="4" width="15.5"/>
+    <col customWidth="1" min="5" max="5" width="11.63"/>
+    <col customWidth="1" min="6" max="6" width="9.63"/>
+    <col customWidth="1" min="7" max="7" width="23.75"/>
+    <col customWidth="1" min="8" max="8" width="14.13"/>
+    <col customWidth="1" min="9" max="9" width="21.25"/>
+    <col customWidth="1" min="10" max="10" width="27.38"/>
+    <col customWidth="1" min="11" max="20" width="9.63"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:26">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1354,7 +544,7 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="3" t="s">
@@ -1366,21 +556,11 @@
       <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>12</v>
-      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
       <c r="P1" s="3"/>
@@ -1388,53 +568,43 @@
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-    </row>
-    <row r="2" ht="13.2" spans="1:26">
+    </row>
+    <row r="2">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>16</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
       <c r="N2" s="3"/>
       <c r="O2" s="3"/>
       <c r="P2" s="3"/>
@@ -1442,53 +612,43 @@
       <c r="R2" s="3"/>
       <c r="S2" s="3"/>
       <c r="T2" s="3"/>
-      <c r="U2" s="3"/>
-      <c r="V2" s="3"/>
-      <c r="W2" s="3"/>
-      <c r="X2" s="3"/>
-      <c r="Y2" s="3"/>
-      <c r="Z2" s="3"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="J3" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="K3" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="K3" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="M3" s="5" t="s">
-        <v>31</v>
-      </c>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
@@ -1496,39 +656,39 @@
       <c r="R3" s="5"/>
       <c r="S3" s="5"/>
       <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-      <c r="G4" s="3">
-        <v>100</v>
-      </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
+        <v>26</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>100000.0</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
@@ -1538,41 +698,39 @@
       <c r="R4" s="3"/>
       <c r="S4" s="3"/>
       <c r="T4" s="3"/>
-      <c r="U4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
-      <c r="Y4" s="3"/>
-      <c r="Z4" s="3"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
+      </c>
+      <c r="E5" s="3">
+        <v>1.0</v>
       </c>
       <c r="F5" s="3">
-        <v>10</v>
-      </c>
-      <c r="G5" s="3">
-        <v>30</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>100</v>
-      </c>
-      <c r="K5" s="3"/>
+        <v>30.0</v>
+      </c>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>29</v>
+      </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -1582,47 +740,39 @@
       <c r="R5" s="3"/>
       <c r="S5" s="3"/>
       <c r="T5" s="3"/>
-      <c r="U5" s="3"/>
-      <c r="V5" s="3"/>
-      <c r="W5" s="3"/>
-      <c r="X5" s="3"/>
-      <c r="Y5" s="3"/>
-      <c r="Z5" s="3"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A6" s="1" t="s">
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1000.0</v>
+      </c>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F6" s="3">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L6" s="3">
-        <v>50</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
       <c r="P6" s="3"/>
@@ -1630,25 +780,37 @@
       <c r="R6" s="3"/>
       <c r="S6" s="3"/>
       <c r="T6" s="3"/>
-      <c r="U6" s="3"/>
-      <c r="V6" s="3"/>
-      <c r="W6" s="3"/>
-      <c r="X6" s="3"/>
-      <c r="Y6" s="3"/>
-      <c r="Z6" s="3"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
-      <c r="C7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>800.0</v>
+      </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
+      <c r="I7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L7" s="3"/>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
@@ -1658,25 +820,37 @@
       <c r="R7" s="3"/>
       <c r="S7" s="3"/>
       <c r="T7" s="3"/>
-      <c r="U7" s="3"/>
-      <c r="V7" s="3"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="3"/>
-      <c r="Y7" s="3"/>
-      <c r="Z7" s="3"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
-      <c r="C8" s="1"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F8" s="3">
+        <v>700.0</v>
+      </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L8" s="3"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3"/>
@@ -1686,25 +860,37 @@
       <c r="R8" s="3"/>
       <c r="S8" s="3"/>
       <c r="T8" s="3"/>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="3"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1">
+      <c r="A9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>600.0</v>
+      </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L9" s="3"/>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
@@ -1714,25 +900,37 @@
       <c r="R9" s="3"/>
       <c r="S9" s="3"/>
       <c r="T9" s="3"/>
-      <c r="U9" s="3"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="3"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F10" s="3">
+        <v>500.0</v>
+      </c>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L10" s="3"/>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
@@ -1742,25 +940,37 @@
       <c r="R10" s="3"/>
       <c r="S10" s="3"/>
       <c r="T10" s="3"/>
-      <c r="U10" s="3"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
-      <c r="X10" s="3"/>
-      <c r="Y10" s="3"/>
-      <c r="Z10" s="3"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1">
+      <c r="A11" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="F11" s="3">
+        <v>400.0</v>
+      </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
+      <c r="I11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
@@ -1770,25 +980,37 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-      <c r="U11" s="3"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
-      <c r="X11" s="3"/>
-      <c r="Y11" s="3"/>
-      <c r="Z11" s="3"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:26">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
-      <c r="C12" s="1"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>300.0</v>
+      </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>40</v>
+      </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
@@ -1798,14 +1020,8 @@
       <c r="R12" s="3"/>
       <c r="S12" s="3"/>
       <c r="T12" s="3"/>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1826,14 +1042,8 @@
       <c r="R13" s="3"/>
       <c r="S13" s="3"/>
       <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1854,14 +1064,8 @@
       <c r="R14" s="3"/>
       <c r="S14" s="3"/>
       <c r="T14" s="3"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1882,14 +1086,8 @@
       <c r="R15" s="3"/>
       <c r="S15" s="3"/>
       <c r="T15" s="3"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -1910,14 +1108,8 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -1938,14 +1130,8 @@
       <c r="R17" s="3"/>
       <c r="S17" s="3"/>
       <c r="T17" s="3"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1966,14 +1152,8 @@
       <c r="R18" s="3"/>
       <c r="S18" s="3"/>
       <c r="T18" s="3"/>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1994,14 +1174,8 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -2022,14 +1196,8 @@
       <c r="R20" s="3"/>
       <c r="S20" s="3"/>
       <c r="T20" s="3"/>
-      <c r="U20" s="3"/>
-      <c r="V20" s="3"/>
-      <c r="W20" s="3"/>
-      <c r="X20" s="3"/>
-      <c r="Y20" s="3"/>
-      <c r="Z20" s="3"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -2050,14 +1218,8 @@
       <c r="R21" s="3"/>
       <c r="S21" s="3"/>
       <c r="T21" s="3"/>
-      <c r="U21" s="3"/>
-      <c r="V21" s="3"/>
-      <c r="W21" s="3"/>
-      <c r="X21" s="3"/>
-      <c r="Y21" s="3"/>
-      <c r="Z21" s="3"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -2078,14 +1240,8 @@
       <c r="R22" s="3"/>
       <c r="S22" s="3"/>
       <c r="T22" s="3"/>
-      <c r="U22" s="3"/>
-      <c r="V22" s="3"/>
-      <c r="W22" s="3"/>
-      <c r="X22" s="3"/>
-      <c r="Y22" s="3"/>
-      <c r="Z22" s="3"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -2106,14 +1262,8 @@
       <c r="R23" s="3"/>
       <c r="S23" s="3"/>
       <c r="T23" s="3"/>
-      <c r="U23" s="3"/>
-      <c r="V23" s="3"/>
-      <c r="W23" s="3"/>
-      <c r="X23" s="3"/>
-      <c r="Y23" s="3"/>
-      <c r="Z23" s="3"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -2134,14 +1284,8 @@
       <c r="R24" s="3"/>
       <c r="S24" s="3"/>
       <c r="T24" s="3"/>
-      <c r="U24" s="3"/>
-      <c r="V24" s="3"/>
-      <c r="W24" s="3"/>
-      <c r="X24" s="3"/>
-      <c r="Y24" s="3"/>
-      <c r="Z24" s="3"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3"/>
@@ -2162,14 +1306,8 @@
       <c r="R25" s="3"/>
       <c r="S25" s="3"/>
       <c r="T25" s="3"/>
-      <c r="U25" s="3"/>
-      <c r="V25" s="3"/>
-      <c r="W25" s="3"/>
-      <c r="X25" s="3"/>
-      <c r="Y25" s="3"/>
-      <c r="Z25" s="3"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="3"/>
@@ -2190,14 +1328,8 @@
       <c r="R26" s="3"/>
       <c r="S26" s="3"/>
       <c r="T26" s="3"/>
-      <c r="U26" s="3"/>
-      <c r="V26" s="3"/>
-      <c r="W26" s="3"/>
-      <c r="X26" s="3"/>
-      <c r="Y26" s="3"/>
-      <c r="Z26" s="3"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3"/>
@@ -2218,14 +1350,8 @@
       <c r="R27" s="3"/>
       <c r="S27" s="3"/>
       <c r="T27" s="3"/>
-      <c r="U27" s="3"/>
-      <c r="V27" s="3"/>
-      <c r="W27" s="3"/>
-      <c r="X27" s="3"/>
-      <c r="Y27" s="3"/>
-      <c r="Z27" s="3"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="3"/>
@@ -2246,14 +1372,8 @@
       <c r="R28" s="3"/>
       <c r="S28" s="3"/>
       <c r="T28" s="3"/>
-      <c r="U28" s="3"/>
-      <c r="V28" s="3"/>
-      <c r="W28" s="3"/>
-      <c r="X28" s="3"/>
-      <c r="Y28" s="3"/>
-      <c r="Z28" s="3"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3"/>
@@ -2274,14 +1394,8 @@
       <c r="R29" s="3"/>
       <c r="S29" s="3"/>
       <c r="T29" s="3"/>
-      <c r="U29" s="3"/>
-      <c r="V29" s="3"/>
-      <c r="W29" s="3"/>
-      <c r="X29" s="3"/>
-      <c r="Y29" s="3"/>
-      <c r="Z29" s="3"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="3"/>
@@ -2302,14 +1416,8 @@
       <c r="R30" s="3"/>
       <c r="S30" s="3"/>
       <c r="T30" s="3"/>
-      <c r="U30" s="3"/>
-      <c r="V30" s="3"/>
-      <c r="W30" s="3"/>
-      <c r="X30" s="3"/>
-      <c r="Y30" s="3"/>
-      <c r="Z30" s="3"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="3"/>
@@ -2330,14 +1438,8 @@
       <c r="R31" s="3"/>
       <c r="S31" s="3"/>
       <c r="T31" s="3"/>
-      <c r="U31" s="3"/>
-      <c r="V31" s="3"/>
-      <c r="W31" s="3"/>
-      <c r="X31" s="3"/>
-      <c r="Y31" s="3"/>
-      <c r="Z31" s="3"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3"/>
@@ -2358,14 +1460,8 @@
       <c r="R32" s="3"/>
       <c r="S32" s="3"/>
       <c r="T32" s="3"/>
-      <c r="U32" s="3"/>
-      <c r="V32" s="3"/>
-      <c r="W32" s="3"/>
-      <c r="X32" s="3"/>
-      <c r="Y32" s="3"/>
-      <c r="Z32" s="3"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2386,14 +1482,8 @@
       <c r="R33" s="3"/>
       <c r="S33" s="3"/>
       <c r="T33" s="3"/>
-      <c r="U33" s="3"/>
-      <c r="V33" s="3"/>
-      <c r="W33" s="3"/>
-      <c r="X33" s="3"/>
-      <c r="Y33" s="3"/>
-      <c r="Z33" s="3"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3"/>
@@ -2414,14 +1504,8 @@
       <c r="R34" s="3"/>
       <c r="S34" s="3"/>
       <c r="T34" s="3"/>
-      <c r="U34" s="3"/>
-      <c r="V34" s="3"/>
-      <c r="W34" s="3"/>
-      <c r="X34" s="3"/>
-      <c r="Y34" s="3"/>
-      <c r="Z34" s="3"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -2442,14 +1526,8 @@
       <c r="R35" s="3"/>
       <c r="S35" s="3"/>
       <c r="T35" s="3"/>
-      <c r="U35" s="3"/>
-      <c r="V35" s="3"/>
-      <c r="W35" s="3"/>
-      <c r="X35" s="3"/>
-      <c r="Y35" s="3"/>
-      <c r="Z35" s="3"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2470,14 +1548,8 @@
       <c r="R36" s="3"/>
       <c r="S36" s="3"/>
       <c r="T36" s="3"/>
-      <c r="U36" s="3"/>
-      <c r="V36" s="3"/>
-      <c r="W36" s="3"/>
-      <c r="X36" s="3"/>
-      <c r="Y36" s="3"/>
-      <c r="Z36" s="3"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -2498,14 +1570,8 @@
       <c r="R37" s="3"/>
       <c r="S37" s="3"/>
       <c r="T37" s="3"/>
-      <c r="U37" s="3"/>
-      <c r="V37" s="3"/>
-      <c r="W37" s="3"/>
-      <c r="X37" s="3"/>
-      <c r="Y37" s="3"/>
-      <c r="Z37" s="3"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -2526,14 +1592,8 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
       <c r="T38" s="3"/>
-      <c r="U38" s="3"/>
-      <c r="V38" s="3"/>
-      <c r="W38" s="3"/>
-      <c r="X38" s="3"/>
-      <c r="Y38" s="3"/>
-      <c r="Z38" s="3"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2554,14 +1614,8 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-      <c r="U39" s="3"/>
-      <c r="V39" s="3"/>
-      <c r="W39" s="3"/>
-      <c r="X39" s="3"/>
-      <c r="Y39" s="3"/>
-      <c r="Z39" s="3"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -2582,14 +1636,8 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-      <c r="U40" s="3"/>
-      <c r="V40" s="3"/>
-      <c r="W40" s="3"/>
-      <c r="X40" s="3"/>
-      <c r="Y40" s="3"/>
-      <c r="Z40" s="3"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -2610,14 +1658,8 @@
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
       <c r="T41" s="3"/>
-      <c r="U41" s="3"/>
-      <c r="V41" s="3"/>
-      <c r="W41" s="3"/>
-      <c r="X41" s="3"/>
-      <c r="Y41" s="3"/>
-      <c r="Z41" s="3"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2638,14 +1680,8 @@
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
       <c r="T42" s="3"/>
-      <c r="U42" s="3"/>
-      <c r="V42" s="3"/>
-      <c r="W42" s="3"/>
-      <c r="X42" s="3"/>
-      <c r="Y42" s="3"/>
-      <c r="Z42" s="3"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -2666,14 +1702,8 @@
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
       <c r="T43" s="3"/>
-      <c r="U43" s="3"/>
-      <c r="V43" s="3"/>
-      <c r="W43" s="3"/>
-      <c r="X43" s="3"/>
-      <c r="Y43" s="3"/>
-      <c r="Z43" s="3"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -2694,14 +1724,8 @@
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
       <c r="T44" s="3"/>
-      <c r="U44" s="3"/>
-      <c r="V44" s="3"/>
-      <c r="W44" s="3"/>
-      <c r="X44" s="3"/>
-      <c r="Y44" s="3"/>
-      <c r="Z44" s="3"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -2722,14 +1746,8 @@
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
       <c r="T45" s="3"/>
-      <c r="U45" s="3"/>
-      <c r="V45" s="3"/>
-      <c r="W45" s="3"/>
-      <c r="X45" s="3"/>
-      <c r="Y45" s="3"/>
-      <c r="Z45" s="3"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -2750,14 +1768,8 @@
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
       <c r="T46" s="3"/>
-      <c r="U46" s="3"/>
-      <c r="V46" s="3"/>
-      <c r="W46" s="3"/>
-      <c r="X46" s="3"/>
-      <c r="Y46" s="3"/>
-      <c r="Z46" s="3"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -2778,14 +1790,8 @@
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
       <c r="T47" s="3"/>
-      <c r="U47" s="3"/>
-      <c r="V47" s="3"/>
-      <c r="W47" s="3"/>
-      <c r="X47" s="3"/>
-      <c r="Y47" s="3"/>
-      <c r="Z47" s="3"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2806,14 +1812,8 @@
       <c r="R48" s="3"/>
       <c r="S48" s="3"/>
       <c r="T48" s="3"/>
-      <c r="U48" s="3"/>
-      <c r="V48" s="3"/>
-      <c r="W48" s="3"/>
-      <c r="X48" s="3"/>
-      <c r="Y48" s="3"/>
-      <c r="Z48" s="3"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2834,14 +1834,8 @@
       <c r="R49" s="3"/>
       <c r="S49" s="3"/>
       <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-      <c r="X49" s="3"/>
-      <c r="Y49" s="3"/>
-      <c r="Z49" s="3"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2862,14 +1856,8 @@
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
       <c r="T50" s="3"/>
-      <c r="U50" s="3"/>
-      <c r="V50" s="3"/>
-      <c r="W50" s="3"/>
-      <c r="X50" s="3"/>
-      <c r="Y50" s="3"/>
-      <c r="Z50" s="3"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2890,14 +1878,8 @@
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
       <c r="T51" s="3"/>
-      <c r="U51" s="3"/>
-      <c r="V51" s="3"/>
-      <c r="W51" s="3"/>
-      <c r="X51" s="3"/>
-      <c r="Y51" s="3"/>
-      <c r="Z51" s="3"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2918,14 +1900,8 @@
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
       <c r="T52" s="3"/>
-      <c r="U52" s="3"/>
-      <c r="V52" s="3"/>
-      <c r="W52" s="3"/>
-      <c r="X52" s="3"/>
-      <c r="Y52" s="3"/>
-      <c r="Z52" s="3"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2946,14 +1922,8 @@
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
       <c r="T53" s="3"/>
-      <c r="U53" s="3"/>
-      <c r="V53" s="3"/>
-      <c r="W53" s="3"/>
-      <c r="X53" s="3"/>
-      <c r="Y53" s="3"/>
-      <c r="Z53" s="3"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2974,14 +1944,8 @@
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
       <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-      <c r="V54" s="3"/>
-      <c r="W54" s="3"/>
-      <c r="X54" s="3"/>
-      <c r="Y54" s="3"/>
-      <c r="Z54" s="3"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -3002,14 +1966,8 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-      <c r="V55" s="3"/>
-      <c r="W55" s="3"/>
-      <c r="X55" s="3"/>
-      <c r="Y55" s="3"/>
-      <c r="Z55" s="3"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -3030,14 +1988,8 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-      <c r="V56" s="3"/>
-      <c r="W56" s="3"/>
-      <c r="X56" s="3"/>
-      <c r="Y56" s="3"/>
-      <c r="Z56" s="3"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3058,14 +2010,8 @@
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
       <c r="T57" s="3"/>
-      <c r="U57" s="3"/>
-      <c r="V57" s="3"/>
-      <c r="W57" s="3"/>
-      <c r="X57" s="3"/>
-      <c r="Y57" s="3"/>
-      <c r="Z57" s="3"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -3086,14 +2032,8 @@
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
       <c r="T58" s="3"/>
-      <c r="U58" s="3"/>
-      <c r="V58" s="3"/>
-      <c r="W58" s="3"/>
-      <c r="X58" s="3"/>
-      <c r="Y58" s="3"/>
-      <c r="Z58" s="3"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -3114,14 +2054,8 @@
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
       <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-      <c r="X59" s="3"/>
-      <c r="Y59" s="3"/>
-      <c r="Z59" s="3"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3142,14 +2076,8 @@
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
       <c r="T60" s="3"/>
-      <c r="U60" s="3"/>
-      <c r="V60" s="3"/>
-      <c r="W60" s="3"/>
-      <c r="X60" s="3"/>
-      <c r="Y60" s="3"/>
-      <c r="Z60" s="3"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3170,14 +2098,8 @@
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
       <c r="T61" s="3"/>
-      <c r="U61" s="3"/>
-      <c r="V61" s="3"/>
-      <c r="W61" s="3"/>
-      <c r="X61" s="3"/>
-      <c r="Y61" s="3"/>
-      <c r="Z61" s="3"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3198,14 +2120,8 @@
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
       <c r="T62" s="3"/>
-      <c r="U62" s="3"/>
-      <c r="V62" s="3"/>
-      <c r="W62" s="3"/>
-      <c r="X62" s="3"/>
-      <c r="Y62" s="3"/>
-      <c r="Z62" s="3"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3226,14 +2142,8 @@
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
       <c r="T63" s="3"/>
-      <c r="U63" s="3"/>
-      <c r="V63" s="3"/>
-      <c r="W63" s="3"/>
-      <c r="X63" s="3"/>
-      <c r="Y63" s="3"/>
-      <c r="Z63" s="3"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3254,14 +2164,8 @@
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
       <c r="T64" s="3"/>
-      <c r="U64" s="3"/>
-      <c r="V64" s="3"/>
-      <c r="W64" s="3"/>
-      <c r="X64" s="3"/>
-      <c r="Y64" s="3"/>
-      <c r="Z64" s="3"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -3282,14 +2186,8 @@
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
       <c r="T65" s="3"/>
-      <c r="U65" s="3"/>
-      <c r="V65" s="3"/>
-      <c r="W65" s="3"/>
-      <c r="X65" s="3"/>
-      <c r="Y65" s="3"/>
-      <c r="Z65" s="3"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -3310,14 +2208,8 @@
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
       <c r="T66" s="3"/>
-      <c r="U66" s="3"/>
-      <c r="V66" s="3"/>
-      <c r="W66" s="3"/>
-      <c r="X66" s="3"/>
-      <c r="Y66" s="3"/>
-      <c r="Z66" s="3"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -3338,14 +2230,8 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-      <c r="X67" s="3"/>
-      <c r="Y67" s="3"/>
-      <c r="Z67" s="3"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -3366,14 +2252,8 @@
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
       <c r="T68" s="3"/>
-      <c r="U68" s="3"/>
-      <c r="V68" s="3"/>
-      <c r="W68" s="3"/>
-      <c r="X68" s="3"/>
-      <c r="Y68" s="3"/>
-      <c r="Z68" s="3"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -3394,14 +2274,8 @@
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
       <c r="T69" s="3"/>
-      <c r="U69" s="3"/>
-      <c r="V69" s="3"/>
-      <c r="W69" s="3"/>
-      <c r="X69" s="3"/>
-      <c r="Y69" s="3"/>
-      <c r="Z69" s="3"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -3422,14 +2296,8 @@
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
       <c r="T70" s="3"/>
-      <c r="U70" s="3"/>
-      <c r="V70" s="3"/>
-      <c r="W70" s="3"/>
-      <c r="X70" s="3"/>
-      <c r="Y70" s="3"/>
-      <c r="Z70" s="3"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -3450,14 +2318,8 @@
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
       <c r="T71" s="3"/>
-      <c r="U71" s="3"/>
-      <c r="V71" s="3"/>
-      <c r="W71" s="3"/>
-      <c r="X71" s="3"/>
-      <c r="Y71" s="3"/>
-      <c r="Z71" s="3"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -3478,14 +2340,8 @@
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
       <c r="T72" s="3"/>
-      <c r="U72" s="3"/>
-      <c r="V72" s="3"/>
-      <c r="W72" s="3"/>
-      <c r="X72" s="3"/>
-      <c r="Y72" s="3"/>
-      <c r="Z72" s="3"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -3506,14 +2362,8 @@
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
       <c r="T73" s="3"/>
-      <c r="U73" s="3"/>
-      <c r="V73" s="3"/>
-      <c r="W73" s="3"/>
-      <c r="X73" s="3"/>
-      <c r="Y73" s="3"/>
-      <c r="Z73" s="3"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -3534,14 +2384,8 @@
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
       <c r="T74" s="3"/>
-      <c r="U74" s="3"/>
-      <c r="V74" s="3"/>
-      <c r="W74" s="3"/>
-      <c r="X74" s="3"/>
-      <c r="Y74" s="3"/>
-      <c r="Z74" s="3"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -3562,14 +2406,8 @@
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
       <c r="T75" s="3"/>
-      <c r="U75" s="3"/>
-      <c r="V75" s="3"/>
-      <c r="W75" s="3"/>
-      <c r="X75" s="3"/>
-      <c r="Y75" s="3"/>
-      <c r="Z75" s="3"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -3590,14 +2428,8 @@
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
       <c r="T76" s="3"/>
-      <c r="U76" s="3"/>
-      <c r="V76" s="3"/>
-      <c r="W76" s="3"/>
-      <c r="X76" s="3"/>
-      <c r="Y76" s="3"/>
-      <c r="Z76" s="3"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -3618,14 +2450,8 @@
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
       <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-      <c r="X77" s="3"/>
-      <c r="Y77" s="3"/>
-      <c r="Z77" s="3"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -3646,14 +2472,8 @@
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
       <c r="T78" s="3"/>
-      <c r="U78" s="3"/>
-      <c r="V78" s="3"/>
-      <c r="W78" s="3"/>
-      <c r="X78" s="3"/>
-      <c r="Y78" s="3"/>
-      <c r="Z78" s="3"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -3674,14 +2494,8 @@
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
       <c r="T79" s="3"/>
-      <c r="U79" s="3"/>
-      <c r="V79" s="3"/>
-      <c r="W79" s="3"/>
-      <c r="X79" s="3"/>
-      <c r="Y79" s="3"/>
-      <c r="Z79" s="3"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3702,14 +2516,8 @@
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
       <c r="T80" s="3"/>
-      <c r="U80" s="3"/>
-      <c r="V80" s="3"/>
-      <c r="W80" s="3"/>
-      <c r="X80" s="3"/>
-      <c r="Y80" s="3"/>
-      <c r="Z80" s="3"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -3730,14 +2538,8 @@
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
       <c r="T81" s="3"/>
-      <c r="U81" s="3"/>
-      <c r="V81" s="3"/>
-      <c r="W81" s="3"/>
-      <c r="X81" s="3"/>
-      <c r="Y81" s="3"/>
-      <c r="Z81" s="3"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -3758,14 +2560,8 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-      <c r="U82" s="3"/>
-      <c r="V82" s="3"/>
-      <c r="W82" s="3"/>
-      <c r="X82" s="3"/>
-      <c r="Y82" s="3"/>
-      <c r="Z82" s="3"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -3786,14 +2582,8 @@
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
       <c r="T83" s="3"/>
-      <c r="U83" s="3"/>
-      <c r="V83" s="3"/>
-      <c r="W83" s="3"/>
-      <c r="X83" s="3"/>
-      <c r="Y83" s="3"/>
-      <c r="Z83" s="3"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -3814,14 +2604,8 @@
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
       <c r="T84" s="3"/>
-      <c r="U84" s="3"/>
-      <c r="V84" s="3"/>
-      <c r="W84" s="3"/>
-      <c r="X84" s="3"/>
-      <c r="Y84" s="3"/>
-      <c r="Z84" s="3"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -3842,14 +2626,8 @@
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
       <c r="T85" s="3"/>
-      <c r="U85" s="3"/>
-      <c r="V85" s="3"/>
-      <c r="W85" s="3"/>
-      <c r="X85" s="3"/>
-      <c r="Y85" s="3"/>
-      <c r="Z85" s="3"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -3870,14 +2648,8 @@
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
       <c r="T86" s="3"/>
-      <c r="U86" s="3"/>
-      <c r="V86" s="3"/>
-      <c r="W86" s="3"/>
-      <c r="X86" s="3"/>
-      <c r="Y86" s="3"/>
-      <c r="Z86" s="3"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -3898,14 +2670,8 @@
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
       <c r="T87" s="3"/>
-      <c r="U87" s="3"/>
-      <c r="V87" s="3"/>
-      <c r="W87" s="3"/>
-      <c r="X87" s="3"/>
-      <c r="Y87" s="3"/>
-      <c r="Z87" s="3"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -3926,14 +2692,8 @@
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
       <c r="T88" s="3"/>
-      <c r="U88" s="3"/>
-      <c r="V88" s="3"/>
-      <c r="W88" s="3"/>
-      <c r="X88" s="3"/>
-      <c r="Y88" s="3"/>
-      <c r="Z88" s="3"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -3954,14 +2714,8 @@
       <c r="R89" s="3"/>
       <c r="S89" s="3"/>
       <c r="T89" s="3"/>
-      <c r="U89" s="3"/>
-      <c r="V89" s="3"/>
-      <c r="W89" s="3"/>
-      <c r="X89" s="3"/>
-      <c r="Y89" s="3"/>
-      <c r="Z89" s="3"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -3982,14 +2736,8 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-      <c r="U90" s="3"/>
-      <c r="V90" s="3"/>
-      <c r="W90" s="3"/>
-      <c r="X90" s="3"/>
-      <c r="Y90" s="3"/>
-      <c r="Z90" s="3"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -4010,14 +2758,8 @@
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
       <c r="T91" s="3"/>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4038,14 +2780,8 @@
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
       <c r="T92" s="3"/>
-      <c r="U92" s="3"/>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="3"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -4066,14 +2802,8 @@
       <c r="R93" s="3"/>
       <c r="S93" s="3"/>
       <c r="T93" s="3"/>
-      <c r="U93" s="3"/>
-      <c r="V93" s="3"/>
-      <c r="W93" s="3"/>
-      <c r="X93" s="3"/>
-      <c r="Y93" s="3"/>
-      <c r="Z93" s="3"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -4094,14 +2824,8 @@
       <c r="R94" s="3"/>
       <c r="S94" s="3"/>
       <c r="T94" s="3"/>
-      <c r="U94" s="3"/>
-      <c r="V94" s="3"/>
-      <c r="W94" s="3"/>
-      <c r="X94" s="3"/>
-      <c r="Y94" s="3"/>
-      <c r="Z94" s="3"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -4122,14 +2846,8 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-      <c r="U95" s="3"/>
-      <c r="V95" s="3"/>
-      <c r="W95" s="3"/>
-      <c r="X95" s="3"/>
-      <c r="Y95" s="3"/>
-      <c r="Z95" s="3"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -4150,14 +2868,8 @@
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
       <c r="T96" s="3"/>
-      <c r="U96" s="3"/>
-      <c r="V96" s="3"/>
-      <c r="W96" s="3"/>
-      <c r="X96" s="3"/>
-      <c r="Y96" s="3"/>
-      <c r="Z96" s="3"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -4178,14 +2890,8 @@
       <c r="R97" s="3"/>
       <c r="S97" s="3"/>
       <c r="T97" s="3"/>
-      <c r="U97" s="3"/>
-      <c r="V97" s="3"/>
-      <c r="W97" s="3"/>
-      <c r="X97" s="3"/>
-      <c r="Y97" s="3"/>
-      <c r="Z97" s="3"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -4206,14 +2912,8 @@
       <c r="R98" s="3"/>
       <c r="S98" s="3"/>
       <c r="T98" s="3"/>
-      <c r="U98" s="3"/>
-      <c r="V98" s="3"/>
-      <c r="W98" s="3"/>
-      <c r="X98" s="3"/>
-      <c r="Y98" s="3"/>
-      <c r="Z98" s="3"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -4234,14 +2934,8 @@
       <c r="R99" s="3"/>
       <c r="S99" s="3"/>
       <c r="T99" s="3"/>
-      <c r="U99" s="3"/>
-      <c r="V99" s="3"/>
-      <c r="W99" s="3"/>
-      <c r="X99" s="3"/>
-      <c r="Y99" s="3"/>
-      <c r="Z99" s="3"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -4262,14 +2956,8 @@
       <c r="R100" s="3"/>
       <c r="S100" s="3"/>
       <c r="T100" s="3"/>
-      <c r="U100" s="3"/>
-      <c r="V100" s="3"/>
-      <c r="W100" s="3"/>
-      <c r="X100" s="3"/>
-      <c r="Y100" s="3"/>
-      <c r="Z100" s="3"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -4290,14 +2978,8 @@
       <c r="R101" s="3"/>
       <c r="S101" s="3"/>
       <c r="T101" s="3"/>
-      <c r="U101" s="3"/>
-      <c r="V101" s="3"/>
-      <c r="W101" s="3"/>
-      <c r="X101" s="3"/>
-      <c r="Y101" s="3"/>
-      <c r="Z101" s="3"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -4318,14 +3000,8 @@
       <c r="R102" s="3"/>
       <c r="S102" s="3"/>
       <c r="T102" s="3"/>
-      <c r="U102" s="3"/>
-      <c r="V102" s="3"/>
-      <c r="W102" s="3"/>
-      <c r="X102" s="3"/>
-      <c r="Y102" s="3"/>
-      <c r="Z102" s="3"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -4346,14 +3022,8 @@
       <c r="R103" s="3"/>
       <c r="S103" s="3"/>
       <c r="T103" s="3"/>
-      <c r="U103" s="3"/>
-      <c r="V103" s="3"/>
-      <c r="W103" s="3"/>
-      <c r="X103" s="3"/>
-      <c r="Y103" s="3"/>
-      <c r="Z103" s="3"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -4374,14 +3044,8 @@
       <c r="R104" s="3"/>
       <c r="S104" s="3"/>
       <c r="T104" s="3"/>
-      <c r="U104" s="3"/>
-      <c r="V104" s="3"/>
-      <c r="W104" s="3"/>
-      <c r="X104" s="3"/>
-      <c r="Y104" s="3"/>
-      <c r="Z104" s="3"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -4402,14 +3066,8 @@
       <c r="R105" s="3"/>
       <c r="S105" s="3"/>
       <c r="T105" s="3"/>
-      <c r="U105" s="3"/>
-      <c r="V105" s="3"/>
-      <c r="W105" s="3"/>
-      <c r="X105" s="3"/>
-      <c r="Y105" s="3"/>
-      <c r="Z105" s="3"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -4430,14 +3088,8 @@
       <c r="R106" s="3"/>
       <c r="S106" s="3"/>
       <c r="T106" s="3"/>
-      <c r="U106" s="3"/>
-      <c r="V106" s="3"/>
-      <c r="W106" s="3"/>
-      <c r="X106" s="3"/>
-      <c r="Y106" s="3"/>
-      <c r="Z106" s="3"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -4458,14 +3110,8 @@
       <c r="R107" s="3"/>
       <c r="S107" s="3"/>
       <c r="T107" s="3"/>
-      <c r="U107" s="3"/>
-      <c r="V107" s="3"/>
-      <c r="W107" s="3"/>
-      <c r="X107" s="3"/>
-      <c r="Y107" s="3"/>
-      <c r="Z107" s="3"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -4486,14 +3132,8 @@
       <c r="R108" s="3"/>
       <c r="S108" s="3"/>
       <c r="T108" s="3"/>
-      <c r="U108" s="3"/>
-      <c r="V108" s="3"/>
-      <c r="W108" s="3"/>
-      <c r="X108" s="3"/>
-      <c r="Y108" s="3"/>
-      <c r="Z108" s="3"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -4514,14 +3154,8 @@
       <c r="R109" s="3"/>
       <c r="S109" s="3"/>
       <c r="T109" s="3"/>
-      <c r="U109" s="3"/>
-      <c r="V109" s="3"/>
-      <c r="W109" s="3"/>
-      <c r="X109" s="3"/>
-      <c r="Y109" s="3"/>
-      <c r="Z109" s="3"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -4542,14 +3176,8 @@
       <c r="R110" s="3"/>
       <c r="S110" s="3"/>
       <c r="T110" s="3"/>
-      <c r="U110" s="3"/>
-      <c r="V110" s="3"/>
-      <c r="W110" s="3"/>
-      <c r="X110" s="3"/>
-      <c r="Y110" s="3"/>
-      <c r="Z110" s="3"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -4570,14 +3198,8 @@
       <c r="R111" s="3"/>
       <c r="S111" s="3"/>
       <c r="T111" s="3"/>
-      <c r="U111" s="3"/>
-      <c r="V111" s="3"/>
-      <c r="W111" s="3"/>
-      <c r="X111" s="3"/>
-      <c r="Y111" s="3"/>
-      <c r="Z111" s="3"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -4598,14 +3220,8 @@
       <c r="R112" s="3"/>
       <c r="S112" s="3"/>
       <c r="T112" s="3"/>
-      <c r="U112" s="3"/>
-      <c r="V112" s="3"/>
-      <c r="W112" s="3"/>
-      <c r="X112" s="3"/>
-      <c r="Y112" s="3"/>
-      <c r="Z112" s="3"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="3"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -4626,14 +3242,8 @@
       <c r="R113" s="3"/>
       <c r="S113" s="3"/>
       <c r="T113" s="3"/>
-      <c r="U113" s="3"/>
-      <c r="V113" s="3"/>
-      <c r="W113" s="3"/>
-      <c r="X113" s="3"/>
-      <c r="Y113" s="3"/>
-      <c r="Z113" s="3"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="3"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -4654,14 +3264,8 @@
       <c r="R114" s="3"/>
       <c r="S114" s="3"/>
       <c r="T114" s="3"/>
-      <c r="U114" s="3"/>
-      <c r="V114" s="3"/>
-      <c r="W114" s="3"/>
-      <c r="X114" s="3"/>
-      <c r="Y114" s="3"/>
-      <c r="Z114" s="3"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="3"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -4682,14 +3286,8 @@
       <c r="R115" s="3"/>
       <c r="S115" s="3"/>
       <c r="T115" s="3"/>
-      <c r="U115" s="3"/>
-      <c r="V115" s="3"/>
-      <c r="W115" s="3"/>
-      <c r="X115" s="3"/>
-      <c r="Y115" s="3"/>
-      <c r="Z115" s="3"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="3"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -4710,14 +3308,8 @@
       <c r="R116" s="3"/>
       <c r="S116" s="3"/>
       <c r="T116" s="3"/>
-      <c r="U116" s="3"/>
-      <c r="V116" s="3"/>
-      <c r="W116" s="3"/>
-      <c r="X116" s="3"/>
-      <c r="Y116" s="3"/>
-      <c r="Z116" s="3"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="3"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -4738,14 +3330,8 @@
       <c r="R117" s="3"/>
       <c r="S117" s="3"/>
       <c r="T117" s="3"/>
-      <c r="U117" s="3"/>
-      <c r="V117" s="3"/>
-      <c r="W117" s="3"/>
-      <c r="X117" s="3"/>
-      <c r="Y117" s="3"/>
-      <c r="Z117" s="3"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -4766,14 +3352,8 @@
       <c r="R118" s="3"/>
       <c r="S118" s="3"/>
       <c r="T118" s="3"/>
-      <c r="U118" s="3"/>
-      <c r="V118" s="3"/>
-      <c r="W118" s="3"/>
-      <c r="X118" s="3"/>
-      <c r="Y118" s="3"/>
-      <c r="Z118" s="3"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -4794,14 +3374,8 @@
       <c r="R119" s="3"/>
       <c r="S119" s="3"/>
       <c r="T119" s="3"/>
-      <c r="U119" s="3"/>
-      <c r="V119" s="3"/>
-      <c r="W119" s="3"/>
-      <c r="X119" s="3"/>
-      <c r="Y119" s="3"/>
-      <c r="Z119" s="3"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -4822,14 +3396,8 @@
       <c r="R120" s="3"/>
       <c r="S120" s="3"/>
       <c r="T120" s="3"/>
-      <c r="U120" s="3"/>
-      <c r="V120" s="3"/>
-      <c r="W120" s="3"/>
-      <c r="X120" s="3"/>
-      <c r="Y120" s="3"/>
-      <c r="Z120" s="3"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -4850,14 +3418,8 @@
       <c r="R121" s="3"/>
       <c r="S121" s="3"/>
       <c r="T121" s="3"/>
-      <c r="U121" s="3"/>
-      <c r="V121" s="3"/>
-      <c r="W121" s="3"/>
-      <c r="X121" s="3"/>
-      <c r="Y121" s="3"/>
-      <c r="Z121" s="3"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -4878,14 +3440,8 @@
       <c r="R122" s="3"/>
       <c r="S122" s="3"/>
       <c r="T122" s="3"/>
-      <c r="U122" s="3"/>
-      <c r="V122" s="3"/>
-      <c r="W122" s="3"/>
-      <c r="X122" s="3"/>
-      <c r="Y122" s="3"/>
-      <c r="Z122" s="3"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -4906,14 +3462,8 @@
       <c r="R123" s="3"/>
       <c r="S123" s="3"/>
       <c r="T123" s="3"/>
-      <c r="U123" s="3"/>
-      <c r="V123" s="3"/>
-      <c r="W123" s="3"/>
-      <c r="X123" s="3"/>
-      <c r="Y123" s="3"/>
-      <c r="Z123" s="3"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -4934,14 +3484,8 @@
       <c r="R124" s="3"/>
       <c r="S124" s="3"/>
       <c r="T124" s="3"/>
-      <c r="U124" s="3"/>
-      <c r="V124" s="3"/>
-      <c r="W124" s="3"/>
-      <c r="X124" s="3"/>
-      <c r="Y124" s="3"/>
-      <c r="Z124" s="3"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -4962,14 +3506,8 @@
       <c r="R125" s="3"/>
       <c r="S125" s="3"/>
       <c r="T125" s="3"/>
-      <c r="U125" s="3"/>
-      <c r="V125" s="3"/>
-      <c r="W125" s="3"/>
-      <c r="X125" s="3"/>
-      <c r="Y125" s="3"/>
-      <c r="Z125" s="3"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -4990,14 +3528,8 @@
       <c r="R126" s="3"/>
       <c r="S126" s="3"/>
       <c r="T126" s="3"/>
-      <c r="U126" s="3"/>
-      <c r="V126" s="3"/>
-      <c r="W126" s="3"/>
-      <c r="X126" s="3"/>
-      <c r="Y126" s="3"/>
-      <c r="Z126" s="3"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -5018,14 +3550,8 @@
       <c r="R127" s="3"/>
       <c r="S127" s="3"/>
       <c r="T127" s="3"/>
-      <c r="U127" s="3"/>
-      <c r="V127" s="3"/>
-      <c r="W127" s="3"/>
-      <c r="X127" s="3"/>
-      <c r="Y127" s="3"/>
-      <c r="Z127" s="3"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -5046,14 +3572,8 @@
       <c r="R128" s="3"/>
       <c r="S128" s="3"/>
       <c r="T128" s="3"/>
-      <c r="U128" s="3"/>
-      <c r="V128" s="3"/>
-      <c r="W128" s="3"/>
-      <c r="X128" s="3"/>
-      <c r="Y128" s="3"/>
-      <c r="Z128" s="3"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -5074,14 +3594,8 @@
       <c r="R129" s="3"/>
       <c r="S129" s="3"/>
       <c r="T129" s="3"/>
-      <c r="U129" s="3"/>
-      <c r="V129" s="3"/>
-      <c r="W129" s="3"/>
-      <c r="X129" s="3"/>
-      <c r="Y129" s="3"/>
-      <c r="Z129" s="3"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -5102,14 +3616,8 @@
       <c r="R130" s="3"/>
       <c r="S130" s="3"/>
       <c r="T130" s="3"/>
-      <c r="U130" s="3"/>
-      <c r="V130" s="3"/>
-      <c r="W130" s="3"/>
-      <c r="X130" s="3"/>
-      <c r="Y130" s="3"/>
-      <c r="Z130" s="3"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -5130,14 +3638,8 @@
       <c r="R131" s="3"/>
       <c r="S131" s="3"/>
       <c r="T131" s="3"/>
-      <c r="U131" s="3"/>
-      <c r="V131" s="3"/>
-      <c r="W131" s="3"/>
-      <c r="X131" s="3"/>
-      <c r="Y131" s="3"/>
-      <c r="Z131" s="3"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -5158,14 +3660,8 @@
       <c r="R132" s="3"/>
       <c r="S132" s="3"/>
       <c r="T132" s="3"/>
-      <c r="U132" s="3"/>
-      <c r="V132" s="3"/>
-      <c r="W132" s="3"/>
-      <c r="X132" s="3"/>
-      <c r="Y132" s="3"/>
-      <c r="Z132" s="3"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -5186,14 +3682,8 @@
       <c r="R133" s="3"/>
       <c r="S133" s="3"/>
       <c r="T133" s="3"/>
-      <c r="U133" s="3"/>
-      <c r="V133" s="3"/>
-      <c r="W133" s="3"/>
-      <c r="X133" s="3"/>
-      <c r="Y133" s="3"/>
-      <c r="Z133" s="3"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -5214,14 +3704,8 @@
       <c r="R134" s="3"/>
       <c r="S134" s="3"/>
       <c r="T134" s="3"/>
-      <c r="U134" s="3"/>
-      <c r="V134" s="3"/>
-      <c r="W134" s="3"/>
-      <c r="X134" s="3"/>
-      <c r="Y134" s="3"/>
-      <c r="Z134" s="3"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="3"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -5242,14 +3726,8 @@
       <c r="R135" s="3"/>
       <c r="S135" s="3"/>
       <c r="T135" s="3"/>
-      <c r="U135" s="3"/>
-      <c r="V135" s="3"/>
-      <c r="W135" s="3"/>
-      <c r="X135" s="3"/>
-      <c r="Y135" s="3"/>
-      <c r="Z135" s="3"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="3"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -5270,14 +3748,8 @@
       <c r="R136" s="3"/>
       <c r="S136" s="3"/>
       <c r="T136" s="3"/>
-      <c r="U136" s="3"/>
-      <c r="V136" s="3"/>
-      <c r="W136" s="3"/>
-      <c r="X136" s="3"/>
-      <c r="Y136" s="3"/>
-      <c r="Z136" s="3"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="3"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -5298,14 +3770,8 @@
       <c r="R137" s="3"/>
       <c r="S137" s="3"/>
       <c r="T137" s="3"/>
-      <c r="U137" s="3"/>
-      <c r="V137" s="3"/>
-      <c r="W137" s="3"/>
-      <c r="X137" s="3"/>
-      <c r="Y137" s="3"/>
-      <c r="Z137" s="3"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="3"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -5326,14 +3792,8 @@
       <c r="R138" s="3"/>
       <c r="S138" s="3"/>
       <c r="T138" s="3"/>
-      <c r="U138" s="3"/>
-      <c r="V138" s="3"/>
-      <c r="W138" s="3"/>
-      <c r="X138" s="3"/>
-      <c r="Y138" s="3"/>
-      <c r="Z138" s="3"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="3"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -5354,14 +3814,8 @@
       <c r="R139" s="3"/>
       <c r="S139" s="3"/>
       <c r="T139" s="3"/>
-      <c r="U139" s="3"/>
-      <c r="V139" s="3"/>
-      <c r="W139" s="3"/>
-      <c r="X139" s="3"/>
-      <c r="Y139" s="3"/>
-      <c r="Z139" s="3"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="3"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -5382,14 +3836,8 @@
       <c r="R140" s="3"/>
       <c r="S140" s="3"/>
       <c r="T140" s="3"/>
-      <c r="U140" s="3"/>
-      <c r="V140" s="3"/>
-      <c r="W140" s="3"/>
-      <c r="X140" s="3"/>
-      <c r="Y140" s="3"/>
-      <c r="Z140" s="3"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="3"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -5410,14 +3858,8 @@
       <c r="R141" s="3"/>
       <c r="S141" s="3"/>
       <c r="T141" s="3"/>
-      <c r="U141" s="3"/>
-      <c r="V141" s="3"/>
-      <c r="W141" s="3"/>
-      <c r="X141" s="3"/>
-      <c r="Y141" s="3"/>
-      <c r="Z141" s="3"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="3"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -5438,14 +3880,8 @@
       <c r="R142" s="3"/>
       <c r="S142" s="3"/>
       <c r="T142" s="3"/>
-      <c r="U142" s="3"/>
-      <c r="V142" s="3"/>
-      <c r="W142" s="3"/>
-      <c r="X142" s="3"/>
-      <c r="Y142" s="3"/>
-      <c r="Z142" s="3"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="3"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -5466,14 +3902,8 @@
       <c r="R143" s="3"/>
       <c r="S143" s="3"/>
       <c r="T143" s="3"/>
-      <c r="U143" s="3"/>
-      <c r="V143" s="3"/>
-      <c r="W143" s="3"/>
-      <c r="X143" s="3"/>
-      <c r="Y143" s="3"/>
-      <c r="Z143" s="3"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="3"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -5494,14 +3924,8 @@
       <c r="R144" s="3"/>
       <c r="S144" s="3"/>
       <c r="T144" s="3"/>
-      <c r="U144" s="3"/>
-      <c r="V144" s="3"/>
-      <c r="W144" s="3"/>
-      <c r="X144" s="3"/>
-      <c r="Y144" s="3"/>
-      <c r="Z144" s="3"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="3"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -5522,14 +3946,8 @@
       <c r="R145" s="3"/>
       <c r="S145" s="3"/>
       <c r="T145" s="3"/>
-      <c r="U145" s="3"/>
-      <c r="V145" s="3"/>
-      <c r="W145" s="3"/>
-      <c r="X145" s="3"/>
-      <c r="Y145" s="3"/>
-      <c r="Z145" s="3"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="3"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -5550,14 +3968,8 @@
       <c r="R146" s="3"/>
       <c r="S146" s="3"/>
       <c r="T146" s="3"/>
-      <c r="U146" s="3"/>
-      <c r="V146" s="3"/>
-      <c r="W146" s="3"/>
-      <c r="X146" s="3"/>
-      <c r="Y146" s="3"/>
-      <c r="Z146" s="3"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="3"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -5578,14 +3990,8 @@
       <c r="R147" s="3"/>
       <c r="S147" s="3"/>
       <c r="T147" s="3"/>
-      <c r="U147" s="3"/>
-      <c r="V147" s="3"/>
-      <c r="W147" s="3"/>
-      <c r="X147" s="3"/>
-      <c r="Y147" s="3"/>
-      <c r="Z147" s="3"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="3"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -5606,14 +4012,8 @@
       <c r="R148" s="3"/>
       <c r="S148" s="3"/>
       <c r="T148" s="3"/>
-      <c r="U148" s="3"/>
-      <c r="V148" s="3"/>
-      <c r="W148" s="3"/>
-      <c r="X148" s="3"/>
-      <c r="Y148" s="3"/>
-      <c r="Z148" s="3"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="3"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -5634,14 +4034,8 @@
       <c r="R149" s="3"/>
       <c r="S149" s="3"/>
       <c r="T149" s="3"/>
-      <c r="U149" s="3"/>
-      <c r="V149" s="3"/>
-      <c r="W149" s="3"/>
-      <c r="X149" s="3"/>
-      <c r="Y149" s="3"/>
-      <c r="Z149" s="3"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="3"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -5662,14 +4056,8 @@
       <c r="R150" s="3"/>
       <c r="S150" s="3"/>
       <c r="T150" s="3"/>
-      <c r="U150" s="3"/>
-      <c r="V150" s="3"/>
-      <c r="W150" s="3"/>
-      <c r="X150" s="3"/>
-      <c r="Y150" s="3"/>
-      <c r="Z150" s="3"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="3"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -5690,14 +4078,8 @@
       <c r="R151" s="3"/>
       <c r="S151" s="3"/>
       <c r="T151" s="3"/>
-      <c r="U151" s="3"/>
-      <c r="V151" s="3"/>
-      <c r="W151" s="3"/>
-      <c r="X151" s="3"/>
-      <c r="Y151" s="3"/>
-      <c r="Z151" s="3"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="3"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -5718,14 +4100,8 @@
       <c r="R152" s="3"/>
       <c r="S152" s="3"/>
       <c r="T152" s="3"/>
-      <c r="U152" s="3"/>
-      <c r="V152" s="3"/>
-      <c r="W152" s="3"/>
-      <c r="X152" s="3"/>
-      <c r="Y152" s="3"/>
-      <c r="Z152" s="3"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="3"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -5746,14 +4122,8 @@
       <c r="R153" s="3"/>
       <c r="S153" s="3"/>
       <c r="T153" s="3"/>
-      <c r="U153" s="3"/>
-      <c r="V153" s="3"/>
-      <c r="W153" s="3"/>
-      <c r="X153" s="3"/>
-      <c r="Y153" s="3"/>
-      <c r="Z153" s="3"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="3"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -5774,14 +4144,8 @@
       <c r="R154" s="3"/>
       <c r="S154" s="3"/>
       <c r="T154" s="3"/>
-      <c r="U154" s="3"/>
-      <c r="V154" s="3"/>
-      <c r="W154" s="3"/>
-      <c r="X154" s="3"/>
-      <c r="Y154" s="3"/>
-      <c r="Z154" s="3"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="3"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -5802,14 +4166,8 @@
       <c r="R155" s="3"/>
       <c r="S155" s="3"/>
       <c r="T155" s="3"/>
-      <c r="U155" s="3"/>
-      <c r="V155" s="3"/>
-      <c r="W155" s="3"/>
-      <c r="X155" s="3"/>
-      <c r="Y155" s="3"/>
-      <c r="Z155" s="3"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="3"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -5830,14 +4188,8 @@
       <c r="R156" s="3"/>
       <c r="S156" s="3"/>
       <c r="T156" s="3"/>
-      <c r="U156" s="3"/>
-      <c r="V156" s="3"/>
-      <c r="W156" s="3"/>
-      <c r="X156" s="3"/>
-      <c r="Y156" s="3"/>
-      <c r="Z156" s="3"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="3"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -5858,14 +4210,8 @@
       <c r="R157" s="3"/>
       <c r="S157" s="3"/>
       <c r="T157" s="3"/>
-      <c r="U157" s="3"/>
-      <c r="V157" s="3"/>
-      <c r="W157" s="3"/>
-      <c r="X157" s="3"/>
-      <c r="Y157" s="3"/>
-      <c r="Z157" s="3"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="3"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -5886,14 +4232,8 @@
       <c r="R158" s="3"/>
       <c r="S158" s="3"/>
       <c r="T158" s="3"/>
-      <c r="U158" s="3"/>
-      <c r="V158" s="3"/>
-      <c r="W158" s="3"/>
-      <c r="X158" s="3"/>
-      <c r="Y158" s="3"/>
-      <c r="Z158" s="3"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="3"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -5914,14 +4254,8 @@
       <c r="R159" s="3"/>
       <c r="S159" s="3"/>
       <c r="T159" s="3"/>
-      <c r="U159" s="3"/>
-      <c r="V159" s="3"/>
-      <c r="W159" s="3"/>
-      <c r="X159" s="3"/>
-      <c r="Y159" s="3"/>
-      <c r="Z159" s="3"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -5942,14 +4276,8 @@
       <c r="R160" s="3"/>
       <c r="S160" s="3"/>
       <c r="T160" s="3"/>
-      <c r="U160" s="3"/>
-      <c r="V160" s="3"/>
-      <c r="W160" s="3"/>
-      <c r="X160" s="3"/>
-      <c r="Y160" s="3"/>
-      <c r="Z160" s="3"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="3"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -5970,14 +4298,8 @@
       <c r="R161" s="3"/>
       <c r="S161" s="3"/>
       <c r="T161" s="3"/>
-      <c r="U161" s="3"/>
-      <c r="V161" s="3"/>
-      <c r="W161" s="3"/>
-      <c r="X161" s="3"/>
-      <c r="Y161" s="3"/>
-      <c r="Z161" s="3"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="3"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -5998,14 +4320,8 @@
       <c r="R162" s="3"/>
       <c r="S162" s="3"/>
       <c r="T162" s="3"/>
-      <c r="U162" s="3"/>
-      <c r="V162" s="3"/>
-      <c r="W162" s="3"/>
-      <c r="X162" s="3"/>
-      <c r="Y162" s="3"/>
-      <c r="Z162" s="3"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="3"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -6026,14 +4342,8 @@
       <c r="R163" s="3"/>
       <c r="S163" s="3"/>
       <c r="T163" s="3"/>
-      <c r="U163" s="3"/>
-      <c r="V163" s="3"/>
-      <c r="W163" s="3"/>
-      <c r="X163" s="3"/>
-      <c r="Y163" s="3"/>
-      <c r="Z163" s="3"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="3"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -6054,14 +4364,8 @@
       <c r="R164" s="3"/>
       <c r="S164" s="3"/>
       <c r="T164" s="3"/>
-      <c r="U164" s="3"/>
-      <c r="V164" s="3"/>
-      <c r="W164" s="3"/>
-      <c r="X164" s="3"/>
-      <c r="Y164" s="3"/>
-      <c r="Z164" s="3"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="3"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -6082,14 +4386,8 @@
       <c r="R165" s="3"/>
       <c r="S165" s="3"/>
       <c r="T165" s="3"/>
-      <c r="U165" s="3"/>
-      <c r="V165" s="3"/>
-      <c r="W165" s="3"/>
-      <c r="X165" s="3"/>
-      <c r="Y165" s="3"/>
-      <c r="Z165" s="3"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="3"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -6110,14 +4408,8 @@
       <c r="R166" s="3"/>
       <c r="S166" s="3"/>
       <c r="T166" s="3"/>
-      <c r="U166" s="3"/>
-      <c r="V166" s="3"/>
-      <c r="W166" s="3"/>
-      <c r="X166" s="3"/>
-      <c r="Y166" s="3"/>
-      <c r="Z166" s="3"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -6138,14 +4430,8 @@
       <c r="R167" s="3"/>
       <c r="S167" s="3"/>
       <c r="T167" s="3"/>
-      <c r="U167" s="3"/>
-      <c r="V167" s="3"/>
-      <c r="W167" s="3"/>
-      <c r="X167" s="3"/>
-      <c r="Y167" s="3"/>
-      <c r="Z167" s="3"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="3"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -6166,14 +4452,8 @@
       <c r="R168" s="3"/>
       <c r="S168" s="3"/>
       <c r="T168" s="3"/>
-      <c r="U168" s="3"/>
-      <c r="V168" s="3"/>
-      <c r="W168" s="3"/>
-      <c r="X168" s="3"/>
-      <c r="Y168" s="3"/>
-      <c r="Z168" s="3"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="3"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -6194,14 +4474,8 @@
       <c r="R169" s="3"/>
       <c r="S169" s="3"/>
       <c r="T169" s="3"/>
-      <c r="U169" s="3"/>
-      <c r="V169" s="3"/>
-      <c r="W169" s="3"/>
-      <c r="X169" s="3"/>
-      <c r="Y169" s="3"/>
-      <c r="Z169" s="3"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="3"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -6222,14 +4496,8 @@
       <c r="R170" s="3"/>
       <c r="S170" s="3"/>
       <c r="T170" s="3"/>
-      <c r="U170" s="3"/>
-      <c r="V170" s="3"/>
-      <c r="W170" s="3"/>
-      <c r="X170" s="3"/>
-      <c r="Y170" s="3"/>
-      <c r="Z170" s="3"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="3"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -6250,14 +4518,8 @@
       <c r="R171" s="3"/>
       <c r="S171" s="3"/>
       <c r="T171" s="3"/>
-      <c r="U171" s="3"/>
-      <c r="V171" s="3"/>
-      <c r="W171" s="3"/>
-      <c r="X171" s="3"/>
-      <c r="Y171" s="3"/>
-      <c r="Z171" s="3"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="3"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -6278,14 +4540,8 @@
       <c r="R172" s="3"/>
       <c r="S172" s="3"/>
       <c r="T172" s="3"/>
-      <c r="U172" s="3"/>
-      <c r="V172" s="3"/>
-      <c r="W172" s="3"/>
-      <c r="X172" s="3"/>
-      <c r="Y172" s="3"/>
-      <c r="Z172" s="3"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="3"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -6306,14 +4562,8 @@
       <c r="R173" s="3"/>
       <c r="S173" s="3"/>
       <c r="T173" s="3"/>
-      <c r="U173" s="3"/>
-      <c r="V173" s="3"/>
-      <c r="W173" s="3"/>
-      <c r="X173" s="3"/>
-      <c r="Y173" s="3"/>
-      <c r="Z173" s="3"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="3"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -6334,14 +4584,8 @@
       <c r="R174" s="3"/>
       <c r="S174" s="3"/>
       <c r="T174" s="3"/>
-      <c r="U174" s="3"/>
-      <c r="V174" s="3"/>
-      <c r="W174" s="3"/>
-      <c r="X174" s="3"/>
-      <c r="Y174" s="3"/>
-      <c r="Z174" s="3"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="3"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -6362,14 +4606,8 @@
       <c r="R175" s="3"/>
       <c r="S175" s="3"/>
       <c r="T175" s="3"/>
-      <c r="U175" s="3"/>
-      <c r="V175" s="3"/>
-      <c r="W175" s="3"/>
-      <c r="X175" s="3"/>
-      <c r="Y175" s="3"/>
-      <c r="Z175" s="3"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="3"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -6390,14 +4628,8 @@
       <c r="R176" s="3"/>
       <c r="S176" s="3"/>
       <c r="T176" s="3"/>
-      <c r="U176" s="3"/>
-      <c r="V176" s="3"/>
-      <c r="W176" s="3"/>
-      <c r="X176" s="3"/>
-      <c r="Y176" s="3"/>
-      <c r="Z176" s="3"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="3"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -6418,14 +4650,8 @@
       <c r="R177" s="3"/>
       <c r="S177" s="3"/>
       <c r="T177" s="3"/>
-      <c r="U177" s="3"/>
-      <c r="V177" s="3"/>
-      <c r="W177" s="3"/>
-      <c r="X177" s="3"/>
-      <c r="Y177" s="3"/>
-      <c r="Z177" s="3"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="3"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -6446,14 +4672,8 @@
       <c r="R178" s="3"/>
       <c r="S178" s="3"/>
       <c r="T178" s="3"/>
-      <c r="U178" s="3"/>
-      <c r="V178" s="3"/>
-      <c r="W178" s="3"/>
-      <c r="X178" s="3"/>
-      <c r="Y178" s="3"/>
-      <c r="Z178" s="3"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="3"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -6474,14 +4694,8 @@
       <c r="R179" s="3"/>
       <c r="S179" s="3"/>
       <c r="T179" s="3"/>
-      <c r="U179" s="3"/>
-      <c r="V179" s="3"/>
-      <c r="W179" s="3"/>
-      <c r="X179" s="3"/>
-      <c r="Y179" s="3"/>
-      <c r="Z179" s="3"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="3"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -6502,14 +4716,8 @@
       <c r="R180" s="3"/>
       <c r="S180" s="3"/>
       <c r="T180" s="3"/>
-      <c r="U180" s="3"/>
-      <c r="V180" s="3"/>
-      <c r="W180" s="3"/>
-      <c r="X180" s="3"/>
-      <c r="Y180" s="3"/>
-      <c r="Z180" s="3"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="3"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -6530,14 +4738,8 @@
       <c r="R181" s="3"/>
       <c r="S181" s="3"/>
       <c r="T181" s="3"/>
-      <c r="U181" s="3"/>
-      <c r="V181" s="3"/>
-      <c r="W181" s="3"/>
-      <c r="X181" s="3"/>
-      <c r="Y181" s="3"/>
-      <c r="Z181" s="3"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="3"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -6558,14 +4760,8 @@
       <c r="R182" s="3"/>
       <c r="S182" s="3"/>
       <c r="T182" s="3"/>
-      <c r="U182" s="3"/>
-      <c r="V182" s="3"/>
-      <c r="W182" s="3"/>
-      <c r="X182" s="3"/>
-      <c r="Y182" s="3"/>
-      <c r="Z182" s="3"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="3"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -6586,14 +4782,8 @@
       <c r="R183" s="3"/>
       <c r="S183" s="3"/>
       <c r="T183" s="3"/>
-      <c r="U183" s="3"/>
-      <c r="V183" s="3"/>
-      <c r="W183" s="3"/>
-      <c r="X183" s="3"/>
-      <c r="Y183" s="3"/>
-      <c r="Z183" s="3"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="3"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -6614,14 +4804,8 @@
       <c r="R184" s="3"/>
       <c r="S184" s="3"/>
       <c r="T184" s="3"/>
-      <c r="U184" s="3"/>
-      <c r="V184" s="3"/>
-      <c r="W184" s="3"/>
-      <c r="X184" s="3"/>
-      <c r="Y184" s="3"/>
-      <c r="Z184" s="3"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="3"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -6642,14 +4826,8 @@
       <c r="R185" s="3"/>
       <c r="S185" s="3"/>
       <c r="T185" s="3"/>
-      <c r="U185" s="3"/>
-      <c r="V185" s="3"/>
-      <c r="W185" s="3"/>
-      <c r="X185" s="3"/>
-      <c r="Y185" s="3"/>
-      <c r="Z185" s="3"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="3"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -6670,14 +4848,8 @@
       <c r="R186" s="3"/>
       <c r="S186" s="3"/>
       <c r="T186" s="3"/>
-      <c r="U186" s="3"/>
-      <c r="V186" s="3"/>
-      <c r="W186" s="3"/>
-      <c r="X186" s="3"/>
-      <c r="Y186" s="3"/>
-      <c r="Z186" s="3"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="3"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -6698,14 +4870,8 @@
       <c r="R187" s="3"/>
       <c r="S187" s="3"/>
       <c r="T187" s="3"/>
-      <c r="U187" s="3"/>
-      <c r="V187" s="3"/>
-      <c r="W187" s="3"/>
-      <c r="X187" s="3"/>
-      <c r="Y187" s="3"/>
-      <c r="Z187" s="3"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="3"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -6726,14 +4892,8 @@
       <c r="R188" s="3"/>
       <c r="S188" s="3"/>
       <c r="T188" s="3"/>
-      <c r="U188" s="3"/>
-      <c r="V188" s="3"/>
-      <c r="W188" s="3"/>
-      <c r="X188" s="3"/>
-      <c r="Y188" s="3"/>
-      <c r="Z188" s="3"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="3"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -6754,14 +4914,8 @@
       <c r="R189" s="3"/>
       <c r="S189" s="3"/>
       <c r="T189" s="3"/>
-      <c r="U189" s="3"/>
-      <c r="V189" s="3"/>
-      <c r="W189" s="3"/>
-      <c r="X189" s="3"/>
-      <c r="Y189" s="3"/>
-      <c r="Z189" s="3"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="3"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -6782,14 +4936,8 @@
       <c r="R190" s="3"/>
       <c r="S190" s="3"/>
       <c r="T190" s="3"/>
-      <c r="U190" s="3"/>
-      <c r="V190" s="3"/>
-      <c r="W190" s="3"/>
-      <c r="X190" s="3"/>
-      <c r="Y190" s="3"/>
-      <c r="Z190" s="3"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="3"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -6810,14 +4958,8 @@
       <c r="R191" s="3"/>
       <c r="S191" s="3"/>
       <c r="T191" s="3"/>
-      <c r="U191" s="3"/>
-      <c r="V191" s="3"/>
-      <c r="W191" s="3"/>
-      <c r="X191" s="3"/>
-      <c r="Y191" s="3"/>
-      <c r="Z191" s="3"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="3"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -6838,14 +4980,8 @@
       <c r="R192" s="3"/>
       <c r="S192" s="3"/>
       <c r="T192" s="3"/>
-      <c r="U192" s="3"/>
-      <c r="V192" s="3"/>
-      <c r="W192" s="3"/>
-      <c r="X192" s="3"/>
-      <c r="Y192" s="3"/>
-      <c r="Z192" s="3"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="3"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -6866,14 +5002,8 @@
       <c r="R193" s="3"/>
       <c r="S193" s="3"/>
       <c r="T193" s="3"/>
-      <c r="U193" s="3"/>
-      <c r="V193" s="3"/>
-      <c r="W193" s="3"/>
-      <c r="X193" s="3"/>
-      <c r="Y193" s="3"/>
-      <c r="Z193" s="3"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="3"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -6894,14 +5024,8 @@
       <c r="R194" s="3"/>
       <c r="S194" s="3"/>
       <c r="T194" s="3"/>
-      <c r="U194" s="3"/>
-      <c r="V194" s="3"/>
-      <c r="W194" s="3"/>
-      <c r="X194" s="3"/>
-      <c r="Y194" s="3"/>
-      <c r="Z194" s="3"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="3"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -6922,14 +5046,8 @@
       <c r="R195" s="3"/>
       <c r="S195" s="3"/>
       <c r="T195" s="3"/>
-      <c r="U195" s="3"/>
-      <c r="V195" s="3"/>
-      <c r="W195" s="3"/>
-      <c r="X195" s="3"/>
-      <c r="Y195" s="3"/>
-      <c r="Z195" s="3"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="3"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -6950,14 +5068,8 @@
       <c r="R196" s="3"/>
       <c r="S196" s="3"/>
       <c r="T196" s="3"/>
-      <c r="U196" s="3"/>
-      <c r="V196" s="3"/>
-      <c r="W196" s="3"/>
-      <c r="X196" s="3"/>
-      <c r="Y196" s="3"/>
-      <c r="Z196" s="3"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="3"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -6978,14 +5090,8 @@
       <c r="R197" s="3"/>
       <c r="S197" s="3"/>
       <c r="T197" s="3"/>
-      <c r="U197" s="3"/>
-      <c r="V197" s="3"/>
-      <c r="W197" s="3"/>
-      <c r="X197" s="3"/>
-      <c r="Y197" s="3"/>
-      <c r="Z197" s="3"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="3"/>
       <c r="B198" s="3"/>
       <c r="C198" s="3"/>
@@ -7006,14 +5112,8 @@
       <c r="R198" s="3"/>
       <c r="S198" s="3"/>
       <c r="T198" s="3"/>
-      <c r="U198" s="3"/>
-      <c r="V198" s="3"/>
-      <c r="W198" s="3"/>
-      <c r="X198" s="3"/>
-      <c r="Y198" s="3"/>
-      <c r="Z198" s="3"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="3"/>
       <c r="B199" s="3"/>
       <c r="C199" s="3"/>
@@ -7034,14 +5134,8 @@
       <c r="R199" s="3"/>
       <c r="S199" s="3"/>
       <c r="T199" s="3"/>
-      <c r="U199" s="3"/>
-      <c r="V199" s="3"/>
-      <c r="W199" s="3"/>
-      <c r="X199" s="3"/>
-      <c r="Y199" s="3"/>
-      <c r="Z199" s="3"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="3"/>
       <c r="B200" s="3"/>
       <c r="C200" s="3"/>
@@ -7062,14 +5156,8 @@
       <c r="R200" s="3"/>
       <c r="S200" s="3"/>
       <c r="T200" s="3"/>
-      <c r="U200" s="3"/>
-      <c r="V200" s="3"/>
-      <c r="W200" s="3"/>
-      <c r="X200" s="3"/>
-      <c r="Y200" s="3"/>
-      <c r="Z200" s="3"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="3"/>
       <c r="B201" s="3"/>
       <c r="C201" s="3"/>
@@ -7090,14 +5178,8 @@
       <c r="R201" s="3"/>
       <c r="S201" s="3"/>
       <c r="T201" s="3"/>
-      <c r="U201" s="3"/>
-      <c r="V201" s="3"/>
-      <c r="W201" s="3"/>
-      <c r="X201" s="3"/>
-      <c r="Y201" s="3"/>
-      <c r="Z201" s="3"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="3"/>
       <c r="B202" s="3"/>
       <c r="C202" s="3"/>
@@ -7118,14 +5200,8 @@
       <c r="R202" s="3"/>
       <c r="S202" s="3"/>
       <c r="T202" s="3"/>
-      <c r="U202" s="3"/>
-      <c r="V202" s="3"/>
-      <c r="W202" s="3"/>
-      <c r="X202" s="3"/>
-      <c r="Y202" s="3"/>
-      <c r="Z202" s="3"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="3"/>
       <c r="B203" s="3"/>
       <c r="C203" s="3"/>
@@ -7146,14 +5222,8 @@
       <c r="R203" s="3"/>
       <c r="S203" s="3"/>
       <c r="T203" s="3"/>
-      <c r="U203" s="3"/>
-      <c r="V203" s="3"/>
-      <c r="W203" s="3"/>
-      <c r="X203" s="3"/>
-      <c r="Y203" s="3"/>
-      <c r="Z203" s="3"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="3"/>
       <c r="B204" s="3"/>
       <c r="C204" s="3"/>
@@ -7174,14 +5244,8 @@
       <c r="R204" s="3"/>
       <c r="S204" s="3"/>
       <c r="T204" s="3"/>
-      <c r="U204" s="3"/>
-      <c r="V204" s="3"/>
-      <c r="W204" s="3"/>
-      <c r="X204" s="3"/>
-      <c r="Y204" s="3"/>
-      <c r="Z204" s="3"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="3"/>
       <c r="B205" s="3"/>
       <c r="C205" s="3"/>
@@ -7202,14 +5266,8 @@
       <c r="R205" s="3"/>
       <c r="S205" s="3"/>
       <c r="T205" s="3"/>
-      <c r="U205" s="3"/>
-      <c r="V205" s="3"/>
-      <c r="W205" s="3"/>
-      <c r="X205" s="3"/>
-      <c r="Y205" s="3"/>
-      <c r="Z205" s="3"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="3"/>
       <c r="B206" s="3"/>
       <c r="C206" s="3"/>
@@ -7230,14 +5288,8 @@
       <c r="R206" s="3"/>
       <c r="S206" s="3"/>
       <c r="T206" s="3"/>
-      <c r="U206" s="3"/>
-      <c r="V206" s="3"/>
-      <c r="W206" s="3"/>
-      <c r="X206" s="3"/>
-      <c r="Y206" s="3"/>
-      <c r="Z206" s="3"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="3"/>
       <c r="B207" s="3"/>
       <c r="C207" s="3"/>
@@ -7258,14 +5310,8 @@
       <c r="R207" s="3"/>
       <c r="S207" s="3"/>
       <c r="T207" s="3"/>
-      <c r="U207" s="3"/>
-      <c r="V207" s="3"/>
-      <c r="W207" s="3"/>
-      <c r="X207" s="3"/>
-      <c r="Y207" s="3"/>
-      <c r="Z207" s="3"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="3"/>
       <c r="B208" s="3"/>
       <c r="C208" s="3"/>
@@ -7286,14 +5332,8 @@
       <c r="R208" s="3"/>
       <c r="S208" s="3"/>
       <c r="T208" s="3"/>
-      <c r="U208" s="3"/>
-      <c r="V208" s="3"/>
-      <c r="W208" s="3"/>
-      <c r="X208" s="3"/>
-      <c r="Y208" s="3"/>
-      <c r="Z208" s="3"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="3"/>
       <c r="B209" s="3"/>
       <c r="C209" s="3"/>
@@ -7314,14 +5354,8 @@
       <c r="R209" s="3"/>
       <c r="S209" s="3"/>
       <c r="T209" s="3"/>
-      <c r="U209" s="3"/>
-      <c r="V209" s="3"/>
-      <c r="W209" s="3"/>
-      <c r="X209" s="3"/>
-      <c r="Y209" s="3"/>
-      <c r="Z209" s="3"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="3"/>
       <c r="B210" s="3"/>
       <c r="C210" s="3"/>
@@ -7342,14 +5376,8 @@
       <c r="R210" s="3"/>
       <c r="S210" s="3"/>
       <c r="T210" s="3"/>
-      <c r="U210" s="3"/>
-      <c r="V210" s="3"/>
-      <c r="W210" s="3"/>
-      <c r="X210" s="3"/>
-      <c r="Y210" s="3"/>
-      <c r="Z210" s="3"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="3"/>
       <c r="B211" s="3"/>
       <c r="C211" s="3"/>
@@ -7370,14 +5398,8 @@
       <c r="R211" s="3"/>
       <c r="S211" s="3"/>
       <c r="T211" s="3"/>
-      <c r="U211" s="3"/>
-      <c r="V211" s="3"/>
-      <c r="W211" s="3"/>
-      <c r="X211" s="3"/>
-      <c r="Y211" s="3"/>
-      <c r="Z211" s="3"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="3"/>
       <c r="B212" s="3"/>
       <c r="C212" s="3"/>
@@ -7398,14 +5420,8 @@
       <c r="R212" s="3"/>
       <c r="S212" s="3"/>
       <c r="T212" s="3"/>
-      <c r="U212" s="3"/>
-      <c r="V212" s="3"/>
-      <c r="W212" s="3"/>
-      <c r="X212" s="3"/>
-      <c r="Y212" s="3"/>
-      <c r="Z212" s="3"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="3"/>
       <c r="B213" s="3"/>
       <c r="C213" s="3"/>
@@ -7426,14 +5442,8 @@
       <c r="R213" s="3"/>
       <c r="S213" s="3"/>
       <c r="T213" s="3"/>
-      <c r="U213" s="3"/>
-      <c r="V213" s="3"/>
-      <c r="W213" s="3"/>
-      <c r="X213" s="3"/>
-      <c r="Y213" s="3"/>
-      <c r="Z213" s="3"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="3"/>
       <c r="B214" s="3"/>
       <c r="C214" s="3"/>
@@ -7454,14 +5464,8 @@
       <c r="R214" s="3"/>
       <c r="S214" s="3"/>
       <c r="T214" s="3"/>
-      <c r="U214" s="3"/>
-      <c r="V214" s="3"/>
-      <c r="W214" s="3"/>
-      <c r="X214" s="3"/>
-      <c r="Y214" s="3"/>
-      <c r="Z214" s="3"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="3"/>
       <c r="B215" s="3"/>
       <c r="C215" s="3"/>
@@ -7482,14 +5486,8 @@
       <c r="R215" s="3"/>
       <c r="S215" s="3"/>
       <c r="T215" s="3"/>
-      <c r="U215" s="3"/>
-      <c r="V215" s="3"/>
-      <c r="W215" s="3"/>
-      <c r="X215" s="3"/>
-      <c r="Y215" s="3"/>
-      <c r="Z215" s="3"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="3"/>
       <c r="B216" s="3"/>
       <c r="C216" s="3"/>
@@ -7510,14 +5508,8 @@
       <c r="R216" s="3"/>
       <c r="S216" s="3"/>
       <c r="T216" s="3"/>
-      <c r="U216" s="3"/>
-      <c r="V216" s="3"/>
-      <c r="W216" s="3"/>
-      <c r="X216" s="3"/>
-      <c r="Y216" s="3"/>
-      <c r="Z216" s="3"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="3"/>
       <c r="B217" s="3"/>
       <c r="C217" s="3"/>
@@ -7538,14 +5530,8 @@
       <c r="R217" s="3"/>
       <c r="S217" s="3"/>
       <c r="T217" s="3"/>
-      <c r="U217" s="3"/>
-      <c r="V217" s="3"/>
-      <c r="W217" s="3"/>
-      <c r="X217" s="3"/>
-      <c r="Y217" s="3"/>
-      <c r="Z217" s="3"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="3"/>
       <c r="B218" s="3"/>
       <c r="C218" s="3"/>
@@ -7566,14 +5552,8 @@
       <c r="R218" s="3"/>
       <c r="S218" s="3"/>
       <c r="T218" s="3"/>
-      <c r="U218" s="3"/>
-      <c r="V218" s="3"/>
-      <c r="W218" s="3"/>
-      <c r="X218" s="3"/>
-      <c r="Y218" s="3"/>
-      <c r="Z218" s="3"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="3"/>
       <c r="B219" s="3"/>
       <c r="C219" s="3"/>
@@ -7594,14 +5574,8 @@
       <c r="R219" s="3"/>
       <c r="S219" s="3"/>
       <c r="T219" s="3"/>
-      <c r="U219" s="3"/>
-      <c r="V219" s="3"/>
-      <c r="W219" s="3"/>
-      <c r="X219" s="3"/>
-      <c r="Y219" s="3"/>
-      <c r="Z219" s="3"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1" spans="1:26">
+    </row>
+    <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="3"/>
       <c r="B220" s="3"/>
       <c r="C220" s="3"/>
@@ -7622,796 +5596,3131 @@
       <c r="R220" s="3"/>
       <c r="S220" s="3"/>
       <c r="T220" s="3"/>
-      <c r="U220" s="3"/>
-      <c r="V220" s="3"/>
-      <c r="W220" s="3"/>
-      <c r="X220" s="3"/>
-      <c r="Y220" s="3"/>
-      <c r="Z220" s="3"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1"/>
-    <row r="222" ht="15.75" customHeight="1"/>
-    <row r="223" ht="15.75" customHeight="1"/>
-    <row r="224" ht="15.75" customHeight="1"/>
-    <row r="225" ht="15.75" customHeight="1"/>
-    <row r="226" ht="15.75" customHeight="1"/>
-    <row r="227" ht="15.75" customHeight="1"/>
-    <row r="228" ht="15.75" customHeight="1"/>
-    <row r="229" ht="15.75" customHeight="1"/>
-    <row r="230" ht="15.75" customHeight="1"/>
-    <row r="231" ht="15.75" customHeight="1"/>
-    <row r="232" ht="15.75" customHeight="1"/>
-    <row r="233" ht="15.75" customHeight="1"/>
-    <row r="234" ht="15.75" customHeight="1"/>
-    <row r="235" ht="15.75" customHeight="1"/>
-    <row r="236" ht="15.75" customHeight="1"/>
-    <row r="237" ht="15.75" customHeight="1"/>
-    <row r="238" ht="15.75" customHeight="1"/>
-    <row r="239" ht="15.75" customHeight="1"/>
-    <row r="240" ht="15.75" customHeight="1"/>
-    <row r="241" ht="15.75" customHeight="1"/>
-    <row r="242" ht="15.75" customHeight="1"/>
-    <row r="243" ht="15.75" customHeight="1"/>
-    <row r="244" ht="15.75" customHeight="1"/>
-    <row r="245" ht="15.75" customHeight="1"/>
-    <row r="246" ht="15.75" customHeight="1"/>
-    <row r="247" ht="15.75" customHeight="1"/>
-    <row r="248" ht="15.75" customHeight="1"/>
-    <row r="249" ht="15.75" customHeight="1"/>
-    <row r="250" ht="15.75" customHeight="1"/>
-    <row r="251" ht="15.75" customHeight="1"/>
-    <row r="252" ht="15.75" customHeight="1"/>
-    <row r="253" ht="15.75" customHeight="1"/>
-    <row r="254" ht="15.75" customHeight="1"/>
-    <row r="255" ht="15.75" customHeight="1"/>
-    <row r="256" ht="15.75" customHeight="1"/>
-    <row r="257" ht="15.75" customHeight="1"/>
-    <row r="258" ht="15.75" customHeight="1"/>
-    <row r="259" ht="15.75" customHeight="1"/>
-    <row r="260" ht="15.75" customHeight="1"/>
-    <row r="261" ht="15.75" customHeight="1"/>
-    <row r="262" ht="15.75" customHeight="1"/>
-    <row r="263" ht="15.75" customHeight="1"/>
-    <row r="264" ht="15.75" customHeight="1"/>
-    <row r="265" ht="15.75" customHeight="1"/>
-    <row r="266" ht="15.75" customHeight="1"/>
-    <row r="267" ht="15.75" customHeight="1"/>
-    <row r="268" ht="15.75" customHeight="1"/>
-    <row r="269" ht="15.75" customHeight="1"/>
-    <row r="270" ht="15.75" customHeight="1"/>
-    <row r="271" ht="15.75" customHeight="1"/>
-    <row r="272" ht="15.75" customHeight="1"/>
-    <row r="273" ht="15.75" customHeight="1"/>
-    <row r="274" ht="15.75" customHeight="1"/>
-    <row r="275" ht="15.75" customHeight="1"/>
-    <row r="276" ht="15.75" customHeight="1"/>
-    <row r="277" ht="15.75" customHeight="1"/>
-    <row r="278" ht="15.75" customHeight="1"/>
-    <row r="279" ht="15.75" customHeight="1"/>
-    <row r="280" ht="15.75" customHeight="1"/>
-    <row r="281" ht="15.75" customHeight="1"/>
-    <row r="282" ht="15.75" customHeight="1"/>
-    <row r="283" ht="15.75" customHeight="1"/>
-    <row r="284" ht="15.75" customHeight="1"/>
-    <row r="285" ht="15.75" customHeight="1"/>
-    <row r="286" ht="15.75" customHeight="1"/>
-    <row r="287" ht="15.75" customHeight="1"/>
-    <row r="288" ht="15.75" customHeight="1"/>
-    <row r="289" ht="15.75" customHeight="1"/>
-    <row r="290" ht="15.75" customHeight="1"/>
-    <row r="291" ht="15.75" customHeight="1"/>
-    <row r="292" ht="15.75" customHeight="1"/>
-    <row r="293" ht="15.75" customHeight="1"/>
-    <row r="294" ht="15.75" customHeight="1"/>
-    <row r="295" ht="15.75" customHeight="1"/>
-    <row r="296" ht="15.75" customHeight="1"/>
-    <row r="297" ht="15.75" customHeight="1"/>
-    <row r="298" ht="15.75" customHeight="1"/>
-    <row r="299" ht="15.75" customHeight="1"/>
-    <row r="300" ht="15.75" customHeight="1"/>
-    <row r="301" ht="15.75" customHeight="1"/>
-    <row r="302" ht="15.75" customHeight="1"/>
-    <row r="303" ht="15.75" customHeight="1"/>
-    <row r="304" ht="15.75" customHeight="1"/>
-    <row r="305" ht="15.75" customHeight="1"/>
-    <row r="306" ht="15.75" customHeight="1"/>
-    <row r="307" ht="15.75" customHeight="1"/>
-    <row r="308" ht="15.75" customHeight="1"/>
-    <row r="309" ht="15.75" customHeight="1"/>
-    <row r="310" ht="15.75" customHeight="1"/>
-    <row r="311" ht="15.75" customHeight="1"/>
-    <row r="312" ht="15.75" customHeight="1"/>
-    <row r="313" ht="15.75" customHeight="1"/>
-    <row r="314" ht="15.75" customHeight="1"/>
-    <row r="315" ht="15.75" customHeight="1"/>
-    <row r="316" ht="15.75" customHeight="1"/>
-    <row r="317" ht="15.75" customHeight="1"/>
-    <row r="318" ht="15.75" customHeight="1"/>
-    <row r="319" ht="15.75" customHeight="1"/>
-    <row r="320" ht="15.75" customHeight="1"/>
-    <row r="321" ht="15.75" customHeight="1"/>
-    <row r="322" ht="15.75" customHeight="1"/>
-    <row r="323" ht="15.75" customHeight="1"/>
-    <row r="324" ht="15.75" customHeight="1"/>
-    <row r="325" ht="15.75" customHeight="1"/>
-    <row r="326" ht="15.75" customHeight="1"/>
-    <row r="327" ht="15.75" customHeight="1"/>
-    <row r="328" ht="15.75" customHeight="1"/>
-    <row r="329" ht="15.75" customHeight="1"/>
-    <row r="330" ht="15.75" customHeight="1"/>
-    <row r="331" ht="15.75" customHeight="1"/>
-    <row r="332" ht="15.75" customHeight="1"/>
-    <row r="333" ht="15.75" customHeight="1"/>
-    <row r="334" ht="15.75" customHeight="1"/>
-    <row r="335" ht="15.75" customHeight="1"/>
-    <row r="336" ht="15.75" customHeight="1"/>
-    <row r="337" ht="15.75" customHeight="1"/>
-    <row r="338" ht="15.75" customHeight="1"/>
-    <row r="339" ht="15.75" customHeight="1"/>
-    <row r="340" ht="15.75" customHeight="1"/>
-    <row r="341" ht="15.75" customHeight="1"/>
-    <row r="342" ht="15.75" customHeight="1"/>
-    <row r="343" ht="15.75" customHeight="1"/>
-    <row r="344" ht="15.75" customHeight="1"/>
-    <row r="345" ht="15.75" customHeight="1"/>
-    <row r="346" ht="15.75" customHeight="1"/>
-    <row r="347" ht="15.75" customHeight="1"/>
-    <row r="348" ht="15.75" customHeight="1"/>
-    <row r="349" ht="15.75" customHeight="1"/>
-    <row r="350" ht="15.75" customHeight="1"/>
-    <row r="351" ht="15.75" customHeight="1"/>
-    <row r="352" ht="15.75" customHeight="1"/>
-    <row r="353" ht="15.75" customHeight="1"/>
-    <row r="354" ht="15.75" customHeight="1"/>
-    <row r="355" ht="15.75" customHeight="1"/>
-    <row r="356" ht="15.75" customHeight="1"/>
-    <row r="357" ht="15.75" customHeight="1"/>
-    <row r="358" ht="15.75" customHeight="1"/>
-    <row r="359" ht="15.75" customHeight="1"/>
-    <row r="360" ht="15.75" customHeight="1"/>
-    <row r="361" ht="15.75" customHeight="1"/>
-    <row r="362" ht="15.75" customHeight="1"/>
-    <row r="363" ht="15.75" customHeight="1"/>
-    <row r="364" ht="15.75" customHeight="1"/>
-    <row r="365" ht="15.75" customHeight="1"/>
-    <row r="366" ht="15.75" customHeight="1"/>
-    <row r="367" ht="15.75" customHeight="1"/>
-    <row r="368" ht="15.75" customHeight="1"/>
-    <row r="369" ht="15.75" customHeight="1"/>
-    <row r="370" ht="15.75" customHeight="1"/>
-    <row r="371" ht="15.75" customHeight="1"/>
-    <row r="372" ht="15.75" customHeight="1"/>
-    <row r="373" ht="15.75" customHeight="1"/>
-    <row r="374" ht="15.75" customHeight="1"/>
-    <row r="375" ht="15.75" customHeight="1"/>
-    <row r="376" ht="15.75" customHeight="1"/>
-    <row r="377" ht="15.75" customHeight="1"/>
-    <row r="378" ht="15.75" customHeight="1"/>
-    <row r="379" ht="15.75" customHeight="1"/>
-    <row r="380" ht="15.75" customHeight="1"/>
-    <row r="381" ht="15.75" customHeight="1"/>
-    <row r="382" ht="15.75" customHeight="1"/>
-    <row r="383" ht="15.75" customHeight="1"/>
-    <row r="384" ht="15.75" customHeight="1"/>
-    <row r="385" ht="15.75" customHeight="1"/>
-    <row r="386" ht="15.75" customHeight="1"/>
-    <row r="387" ht="15.75" customHeight="1"/>
-    <row r="388" ht="15.75" customHeight="1"/>
-    <row r="389" ht="15.75" customHeight="1"/>
-    <row r="390" ht="15.75" customHeight="1"/>
-    <row r="391" ht="15.75" customHeight="1"/>
-    <row r="392" ht="15.75" customHeight="1"/>
-    <row r="393" ht="15.75" customHeight="1"/>
-    <row r="394" ht="15.75" customHeight="1"/>
-    <row r="395" ht="15.75" customHeight="1"/>
-    <row r="396" ht="15.75" customHeight="1"/>
-    <row r="397" ht="15.75" customHeight="1"/>
-    <row r="398" ht="15.75" customHeight="1"/>
-    <row r="399" ht="15.75" customHeight="1"/>
-    <row r="400" ht="15.75" customHeight="1"/>
-    <row r="401" ht="15.75" customHeight="1"/>
-    <row r="402" ht="15.75" customHeight="1"/>
-    <row r="403" ht="15.75" customHeight="1"/>
-    <row r="404" ht="15.75" customHeight="1"/>
-    <row r="405" ht="15.75" customHeight="1"/>
-    <row r="406" ht="15.75" customHeight="1"/>
-    <row r="407" ht="15.75" customHeight="1"/>
-    <row r="408" ht="15.75" customHeight="1"/>
-    <row r="409" ht="15.75" customHeight="1"/>
-    <row r="410" ht="15.75" customHeight="1"/>
-    <row r="411" ht="15.75" customHeight="1"/>
-    <row r="412" ht="15.75" customHeight="1"/>
-    <row r="413" ht="15.75" customHeight="1"/>
-    <row r="414" ht="15.75" customHeight="1"/>
-    <row r="415" ht="15.75" customHeight="1"/>
-    <row r="416" ht="15.75" customHeight="1"/>
-    <row r="417" ht="15.75" customHeight="1"/>
-    <row r="418" ht="15.75" customHeight="1"/>
-    <row r="419" ht="15.75" customHeight="1"/>
-    <row r="420" ht="15.75" customHeight="1"/>
-    <row r="421" ht="15.75" customHeight="1"/>
-    <row r="422" ht="15.75" customHeight="1"/>
-    <row r="423" ht="15.75" customHeight="1"/>
-    <row r="424" ht="15.75" customHeight="1"/>
-    <row r="425" ht="15.75" customHeight="1"/>
-    <row r="426" ht="15.75" customHeight="1"/>
-    <row r="427" ht="15.75" customHeight="1"/>
-    <row r="428" ht="15.75" customHeight="1"/>
-    <row r="429" ht="15.75" customHeight="1"/>
-    <row r="430" ht="15.75" customHeight="1"/>
-    <row r="431" ht="15.75" customHeight="1"/>
-    <row r="432" ht="15.75" customHeight="1"/>
-    <row r="433" ht="15.75" customHeight="1"/>
-    <row r="434" ht="15.75" customHeight="1"/>
-    <row r="435" ht="15.75" customHeight="1"/>
-    <row r="436" ht="15.75" customHeight="1"/>
-    <row r="437" ht="15.75" customHeight="1"/>
-    <row r="438" ht="15.75" customHeight="1"/>
-    <row r="439" ht="15.75" customHeight="1"/>
-    <row r="440" ht="15.75" customHeight="1"/>
-    <row r="441" ht="15.75" customHeight="1"/>
-    <row r="442" ht="15.75" customHeight="1"/>
-    <row r="443" ht="15.75" customHeight="1"/>
-    <row r="444" ht="15.75" customHeight="1"/>
-    <row r="445" ht="15.75" customHeight="1"/>
-    <row r="446" ht="15.75" customHeight="1"/>
-    <row r="447" ht="15.75" customHeight="1"/>
-    <row r="448" ht="15.75" customHeight="1"/>
-    <row r="449" ht="15.75" customHeight="1"/>
-    <row r="450" ht="15.75" customHeight="1"/>
-    <row r="451" ht="15.75" customHeight="1"/>
-    <row r="452" ht="15.75" customHeight="1"/>
-    <row r="453" ht="15.75" customHeight="1"/>
-    <row r="454" ht="15.75" customHeight="1"/>
-    <row r="455" ht="15.75" customHeight="1"/>
-    <row r="456" ht="15.75" customHeight="1"/>
-    <row r="457" ht="15.75" customHeight="1"/>
-    <row r="458" ht="15.75" customHeight="1"/>
-    <row r="459" ht="15.75" customHeight="1"/>
-    <row r="460" ht="15.75" customHeight="1"/>
-    <row r="461" ht="15.75" customHeight="1"/>
-    <row r="462" ht="15.75" customHeight="1"/>
-    <row r="463" ht="15.75" customHeight="1"/>
-    <row r="464" ht="15.75" customHeight="1"/>
-    <row r="465" ht="15.75" customHeight="1"/>
-    <row r="466" ht="15.75" customHeight="1"/>
-    <row r="467" ht="15.75" customHeight="1"/>
-    <row r="468" ht="15.75" customHeight="1"/>
-    <row r="469" ht="15.75" customHeight="1"/>
-    <row r="470" ht="15.75" customHeight="1"/>
-    <row r="471" ht="15.75" customHeight="1"/>
-    <row r="472" ht="15.75" customHeight="1"/>
-    <row r="473" ht="15.75" customHeight="1"/>
-    <row r="474" ht="15.75" customHeight="1"/>
-    <row r="475" ht="15.75" customHeight="1"/>
-    <row r="476" ht="15.75" customHeight="1"/>
-    <row r="477" ht="15.75" customHeight="1"/>
-    <row r="478" ht="15.75" customHeight="1"/>
-    <row r="479" ht="15.75" customHeight="1"/>
-    <row r="480" ht="15.75" customHeight="1"/>
-    <row r="481" ht="15.75" customHeight="1"/>
-    <row r="482" ht="15.75" customHeight="1"/>
-    <row r="483" ht="15.75" customHeight="1"/>
-    <row r="484" ht="15.75" customHeight="1"/>
-    <row r="485" ht="15.75" customHeight="1"/>
-    <row r="486" ht="15.75" customHeight="1"/>
-    <row r="487" ht="15.75" customHeight="1"/>
-    <row r="488" ht="15.75" customHeight="1"/>
-    <row r="489" ht="15.75" customHeight="1"/>
-    <row r="490" ht="15.75" customHeight="1"/>
-    <row r="491" ht="15.75" customHeight="1"/>
-    <row r="492" ht="15.75" customHeight="1"/>
-    <row r="493" ht="15.75" customHeight="1"/>
-    <row r="494" ht="15.75" customHeight="1"/>
-    <row r="495" ht="15.75" customHeight="1"/>
-    <row r="496" ht="15.75" customHeight="1"/>
-    <row r="497" ht="15.75" customHeight="1"/>
-    <row r="498" ht="15.75" customHeight="1"/>
-    <row r="499" ht="15.75" customHeight="1"/>
-    <row r="500" ht="15.75" customHeight="1"/>
-    <row r="501" ht="15.75" customHeight="1"/>
-    <row r="502" ht="15.75" customHeight="1"/>
-    <row r="503" ht="15.75" customHeight="1"/>
-    <row r="504" ht="15.75" customHeight="1"/>
-    <row r="505" ht="15.75" customHeight="1"/>
-    <row r="506" ht="15.75" customHeight="1"/>
-    <row r="507" ht="15.75" customHeight="1"/>
-    <row r="508" ht="15.75" customHeight="1"/>
-    <row r="509" ht="15.75" customHeight="1"/>
-    <row r="510" ht="15.75" customHeight="1"/>
-    <row r="511" ht="15.75" customHeight="1"/>
-    <row r="512" ht="15.75" customHeight="1"/>
-    <row r="513" ht="15.75" customHeight="1"/>
-    <row r="514" ht="15.75" customHeight="1"/>
-    <row r="515" ht="15.75" customHeight="1"/>
-    <row r="516" ht="15.75" customHeight="1"/>
-    <row r="517" ht="15.75" customHeight="1"/>
-    <row r="518" ht="15.75" customHeight="1"/>
-    <row r="519" ht="15.75" customHeight="1"/>
-    <row r="520" ht="15.75" customHeight="1"/>
-    <row r="521" ht="15.75" customHeight="1"/>
-    <row r="522" ht="15.75" customHeight="1"/>
-    <row r="523" ht="15.75" customHeight="1"/>
-    <row r="524" ht="15.75" customHeight="1"/>
-    <row r="525" ht="15.75" customHeight="1"/>
-    <row r="526" ht="15.75" customHeight="1"/>
-    <row r="527" ht="15.75" customHeight="1"/>
-    <row r="528" ht="15.75" customHeight="1"/>
-    <row r="529" ht="15.75" customHeight="1"/>
-    <row r="530" ht="15.75" customHeight="1"/>
-    <row r="531" ht="15.75" customHeight="1"/>
-    <row r="532" ht="15.75" customHeight="1"/>
-    <row r="533" ht="15.75" customHeight="1"/>
-    <row r="534" ht="15.75" customHeight="1"/>
-    <row r="535" ht="15.75" customHeight="1"/>
-    <row r="536" ht="15.75" customHeight="1"/>
-    <row r="537" ht="15.75" customHeight="1"/>
-    <row r="538" ht="15.75" customHeight="1"/>
-    <row r="539" ht="15.75" customHeight="1"/>
-    <row r="540" ht="15.75" customHeight="1"/>
-    <row r="541" ht="15.75" customHeight="1"/>
-    <row r="542" ht="15.75" customHeight="1"/>
-    <row r="543" ht="15.75" customHeight="1"/>
-    <row r="544" ht="15.75" customHeight="1"/>
-    <row r="545" ht="15.75" customHeight="1"/>
-    <row r="546" ht="15.75" customHeight="1"/>
-    <row r="547" ht="15.75" customHeight="1"/>
-    <row r="548" ht="15.75" customHeight="1"/>
-    <row r="549" ht="15.75" customHeight="1"/>
-    <row r="550" ht="15.75" customHeight="1"/>
-    <row r="551" ht="15.75" customHeight="1"/>
-    <row r="552" ht="15.75" customHeight="1"/>
-    <row r="553" ht="15.75" customHeight="1"/>
-    <row r="554" ht="15.75" customHeight="1"/>
-    <row r="555" ht="15.75" customHeight="1"/>
-    <row r="556" ht="15.75" customHeight="1"/>
-    <row r="557" ht="15.75" customHeight="1"/>
-    <row r="558" ht="15.75" customHeight="1"/>
-    <row r="559" ht="15.75" customHeight="1"/>
-    <row r="560" ht="15.75" customHeight="1"/>
-    <row r="561" ht="15.75" customHeight="1"/>
-    <row r="562" ht="15.75" customHeight="1"/>
-    <row r="563" ht="15.75" customHeight="1"/>
-    <row r="564" ht="15.75" customHeight="1"/>
-    <row r="565" ht="15.75" customHeight="1"/>
-    <row r="566" ht="15.75" customHeight="1"/>
-    <row r="567" ht="15.75" customHeight="1"/>
-    <row r="568" ht="15.75" customHeight="1"/>
-    <row r="569" ht="15.75" customHeight="1"/>
-    <row r="570" ht="15.75" customHeight="1"/>
-    <row r="571" ht="15.75" customHeight="1"/>
-    <row r="572" ht="15.75" customHeight="1"/>
-    <row r="573" ht="15.75" customHeight="1"/>
-    <row r="574" ht="15.75" customHeight="1"/>
-    <row r="575" ht="15.75" customHeight="1"/>
-    <row r="576" ht="15.75" customHeight="1"/>
-    <row r="577" ht="15.75" customHeight="1"/>
-    <row r="578" ht="15.75" customHeight="1"/>
-    <row r="579" ht="15.75" customHeight="1"/>
-    <row r="580" ht="15.75" customHeight="1"/>
-    <row r="581" ht="15.75" customHeight="1"/>
-    <row r="582" ht="15.75" customHeight="1"/>
-    <row r="583" ht="15.75" customHeight="1"/>
-    <row r="584" ht="15.75" customHeight="1"/>
-    <row r="585" ht="15.75" customHeight="1"/>
-    <row r="586" ht="15.75" customHeight="1"/>
-    <row r="587" ht="15.75" customHeight="1"/>
-    <row r="588" ht="15.75" customHeight="1"/>
-    <row r="589" ht="15.75" customHeight="1"/>
-    <row r="590" ht="15.75" customHeight="1"/>
-    <row r="591" ht="15.75" customHeight="1"/>
-    <row r="592" ht="15.75" customHeight="1"/>
-    <row r="593" ht="15.75" customHeight="1"/>
-    <row r="594" ht="15.75" customHeight="1"/>
-    <row r="595" ht="15.75" customHeight="1"/>
-    <row r="596" ht="15.75" customHeight="1"/>
-    <row r="597" ht="15.75" customHeight="1"/>
-    <row r="598" ht="15.75" customHeight="1"/>
-    <row r="599" ht="15.75" customHeight="1"/>
-    <row r="600" ht="15.75" customHeight="1"/>
-    <row r="601" ht="15.75" customHeight="1"/>
-    <row r="602" ht="15.75" customHeight="1"/>
-    <row r="603" ht="15.75" customHeight="1"/>
-    <row r="604" ht="15.75" customHeight="1"/>
-    <row r="605" ht="15.75" customHeight="1"/>
-    <row r="606" ht="15.75" customHeight="1"/>
-    <row r="607" ht="15.75" customHeight="1"/>
-    <row r="608" ht="15.75" customHeight="1"/>
-    <row r="609" ht="15.75" customHeight="1"/>
-    <row r="610" ht="15.75" customHeight="1"/>
-    <row r="611" ht="15.75" customHeight="1"/>
-    <row r="612" ht="15.75" customHeight="1"/>
-    <row r="613" ht="15.75" customHeight="1"/>
-    <row r="614" ht="15.75" customHeight="1"/>
-    <row r="615" ht="15.75" customHeight="1"/>
-    <row r="616" ht="15.75" customHeight="1"/>
-    <row r="617" ht="15.75" customHeight="1"/>
-    <row r="618" ht="15.75" customHeight="1"/>
-    <row r="619" ht="15.75" customHeight="1"/>
-    <row r="620" ht="15.75" customHeight="1"/>
-    <row r="621" ht="15.75" customHeight="1"/>
-    <row r="622" ht="15.75" customHeight="1"/>
-    <row r="623" ht="15.75" customHeight="1"/>
-    <row r="624" ht="15.75" customHeight="1"/>
-    <row r="625" ht="15.75" customHeight="1"/>
-    <row r="626" ht="15.75" customHeight="1"/>
-    <row r="627" ht="15.75" customHeight="1"/>
-    <row r="628" ht="15.75" customHeight="1"/>
-    <row r="629" ht="15.75" customHeight="1"/>
-    <row r="630" ht="15.75" customHeight="1"/>
-    <row r="631" ht="15.75" customHeight="1"/>
-    <row r="632" ht="15.75" customHeight="1"/>
-    <row r="633" ht="15.75" customHeight="1"/>
-    <row r="634" ht="15.75" customHeight="1"/>
-    <row r="635" ht="15.75" customHeight="1"/>
-    <row r="636" ht="15.75" customHeight="1"/>
-    <row r="637" ht="15.75" customHeight="1"/>
-    <row r="638" ht="15.75" customHeight="1"/>
-    <row r="639" ht="15.75" customHeight="1"/>
-    <row r="640" ht="15.75" customHeight="1"/>
-    <row r="641" ht="15.75" customHeight="1"/>
-    <row r="642" ht="15.75" customHeight="1"/>
-    <row r="643" ht="15.75" customHeight="1"/>
-    <row r="644" ht="15.75" customHeight="1"/>
-    <row r="645" ht="15.75" customHeight="1"/>
-    <row r="646" ht="15.75" customHeight="1"/>
-    <row r="647" ht="15.75" customHeight="1"/>
-    <row r="648" ht="15.75" customHeight="1"/>
-    <row r="649" ht="15.75" customHeight="1"/>
-    <row r="650" ht="15.75" customHeight="1"/>
-    <row r="651" ht="15.75" customHeight="1"/>
-    <row r="652" ht="15.75" customHeight="1"/>
-    <row r="653" ht="15.75" customHeight="1"/>
-    <row r="654" ht="15.75" customHeight="1"/>
-    <row r="655" ht="15.75" customHeight="1"/>
-    <row r="656" ht="15.75" customHeight="1"/>
-    <row r="657" ht="15.75" customHeight="1"/>
-    <row r="658" ht="15.75" customHeight="1"/>
-    <row r="659" ht="15.75" customHeight="1"/>
-    <row r="660" ht="15.75" customHeight="1"/>
-    <row r="661" ht="15.75" customHeight="1"/>
-    <row r="662" ht="15.75" customHeight="1"/>
-    <row r="663" ht="15.75" customHeight="1"/>
-    <row r="664" ht="15.75" customHeight="1"/>
-    <row r="665" ht="15.75" customHeight="1"/>
-    <row r="666" ht="15.75" customHeight="1"/>
-    <row r="667" ht="15.75" customHeight="1"/>
-    <row r="668" ht="15.75" customHeight="1"/>
-    <row r="669" ht="15.75" customHeight="1"/>
-    <row r="670" ht="15.75" customHeight="1"/>
-    <row r="671" ht="15.75" customHeight="1"/>
-    <row r="672" ht="15.75" customHeight="1"/>
-    <row r="673" ht="15.75" customHeight="1"/>
-    <row r="674" ht="15.75" customHeight="1"/>
-    <row r="675" ht="15.75" customHeight="1"/>
-    <row r="676" ht="15.75" customHeight="1"/>
-    <row r="677" ht="15.75" customHeight="1"/>
-    <row r="678" ht="15.75" customHeight="1"/>
-    <row r="679" ht="15.75" customHeight="1"/>
-    <row r="680" ht="15.75" customHeight="1"/>
-    <row r="681" ht="15.75" customHeight="1"/>
-    <row r="682" ht="15.75" customHeight="1"/>
-    <row r="683" ht="15.75" customHeight="1"/>
-    <row r="684" ht="15.75" customHeight="1"/>
-    <row r="685" ht="15.75" customHeight="1"/>
-    <row r="686" ht="15.75" customHeight="1"/>
-    <row r="687" ht="15.75" customHeight="1"/>
-    <row r="688" ht="15.75" customHeight="1"/>
-    <row r="689" ht="15.75" customHeight="1"/>
-    <row r="690" ht="15.75" customHeight="1"/>
-    <row r="691" ht="15.75" customHeight="1"/>
-    <row r="692" ht="15.75" customHeight="1"/>
-    <row r="693" ht="15.75" customHeight="1"/>
-    <row r="694" ht="15.75" customHeight="1"/>
-    <row r="695" ht="15.75" customHeight="1"/>
-    <row r="696" ht="15.75" customHeight="1"/>
-    <row r="697" ht="15.75" customHeight="1"/>
-    <row r="698" ht="15.75" customHeight="1"/>
-    <row r="699" ht="15.75" customHeight="1"/>
-    <row r="700" ht="15.75" customHeight="1"/>
-    <row r="701" ht="15.75" customHeight="1"/>
-    <row r="702" ht="15.75" customHeight="1"/>
-    <row r="703" ht="15.75" customHeight="1"/>
-    <row r="704" ht="15.75" customHeight="1"/>
-    <row r="705" ht="15.75" customHeight="1"/>
-    <row r="706" ht="15.75" customHeight="1"/>
-    <row r="707" ht="15.75" customHeight="1"/>
-    <row r="708" ht="15.75" customHeight="1"/>
-    <row r="709" ht="15.75" customHeight="1"/>
-    <row r="710" ht="15.75" customHeight="1"/>
-    <row r="711" ht="15.75" customHeight="1"/>
-    <row r="712" ht="15.75" customHeight="1"/>
-    <row r="713" ht="15.75" customHeight="1"/>
-    <row r="714" ht="15.75" customHeight="1"/>
-    <row r="715" ht="15.75" customHeight="1"/>
-    <row r="716" ht="15.75" customHeight="1"/>
-    <row r="717" ht="15.75" customHeight="1"/>
-    <row r="718" ht="15.75" customHeight="1"/>
-    <row r="719" ht="15.75" customHeight="1"/>
-    <row r="720" ht="15.75" customHeight="1"/>
-    <row r="721" ht="15.75" customHeight="1"/>
-    <row r="722" ht="15.75" customHeight="1"/>
-    <row r="723" ht="15.75" customHeight="1"/>
-    <row r="724" ht="15.75" customHeight="1"/>
-    <row r="725" ht="15.75" customHeight="1"/>
-    <row r="726" ht="15.75" customHeight="1"/>
-    <row r="727" ht="15.75" customHeight="1"/>
-    <row r="728" ht="15.75" customHeight="1"/>
-    <row r="729" ht="15.75" customHeight="1"/>
-    <row r="730" ht="15.75" customHeight="1"/>
-    <row r="731" ht="15.75" customHeight="1"/>
-    <row r="732" ht="15.75" customHeight="1"/>
-    <row r="733" ht="15.75" customHeight="1"/>
-    <row r="734" ht="15.75" customHeight="1"/>
-    <row r="735" ht="15.75" customHeight="1"/>
-    <row r="736" ht="15.75" customHeight="1"/>
-    <row r="737" ht="15.75" customHeight="1"/>
-    <row r="738" ht="15.75" customHeight="1"/>
-    <row r="739" ht="15.75" customHeight="1"/>
-    <row r="740" ht="15.75" customHeight="1"/>
-    <row r="741" ht="15.75" customHeight="1"/>
-    <row r="742" ht="15.75" customHeight="1"/>
-    <row r="743" ht="15.75" customHeight="1"/>
-    <row r="744" ht="15.75" customHeight="1"/>
-    <row r="745" ht="15.75" customHeight="1"/>
-    <row r="746" ht="15.75" customHeight="1"/>
-    <row r="747" ht="15.75" customHeight="1"/>
-    <row r="748" ht="15.75" customHeight="1"/>
-    <row r="749" ht="15.75" customHeight="1"/>
-    <row r="750" ht="15.75" customHeight="1"/>
-    <row r="751" ht="15.75" customHeight="1"/>
-    <row r="752" ht="15.75" customHeight="1"/>
-    <row r="753" ht="15.75" customHeight="1"/>
-    <row r="754" ht="15.75" customHeight="1"/>
-    <row r="755" ht="15.75" customHeight="1"/>
-    <row r="756" ht="15.75" customHeight="1"/>
-    <row r="757" ht="15.75" customHeight="1"/>
-    <row r="758" ht="15.75" customHeight="1"/>
-    <row r="759" ht="15.75" customHeight="1"/>
-    <row r="760" ht="15.75" customHeight="1"/>
-    <row r="761" ht="15.75" customHeight="1"/>
-    <row r="762" ht="15.75" customHeight="1"/>
-    <row r="763" ht="15.75" customHeight="1"/>
-    <row r="764" ht="15.75" customHeight="1"/>
-    <row r="765" ht="15.75" customHeight="1"/>
-    <row r="766" ht="15.75" customHeight="1"/>
-    <row r="767" ht="15.75" customHeight="1"/>
-    <row r="768" ht="15.75" customHeight="1"/>
-    <row r="769" ht="15.75" customHeight="1"/>
-    <row r="770" ht="15.75" customHeight="1"/>
-    <row r="771" ht="15.75" customHeight="1"/>
-    <row r="772" ht="15.75" customHeight="1"/>
-    <row r="773" ht="15.75" customHeight="1"/>
-    <row r="774" ht="15.75" customHeight="1"/>
-    <row r="775" ht="15.75" customHeight="1"/>
-    <row r="776" ht="15.75" customHeight="1"/>
-    <row r="777" ht="15.75" customHeight="1"/>
-    <row r="778" ht="15.75" customHeight="1"/>
-    <row r="779" ht="15.75" customHeight="1"/>
-    <row r="780" ht="15.75" customHeight="1"/>
-    <row r="781" ht="15.75" customHeight="1"/>
-    <row r="782" ht="15.75" customHeight="1"/>
-    <row r="783" ht="15.75" customHeight="1"/>
-    <row r="784" ht="15.75" customHeight="1"/>
-    <row r="785" ht="15.75" customHeight="1"/>
-    <row r="786" ht="15.75" customHeight="1"/>
-    <row r="787" ht="15.75" customHeight="1"/>
-    <row r="788" ht="15.75" customHeight="1"/>
-    <row r="789" ht="15.75" customHeight="1"/>
-    <row r="790" ht="15.75" customHeight="1"/>
-    <row r="791" ht="15.75" customHeight="1"/>
-    <row r="792" ht="15.75" customHeight="1"/>
-    <row r="793" ht="15.75" customHeight="1"/>
-    <row r="794" ht="15.75" customHeight="1"/>
-    <row r="795" ht="15.75" customHeight="1"/>
-    <row r="796" ht="15.75" customHeight="1"/>
-    <row r="797" ht="15.75" customHeight="1"/>
-    <row r="798" ht="15.75" customHeight="1"/>
-    <row r="799" ht="15.75" customHeight="1"/>
-    <row r="800" ht="15.75" customHeight="1"/>
-    <row r="801" ht="15.75" customHeight="1"/>
-    <row r="802" ht="15.75" customHeight="1"/>
-    <row r="803" ht="15.75" customHeight="1"/>
-    <row r="804" ht="15.75" customHeight="1"/>
-    <row r="805" ht="15.75" customHeight="1"/>
-    <row r="806" ht="15.75" customHeight="1"/>
-    <row r="807" ht="15.75" customHeight="1"/>
-    <row r="808" ht="15.75" customHeight="1"/>
-    <row r="809" ht="15.75" customHeight="1"/>
-    <row r="810" ht="15.75" customHeight="1"/>
-    <row r="811" ht="15.75" customHeight="1"/>
-    <row r="812" ht="15.75" customHeight="1"/>
-    <row r="813" ht="15.75" customHeight="1"/>
-    <row r="814" ht="15.75" customHeight="1"/>
-    <row r="815" ht="15.75" customHeight="1"/>
-    <row r="816" ht="15.75" customHeight="1"/>
-    <row r="817" ht="15.75" customHeight="1"/>
-    <row r="818" ht="15.75" customHeight="1"/>
-    <row r="819" ht="15.75" customHeight="1"/>
-    <row r="820" ht="15.75" customHeight="1"/>
-    <row r="821" ht="15.75" customHeight="1"/>
-    <row r="822" ht="15.75" customHeight="1"/>
-    <row r="823" ht="15.75" customHeight="1"/>
-    <row r="824" ht="15.75" customHeight="1"/>
-    <row r="825" ht="15.75" customHeight="1"/>
-    <row r="826" ht="15.75" customHeight="1"/>
-    <row r="827" ht="15.75" customHeight="1"/>
-    <row r="828" ht="15.75" customHeight="1"/>
-    <row r="829" ht="15.75" customHeight="1"/>
-    <row r="830" ht="15.75" customHeight="1"/>
-    <row r="831" ht="15.75" customHeight="1"/>
-    <row r="832" ht="15.75" customHeight="1"/>
-    <row r="833" ht="15.75" customHeight="1"/>
-    <row r="834" ht="15.75" customHeight="1"/>
-    <row r="835" ht="15.75" customHeight="1"/>
-    <row r="836" ht="15.75" customHeight="1"/>
-    <row r="837" ht="15.75" customHeight="1"/>
-    <row r="838" ht="15.75" customHeight="1"/>
-    <row r="839" ht="15.75" customHeight="1"/>
-    <row r="840" ht="15.75" customHeight="1"/>
-    <row r="841" ht="15.75" customHeight="1"/>
-    <row r="842" ht="15.75" customHeight="1"/>
-    <row r="843" ht="15.75" customHeight="1"/>
-    <row r="844" ht="15.75" customHeight="1"/>
-    <row r="845" ht="15.75" customHeight="1"/>
-    <row r="846" ht="15.75" customHeight="1"/>
-    <row r="847" ht="15.75" customHeight="1"/>
-    <row r="848" ht="15.75" customHeight="1"/>
-    <row r="849" ht="15.75" customHeight="1"/>
-    <row r="850" ht="15.75" customHeight="1"/>
-    <row r="851" ht="15.75" customHeight="1"/>
-    <row r="852" ht="15.75" customHeight="1"/>
-    <row r="853" ht="15.75" customHeight="1"/>
-    <row r="854" ht="15.75" customHeight="1"/>
-    <row r="855" ht="15.75" customHeight="1"/>
-    <row r="856" ht="15.75" customHeight="1"/>
-    <row r="857" ht="15.75" customHeight="1"/>
-    <row r="858" ht="15.75" customHeight="1"/>
-    <row r="859" ht="15.75" customHeight="1"/>
-    <row r="860" ht="15.75" customHeight="1"/>
-    <row r="861" ht="15.75" customHeight="1"/>
-    <row r="862" ht="15.75" customHeight="1"/>
-    <row r="863" ht="15.75" customHeight="1"/>
-    <row r="864" ht="15.75" customHeight="1"/>
-    <row r="865" ht="15.75" customHeight="1"/>
-    <row r="866" ht="15.75" customHeight="1"/>
-    <row r="867" ht="15.75" customHeight="1"/>
-    <row r="868" ht="15.75" customHeight="1"/>
-    <row r="869" ht="15.75" customHeight="1"/>
-    <row r="870" ht="15.75" customHeight="1"/>
-    <row r="871" ht="15.75" customHeight="1"/>
-    <row r="872" ht="15.75" customHeight="1"/>
-    <row r="873" ht="15.75" customHeight="1"/>
-    <row r="874" ht="15.75" customHeight="1"/>
-    <row r="875" ht="15.75" customHeight="1"/>
-    <row r="876" ht="15.75" customHeight="1"/>
-    <row r="877" ht="15.75" customHeight="1"/>
-    <row r="878" ht="15.75" customHeight="1"/>
-    <row r="879" ht="15.75" customHeight="1"/>
-    <row r="880" ht="15.75" customHeight="1"/>
-    <row r="881" ht="15.75" customHeight="1"/>
-    <row r="882" ht="15.75" customHeight="1"/>
-    <row r="883" ht="15.75" customHeight="1"/>
-    <row r="884" ht="15.75" customHeight="1"/>
-    <row r="885" ht="15.75" customHeight="1"/>
-    <row r="886" ht="15.75" customHeight="1"/>
-    <row r="887" ht="15.75" customHeight="1"/>
-    <row r="888" ht="15.75" customHeight="1"/>
-    <row r="889" ht="15.75" customHeight="1"/>
-    <row r="890" ht="15.75" customHeight="1"/>
-    <row r="891" ht="15.75" customHeight="1"/>
-    <row r="892" ht="15.75" customHeight="1"/>
-    <row r="893" ht="15.75" customHeight="1"/>
-    <row r="894" ht="15.75" customHeight="1"/>
-    <row r="895" ht="15.75" customHeight="1"/>
-    <row r="896" ht="15.75" customHeight="1"/>
-    <row r="897" ht="15.75" customHeight="1"/>
-    <row r="898" ht="15.75" customHeight="1"/>
-    <row r="899" ht="15.75" customHeight="1"/>
-    <row r="900" ht="15.75" customHeight="1"/>
-    <row r="901" ht="15.75" customHeight="1"/>
-    <row r="902" ht="15.75" customHeight="1"/>
-    <row r="903" ht="15.75" customHeight="1"/>
-    <row r="904" ht="15.75" customHeight="1"/>
-    <row r="905" ht="15.75" customHeight="1"/>
-    <row r="906" ht="15.75" customHeight="1"/>
-    <row r="907" ht="15.75" customHeight="1"/>
-    <row r="908" ht="15.75" customHeight="1"/>
-    <row r="909" ht="15.75" customHeight="1"/>
-    <row r="910" ht="15.75" customHeight="1"/>
-    <row r="911" ht="15.75" customHeight="1"/>
-    <row r="912" ht="15.75" customHeight="1"/>
-    <row r="913" ht="15.75" customHeight="1"/>
-    <row r="914" ht="15.75" customHeight="1"/>
-    <row r="915" ht="15.75" customHeight="1"/>
-    <row r="916" ht="15.75" customHeight="1"/>
-    <row r="917" ht="15.75" customHeight="1"/>
-    <row r="918" ht="15.75" customHeight="1"/>
-    <row r="919" ht="15.75" customHeight="1"/>
-    <row r="920" ht="15.75" customHeight="1"/>
-    <row r="921" ht="15.75" customHeight="1"/>
-    <row r="922" ht="15.75" customHeight="1"/>
-    <row r="923" ht="15.75" customHeight="1"/>
-    <row r="924" ht="15.75" customHeight="1"/>
-    <row r="925" ht="15.75" customHeight="1"/>
-    <row r="926" ht="15.75" customHeight="1"/>
-    <row r="927" ht="15.75" customHeight="1"/>
-    <row r="928" ht="15.75" customHeight="1"/>
-    <row r="929" ht="15.75" customHeight="1"/>
-    <row r="930" ht="15.75" customHeight="1"/>
-    <row r="931" ht="15.75" customHeight="1"/>
-    <row r="932" ht="15.75" customHeight="1"/>
-    <row r="933" ht="15.75" customHeight="1"/>
-    <row r="934" ht="15.75" customHeight="1"/>
-    <row r="935" ht="15.75" customHeight="1"/>
-    <row r="936" ht="15.75" customHeight="1"/>
-    <row r="937" ht="15.75" customHeight="1"/>
-    <row r="938" ht="15.75" customHeight="1"/>
-    <row r="939" ht="15.75" customHeight="1"/>
-    <row r="940" ht="15.75" customHeight="1"/>
-    <row r="941" ht="15.75" customHeight="1"/>
-    <row r="942" ht="15.75" customHeight="1"/>
-    <row r="943" ht="15.75" customHeight="1"/>
-    <row r="944" ht="15.75" customHeight="1"/>
-    <row r="945" ht="15.75" customHeight="1"/>
-    <row r="946" ht="15.75" customHeight="1"/>
-    <row r="947" ht="15.75" customHeight="1"/>
-    <row r="948" ht="15.75" customHeight="1"/>
-    <row r="949" ht="15.75" customHeight="1"/>
-    <row r="950" ht="15.75" customHeight="1"/>
-    <row r="951" ht="15.75" customHeight="1"/>
-    <row r="952" ht="15.75" customHeight="1"/>
-    <row r="953" ht="15.75" customHeight="1"/>
-    <row r="954" ht="15.75" customHeight="1"/>
-    <row r="955" ht="15.75" customHeight="1"/>
-    <row r="956" ht="15.75" customHeight="1"/>
-    <row r="957" ht="15.75" customHeight="1"/>
-    <row r="958" ht="15.75" customHeight="1"/>
-    <row r="959" ht="15.75" customHeight="1"/>
-    <row r="960" ht="15.75" customHeight="1"/>
-    <row r="961" ht="15.75" customHeight="1"/>
-    <row r="962" ht="15.75" customHeight="1"/>
-    <row r="963" ht="15.75" customHeight="1"/>
-    <row r="964" ht="15.75" customHeight="1"/>
-    <row r="965" ht="15.75" customHeight="1"/>
-    <row r="966" ht="15.75" customHeight="1"/>
-    <row r="967" ht="15.75" customHeight="1"/>
-    <row r="968" ht="15.75" customHeight="1"/>
-    <row r="969" ht="15.75" customHeight="1"/>
-    <row r="970" ht="15.75" customHeight="1"/>
-    <row r="971" ht="15.75" customHeight="1"/>
-    <row r="972" ht="15.75" customHeight="1"/>
-    <row r="973" ht="15.75" customHeight="1"/>
-    <row r="974" ht="15.75" customHeight="1"/>
-    <row r="975" ht="15.75" customHeight="1"/>
-    <row r="976" ht="15.75" customHeight="1"/>
-    <row r="977" ht="15.75" customHeight="1"/>
-    <row r="978" ht="15.75" customHeight="1"/>
-    <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
-    <row r="981" ht="15.75" customHeight="1"/>
-    <row r="982" ht="15.75" customHeight="1"/>
-    <row r="983" ht="15.75" customHeight="1"/>
-    <row r="984" ht="15.75" customHeight="1"/>
-    <row r="985" ht="15.75" customHeight="1"/>
-    <row r="986" ht="15.75" customHeight="1"/>
-    <row r="987" ht="15.75" customHeight="1"/>
-    <row r="988" ht="15.75" customHeight="1"/>
-    <row r="989" ht="15.75" customHeight="1"/>
-    <row r="990" ht="15.75" customHeight="1"/>
-    <row r="991" ht="15.75" customHeight="1"/>
-    <row r="992" ht="15.75" customHeight="1"/>
-    <row r="993" ht="15.75" customHeight="1"/>
-    <row r="994" ht="15.75" customHeight="1"/>
-    <row r="995" ht="15.75" customHeight="1"/>
-    <row r="996" ht="15.75" customHeight="1"/>
-    <row r="997" ht="15.75" customHeight="1"/>
-    <row r="998" ht="15.75" customHeight="1"/>
-    <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
+    </row>
+    <row r="221" ht="15.75" customHeight="1">
+      <c r="A221" s="7"/>
+      <c r="B221" s="7"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1">
+      <c r="A222" s="7"/>
+      <c r="B222" s="7"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1">
+      <c r="A223" s="7"/>
+      <c r="B223" s="7"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1">
+      <c r="A224" s="7"/>
+      <c r="B224" s="7"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1">
+      <c r="A225" s="7"/>
+      <c r="B225" s="7"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1">
+      <c r="A226" s="7"/>
+      <c r="B226" s="7"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1">
+      <c r="A227" s="7"/>
+      <c r="B227" s="7"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1">
+      <c r="A228" s="7"/>
+      <c r="B228" s="7"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1">
+      <c r="A229" s="7"/>
+      <c r="B229" s="7"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1">
+      <c r="A230" s="7"/>
+      <c r="B230" s="7"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1">
+      <c r="A231" s="7"/>
+      <c r="B231" s="7"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1">
+      <c r="A232" s="7"/>
+      <c r="B232" s="7"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1">
+      <c r="A233" s="7"/>
+      <c r="B233" s="7"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1">
+      <c r="A234" s="7"/>
+      <c r="B234" s="7"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1">
+      <c r="A235" s="7"/>
+      <c r="B235" s="7"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1">
+      <c r="A236" s="7"/>
+      <c r="B236" s="7"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1">
+      <c r="A237" s="7"/>
+      <c r="B237" s="7"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1">
+      <c r="A238" s="7"/>
+      <c r="B238" s="7"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1">
+      <c r="A239" s="7"/>
+      <c r="B239" s="7"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1">
+      <c r="A240" s="7"/>
+      <c r="B240" s="7"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1">
+      <c r="A241" s="7"/>
+      <c r="B241" s="7"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1">
+      <c r="A242" s="7"/>
+      <c r="B242" s="7"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1">
+      <c r="A243" s="7"/>
+      <c r="B243" s="7"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1">
+      <c r="A244" s="7"/>
+      <c r="B244" s="7"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1">
+      <c r="A245" s="7"/>
+      <c r="B245" s="7"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1">
+      <c r="A246" s="7"/>
+      <c r="B246" s="7"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1">
+      <c r="A247" s="7"/>
+      <c r="B247" s="7"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1">
+      <c r="A248" s="7"/>
+      <c r="B248" s="7"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1">
+      <c r="A249" s="7"/>
+      <c r="B249" s="7"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1">
+      <c r="A250" s="7"/>
+      <c r="B250" s="7"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1">
+      <c r="A251" s="7"/>
+      <c r="B251" s="7"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1">
+      <c r="A252" s="7"/>
+      <c r="B252" s="7"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1">
+      <c r="A253" s="7"/>
+      <c r="B253" s="7"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1">
+      <c r="A254" s="7"/>
+      <c r="B254" s="7"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1">
+      <c r="A255" s="7"/>
+      <c r="B255" s="7"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1">
+      <c r="A256" s="7"/>
+      <c r="B256" s="7"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1">
+      <c r="A257" s="7"/>
+      <c r="B257" s="7"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1">
+      <c r="A258" s="7"/>
+      <c r="B258" s="7"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1">
+      <c r="A259" s="7"/>
+      <c r="B259" s="7"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1">
+      <c r="A260" s="7"/>
+      <c r="B260" s="7"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1">
+      <c r="A261" s="7"/>
+      <c r="B261" s="7"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1">
+      <c r="A262" s="7"/>
+      <c r="B262" s="7"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1">
+      <c r="A263" s="7"/>
+      <c r="B263" s="7"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1">
+      <c r="A264" s="7"/>
+      <c r="B264" s="7"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1">
+      <c r="A265" s="7"/>
+      <c r="B265" s="7"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1">
+      <c r="A266" s="7"/>
+      <c r="B266" s="7"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1">
+      <c r="A267" s="7"/>
+      <c r="B267" s="7"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1">
+      <c r="A268" s="7"/>
+      <c r="B268" s="7"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1">
+      <c r="A269" s="7"/>
+      <c r="B269" s="7"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1">
+      <c r="A270" s="7"/>
+      <c r="B270" s="7"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1">
+      <c r="A271" s="7"/>
+      <c r="B271" s="7"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1">
+      <c r="A272" s="7"/>
+      <c r="B272" s="7"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1">
+      <c r="A273" s="7"/>
+      <c r="B273" s="7"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1">
+      <c r="A274" s="7"/>
+      <c r="B274" s="7"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1">
+      <c r="A275" s="7"/>
+      <c r="B275" s="7"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1">
+      <c r="A276" s="7"/>
+      <c r="B276" s="7"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1">
+      <c r="A277" s="7"/>
+      <c r="B277" s="7"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1">
+      <c r="A278" s="7"/>
+      <c r="B278" s="7"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1">
+      <c r="A279" s="7"/>
+      <c r="B279" s="7"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1">
+      <c r="A280" s="7"/>
+      <c r="B280" s="7"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1">
+      <c r="A281" s="7"/>
+      <c r="B281" s="7"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1">
+      <c r="A282" s="7"/>
+      <c r="B282" s="7"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1">
+      <c r="A283" s="7"/>
+      <c r="B283" s="7"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1">
+      <c r="A284" s="7"/>
+      <c r="B284" s="7"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1">
+      <c r="A285" s="7"/>
+      <c r="B285" s="7"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1">
+      <c r="A286" s="7"/>
+      <c r="B286" s="7"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1">
+      <c r="A287" s="7"/>
+      <c r="B287" s="7"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1">
+      <c r="A288" s="7"/>
+      <c r="B288" s="7"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1">
+      <c r="A289" s="7"/>
+      <c r="B289" s="7"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1">
+      <c r="A290" s="7"/>
+      <c r="B290" s="7"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1">
+      <c r="A291" s="7"/>
+      <c r="B291" s="7"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1">
+      <c r="A292" s="7"/>
+      <c r="B292" s="7"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1">
+      <c r="A293" s="7"/>
+      <c r="B293" s="7"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1">
+      <c r="A294" s="7"/>
+      <c r="B294" s="7"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1">
+      <c r="A295" s="7"/>
+      <c r="B295" s="7"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1">
+      <c r="A296" s="7"/>
+      <c r="B296" s="7"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1">
+      <c r="A297" s="7"/>
+      <c r="B297" s="7"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1">
+      <c r="A298" s="7"/>
+      <c r="B298" s="7"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1">
+      <c r="A299" s="7"/>
+      <c r="B299" s="7"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1">
+      <c r="A300" s="7"/>
+      <c r="B300" s="7"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1">
+      <c r="A301" s="7"/>
+      <c r="B301" s="7"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1">
+      <c r="A302" s="7"/>
+      <c r="B302" s="7"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1">
+      <c r="A303" s="7"/>
+      <c r="B303" s="7"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1">
+      <c r="A304" s="7"/>
+      <c r="B304" s="7"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1">
+      <c r="A305" s="7"/>
+      <c r="B305" s="7"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1">
+      <c r="A306" s="7"/>
+      <c r="B306" s="7"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1">
+      <c r="A307" s="7"/>
+      <c r="B307" s="7"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1">
+      <c r="A308" s="7"/>
+      <c r="B308" s="7"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1">
+      <c r="A309" s="7"/>
+      <c r="B309" s="7"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1">
+      <c r="A310" s="7"/>
+      <c r="B310" s="7"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1">
+      <c r="A311" s="7"/>
+      <c r="B311" s="7"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1">
+      <c r="A312" s="7"/>
+      <c r="B312" s="7"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1">
+      <c r="A313" s="7"/>
+      <c r="B313" s="7"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1">
+      <c r="A314" s="7"/>
+      <c r="B314" s="7"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1">
+      <c r="A315" s="7"/>
+      <c r="B315" s="7"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1">
+      <c r="A316" s="7"/>
+      <c r="B316" s="7"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1">
+      <c r="A317" s="7"/>
+      <c r="B317" s="7"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1">
+      <c r="A318" s="7"/>
+      <c r="B318" s="7"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1">
+      <c r="A319" s="7"/>
+      <c r="B319" s="7"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1">
+      <c r="A320" s="7"/>
+      <c r="B320" s="7"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1">
+      <c r="A321" s="7"/>
+      <c r="B321" s="7"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1">
+      <c r="A322" s="7"/>
+      <c r="B322" s="7"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1">
+      <c r="A323" s="7"/>
+      <c r="B323" s="7"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1">
+      <c r="A324" s="7"/>
+      <c r="B324" s="7"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1">
+      <c r="A325" s="7"/>
+      <c r="B325" s="7"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1">
+      <c r="A326" s="7"/>
+      <c r="B326" s="7"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1">
+      <c r="A327" s="7"/>
+      <c r="B327" s="7"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1">
+      <c r="A328" s="7"/>
+      <c r="B328" s="7"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1">
+      <c r="A329" s="7"/>
+      <c r="B329" s="7"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1">
+      <c r="A330" s="7"/>
+      <c r="B330" s="7"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1">
+      <c r="A331" s="7"/>
+      <c r="B331" s="7"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1">
+      <c r="A332" s="7"/>
+      <c r="B332" s="7"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1">
+      <c r="A333" s="7"/>
+      <c r="B333" s="7"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1">
+      <c r="A334" s="7"/>
+      <c r="B334" s="7"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1">
+      <c r="A335" s="7"/>
+      <c r="B335" s="7"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1">
+      <c r="A336" s="7"/>
+      <c r="B336" s="7"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1">
+      <c r="A337" s="7"/>
+      <c r="B337" s="7"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1">
+      <c r="A338" s="7"/>
+      <c r="B338" s="7"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1">
+      <c r="A339" s="7"/>
+      <c r="B339" s="7"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1">
+      <c r="A340" s="7"/>
+      <c r="B340" s="7"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1">
+      <c r="A341" s="7"/>
+      <c r="B341" s="7"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1">
+      <c r="A342" s="7"/>
+      <c r="B342" s="7"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1">
+      <c r="A343" s="7"/>
+      <c r="B343" s="7"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1">
+      <c r="A344" s="7"/>
+      <c r="B344" s="7"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1">
+      <c r="A345" s="7"/>
+      <c r="B345" s="7"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1">
+      <c r="A346" s="7"/>
+      <c r="B346" s="7"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1">
+      <c r="A347" s="7"/>
+      <c r="B347" s="7"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1">
+      <c r="A348" s="7"/>
+      <c r="B348" s="7"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1">
+      <c r="A349" s="7"/>
+      <c r="B349" s="7"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1">
+      <c r="A350" s="7"/>
+      <c r="B350" s="7"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1">
+      <c r="A351" s="7"/>
+      <c r="B351" s="7"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1">
+      <c r="A352" s="7"/>
+      <c r="B352" s="7"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1">
+      <c r="A353" s="7"/>
+      <c r="B353" s="7"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1">
+      <c r="A354" s="7"/>
+      <c r="B354" s="7"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1">
+      <c r="A355" s="7"/>
+      <c r="B355" s="7"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1">
+      <c r="A356" s="7"/>
+      <c r="B356" s="7"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1">
+      <c r="A357" s="7"/>
+      <c r="B357" s="7"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1">
+      <c r="A358" s="7"/>
+      <c r="B358" s="7"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1">
+      <c r="A359" s="7"/>
+      <c r="B359" s="7"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1">
+      <c r="A360" s="7"/>
+      <c r="B360" s="7"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1">
+      <c r="A361" s="7"/>
+      <c r="B361" s="7"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1">
+      <c r="A362" s="7"/>
+      <c r="B362" s="7"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1">
+      <c r="A363" s="7"/>
+      <c r="B363" s="7"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1">
+      <c r="A364" s="7"/>
+      <c r="B364" s="7"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1">
+      <c r="A365" s="7"/>
+      <c r="B365" s="7"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1">
+      <c r="A366" s="7"/>
+      <c r="B366" s="7"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1">
+      <c r="A367" s="7"/>
+      <c r="B367" s="7"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1">
+      <c r="A368" s="7"/>
+      <c r="B368" s="7"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1">
+      <c r="A369" s="7"/>
+      <c r="B369" s="7"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1">
+      <c r="A370" s="7"/>
+      <c r="B370" s="7"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1">
+      <c r="A371" s="7"/>
+      <c r="B371" s="7"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1">
+      <c r="A372" s="7"/>
+      <c r="B372" s="7"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1">
+      <c r="A373" s="7"/>
+      <c r="B373" s="7"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1">
+      <c r="A374" s="7"/>
+      <c r="B374" s="7"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1">
+      <c r="A375" s="7"/>
+      <c r="B375" s="7"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1">
+      <c r="A376" s="7"/>
+      <c r="B376" s="7"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1">
+      <c r="A377" s="7"/>
+      <c r="B377" s="7"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1">
+      <c r="A378" s="7"/>
+      <c r="B378" s="7"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1">
+      <c r="A379" s="7"/>
+      <c r="B379" s="7"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1">
+      <c r="A380" s="7"/>
+      <c r="B380" s="7"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1">
+      <c r="A381" s="7"/>
+      <c r="B381" s="7"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1">
+      <c r="A382" s="7"/>
+      <c r="B382" s="7"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1">
+      <c r="A383" s="7"/>
+      <c r="B383" s="7"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1">
+      <c r="A384" s="7"/>
+      <c r="B384" s="7"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1">
+      <c r="A385" s="7"/>
+      <c r="B385" s="7"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1">
+      <c r="A386" s="7"/>
+      <c r="B386" s="7"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1">
+      <c r="A387" s="7"/>
+      <c r="B387" s="7"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1">
+      <c r="A388" s="7"/>
+      <c r="B388" s="7"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1">
+      <c r="A389" s="7"/>
+      <c r="B389" s="7"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1">
+      <c r="A390" s="7"/>
+      <c r="B390" s="7"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1">
+      <c r="A391" s="7"/>
+      <c r="B391" s="7"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1">
+      <c r="A392" s="7"/>
+      <c r="B392" s="7"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1">
+      <c r="A393" s="7"/>
+      <c r="B393" s="7"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1">
+      <c r="A394" s="7"/>
+      <c r="B394" s="7"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1">
+      <c r="A395" s="7"/>
+      <c r="B395" s="7"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1">
+      <c r="A396" s="7"/>
+      <c r="B396" s="7"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1">
+      <c r="A397" s="7"/>
+      <c r="B397" s="7"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1">
+      <c r="A398" s="7"/>
+      <c r="B398" s="7"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1">
+      <c r="A399" s="7"/>
+      <c r="B399" s="7"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1">
+      <c r="A400" s="7"/>
+      <c r="B400" s="7"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1">
+      <c r="A401" s="7"/>
+      <c r="B401" s="7"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1">
+      <c r="A402" s="7"/>
+      <c r="B402" s="7"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1">
+      <c r="A403" s="7"/>
+      <c r="B403" s="7"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1">
+      <c r="A404" s="7"/>
+      <c r="B404" s="7"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1">
+      <c r="A405" s="7"/>
+      <c r="B405" s="7"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1">
+      <c r="A406" s="7"/>
+      <c r="B406" s="7"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1">
+      <c r="A407" s="7"/>
+      <c r="B407" s="7"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1">
+      <c r="A408" s="7"/>
+      <c r="B408" s="7"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1">
+      <c r="A409" s="7"/>
+      <c r="B409" s="7"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1">
+      <c r="A410" s="7"/>
+      <c r="B410" s="7"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1">
+      <c r="A411" s="7"/>
+      <c r="B411" s="7"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1">
+      <c r="A412" s="7"/>
+      <c r="B412" s="7"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1">
+      <c r="A413" s="7"/>
+      <c r="B413" s="7"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1">
+      <c r="A414" s="7"/>
+      <c r="B414" s="7"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1">
+      <c r="A415" s="7"/>
+      <c r="B415" s="7"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1">
+      <c r="A416" s="7"/>
+      <c r="B416" s="7"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1">
+      <c r="A417" s="7"/>
+      <c r="B417" s="7"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1">
+      <c r="A418" s="7"/>
+      <c r="B418" s="7"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1">
+      <c r="A419" s="7"/>
+      <c r="B419" s="7"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1">
+      <c r="A420" s="7"/>
+      <c r="B420" s="7"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1">
+      <c r="A421" s="7"/>
+      <c r="B421" s="7"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1">
+      <c r="A422" s="7"/>
+      <c r="B422" s="7"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1">
+      <c r="A423" s="7"/>
+      <c r="B423" s="7"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1">
+      <c r="A424" s="7"/>
+      <c r="B424" s="7"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1">
+      <c r="A425" s="7"/>
+      <c r="B425" s="7"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1">
+      <c r="A426" s="7"/>
+      <c r="B426" s="7"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1">
+      <c r="A427" s="7"/>
+      <c r="B427" s="7"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1">
+      <c r="A428" s="7"/>
+      <c r="B428" s="7"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1">
+      <c r="A429" s="7"/>
+      <c r="B429" s="7"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1">
+      <c r="A430" s="7"/>
+      <c r="B430" s="7"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1">
+      <c r="A431" s="7"/>
+      <c r="B431" s="7"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1">
+      <c r="A432" s="7"/>
+      <c r="B432" s="7"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1">
+      <c r="A433" s="7"/>
+      <c r="B433" s="7"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1">
+      <c r="A434" s="7"/>
+      <c r="B434" s="7"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1">
+      <c r="A435" s="7"/>
+      <c r="B435" s="7"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1">
+      <c r="A436" s="7"/>
+      <c r="B436" s="7"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="A437" s="7"/>
+      <c r="B437" s="7"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1">
+      <c r="A438" s="7"/>
+      <c r="B438" s="7"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1">
+      <c r="A439" s="7"/>
+      <c r="B439" s="7"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1">
+      <c r="A440" s="7"/>
+      <c r="B440" s="7"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1">
+      <c r="A441" s="7"/>
+      <c r="B441" s="7"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1">
+      <c r="A442" s="7"/>
+      <c r="B442" s="7"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1">
+      <c r="A443" s="7"/>
+      <c r="B443" s="7"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1">
+      <c r="A444" s="7"/>
+      <c r="B444" s="7"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1">
+      <c r="A445" s="7"/>
+      <c r="B445" s="7"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1">
+      <c r="A446" s="7"/>
+      <c r="B446" s="7"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1">
+      <c r="A447" s="7"/>
+      <c r="B447" s="7"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1">
+      <c r="A448" s="7"/>
+      <c r="B448" s="7"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1">
+      <c r="A449" s="7"/>
+      <c r="B449" s="7"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1">
+      <c r="A450" s="7"/>
+      <c r="B450" s="7"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1">
+      <c r="A451" s="7"/>
+      <c r="B451" s="7"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1">
+      <c r="A452" s="7"/>
+      <c r="B452" s="7"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1">
+      <c r="A453" s="7"/>
+      <c r="B453" s="7"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1">
+      <c r="A454" s="7"/>
+      <c r="B454" s="7"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1">
+      <c r="A455" s="7"/>
+      <c r="B455" s="7"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1">
+      <c r="A456" s="7"/>
+      <c r="B456" s="7"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1">
+      <c r="A457" s="7"/>
+      <c r="B457" s="7"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1">
+      <c r="A458" s="7"/>
+      <c r="B458" s="7"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1">
+      <c r="A459" s="7"/>
+      <c r="B459" s="7"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1">
+      <c r="A460" s="7"/>
+      <c r="B460" s="7"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1">
+      <c r="A461" s="7"/>
+      <c r="B461" s="7"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1">
+      <c r="A462" s="7"/>
+      <c r="B462" s="7"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1">
+      <c r="A463" s="7"/>
+      <c r="B463" s="7"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1">
+      <c r="A464" s="7"/>
+      <c r="B464" s="7"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1">
+      <c r="A465" s="7"/>
+      <c r="B465" s="7"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1">
+      <c r="A466" s="7"/>
+      <c r="B466" s="7"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1">
+      <c r="A467" s="7"/>
+      <c r="B467" s="7"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1">
+      <c r="A468" s="7"/>
+      <c r="B468" s="7"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1">
+      <c r="A469" s="7"/>
+      <c r="B469" s="7"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1">
+      <c r="A470" s="7"/>
+      <c r="B470" s="7"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1">
+      <c r="A471" s="7"/>
+      <c r="B471" s="7"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1">
+      <c r="A472" s="7"/>
+      <c r="B472" s="7"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1">
+      <c r="A473" s="7"/>
+      <c r="B473" s="7"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1">
+      <c r="A474" s="7"/>
+      <c r="B474" s="7"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1">
+      <c r="A475" s="7"/>
+      <c r="B475" s="7"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="A476" s="7"/>
+      <c r="B476" s="7"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="A477" s="7"/>
+      <c r="B477" s="7"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="A478" s="7"/>
+      <c r="B478" s="7"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="A479" s="7"/>
+      <c r="B479" s="7"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="A480" s="7"/>
+      <c r="B480" s="7"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="A481" s="7"/>
+      <c r="B481" s="7"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="A482" s="7"/>
+      <c r="B482" s="7"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1">
+      <c r="A483" s="7"/>
+      <c r="B483" s="7"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1">
+      <c r="A484" s="7"/>
+      <c r="B484" s="7"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1">
+      <c r="A485" s="7"/>
+      <c r="B485" s="7"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1">
+      <c r="A486" s="7"/>
+      <c r="B486" s="7"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="A487" s="7"/>
+      <c r="B487" s="7"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="A488" s="7"/>
+      <c r="B488" s="7"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="A489" s="7"/>
+      <c r="B489" s="7"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="A490" s="7"/>
+      <c r="B490" s="7"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="A491" s="7"/>
+      <c r="B491" s="7"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="A492" s="7"/>
+      <c r="B492" s="7"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1">
+      <c r="A493" s="7"/>
+      <c r="B493" s="7"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1">
+      <c r="A494" s="7"/>
+      <c r="B494" s="7"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1">
+      <c r="A495" s="7"/>
+      <c r="B495" s="7"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1">
+      <c r="A496" s="7"/>
+      <c r="B496" s="7"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1">
+      <c r="A497" s="7"/>
+      <c r="B497" s="7"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1">
+      <c r="A498" s="7"/>
+      <c r="B498" s="7"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1">
+      <c r="A499" s="7"/>
+      <c r="B499" s="7"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1">
+      <c r="A500" s="7"/>
+      <c r="B500" s="7"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1">
+      <c r="A501" s="7"/>
+      <c r="B501" s="7"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1">
+      <c r="A502" s="7"/>
+      <c r="B502" s="7"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1">
+      <c r="A503" s="7"/>
+      <c r="B503" s="7"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1">
+      <c r="A504" s="7"/>
+      <c r="B504" s="7"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1">
+      <c r="A505" s="7"/>
+      <c r="B505" s="7"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1">
+      <c r="A506" s="7"/>
+      <c r="B506" s="7"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1">
+      <c r="A507" s="7"/>
+      <c r="B507" s="7"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1">
+      <c r="A508" s="7"/>
+      <c r="B508" s="7"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1">
+      <c r="A509" s="7"/>
+      <c r="B509" s="7"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1">
+      <c r="A510" s="7"/>
+      <c r="B510" s="7"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1">
+      <c r="A511" s="7"/>
+      <c r="B511" s="7"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1">
+      <c r="A512" s="7"/>
+      <c r="B512" s="7"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1">
+      <c r="A513" s="7"/>
+      <c r="B513" s="7"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1">
+      <c r="A514" s="7"/>
+      <c r="B514" s="7"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1">
+      <c r="A515" s="7"/>
+      <c r="B515" s="7"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1">
+      <c r="A516" s="7"/>
+      <c r="B516" s="7"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1">
+      <c r="A517" s="7"/>
+      <c r="B517" s="7"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1">
+      <c r="A518" s="7"/>
+      <c r="B518" s="7"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1">
+      <c r="A519" s="7"/>
+      <c r="B519" s="7"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1">
+      <c r="A520" s="7"/>
+      <c r="B520" s="7"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1">
+      <c r="A521" s="7"/>
+      <c r="B521" s="7"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1">
+      <c r="A522" s="7"/>
+      <c r="B522" s="7"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1">
+      <c r="A523" s="7"/>
+      <c r="B523" s="7"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1">
+      <c r="A524" s="7"/>
+      <c r="B524" s="7"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1">
+      <c r="A525" s="7"/>
+      <c r="B525" s="7"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1">
+      <c r="A526" s="7"/>
+      <c r="B526" s="7"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1">
+      <c r="A527" s="7"/>
+      <c r="B527" s="7"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1">
+      <c r="A528" s="7"/>
+      <c r="B528" s="7"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1">
+      <c r="A529" s="7"/>
+      <c r="B529" s="7"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1">
+      <c r="A530" s="7"/>
+      <c r="B530" s="7"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1">
+      <c r="A531" s="7"/>
+      <c r="B531" s="7"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1">
+      <c r="A532" s="7"/>
+      <c r="B532" s="7"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1">
+      <c r="A533" s="7"/>
+      <c r="B533" s="7"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1">
+      <c r="A534" s="7"/>
+      <c r="B534" s="7"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1">
+      <c r="A535" s="7"/>
+      <c r="B535" s="7"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1">
+      <c r="A536" s="7"/>
+      <c r="B536" s="7"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1">
+      <c r="A537" s="7"/>
+      <c r="B537" s="7"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1">
+      <c r="A538" s="7"/>
+      <c r="B538" s="7"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1">
+      <c r="A539" s="7"/>
+      <c r="B539" s="7"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1">
+      <c r="A540" s="7"/>
+      <c r="B540" s="7"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1">
+      <c r="A541" s="7"/>
+      <c r="B541" s="7"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1">
+      <c r="A542" s="7"/>
+      <c r="B542" s="7"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1">
+      <c r="A543" s="7"/>
+      <c r="B543" s="7"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1">
+      <c r="A544" s="7"/>
+      <c r="B544" s="7"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1">
+      <c r="A545" s="7"/>
+      <c r="B545" s="7"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1">
+      <c r="A546" s="7"/>
+      <c r="B546" s="7"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1">
+      <c r="A547" s="7"/>
+      <c r="B547" s="7"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1">
+      <c r="A548" s="7"/>
+      <c r="B548" s="7"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1">
+      <c r="A549" s="7"/>
+      <c r="B549" s="7"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1">
+      <c r="A550" s="7"/>
+      <c r="B550" s="7"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1">
+      <c r="A551" s="7"/>
+      <c r="B551" s="7"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1">
+      <c r="A552" s="7"/>
+      <c r="B552" s="7"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1">
+      <c r="A553" s="7"/>
+      <c r="B553" s="7"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1">
+      <c r="A554" s="7"/>
+      <c r="B554" s="7"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1">
+      <c r="A555" s="7"/>
+      <c r="B555" s="7"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1">
+      <c r="A556" s="7"/>
+      <c r="B556" s="7"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1">
+      <c r="A557" s="7"/>
+      <c r="B557" s="7"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1">
+      <c r="A558" s="7"/>
+      <c r="B558" s="7"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1">
+      <c r="A559" s="7"/>
+      <c r="B559" s="7"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1">
+      <c r="A560" s="7"/>
+      <c r="B560" s="7"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1">
+      <c r="A561" s="7"/>
+      <c r="B561" s="7"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1">
+      <c r="A562" s="7"/>
+      <c r="B562" s="7"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1">
+      <c r="A563" s="7"/>
+      <c r="B563" s="7"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1">
+      <c r="A564" s="7"/>
+      <c r="B564" s="7"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1">
+      <c r="A565" s="7"/>
+      <c r="B565" s="7"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1">
+      <c r="A566" s="7"/>
+      <c r="B566" s="7"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1">
+      <c r="A567" s="7"/>
+      <c r="B567" s="7"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1">
+      <c r="A568" s="7"/>
+      <c r="B568" s="7"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1">
+      <c r="A569" s="7"/>
+      <c r="B569" s="7"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1">
+      <c r="A570" s="7"/>
+      <c r="B570" s="7"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1">
+      <c r="A571" s="7"/>
+      <c r="B571" s="7"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1">
+      <c r="A572" s="7"/>
+      <c r="B572" s="7"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1">
+      <c r="A573" s="7"/>
+      <c r="B573" s="7"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1">
+      <c r="A574" s="7"/>
+      <c r="B574" s="7"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1">
+      <c r="A575" s="7"/>
+      <c r="B575" s="7"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1">
+      <c r="A576" s="7"/>
+      <c r="B576" s="7"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1">
+      <c r="A577" s="7"/>
+      <c r="B577" s="7"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1">
+      <c r="A578" s="7"/>
+      <c r="B578" s="7"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1">
+      <c r="A579" s="7"/>
+      <c r="B579" s="7"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1">
+      <c r="A580" s="7"/>
+      <c r="B580" s="7"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1">
+      <c r="A581" s="7"/>
+      <c r="B581" s="7"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1">
+      <c r="A582" s="7"/>
+      <c r="B582" s="7"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1">
+      <c r="A583" s="7"/>
+      <c r="B583" s="7"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1">
+      <c r="A584" s="7"/>
+      <c r="B584" s="7"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1">
+      <c r="A585" s="7"/>
+      <c r="B585" s="7"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1">
+      <c r="A586" s="7"/>
+      <c r="B586" s="7"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1">
+      <c r="A587" s="7"/>
+      <c r="B587" s="7"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1">
+      <c r="A588" s="7"/>
+      <c r="B588" s="7"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1">
+      <c r="A589" s="7"/>
+      <c r="B589" s="7"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1">
+      <c r="A590" s="7"/>
+      <c r="B590" s="7"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1">
+      <c r="A591" s="7"/>
+      <c r="B591" s="7"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1">
+      <c r="A592" s="7"/>
+      <c r="B592" s="7"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1">
+      <c r="A593" s="7"/>
+      <c r="B593" s="7"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1">
+      <c r="A594" s="7"/>
+      <c r="B594" s="7"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1">
+      <c r="A595" s="7"/>
+      <c r="B595" s="7"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1">
+      <c r="A596" s="7"/>
+      <c r="B596" s="7"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1">
+      <c r="A597" s="7"/>
+      <c r="B597" s="7"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1">
+      <c r="A598" s="7"/>
+      <c r="B598" s="7"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1">
+      <c r="A599" s="7"/>
+      <c r="B599" s="7"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1">
+      <c r="A600" s="7"/>
+      <c r="B600" s="7"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1">
+      <c r="A601" s="7"/>
+      <c r="B601" s="7"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1">
+      <c r="A602" s="7"/>
+      <c r="B602" s="7"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1">
+      <c r="A603" s="7"/>
+      <c r="B603" s="7"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1">
+      <c r="A604" s="7"/>
+      <c r="B604" s="7"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1">
+      <c r="A605" s="7"/>
+      <c r="B605" s="7"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1">
+      <c r="A606" s="7"/>
+      <c r="B606" s="7"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1">
+      <c r="A607" s="7"/>
+      <c r="B607" s="7"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1">
+      <c r="A608" s="7"/>
+      <c r="B608" s="7"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1">
+      <c r="A609" s="7"/>
+      <c r="B609" s="7"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1">
+      <c r="A610" s="7"/>
+      <c r="B610" s="7"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1">
+      <c r="A611" s="7"/>
+      <c r="B611" s="7"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1">
+      <c r="A612" s="7"/>
+      <c r="B612" s="7"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1">
+      <c r="A613" s="7"/>
+      <c r="B613" s="7"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1">
+      <c r="A614" s="7"/>
+      <c r="B614" s="7"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1">
+      <c r="A615" s="7"/>
+      <c r="B615" s="7"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1">
+      <c r="A616" s="7"/>
+      <c r="B616" s="7"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1">
+      <c r="A617" s="7"/>
+      <c r="B617" s="7"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1">
+      <c r="A618" s="7"/>
+      <c r="B618" s="7"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1">
+      <c r="A619" s="7"/>
+      <c r="B619" s="7"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1">
+      <c r="A620" s="7"/>
+      <c r="B620" s="7"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1">
+      <c r="A621" s="7"/>
+      <c r="B621" s="7"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1">
+      <c r="A622" s="7"/>
+      <c r="B622" s="7"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1">
+      <c r="A623" s="7"/>
+      <c r="B623" s="7"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1">
+      <c r="A624" s="7"/>
+      <c r="B624" s="7"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1">
+      <c r="A625" s="7"/>
+      <c r="B625" s="7"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1">
+      <c r="A626" s="7"/>
+      <c r="B626" s="7"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1">
+      <c r="A627" s="7"/>
+      <c r="B627" s="7"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1">
+      <c r="A628" s="7"/>
+      <c r="B628" s="7"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1">
+      <c r="A629" s="7"/>
+      <c r="B629" s="7"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1">
+      <c r="A630" s="7"/>
+      <c r="B630" s="7"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1">
+      <c r="A631" s="7"/>
+      <c r="B631" s="7"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1">
+      <c r="A632" s="7"/>
+      <c r="B632" s="7"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1">
+      <c r="A633" s="7"/>
+      <c r="B633" s="7"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1">
+      <c r="A634" s="7"/>
+      <c r="B634" s="7"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1">
+      <c r="A635" s="7"/>
+      <c r="B635" s="7"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1">
+      <c r="A636" s="7"/>
+      <c r="B636" s="7"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1">
+      <c r="A637" s="7"/>
+      <c r="B637" s="7"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1">
+      <c r="A638" s="7"/>
+      <c r="B638" s="7"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1">
+      <c r="A639" s="7"/>
+      <c r="B639" s="7"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1">
+      <c r="A640" s="7"/>
+      <c r="B640" s="7"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1">
+      <c r="A641" s="7"/>
+      <c r="B641" s="7"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1">
+      <c r="A642" s="7"/>
+      <c r="B642" s="7"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1">
+      <c r="A643" s="7"/>
+      <c r="B643" s="7"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1">
+      <c r="A644" s="7"/>
+      <c r="B644" s="7"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1">
+      <c r="A645" s="7"/>
+      <c r="B645" s="7"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1">
+      <c r="A646" s="7"/>
+      <c r="B646" s="7"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1">
+      <c r="A647" s="7"/>
+      <c r="B647" s="7"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1">
+      <c r="A648" s="7"/>
+      <c r="B648" s="7"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1">
+      <c r="A649" s="7"/>
+      <c r="B649" s="7"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1">
+      <c r="A650" s="7"/>
+      <c r="B650" s="7"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1">
+      <c r="A651" s="7"/>
+      <c r="B651" s="7"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1">
+      <c r="A652" s="7"/>
+      <c r="B652" s="7"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1">
+      <c r="A653" s="7"/>
+      <c r="B653" s="7"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1">
+      <c r="A654" s="7"/>
+      <c r="B654" s="7"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1">
+      <c r="A655" s="7"/>
+      <c r="B655" s="7"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1">
+      <c r="A656" s="7"/>
+      <c r="B656" s="7"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1">
+      <c r="A657" s="7"/>
+      <c r="B657" s="7"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1">
+      <c r="A658" s="7"/>
+      <c r="B658" s="7"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1">
+      <c r="A659" s="7"/>
+      <c r="B659" s="7"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1">
+      <c r="A660" s="7"/>
+      <c r="B660" s="7"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1">
+      <c r="A661" s="7"/>
+      <c r="B661" s="7"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1">
+      <c r="A662" s="7"/>
+      <c r="B662" s="7"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1">
+      <c r="A663" s="7"/>
+      <c r="B663" s="7"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1">
+      <c r="A664" s="7"/>
+      <c r="B664" s="7"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1">
+      <c r="A665" s="7"/>
+      <c r="B665" s="7"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1">
+      <c r="A666" s="7"/>
+      <c r="B666" s="7"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1">
+      <c r="A667" s="7"/>
+      <c r="B667" s="7"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1">
+      <c r="A668" s="7"/>
+      <c r="B668" s="7"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1">
+      <c r="A669" s="7"/>
+      <c r="B669" s="7"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1">
+      <c r="A670" s="7"/>
+      <c r="B670" s="7"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1">
+      <c r="A671" s="7"/>
+      <c r="B671" s="7"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1">
+      <c r="A672" s="7"/>
+      <c r="B672" s="7"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1">
+      <c r="A673" s="7"/>
+      <c r="B673" s="7"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1">
+      <c r="A674" s="7"/>
+      <c r="B674" s="7"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1">
+      <c r="A675" s="7"/>
+      <c r="B675" s="7"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1">
+      <c r="A676" s="7"/>
+      <c r="B676" s="7"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1">
+      <c r="A677" s="7"/>
+      <c r="B677" s="7"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1">
+      <c r="A678" s="7"/>
+      <c r="B678" s="7"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1">
+      <c r="A679" s="7"/>
+      <c r="B679" s="7"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1">
+      <c r="A680" s="7"/>
+      <c r="B680" s="7"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1">
+      <c r="A681" s="7"/>
+      <c r="B681" s="7"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1">
+      <c r="A682" s="7"/>
+      <c r="B682" s="7"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1">
+      <c r="A683" s="7"/>
+      <c r="B683" s="7"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1">
+      <c r="A684" s="7"/>
+      <c r="B684" s="7"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1">
+      <c r="A685" s="7"/>
+      <c r="B685" s="7"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1">
+      <c r="A686" s="7"/>
+      <c r="B686" s="7"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1">
+      <c r="A687" s="7"/>
+      <c r="B687" s="7"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1">
+      <c r="A688" s="7"/>
+      <c r="B688" s="7"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1">
+      <c r="A689" s="7"/>
+      <c r="B689" s="7"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1">
+      <c r="A690" s="7"/>
+      <c r="B690" s="7"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1">
+      <c r="A691" s="7"/>
+      <c r="B691" s="7"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1">
+      <c r="A692" s="7"/>
+      <c r="B692" s="7"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1">
+      <c r="A693" s="7"/>
+      <c r="B693" s="7"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1">
+      <c r="A694" s="7"/>
+      <c r="B694" s="7"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1">
+      <c r="A695" s="7"/>
+      <c r="B695" s="7"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1">
+      <c r="A696" s="7"/>
+      <c r="B696" s="7"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1">
+      <c r="A697" s="7"/>
+      <c r="B697" s="7"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1">
+      <c r="A698" s="7"/>
+      <c r="B698" s="7"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1">
+      <c r="A699" s="7"/>
+      <c r="B699" s="7"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1">
+      <c r="A700" s="7"/>
+      <c r="B700" s="7"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1">
+      <c r="A701" s="7"/>
+      <c r="B701" s="7"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1">
+      <c r="A702" s="7"/>
+      <c r="B702" s="7"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1">
+      <c r="A703" s="7"/>
+      <c r="B703" s="7"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1">
+      <c r="A704" s="7"/>
+      <c r="B704" s="7"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1">
+      <c r="A705" s="7"/>
+      <c r="B705" s="7"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1">
+      <c r="A706" s="7"/>
+      <c r="B706" s="7"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1">
+      <c r="A707" s="7"/>
+      <c r="B707" s="7"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1">
+      <c r="A708" s="7"/>
+      <c r="B708" s="7"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1">
+      <c r="A709" s="7"/>
+      <c r="B709" s="7"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1">
+      <c r="A710" s="7"/>
+      <c r="B710" s="7"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1">
+      <c r="A711" s="7"/>
+      <c r="B711" s="7"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1">
+      <c r="A712" s="7"/>
+      <c r="B712" s="7"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1">
+      <c r="A713" s="7"/>
+      <c r="B713" s="7"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1">
+      <c r="A714" s="7"/>
+      <c r="B714" s="7"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1">
+      <c r="A715" s="7"/>
+      <c r="B715" s="7"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1">
+      <c r="A716" s="7"/>
+      <c r="B716" s="7"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1">
+      <c r="A717" s="7"/>
+      <c r="B717" s="7"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1">
+      <c r="A718" s="7"/>
+      <c r="B718" s="7"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1">
+      <c r="A719" s="7"/>
+      <c r="B719" s="7"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1">
+      <c r="A720" s="7"/>
+      <c r="B720" s="7"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1">
+      <c r="A721" s="7"/>
+      <c r="B721" s="7"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1">
+      <c r="A722" s="7"/>
+      <c r="B722" s="7"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1">
+      <c r="A723" s="7"/>
+      <c r="B723" s="7"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1">
+      <c r="A724" s="7"/>
+      <c r="B724" s="7"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1">
+      <c r="A725" s="7"/>
+      <c r="B725" s="7"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1">
+      <c r="A726" s="7"/>
+      <c r="B726" s="7"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1">
+      <c r="A727" s="7"/>
+      <c r="B727" s="7"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1">
+      <c r="A728" s="7"/>
+      <c r="B728" s="7"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1">
+      <c r="A729" s="7"/>
+      <c r="B729" s="7"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1">
+      <c r="A730" s="7"/>
+      <c r="B730" s="7"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1">
+      <c r="A731" s="7"/>
+      <c r="B731" s="7"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1">
+      <c r="A732" s="7"/>
+      <c r="B732" s="7"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1">
+      <c r="A733" s="7"/>
+      <c r="B733" s="7"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1">
+      <c r="A734" s="7"/>
+      <c r="B734" s="7"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1">
+      <c r="A735" s="7"/>
+      <c r="B735" s="7"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1">
+      <c r="A736" s="7"/>
+      <c r="B736" s="7"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1">
+      <c r="A737" s="7"/>
+      <c r="B737" s="7"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1">
+      <c r="A738" s="7"/>
+      <c r="B738" s="7"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1">
+      <c r="A739" s="7"/>
+      <c r="B739" s="7"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1">
+      <c r="A740" s="7"/>
+      <c r="B740" s="7"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1">
+      <c r="A741" s="7"/>
+      <c r="B741" s="7"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1">
+      <c r="A742" s="7"/>
+      <c r="B742" s="7"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1">
+      <c r="A743" s="7"/>
+      <c r="B743" s="7"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1">
+      <c r="A744" s="7"/>
+      <c r="B744" s="7"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1">
+      <c r="A745" s="7"/>
+      <c r="B745" s="7"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1">
+      <c r="A746" s="7"/>
+      <c r="B746" s="7"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1">
+      <c r="A747" s="7"/>
+      <c r="B747" s="7"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1">
+      <c r="A748" s="7"/>
+      <c r="B748" s="7"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1">
+      <c r="A749" s="7"/>
+      <c r="B749" s="7"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1">
+      <c r="A750" s="7"/>
+      <c r="B750" s="7"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1">
+      <c r="A751" s="7"/>
+      <c r="B751" s="7"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1">
+      <c r="A752" s="7"/>
+      <c r="B752" s="7"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1">
+      <c r="A753" s="7"/>
+      <c r="B753" s="7"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1">
+      <c r="A754" s="7"/>
+      <c r="B754" s="7"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1">
+      <c r="A755" s="7"/>
+      <c r="B755" s="7"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1">
+      <c r="A756" s="7"/>
+      <c r="B756" s="7"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1">
+      <c r="A757" s="7"/>
+      <c r="B757" s="7"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1">
+      <c r="A758" s="7"/>
+      <c r="B758" s="7"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1">
+      <c r="A759" s="7"/>
+      <c r="B759" s="7"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1">
+      <c r="A760" s="7"/>
+      <c r="B760" s="7"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1">
+      <c r="A761" s="7"/>
+      <c r="B761" s="7"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1">
+      <c r="A762" s="7"/>
+      <c r="B762" s="7"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1">
+      <c r="A763" s="7"/>
+      <c r="B763" s="7"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1">
+      <c r="A764" s="7"/>
+      <c r="B764" s="7"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1">
+      <c r="A765" s="7"/>
+      <c r="B765" s="7"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1">
+      <c r="A766" s="7"/>
+      <c r="B766" s="7"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1">
+      <c r="A767" s="7"/>
+      <c r="B767" s="7"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1">
+      <c r="A768" s="7"/>
+      <c r="B768" s="7"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1">
+      <c r="A769" s="7"/>
+      <c r="B769" s="7"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1">
+      <c r="A770" s="7"/>
+      <c r="B770" s="7"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1">
+      <c r="A771" s="7"/>
+      <c r="B771" s="7"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1">
+      <c r="A772" s="7"/>
+      <c r="B772" s="7"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1">
+      <c r="A773" s="7"/>
+      <c r="B773" s="7"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1">
+      <c r="A774" s="7"/>
+      <c r="B774" s="7"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1">
+      <c r="A775" s="7"/>
+      <c r="B775" s="7"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1">
+      <c r="A776" s="7"/>
+      <c r="B776" s="7"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1">
+      <c r="A777" s="7"/>
+      <c r="B777" s="7"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1">
+      <c r="A778" s="7"/>
+      <c r="B778" s="7"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1">
+      <c r="A779" s="7"/>
+      <c r="B779" s="7"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1">
+      <c r="A780" s="7"/>
+      <c r="B780" s="7"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1">
+      <c r="A781" s="7"/>
+      <c r="B781" s="7"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1">
+      <c r="A782" s="7"/>
+      <c r="B782" s="7"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1">
+      <c r="A783" s="7"/>
+      <c r="B783" s="7"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1">
+      <c r="A784" s="7"/>
+      <c r="B784" s="7"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1">
+      <c r="A785" s="7"/>
+      <c r="B785" s="7"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1">
+      <c r="A786" s="7"/>
+      <c r="B786" s="7"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1">
+      <c r="A787" s="7"/>
+      <c r="B787" s="7"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1">
+      <c r="A788" s="7"/>
+      <c r="B788" s="7"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1">
+      <c r="A789" s="7"/>
+      <c r="B789" s="7"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1">
+      <c r="A790" s="7"/>
+      <c r="B790" s="7"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1">
+      <c r="A791" s="7"/>
+      <c r="B791" s="7"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1">
+      <c r="A792" s="7"/>
+      <c r="B792" s="7"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1">
+      <c r="A793" s="7"/>
+      <c r="B793" s="7"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1">
+      <c r="A794" s="7"/>
+      <c r="B794" s="7"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1">
+      <c r="A795" s="7"/>
+      <c r="B795" s="7"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1">
+      <c r="A796" s="7"/>
+      <c r="B796" s="7"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1">
+      <c r="A797" s="7"/>
+      <c r="B797" s="7"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1">
+      <c r="A798" s="7"/>
+      <c r="B798" s="7"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1">
+      <c r="A799" s="7"/>
+      <c r="B799" s="7"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1">
+      <c r="A800" s="7"/>
+      <c r="B800" s="7"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1">
+      <c r="A801" s="7"/>
+      <c r="B801" s="7"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1">
+      <c r="A802" s="7"/>
+      <c r="B802" s="7"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1">
+      <c r="A803" s="7"/>
+      <c r="B803" s="7"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1">
+      <c r="A804" s="7"/>
+      <c r="B804" s="7"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1">
+      <c r="A805" s="7"/>
+      <c r="B805" s="7"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1">
+      <c r="A806" s="7"/>
+      <c r="B806" s="7"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1">
+      <c r="A807" s="7"/>
+      <c r="B807" s="7"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1">
+      <c r="A808" s="7"/>
+      <c r="B808" s="7"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1">
+      <c r="A809" s="7"/>
+      <c r="B809" s="7"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1">
+      <c r="A810" s="7"/>
+      <c r="B810" s="7"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1">
+      <c r="A811" s="7"/>
+      <c r="B811" s="7"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1">
+      <c r="A812" s="7"/>
+      <c r="B812" s="7"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1">
+      <c r="A813" s="7"/>
+      <c r="B813" s="7"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1">
+      <c r="A814" s="7"/>
+      <c r="B814" s="7"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1">
+      <c r="A815" s="7"/>
+      <c r="B815" s="7"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1">
+      <c r="A816" s="7"/>
+      <c r="B816" s="7"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1">
+      <c r="A817" s="7"/>
+      <c r="B817" s="7"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1">
+      <c r="A818" s="7"/>
+      <c r="B818" s="7"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1">
+      <c r="A819" s="7"/>
+      <c r="B819" s="7"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1">
+      <c r="A820" s="7"/>
+      <c r="B820" s="7"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1">
+      <c r="A821" s="7"/>
+      <c r="B821" s="7"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1">
+      <c r="A822" s="7"/>
+      <c r="B822" s="7"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1">
+      <c r="A823" s="7"/>
+      <c r="B823" s="7"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1">
+      <c r="A824" s="7"/>
+      <c r="B824" s="7"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1">
+      <c r="A825" s="7"/>
+      <c r="B825" s="7"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1">
+      <c r="A826" s="7"/>
+      <c r="B826" s="7"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1">
+      <c r="A827" s="7"/>
+      <c r="B827" s="7"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1">
+      <c r="A828" s="7"/>
+      <c r="B828" s="7"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1">
+      <c r="A829" s="7"/>
+      <c r="B829" s="7"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1">
+      <c r="A830" s="7"/>
+      <c r="B830" s="7"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1">
+      <c r="A831" s="7"/>
+      <c r="B831" s="7"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1">
+      <c r="A832" s="7"/>
+      <c r="B832" s="7"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1">
+      <c r="A833" s="7"/>
+      <c r="B833" s="7"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1">
+      <c r="A834" s="7"/>
+      <c r="B834" s="7"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1">
+      <c r="A835" s="7"/>
+      <c r="B835" s="7"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1">
+      <c r="A836" s="7"/>
+      <c r="B836" s="7"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1">
+      <c r="A837" s="7"/>
+      <c r="B837" s="7"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1">
+      <c r="A838" s="7"/>
+      <c r="B838" s="7"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1">
+      <c r="A839" s="7"/>
+      <c r="B839" s="7"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1">
+      <c r="A840" s="7"/>
+      <c r="B840" s="7"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1">
+      <c r="A841" s="7"/>
+      <c r="B841" s="7"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1">
+      <c r="A842" s="7"/>
+      <c r="B842" s="7"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1">
+      <c r="A843" s="7"/>
+      <c r="B843" s="7"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1">
+      <c r="A844" s="7"/>
+      <c r="B844" s="7"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1">
+      <c r="A845" s="7"/>
+      <c r="B845" s="7"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1">
+      <c r="A846" s="7"/>
+      <c r="B846" s="7"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1">
+      <c r="A847" s="7"/>
+      <c r="B847" s="7"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1">
+      <c r="A848" s="7"/>
+      <c r="B848" s="7"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1">
+      <c r="A849" s="7"/>
+      <c r="B849" s="7"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1">
+      <c r="A850" s="7"/>
+      <c r="B850" s="7"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1">
+      <c r="A851" s="7"/>
+      <c r="B851" s="7"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1">
+      <c r="A852" s="7"/>
+      <c r="B852" s="7"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1">
+      <c r="A853" s="7"/>
+      <c r="B853" s="7"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1">
+      <c r="A854" s="7"/>
+      <c r="B854" s="7"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1">
+      <c r="A855" s="7"/>
+      <c r="B855" s="7"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1">
+      <c r="A856" s="7"/>
+      <c r="B856" s="7"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1">
+      <c r="A857" s="7"/>
+      <c r="B857" s="7"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1">
+      <c r="A858" s="7"/>
+      <c r="B858" s="7"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1">
+      <c r="A859" s="7"/>
+      <c r="B859" s="7"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1">
+      <c r="A860" s="7"/>
+      <c r="B860" s="7"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1">
+      <c r="A861" s="7"/>
+      <c r="B861" s="7"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1">
+      <c r="A862" s="7"/>
+      <c r="B862" s="7"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1">
+      <c r="A863" s="7"/>
+      <c r="B863" s="7"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1">
+      <c r="A864" s="7"/>
+      <c r="B864" s="7"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1">
+      <c r="A865" s="7"/>
+      <c r="B865" s="7"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1">
+      <c r="A866" s="7"/>
+      <c r="B866" s="7"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1">
+      <c r="A867" s="7"/>
+      <c r="B867" s="7"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1">
+      <c r="A868" s="7"/>
+      <c r="B868" s="7"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1">
+      <c r="A869" s="7"/>
+      <c r="B869" s="7"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1">
+      <c r="A870" s="7"/>
+      <c r="B870" s="7"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1">
+      <c r="A871" s="7"/>
+      <c r="B871" s="7"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1">
+      <c r="A872" s="7"/>
+      <c r="B872" s="7"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1">
+      <c r="A873" s="7"/>
+      <c r="B873" s="7"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1">
+      <c r="A874" s="7"/>
+      <c r="B874" s="7"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1">
+      <c r="A875" s="7"/>
+      <c r="B875" s="7"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1">
+      <c r="A876" s="7"/>
+      <c r="B876" s="7"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1">
+      <c r="A877" s="7"/>
+      <c r="B877" s="7"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1">
+      <c r="A878" s="7"/>
+      <c r="B878" s="7"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1">
+      <c r="A879" s="7"/>
+      <c r="B879" s="7"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1">
+      <c r="A880" s="7"/>
+      <c r="B880" s="7"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1">
+      <c r="A881" s="7"/>
+      <c r="B881" s="7"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1">
+      <c r="A882" s="7"/>
+      <c r="B882" s="7"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1">
+      <c r="A883" s="7"/>
+      <c r="B883" s="7"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1">
+      <c r="A884" s="7"/>
+      <c r="B884" s="7"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1">
+      <c r="A885" s="7"/>
+      <c r="B885" s="7"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1">
+      <c r="A886" s="7"/>
+      <c r="B886" s="7"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1">
+      <c r="A887" s="7"/>
+      <c r="B887" s="7"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1">
+      <c r="A888" s="7"/>
+      <c r="B888" s="7"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1">
+      <c r="A889" s="7"/>
+      <c r="B889" s="7"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1">
+      <c r="A890" s="7"/>
+      <c r="B890" s="7"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1">
+      <c r="A891" s="7"/>
+      <c r="B891" s="7"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1">
+      <c r="A892" s="7"/>
+      <c r="B892" s="7"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1">
+      <c r="A893" s="7"/>
+      <c r="B893" s="7"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1">
+      <c r="A894" s="7"/>
+      <c r="B894" s="7"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1">
+      <c r="A895" s="7"/>
+      <c r="B895" s="7"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1">
+      <c r="A896" s="7"/>
+      <c r="B896" s="7"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1">
+      <c r="A897" s="7"/>
+      <c r="B897" s="7"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1">
+      <c r="A898" s="7"/>
+      <c r="B898" s="7"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1">
+      <c r="A899" s="7"/>
+      <c r="B899" s="7"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1">
+      <c r="A900" s="7"/>
+      <c r="B900" s="7"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1">
+      <c r="A901" s="7"/>
+      <c r="B901" s="7"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1">
+      <c r="A902" s="7"/>
+      <c r="B902" s="7"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1">
+      <c r="A903" s="7"/>
+      <c r="B903" s="7"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1">
+      <c r="A904" s="7"/>
+      <c r="B904" s="7"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1">
+      <c r="A905" s="7"/>
+      <c r="B905" s="7"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1">
+      <c r="A906" s="7"/>
+      <c r="B906" s="7"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1">
+      <c r="A907" s="7"/>
+      <c r="B907" s="7"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1">
+      <c r="A908" s="7"/>
+      <c r="B908" s="7"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1">
+      <c r="A909" s="7"/>
+      <c r="B909" s="7"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1">
+      <c r="A910" s="7"/>
+      <c r="B910" s="7"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1">
+      <c r="A911" s="7"/>
+      <c r="B911" s="7"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1">
+      <c r="A912" s="7"/>
+      <c r="B912" s="7"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1">
+      <c r="A913" s="7"/>
+      <c r="B913" s="7"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1">
+      <c r="A914" s="7"/>
+      <c r="B914" s="7"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1">
+      <c r="A915" s="7"/>
+      <c r="B915" s="7"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1">
+      <c r="A916" s="7"/>
+      <c r="B916" s="7"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1">
+      <c r="A917" s="7"/>
+      <c r="B917" s="7"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1">
+      <c r="A918" s="7"/>
+      <c r="B918" s="7"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1">
+      <c r="A919" s="7"/>
+      <c r="B919" s="7"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1">
+      <c r="A920" s="7"/>
+      <c r="B920" s="7"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1">
+      <c r="A921" s="7"/>
+      <c r="B921" s="7"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1">
+      <c r="A922" s="7"/>
+      <c r="B922" s="7"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1">
+      <c r="A923" s="7"/>
+      <c r="B923" s="7"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1">
+      <c r="A924" s="7"/>
+      <c r="B924" s="7"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1">
+      <c r="A925" s="7"/>
+      <c r="B925" s="7"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1">
+      <c r="A926" s="7"/>
+      <c r="B926" s="7"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1">
+      <c r="A927" s="7"/>
+      <c r="B927" s="7"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1">
+      <c r="A928" s="7"/>
+      <c r="B928" s="7"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1">
+      <c r="A929" s="7"/>
+      <c r="B929" s="7"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1">
+      <c r="A930" s="7"/>
+      <c r="B930" s="7"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1">
+      <c r="A931" s="7"/>
+      <c r="B931" s="7"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1">
+      <c r="A932" s="7"/>
+      <c r="B932" s="7"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1">
+      <c r="A933" s="7"/>
+      <c r="B933" s="7"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1">
+      <c r="A934" s="7"/>
+      <c r="B934" s="7"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1">
+      <c r="A935" s="7"/>
+      <c r="B935" s="7"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1">
+      <c r="A936" s="7"/>
+      <c r="B936" s="7"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1">
+      <c r="A937" s="7"/>
+      <c r="B937" s="7"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1">
+      <c r="A938" s="7"/>
+      <c r="B938" s="7"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1">
+      <c r="A939" s="7"/>
+      <c r="B939" s="7"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1">
+      <c r="A940" s="7"/>
+      <c r="B940" s="7"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1">
+      <c r="A941" s="7"/>
+      <c r="B941" s="7"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1">
+      <c r="A942" s="7"/>
+      <c r="B942" s="7"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1">
+      <c r="A943" s="7"/>
+      <c r="B943" s="7"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1">
+      <c r="A944" s="7"/>
+      <c r="B944" s="7"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1">
+      <c r="A945" s="7"/>
+      <c r="B945" s="7"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1">
+      <c r="A946" s="7"/>
+      <c r="B946" s="7"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1">
+      <c r="A947" s="7"/>
+      <c r="B947" s="7"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1">
+      <c r="A948" s="7"/>
+      <c r="B948" s="7"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1">
+      <c r="A949" s="7"/>
+      <c r="B949" s="7"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1">
+      <c r="A950" s="7"/>
+      <c r="B950" s="7"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1">
+      <c r="A951" s="7"/>
+      <c r="B951" s="7"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1">
+      <c r="A952" s="7"/>
+      <c r="B952" s="7"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1">
+      <c r="A953" s="7"/>
+      <c r="B953" s="7"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1">
+      <c r="A954" s="7"/>
+      <c r="B954" s="7"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1">
+      <c r="A955" s="7"/>
+      <c r="B955" s="7"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1">
+      <c r="A956" s="7"/>
+      <c r="B956" s="7"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1">
+      <c r="A957" s="7"/>
+      <c r="B957" s="7"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1">
+      <c r="A958" s="7"/>
+      <c r="B958" s="7"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1">
+      <c r="A959" s="7"/>
+      <c r="B959" s="7"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1">
+      <c r="A960" s="7"/>
+      <c r="B960" s="7"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1">
+      <c r="A961" s="7"/>
+      <c r="B961" s="7"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1">
+      <c r="A962" s="7"/>
+      <c r="B962" s="7"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1">
+      <c r="A963" s="7"/>
+      <c r="B963" s="7"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1">
+      <c r="A964" s="7"/>
+      <c r="B964" s="7"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1">
+      <c r="A965" s="7"/>
+      <c r="B965" s="7"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1">
+      <c r="A966" s="7"/>
+      <c r="B966" s="7"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1">
+      <c r="A967" s="7"/>
+      <c r="B967" s="7"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1">
+      <c r="A968" s="7"/>
+      <c r="B968" s="7"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1">
+      <c r="A969" s="7"/>
+      <c r="B969" s="7"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1">
+      <c r="A970" s="7"/>
+      <c r="B970" s="7"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1">
+      <c r="A971" s="7"/>
+      <c r="B971" s="7"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1">
+      <c r="A972" s="7"/>
+      <c r="B972" s="7"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1">
+      <c r="A973" s="7"/>
+      <c r="B973" s="7"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1">
+      <c r="A974" s="7"/>
+      <c r="B974" s="7"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1">
+      <c r="A975" s="7"/>
+      <c r="B975" s="7"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1">
+      <c r="A976" s="7"/>
+      <c r="B976" s="7"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1">
+      <c r="A977" s="7"/>
+      <c r="B977" s="7"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1">
+      <c r="A978" s="7"/>
+      <c r="B978" s="7"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1">
+      <c r="A979" s="7"/>
+      <c r="B979" s="7"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1">
+      <c r="A980" s="7"/>
+      <c r="B980" s="7"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1">
+      <c r="A981" s="7"/>
+      <c r="B981" s="7"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1">
+      <c r="A982" s="7"/>
+      <c r="B982" s="7"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="A983" s="7"/>
+      <c r="B983" s="7"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1">
+      <c r="A984" s="7"/>
+      <c r="B984" s="7"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1">
+      <c r="A985" s="7"/>
+      <c r="B985" s="7"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1">
+      <c r="A986" s="7"/>
+      <c r="B986" s="7"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1">
+      <c r="A987" s="7"/>
+      <c r="B987" s="7"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1">
+      <c r="A988" s="7"/>
+      <c r="B988" s="7"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1">
+      <c r="A989" s="7"/>
+      <c r="B989" s="7"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1">
+      <c r="A990" s="7"/>
+      <c r="B990" s="7"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1">
+      <c r="A991" s="7"/>
+      <c r="B991" s="7"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1">
+      <c r="A992" s="7"/>
+      <c r="B992" s="7"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1">
+      <c r="A993" s="7"/>
+      <c r="B993" s="7"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1">
+      <c r="A994" s="7"/>
+      <c r="B994" s="7"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1">
+      <c r="A995" s="7"/>
+      <c r="B995" s="7"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1">
+      <c r="A996" s="7"/>
+      <c r="B996" s="7"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1">
+      <c r="A997" s="7"/>
+      <c r="B997" s="7"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1">
+      <c r="A998" s="7"/>
+      <c r="B998" s="7"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1">
+      <c r="A999" s="7"/>
+      <c r="B999" s="7"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1">
+      <c r="A1000" s="7"/>
+      <c r="B1000" s="7"/>
+    </row>
   </sheetData>
-  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <printOptions/>
+  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -80,7 +80,7 @@
     <t>StringItemType</t>
   </si>
   <si>
-    <t>stringItemGrade</t>
+    <t>StringItemGrade</t>
   </si>
   <si>
     <t>Weight</t>
@@ -117,6 +117,9 @@
     <t>Tool</t>
   </si>
   <si>
+    <t>Legendary</t>
+  </si>
+  <si>
     <t>Yellow</t>
   </si>
   <si>
@@ -134,6 +137,9 @@
   <si>
     <t>잠겨있는 무언가를 열 수 있다.
 한 번만 사용 할 수 있다.</t>
+  </si>
+  <si>
+    <t>Rare</t>
   </si>
   <si>
     <t>Black</t>
@@ -169,6 +175,9 @@
     <t>자수정이다.</t>
   </si>
   <si>
+    <t>Unique</t>
+  </si>
+  <si>
     <t>M_Gemstone_Amethyst</t>
   </si>
   <si>
@@ -191,6 +200,9 @@
   </si>
   <si>
     <t>에메랄드다.</t>
+  </si>
+  <si>
+    <t>Epic</t>
   </si>
   <si>
     <t>M_Gemstone_Emerald</t>
@@ -1252,7 +1264,7 @@
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" ht="13.2" spans="1:21">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
@@ -1359,7 +1371,9 @@
       <c r="D4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="5"/>
+      <c r="E4" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="F4" s="5">
         <v>2</v>
       </c>
@@ -1371,13 +1385,13 @@
         <v>-1</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
@@ -1391,18 +1405,20 @@
     </row>
     <row r="5" customHeight="1" spans="1:21">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="5"/>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="F5" s="5">
         <v>1</v>
       </c>
@@ -1414,13 +1430,13 @@
         <v>1</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="5"/>
@@ -1434,18 +1450,20 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:21">
       <c r="A6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E6" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="F6" s="5">
         <v>10</v>
       </c>
@@ -1455,13 +1473,13 @@
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M6" s="5"/>
       <c r="N6" s="5"/>
@@ -1475,18 +1493,20 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:21">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>48</v>
+      </c>
       <c r="F7" s="5">
         <v>8</v>
       </c>
@@ -1496,13 +1516,13 @@
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M7" s="5"/>
       <c r="N7" s="5"/>
@@ -1516,18 +1536,20 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:21">
       <c r="A8" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E8" s="5"/>
       <c r="F8" s="5">
         <v>7</v>
       </c>
@@ -1537,13 +1559,13 @@
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M8" s="5"/>
       <c r="N8" s="5"/>
@@ -1557,18 +1579,20 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:21">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>57</v>
+      </c>
       <c r="F9" s="5">
         <v>6</v>
       </c>
@@ -1578,13 +1602,13 @@
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M9" s="5"/>
       <c r="N9" s="5"/>
@@ -1598,18 +1622,20 @@
     </row>
     <row r="10" ht="15.75" customHeight="1" spans="1:21">
       <c r="A10" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" s="5"/>
       <c r="F10" s="5">
         <v>5</v>
       </c>
@@ -1619,13 +1645,13 @@
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M10" s="5"/>
       <c r="N10" s="5"/>
@@ -1639,18 +1665,20 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:21">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="F11" s="5">
         <v>4</v>
       </c>
@@ -1660,13 +1688,13 @@
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M11" s="5"/>
       <c r="N11" s="5"/>
@@ -1680,18 +1708,20 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:21">
       <c r="A12" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="5"/>
+        <v>41</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>36</v>
+      </c>
       <c r="F12" s="5">
         <v>3</v>
       </c>
@@ -1701,13 +1731,13 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L12" s="5" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="M12" s="5"/>
       <c r="N12" s="5"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -1,22 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="ItemData" sheetId="1" r:id="rId4"/>
+    <sheet name="ItemData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PSHgN1/kfcCjDd8eM0S9gC4F43mGfiTG0/AQb1lJB4c="/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="95">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -247,54 +258,277 @@
   <si>
     <t>M_Gemstone_Topaz</t>
   </si>
+  <si>
+    <t>Item_Painting_01</t>
+  </si>
+  <si>
+    <t>명화</t>
+  </si>
+  <si>
+    <t>벽에 걸려있는 그림이다.</t>
+  </si>
+  <si>
+    <t>Painting</t>
+  </si>
+  <si>
+    <t>Painting_1,PaintingFrame_White,PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>Painting_1[Painting_1]</t>
+  </si>
+  <si>
+    <t>PaintingObject</t>
+  </si>
+  <si>
+    <t>Item_Painting_02</t>
+  </si>
+  <si>
+    <t>Painting_6,PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>Painting_2[Painting_2]</t>
+  </si>
+  <si>
+    <t>Item_Painting_03</t>
+  </si>
+  <si>
+    <t>Painting_8,PaintingFrame_Gold,PaintingFrame_Black</t>
+  </si>
+  <si>
+    <t>Painting_3[Painting_8]</t>
+  </si>
+  <si>
+    <t>Item_Painting_04</t>
+  </si>
+  <si>
+    <t>Painting_3,PaintingFrame_White</t>
+  </si>
+  <si>
+    <t>Painting_4[Painting_4]</t>
+  </si>
+  <si>
+    <t>Item_Painting_05</t>
+  </si>
+  <si>
+    <t>Painting_2,PaintingFrame_WoodHell</t>
+  </si>
+  <si>
+    <t>Painting_5[Painting_5]</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="27">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Malgun Gothic"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FF008000"/>
       <name val="&quot;맑은 고딕&quot;"/>
+      <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -308,9 +542,201 @@
         <bgColor rgb="FFD2F2DB"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -324,57 +750,547 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -564,33 +1480,34 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
-    <pageSetUpPr/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <dimension ref="A1:U1000"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
-    <col customWidth="1" min="2" max="2" width="15.0"/>
-    <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="15.5"/>
-    <col customWidth="1" min="5" max="5" width="14.5"/>
-    <col customWidth="1" min="6" max="6" width="11.63"/>
-    <col customWidth="1" min="7" max="7" width="9.63"/>
-    <col customWidth="1" min="8" max="8" width="23.75"/>
-    <col customWidth="1" min="9" max="9" width="14.13"/>
-    <col customWidth="1" min="10" max="10" width="21.25"/>
-    <col customWidth="1" min="11" max="11" width="27.38"/>
-    <col customWidth="1" min="12" max="12" width="11.75"/>
-    <col customWidth="1" min="13" max="21" width="9.63"/>
+    <col min="1" max="1" width="17.6296296296296" customWidth="1"/>
+    <col min="2" max="2" width="15" customWidth="1"/>
+    <col min="3" max="3" width="24.25" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="6" width="11.6296296296296" customWidth="1"/>
+    <col min="7" max="7" width="9.62962962962963" customWidth="1"/>
+    <col min="8" max="8" width="23.75" customWidth="1"/>
+    <col min="9" max="9" width="14.1296296296296" customWidth="1"/>
+    <col min="10" max="10" width="52.6666666666667" customWidth="1"/>
+    <col min="11" max="11" width="27.3796296296296" customWidth="1"/>
+    <col min="12" max="12" width="11.75" customWidth="1"/>
+    <col min="13" max="21" width="9.62962962962963" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="15.75" customHeight="1" spans="1:21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -633,7 +1550,7 @@
       <c r="T1" s="4"/>
       <c r="U1" s="4"/>
     </row>
-    <row r="2">
+    <row r="2" ht="13.2" spans="1:21">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -643,10 +1560,10 @@
       <c r="C2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -670,7 +1587,7 @@
       <c r="L2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="4"/>
@@ -682,56 +1599,56 @@
       <c r="T2" s="4"/>
       <c r="U2" s="4"/>
     </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="8" t="s">
+    <row r="3" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="G3" s="10" t="s">
+      <c r="G3" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="10"/>
-      <c r="O3" s="10"/>
-      <c r="P3" s="10"/>
-      <c r="Q3" s="10"/>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-    </row>
-    <row r="4" ht="15.0" customHeight="1">
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="8"/>
+      <c r="R3" s="8"/>
+      <c r="S3" s="8"/>
+      <c r="T3" s="8"/>
+      <c r="U3" s="8"/>
+    </row>
+    <row r="4" customHeight="1" spans="1:21">
       <c r="A4" s="1" t="s">
         <v>27</v>
       </c>
@@ -748,14 +1665,14 @@
         <v>31</v>
       </c>
       <c r="F4" s="4">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G4" s="4">
-        <v>100000.0</v>
+        <v>100000</v>
       </c>
       <c r="H4" s="4"/>
       <c r="I4" s="4">
-        <v>-1.0</v>
+        <v>-1</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>32</v>
@@ -776,7 +1693,7 @@
       <c r="T4" s="4"/>
       <c r="U4" s="4"/>
     </row>
-    <row r="5" ht="15.0" customHeight="1">
+    <row r="5" customHeight="1" spans="1:21">
       <c r="A5" s="1" t="s">
         <v>35</v>
       </c>
@@ -793,14 +1710,14 @@
         <v>31</v>
       </c>
       <c r="F5" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="4">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4"/>
       <c r="I5" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>38</v>
@@ -821,8 +1738,8 @@
       <c r="T5" s="4"/>
       <c r="U5" s="4"/>
     </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="6" t="s">
+    <row r="6" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -838,10 +1755,10 @@
         <v>43</v>
       </c>
       <c r="F6" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="4">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -854,7 +1771,7 @@
       <c r="L6" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="9" t="s">
         <v>47</v>
       </c>
       <c r="N6" s="4"/>
@@ -866,7 +1783,7 @@
       <c r="T6" s="4"/>
       <c r="U6" s="4"/>
     </row>
-    <row r="7" ht="15.75" customHeight="1">
+    <row r="7" ht="15.75" customHeight="1" spans="1:21">
       <c r="A7" s="1" t="s">
         <v>48</v>
       </c>
@@ -883,10 +1800,10 @@
         <v>43</v>
       </c>
       <c r="F7" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="G7" s="4">
-        <v>800.0</v>
+        <v>800</v>
       </c>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -899,7 +1816,7 @@
       <c r="L7" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="9" t="s">
         <v>52</v>
       </c>
       <c r="N7" s="4"/>
@@ -911,7 +1828,7 @@
       <c r="T7" s="4"/>
       <c r="U7" s="4"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="15.75" customHeight="1" spans="1:21">
       <c r="A8" s="1" t="s">
         <v>53</v>
       </c>
@@ -928,10 +1845,10 @@
         <v>56</v>
       </c>
       <c r="F8" s="4">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="G8" s="4">
-        <v>700.0</v>
+        <v>700</v>
       </c>
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
@@ -944,7 +1861,7 @@
       <c r="L8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="9" t="s">
         <v>52</v>
       </c>
       <c r="N8" s="4"/>
@@ -956,7 +1873,7 @@
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
     </row>
-    <row r="9" ht="15.75" customHeight="1">
+    <row r="9" ht="15.75" customHeight="1" spans="1:21">
       <c r="A9" s="1" t="s">
         <v>58</v>
       </c>
@@ -973,10 +1890,10 @@
         <v>61</v>
       </c>
       <c r="F9" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="G9" s="4">
-        <v>600.0</v>
+        <v>600</v>
       </c>
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
@@ -989,7 +1906,7 @@
       <c r="L9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="9" t="s">
         <v>52</v>
       </c>
       <c r="N9" s="4"/>
@@ -1001,7 +1918,7 @@
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
     </row>
-    <row r="10" ht="15.75" customHeight="1">
+    <row r="10" ht="15.75" customHeight="1" spans="1:21">
       <c r="A10" s="1" t="s">
         <v>63</v>
       </c>
@@ -1018,10 +1935,10 @@
         <v>61</v>
       </c>
       <c r="F10" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G10" s="4">
-        <v>500.0</v>
+        <v>500</v>
       </c>
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
@@ -1034,7 +1951,7 @@
       <c r="L10" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="9" t="s">
         <v>47</v>
       </c>
       <c r="N10" s="4"/>
@@ -1046,7 +1963,7 @@
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
     </row>
-    <row r="11" ht="15.75" customHeight="1">
+    <row r="11" ht="15.75" customHeight="1" spans="1:21">
       <c r="A11" s="1" t="s">
         <v>67</v>
       </c>
@@ -1063,10 +1980,10 @@
         <v>70</v>
       </c>
       <c r="F11" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="G11" s="4">
-        <v>400.0</v>
+        <v>400</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -1079,7 +1996,7 @@
       <c r="L11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="9" t="s">
         <v>52</v>
       </c>
       <c r="N11" s="4"/>
@@ -1091,7 +2008,7 @@
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
     </row>
-    <row r="12" ht="15.75" customHeight="1">
+    <row r="12" ht="15.75" customHeight="1" spans="1:21">
       <c r="A12" s="1" t="s">
         <v>72</v>
       </c>
@@ -1108,10 +2025,10 @@
         <v>70</v>
       </c>
       <c r="F12" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G12" s="4">
-        <v>300.0</v>
+        <v>300</v>
       </c>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -1124,7 +2041,7 @@
       <c r="L12" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="9" t="s">
         <v>52</v>
       </c>
       <c r="N12" s="4"/>
@@ -1136,20 +2053,42 @@
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
     </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
+    <row r="13" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A13" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="4">
+        <v>12</v>
+      </c>
+      <c r="G13" s="4">
+        <v>1200</v>
+      </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
+      <c r="J13" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M13" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="4"/>
@@ -1159,20 +2098,42 @@
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
     </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
+    <row r="14" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A14" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="4">
+        <v>12</v>
+      </c>
+      <c r="G14" s="4">
+        <v>1200</v>
+      </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
+      <c r="J14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="4"/>
@@ -1182,20 +2143,42 @@
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
     </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
+    <row r="15" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A15" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="4">
+        <v>12</v>
+      </c>
+      <c r="G15" s="4">
+        <v>1200</v>
+      </c>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
+      <c r="J15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="4"/>
@@ -1205,20 +2188,42 @@
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
     </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
+    <row r="16" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="4">
+        <v>12</v>
+      </c>
+      <c r="G16" s="4">
+        <v>1200</v>
+      </c>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
+      <c r="J16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="4"/>
@@ -1228,20 +2233,42 @@
       <c r="T16" s="4"/>
       <c r="U16" s="4"/>
     </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
+    <row r="17" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A17" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="4">
+        <v>12</v>
+      </c>
+      <c r="G17" s="4">
+        <v>1200</v>
+      </c>
       <c r="H17" s="4"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
+      <c r="J17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="4"/>
@@ -1251,7 +2278,7 @@
       <c r="T17" s="4"/>
       <c r="U17" s="4"/>
     </row>
-    <row r="18" ht="15.75" customHeight="1">
+    <row r="18" ht="15.75" customHeight="1" spans="1:21">
       <c r="A18" s="4"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -1274,7 +2301,7 @@
       <c r="T18" s="4"/>
       <c r="U18" s="4"/>
     </row>
-    <row r="19" ht="15.75" customHeight="1">
+    <row r="19" ht="15.75" customHeight="1" spans="1:21">
       <c r="A19" s="4"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1297,7 +2324,7 @@
       <c r="T19" s="4"/>
       <c r="U19" s="4"/>
     </row>
-    <row r="20" ht="15.75" customHeight="1">
+    <row r="20" ht="15.75" customHeight="1" spans="1:21">
       <c r="A20" s="4"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1320,7 +2347,7 @@
       <c r="T20" s="4"/>
       <c r="U20" s="4"/>
     </row>
-    <row r="21" ht="15.75" customHeight="1">
+    <row r="21" ht="15.75" customHeight="1" spans="1:21">
       <c r="A21" s="4"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1343,7 +2370,7 @@
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
     </row>
-    <row r="22" ht="15.75" customHeight="1">
+    <row r="22" ht="15.75" customHeight="1" spans="1:21">
       <c r="A22" s="4"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1366,7 +2393,7 @@
       <c r="T22" s="4"/>
       <c r="U22" s="4"/>
     </row>
-    <row r="23" ht="15.75" customHeight="1">
+    <row r="23" ht="15.75" customHeight="1" spans="1:21">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1389,7 +2416,7 @@
       <c r="T23" s="4"/>
       <c r="U23" s="4"/>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
+    <row r="24" ht="15.75" customHeight="1" spans="1:21">
       <c r="A24" s="4"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1412,7 +2439,7 @@
       <c r="T24" s="4"/>
       <c r="U24" s="4"/>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
+    <row r="25" ht="15.75" customHeight="1" spans="1:21">
       <c r="A25" s="4"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1435,7 +2462,7 @@
       <c r="T25" s="4"/>
       <c r="U25" s="4"/>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1" spans="1:21">
       <c r="A26" s="4"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1458,7 +2485,7 @@
       <c r="T26" s="4"/>
       <c r="U26" s="4"/>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
+    <row r="27" ht="15.75" customHeight="1" spans="1:21">
       <c r="A27" s="4"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1481,7 +2508,7 @@
       <c r="T27" s="4"/>
       <c r="U27" s="4"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="15.75" customHeight="1" spans="1:21">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1504,7 +2531,7 @@
       <c r="T28" s="4"/>
       <c r="U28" s="4"/>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1" spans="1:21">
       <c r="A29" s="4"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1527,7 +2554,7 @@
       <c r="T29" s="4"/>
       <c r="U29" s="4"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="15.75" customHeight="1" spans="1:21">
       <c r="A30" s="4"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1550,7 +2577,7 @@
       <c r="T30" s="4"/>
       <c r="U30" s="4"/>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
+    <row r="31" ht="15.75" customHeight="1" spans="1:21">
       <c r="A31" s="4"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1573,7 +2600,7 @@
       <c r="T31" s="4"/>
       <c r="U31" s="4"/>
     </row>
-    <row r="32" ht="15.75" customHeight="1">
+    <row r="32" ht="15.75" customHeight="1" spans="1:21">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1596,7 +2623,7 @@
       <c r="T32" s="4"/>
       <c r="U32" s="4"/>
     </row>
-    <row r="33" ht="15.75" customHeight="1">
+    <row r="33" ht="15.75" customHeight="1" spans="1:21">
       <c r="A33" s="4"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1619,7 +2646,7 @@
       <c r="T33" s="4"/>
       <c r="U33" s="4"/>
     </row>
-    <row r="34" ht="15.75" customHeight="1">
+    <row r="34" ht="15.75" customHeight="1" spans="1:21">
       <c r="A34" s="4"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1642,7 +2669,7 @@
       <c r="T34" s="4"/>
       <c r="U34" s="4"/>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
+    <row r="35" ht="15.75" customHeight="1" spans="1:21">
       <c r="A35" s="4"/>
       <c r="B35" s="4"/>
       <c r="C35" s="4"/>
@@ -1665,7 +2692,7 @@
       <c r="T35" s="4"/>
       <c r="U35" s="4"/>
     </row>
-    <row r="36" ht="15.75" customHeight="1">
+    <row r="36" ht="15.75" customHeight="1" spans="1:21">
       <c r="A36" s="4"/>
       <c r="B36" s="4"/>
       <c r="C36" s="4"/>
@@ -1688,7 +2715,7 @@
       <c r="T36" s="4"/>
       <c r="U36" s="4"/>
     </row>
-    <row r="37" ht="15.75" customHeight="1">
+    <row r="37" ht="15.75" customHeight="1" spans="1:21">
       <c r="A37" s="4"/>
       <c r="B37" s="4"/>
       <c r="C37" s="4"/>
@@ -1711,7 +2738,7 @@
       <c r="T37" s="4"/>
       <c r="U37" s="4"/>
     </row>
-    <row r="38" ht="15.75" customHeight="1">
+    <row r="38" ht="15.75" customHeight="1" spans="1:21">
       <c r="A38" s="4"/>
       <c r="B38" s="4"/>
       <c r="C38" s="4"/>
@@ -1734,7 +2761,7 @@
       <c r="T38" s="4"/>
       <c r="U38" s="4"/>
     </row>
-    <row r="39" ht="15.75" customHeight="1">
+    <row r="39" ht="15.75" customHeight="1" spans="1:21">
       <c r="A39" s="4"/>
       <c r="B39" s="4"/>
       <c r="C39" s="4"/>
@@ -1757,7 +2784,7 @@
       <c r="T39" s="4"/>
       <c r="U39" s="4"/>
     </row>
-    <row r="40" ht="15.75" customHeight="1">
+    <row r="40" ht="15.75" customHeight="1" spans="1:21">
       <c r="A40" s="4"/>
       <c r="B40" s="4"/>
       <c r="C40" s="4"/>
@@ -1780,7 +2807,7 @@
       <c r="T40" s="4"/>
       <c r="U40" s="4"/>
     </row>
-    <row r="41" ht="15.75" customHeight="1">
+    <row r="41" ht="15.75" customHeight="1" spans="1:21">
       <c r="A41" s="4"/>
       <c r="B41" s="4"/>
       <c r="C41" s="4"/>
@@ -1803,7 +2830,7 @@
       <c r="T41" s="4"/>
       <c r="U41" s="4"/>
     </row>
-    <row r="42" ht="15.75" customHeight="1">
+    <row r="42" ht="15.75" customHeight="1" spans="1:21">
       <c r="A42" s="4"/>
       <c r="B42" s="4"/>
       <c r="C42" s="4"/>
@@ -1826,7 +2853,7 @@
       <c r="T42" s="4"/>
       <c r="U42" s="4"/>
     </row>
-    <row r="43" ht="15.75" customHeight="1">
+    <row r="43" ht="15.75" customHeight="1" spans="1:21">
       <c r="A43" s="4"/>
       <c r="B43" s="4"/>
       <c r="C43" s="4"/>
@@ -1849,7 +2876,7 @@
       <c r="T43" s="4"/>
       <c r="U43" s="4"/>
     </row>
-    <row r="44" ht="15.75" customHeight="1">
+    <row r="44" ht="15.75" customHeight="1" spans="1:21">
       <c r="A44" s="4"/>
       <c r="B44" s="4"/>
       <c r="C44" s="4"/>
@@ -1872,7 +2899,7 @@
       <c r="T44" s="4"/>
       <c r="U44" s="4"/>
     </row>
-    <row r="45" ht="15.75" customHeight="1">
+    <row r="45" ht="15.75" customHeight="1" spans="1:21">
       <c r="A45" s="4"/>
       <c r="B45" s="4"/>
       <c r="C45" s="4"/>
@@ -1895,7 +2922,7 @@
       <c r="T45" s="4"/>
       <c r="U45" s="4"/>
     </row>
-    <row r="46" ht="15.75" customHeight="1">
+    <row r="46" ht="15.75" customHeight="1" spans="1:21">
       <c r="A46" s="4"/>
       <c r="B46" s="4"/>
       <c r="C46" s="4"/>
@@ -1918,7 +2945,7 @@
       <c r="T46" s="4"/>
       <c r="U46" s="4"/>
     </row>
-    <row r="47" ht="15.75" customHeight="1">
+    <row r="47" ht="15.75" customHeight="1" spans="1:21">
       <c r="A47" s="4"/>
       <c r="B47" s="4"/>
       <c r="C47" s="4"/>
@@ -1941,7 +2968,7 @@
       <c r="T47" s="4"/>
       <c r="U47" s="4"/>
     </row>
-    <row r="48" ht="15.75" customHeight="1">
+    <row r="48" ht="15.75" customHeight="1" spans="1:21">
       <c r="A48" s="4"/>
       <c r="B48" s="4"/>
       <c r="C48" s="4"/>
@@ -1964,7 +2991,7 @@
       <c r="T48" s="4"/>
       <c r="U48" s="4"/>
     </row>
-    <row r="49" ht="15.75" customHeight="1">
+    <row r="49" ht="15.75" customHeight="1" spans="1:21">
       <c r="A49" s="4"/>
       <c r="B49" s="4"/>
       <c r="C49" s="4"/>
@@ -1987,7 +3014,7 @@
       <c r="T49" s="4"/>
       <c r="U49" s="4"/>
     </row>
-    <row r="50" ht="15.75" customHeight="1">
+    <row r="50" ht="15.75" customHeight="1" spans="1:21">
       <c r="A50" s="4"/>
       <c r="B50" s="4"/>
       <c r="C50" s="4"/>
@@ -2010,7 +3037,7 @@
       <c r="T50" s="4"/>
       <c r="U50" s="4"/>
     </row>
-    <row r="51" ht="15.75" customHeight="1">
+    <row r="51" ht="15.75" customHeight="1" spans="1:21">
       <c r="A51" s="4"/>
       <c r="B51" s="4"/>
       <c r="C51" s="4"/>
@@ -2033,7 +3060,7 @@
       <c r="T51" s="4"/>
       <c r="U51" s="4"/>
     </row>
-    <row r="52" ht="15.75" customHeight="1">
+    <row r="52" ht="15.75" customHeight="1" spans="1:21">
       <c r="A52" s="4"/>
       <c r="B52" s="4"/>
       <c r="C52" s="4"/>
@@ -2056,7 +3083,7 @@
       <c r="T52" s="4"/>
       <c r="U52" s="4"/>
     </row>
-    <row r="53" ht="15.75" customHeight="1">
+    <row r="53" ht="15.75" customHeight="1" spans="1:21">
       <c r="A53" s="4"/>
       <c r="B53" s="4"/>
       <c r="C53" s="4"/>
@@ -2079,7 +3106,7 @@
       <c r="T53" s="4"/>
       <c r="U53" s="4"/>
     </row>
-    <row r="54" ht="15.75" customHeight="1">
+    <row r="54" ht="15.75" customHeight="1" spans="1:21">
       <c r="A54" s="4"/>
       <c r="B54" s="4"/>
       <c r="C54" s="4"/>
@@ -2102,7 +3129,7 @@
       <c r="T54" s="4"/>
       <c r="U54" s="4"/>
     </row>
-    <row r="55" ht="15.75" customHeight="1">
+    <row r="55" ht="15.75" customHeight="1" spans="1:21">
       <c r="A55" s="4"/>
       <c r="B55" s="4"/>
       <c r="C55" s="4"/>
@@ -2125,7 +3152,7 @@
       <c r="T55" s="4"/>
       <c r="U55" s="4"/>
     </row>
-    <row r="56" ht="15.75" customHeight="1">
+    <row r="56" ht="15.75" customHeight="1" spans="1:21">
       <c r="A56" s="4"/>
       <c r="B56" s="4"/>
       <c r="C56" s="4"/>
@@ -2148,7 +3175,7 @@
       <c r="T56" s="4"/>
       <c r="U56" s="4"/>
     </row>
-    <row r="57" ht="15.75" customHeight="1">
+    <row r="57" ht="15.75" customHeight="1" spans="1:21">
       <c r="A57" s="4"/>
       <c r="B57" s="4"/>
       <c r="C57" s="4"/>
@@ -2171,7 +3198,7 @@
       <c r="T57" s="4"/>
       <c r="U57" s="4"/>
     </row>
-    <row r="58" ht="15.75" customHeight="1">
+    <row r="58" ht="15.75" customHeight="1" spans="1:21">
       <c r="A58" s="4"/>
       <c r="B58" s="4"/>
       <c r="C58" s="4"/>
@@ -2194,7 +3221,7 @@
       <c r="T58" s="4"/>
       <c r="U58" s="4"/>
     </row>
-    <row r="59" ht="15.75" customHeight="1">
+    <row r="59" ht="15.75" customHeight="1" spans="1:21">
       <c r="A59" s="4"/>
       <c r="B59" s="4"/>
       <c r="C59" s="4"/>
@@ -2217,7 +3244,7 @@
       <c r="T59" s="4"/>
       <c r="U59" s="4"/>
     </row>
-    <row r="60" ht="15.75" customHeight="1">
+    <row r="60" ht="15.75" customHeight="1" spans="1:21">
       <c r="A60" s="4"/>
       <c r="B60" s="4"/>
       <c r="C60" s="4"/>
@@ -2240,7 +3267,7 @@
       <c r="T60" s="4"/>
       <c r="U60" s="4"/>
     </row>
-    <row r="61" ht="15.75" customHeight="1">
+    <row r="61" ht="15.75" customHeight="1" spans="1:21">
       <c r="A61" s="4"/>
       <c r="B61" s="4"/>
       <c r="C61" s="4"/>
@@ -2263,7 +3290,7 @@
       <c r="T61" s="4"/>
       <c r="U61" s="4"/>
     </row>
-    <row r="62" ht="15.75" customHeight="1">
+    <row r="62" ht="15.75" customHeight="1" spans="1:21">
       <c r="A62" s="4"/>
       <c r="B62" s="4"/>
       <c r="C62" s="4"/>
@@ -2286,7 +3313,7 @@
       <c r="T62" s="4"/>
       <c r="U62" s="4"/>
     </row>
-    <row r="63" ht="15.75" customHeight="1">
+    <row r="63" ht="15.75" customHeight="1" spans="1:21">
       <c r="A63" s="4"/>
       <c r="B63" s="4"/>
       <c r="C63" s="4"/>
@@ -2309,7 +3336,7 @@
       <c r="T63" s="4"/>
       <c r="U63" s="4"/>
     </row>
-    <row r="64" ht="15.75" customHeight="1">
+    <row r="64" ht="15.75" customHeight="1" spans="1:21">
       <c r="A64" s="4"/>
       <c r="B64" s="4"/>
       <c r="C64" s="4"/>
@@ -2332,7 +3359,7 @@
       <c r="T64" s="4"/>
       <c r="U64" s="4"/>
     </row>
-    <row r="65" ht="15.75" customHeight="1">
+    <row r="65" ht="15.75" customHeight="1" spans="1:21">
       <c r="A65" s="4"/>
       <c r="B65" s="4"/>
       <c r="C65" s="4"/>
@@ -2355,7 +3382,7 @@
       <c r="T65" s="4"/>
       <c r="U65" s="4"/>
     </row>
-    <row r="66" ht="15.75" customHeight="1">
+    <row r="66" ht="15.75" customHeight="1" spans="1:21">
       <c r="A66" s="4"/>
       <c r="B66" s="4"/>
       <c r="C66" s="4"/>
@@ -2378,7 +3405,7 @@
       <c r="T66" s="4"/>
       <c r="U66" s="4"/>
     </row>
-    <row r="67" ht="15.75" customHeight="1">
+    <row r="67" ht="15.75" customHeight="1" spans="1:21">
       <c r="A67" s="4"/>
       <c r="B67" s="4"/>
       <c r="C67" s="4"/>
@@ -2401,7 +3428,7 @@
       <c r="T67" s="4"/>
       <c r="U67" s="4"/>
     </row>
-    <row r="68" ht="15.75" customHeight="1">
+    <row r="68" ht="15.75" customHeight="1" spans="1:21">
       <c r="A68" s="4"/>
       <c r="B68" s="4"/>
       <c r="C68" s="4"/>
@@ -2424,7 +3451,7 @@
       <c r="T68" s="4"/>
       <c r="U68" s="4"/>
     </row>
-    <row r="69" ht="15.75" customHeight="1">
+    <row r="69" ht="15.75" customHeight="1" spans="1:21">
       <c r="A69" s="4"/>
       <c r="B69" s="4"/>
       <c r="C69" s="4"/>
@@ -2447,7 +3474,7 @@
       <c r="T69" s="4"/>
       <c r="U69" s="4"/>
     </row>
-    <row r="70" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1" spans="1:21">
       <c r="A70" s="4"/>
       <c r="B70" s="4"/>
       <c r="C70" s="4"/>
@@ -2470,7 +3497,7 @@
       <c r="T70" s="4"/>
       <c r="U70" s="4"/>
     </row>
-    <row r="71" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1" spans="1:21">
       <c r="A71" s="4"/>
       <c r="B71" s="4"/>
       <c r="C71" s="4"/>
@@ -2493,7 +3520,7 @@
       <c r="T71" s="4"/>
       <c r="U71" s="4"/>
     </row>
-    <row r="72" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1" spans="1:21">
       <c r="A72" s="4"/>
       <c r="B72" s="4"/>
       <c r="C72" s="4"/>
@@ -2516,7 +3543,7 @@
       <c r="T72" s="4"/>
       <c r="U72" s="4"/>
     </row>
-    <row r="73" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1" spans="1:21">
       <c r="A73" s="4"/>
       <c r="B73" s="4"/>
       <c r="C73" s="4"/>
@@ -2539,7 +3566,7 @@
       <c r="T73" s="4"/>
       <c r="U73" s="4"/>
     </row>
-    <row r="74" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1" spans="1:21">
       <c r="A74" s="4"/>
       <c r="B74" s="4"/>
       <c r="C74" s="4"/>
@@ -2562,7 +3589,7 @@
       <c r="T74" s="4"/>
       <c r="U74" s="4"/>
     </row>
-    <row r="75" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1" spans="1:21">
       <c r="A75" s="4"/>
       <c r="B75" s="4"/>
       <c r="C75" s="4"/>
@@ -2585,7 +3612,7 @@
       <c r="T75" s="4"/>
       <c r="U75" s="4"/>
     </row>
-    <row r="76" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1" spans="1:21">
       <c r="A76" s="4"/>
       <c r="B76" s="4"/>
       <c r="C76" s="4"/>
@@ -2608,7 +3635,7 @@
       <c r="T76" s="4"/>
       <c r="U76" s="4"/>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1" spans="1:21">
       <c r="A77" s="4"/>
       <c r="B77" s="4"/>
       <c r="C77" s="4"/>
@@ -2631,7 +3658,7 @@
       <c r="T77" s="4"/>
       <c r="U77" s="4"/>
     </row>
-    <row r="78" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1" spans="1:21">
       <c r="A78" s="4"/>
       <c r="B78" s="4"/>
       <c r="C78" s="4"/>
@@ -2654,7 +3681,7 @@
       <c r="T78" s="4"/>
       <c r="U78" s="4"/>
     </row>
-    <row r="79" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1" spans="1:21">
       <c r="A79" s="4"/>
       <c r="B79" s="4"/>
       <c r="C79" s="4"/>
@@ -2677,7 +3704,7 @@
       <c r="T79" s="4"/>
       <c r="U79" s="4"/>
     </row>
-    <row r="80" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1" spans="1:21">
       <c r="A80" s="4"/>
       <c r="B80" s="4"/>
       <c r="C80" s="4"/>
@@ -2700,7 +3727,7 @@
       <c r="T80" s="4"/>
       <c r="U80" s="4"/>
     </row>
-    <row r="81" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1" spans="1:21">
       <c r="A81" s="4"/>
       <c r="B81" s="4"/>
       <c r="C81" s="4"/>
@@ -2723,7 +3750,7 @@
       <c r="T81" s="4"/>
       <c r="U81" s="4"/>
     </row>
-    <row r="82" ht="15.75" customHeight="1">
+    <row r="82" ht="15.75" customHeight="1" spans="1:21">
       <c r="A82" s="4"/>
       <c r="B82" s="4"/>
       <c r="C82" s="4"/>
@@ -2746,7 +3773,7 @@
       <c r="T82" s="4"/>
       <c r="U82" s="4"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1">
+    <row r="83" ht="15.75" customHeight="1" spans="1:21">
       <c r="A83" s="4"/>
       <c r="B83" s="4"/>
       <c r="C83" s="4"/>
@@ -2769,7 +3796,7 @@
       <c r="T83" s="4"/>
       <c r="U83" s="4"/>
     </row>
-    <row r="84" ht="15.75" customHeight="1">
+    <row r="84" ht="15.75" customHeight="1" spans="1:21">
       <c r="A84" s="4"/>
       <c r="B84" s="4"/>
       <c r="C84" s="4"/>
@@ -2792,7 +3819,7 @@
       <c r="T84" s="4"/>
       <c r="U84" s="4"/>
     </row>
-    <row r="85" ht="15.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1" spans="1:21">
       <c r="A85" s="4"/>
       <c r="B85" s="4"/>
       <c r="C85" s="4"/>
@@ -2815,7 +3842,7 @@
       <c r="T85" s="4"/>
       <c r="U85" s="4"/>
     </row>
-    <row r="86" ht="15.75" customHeight="1">
+    <row r="86" ht="15.75" customHeight="1" spans="1:21">
       <c r="A86" s="4"/>
       <c r="B86" s="4"/>
       <c r="C86" s="4"/>
@@ -2838,7 +3865,7 @@
       <c r="T86" s="4"/>
       <c r="U86" s="4"/>
     </row>
-    <row r="87" ht="15.75" customHeight="1">
+    <row r="87" ht="15.75" customHeight="1" spans="1:21">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="4"/>
@@ -2861,7 +3888,7 @@
       <c r="T87" s="4"/>
       <c r="U87" s="4"/>
     </row>
-    <row r="88" ht="15.75" customHeight="1">
+    <row r="88" ht="15.75" customHeight="1" spans="1:21">
       <c r="A88" s="4"/>
       <c r="B88" s="4"/>
       <c r="C88" s="4"/>
@@ -2884,7 +3911,7 @@
       <c r="T88" s="4"/>
       <c r="U88" s="4"/>
     </row>
-    <row r="89" ht="15.75" customHeight="1">
+    <row r="89" ht="15.75" customHeight="1" spans="1:21">
       <c r="A89" s="4"/>
       <c r="B89" s="4"/>
       <c r="C89" s="4"/>
@@ -2907,7 +3934,7 @@
       <c r="T89" s="4"/>
       <c r="U89" s="4"/>
     </row>
-    <row r="90" ht="15.75" customHeight="1">
+    <row r="90" ht="15.75" customHeight="1" spans="1:21">
       <c r="A90" s="4"/>
       <c r="B90" s="4"/>
       <c r="C90" s="4"/>
@@ -2930,7 +3957,7 @@
       <c r="T90" s="4"/>
       <c r="U90" s="4"/>
     </row>
-    <row r="91" ht="15.75" customHeight="1">
+    <row r="91" ht="15.75" customHeight="1" spans="1:21">
       <c r="A91" s="4"/>
       <c r="B91" s="4"/>
       <c r="C91" s="4"/>
@@ -2953,7 +3980,7 @@
       <c r="T91" s="4"/>
       <c r="U91" s="4"/>
     </row>
-    <row r="92" ht="15.75" customHeight="1">
+    <row r="92" ht="15.75" customHeight="1" spans="1:21">
       <c r="A92" s="4"/>
       <c r="B92" s="4"/>
       <c r="C92" s="4"/>
@@ -2976,7 +4003,7 @@
       <c r="T92" s="4"/>
       <c r="U92" s="4"/>
     </row>
-    <row r="93" ht="15.75" customHeight="1">
+    <row r="93" ht="15.75" customHeight="1" spans="1:21">
       <c r="A93" s="4"/>
       <c r="B93" s="4"/>
       <c r="C93" s="4"/>
@@ -2999,7 +4026,7 @@
       <c r="T93" s="4"/>
       <c r="U93" s="4"/>
     </row>
-    <row r="94" ht="15.75" customHeight="1">
+    <row r="94" ht="15.75" customHeight="1" spans="1:21">
       <c r="A94" s="4"/>
       <c r="B94" s="4"/>
       <c r="C94" s="4"/>
@@ -3022,7 +4049,7 @@
       <c r="T94" s="4"/>
       <c r="U94" s="4"/>
     </row>
-    <row r="95" ht="15.75" customHeight="1">
+    <row r="95" ht="15.75" customHeight="1" spans="1:21">
       <c r="A95" s="4"/>
       <c r="B95" s="4"/>
       <c r="C95" s="4"/>
@@ -3045,7 +4072,7 @@
       <c r="T95" s="4"/>
       <c r="U95" s="4"/>
     </row>
-    <row r="96" ht="15.75" customHeight="1">
+    <row r="96" ht="15.75" customHeight="1" spans="1:21">
       <c r="A96" s="4"/>
       <c r="B96" s="4"/>
       <c r="C96" s="4"/>
@@ -3068,7 +4095,7 @@
       <c r="T96" s="4"/>
       <c r="U96" s="4"/>
     </row>
-    <row r="97" ht="15.75" customHeight="1">
+    <row r="97" ht="15.75" customHeight="1" spans="1:21">
       <c r="A97" s="4"/>
       <c r="B97" s="4"/>
       <c r="C97" s="4"/>
@@ -3091,7 +4118,7 @@
       <c r="T97" s="4"/>
       <c r="U97" s="4"/>
     </row>
-    <row r="98" ht="15.75" customHeight="1">
+    <row r="98" ht="15.75" customHeight="1" spans="1:21">
       <c r="A98" s="4"/>
       <c r="B98" s="4"/>
       <c r="C98" s="4"/>
@@ -3114,7 +4141,7 @@
       <c r="T98" s="4"/>
       <c r="U98" s="4"/>
     </row>
-    <row r="99" ht="15.75" customHeight="1">
+    <row r="99" ht="15.75" customHeight="1" spans="1:21">
       <c r="A99" s="4"/>
       <c r="B99" s="4"/>
       <c r="C99" s="4"/>
@@ -3137,7 +4164,7 @@
       <c r="T99" s="4"/>
       <c r="U99" s="4"/>
     </row>
-    <row r="100" ht="15.75" customHeight="1">
+    <row r="100" ht="15.75" customHeight="1" spans="1:21">
       <c r="A100" s="4"/>
       <c r="B100" s="4"/>
       <c r="C100" s="4"/>
@@ -3160,7 +4187,7 @@
       <c r="T100" s="4"/>
       <c r="U100" s="4"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="15.75" customHeight="1" spans="1:21">
       <c r="A101" s="4"/>
       <c r="B101" s="4"/>
       <c r="C101" s="4"/>
@@ -3183,7 +4210,7 @@
       <c r="T101" s="4"/>
       <c r="U101" s="4"/>
     </row>
-    <row r="102" ht="15.75" customHeight="1">
+    <row r="102" ht="15.75" customHeight="1" spans="1:21">
       <c r="A102" s="4"/>
       <c r="B102" s="4"/>
       <c r="C102" s="4"/>
@@ -3206,7 +4233,7 @@
       <c r="T102" s="4"/>
       <c r="U102" s="4"/>
     </row>
-    <row r="103" ht="15.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1" spans="1:21">
       <c r="A103" s="4"/>
       <c r="B103" s="4"/>
       <c r="C103" s="4"/>
@@ -3229,7 +4256,7 @@
       <c r="T103" s="4"/>
       <c r="U103" s="4"/>
     </row>
-    <row r="104" ht="15.75" customHeight="1">
+    <row r="104" ht="15.75" customHeight="1" spans="1:21">
       <c r="A104" s="4"/>
       <c r="B104" s="4"/>
       <c r="C104" s="4"/>
@@ -3252,7 +4279,7 @@
       <c r="T104" s="4"/>
       <c r="U104" s="4"/>
     </row>
-    <row r="105" ht="15.75" customHeight="1">
+    <row r="105" ht="15.75" customHeight="1" spans="1:21">
       <c r="A105" s="4"/>
       <c r="B105" s="4"/>
       <c r="C105" s="4"/>
@@ -3275,7 +4302,7 @@
       <c r="T105" s="4"/>
       <c r="U105" s="4"/>
     </row>
-    <row r="106" ht="15.75" customHeight="1">
+    <row r="106" ht="15.75" customHeight="1" spans="1:21">
       <c r="A106" s="4"/>
       <c r="B106" s="4"/>
       <c r="C106" s="4"/>
@@ -3298,7 +4325,7 @@
       <c r="T106" s="4"/>
       <c r="U106" s="4"/>
     </row>
-    <row r="107" ht="15.75" customHeight="1">
+    <row r="107" ht="15.75" customHeight="1" spans="1:21">
       <c r="A107" s="4"/>
       <c r="B107" s="4"/>
       <c r="C107" s="4"/>
@@ -3321,7 +4348,7 @@
       <c r="T107" s="4"/>
       <c r="U107" s="4"/>
     </row>
-    <row r="108" ht="15.75" customHeight="1">
+    <row r="108" ht="15.75" customHeight="1" spans="1:21">
       <c r="A108" s="4"/>
       <c r="B108" s="4"/>
       <c r="C108" s="4"/>
@@ -3344,7 +4371,7 @@
       <c r="T108" s="4"/>
       <c r="U108" s="4"/>
     </row>
-    <row r="109" ht="15.75" customHeight="1">
+    <row r="109" ht="15.75" customHeight="1" spans="1:21">
       <c r="A109" s="4"/>
       <c r="B109" s="4"/>
       <c r="C109" s="4"/>
@@ -3367,7 +4394,7 @@
       <c r="T109" s="4"/>
       <c r="U109" s="4"/>
     </row>
-    <row r="110" ht="15.75" customHeight="1">
+    <row r="110" ht="15.75" customHeight="1" spans="1:21">
       <c r="A110" s="4"/>
       <c r="B110" s="4"/>
       <c r="C110" s="4"/>
@@ -3390,7 +4417,7 @@
       <c r="T110" s="4"/>
       <c r="U110" s="4"/>
     </row>
-    <row r="111" ht="15.75" customHeight="1">
+    <row r="111" ht="15.75" customHeight="1" spans="1:21">
       <c r="A111" s="4"/>
       <c r="B111" s="4"/>
       <c r="C111" s="4"/>
@@ -3413,7 +4440,7 @@
       <c r="T111" s="4"/>
       <c r="U111" s="4"/>
     </row>
-    <row r="112" ht="15.75" customHeight="1">
+    <row r="112" ht="15.75" customHeight="1" spans="1:21">
       <c r="A112" s="4"/>
       <c r="B112" s="4"/>
       <c r="C112" s="4"/>
@@ -3436,7 +4463,7 @@
       <c r="T112" s="4"/>
       <c r="U112" s="4"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="15.75" customHeight="1" spans="1:21">
       <c r="A113" s="4"/>
       <c r="B113" s="4"/>
       <c r="C113" s="4"/>
@@ -3459,7 +4486,7 @@
       <c r="T113" s="4"/>
       <c r="U113" s="4"/>
     </row>
-    <row r="114" ht="15.75" customHeight="1">
+    <row r="114" ht="15.75" customHeight="1" spans="1:21">
       <c r="A114" s="4"/>
       <c r="B114" s="4"/>
       <c r="C114" s="4"/>
@@ -3482,7 +4509,7 @@
       <c r="T114" s="4"/>
       <c r="U114" s="4"/>
     </row>
-    <row r="115" ht="15.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1" spans="1:21">
       <c r="A115" s="4"/>
       <c r="B115" s="4"/>
       <c r="C115" s="4"/>
@@ -3505,7 +4532,7 @@
       <c r="T115" s="4"/>
       <c r="U115" s="4"/>
     </row>
-    <row r="116" ht="15.75" customHeight="1">
+    <row r="116" ht="15.75" customHeight="1" spans="1:21">
       <c r="A116" s="4"/>
       <c r="B116" s="4"/>
       <c r="C116" s="4"/>
@@ -3528,7 +4555,7 @@
       <c r="T116" s="4"/>
       <c r="U116" s="4"/>
     </row>
-    <row r="117" ht="15.75" customHeight="1">
+    <row r="117" ht="15.75" customHeight="1" spans="1:21">
       <c r="A117" s="4"/>
       <c r="B117" s="4"/>
       <c r="C117" s="4"/>
@@ -3551,7 +4578,7 @@
       <c r="T117" s="4"/>
       <c r="U117" s="4"/>
     </row>
-    <row r="118" ht="15.75" customHeight="1">
+    <row r="118" ht="15.75" customHeight="1" spans="1:21">
       <c r="A118" s="4"/>
       <c r="B118" s="4"/>
       <c r="C118" s="4"/>
@@ -3574,7 +4601,7 @@
       <c r="T118" s="4"/>
       <c r="U118" s="4"/>
     </row>
-    <row r="119" ht="15.75" customHeight="1">
+    <row r="119" ht="15.75" customHeight="1" spans="1:21">
       <c r="A119" s="4"/>
       <c r="B119" s="4"/>
       <c r="C119" s="4"/>
@@ -3597,7 +4624,7 @@
       <c r="T119" s="4"/>
       <c r="U119" s="4"/>
     </row>
-    <row r="120" ht="15.75" customHeight="1">
+    <row r="120" ht="15.75" customHeight="1" spans="1:21">
       <c r="A120" s="4"/>
       <c r="B120" s="4"/>
       <c r="C120" s="4"/>
@@ -3620,7 +4647,7 @@
       <c r="T120" s="4"/>
       <c r="U120" s="4"/>
     </row>
-    <row r="121" ht="15.75" customHeight="1">
+    <row r="121" ht="15.75" customHeight="1" spans="1:21">
       <c r="A121" s="4"/>
       <c r="B121" s="4"/>
       <c r="C121" s="4"/>
@@ -3643,7 +4670,7 @@
       <c r="T121" s="4"/>
       <c r="U121" s="4"/>
     </row>
-    <row r="122" ht="15.75" customHeight="1">
+    <row r="122" ht="15.75" customHeight="1" spans="1:21">
       <c r="A122" s="4"/>
       <c r="B122" s="4"/>
       <c r="C122" s="4"/>
@@ -3666,7 +4693,7 @@
       <c r="T122" s="4"/>
       <c r="U122" s="4"/>
     </row>
-    <row r="123" ht="15.75" customHeight="1">
+    <row r="123" ht="15.75" customHeight="1" spans="1:21">
       <c r="A123" s="4"/>
       <c r="B123" s="4"/>
       <c r="C123" s="4"/>
@@ -3689,7 +4716,7 @@
       <c r="T123" s="4"/>
       <c r="U123" s="4"/>
     </row>
-    <row r="124" ht="15.75" customHeight="1">
+    <row r="124" ht="15.75" customHeight="1" spans="1:21">
       <c r="A124" s="4"/>
       <c r="B124" s="4"/>
       <c r="C124" s="4"/>
@@ -3712,7 +4739,7 @@
       <c r="T124" s="4"/>
       <c r="U124" s="4"/>
     </row>
-    <row r="125" ht="15.75" customHeight="1">
+    <row r="125" ht="15.75" customHeight="1" spans="1:21">
       <c r="A125" s="4"/>
       <c r="B125" s="4"/>
       <c r="C125" s="4"/>
@@ -3735,7 +4762,7 @@
       <c r="T125" s="4"/>
       <c r="U125" s="4"/>
     </row>
-    <row r="126" ht="15.75" customHeight="1">
+    <row r="126" ht="15.75" customHeight="1" spans="1:21">
       <c r="A126" s="4"/>
       <c r="B126" s="4"/>
       <c r="C126" s="4"/>
@@ -3758,7 +4785,7 @@
       <c r="T126" s="4"/>
       <c r="U126" s="4"/>
     </row>
-    <row r="127" ht="15.75" customHeight="1">
+    <row r="127" ht="15.75" customHeight="1" spans="1:21">
       <c r="A127" s="4"/>
       <c r="B127" s="4"/>
       <c r="C127" s="4"/>
@@ -3781,7 +4808,7 @@
       <c r="T127" s="4"/>
       <c r="U127" s="4"/>
     </row>
-    <row r="128" ht="15.75" customHeight="1">
+    <row r="128" ht="15.75" customHeight="1" spans="1:21">
       <c r="A128" s="4"/>
       <c r="B128" s="4"/>
       <c r="C128" s="4"/>
@@ -3804,7 +4831,7 @@
       <c r="T128" s="4"/>
       <c r="U128" s="4"/>
     </row>
-    <row r="129" ht="15.75" customHeight="1">
+    <row r="129" ht="15.75" customHeight="1" spans="1:21">
       <c r="A129" s="4"/>
       <c r="B129" s="4"/>
       <c r="C129" s="4"/>
@@ -3827,7 +4854,7 @@
       <c r="T129" s="4"/>
       <c r="U129" s="4"/>
     </row>
-    <row r="130" ht="15.75" customHeight="1">
+    <row r="130" ht="15.75" customHeight="1" spans="1:21">
       <c r="A130" s="4"/>
       <c r="B130" s="4"/>
       <c r="C130" s="4"/>
@@ -3850,7 +4877,7 @@
       <c r="T130" s="4"/>
       <c r="U130" s="4"/>
     </row>
-    <row r="131" ht="15.75" customHeight="1">
+    <row r="131" ht="15.75" customHeight="1" spans="1:21">
       <c r="A131" s="4"/>
       <c r="B131" s="4"/>
       <c r="C131" s="4"/>
@@ -3873,7 +4900,7 @@
       <c r="T131" s="4"/>
       <c r="U131" s="4"/>
     </row>
-    <row r="132" ht="15.75" customHeight="1">
+    <row r="132" ht="15.75" customHeight="1" spans="1:21">
       <c r="A132" s="4"/>
       <c r="B132" s="4"/>
       <c r="C132" s="4"/>
@@ -3896,7 +4923,7 @@
       <c r="T132" s="4"/>
       <c r="U132" s="4"/>
     </row>
-    <row r="133" ht="15.75" customHeight="1">
+    <row r="133" ht="15.75" customHeight="1" spans="1:21">
       <c r="A133" s="4"/>
       <c r="B133" s="4"/>
       <c r="C133" s="4"/>
@@ -3919,7 +4946,7 @@
       <c r="T133" s="4"/>
       <c r="U133" s="4"/>
     </row>
-    <row r="134" ht="15.75" customHeight="1">
+    <row r="134" ht="15.75" customHeight="1" spans="1:21">
       <c r="A134" s="4"/>
       <c r="B134" s="4"/>
       <c r="C134" s="4"/>
@@ -3942,7 +4969,7 @@
       <c r="T134" s="4"/>
       <c r="U134" s="4"/>
     </row>
-    <row r="135" ht="15.75" customHeight="1">
+    <row r="135" ht="15.75" customHeight="1" spans="1:21">
       <c r="A135" s="4"/>
       <c r="B135" s="4"/>
       <c r="C135" s="4"/>
@@ -3965,7 +4992,7 @@
       <c r="T135" s="4"/>
       <c r="U135" s="4"/>
     </row>
-    <row r="136" ht="15.75" customHeight="1">
+    <row r="136" ht="15.75" customHeight="1" spans="1:21">
       <c r="A136" s="4"/>
       <c r="B136" s="4"/>
       <c r="C136" s="4"/>
@@ -3988,7 +5015,7 @@
       <c r="T136" s="4"/>
       <c r="U136" s="4"/>
     </row>
-    <row r="137" ht="15.75" customHeight="1">
+    <row r="137" ht="15.75" customHeight="1" spans="1:21">
       <c r="A137" s="4"/>
       <c r="B137" s="4"/>
       <c r="C137" s="4"/>
@@ -4011,7 +5038,7 @@
       <c r="T137" s="4"/>
       <c r="U137" s="4"/>
     </row>
-    <row r="138" ht="15.75" customHeight="1">
+    <row r="138" ht="15.75" customHeight="1" spans="1:21">
       <c r="A138" s="4"/>
       <c r="B138" s="4"/>
       <c r="C138" s="4"/>
@@ -4034,7 +5061,7 @@
       <c r="T138" s="4"/>
       <c r="U138" s="4"/>
     </row>
-    <row r="139" ht="15.75" customHeight="1">
+    <row r="139" ht="15.75" customHeight="1" spans="1:21">
       <c r="A139" s="4"/>
       <c r="B139" s="4"/>
       <c r="C139" s="4"/>
@@ -4057,7 +5084,7 @@
       <c r="T139" s="4"/>
       <c r="U139" s="4"/>
     </row>
-    <row r="140" ht="15.75" customHeight="1">
+    <row r="140" ht="15.75" customHeight="1" spans="1:21">
       <c r="A140" s="4"/>
       <c r="B140" s="4"/>
       <c r="C140" s="4"/>
@@ -4080,7 +5107,7 @@
       <c r="T140" s="4"/>
       <c r="U140" s="4"/>
     </row>
-    <row r="141" ht="15.75" customHeight="1">
+    <row r="141" ht="15.75" customHeight="1" spans="1:21">
       <c r="A141" s="4"/>
       <c r="B141" s="4"/>
       <c r="C141" s="4"/>
@@ -4103,7 +5130,7 @@
       <c r="T141" s="4"/>
       <c r="U141" s="4"/>
     </row>
-    <row r="142" ht="15.75" customHeight="1">
+    <row r="142" ht="15.75" customHeight="1" spans="1:21">
       <c r="A142" s="4"/>
       <c r="B142" s="4"/>
       <c r="C142" s="4"/>
@@ -4126,7 +5153,7 @@
       <c r="T142" s="4"/>
       <c r="U142" s="4"/>
     </row>
-    <row r="143" ht="15.75" customHeight="1">
+    <row r="143" ht="15.75" customHeight="1" spans="1:21">
       <c r="A143" s="4"/>
       <c r="B143" s="4"/>
       <c r="C143" s="4"/>
@@ -4149,7 +5176,7 @@
       <c r="T143" s="4"/>
       <c r="U143" s="4"/>
     </row>
-    <row r="144" ht="15.75" customHeight="1">
+    <row r="144" ht="15.75" customHeight="1" spans="1:21">
       <c r="A144" s="4"/>
       <c r="B144" s="4"/>
       <c r="C144" s="4"/>
@@ -4172,7 +5199,7 @@
       <c r="T144" s="4"/>
       <c r="U144" s="4"/>
     </row>
-    <row r="145" ht="15.75" customHeight="1">
+    <row r="145" ht="15.75" customHeight="1" spans="1:21">
       <c r="A145" s="4"/>
       <c r="B145" s="4"/>
       <c r="C145" s="4"/>
@@ -4195,7 +5222,7 @@
       <c r="T145" s="4"/>
       <c r="U145" s="4"/>
     </row>
-    <row r="146" ht="15.75" customHeight="1">
+    <row r="146" ht="15.75" customHeight="1" spans="1:21">
       <c r="A146" s="4"/>
       <c r="B146" s="4"/>
       <c r="C146" s="4"/>
@@ -4218,7 +5245,7 @@
       <c r="T146" s="4"/>
       <c r="U146" s="4"/>
     </row>
-    <row r="147" ht="15.75" customHeight="1">
+    <row r="147" ht="15.75" customHeight="1" spans="1:21">
       <c r="A147" s="4"/>
       <c r="B147" s="4"/>
       <c r="C147" s="4"/>
@@ -4241,7 +5268,7 @@
       <c r="T147" s="4"/>
       <c r="U147" s="4"/>
     </row>
-    <row r="148" ht="15.75" customHeight="1">
+    <row r="148" ht="15.75" customHeight="1" spans="1:21">
       <c r="A148" s="4"/>
       <c r="B148" s="4"/>
       <c r="C148" s="4"/>
@@ -4264,7 +5291,7 @@
       <c r="T148" s="4"/>
       <c r="U148" s="4"/>
     </row>
-    <row r="149" ht="15.75" customHeight="1">
+    <row r="149" ht="15.75" customHeight="1" spans="1:21">
       <c r="A149" s="4"/>
       <c r="B149" s="4"/>
       <c r="C149" s="4"/>
@@ -4287,7 +5314,7 @@
       <c r="T149" s="4"/>
       <c r="U149" s="4"/>
     </row>
-    <row r="150" ht="15.75" customHeight="1">
+    <row r="150" ht="15.75" customHeight="1" spans="1:21">
       <c r="A150" s="4"/>
       <c r="B150" s="4"/>
       <c r="C150" s="4"/>
@@ -4310,7 +5337,7 @@
       <c r="T150" s="4"/>
       <c r="U150" s="4"/>
     </row>
-    <row r="151" ht="15.75" customHeight="1">
+    <row r="151" ht="15.75" customHeight="1" spans="1:21">
       <c r="A151" s="4"/>
       <c r="B151" s="4"/>
       <c r="C151" s="4"/>
@@ -4333,7 +5360,7 @@
       <c r="T151" s="4"/>
       <c r="U151" s="4"/>
     </row>
-    <row r="152" ht="15.75" customHeight="1">
+    <row r="152" ht="15.75" customHeight="1" spans="1:21">
       <c r="A152" s="4"/>
       <c r="B152" s="4"/>
       <c r="C152" s="4"/>
@@ -4356,7 +5383,7 @@
       <c r="T152" s="4"/>
       <c r="U152" s="4"/>
     </row>
-    <row r="153" ht="15.75" customHeight="1">
+    <row r="153" ht="15.75" customHeight="1" spans="1:21">
       <c r="A153" s="4"/>
       <c r="B153" s="4"/>
       <c r="C153" s="4"/>
@@ -4379,7 +5406,7 @@
       <c r="T153" s="4"/>
       <c r="U153" s="4"/>
     </row>
-    <row r="154" ht="15.75" customHeight="1">
+    <row r="154" ht="15.75" customHeight="1" spans="1:21">
       <c r="A154" s="4"/>
       <c r="B154" s="4"/>
       <c r="C154" s="4"/>
@@ -4402,7 +5429,7 @@
       <c r="T154" s="4"/>
       <c r="U154" s="4"/>
     </row>
-    <row r="155" ht="15.75" customHeight="1">
+    <row r="155" ht="15.75" customHeight="1" spans="1:21">
       <c r="A155" s="4"/>
       <c r="B155" s="4"/>
       <c r="C155" s="4"/>
@@ -4425,7 +5452,7 @@
       <c r="T155" s="4"/>
       <c r="U155" s="4"/>
     </row>
-    <row r="156" ht="15.75" customHeight="1">
+    <row r="156" ht="15.75" customHeight="1" spans="1:21">
       <c r="A156" s="4"/>
       <c r="B156" s="4"/>
       <c r="C156" s="4"/>
@@ -4448,7 +5475,7 @@
       <c r="T156" s="4"/>
       <c r="U156" s="4"/>
     </row>
-    <row r="157" ht="15.75" customHeight="1">
+    <row r="157" ht="15.75" customHeight="1" spans="1:21">
       <c r="A157" s="4"/>
       <c r="B157" s="4"/>
       <c r="C157" s="4"/>
@@ -4471,7 +5498,7 @@
       <c r="T157" s="4"/>
       <c r="U157" s="4"/>
     </row>
-    <row r="158" ht="15.75" customHeight="1">
+    <row r="158" ht="15.75" customHeight="1" spans="1:21">
       <c r="A158" s="4"/>
       <c r="B158" s="4"/>
       <c r="C158" s="4"/>
@@ -4494,7 +5521,7 @@
       <c r="T158" s="4"/>
       <c r="U158" s="4"/>
     </row>
-    <row r="159" ht="15.75" customHeight="1">
+    <row r="159" ht="15.75" customHeight="1" spans="1:21">
       <c r="A159" s="4"/>
       <c r="B159" s="4"/>
       <c r="C159" s="4"/>
@@ -4517,7 +5544,7 @@
       <c r="T159" s="4"/>
       <c r="U159" s="4"/>
     </row>
-    <row r="160" ht="15.75" customHeight="1">
+    <row r="160" ht="15.75" customHeight="1" spans="1:21">
       <c r="A160" s="4"/>
       <c r="B160" s="4"/>
       <c r="C160" s="4"/>
@@ -4540,7 +5567,7 @@
       <c r="T160" s="4"/>
       <c r="U160" s="4"/>
     </row>
-    <row r="161" ht="15.75" customHeight="1">
+    <row r="161" ht="15.75" customHeight="1" spans="1:21">
       <c r="A161" s="4"/>
       <c r="B161" s="4"/>
       <c r="C161" s="4"/>
@@ -4563,7 +5590,7 @@
       <c r="T161" s="4"/>
       <c r="U161" s="4"/>
     </row>
-    <row r="162" ht="15.75" customHeight="1">
+    <row r="162" ht="15.75" customHeight="1" spans="1:21">
       <c r="A162" s="4"/>
       <c r="B162" s="4"/>
       <c r="C162" s="4"/>
@@ -4586,7 +5613,7 @@
       <c r="T162" s="4"/>
       <c r="U162" s="4"/>
     </row>
-    <row r="163" ht="15.75" customHeight="1">
+    <row r="163" ht="15.75" customHeight="1" spans="1:21">
       <c r="A163" s="4"/>
       <c r="B163" s="4"/>
       <c r="C163" s="4"/>
@@ -4609,7 +5636,7 @@
       <c r="T163" s="4"/>
       <c r="U163" s="4"/>
     </row>
-    <row r="164" ht="15.75" customHeight="1">
+    <row r="164" ht="15.75" customHeight="1" spans="1:21">
       <c r="A164" s="4"/>
       <c r="B164" s="4"/>
       <c r="C164" s="4"/>
@@ -4632,7 +5659,7 @@
       <c r="T164" s="4"/>
       <c r="U164" s="4"/>
     </row>
-    <row r="165" ht="15.75" customHeight="1">
+    <row r="165" ht="15.75" customHeight="1" spans="1:21">
       <c r="A165" s="4"/>
       <c r="B165" s="4"/>
       <c r="C165" s="4"/>
@@ -4655,7 +5682,7 @@
       <c r="T165" s="4"/>
       <c r="U165" s="4"/>
     </row>
-    <row r="166" ht="15.75" customHeight="1">
+    <row r="166" ht="15.75" customHeight="1" spans="1:21">
       <c r="A166" s="4"/>
       <c r="B166" s="4"/>
       <c r="C166" s="4"/>
@@ -4678,7 +5705,7 @@
       <c r="T166" s="4"/>
       <c r="U166" s="4"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="15.75" customHeight="1" spans="1:21">
       <c r="A167" s="4"/>
       <c r="B167" s="4"/>
       <c r="C167" s="4"/>
@@ -4701,7 +5728,7 @@
       <c r="T167" s="4"/>
       <c r="U167" s="4"/>
     </row>
-    <row r="168" ht="15.75" customHeight="1">
+    <row r="168" ht="15.75" customHeight="1" spans="1:21">
       <c r="A168" s="4"/>
       <c r="B168" s="4"/>
       <c r="C168" s="4"/>
@@ -4724,7 +5751,7 @@
       <c r="T168" s="4"/>
       <c r="U168" s="4"/>
     </row>
-    <row r="169" ht="15.75" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1" spans="1:21">
       <c r="A169" s="4"/>
       <c r="B169" s="4"/>
       <c r="C169" s="4"/>
@@ -4747,7 +5774,7 @@
       <c r="T169" s="4"/>
       <c r="U169" s="4"/>
     </row>
-    <row r="170" ht="15.75" customHeight="1">
+    <row r="170" ht="15.75" customHeight="1" spans="1:21">
       <c r="A170" s="4"/>
       <c r="B170" s="4"/>
       <c r="C170" s="4"/>
@@ -4770,7 +5797,7 @@
       <c r="T170" s="4"/>
       <c r="U170" s="4"/>
     </row>
-    <row r="171" ht="15.75" customHeight="1">
+    <row r="171" ht="15.75" customHeight="1" spans="1:21">
       <c r="A171" s="4"/>
       <c r="B171" s="4"/>
       <c r="C171" s="4"/>
@@ -4793,7 +5820,7 @@
       <c r="T171" s="4"/>
       <c r="U171" s="4"/>
     </row>
-    <row r="172" ht="15.75" customHeight="1">
+    <row r="172" ht="15.75" customHeight="1" spans="1:21">
       <c r="A172" s="4"/>
       <c r="B172" s="4"/>
       <c r="C172" s="4"/>
@@ -4816,7 +5843,7 @@
       <c r="T172" s="4"/>
       <c r="U172" s="4"/>
     </row>
-    <row r="173" ht="15.75" customHeight="1">
+    <row r="173" ht="15.75" customHeight="1" spans="1:21">
       <c r="A173" s="4"/>
       <c r="B173" s="4"/>
       <c r="C173" s="4"/>
@@ -4839,7 +5866,7 @@
       <c r="T173" s="4"/>
       <c r="U173" s="4"/>
     </row>
-    <row r="174" ht="15.75" customHeight="1">
+    <row r="174" ht="15.75" customHeight="1" spans="1:21">
       <c r="A174" s="4"/>
       <c r="B174" s="4"/>
       <c r="C174" s="4"/>
@@ -4862,7 +5889,7 @@
       <c r="T174" s="4"/>
       <c r="U174" s="4"/>
     </row>
-    <row r="175" ht="15.75" customHeight="1">
+    <row r="175" ht="15.75" customHeight="1" spans="1:21">
       <c r="A175" s="4"/>
       <c r="B175" s="4"/>
       <c r="C175" s="4"/>
@@ -4885,7 +5912,7 @@
       <c r="T175" s="4"/>
       <c r="U175" s="4"/>
     </row>
-    <row r="176" ht="15.75" customHeight="1">
+    <row r="176" ht="15.75" customHeight="1" spans="1:21">
       <c r="A176" s="4"/>
       <c r="B176" s="4"/>
       <c r="C176" s="4"/>
@@ -4908,7 +5935,7 @@
       <c r="T176" s="4"/>
       <c r="U176" s="4"/>
     </row>
-    <row r="177" ht="15.75" customHeight="1">
+    <row r="177" ht="15.75" customHeight="1" spans="1:21">
       <c r="A177" s="4"/>
       <c r="B177" s="4"/>
       <c r="C177" s="4"/>
@@ -4931,7 +5958,7 @@
       <c r="T177" s="4"/>
       <c r="U177" s="4"/>
     </row>
-    <row r="178" ht="15.75" customHeight="1">
+    <row r="178" ht="15.75" customHeight="1" spans="1:21">
       <c r="A178" s="4"/>
       <c r="B178" s="4"/>
       <c r="C178" s="4"/>
@@ -4954,7 +5981,7 @@
       <c r="T178" s="4"/>
       <c r="U178" s="4"/>
     </row>
-    <row r="179" ht="15.75" customHeight="1">
+    <row r="179" ht="15.75" customHeight="1" spans="1:21">
       <c r="A179" s="4"/>
       <c r="B179" s="4"/>
       <c r="C179" s="4"/>
@@ -4977,7 +6004,7 @@
       <c r="T179" s="4"/>
       <c r="U179" s="4"/>
     </row>
-    <row r="180" ht="15.75" customHeight="1">
+    <row r="180" ht="15.75" customHeight="1" spans="1:21">
       <c r="A180" s="4"/>
       <c r="B180" s="4"/>
       <c r="C180" s="4"/>
@@ -5000,7 +6027,7 @@
       <c r="T180" s="4"/>
       <c r="U180" s="4"/>
     </row>
-    <row r="181" ht="15.75" customHeight="1">
+    <row r="181" ht="15.75" customHeight="1" spans="1:21">
       <c r="A181" s="4"/>
       <c r="B181" s="4"/>
       <c r="C181" s="4"/>
@@ -5023,7 +6050,7 @@
       <c r="T181" s="4"/>
       <c r="U181" s="4"/>
     </row>
-    <row r="182" ht="15.75" customHeight="1">
+    <row r="182" ht="15.75" customHeight="1" spans="1:21">
       <c r="A182" s="4"/>
       <c r="B182" s="4"/>
       <c r="C182" s="4"/>
@@ -5046,7 +6073,7 @@
       <c r="T182" s="4"/>
       <c r="U182" s="4"/>
     </row>
-    <row r="183" ht="15.75" customHeight="1">
+    <row r="183" ht="15.75" customHeight="1" spans="1:21">
       <c r="A183" s="4"/>
       <c r="B183" s="4"/>
       <c r="C183" s="4"/>
@@ -5069,7 +6096,7 @@
       <c r="T183" s="4"/>
       <c r="U183" s="4"/>
     </row>
-    <row r="184" ht="15.75" customHeight="1">
+    <row r="184" ht="15.75" customHeight="1" spans="1:21">
       <c r="A184" s="4"/>
       <c r="B184" s="4"/>
       <c r="C184" s="4"/>
@@ -5092,7 +6119,7 @@
       <c r="T184" s="4"/>
       <c r="U184" s="4"/>
     </row>
-    <row r="185" ht="15.75" customHeight="1">
+    <row r="185" ht="15.75" customHeight="1" spans="1:21">
       <c r="A185" s="4"/>
       <c r="B185" s="4"/>
       <c r="C185" s="4"/>
@@ -5115,7 +6142,7 @@
       <c r="T185" s="4"/>
       <c r="U185" s="4"/>
     </row>
-    <row r="186" ht="15.75" customHeight="1">
+    <row r="186" ht="15.75" customHeight="1" spans="1:21">
       <c r="A186" s="4"/>
       <c r="B186" s="4"/>
       <c r="C186" s="4"/>
@@ -5138,7 +6165,7 @@
       <c r="T186" s="4"/>
       <c r="U186" s="4"/>
     </row>
-    <row r="187" ht="15.75" customHeight="1">
+    <row r="187" ht="15.75" customHeight="1" spans="1:21">
       <c r="A187" s="4"/>
       <c r="B187" s="4"/>
       <c r="C187" s="4"/>
@@ -5161,7 +6188,7 @@
       <c r="T187" s="4"/>
       <c r="U187" s="4"/>
     </row>
-    <row r="188" ht="15.75" customHeight="1">
+    <row r="188" ht="15.75" customHeight="1" spans="1:21">
       <c r="A188" s="4"/>
       <c r="B188" s="4"/>
       <c r="C188" s="4"/>
@@ -5184,7 +6211,7 @@
       <c r="T188" s="4"/>
       <c r="U188" s="4"/>
     </row>
-    <row r="189" ht="15.75" customHeight="1">
+    <row r="189" ht="15.75" customHeight="1" spans="1:21">
       <c r="A189" s="4"/>
       <c r="B189" s="4"/>
       <c r="C189" s="4"/>
@@ -5207,7 +6234,7 @@
       <c r="T189" s="4"/>
       <c r="U189" s="4"/>
     </row>
-    <row r="190" ht="15.75" customHeight="1">
+    <row r="190" ht="15.75" customHeight="1" spans="1:21">
       <c r="A190" s="4"/>
       <c r="B190" s="4"/>
       <c r="C190" s="4"/>
@@ -5230,7 +6257,7 @@
       <c r="T190" s="4"/>
       <c r="U190" s="4"/>
     </row>
-    <row r="191" ht="15.75" customHeight="1">
+    <row r="191" ht="15.75" customHeight="1" spans="1:21">
       <c r="A191" s="4"/>
       <c r="B191" s="4"/>
       <c r="C191" s="4"/>
@@ -5253,7 +6280,7 @@
       <c r="T191" s="4"/>
       <c r="U191" s="4"/>
     </row>
-    <row r="192" ht="15.75" customHeight="1">
+    <row r="192" ht="15.75" customHeight="1" spans="1:21">
       <c r="A192" s="4"/>
       <c r="B192" s="4"/>
       <c r="C192" s="4"/>
@@ -5276,7 +6303,7 @@
       <c r="T192" s="4"/>
       <c r="U192" s="4"/>
     </row>
-    <row r="193" ht="15.75" customHeight="1">
+    <row r="193" ht="15.75" customHeight="1" spans="1:21">
       <c r="A193" s="4"/>
       <c r="B193" s="4"/>
       <c r="C193" s="4"/>
@@ -5299,7 +6326,7 @@
       <c r="T193" s="4"/>
       <c r="U193" s="4"/>
     </row>
-    <row r="194" ht="15.75" customHeight="1">
+    <row r="194" ht="15.75" customHeight="1" spans="1:21">
       <c r="A194" s="4"/>
       <c r="B194" s="4"/>
       <c r="C194" s="4"/>
@@ -5322,7 +6349,7 @@
       <c r="T194" s="4"/>
       <c r="U194" s="4"/>
     </row>
-    <row r="195" ht="15.75" customHeight="1">
+    <row r="195" ht="15.75" customHeight="1" spans="1:21">
       <c r="A195" s="4"/>
       <c r="B195" s="4"/>
       <c r="C195" s="4"/>
@@ -5345,7 +6372,7 @@
       <c r="T195" s="4"/>
       <c r="U195" s="4"/>
     </row>
-    <row r="196" ht="15.75" customHeight="1">
+    <row r="196" ht="15.75" customHeight="1" spans="1:21">
       <c r="A196" s="4"/>
       <c r="B196" s="4"/>
       <c r="C196" s="4"/>
@@ -5368,7 +6395,7 @@
       <c r="T196" s="4"/>
       <c r="U196" s="4"/>
     </row>
-    <row r="197" ht="15.75" customHeight="1">
+    <row r="197" ht="15.75" customHeight="1" spans="1:21">
       <c r="A197" s="4"/>
       <c r="B197" s="4"/>
       <c r="C197" s="4"/>
@@ -5391,7 +6418,7 @@
       <c r="T197" s="4"/>
       <c r="U197" s="4"/>
     </row>
-    <row r="198" ht="15.75" customHeight="1">
+    <row r="198" ht="15.75" customHeight="1" spans="1:21">
       <c r="A198" s="4"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -5414,7 +6441,7 @@
       <c r="T198" s="4"/>
       <c r="U198" s="4"/>
     </row>
-    <row r="199" ht="15.75" customHeight="1">
+    <row r="199" ht="15.75" customHeight="1" spans="1:21">
       <c r="A199" s="4"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -5437,7 +6464,7 @@
       <c r="T199" s="4"/>
       <c r="U199" s="4"/>
     </row>
-    <row r="200" ht="15.75" customHeight="1">
+    <row r="200" ht="15.75" customHeight="1" spans="1:21">
       <c r="A200" s="4"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -5460,7 +6487,7 @@
       <c r="T200" s="4"/>
       <c r="U200" s="4"/>
     </row>
-    <row r="201" ht="15.75" customHeight="1">
+    <row r="201" ht="15.75" customHeight="1" spans="1:21">
       <c r="A201" s="4"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -5483,7 +6510,7 @@
       <c r="T201" s="4"/>
       <c r="U201" s="4"/>
     </row>
-    <row r="202" ht="15.75" customHeight="1">
+    <row r="202" ht="15.75" customHeight="1" spans="1:21">
       <c r="A202" s="4"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -5506,7 +6533,7 @@
       <c r="T202" s="4"/>
       <c r="U202" s="4"/>
     </row>
-    <row r="203" ht="15.75" customHeight="1">
+    <row r="203" ht="15.75" customHeight="1" spans="1:21">
       <c r="A203" s="4"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -5529,7 +6556,7 @@
       <c r="T203" s="4"/>
       <c r="U203" s="4"/>
     </row>
-    <row r="204" ht="15.75" customHeight="1">
+    <row r="204" ht="15.75" customHeight="1" spans="1:21">
       <c r="A204" s="4"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -5552,7 +6579,7 @@
       <c r="T204" s="4"/>
       <c r="U204" s="4"/>
     </row>
-    <row r="205" ht="15.75" customHeight="1">
+    <row r="205" ht="15.75" customHeight="1" spans="1:21">
       <c r="A205" s="4"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -5575,7 +6602,7 @@
       <c r="T205" s="4"/>
       <c r="U205" s="4"/>
     </row>
-    <row r="206" ht="15.75" customHeight="1">
+    <row r="206" ht="15.75" customHeight="1" spans="1:21">
       <c r="A206" s="4"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5598,7 +6625,7 @@
       <c r="T206" s="4"/>
       <c r="U206" s="4"/>
     </row>
-    <row r="207" ht="15.75" customHeight="1">
+    <row r="207" ht="15.75" customHeight="1" spans="1:21">
       <c r="A207" s="4"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5621,7 +6648,7 @@
       <c r="T207" s="4"/>
       <c r="U207" s="4"/>
     </row>
-    <row r="208" ht="15.75" customHeight="1">
+    <row r="208" ht="15.75" customHeight="1" spans="1:21">
       <c r="A208" s="4"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5644,7 +6671,7 @@
       <c r="T208" s="4"/>
       <c r="U208" s="4"/>
     </row>
-    <row r="209" ht="15.75" customHeight="1">
+    <row r="209" ht="15.75" customHeight="1" spans="1:21">
       <c r="A209" s="4"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -5667,7 +6694,7 @@
       <c r="T209" s="4"/>
       <c r="U209" s="4"/>
     </row>
-    <row r="210" ht="15.75" customHeight="1">
+    <row r="210" ht="15.75" customHeight="1" spans="1:21">
       <c r="A210" s="4"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -5690,7 +6717,7 @@
       <c r="T210" s="4"/>
       <c r="U210" s="4"/>
     </row>
-    <row r="211" ht="15.75" customHeight="1">
+    <row r="211" ht="15.75" customHeight="1" spans="1:21">
       <c r="A211" s="4"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -5713,7 +6740,7 @@
       <c r="T211" s="4"/>
       <c r="U211" s="4"/>
     </row>
-    <row r="212" ht="15.75" customHeight="1">
+    <row r="212" ht="15.75" customHeight="1" spans="1:21">
       <c r="A212" s="4"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5736,7 +6763,7 @@
       <c r="T212" s="4"/>
       <c r="U212" s="4"/>
     </row>
-    <row r="213" ht="15.75" customHeight="1">
+    <row r="213" ht="15.75" customHeight="1" spans="1:21">
       <c r="A213" s="4"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5759,7 +6786,7 @@
       <c r="T213" s="4"/>
       <c r="U213" s="4"/>
     </row>
-    <row r="214" ht="15.75" customHeight="1">
+    <row r="214" ht="15.75" customHeight="1" spans="1:21">
       <c r="A214" s="4"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5782,7 +6809,7 @@
       <c r="T214" s="4"/>
       <c r="U214" s="4"/>
     </row>
-    <row r="215" ht="15.75" customHeight="1">
+    <row r="215" ht="15.75" customHeight="1" spans="1:21">
       <c r="A215" s="4"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5805,7 +6832,7 @@
       <c r="T215" s="4"/>
       <c r="U215" s="4"/>
     </row>
-    <row r="216" ht="15.75" customHeight="1">
+    <row r="216" ht="15.75" customHeight="1" spans="1:21">
       <c r="A216" s="4"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5828,7 +6855,7 @@
       <c r="T216" s="4"/>
       <c r="U216" s="4"/>
     </row>
-    <row r="217" ht="15.75" customHeight="1">
+    <row r="217" ht="15.75" customHeight="1" spans="1:21">
       <c r="A217" s="4"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5851,7 +6878,7 @@
       <c r="T217" s="4"/>
       <c r="U217" s="4"/>
     </row>
-    <row r="218" ht="15.75" customHeight="1">
+    <row r="218" ht="15.75" customHeight="1" spans="1:21">
       <c r="A218" s="4"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5874,7 +6901,7 @@
       <c r="T218" s="4"/>
       <c r="U218" s="4"/>
     </row>
-    <row r="219" ht="15.75" customHeight="1">
+    <row r="219" ht="15.75" customHeight="1" spans="1:21">
       <c r="A219" s="4"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5897,7 +6924,7 @@
       <c r="T219" s="4"/>
       <c r="U219" s="4"/>
     </row>
-    <row r="220" ht="15.75" customHeight="1">
+    <row r="220" ht="15.75" customHeight="1" spans="1:21">
       <c r="A220" s="4"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5920,3130 +6947,3129 @@
       <c r="T220" s="4"/>
       <c r="U220" s="4"/>
     </row>
-    <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="12"/>
-      <c r="B221" s="12"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="12"/>
-      <c r="B222" s="12"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="12"/>
-      <c r="B223" s="12"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="12"/>
-      <c r="B224" s="12"/>
-    </row>
-    <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="12"/>
-      <c r="B225" s="12"/>
-    </row>
-    <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="12"/>
-      <c r="B226" s="12"/>
-    </row>
-    <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="12"/>
-      <c r="B227" s="12"/>
-    </row>
-    <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="12"/>
-      <c r="B228" s="12"/>
-    </row>
-    <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="12"/>
-      <c r="B229" s="12"/>
-    </row>
-    <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="12"/>
-      <c r="B230" s="12"/>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="12"/>
-      <c r="B231" s="12"/>
-    </row>
-    <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="12"/>
-      <c r="B232" s="12"/>
-    </row>
-    <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="12"/>
-      <c r="B233" s="12"/>
-    </row>
-    <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="12"/>
-      <c r="B234" s="12"/>
-    </row>
-    <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="12"/>
-      <c r="B235" s="12"/>
-    </row>
-    <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="12"/>
-      <c r="B236" s="12"/>
-    </row>
-    <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="12"/>
-      <c r="B237" s="12"/>
-    </row>
-    <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="12"/>
-      <c r="B238" s="12"/>
-    </row>
-    <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="12"/>
-      <c r="B239" s="12"/>
-    </row>
-    <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="12"/>
-      <c r="B240" s="12"/>
-    </row>
-    <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="12"/>
-      <c r="B241" s="12"/>
-    </row>
-    <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="12"/>
-      <c r="B242" s="12"/>
-    </row>
-    <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="12"/>
-      <c r="B243" s="12"/>
-    </row>
-    <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="12"/>
-      <c r="B244" s="12"/>
-    </row>
-    <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="12"/>
-      <c r="B245" s="12"/>
-    </row>
-    <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="12"/>
-      <c r="B246" s="12"/>
-    </row>
-    <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="12"/>
-      <c r="B247" s="12"/>
-    </row>
-    <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="12"/>
-      <c r="B248" s="12"/>
-    </row>
-    <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="12"/>
-      <c r="B249" s="12"/>
-    </row>
-    <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="12"/>
-      <c r="B250" s="12"/>
-    </row>
-    <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="12"/>
-      <c r="B251" s="12"/>
-    </row>
-    <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="12"/>
-      <c r="B252" s="12"/>
-    </row>
-    <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="12"/>
-      <c r="B253" s="12"/>
-    </row>
-    <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="12"/>
-      <c r="B254" s="12"/>
-    </row>
-    <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="12"/>
-      <c r="B255" s="12"/>
-    </row>
-    <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="12"/>
-      <c r="B256" s="12"/>
-    </row>
-    <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="12"/>
-      <c r="B257" s="12"/>
-    </row>
-    <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="12"/>
-      <c r="B258" s="12"/>
-    </row>
-    <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="12"/>
-      <c r="B259" s="12"/>
-    </row>
-    <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="12"/>
-      <c r="B260" s="12"/>
-    </row>
-    <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="12"/>
-      <c r="B261" s="12"/>
-    </row>
-    <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="12"/>
-      <c r="B262" s="12"/>
-    </row>
-    <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="12"/>
-      <c r="B263" s="12"/>
-    </row>
-    <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="12"/>
-      <c r="B264" s="12"/>
-    </row>
-    <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="12"/>
-      <c r="B265" s="12"/>
-    </row>
-    <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="12"/>
-      <c r="B266" s="12"/>
-    </row>
-    <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="12"/>
-      <c r="B267" s="12"/>
-    </row>
-    <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="12"/>
-      <c r="B268" s="12"/>
-    </row>
-    <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="12"/>
-      <c r="B269" s="12"/>
-    </row>
-    <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="12"/>
-      <c r="B270" s="12"/>
-    </row>
-    <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="12"/>
-      <c r="B271" s="12"/>
-    </row>
-    <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="12"/>
-      <c r="B272" s="12"/>
-    </row>
-    <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="12"/>
-      <c r="B273" s="12"/>
-    </row>
-    <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="12"/>
-      <c r="B274" s="12"/>
-    </row>
-    <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="12"/>
-      <c r="B275" s="12"/>
-    </row>
-    <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="12"/>
-      <c r="B276" s="12"/>
-    </row>
-    <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="12"/>
-      <c r="B277" s="12"/>
-    </row>
-    <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="12"/>
-      <c r="B278" s="12"/>
-    </row>
-    <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="12"/>
-      <c r="B279" s="12"/>
-    </row>
-    <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="12"/>
-      <c r="B280" s="12"/>
-    </row>
-    <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="12"/>
-      <c r="B281" s="12"/>
-    </row>
-    <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="12"/>
-      <c r="B282" s="12"/>
-    </row>
-    <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="12"/>
-      <c r="B283" s="12"/>
-    </row>
-    <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="12"/>
-      <c r="B284" s="12"/>
-    </row>
-    <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="12"/>
-      <c r="B285" s="12"/>
-    </row>
-    <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="12"/>
-      <c r="B286" s="12"/>
-    </row>
-    <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="12"/>
-      <c r="B287" s="12"/>
-    </row>
-    <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="12"/>
-      <c r="B288" s="12"/>
-    </row>
-    <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="12"/>
-      <c r="B289" s="12"/>
-    </row>
-    <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="12"/>
-      <c r="B290" s="12"/>
-    </row>
-    <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="12"/>
-      <c r="B291" s="12"/>
-    </row>
-    <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="12"/>
-      <c r="B292" s="12"/>
-    </row>
-    <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="12"/>
-      <c r="B293" s="12"/>
-    </row>
-    <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="12"/>
-      <c r="B294" s="12"/>
-    </row>
-    <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="12"/>
-      <c r="B295" s="12"/>
-    </row>
-    <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="12"/>
-      <c r="B296" s="12"/>
-    </row>
-    <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="12"/>
-      <c r="B297" s="12"/>
-    </row>
-    <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="12"/>
-      <c r="B298" s="12"/>
-    </row>
-    <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="12"/>
-      <c r="B299" s="12"/>
-    </row>
-    <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="12"/>
-      <c r="B300" s="12"/>
-    </row>
-    <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="12"/>
-      <c r="B301" s="12"/>
-    </row>
-    <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="12"/>
-      <c r="B302" s="12"/>
-    </row>
-    <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="12"/>
-      <c r="B303" s="12"/>
-    </row>
-    <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="12"/>
-      <c r="B304" s="12"/>
-    </row>
-    <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="12"/>
-      <c r="B305" s="12"/>
-    </row>
-    <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="12"/>
-      <c r="B306" s="12"/>
-    </row>
-    <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="12"/>
-      <c r="B307" s="12"/>
-    </row>
-    <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="12"/>
-      <c r="B308" s="12"/>
-    </row>
-    <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="12"/>
-      <c r="B309" s="12"/>
-    </row>
-    <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="12"/>
-      <c r="B310" s="12"/>
-    </row>
-    <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="12"/>
-      <c r="B311" s="12"/>
-    </row>
-    <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="12"/>
-      <c r="B312" s="12"/>
-    </row>
-    <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="12"/>
-      <c r="B313" s="12"/>
-    </row>
-    <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="12"/>
-      <c r="B314" s="12"/>
-    </row>
-    <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="12"/>
-      <c r="B315" s="12"/>
-    </row>
-    <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="12"/>
-      <c r="B316" s="12"/>
-    </row>
-    <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="12"/>
-      <c r="B317" s="12"/>
-    </row>
-    <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="12"/>
-      <c r="B318" s="12"/>
-    </row>
-    <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="12"/>
-      <c r="B319" s="12"/>
-    </row>
-    <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="12"/>
-      <c r="B320" s="12"/>
-    </row>
-    <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="12"/>
-      <c r="B321" s="12"/>
-    </row>
-    <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="12"/>
-      <c r="B322" s="12"/>
-    </row>
-    <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="12"/>
-      <c r="B323" s="12"/>
-    </row>
-    <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="12"/>
-      <c r="B324" s="12"/>
-    </row>
-    <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="12"/>
-      <c r="B325" s="12"/>
-    </row>
-    <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="12"/>
-      <c r="B326" s="12"/>
-    </row>
-    <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="12"/>
-      <c r="B327" s="12"/>
-    </row>
-    <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="12"/>
-      <c r="B328" s="12"/>
-    </row>
-    <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="12"/>
-      <c r="B329" s="12"/>
-    </row>
-    <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="12"/>
-      <c r="B330" s="12"/>
-    </row>
-    <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="12"/>
-      <c r="B331" s="12"/>
-    </row>
-    <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="12"/>
-      <c r="B332" s="12"/>
-    </row>
-    <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="12"/>
-      <c r="B333" s="12"/>
-    </row>
-    <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="12"/>
-      <c r="B334" s="12"/>
-    </row>
-    <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="12"/>
-      <c r="B335" s="12"/>
-    </row>
-    <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="12"/>
-      <c r="B336" s="12"/>
-    </row>
-    <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="12"/>
-      <c r="B337" s="12"/>
-    </row>
-    <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="12"/>
-      <c r="B338" s="12"/>
-    </row>
-    <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="12"/>
-      <c r="B339" s="12"/>
-    </row>
-    <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="12"/>
-      <c r="B340" s="12"/>
-    </row>
-    <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="12"/>
-      <c r="B341" s="12"/>
-    </row>
-    <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="12"/>
-      <c r="B342" s="12"/>
-    </row>
-    <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="12"/>
-      <c r="B343" s="12"/>
-    </row>
-    <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="12"/>
-      <c r="B344" s="12"/>
-    </row>
-    <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="12"/>
-      <c r="B345" s="12"/>
-    </row>
-    <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="12"/>
-      <c r="B346" s="12"/>
-    </row>
-    <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="12"/>
-      <c r="B347" s="12"/>
-    </row>
-    <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="12"/>
-      <c r="B348" s="12"/>
-    </row>
-    <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="12"/>
-      <c r="B349" s="12"/>
-    </row>
-    <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="12"/>
-      <c r="B350" s="12"/>
-    </row>
-    <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="12"/>
-      <c r="B351" s="12"/>
-    </row>
-    <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="12"/>
-      <c r="B352" s="12"/>
-    </row>
-    <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="12"/>
-      <c r="B353" s="12"/>
-    </row>
-    <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="12"/>
-      <c r="B354" s="12"/>
-    </row>
-    <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="12"/>
-      <c r="B355" s="12"/>
-    </row>
-    <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="12"/>
-      <c r="B356" s="12"/>
-    </row>
-    <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="12"/>
-      <c r="B357" s="12"/>
-    </row>
-    <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="12"/>
-      <c r="B358" s="12"/>
-    </row>
-    <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="12"/>
-      <c r="B359" s="12"/>
-    </row>
-    <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="12"/>
-      <c r="B360" s="12"/>
-    </row>
-    <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="12"/>
-      <c r="B361" s="12"/>
-    </row>
-    <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="12"/>
-      <c r="B362" s="12"/>
-    </row>
-    <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="12"/>
-      <c r="B363" s="12"/>
-    </row>
-    <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="12"/>
-      <c r="B364" s="12"/>
-    </row>
-    <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="12"/>
-      <c r="B365" s="12"/>
-    </row>
-    <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="12"/>
-      <c r="B366" s="12"/>
-    </row>
-    <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="12"/>
-      <c r="B367" s="12"/>
-    </row>
-    <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="12"/>
-      <c r="B368" s="12"/>
-    </row>
-    <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="12"/>
-      <c r="B369" s="12"/>
-    </row>
-    <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="12"/>
-      <c r="B370" s="12"/>
-    </row>
-    <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="12"/>
-      <c r="B371" s="12"/>
-    </row>
-    <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="12"/>
-      <c r="B372" s="12"/>
-    </row>
-    <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="12"/>
-      <c r="B373" s="12"/>
-    </row>
-    <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="12"/>
-      <c r="B374" s="12"/>
-    </row>
-    <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="12"/>
-      <c r="B375" s="12"/>
-    </row>
-    <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="12"/>
-      <c r="B376" s="12"/>
-    </row>
-    <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="12"/>
-      <c r="B377" s="12"/>
-    </row>
-    <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="12"/>
-      <c r="B378" s="12"/>
-    </row>
-    <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="12"/>
-      <c r="B379" s="12"/>
-    </row>
-    <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="12"/>
-      <c r="B380" s="12"/>
-    </row>
-    <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="12"/>
-      <c r="B381" s="12"/>
-    </row>
-    <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="12"/>
-      <c r="B382" s="12"/>
-    </row>
-    <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="12"/>
-      <c r="B383" s="12"/>
-    </row>
-    <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="12"/>
-      <c r="B384" s="12"/>
-    </row>
-    <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="12"/>
-      <c r="B385" s="12"/>
-    </row>
-    <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="12"/>
-      <c r="B386" s="12"/>
-    </row>
-    <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="12"/>
-      <c r="B387" s="12"/>
-    </row>
-    <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="12"/>
-      <c r="B388" s="12"/>
-    </row>
-    <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="12"/>
-      <c r="B389" s="12"/>
-    </row>
-    <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="12"/>
-      <c r="B390" s="12"/>
-    </row>
-    <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="12"/>
-      <c r="B391" s="12"/>
-    </row>
-    <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="12"/>
-      <c r="B392" s="12"/>
-    </row>
-    <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="12"/>
-      <c r="B393" s="12"/>
-    </row>
-    <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="12"/>
-      <c r="B394" s="12"/>
-    </row>
-    <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="12"/>
-      <c r="B395" s="12"/>
-    </row>
-    <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="12"/>
-      <c r="B396" s="12"/>
-    </row>
-    <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="12"/>
-      <c r="B397" s="12"/>
-    </row>
-    <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="12"/>
-      <c r="B398" s="12"/>
-    </row>
-    <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="12"/>
-      <c r="B399" s="12"/>
-    </row>
-    <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="12"/>
-      <c r="B400" s="12"/>
-    </row>
-    <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="12"/>
-      <c r="B401" s="12"/>
-    </row>
-    <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="12"/>
-      <c r="B402" s="12"/>
-    </row>
-    <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="12"/>
-      <c r="B403" s="12"/>
-    </row>
-    <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="12"/>
-      <c r="B404" s="12"/>
-    </row>
-    <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="12"/>
-      <c r="B405" s="12"/>
-    </row>
-    <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="12"/>
-      <c r="B406" s="12"/>
-    </row>
-    <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="12"/>
-      <c r="B407" s="12"/>
-    </row>
-    <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="12"/>
-      <c r="B408" s="12"/>
-    </row>
-    <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="12"/>
-      <c r="B409" s="12"/>
-    </row>
-    <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="12"/>
-      <c r="B410" s="12"/>
-    </row>
-    <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="12"/>
-      <c r="B411" s="12"/>
-    </row>
-    <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="12"/>
-      <c r="B412" s="12"/>
-    </row>
-    <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="12"/>
-      <c r="B413" s="12"/>
-    </row>
-    <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="12"/>
-      <c r="B414" s="12"/>
-    </row>
-    <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="12"/>
-      <c r="B415" s="12"/>
-    </row>
-    <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="12"/>
-      <c r="B416" s="12"/>
-    </row>
-    <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="12"/>
-      <c r="B417" s="12"/>
-    </row>
-    <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="12"/>
-      <c r="B418" s="12"/>
-    </row>
-    <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="12"/>
-      <c r="B419" s="12"/>
-    </row>
-    <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="12"/>
-      <c r="B420" s="12"/>
-    </row>
-    <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="12"/>
-      <c r="B421" s="12"/>
-    </row>
-    <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="12"/>
-      <c r="B422" s="12"/>
-    </row>
-    <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="12"/>
-      <c r="B423" s="12"/>
-    </row>
-    <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="12"/>
-      <c r="B424" s="12"/>
-    </row>
-    <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="12"/>
-      <c r="B425" s="12"/>
-    </row>
-    <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="12"/>
-      <c r="B426" s="12"/>
-    </row>
-    <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="12"/>
-      <c r="B427" s="12"/>
-    </row>
-    <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="12"/>
-      <c r="B428" s="12"/>
-    </row>
-    <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="12"/>
-      <c r="B429" s="12"/>
-    </row>
-    <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="12"/>
-      <c r="B430" s="12"/>
-    </row>
-    <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="12"/>
-      <c r="B431" s="12"/>
-    </row>
-    <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="12"/>
-      <c r="B432" s="12"/>
-    </row>
-    <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="12"/>
-      <c r="B433" s="12"/>
-    </row>
-    <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="12"/>
-      <c r="B434" s="12"/>
-    </row>
-    <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="12"/>
-      <c r="B435" s="12"/>
-    </row>
-    <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="12"/>
-      <c r="B436" s="12"/>
-    </row>
-    <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="12"/>
-      <c r="B437" s="12"/>
-    </row>
-    <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="12"/>
-      <c r="B438" s="12"/>
-    </row>
-    <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="12"/>
-      <c r="B439" s="12"/>
-    </row>
-    <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="12"/>
-      <c r="B440" s="12"/>
-    </row>
-    <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="12"/>
-      <c r="B441" s="12"/>
-    </row>
-    <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="12"/>
-      <c r="B442" s="12"/>
-    </row>
-    <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="12"/>
-      <c r="B443" s="12"/>
-    </row>
-    <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="12"/>
-      <c r="B444" s="12"/>
-    </row>
-    <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="12"/>
-      <c r="B445" s="12"/>
-    </row>
-    <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="12"/>
-      <c r="B446" s="12"/>
-    </row>
-    <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="12"/>
-      <c r="B447" s="12"/>
-    </row>
-    <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="12"/>
-      <c r="B448" s="12"/>
-    </row>
-    <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="12"/>
-      <c r="B449" s="12"/>
-    </row>
-    <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="12"/>
-      <c r="B450" s="12"/>
-    </row>
-    <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="12"/>
-      <c r="B451" s="12"/>
-    </row>
-    <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="12"/>
-      <c r="B452" s="12"/>
-    </row>
-    <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="12"/>
-      <c r="B453" s="12"/>
-    </row>
-    <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="12"/>
-      <c r="B454" s="12"/>
-    </row>
-    <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="12"/>
-      <c r="B455" s="12"/>
-    </row>
-    <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="12"/>
-      <c r="B456" s="12"/>
-    </row>
-    <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="12"/>
-      <c r="B457" s="12"/>
-    </row>
-    <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="12"/>
-      <c r="B458" s="12"/>
-    </row>
-    <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="12"/>
-      <c r="B459" s="12"/>
-    </row>
-    <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="12"/>
-      <c r="B460" s="12"/>
-    </row>
-    <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="12"/>
-      <c r="B461" s="12"/>
-    </row>
-    <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="12"/>
-      <c r="B462" s="12"/>
-    </row>
-    <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="12"/>
-      <c r="B463" s="12"/>
-    </row>
-    <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="12"/>
-      <c r="B464" s="12"/>
-    </row>
-    <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="12"/>
-      <c r="B465" s="12"/>
-    </row>
-    <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="12"/>
-      <c r="B466" s="12"/>
-    </row>
-    <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="12"/>
-      <c r="B467" s="12"/>
-    </row>
-    <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="12"/>
-      <c r="B468" s="12"/>
-    </row>
-    <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="12"/>
-      <c r="B469" s="12"/>
-    </row>
-    <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="12"/>
-      <c r="B470" s="12"/>
-    </row>
-    <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="12"/>
-      <c r="B471" s="12"/>
-    </row>
-    <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="12"/>
-      <c r="B472" s="12"/>
-    </row>
-    <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="12"/>
-      <c r="B473" s="12"/>
-    </row>
-    <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="12"/>
-      <c r="B474" s="12"/>
-    </row>
-    <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="12"/>
-      <c r="B475" s="12"/>
-    </row>
-    <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="12"/>
-      <c r="B476" s="12"/>
-    </row>
-    <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="12"/>
-      <c r="B477" s="12"/>
-    </row>
-    <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="12"/>
-      <c r="B478" s="12"/>
-    </row>
-    <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="12"/>
-      <c r="B479" s="12"/>
-    </row>
-    <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="12"/>
-      <c r="B480" s="12"/>
-    </row>
-    <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="12"/>
-      <c r="B481" s="12"/>
-    </row>
-    <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="12"/>
-      <c r="B482" s="12"/>
-    </row>
-    <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="12"/>
-      <c r="B483" s="12"/>
-    </row>
-    <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="12"/>
-      <c r="B484" s="12"/>
-    </row>
-    <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="12"/>
-      <c r="B485" s="12"/>
-    </row>
-    <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="12"/>
-      <c r="B486" s="12"/>
-    </row>
-    <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="12"/>
-      <c r="B487" s="12"/>
-    </row>
-    <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="12"/>
-      <c r="B488" s="12"/>
-    </row>
-    <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="12"/>
-      <c r="B489" s="12"/>
-    </row>
-    <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="12"/>
-      <c r="B490" s="12"/>
-    </row>
-    <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="12"/>
-      <c r="B491" s="12"/>
-    </row>
-    <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="12"/>
-      <c r="B492" s="12"/>
-    </row>
-    <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="12"/>
-      <c r="B493" s="12"/>
-    </row>
-    <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="12"/>
-      <c r="B494" s="12"/>
-    </row>
-    <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="12"/>
-      <c r="B495" s="12"/>
-    </row>
-    <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="12"/>
-      <c r="B496" s="12"/>
-    </row>
-    <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="12"/>
-      <c r="B497" s="12"/>
-    </row>
-    <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="12"/>
-      <c r="B498" s="12"/>
-    </row>
-    <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="12"/>
-      <c r="B499" s="12"/>
-    </row>
-    <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="12"/>
-      <c r="B500" s="12"/>
-    </row>
-    <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="12"/>
-      <c r="B501" s="12"/>
-    </row>
-    <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="12"/>
-      <c r="B502" s="12"/>
-    </row>
-    <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="12"/>
-      <c r="B503" s="12"/>
-    </row>
-    <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="12"/>
-      <c r="B504" s="12"/>
-    </row>
-    <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="12"/>
-      <c r="B505" s="12"/>
-    </row>
-    <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="12"/>
-      <c r="B506" s="12"/>
-    </row>
-    <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="12"/>
-      <c r="B507" s="12"/>
-    </row>
-    <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="12"/>
-      <c r="B508" s="12"/>
-    </row>
-    <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="12"/>
-      <c r="B509" s="12"/>
-    </row>
-    <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="12"/>
-      <c r="B510" s="12"/>
-    </row>
-    <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="12"/>
-      <c r="B511" s="12"/>
-    </row>
-    <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="12"/>
-      <c r="B512" s="12"/>
-    </row>
-    <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="12"/>
-      <c r="B513" s="12"/>
-    </row>
-    <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="12"/>
-      <c r="B514" s="12"/>
-    </row>
-    <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="12"/>
-      <c r="B515" s="12"/>
-    </row>
-    <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="12"/>
-      <c r="B516" s="12"/>
-    </row>
-    <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="12"/>
-      <c r="B517" s="12"/>
-    </row>
-    <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="12"/>
-      <c r="B518" s="12"/>
-    </row>
-    <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="12"/>
-      <c r="B519" s="12"/>
-    </row>
-    <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="12"/>
-      <c r="B520" s="12"/>
-    </row>
-    <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="12"/>
-      <c r="B521" s="12"/>
-    </row>
-    <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="12"/>
-      <c r="B522" s="12"/>
-    </row>
-    <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="12"/>
-      <c r="B523" s="12"/>
-    </row>
-    <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="12"/>
-      <c r="B524" s="12"/>
-    </row>
-    <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="12"/>
-      <c r="B525" s="12"/>
-    </row>
-    <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="12"/>
-      <c r="B526" s="12"/>
-    </row>
-    <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="12"/>
-      <c r="B527" s="12"/>
-    </row>
-    <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="12"/>
-      <c r="B528" s="12"/>
-    </row>
-    <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="12"/>
-      <c r="B529" s="12"/>
-    </row>
-    <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="12"/>
-      <c r="B530" s="12"/>
-    </row>
-    <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="12"/>
-      <c r="B531" s="12"/>
-    </row>
-    <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="12"/>
-      <c r="B532" s="12"/>
-    </row>
-    <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="12"/>
-      <c r="B533" s="12"/>
-    </row>
-    <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="12"/>
-      <c r="B534" s="12"/>
-    </row>
-    <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="12"/>
-      <c r="B535" s="12"/>
-    </row>
-    <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="12"/>
-      <c r="B536" s="12"/>
-    </row>
-    <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="12"/>
-      <c r="B537" s="12"/>
-    </row>
-    <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="12"/>
-      <c r="B538" s="12"/>
-    </row>
-    <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="12"/>
-      <c r="B539" s="12"/>
-    </row>
-    <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="12"/>
-      <c r="B540" s="12"/>
-    </row>
-    <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="12"/>
-      <c r="B541" s="12"/>
-    </row>
-    <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="12"/>
-      <c r="B542" s="12"/>
-    </row>
-    <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="12"/>
-      <c r="B543" s="12"/>
-    </row>
-    <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="12"/>
-      <c r="B544" s="12"/>
-    </row>
-    <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="12"/>
-      <c r="B545" s="12"/>
-    </row>
-    <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="12"/>
-      <c r="B546" s="12"/>
-    </row>
-    <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="12"/>
-      <c r="B547" s="12"/>
-    </row>
-    <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="12"/>
-      <c r="B548" s="12"/>
-    </row>
-    <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="12"/>
-      <c r="B549" s="12"/>
-    </row>
-    <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="12"/>
-      <c r="B550" s="12"/>
-    </row>
-    <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="12"/>
-      <c r="B551" s="12"/>
-    </row>
-    <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="12"/>
-      <c r="B552" s="12"/>
-    </row>
-    <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="12"/>
-      <c r="B553" s="12"/>
-    </row>
-    <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="12"/>
-      <c r="B554" s="12"/>
-    </row>
-    <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="12"/>
-      <c r="B555" s="12"/>
-    </row>
-    <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="12"/>
-      <c r="B556" s="12"/>
-    </row>
-    <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="12"/>
-      <c r="B557" s="12"/>
-    </row>
-    <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="12"/>
-      <c r="B558" s="12"/>
-    </row>
-    <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="12"/>
-      <c r="B559" s="12"/>
-    </row>
-    <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="12"/>
-      <c r="B560" s="12"/>
-    </row>
-    <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="12"/>
-      <c r="B561" s="12"/>
-    </row>
-    <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="12"/>
-      <c r="B562" s="12"/>
-    </row>
-    <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="12"/>
-      <c r="B563" s="12"/>
-    </row>
-    <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="12"/>
-      <c r="B564" s="12"/>
-    </row>
-    <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="12"/>
-      <c r="B565" s="12"/>
-    </row>
-    <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="12"/>
-      <c r="B566" s="12"/>
-    </row>
-    <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="12"/>
-      <c r="B567" s="12"/>
-    </row>
-    <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="12"/>
-      <c r="B568" s="12"/>
-    </row>
-    <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="12"/>
-      <c r="B569" s="12"/>
-    </row>
-    <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="12"/>
-      <c r="B570" s="12"/>
-    </row>
-    <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="12"/>
-      <c r="B571" s="12"/>
-    </row>
-    <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="12"/>
-      <c r="B572" s="12"/>
-    </row>
-    <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="12"/>
-      <c r="B573" s="12"/>
-    </row>
-    <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="12"/>
-      <c r="B574" s="12"/>
-    </row>
-    <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="12"/>
-      <c r="B575" s="12"/>
-    </row>
-    <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="12"/>
-      <c r="B576" s="12"/>
-    </row>
-    <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="12"/>
-      <c r="B577" s="12"/>
-    </row>
-    <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="12"/>
-      <c r="B578" s="12"/>
-    </row>
-    <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="12"/>
-      <c r="B579" s="12"/>
-    </row>
-    <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="12"/>
-      <c r="B580" s="12"/>
-    </row>
-    <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="12"/>
-      <c r="B581" s="12"/>
-    </row>
-    <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="12"/>
-      <c r="B582" s="12"/>
-    </row>
-    <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="12"/>
-      <c r="B583" s="12"/>
-    </row>
-    <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="12"/>
-      <c r="B584" s="12"/>
-    </row>
-    <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="12"/>
-      <c r="B585" s="12"/>
-    </row>
-    <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="12"/>
-      <c r="B586" s="12"/>
-    </row>
-    <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="12"/>
-      <c r="B587" s="12"/>
-    </row>
-    <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="12"/>
-      <c r="B588" s="12"/>
-    </row>
-    <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="12"/>
-      <c r="B589" s="12"/>
-    </row>
-    <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="12"/>
-      <c r="B590" s="12"/>
-    </row>
-    <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="12"/>
-      <c r="B591" s="12"/>
-    </row>
-    <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="12"/>
-      <c r="B592" s="12"/>
-    </row>
-    <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="12"/>
-      <c r="B593" s="12"/>
-    </row>
-    <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="12"/>
-      <c r="B594" s="12"/>
-    </row>
-    <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="12"/>
-      <c r="B595" s="12"/>
-    </row>
-    <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="12"/>
-      <c r="B596" s="12"/>
-    </row>
-    <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="12"/>
-      <c r="B597" s="12"/>
-    </row>
-    <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="12"/>
-      <c r="B598" s="12"/>
-    </row>
-    <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="12"/>
-      <c r="B599" s="12"/>
-    </row>
-    <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="12"/>
-      <c r="B600" s="12"/>
-    </row>
-    <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="12"/>
-      <c r="B601" s="12"/>
-    </row>
-    <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="12"/>
-      <c r="B602" s="12"/>
-    </row>
-    <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="12"/>
-      <c r="B603" s="12"/>
-    </row>
-    <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="12"/>
-      <c r="B604" s="12"/>
-    </row>
-    <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="12"/>
-      <c r="B605" s="12"/>
-    </row>
-    <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="12"/>
-      <c r="B606" s="12"/>
-    </row>
-    <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="12"/>
-      <c r="B607" s="12"/>
-    </row>
-    <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="12"/>
-      <c r="B608" s="12"/>
-    </row>
-    <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="12"/>
-      <c r="B609" s="12"/>
-    </row>
-    <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="12"/>
-      <c r="B610" s="12"/>
-    </row>
-    <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="12"/>
-      <c r="B611" s="12"/>
-    </row>
-    <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="12"/>
-      <c r="B612" s="12"/>
-    </row>
-    <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="12"/>
-      <c r="B613" s="12"/>
-    </row>
-    <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="12"/>
-      <c r="B614" s="12"/>
-    </row>
-    <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="12"/>
-      <c r="B615" s="12"/>
-    </row>
-    <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="12"/>
-      <c r="B616" s="12"/>
-    </row>
-    <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="12"/>
-      <c r="B617" s="12"/>
-    </row>
-    <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="12"/>
-      <c r="B618" s="12"/>
-    </row>
-    <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="12"/>
-      <c r="B619" s="12"/>
-    </row>
-    <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="12"/>
-      <c r="B620" s="12"/>
-    </row>
-    <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="12"/>
-      <c r="B621" s="12"/>
-    </row>
-    <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="12"/>
-      <c r="B622" s="12"/>
-    </row>
-    <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="12"/>
-      <c r="B623" s="12"/>
-    </row>
-    <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="12"/>
-      <c r="B624" s="12"/>
-    </row>
-    <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="12"/>
-      <c r="B625" s="12"/>
-    </row>
-    <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="12"/>
-      <c r="B626" s="12"/>
-    </row>
-    <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="12"/>
-      <c r="B627" s="12"/>
-    </row>
-    <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="12"/>
-      <c r="B628" s="12"/>
-    </row>
-    <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="12"/>
-      <c r="B629" s="12"/>
-    </row>
-    <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="12"/>
-      <c r="B630" s="12"/>
-    </row>
-    <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="12"/>
-      <c r="B631" s="12"/>
-    </row>
-    <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="12"/>
-      <c r="B632" s="12"/>
-    </row>
-    <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="12"/>
-      <c r="B633" s="12"/>
-    </row>
-    <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="12"/>
-      <c r="B634" s="12"/>
-    </row>
-    <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="12"/>
-      <c r="B635" s="12"/>
-    </row>
-    <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="12"/>
-      <c r="B636" s="12"/>
-    </row>
-    <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="12"/>
-      <c r="B637" s="12"/>
-    </row>
-    <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="12"/>
-      <c r="B638" s="12"/>
-    </row>
-    <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="12"/>
-      <c r="B639" s="12"/>
-    </row>
-    <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="12"/>
-      <c r="B640" s="12"/>
-    </row>
-    <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="12"/>
-      <c r="B641" s="12"/>
-    </row>
-    <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="12"/>
-      <c r="B642" s="12"/>
-    </row>
-    <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="12"/>
-      <c r="B643" s="12"/>
-    </row>
-    <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="12"/>
-      <c r="B644" s="12"/>
-    </row>
-    <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="12"/>
-      <c r="B645" s="12"/>
-    </row>
-    <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="12"/>
-      <c r="B646" s="12"/>
-    </row>
-    <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="12"/>
-      <c r="B647" s="12"/>
-    </row>
-    <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="12"/>
-      <c r="B648" s="12"/>
-    </row>
-    <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="12"/>
-      <c r="B649" s="12"/>
-    </row>
-    <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="12"/>
-      <c r="B650" s="12"/>
-    </row>
-    <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="12"/>
-      <c r="B651" s="12"/>
-    </row>
-    <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="12"/>
-      <c r="B652" s="12"/>
-    </row>
-    <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="12"/>
-      <c r="B653" s="12"/>
-    </row>
-    <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="12"/>
-      <c r="B654" s="12"/>
-    </row>
-    <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="12"/>
-      <c r="B655" s="12"/>
-    </row>
-    <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="12"/>
-      <c r="B656" s="12"/>
-    </row>
-    <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="12"/>
-      <c r="B657" s="12"/>
-    </row>
-    <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="12"/>
-      <c r="B658" s="12"/>
-    </row>
-    <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="12"/>
-      <c r="B659" s="12"/>
-    </row>
-    <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="12"/>
-      <c r="B660" s="12"/>
-    </row>
-    <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="12"/>
-      <c r="B661" s="12"/>
-    </row>
-    <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="12"/>
-      <c r="B662" s="12"/>
-    </row>
-    <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="12"/>
-      <c r="B663" s="12"/>
-    </row>
-    <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="12"/>
-      <c r="B664" s="12"/>
-    </row>
-    <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="12"/>
-      <c r="B665" s="12"/>
-    </row>
-    <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="12"/>
-      <c r="B666" s="12"/>
-    </row>
-    <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="12"/>
-      <c r="B667" s="12"/>
-    </row>
-    <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="12"/>
-      <c r="B668" s="12"/>
-    </row>
-    <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="12"/>
-      <c r="B669" s="12"/>
-    </row>
-    <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="12"/>
-      <c r="B670" s="12"/>
-    </row>
-    <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="12"/>
-      <c r="B671" s="12"/>
-    </row>
-    <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="12"/>
-      <c r="B672" s="12"/>
-    </row>
-    <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="12"/>
-      <c r="B673" s="12"/>
-    </row>
-    <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="12"/>
-      <c r="B674" s="12"/>
-    </row>
-    <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="12"/>
-      <c r="B675" s="12"/>
-    </row>
-    <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="12"/>
-      <c r="B676" s="12"/>
-    </row>
-    <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="12"/>
-      <c r="B677" s="12"/>
-    </row>
-    <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="12"/>
-      <c r="B678" s="12"/>
-    </row>
-    <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="12"/>
-      <c r="B679" s="12"/>
-    </row>
-    <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="12"/>
-      <c r="B680" s="12"/>
-    </row>
-    <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="12"/>
-      <c r="B681" s="12"/>
-    </row>
-    <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="12"/>
-      <c r="B682" s="12"/>
-    </row>
-    <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="12"/>
-      <c r="B683" s="12"/>
-    </row>
-    <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="12"/>
-      <c r="B684" s="12"/>
-    </row>
-    <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="12"/>
-      <c r="B685" s="12"/>
-    </row>
-    <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="12"/>
-      <c r="B686" s="12"/>
-    </row>
-    <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="12"/>
-      <c r="B687" s="12"/>
-    </row>
-    <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="12"/>
-      <c r="B688" s="12"/>
-    </row>
-    <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="12"/>
-      <c r="B689" s="12"/>
-    </row>
-    <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="12"/>
-      <c r="B690" s="12"/>
-    </row>
-    <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="12"/>
-      <c r="B691" s="12"/>
-    </row>
-    <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="12"/>
-      <c r="B692" s="12"/>
-    </row>
-    <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="12"/>
-      <c r="B693" s="12"/>
-    </row>
-    <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="12"/>
-      <c r="B694" s="12"/>
-    </row>
-    <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="12"/>
-      <c r="B695" s="12"/>
-    </row>
-    <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="12"/>
-      <c r="B696" s="12"/>
-    </row>
-    <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="12"/>
-      <c r="B697" s="12"/>
-    </row>
-    <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="12"/>
-      <c r="B698" s="12"/>
-    </row>
-    <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="12"/>
-      <c r="B699" s="12"/>
-    </row>
-    <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="12"/>
-      <c r="B700" s="12"/>
-    </row>
-    <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="12"/>
-      <c r="B701" s="12"/>
-    </row>
-    <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="12"/>
-      <c r="B702" s="12"/>
-    </row>
-    <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="12"/>
-      <c r="B703" s="12"/>
-    </row>
-    <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="12"/>
-      <c r="B704" s="12"/>
-    </row>
-    <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="12"/>
-      <c r="B705" s="12"/>
-    </row>
-    <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="12"/>
-      <c r="B706" s="12"/>
-    </row>
-    <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="12"/>
-      <c r="B707" s="12"/>
-    </row>
-    <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="12"/>
-      <c r="B708" s="12"/>
-    </row>
-    <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="12"/>
-      <c r="B709" s="12"/>
-    </row>
-    <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="12"/>
-      <c r="B710" s="12"/>
-    </row>
-    <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="12"/>
-      <c r="B711" s="12"/>
-    </row>
-    <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="12"/>
-      <c r="B712" s="12"/>
-    </row>
-    <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="12"/>
-      <c r="B713" s="12"/>
-    </row>
-    <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="12"/>
-      <c r="B714" s="12"/>
-    </row>
-    <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="12"/>
-      <c r="B715" s="12"/>
-    </row>
-    <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="12"/>
-      <c r="B716" s="12"/>
-    </row>
-    <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="12"/>
-      <c r="B717" s="12"/>
-    </row>
-    <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="12"/>
-      <c r="B718" s="12"/>
-    </row>
-    <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="12"/>
-      <c r="B719" s="12"/>
-    </row>
-    <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="12"/>
-      <c r="B720" s="12"/>
-    </row>
-    <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="12"/>
-      <c r="B721" s="12"/>
-    </row>
-    <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="12"/>
-      <c r="B722" s="12"/>
-    </row>
-    <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="12"/>
-      <c r="B723" s="12"/>
-    </row>
-    <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="12"/>
-      <c r="B724" s="12"/>
-    </row>
-    <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="12"/>
-      <c r="B725" s="12"/>
-    </row>
-    <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="12"/>
-      <c r="B726" s="12"/>
-    </row>
-    <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="12"/>
-      <c r="B727" s="12"/>
-    </row>
-    <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="12"/>
-      <c r="B728" s="12"/>
-    </row>
-    <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="12"/>
-      <c r="B729" s="12"/>
-    </row>
-    <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="12"/>
-      <c r="B730" s="12"/>
-    </row>
-    <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="12"/>
-      <c r="B731" s="12"/>
-    </row>
-    <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="12"/>
-      <c r="B732" s="12"/>
-    </row>
-    <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="12"/>
-      <c r="B733" s="12"/>
-    </row>
-    <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="12"/>
-      <c r="B734" s="12"/>
-    </row>
-    <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="12"/>
-      <c r="B735" s="12"/>
-    </row>
-    <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="12"/>
-      <c r="B736" s="12"/>
-    </row>
-    <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="12"/>
-      <c r="B737" s="12"/>
-    </row>
-    <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="12"/>
-      <c r="B738" s="12"/>
-    </row>
-    <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="12"/>
-      <c r="B739" s="12"/>
-    </row>
-    <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="12"/>
-      <c r="B740" s="12"/>
-    </row>
-    <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="12"/>
-      <c r="B741" s="12"/>
-    </row>
-    <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="12"/>
-      <c r="B742" s="12"/>
-    </row>
-    <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="12"/>
-      <c r="B743" s="12"/>
-    </row>
-    <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="12"/>
-      <c r="B744" s="12"/>
-    </row>
-    <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="12"/>
-      <c r="B745" s="12"/>
-    </row>
-    <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="12"/>
-      <c r="B746" s="12"/>
-    </row>
-    <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="12"/>
-      <c r="B747" s="12"/>
-    </row>
-    <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="12"/>
-      <c r="B748" s="12"/>
-    </row>
-    <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="12"/>
-      <c r="B749" s="12"/>
-    </row>
-    <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="12"/>
-      <c r="B750" s="12"/>
-    </row>
-    <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="12"/>
-      <c r="B751" s="12"/>
-    </row>
-    <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="12"/>
-      <c r="B752" s="12"/>
-    </row>
-    <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="12"/>
-      <c r="B753" s="12"/>
-    </row>
-    <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="12"/>
-      <c r="B754" s="12"/>
-    </row>
-    <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="12"/>
-      <c r="B755" s="12"/>
-    </row>
-    <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="12"/>
-      <c r="B756" s="12"/>
-    </row>
-    <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="12"/>
-      <c r="B757" s="12"/>
-    </row>
-    <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="12"/>
-      <c r="B758" s="12"/>
-    </row>
-    <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="12"/>
-      <c r="B759" s="12"/>
-    </row>
-    <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="12"/>
-      <c r="B760" s="12"/>
-    </row>
-    <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="12"/>
-      <c r="B761" s="12"/>
-    </row>
-    <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="12"/>
-      <c r="B762" s="12"/>
-    </row>
-    <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="12"/>
-      <c r="B763" s="12"/>
-    </row>
-    <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="12"/>
-      <c r="B764" s="12"/>
-    </row>
-    <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="12"/>
-      <c r="B765" s="12"/>
-    </row>
-    <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="12"/>
-      <c r="B766" s="12"/>
-    </row>
-    <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="12"/>
-      <c r="B767" s="12"/>
-    </row>
-    <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="12"/>
-      <c r="B768" s="12"/>
-    </row>
-    <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="12"/>
-      <c r="B769" s="12"/>
-    </row>
-    <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="12"/>
-      <c r="B770" s="12"/>
-    </row>
-    <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="12"/>
-      <c r="B771" s="12"/>
-    </row>
-    <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="12"/>
-      <c r="B772" s="12"/>
-    </row>
-    <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="12"/>
-      <c r="B773" s="12"/>
-    </row>
-    <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="12"/>
-      <c r="B774" s="12"/>
-    </row>
-    <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="12"/>
-      <c r="B775" s="12"/>
-    </row>
-    <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="12"/>
-      <c r="B776" s="12"/>
-    </row>
-    <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="12"/>
-      <c r="B777" s="12"/>
-    </row>
-    <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="12"/>
-      <c r="B778" s="12"/>
-    </row>
-    <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="12"/>
-      <c r="B779" s="12"/>
-    </row>
-    <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="12"/>
-      <c r="B780" s="12"/>
-    </row>
-    <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="12"/>
-      <c r="B781" s="12"/>
-    </row>
-    <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="12"/>
-      <c r="B782" s="12"/>
-    </row>
-    <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="12"/>
-      <c r="B783" s="12"/>
-    </row>
-    <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="12"/>
-      <c r="B784" s="12"/>
-    </row>
-    <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="12"/>
-      <c r="B785" s="12"/>
-    </row>
-    <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="12"/>
-      <c r="B786" s="12"/>
-    </row>
-    <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="12"/>
-      <c r="B787" s="12"/>
-    </row>
-    <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="12"/>
-      <c r="B788" s="12"/>
-    </row>
-    <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="12"/>
-      <c r="B789" s="12"/>
-    </row>
-    <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="12"/>
-      <c r="B790" s="12"/>
-    </row>
-    <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="12"/>
-      <c r="B791" s="12"/>
-    </row>
-    <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="12"/>
-      <c r="B792" s="12"/>
-    </row>
-    <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="12"/>
-      <c r="B793" s="12"/>
-    </row>
-    <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="12"/>
-      <c r="B794" s="12"/>
-    </row>
-    <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="12"/>
-      <c r="B795" s="12"/>
-    </row>
-    <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="12"/>
-      <c r="B796" s="12"/>
-    </row>
-    <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="12"/>
-      <c r="B797" s="12"/>
-    </row>
-    <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="12"/>
-      <c r="B798" s="12"/>
-    </row>
-    <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="12"/>
-      <c r="B799" s="12"/>
-    </row>
-    <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="12"/>
-      <c r="B800" s="12"/>
-    </row>
-    <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="12"/>
-      <c r="B801" s="12"/>
-    </row>
-    <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="12"/>
-      <c r="B802" s="12"/>
-    </row>
-    <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="12"/>
-      <c r="B803" s="12"/>
-    </row>
-    <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="12"/>
-      <c r="B804" s="12"/>
-    </row>
-    <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="12"/>
-      <c r="B805" s="12"/>
-    </row>
-    <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="12"/>
-      <c r="B806" s="12"/>
-    </row>
-    <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="12"/>
-      <c r="B807" s="12"/>
-    </row>
-    <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="12"/>
-      <c r="B808" s="12"/>
-    </row>
-    <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="12"/>
-      <c r="B809" s="12"/>
-    </row>
-    <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="12"/>
-      <c r="B810" s="12"/>
-    </row>
-    <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="12"/>
-      <c r="B811" s="12"/>
-    </row>
-    <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="12"/>
-      <c r="B812" s="12"/>
-    </row>
-    <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="12"/>
-      <c r="B813" s="12"/>
-    </row>
-    <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="12"/>
-      <c r="B814" s="12"/>
-    </row>
-    <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="12"/>
-      <c r="B815" s="12"/>
-    </row>
-    <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="12"/>
-      <c r="B816" s="12"/>
-    </row>
-    <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="12"/>
-      <c r="B817" s="12"/>
-    </row>
-    <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="12"/>
-      <c r="B818" s="12"/>
-    </row>
-    <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="12"/>
-      <c r="B819" s="12"/>
-    </row>
-    <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="12"/>
-      <c r="B820" s="12"/>
-    </row>
-    <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="12"/>
-      <c r="B821" s="12"/>
-    </row>
-    <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="12"/>
-      <c r="B822" s="12"/>
-    </row>
-    <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="12"/>
-      <c r="B823" s="12"/>
-    </row>
-    <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="12"/>
-      <c r="B824" s="12"/>
-    </row>
-    <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="12"/>
-      <c r="B825" s="12"/>
-    </row>
-    <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="12"/>
-      <c r="B826" s="12"/>
-    </row>
-    <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="12"/>
-      <c r="B827" s="12"/>
-    </row>
-    <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="12"/>
-      <c r="B828" s="12"/>
-    </row>
-    <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="12"/>
-      <c r="B829" s="12"/>
-    </row>
-    <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="12"/>
-      <c r="B830" s="12"/>
-    </row>
-    <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="12"/>
-      <c r="B831" s="12"/>
-    </row>
-    <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="12"/>
-      <c r="B832" s="12"/>
-    </row>
-    <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="12"/>
-      <c r="B833" s="12"/>
-    </row>
-    <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="12"/>
-      <c r="B834" s="12"/>
-    </row>
-    <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="12"/>
-      <c r="B835" s="12"/>
-    </row>
-    <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="12"/>
-      <c r="B836" s="12"/>
-    </row>
-    <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="12"/>
-      <c r="B837" s="12"/>
-    </row>
-    <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="12"/>
-      <c r="B838" s="12"/>
-    </row>
-    <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="12"/>
-      <c r="B839" s="12"/>
-    </row>
-    <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="12"/>
-      <c r="B840" s="12"/>
-    </row>
-    <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="12"/>
-      <c r="B841" s="12"/>
-    </row>
-    <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="12"/>
-      <c r="B842" s="12"/>
-    </row>
-    <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="12"/>
-      <c r="B843" s="12"/>
-    </row>
-    <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="12"/>
-      <c r="B844" s="12"/>
-    </row>
-    <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="12"/>
-      <c r="B845" s="12"/>
-    </row>
-    <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="12"/>
-      <c r="B846" s="12"/>
-    </row>
-    <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="12"/>
-      <c r="B847" s="12"/>
-    </row>
-    <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="12"/>
-      <c r="B848" s="12"/>
-    </row>
-    <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="12"/>
-      <c r="B849" s="12"/>
-    </row>
-    <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="12"/>
-      <c r="B850" s="12"/>
-    </row>
-    <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="12"/>
-      <c r="B851" s="12"/>
-    </row>
-    <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="12"/>
-      <c r="B852" s="12"/>
-    </row>
-    <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="12"/>
-      <c r="B853" s="12"/>
-    </row>
-    <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="12"/>
-      <c r="B854" s="12"/>
-    </row>
-    <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="12"/>
-      <c r="B855" s="12"/>
-    </row>
-    <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="12"/>
-      <c r="B856" s="12"/>
-    </row>
-    <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="12"/>
-      <c r="B857" s="12"/>
-    </row>
-    <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="12"/>
-      <c r="B858" s="12"/>
-    </row>
-    <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="12"/>
-      <c r="B859" s="12"/>
-    </row>
-    <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="12"/>
-      <c r="B860" s="12"/>
-    </row>
-    <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="12"/>
-      <c r="B861" s="12"/>
-    </row>
-    <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="12"/>
-      <c r="B862" s="12"/>
-    </row>
-    <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="12"/>
-      <c r="B863" s="12"/>
-    </row>
-    <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="12"/>
-      <c r="B864" s="12"/>
-    </row>
-    <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="12"/>
-      <c r="B865" s="12"/>
-    </row>
-    <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="12"/>
-      <c r="B866" s="12"/>
-    </row>
-    <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="12"/>
-      <c r="B867" s="12"/>
-    </row>
-    <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="12"/>
-      <c r="B868" s="12"/>
-    </row>
-    <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="12"/>
-      <c r="B869" s="12"/>
-    </row>
-    <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="12"/>
-      <c r="B870" s="12"/>
-    </row>
-    <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="12"/>
-      <c r="B871" s="12"/>
-    </row>
-    <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="12"/>
-      <c r="B872" s="12"/>
-    </row>
-    <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="12"/>
-      <c r="B873" s="12"/>
-    </row>
-    <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="12"/>
-      <c r="B874" s="12"/>
-    </row>
-    <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="12"/>
-      <c r="B875" s="12"/>
-    </row>
-    <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="12"/>
-      <c r="B876" s="12"/>
-    </row>
-    <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="12"/>
-      <c r="B877" s="12"/>
-    </row>
-    <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="12"/>
-      <c r="B878" s="12"/>
-    </row>
-    <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="12"/>
-      <c r="B879" s="12"/>
-    </row>
-    <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="12"/>
-      <c r="B880" s="12"/>
-    </row>
-    <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="12"/>
-      <c r="B881" s="12"/>
-    </row>
-    <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="12"/>
-      <c r="B882" s="12"/>
-    </row>
-    <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="12"/>
-      <c r="B883" s="12"/>
-    </row>
-    <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="12"/>
-      <c r="B884" s="12"/>
-    </row>
-    <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="12"/>
-      <c r="B885" s="12"/>
-    </row>
-    <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="12"/>
-      <c r="B886" s="12"/>
-    </row>
-    <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="12"/>
-      <c r="B887" s="12"/>
-    </row>
-    <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="12"/>
-      <c r="B888" s="12"/>
-    </row>
-    <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="12"/>
-      <c r="B889" s="12"/>
-    </row>
-    <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="12"/>
-      <c r="B890" s="12"/>
-    </row>
-    <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="12"/>
-      <c r="B891" s="12"/>
-    </row>
-    <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="12"/>
-      <c r="B892" s="12"/>
-    </row>
-    <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="12"/>
-      <c r="B893" s="12"/>
-    </row>
-    <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="12"/>
-      <c r="B894" s="12"/>
-    </row>
-    <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="12"/>
-      <c r="B895" s="12"/>
-    </row>
-    <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="12"/>
-      <c r="B896" s="12"/>
-    </row>
-    <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="12"/>
-      <c r="B897" s="12"/>
-    </row>
-    <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="12"/>
-      <c r="B898" s="12"/>
-    </row>
-    <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="12"/>
-      <c r="B899" s="12"/>
-    </row>
-    <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="12"/>
-      <c r="B900" s="12"/>
-    </row>
-    <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="12"/>
-      <c r="B901" s="12"/>
-    </row>
-    <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="12"/>
-      <c r="B902" s="12"/>
-    </row>
-    <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="12"/>
-      <c r="B903" s="12"/>
-    </row>
-    <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="12"/>
-      <c r="B904" s="12"/>
-    </row>
-    <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="12"/>
-      <c r="B905" s="12"/>
-    </row>
-    <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="12"/>
-      <c r="B906" s="12"/>
-    </row>
-    <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="12"/>
-      <c r="B907" s="12"/>
-    </row>
-    <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="12"/>
-      <c r="B908" s="12"/>
-    </row>
-    <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="12"/>
-      <c r="B909" s="12"/>
-    </row>
-    <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="12"/>
-      <c r="B910" s="12"/>
-    </row>
-    <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="12"/>
-      <c r="B911" s="12"/>
-    </row>
-    <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="12"/>
-      <c r="B912" s="12"/>
-    </row>
-    <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="12"/>
-      <c r="B913" s="12"/>
-    </row>
-    <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="12"/>
-      <c r="B914" s="12"/>
-    </row>
-    <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="12"/>
-      <c r="B915" s="12"/>
-    </row>
-    <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="12"/>
-      <c r="B916" s="12"/>
-    </row>
-    <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="12"/>
-      <c r="B917" s="12"/>
-    </row>
-    <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="12"/>
-      <c r="B918" s="12"/>
-    </row>
-    <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="12"/>
-      <c r="B919" s="12"/>
-    </row>
-    <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="12"/>
-      <c r="B920" s="12"/>
-    </row>
-    <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="12"/>
-      <c r="B921" s="12"/>
-    </row>
-    <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="12"/>
-      <c r="B922" s="12"/>
-    </row>
-    <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="12"/>
-      <c r="B923" s="12"/>
-    </row>
-    <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="12"/>
-      <c r="B924" s="12"/>
-    </row>
-    <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="12"/>
-      <c r="B925" s="12"/>
-    </row>
-    <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="12"/>
-      <c r="B926" s="12"/>
-    </row>
-    <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="12"/>
-      <c r="B927" s="12"/>
-    </row>
-    <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="12"/>
-      <c r="B928" s="12"/>
-    </row>
-    <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="12"/>
-      <c r="B929" s="12"/>
-    </row>
-    <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="12"/>
-      <c r="B930" s="12"/>
-    </row>
-    <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="12"/>
-      <c r="B931" s="12"/>
-    </row>
-    <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="12"/>
-      <c r="B932" s="12"/>
-    </row>
-    <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="12"/>
-      <c r="B933" s="12"/>
-    </row>
-    <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="12"/>
-      <c r="B934" s="12"/>
-    </row>
-    <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="12"/>
-      <c r="B935" s="12"/>
-    </row>
-    <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="12"/>
-      <c r="B936" s="12"/>
-    </row>
-    <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="12"/>
-      <c r="B937" s="12"/>
-    </row>
-    <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="12"/>
-      <c r="B938" s="12"/>
-    </row>
-    <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="12"/>
-      <c r="B939" s="12"/>
-    </row>
-    <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="12"/>
-      <c r="B940" s="12"/>
-    </row>
-    <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="12"/>
-      <c r="B941" s="12"/>
-    </row>
-    <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="12"/>
-      <c r="B942" s="12"/>
-    </row>
-    <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="12"/>
-      <c r="B943" s="12"/>
-    </row>
-    <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="12"/>
-      <c r="B944" s="12"/>
-    </row>
-    <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="12"/>
-      <c r="B945" s="12"/>
-    </row>
-    <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="12"/>
-      <c r="B946" s="12"/>
-    </row>
-    <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="12"/>
-      <c r="B947" s="12"/>
-    </row>
-    <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="12"/>
-      <c r="B948" s="12"/>
-    </row>
-    <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="12"/>
-      <c r="B949" s="12"/>
-    </row>
-    <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="12"/>
-      <c r="B950" s="12"/>
-    </row>
-    <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="12"/>
-      <c r="B951" s="12"/>
-    </row>
-    <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="12"/>
-      <c r="B952" s="12"/>
-    </row>
-    <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="12"/>
-      <c r="B953" s="12"/>
-    </row>
-    <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="12"/>
-      <c r="B954" s="12"/>
-    </row>
-    <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="12"/>
-      <c r="B955" s="12"/>
-    </row>
-    <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="12"/>
-      <c r="B956" s="12"/>
-    </row>
-    <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="12"/>
-      <c r="B957" s="12"/>
-    </row>
-    <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="12"/>
-      <c r="B958" s="12"/>
-    </row>
-    <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="12"/>
-      <c r="B959" s="12"/>
-    </row>
-    <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="12"/>
-      <c r="B960" s="12"/>
-    </row>
-    <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="12"/>
-      <c r="B961" s="12"/>
-    </row>
-    <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="12"/>
-      <c r="B962" s="12"/>
-    </row>
-    <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="12"/>
-      <c r="B963" s="12"/>
-    </row>
-    <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="12"/>
-      <c r="B964" s="12"/>
-    </row>
-    <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="12"/>
-      <c r="B965" s="12"/>
-    </row>
-    <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="12"/>
-      <c r="B966" s="12"/>
-    </row>
-    <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="12"/>
-      <c r="B967" s="12"/>
-    </row>
-    <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="12"/>
-      <c r="B968" s="12"/>
-    </row>
-    <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="12"/>
-      <c r="B969" s="12"/>
-    </row>
-    <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="12"/>
-      <c r="B970" s="12"/>
-    </row>
-    <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="12"/>
-      <c r="B971" s="12"/>
-    </row>
-    <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="12"/>
-      <c r="B972" s="12"/>
-    </row>
-    <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="12"/>
-      <c r="B973" s="12"/>
-    </row>
-    <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="12"/>
-      <c r="B974" s="12"/>
-    </row>
-    <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="12"/>
-      <c r="B975" s="12"/>
-    </row>
-    <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="12"/>
-      <c r="B976" s="12"/>
-    </row>
-    <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="12"/>
-      <c r="B977" s="12"/>
-    </row>
-    <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="12"/>
-      <c r="B978" s="12"/>
-    </row>
-    <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="12"/>
-      <c r="B979" s="12"/>
-    </row>
-    <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="12"/>
-      <c r="B980" s="12"/>
-    </row>
-    <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="12"/>
-      <c r="B981" s="12"/>
-    </row>
-    <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="12"/>
-      <c r="B982" s="12"/>
-    </row>
-    <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="12"/>
-      <c r="B983" s="12"/>
-    </row>
-    <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="12"/>
-      <c r="B984" s="12"/>
-    </row>
-    <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="12"/>
-      <c r="B985" s="12"/>
-    </row>
-    <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="12"/>
-      <c r="B986" s="12"/>
-    </row>
-    <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="12"/>
-      <c r="B987" s="12"/>
-    </row>
-    <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="12"/>
-      <c r="B988" s="12"/>
-    </row>
-    <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="12"/>
-      <c r="B989" s="12"/>
-    </row>
-    <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="12"/>
-      <c r="B990" s="12"/>
-    </row>
-    <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="12"/>
-      <c r="B991" s="12"/>
-    </row>
-    <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="12"/>
-      <c r="B992" s="12"/>
-    </row>
-    <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="12"/>
-      <c r="B993" s="12"/>
-    </row>
-    <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="12"/>
-      <c r="B994" s="12"/>
-    </row>
-    <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="12"/>
-      <c r="B995" s="12"/>
-    </row>
-    <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="12"/>
-      <c r="B996" s="12"/>
-    </row>
-    <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="12"/>
-      <c r="B997" s="12"/>
-    </row>
-    <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="12"/>
-      <c r="B998" s="12"/>
-    </row>
-    <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="12"/>
-      <c r="B999" s="12"/>
-    </row>
-    <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="12"/>
-      <c r="B1000" s="12"/>
+    <row r="221" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A221" s="10"/>
+      <c r="B221" s="10"/>
+    </row>
+    <row r="222" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A222" s="10"/>
+      <c r="B222" s="10"/>
+    </row>
+    <row r="223" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A223" s="10"/>
+      <c r="B223" s="10"/>
+    </row>
+    <row r="224" ht="15.75" customHeight="1" spans="1:21">
+      <c r="A224" s="10"/>
+      <c r="B224" s="10"/>
+    </row>
+    <row r="225" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A225" s="10"/>
+      <c r="B225" s="10"/>
+    </row>
+    <row r="226" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A226" s="10"/>
+      <c r="B226" s="10"/>
+    </row>
+    <row r="227" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A227" s="10"/>
+      <c r="B227" s="10"/>
+    </row>
+    <row r="228" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A228" s="10"/>
+      <c r="B228" s="10"/>
+    </row>
+    <row r="229" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A229" s="10"/>
+      <c r="B229" s="10"/>
+    </row>
+    <row r="230" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A230" s="10"/>
+      <c r="B230" s="10"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A231" s="10"/>
+      <c r="B231" s="10"/>
+    </row>
+    <row r="232" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A232" s="10"/>
+      <c r="B232" s="10"/>
+    </row>
+    <row r="233" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A233" s="10"/>
+      <c r="B233" s="10"/>
+    </row>
+    <row r="234" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A234" s="10"/>
+      <c r="B234" s="10"/>
+    </row>
+    <row r="235" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A235" s="10"/>
+      <c r="B235" s="10"/>
+    </row>
+    <row r="236" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A236" s="10"/>
+      <c r="B236" s="10"/>
+    </row>
+    <row r="237" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A237" s="10"/>
+      <c r="B237" s="10"/>
+    </row>
+    <row r="238" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A238" s="10"/>
+      <c r="B238" s="10"/>
+    </row>
+    <row r="239" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A239" s="10"/>
+      <c r="B239" s="10"/>
+    </row>
+    <row r="240" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A240" s="10"/>
+      <c r="B240" s="10"/>
+    </row>
+    <row r="241" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A241" s="10"/>
+      <c r="B241" s="10"/>
+    </row>
+    <row r="242" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A242" s="10"/>
+      <c r="B242" s="10"/>
+    </row>
+    <row r="243" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A243" s="10"/>
+      <c r="B243" s="10"/>
+    </row>
+    <row r="244" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A244" s="10"/>
+      <c r="B244" s="10"/>
+    </row>
+    <row r="245" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A245" s="10"/>
+      <c r="B245" s="10"/>
+    </row>
+    <row r="246" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A246" s="10"/>
+      <c r="B246" s="10"/>
+    </row>
+    <row r="247" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A247" s="10"/>
+      <c r="B247" s="10"/>
+    </row>
+    <row r="248" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A248" s="10"/>
+      <c r="B248" s="10"/>
+    </row>
+    <row r="249" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A249" s="10"/>
+      <c r="B249" s="10"/>
+    </row>
+    <row r="250" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A250" s="10"/>
+      <c r="B250" s="10"/>
+    </row>
+    <row r="251" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A251" s="10"/>
+      <c r="B251" s="10"/>
+    </row>
+    <row r="252" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A252" s="10"/>
+      <c r="B252" s="10"/>
+    </row>
+    <row r="253" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A253" s="10"/>
+      <c r="B253" s="10"/>
+    </row>
+    <row r="254" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A254" s="10"/>
+      <c r="B254" s="10"/>
+    </row>
+    <row r="255" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A255" s="10"/>
+      <c r="B255" s="10"/>
+    </row>
+    <row r="256" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A256" s="10"/>
+      <c r="B256" s="10"/>
+    </row>
+    <row r="257" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A257" s="10"/>
+      <c r="B257" s="10"/>
+    </row>
+    <row r="258" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A258" s="10"/>
+      <c r="B258" s="10"/>
+    </row>
+    <row r="259" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A259" s="10"/>
+      <c r="B259" s="10"/>
+    </row>
+    <row r="260" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A260" s="10"/>
+      <c r="B260" s="10"/>
+    </row>
+    <row r="261" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A261" s="10"/>
+      <c r="B261" s="10"/>
+    </row>
+    <row r="262" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A262" s="10"/>
+      <c r="B262" s="10"/>
+    </row>
+    <row r="263" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A263" s="10"/>
+      <c r="B263" s="10"/>
+    </row>
+    <row r="264" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A264" s="10"/>
+      <c r="B264" s="10"/>
+    </row>
+    <row r="265" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A265" s="10"/>
+      <c r="B265" s="10"/>
+    </row>
+    <row r="266" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A266" s="10"/>
+      <c r="B266" s="10"/>
+    </row>
+    <row r="267" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A267" s="10"/>
+      <c r="B267" s="10"/>
+    </row>
+    <row r="268" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A268" s="10"/>
+      <c r="B268" s="10"/>
+    </row>
+    <row r="269" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A269" s="10"/>
+      <c r="B269" s="10"/>
+    </row>
+    <row r="270" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A270" s="10"/>
+      <c r="B270" s="10"/>
+    </row>
+    <row r="271" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A271" s="10"/>
+      <c r="B271" s="10"/>
+    </row>
+    <row r="272" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A272" s="10"/>
+      <c r="B272" s="10"/>
+    </row>
+    <row r="273" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A273" s="10"/>
+      <c r="B273" s="10"/>
+    </row>
+    <row r="274" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A274" s="10"/>
+      <c r="B274" s="10"/>
+    </row>
+    <row r="275" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A275" s="10"/>
+      <c r="B275" s="10"/>
+    </row>
+    <row r="276" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A276" s="10"/>
+      <c r="B276" s="10"/>
+    </row>
+    <row r="277" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A277" s="10"/>
+      <c r="B277" s="10"/>
+    </row>
+    <row r="278" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A278" s="10"/>
+      <c r="B278" s="10"/>
+    </row>
+    <row r="279" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A279" s="10"/>
+      <c r="B279" s="10"/>
+    </row>
+    <row r="280" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A280" s="10"/>
+      <c r="B280" s="10"/>
+    </row>
+    <row r="281" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A281" s="10"/>
+      <c r="B281" s="10"/>
+    </row>
+    <row r="282" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A282" s="10"/>
+      <c r="B282" s="10"/>
+    </row>
+    <row r="283" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A283" s="10"/>
+      <c r="B283" s="10"/>
+    </row>
+    <row r="284" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A284" s="10"/>
+      <c r="B284" s="10"/>
+    </row>
+    <row r="285" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A285" s="10"/>
+      <c r="B285" s="10"/>
+    </row>
+    <row r="286" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A286" s="10"/>
+      <c r="B286" s="10"/>
+    </row>
+    <row r="287" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A287" s="10"/>
+      <c r="B287" s="10"/>
+    </row>
+    <row r="288" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A288" s="10"/>
+      <c r="B288" s="10"/>
+    </row>
+    <row r="289" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A289" s="10"/>
+      <c r="B289" s="10"/>
+    </row>
+    <row r="290" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A290" s="10"/>
+      <c r="B290" s="10"/>
+    </row>
+    <row r="291" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A291" s="10"/>
+      <c r="B291" s="10"/>
+    </row>
+    <row r="292" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A292" s="10"/>
+      <c r="B292" s="10"/>
+    </row>
+    <row r="293" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A293" s="10"/>
+      <c r="B293" s="10"/>
+    </row>
+    <row r="294" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A294" s="10"/>
+      <c r="B294" s="10"/>
+    </row>
+    <row r="295" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A295" s="10"/>
+      <c r="B295" s="10"/>
+    </row>
+    <row r="296" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A296" s="10"/>
+      <c r="B296" s="10"/>
+    </row>
+    <row r="297" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A297" s="10"/>
+      <c r="B297" s="10"/>
+    </row>
+    <row r="298" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A298" s="10"/>
+      <c r="B298" s="10"/>
+    </row>
+    <row r="299" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A299" s="10"/>
+      <c r="B299" s="10"/>
+    </row>
+    <row r="300" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A300" s="10"/>
+      <c r="B300" s="10"/>
+    </row>
+    <row r="301" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A301" s="10"/>
+      <c r="B301" s="10"/>
+    </row>
+    <row r="302" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A302" s="10"/>
+      <c r="B302" s="10"/>
+    </row>
+    <row r="303" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A303" s="10"/>
+      <c r="B303" s="10"/>
+    </row>
+    <row r="304" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A304" s="10"/>
+      <c r="B304" s="10"/>
+    </row>
+    <row r="305" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A305" s="10"/>
+      <c r="B305" s="10"/>
+    </row>
+    <row r="306" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A306" s="10"/>
+      <c r="B306" s="10"/>
+    </row>
+    <row r="307" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A307" s="10"/>
+      <c r="B307" s="10"/>
+    </row>
+    <row r="308" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A308" s="10"/>
+      <c r="B308" s="10"/>
+    </row>
+    <row r="309" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A309" s="10"/>
+      <c r="B309" s="10"/>
+    </row>
+    <row r="310" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A310" s="10"/>
+      <c r="B310" s="10"/>
+    </row>
+    <row r="311" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A311" s="10"/>
+      <c r="B311" s="10"/>
+    </row>
+    <row r="312" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A312" s="10"/>
+      <c r="B312" s="10"/>
+    </row>
+    <row r="313" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A313" s="10"/>
+      <c r="B313" s="10"/>
+    </row>
+    <row r="314" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A314" s="10"/>
+      <c r="B314" s="10"/>
+    </row>
+    <row r="315" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A315" s="10"/>
+      <c r="B315" s="10"/>
+    </row>
+    <row r="316" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A316" s="10"/>
+      <c r="B316" s="10"/>
+    </row>
+    <row r="317" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A317" s="10"/>
+      <c r="B317" s="10"/>
+    </row>
+    <row r="318" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A318" s="10"/>
+      <c r="B318" s="10"/>
+    </row>
+    <row r="319" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A319" s="10"/>
+      <c r="B319" s="10"/>
+    </row>
+    <row r="320" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A320" s="10"/>
+      <c r="B320" s="10"/>
+    </row>
+    <row r="321" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A321" s="10"/>
+      <c r="B321" s="10"/>
+    </row>
+    <row r="322" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A322" s="10"/>
+      <c r="B322" s="10"/>
+    </row>
+    <row r="323" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A323" s="10"/>
+      <c r="B323" s="10"/>
+    </row>
+    <row r="324" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A324" s="10"/>
+      <c r="B324" s="10"/>
+    </row>
+    <row r="325" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A325" s="10"/>
+      <c r="B325" s="10"/>
+    </row>
+    <row r="326" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A326" s="10"/>
+      <c r="B326" s="10"/>
+    </row>
+    <row r="327" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A327" s="10"/>
+      <c r="B327" s="10"/>
+    </row>
+    <row r="328" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A328" s="10"/>
+      <c r="B328" s="10"/>
+    </row>
+    <row r="329" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A329" s="10"/>
+      <c r="B329" s="10"/>
+    </row>
+    <row r="330" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A330" s="10"/>
+      <c r="B330" s="10"/>
+    </row>
+    <row r="331" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A331" s="10"/>
+      <c r="B331" s="10"/>
+    </row>
+    <row r="332" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A332" s="10"/>
+      <c r="B332" s="10"/>
+    </row>
+    <row r="333" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A333" s="10"/>
+      <c r="B333" s="10"/>
+    </row>
+    <row r="334" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A334" s="10"/>
+      <c r="B334" s="10"/>
+    </row>
+    <row r="335" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A335" s="10"/>
+      <c r="B335" s="10"/>
+    </row>
+    <row r="336" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A336" s="10"/>
+      <c r="B336" s="10"/>
+    </row>
+    <row r="337" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A337" s="10"/>
+      <c r="B337" s="10"/>
+    </row>
+    <row r="338" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A338" s="10"/>
+      <c r="B338" s="10"/>
+    </row>
+    <row r="339" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A339" s="10"/>
+      <c r="B339" s="10"/>
+    </row>
+    <row r="340" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A340" s="10"/>
+      <c r="B340" s="10"/>
+    </row>
+    <row r="341" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A341" s="10"/>
+      <c r="B341" s="10"/>
+    </row>
+    <row r="342" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A342" s="10"/>
+      <c r="B342" s="10"/>
+    </row>
+    <row r="343" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A343" s="10"/>
+      <c r="B343" s="10"/>
+    </row>
+    <row r="344" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A344" s="10"/>
+      <c r="B344" s="10"/>
+    </row>
+    <row r="345" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A345" s="10"/>
+      <c r="B345" s="10"/>
+    </row>
+    <row r="346" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A346" s="10"/>
+      <c r="B346" s="10"/>
+    </row>
+    <row r="347" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A347" s="10"/>
+      <c r="B347" s="10"/>
+    </row>
+    <row r="348" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A348" s="10"/>
+      <c r="B348" s="10"/>
+    </row>
+    <row r="349" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A349" s="10"/>
+      <c r="B349" s="10"/>
+    </row>
+    <row r="350" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A350" s="10"/>
+      <c r="B350" s="10"/>
+    </row>
+    <row r="351" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A351" s="10"/>
+      <c r="B351" s="10"/>
+    </row>
+    <row r="352" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A352" s="10"/>
+      <c r="B352" s="10"/>
+    </row>
+    <row r="353" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A353" s="10"/>
+      <c r="B353" s="10"/>
+    </row>
+    <row r="354" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A354" s="10"/>
+      <c r="B354" s="10"/>
+    </row>
+    <row r="355" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A355" s="10"/>
+      <c r="B355" s="10"/>
+    </row>
+    <row r="356" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A356" s="10"/>
+      <c r="B356" s="10"/>
+    </row>
+    <row r="357" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A357" s="10"/>
+      <c r="B357" s="10"/>
+    </row>
+    <row r="358" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A358" s="10"/>
+      <c r="B358" s="10"/>
+    </row>
+    <row r="359" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A359" s="10"/>
+      <c r="B359" s="10"/>
+    </row>
+    <row r="360" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A360" s="10"/>
+      <c r="B360" s="10"/>
+    </row>
+    <row r="361" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A361" s="10"/>
+      <c r="B361" s="10"/>
+    </row>
+    <row r="362" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A362" s="10"/>
+      <c r="B362" s="10"/>
+    </row>
+    <row r="363" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A363" s="10"/>
+      <c r="B363" s="10"/>
+    </row>
+    <row r="364" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A364" s="10"/>
+      <c r="B364" s="10"/>
+    </row>
+    <row r="365" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A365" s="10"/>
+      <c r="B365" s="10"/>
+    </row>
+    <row r="366" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A366" s="10"/>
+      <c r="B366" s="10"/>
+    </row>
+    <row r="367" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A367" s="10"/>
+      <c r="B367" s="10"/>
+    </row>
+    <row r="368" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A368" s="10"/>
+      <c r="B368" s="10"/>
+    </row>
+    <row r="369" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A369" s="10"/>
+      <c r="B369" s="10"/>
+    </row>
+    <row r="370" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A370" s="10"/>
+      <c r="B370" s="10"/>
+    </row>
+    <row r="371" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A371" s="10"/>
+      <c r="B371" s="10"/>
+    </row>
+    <row r="372" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A372" s="10"/>
+      <c r="B372" s="10"/>
+    </row>
+    <row r="373" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A373" s="10"/>
+      <c r="B373" s="10"/>
+    </row>
+    <row r="374" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A374" s="10"/>
+      <c r="B374" s="10"/>
+    </row>
+    <row r="375" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A375" s="10"/>
+      <c r="B375" s="10"/>
+    </row>
+    <row r="376" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A376" s="10"/>
+      <c r="B376" s="10"/>
+    </row>
+    <row r="377" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A377" s="10"/>
+      <c r="B377" s="10"/>
+    </row>
+    <row r="378" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A378" s="10"/>
+      <c r="B378" s="10"/>
+    </row>
+    <row r="379" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A379" s="10"/>
+      <c r="B379" s="10"/>
+    </row>
+    <row r="380" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A380" s="10"/>
+      <c r="B380" s="10"/>
+    </row>
+    <row r="381" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A381" s="10"/>
+      <c r="B381" s="10"/>
+    </row>
+    <row r="382" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A382" s="10"/>
+      <c r="B382" s="10"/>
+    </row>
+    <row r="383" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A383" s="10"/>
+      <c r="B383" s="10"/>
+    </row>
+    <row r="384" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A384" s="10"/>
+      <c r="B384" s="10"/>
+    </row>
+    <row r="385" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A385" s="10"/>
+      <c r="B385" s="10"/>
+    </row>
+    <row r="386" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A386" s="10"/>
+      <c r="B386" s="10"/>
+    </row>
+    <row r="387" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A387" s="10"/>
+      <c r="B387" s="10"/>
+    </row>
+    <row r="388" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A388" s="10"/>
+      <c r="B388" s="10"/>
+    </row>
+    <row r="389" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A389" s="10"/>
+      <c r="B389" s="10"/>
+    </row>
+    <row r="390" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A390" s="10"/>
+      <c r="B390" s="10"/>
+    </row>
+    <row r="391" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A391" s="10"/>
+      <c r="B391" s="10"/>
+    </row>
+    <row r="392" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A392" s="10"/>
+      <c r="B392" s="10"/>
+    </row>
+    <row r="393" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A393" s="10"/>
+      <c r="B393" s="10"/>
+    </row>
+    <row r="394" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A394" s="10"/>
+      <c r="B394" s="10"/>
+    </row>
+    <row r="395" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A395" s="10"/>
+      <c r="B395" s="10"/>
+    </row>
+    <row r="396" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A396" s="10"/>
+      <c r="B396" s="10"/>
+    </row>
+    <row r="397" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A397" s="10"/>
+      <c r="B397" s="10"/>
+    </row>
+    <row r="398" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A398" s="10"/>
+      <c r="B398" s="10"/>
+    </row>
+    <row r="399" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A399" s="10"/>
+      <c r="B399" s="10"/>
+    </row>
+    <row r="400" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A400" s="10"/>
+      <c r="B400" s="10"/>
+    </row>
+    <row r="401" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A401" s="10"/>
+      <c r="B401" s="10"/>
+    </row>
+    <row r="402" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A402" s="10"/>
+      <c r="B402" s="10"/>
+    </row>
+    <row r="403" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A403" s="10"/>
+      <c r="B403" s="10"/>
+    </row>
+    <row r="404" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A404" s="10"/>
+      <c r="B404" s="10"/>
+    </row>
+    <row r="405" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A405" s="10"/>
+      <c r="B405" s="10"/>
+    </row>
+    <row r="406" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A406" s="10"/>
+      <c r="B406" s="10"/>
+    </row>
+    <row r="407" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A407" s="10"/>
+      <c r="B407" s="10"/>
+    </row>
+    <row r="408" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A408" s="10"/>
+      <c r="B408" s="10"/>
+    </row>
+    <row r="409" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A409" s="10"/>
+      <c r="B409" s="10"/>
+    </row>
+    <row r="410" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A410" s="10"/>
+      <c r="B410" s="10"/>
+    </row>
+    <row r="411" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A411" s="10"/>
+      <c r="B411" s="10"/>
+    </row>
+    <row r="412" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A412" s="10"/>
+      <c r="B412" s="10"/>
+    </row>
+    <row r="413" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A413" s="10"/>
+      <c r="B413" s="10"/>
+    </row>
+    <row r="414" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A414" s="10"/>
+      <c r="B414" s="10"/>
+    </row>
+    <row r="415" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A415" s="10"/>
+      <c r="B415" s="10"/>
+    </row>
+    <row r="416" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A416" s="10"/>
+      <c r="B416" s="10"/>
+    </row>
+    <row r="417" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A417" s="10"/>
+      <c r="B417" s="10"/>
+    </row>
+    <row r="418" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A418" s="10"/>
+      <c r="B418" s="10"/>
+    </row>
+    <row r="419" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A419" s="10"/>
+      <c r="B419" s="10"/>
+    </row>
+    <row r="420" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A420" s="10"/>
+      <c r="B420" s="10"/>
+    </row>
+    <row r="421" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A421" s="10"/>
+      <c r="B421" s="10"/>
+    </row>
+    <row r="422" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A422" s="10"/>
+      <c r="B422" s="10"/>
+    </row>
+    <row r="423" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A423" s="10"/>
+      <c r="B423" s="10"/>
+    </row>
+    <row r="424" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A424" s="10"/>
+      <c r="B424" s="10"/>
+    </row>
+    <row r="425" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A425" s="10"/>
+      <c r="B425" s="10"/>
+    </row>
+    <row r="426" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A426" s="10"/>
+      <c r="B426" s="10"/>
+    </row>
+    <row r="427" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A427" s="10"/>
+      <c r="B427" s="10"/>
+    </row>
+    <row r="428" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A428" s="10"/>
+      <c r="B428" s="10"/>
+    </row>
+    <row r="429" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A429" s="10"/>
+      <c r="B429" s="10"/>
+    </row>
+    <row r="430" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A430" s="10"/>
+      <c r="B430" s="10"/>
+    </row>
+    <row r="431" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A431" s="10"/>
+      <c r="B431" s="10"/>
+    </row>
+    <row r="432" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A432" s="10"/>
+      <c r="B432" s="10"/>
+    </row>
+    <row r="433" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A433" s="10"/>
+      <c r="B433" s="10"/>
+    </row>
+    <row r="434" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A434" s="10"/>
+      <c r="B434" s="10"/>
+    </row>
+    <row r="435" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A435" s="10"/>
+      <c r="B435" s="10"/>
+    </row>
+    <row r="436" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A436" s="10"/>
+      <c r="B436" s="10"/>
+    </row>
+    <row r="437" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A437" s="10"/>
+      <c r="B437" s="10"/>
+    </row>
+    <row r="438" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A438" s="10"/>
+      <c r="B438" s="10"/>
+    </row>
+    <row r="439" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A439" s="10"/>
+      <c r="B439" s="10"/>
+    </row>
+    <row r="440" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A440" s="10"/>
+      <c r="B440" s="10"/>
+    </row>
+    <row r="441" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A441" s="10"/>
+      <c r="B441" s="10"/>
+    </row>
+    <row r="442" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A442" s="10"/>
+      <c r="B442" s="10"/>
+    </row>
+    <row r="443" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A443" s="10"/>
+      <c r="B443" s="10"/>
+    </row>
+    <row r="444" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A444" s="10"/>
+      <c r="B444" s="10"/>
+    </row>
+    <row r="445" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A445" s="10"/>
+      <c r="B445" s="10"/>
+    </row>
+    <row r="446" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A446" s="10"/>
+      <c r="B446" s="10"/>
+    </row>
+    <row r="447" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A447" s="10"/>
+      <c r="B447" s="10"/>
+    </row>
+    <row r="448" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A448" s="10"/>
+      <c r="B448" s="10"/>
+    </row>
+    <row r="449" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A449" s="10"/>
+      <c r="B449" s="10"/>
+    </row>
+    <row r="450" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A450" s="10"/>
+      <c r="B450" s="10"/>
+    </row>
+    <row r="451" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A451" s="10"/>
+      <c r="B451" s="10"/>
+    </row>
+    <row r="452" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A452" s="10"/>
+      <c r="B452" s="10"/>
+    </row>
+    <row r="453" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A453" s="10"/>
+      <c r="B453" s="10"/>
+    </row>
+    <row r="454" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A454" s="10"/>
+      <c r="B454" s="10"/>
+    </row>
+    <row r="455" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A455" s="10"/>
+      <c r="B455" s="10"/>
+    </row>
+    <row r="456" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A456" s="10"/>
+      <c r="B456" s="10"/>
+    </row>
+    <row r="457" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A457" s="10"/>
+      <c r="B457" s="10"/>
+    </row>
+    <row r="458" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A458" s="10"/>
+      <c r="B458" s="10"/>
+    </row>
+    <row r="459" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A459" s="10"/>
+      <c r="B459" s="10"/>
+    </row>
+    <row r="460" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A460" s="10"/>
+      <c r="B460" s="10"/>
+    </row>
+    <row r="461" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A461" s="10"/>
+      <c r="B461" s="10"/>
+    </row>
+    <row r="462" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A462" s="10"/>
+      <c r="B462" s="10"/>
+    </row>
+    <row r="463" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A463" s="10"/>
+      <c r="B463" s="10"/>
+    </row>
+    <row r="464" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A464" s="10"/>
+      <c r="B464" s="10"/>
+    </row>
+    <row r="465" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A465" s="10"/>
+      <c r="B465" s="10"/>
+    </row>
+    <row r="466" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A466" s="10"/>
+      <c r="B466" s="10"/>
+    </row>
+    <row r="467" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A467" s="10"/>
+      <c r="B467" s="10"/>
+    </row>
+    <row r="468" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A468" s="10"/>
+      <c r="B468" s="10"/>
+    </row>
+    <row r="469" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A469" s="10"/>
+      <c r="B469" s="10"/>
+    </row>
+    <row r="470" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A470" s="10"/>
+      <c r="B470" s="10"/>
+    </row>
+    <row r="471" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A471" s="10"/>
+      <c r="B471" s="10"/>
+    </row>
+    <row r="472" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A472" s="10"/>
+      <c r="B472" s="10"/>
+    </row>
+    <row r="473" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A473" s="10"/>
+      <c r="B473" s="10"/>
+    </row>
+    <row r="474" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A474" s="10"/>
+      <c r="B474" s="10"/>
+    </row>
+    <row r="475" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A475" s="10"/>
+      <c r="B475" s="10"/>
+    </row>
+    <row r="476" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A476" s="10"/>
+      <c r="B476" s="10"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A477" s="10"/>
+      <c r="B477" s="10"/>
+    </row>
+    <row r="478" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A478" s="10"/>
+      <c r="B478" s="10"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A479" s="10"/>
+      <c r="B479" s="10"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A480" s="10"/>
+      <c r="B480" s="10"/>
+    </row>
+    <row r="481" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A481" s="10"/>
+      <c r="B481" s="10"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A482" s="10"/>
+      <c r="B482" s="10"/>
+    </row>
+    <row r="483" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A483" s="10"/>
+      <c r="B483" s="10"/>
+    </row>
+    <row r="484" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A484" s="10"/>
+      <c r="B484" s="10"/>
+    </row>
+    <row r="485" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A485" s="10"/>
+      <c r="B485" s="10"/>
+    </row>
+    <row r="486" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A486" s="10"/>
+      <c r="B486" s="10"/>
+    </row>
+    <row r="487" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A487" s="10"/>
+      <c r="B487" s="10"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A488" s="10"/>
+      <c r="B488" s="10"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A489" s="10"/>
+      <c r="B489" s="10"/>
+    </row>
+    <row r="490" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A490" s="10"/>
+      <c r="B490" s="10"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A491" s="10"/>
+      <c r="B491" s="10"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A492" s="10"/>
+      <c r="B492" s="10"/>
+    </row>
+    <row r="493" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A493" s="10"/>
+      <c r="B493" s="10"/>
+    </row>
+    <row r="494" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A494" s="10"/>
+      <c r="B494" s="10"/>
+    </row>
+    <row r="495" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A495" s="10"/>
+      <c r="B495" s="10"/>
+    </row>
+    <row r="496" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A496" s="10"/>
+      <c r="B496" s="10"/>
+    </row>
+    <row r="497" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A497" s="10"/>
+      <c r="B497" s="10"/>
+    </row>
+    <row r="498" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A498" s="10"/>
+      <c r="B498" s="10"/>
+    </row>
+    <row r="499" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A499" s="10"/>
+      <c r="B499" s="10"/>
+    </row>
+    <row r="500" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A500" s="10"/>
+      <c r="B500" s="10"/>
+    </row>
+    <row r="501" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A501" s="10"/>
+      <c r="B501" s="10"/>
+    </row>
+    <row r="502" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A502" s="10"/>
+      <c r="B502" s="10"/>
+    </row>
+    <row r="503" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A503" s="10"/>
+      <c r="B503" s="10"/>
+    </row>
+    <row r="504" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A504" s="10"/>
+      <c r="B504" s="10"/>
+    </row>
+    <row r="505" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A505" s="10"/>
+      <c r="B505" s="10"/>
+    </row>
+    <row r="506" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A506" s="10"/>
+      <c r="B506" s="10"/>
+    </row>
+    <row r="507" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A507" s="10"/>
+      <c r="B507" s="10"/>
+    </row>
+    <row r="508" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A508" s="10"/>
+      <c r="B508" s="10"/>
+    </row>
+    <row r="509" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A509" s="10"/>
+      <c r="B509" s="10"/>
+    </row>
+    <row r="510" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A510" s="10"/>
+      <c r="B510" s="10"/>
+    </row>
+    <row r="511" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A511" s="10"/>
+      <c r="B511" s="10"/>
+    </row>
+    <row r="512" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A512" s="10"/>
+      <c r="B512" s="10"/>
+    </row>
+    <row r="513" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A513" s="10"/>
+      <c r="B513" s="10"/>
+    </row>
+    <row r="514" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A514" s="10"/>
+      <c r="B514" s="10"/>
+    </row>
+    <row r="515" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A515" s="10"/>
+      <c r="B515" s="10"/>
+    </row>
+    <row r="516" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A516" s="10"/>
+      <c r="B516" s="10"/>
+    </row>
+    <row r="517" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A517" s="10"/>
+      <c r="B517" s="10"/>
+    </row>
+    <row r="518" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A518" s="10"/>
+      <c r="B518" s="10"/>
+    </row>
+    <row r="519" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A519" s="10"/>
+      <c r="B519" s="10"/>
+    </row>
+    <row r="520" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A520" s="10"/>
+      <c r="B520" s="10"/>
+    </row>
+    <row r="521" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A521" s="10"/>
+      <c r="B521" s="10"/>
+    </row>
+    <row r="522" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A522" s="10"/>
+      <c r="B522" s="10"/>
+    </row>
+    <row r="523" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A523" s="10"/>
+      <c r="B523" s="10"/>
+    </row>
+    <row r="524" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A524" s="10"/>
+      <c r="B524" s="10"/>
+    </row>
+    <row r="525" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A525" s="10"/>
+      <c r="B525" s="10"/>
+    </row>
+    <row r="526" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A526" s="10"/>
+      <c r="B526" s="10"/>
+    </row>
+    <row r="527" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A527" s="10"/>
+      <c r="B527" s="10"/>
+    </row>
+    <row r="528" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A528" s="10"/>
+      <c r="B528" s="10"/>
+    </row>
+    <row r="529" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A529" s="10"/>
+      <c r="B529" s="10"/>
+    </row>
+    <row r="530" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A530" s="10"/>
+      <c r="B530" s="10"/>
+    </row>
+    <row r="531" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A531" s="10"/>
+      <c r="B531" s="10"/>
+    </row>
+    <row r="532" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A532" s="10"/>
+      <c r="B532" s="10"/>
+    </row>
+    <row r="533" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A533" s="10"/>
+      <c r="B533" s="10"/>
+    </row>
+    <row r="534" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A534" s="10"/>
+      <c r="B534" s="10"/>
+    </row>
+    <row r="535" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A535" s="10"/>
+      <c r="B535" s="10"/>
+    </row>
+    <row r="536" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A536" s="10"/>
+      <c r="B536" s="10"/>
+    </row>
+    <row r="537" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A537" s="10"/>
+      <c r="B537" s="10"/>
+    </row>
+    <row r="538" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A538" s="10"/>
+      <c r="B538" s="10"/>
+    </row>
+    <row r="539" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A539" s="10"/>
+      <c r="B539" s="10"/>
+    </row>
+    <row r="540" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A540" s="10"/>
+      <c r="B540" s="10"/>
+    </row>
+    <row r="541" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A541" s="10"/>
+      <c r="B541" s="10"/>
+    </row>
+    <row r="542" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A542" s="10"/>
+      <c r="B542" s="10"/>
+    </row>
+    <row r="543" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A543" s="10"/>
+      <c r="B543" s="10"/>
+    </row>
+    <row r="544" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A544" s="10"/>
+      <c r="B544" s="10"/>
+    </row>
+    <row r="545" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A545" s="10"/>
+      <c r="B545" s="10"/>
+    </row>
+    <row r="546" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A546" s="10"/>
+      <c r="B546" s="10"/>
+    </row>
+    <row r="547" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A547" s="10"/>
+      <c r="B547" s="10"/>
+    </row>
+    <row r="548" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A548" s="10"/>
+      <c r="B548" s="10"/>
+    </row>
+    <row r="549" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A549" s="10"/>
+      <c r="B549" s="10"/>
+    </row>
+    <row r="550" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A550" s="10"/>
+      <c r="B550" s="10"/>
+    </row>
+    <row r="551" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A551" s="10"/>
+      <c r="B551" s="10"/>
+    </row>
+    <row r="552" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A552" s="10"/>
+      <c r="B552" s="10"/>
+    </row>
+    <row r="553" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A553" s="10"/>
+      <c r="B553" s="10"/>
+    </row>
+    <row r="554" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A554" s="10"/>
+      <c r="B554" s="10"/>
+    </row>
+    <row r="555" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A555" s="10"/>
+      <c r="B555" s="10"/>
+    </row>
+    <row r="556" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A556" s="10"/>
+      <c r="B556" s="10"/>
+    </row>
+    <row r="557" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A557" s="10"/>
+      <c r="B557" s="10"/>
+    </row>
+    <row r="558" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A558" s="10"/>
+      <c r="B558" s="10"/>
+    </row>
+    <row r="559" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A559" s="10"/>
+      <c r="B559" s="10"/>
+    </row>
+    <row r="560" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A560" s="10"/>
+      <c r="B560" s="10"/>
+    </row>
+    <row r="561" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A561" s="10"/>
+      <c r="B561" s="10"/>
+    </row>
+    <row r="562" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A562" s="10"/>
+      <c r="B562" s="10"/>
+    </row>
+    <row r="563" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A563" s="10"/>
+      <c r="B563" s="10"/>
+    </row>
+    <row r="564" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A564" s="10"/>
+      <c r="B564" s="10"/>
+    </row>
+    <row r="565" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A565" s="10"/>
+      <c r="B565" s="10"/>
+    </row>
+    <row r="566" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A566" s="10"/>
+      <c r="B566" s="10"/>
+    </row>
+    <row r="567" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A567" s="10"/>
+      <c r="B567" s="10"/>
+    </row>
+    <row r="568" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A568" s="10"/>
+      <c r="B568" s="10"/>
+    </row>
+    <row r="569" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A569" s="10"/>
+      <c r="B569" s="10"/>
+    </row>
+    <row r="570" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A570" s="10"/>
+      <c r="B570" s="10"/>
+    </row>
+    <row r="571" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A571" s="10"/>
+      <c r="B571" s="10"/>
+    </row>
+    <row r="572" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A572" s="10"/>
+      <c r="B572" s="10"/>
+    </row>
+    <row r="573" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A573" s="10"/>
+      <c r="B573" s="10"/>
+    </row>
+    <row r="574" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A574" s="10"/>
+      <c r="B574" s="10"/>
+    </row>
+    <row r="575" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A575" s="10"/>
+      <c r="B575" s="10"/>
+    </row>
+    <row r="576" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A576" s="10"/>
+      <c r="B576" s="10"/>
+    </row>
+    <row r="577" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A577" s="10"/>
+      <c r="B577" s="10"/>
+    </row>
+    <row r="578" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A578" s="10"/>
+      <c r="B578" s="10"/>
+    </row>
+    <row r="579" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A579" s="10"/>
+      <c r="B579" s="10"/>
+    </row>
+    <row r="580" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A580" s="10"/>
+      <c r="B580" s="10"/>
+    </row>
+    <row r="581" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A581" s="10"/>
+      <c r="B581" s="10"/>
+    </row>
+    <row r="582" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A582" s="10"/>
+      <c r="B582" s="10"/>
+    </row>
+    <row r="583" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A583" s="10"/>
+      <c r="B583" s="10"/>
+    </row>
+    <row r="584" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A584" s="10"/>
+      <c r="B584" s="10"/>
+    </row>
+    <row r="585" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A585" s="10"/>
+      <c r="B585" s="10"/>
+    </row>
+    <row r="586" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A586" s="10"/>
+      <c r="B586" s="10"/>
+    </row>
+    <row r="587" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A587" s="10"/>
+      <c r="B587" s="10"/>
+    </row>
+    <row r="588" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A588" s="10"/>
+      <c r="B588" s="10"/>
+    </row>
+    <row r="589" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A589" s="10"/>
+      <c r="B589" s="10"/>
+    </row>
+    <row r="590" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A590" s="10"/>
+      <c r="B590" s="10"/>
+    </row>
+    <row r="591" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A591" s="10"/>
+      <c r="B591" s="10"/>
+    </row>
+    <row r="592" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A592" s="10"/>
+      <c r="B592" s="10"/>
+    </row>
+    <row r="593" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A593" s="10"/>
+      <c r="B593" s="10"/>
+    </row>
+    <row r="594" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A594" s="10"/>
+      <c r="B594" s="10"/>
+    </row>
+    <row r="595" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A595" s="10"/>
+      <c r="B595" s="10"/>
+    </row>
+    <row r="596" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A596" s="10"/>
+      <c r="B596" s="10"/>
+    </row>
+    <row r="597" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A597" s="10"/>
+      <c r="B597" s="10"/>
+    </row>
+    <row r="598" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A598" s="10"/>
+      <c r="B598" s="10"/>
+    </row>
+    <row r="599" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A599" s="10"/>
+      <c r="B599" s="10"/>
+    </row>
+    <row r="600" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A600" s="10"/>
+      <c r="B600" s="10"/>
+    </row>
+    <row r="601" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A601" s="10"/>
+      <c r="B601" s="10"/>
+    </row>
+    <row r="602" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A602" s="10"/>
+      <c r="B602" s="10"/>
+    </row>
+    <row r="603" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A603" s="10"/>
+      <c r="B603" s="10"/>
+    </row>
+    <row r="604" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A604" s="10"/>
+      <c r="B604" s="10"/>
+    </row>
+    <row r="605" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A605" s="10"/>
+      <c r="B605" s="10"/>
+    </row>
+    <row r="606" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A606" s="10"/>
+      <c r="B606" s="10"/>
+    </row>
+    <row r="607" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A607" s="10"/>
+      <c r="B607" s="10"/>
+    </row>
+    <row r="608" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A608" s="10"/>
+      <c r="B608" s="10"/>
+    </row>
+    <row r="609" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A609" s="10"/>
+      <c r="B609" s="10"/>
+    </row>
+    <row r="610" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A610" s="10"/>
+      <c r="B610" s="10"/>
+    </row>
+    <row r="611" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A611" s="10"/>
+      <c r="B611" s="10"/>
+    </row>
+    <row r="612" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A612" s="10"/>
+      <c r="B612" s="10"/>
+    </row>
+    <row r="613" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A613" s="10"/>
+      <c r="B613" s="10"/>
+    </row>
+    <row r="614" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A614" s="10"/>
+      <c r="B614" s="10"/>
+    </row>
+    <row r="615" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A615" s="10"/>
+      <c r="B615" s="10"/>
+    </row>
+    <row r="616" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A616" s="10"/>
+      <c r="B616" s="10"/>
+    </row>
+    <row r="617" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A617" s="10"/>
+      <c r="B617" s="10"/>
+    </row>
+    <row r="618" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A618" s="10"/>
+      <c r="B618" s="10"/>
+    </row>
+    <row r="619" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A619" s="10"/>
+      <c r="B619" s="10"/>
+    </row>
+    <row r="620" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A620" s="10"/>
+      <c r="B620" s="10"/>
+    </row>
+    <row r="621" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A621" s="10"/>
+      <c r="B621" s="10"/>
+    </row>
+    <row r="622" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A622" s="10"/>
+      <c r="B622" s="10"/>
+    </row>
+    <row r="623" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A623" s="10"/>
+      <c r="B623" s="10"/>
+    </row>
+    <row r="624" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A624" s="10"/>
+      <c r="B624" s="10"/>
+    </row>
+    <row r="625" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A625" s="10"/>
+      <c r="B625" s="10"/>
+    </row>
+    <row r="626" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A626" s="10"/>
+      <c r="B626" s="10"/>
+    </row>
+    <row r="627" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A627" s="10"/>
+      <c r="B627" s="10"/>
+    </row>
+    <row r="628" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A628" s="10"/>
+      <c r="B628" s="10"/>
+    </row>
+    <row r="629" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A629" s="10"/>
+      <c r="B629" s="10"/>
+    </row>
+    <row r="630" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A630" s="10"/>
+      <c r="B630" s="10"/>
+    </row>
+    <row r="631" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A631" s="10"/>
+      <c r="B631" s="10"/>
+    </row>
+    <row r="632" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A632" s="10"/>
+      <c r="B632" s="10"/>
+    </row>
+    <row r="633" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A633" s="10"/>
+      <c r="B633" s="10"/>
+    </row>
+    <row r="634" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A634" s="10"/>
+      <c r="B634" s="10"/>
+    </row>
+    <row r="635" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A635" s="10"/>
+      <c r="B635" s="10"/>
+    </row>
+    <row r="636" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A636" s="10"/>
+      <c r="B636" s="10"/>
+    </row>
+    <row r="637" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A637" s="10"/>
+      <c r="B637" s="10"/>
+    </row>
+    <row r="638" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A638" s="10"/>
+      <c r="B638" s="10"/>
+    </row>
+    <row r="639" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A639" s="10"/>
+      <c r="B639" s="10"/>
+    </row>
+    <row r="640" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A640" s="10"/>
+      <c r="B640" s="10"/>
+    </row>
+    <row r="641" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A641" s="10"/>
+      <c r="B641" s="10"/>
+    </row>
+    <row r="642" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A642" s="10"/>
+      <c r="B642" s="10"/>
+    </row>
+    <row r="643" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A643" s="10"/>
+      <c r="B643" s="10"/>
+    </row>
+    <row r="644" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A644" s="10"/>
+      <c r="B644" s="10"/>
+    </row>
+    <row r="645" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A645" s="10"/>
+      <c r="B645" s="10"/>
+    </row>
+    <row r="646" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A646" s="10"/>
+      <c r="B646" s="10"/>
+    </row>
+    <row r="647" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A647" s="10"/>
+      <c r="B647" s="10"/>
+    </row>
+    <row r="648" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A648" s="10"/>
+      <c r="B648" s="10"/>
+    </row>
+    <row r="649" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A649" s="10"/>
+      <c r="B649" s="10"/>
+    </row>
+    <row r="650" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A650" s="10"/>
+      <c r="B650" s="10"/>
+    </row>
+    <row r="651" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A651" s="10"/>
+      <c r="B651" s="10"/>
+    </row>
+    <row r="652" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A652" s="10"/>
+      <c r="B652" s="10"/>
+    </row>
+    <row r="653" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A653" s="10"/>
+      <c r="B653" s="10"/>
+    </row>
+    <row r="654" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A654" s="10"/>
+      <c r="B654" s="10"/>
+    </row>
+    <row r="655" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A655" s="10"/>
+      <c r="B655" s="10"/>
+    </row>
+    <row r="656" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A656" s="10"/>
+      <c r="B656" s="10"/>
+    </row>
+    <row r="657" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A657" s="10"/>
+      <c r="B657" s="10"/>
+    </row>
+    <row r="658" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A658" s="10"/>
+      <c r="B658" s="10"/>
+    </row>
+    <row r="659" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A659" s="10"/>
+      <c r="B659" s="10"/>
+    </row>
+    <row r="660" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A660" s="10"/>
+      <c r="B660" s="10"/>
+    </row>
+    <row r="661" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A661" s="10"/>
+      <c r="B661" s="10"/>
+    </row>
+    <row r="662" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A662" s="10"/>
+      <c r="B662" s="10"/>
+    </row>
+    <row r="663" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A663" s="10"/>
+      <c r="B663" s="10"/>
+    </row>
+    <row r="664" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A664" s="10"/>
+      <c r="B664" s="10"/>
+    </row>
+    <row r="665" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A665" s="10"/>
+      <c r="B665" s="10"/>
+    </row>
+    <row r="666" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A666" s="10"/>
+      <c r="B666" s="10"/>
+    </row>
+    <row r="667" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A667" s="10"/>
+      <c r="B667" s="10"/>
+    </row>
+    <row r="668" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A668" s="10"/>
+      <c r="B668" s="10"/>
+    </row>
+    <row r="669" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A669" s="10"/>
+      <c r="B669" s="10"/>
+    </row>
+    <row r="670" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A670" s="10"/>
+      <c r="B670" s="10"/>
+    </row>
+    <row r="671" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A671" s="10"/>
+      <c r="B671" s="10"/>
+    </row>
+    <row r="672" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A672" s="10"/>
+      <c r="B672" s="10"/>
+    </row>
+    <row r="673" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A673" s="10"/>
+      <c r="B673" s="10"/>
+    </row>
+    <row r="674" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A674" s="10"/>
+      <c r="B674" s="10"/>
+    </row>
+    <row r="675" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A675" s="10"/>
+      <c r="B675" s="10"/>
+    </row>
+    <row r="676" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A676" s="10"/>
+      <c r="B676" s="10"/>
+    </row>
+    <row r="677" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A677" s="10"/>
+      <c r="B677" s="10"/>
+    </row>
+    <row r="678" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A678" s="10"/>
+      <c r="B678" s="10"/>
+    </row>
+    <row r="679" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A679" s="10"/>
+      <c r="B679" s="10"/>
+    </row>
+    <row r="680" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A680" s="10"/>
+      <c r="B680" s="10"/>
+    </row>
+    <row r="681" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A681" s="10"/>
+      <c r="B681" s="10"/>
+    </row>
+    <row r="682" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A682" s="10"/>
+      <c r="B682" s="10"/>
+    </row>
+    <row r="683" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A683" s="10"/>
+      <c r="B683" s="10"/>
+    </row>
+    <row r="684" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A684" s="10"/>
+      <c r="B684" s="10"/>
+    </row>
+    <row r="685" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A685" s="10"/>
+      <c r="B685" s="10"/>
+    </row>
+    <row r="686" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A686" s="10"/>
+      <c r="B686" s="10"/>
+    </row>
+    <row r="687" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A687" s="10"/>
+      <c r="B687" s="10"/>
+    </row>
+    <row r="688" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A688" s="10"/>
+      <c r="B688" s="10"/>
+    </row>
+    <row r="689" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A689" s="10"/>
+      <c r="B689" s="10"/>
+    </row>
+    <row r="690" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A690" s="10"/>
+      <c r="B690" s="10"/>
+    </row>
+    <row r="691" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A691" s="10"/>
+      <c r="B691" s="10"/>
+    </row>
+    <row r="692" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A692" s="10"/>
+      <c r="B692" s="10"/>
+    </row>
+    <row r="693" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A693" s="10"/>
+      <c r="B693" s="10"/>
+    </row>
+    <row r="694" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A694" s="10"/>
+      <c r="B694" s="10"/>
+    </row>
+    <row r="695" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A695" s="10"/>
+      <c r="B695" s="10"/>
+    </row>
+    <row r="696" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A696" s="10"/>
+      <c r="B696" s="10"/>
+    </row>
+    <row r="697" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A697" s="10"/>
+      <c r="B697" s="10"/>
+    </row>
+    <row r="698" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A698" s="10"/>
+      <c r="B698" s="10"/>
+    </row>
+    <row r="699" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A699" s="10"/>
+      <c r="B699" s="10"/>
+    </row>
+    <row r="700" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A700" s="10"/>
+      <c r="B700" s="10"/>
+    </row>
+    <row r="701" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A701" s="10"/>
+      <c r="B701" s="10"/>
+    </row>
+    <row r="702" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A702" s="10"/>
+      <c r="B702" s="10"/>
+    </row>
+    <row r="703" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A703" s="10"/>
+      <c r="B703" s="10"/>
+    </row>
+    <row r="704" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A704" s="10"/>
+      <c r="B704" s="10"/>
+    </row>
+    <row r="705" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A705" s="10"/>
+      <c r="B705" s="10"/>
+    </row>
+    <row r="706" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A706" s="10"/>
+      <c r="B706" s="10"/>
+    </row>
+    <row r="707" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A707" s="10"/>
+      <c r="B707" s="10"/>
+    </row>
+    <row r="708" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A708" s="10"/>
+      <c r="B708" s="10"/>
+    </row>
+    <row r="709" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A709" s="10"/>
+      <c r="B709" s="10"/>
+    </row>
+    <row r="710" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A710" s="10"/>
+      <c r="B710" s="10"/>
+    </row>
+    <row r="711" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A711" s="10"/>
+      <c r="B711" s="10"/>
+    </row>
+    <row r="712" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A712" s="10"/>
+      <c r="B712" s="10"/>
+    </row>
+    <row r="713" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A713" s="10"/>
+      <c r="B713" s="10"/>
+    </row>
+    <row r="714" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A714" s="10"/>
+      <c r="B714" s="10"/>
+    </row>
+    <row r="715" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A715" s="10"/>
+      <c r="B715" s="10"/>
+    </row>
+    <row r="716" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A716" s="10"/>
+      <c r="B716" s="10"/>
+    </row>
+    <row r="717" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A717" s="10"/>
+      <c r="B717" s="10"/>
+    </row>
+    <row r="718" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A718" s="10"/>
+      <c r="B718" s="10"/>
+    </row>
+    <row r="719" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A719" s="10"/>
+      <c r="B719" s="10"/>
+    </row>
+    <row r="720" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A720" s="10"/>
+      <c r="B720" s="10"/>
+    </row>
+    <row r="721" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A721" s="10"/>
+      <c r="B721" s="10"/>
+    </row>
+    <row r="722" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A722" s="10"/>
+      <c r="B722" s="10"/>
+    </row>
+    <row r="723" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A723" s="10"/>
+      <c r="B723" s="10"/>
+    </row>
+    <row r="724" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A724" s="10"/>
+      <c r="B724" s="10"/>
+    </row>
+    <row r="725" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A725" s="10"/>
+      <c r="B725" s="10"/>
+    </row>
+    <row r="726" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A726" s="10"/>
+      <c r="B726" s="10"/>
+    </row>
+    <row r="727" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A727" s="10"/>
+      <c r="B727" s="10"/>
+    </row>
+    <row r="728" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A728" s="10"/>
+      <c r="B728" s="10"/>
+    </row>
+    <row r="729" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A729" s="10"/>
+      <c r="B729" s="10"/>
+    </row>
+    <row r="730" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A730" s="10"/>
+      <c r="B730" s="10"/>
+    </row>
+    <row r="731" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A731" s="10"/>
+      <c r="B731" s="10"/>
+    </row>
+    <row r="732" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A732" s="10"/>
+      <c r="B732" s="10"/>
+    </row>
+    <row r="733" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A733" s="10"/>
+      <c r="B733" s="10"/>
+    </row>
+    <row r="734" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A734" s="10"/>
+      <c r="B734" s="10"/>
+    </row>
+    <row r="735" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A735" s="10"/>
+      <c r="B735" s="10"/>
+    </row>
+    <row r="736" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A736" s="10"/>
+      <c r="B736" s="10"/>
+    </row>
+    <row r="737" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A737" s="10"/>
+      <c r="B737" s="10"/>
+    </row>
+    <row r="738" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A738" s="10"/>
+      <c r="B738" s="10"/>
+    </row>
+    <row r="739" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A739" s="10"/>
+      <c r="B739" s="10"/>
+    </row>
+    <row r="740" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A740" s="10"/>
+      <c r="B740" s="10"/>
+    </row>
+    <row r="741" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A741" s="10"/>
+      <c r="B741" s="10"/>
+    </row>
+    <row r="742" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A742" s="10"/>
+      <c r="B742" s="10"/>
+    </row>
+    <row r="743" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A743" s="10"/>
+      <c r="B743" s="10"/>
+    </row>
+    <row r="744" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A744" s="10"/>
+      <c r="B744" s="10"/>
+    </row>
+    <row r="745" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A745" s="10"/>
+      <c r="B745" s="10"/>
+    </row>
+    <row r="746" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A746" s="10"/>
+      <c r="B746" s="10"/>
+    </row>
+    <row r="747" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A747" s="10"/>
+      <c r="B747" s="10"/>
+    </row>
+    <row r="748" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A748" s="10"/>
+      <c r="B748" s="10"/>
+    </row>
+    <row r="749" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A749" s="10"/>
+      <c r="B749" s="10"/>
+    </row>
+    <row r="750" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A750" s="10"/>
+      <c r="B750" s="10"/>
+    </row>
+    <row r="751" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A751" s="10"/>
+      <c r="B751" s="10"/>
+    </row>
+    <row r="752" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A752" s="10"/>
+      <c r="B752" s="10"/>
+    </row>
+    <row r="753" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A753" s="10"/>
+      <c r="B753" s="10"/>
+    </row>
+    <row r="754" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A754" s="10"/>
+      <c r="B754" s="10"/>
+    </row>
+    <row r="755" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A755" s="10"/>
+      <c r="B755" s="10"/>
+    </row>
+    <row r="756" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A756" s="10"/>
+      <c r="B756" s="10"/>
+    </row>
+    <row r="757" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A757" s="10"/>
+      <c r="B757" s="10"/>
+    </row>
+    <row r="758" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A758" s="10"/>
+      <c r="B758" s="10"/>
+    </row>
+    <row r="759" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A759" s="10"/>
+      <c r="B759" s="10"/>
+    </row>
+    <row r="760" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A760" s="10"/>
+      <c r="B760" s="10"/>
+    </row>
+    <row r="761" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A761" s="10"/>
+      <c r="B761" s="10"/>
+    </row>
+    <row r="762" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A762" s="10"/>
+      <c r="B762" s="10"/>
+    </row>
+    <row r="763" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A763" s="10"/>
+      <c r="B763" s="10"/>
+    </row>
+    <row r="764" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A764" s="10"/>
+      <c r="B764" s="10"/>
+    </row>
+    <row r="765" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A765" s="10"/>
+      <c r="B765" s="10"/>
+    </row>
+    <row r="766" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A766" s="10"/>
+      <c r="B766" s="10"/>
+    </row>
+    <row r="767" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A767" s="10"/>
+      <c r="B767" s="10"/>
+    </row>
+    <row r="768" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A768" s="10"/>
+      <c r="B768" s="10"/>
+    </row>
+    <row r="769" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A769" s="10"/>
+      <c r="B769" s="10"/>
+    </row>
+    <row r="770" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A770" s="10"/>
+      <c r="B770" s="10"/>
+    </row>
+    <row r="771" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A771" s="10"/>
+      <c r="B771" s="10"/>
+    </row>
+    <row r="772" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A772" s="10"/>
+      <c r="B772" s="10"/>
+    </row>
+    <row r="773" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A773" s="10"/>
+      <c r="B773" s="10"/>
+    </row>
+    <row r="774" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A774" s="10"/>
+      <c r="B774" s="10"/>
+    </row>
+    <row r="775" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A775" s="10"/>
+      <c r="B775" s="10"/>
+    </row>
+    <row r="776" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A776" s="10"/>
+      <c r="B776" s="10"/>
+    </row>
+    <row r="777" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A777" s="10"/>
+      <c r="B777" s="10"/>
+    </row>
+    <row r="778" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A778" s="10"/>
+      <c r="B778" s="10"/>
+    </row>
+    <row r="779" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A779" s="10"/>
+      <c r="B779" s="10"/>
+    </row>
+    <row r="780" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A780" s="10"/>
+      <c r="B780" s="10"/>
+    </row>
+    <row r="781" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A781" s="10"/>
+      <c r="B781" s="10"/>
+    </row>
+    <row r="782" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A782" s="10"/>
+      <c r="B782" s="10"/>
+    </row>
+    <row r="783" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A783" s="10"/>
+      <c r="B783" s="10"/>
+    </row>
+    <row r="784" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A784" s="10"/>
+      <c r="B784" s="10"/>
+    </row>
+    <row r="785" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A785" s="10"/>
+      <c r="B785" s="10"/>
+    </row>
+    <row r="786" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A786" s="10"/>
+      <c r="B786" s="10"/>
+    </row>
+    <row r="787" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A787" s="10"/>
+      <c r="B787" s="10"/>
+    </row>
+    <row r="788" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A788" s="10"/>
+      <c r="B788" s="10"/>
+    </row>
+    <row r="789" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A789" s="10"/>
+      <c r="B789" s="10"/>
+    </row>
+    <row r="790" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A790" s="10"/>
+      <c r="B790" s="10"/>
+    </row>
+    <row r="791" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A791" s="10"/>
+      <c r="B791" s="10"/>
+    </row>
+    <row r="792" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A792" s="10"/>
+      <c r="B792" s="10"/>
+    </row>
+    <row r="793" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A793" s="10"/>
+      <c r="B793" s="10"/>
+    </row>
+    <row r="794" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A794" s="10"/>
+      <c r="B794" s="10"/>
+    </row>
+    <row r="795" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A795" s="10"/>
+      <c r="B795" s="10"/>
+    </row>
+    <row r="796" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A796" s="10"/>
+      <c r="B796" s="10"/>
+    </row>
+    <row r="797" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A797" s="10"/>
+      <c r="B797" s="10"/>
+    </row>
+    <row r="798" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A798" s="10"/>
+      <c r="B798" s="10"/>
+    </row>
+    <row r="799" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A799" s="10"/>
+      <c r="B799" s="10"/>
+    </row>
+    <row r="800" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A800" s="10"/>
+      <c r="B800" s="10"/>
+    </row>
+    <row r="801" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A801" s="10"/>
+      <c r="B801" s="10"/>
+    </row>
+    <row r="802" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A802" s="10"/>
+      <c r="B802" s="10"/>
+    </row>
+    <row r="803" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A803" s="10"/>
+      <c r="B803" s="10"/>
+    </row>
+    <row r="804" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A804" s="10"/>
+      <c r="B804" s="10"/>
+    </row>
+    <row r="805" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A805" s="10"/>
+      <c r="B805" s="10"/>
+    </row>
+    <row r="806" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A806" s="10"/>
+      <c r="B806" s="10"/>
+    </row>
+    <row r="807" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A807" s="10"/>
+      <c r="B807" s="10"/>
+    </row>
+    <row r="808" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A808" s="10"/>
+      <c r="B808" s="10"/>
+    </row>
+    <row r="809" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A809" s="10"/>
+      <c r="B809" s="10"/>
+    </row>
+    <row r="810" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A810" s="10"/>
+      <c r="B810" s="10"/>
+    </row>
+    <row r="811" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A811" s="10"/>
+      <c r="B811" s="10"/>
+    </row>
+    <row r="812" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A812" s="10"/>
+      <c r="B812" s="10"/>
+    </row>
+    <row r="813" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A813" s="10"/>
+      <c r="B813" s="10"/>
+    </row>
+    <row r="814" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A814" s="10"/>
+      <c r="B814" s="10"/>
+    </row>
+    <row r="815" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A815" s="10"/>
+      <c r="B815" s="10"/>
+    </row>
+    <row r="816" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A816" s="10"/>
+      <c r="B816" s="10"/>
+    </row>
+    <row r="817" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A817" s="10"/>
+      <c r="B817" s="10"/>
+    </row>
+    <row r="818" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A818" s="10"/>
+      <c r="B818" s="10"/>
+    </row>
+    <row r="819" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A819" s="10"/>
+      <c r="B819" s="10"/>
+    </row>
+    <row r="820" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A820" s="10"/>
+      <c r="B820" s="10"/>
+    </row>
+    <row r="821" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A821" s="10"/>
+      <c r="B821" s="10"/>
+    </row>
+    <row r="822" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A822" s="10"/>
+      <c r="B822" s="10"/>
+    </row>
+    <row r="823" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A823" s="10"/>
+      <c r="B823" s="10"/>
+    </row>
+    <row r="824" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A824" s="10"/>
+      <c r="B824" s="10"/>
+    </row>
+    <row r="825" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A825" s="10"/>
+      <c r="B825" s="10"/>
+    </row>
+    <row r="826" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A826" s="10"/>
+      <c r="B826" s="10"/>
+    </row>
+    <row r="827" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A827" s="10"/>
+      <c r="B827" s="10"/>
+    </row>
+    <row r="828" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A828" s="10"/>
+      <c r="B828" s="10"/>
+    </row>
+    <row r="829" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A829" s="10"/>
+      <c r="B829" s="10"/>
+    </row>
+    <row r="830" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A830" s="10"/>
+      <c r="B830" s="10"/>
+    </row>
+    <row r="831" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A831" s="10"/>
+      <c r="B831" s="10"/>
+    </row>
+    <row r="832" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A832" s="10"/>
+      <c r="B832" s="10"/>
+    </row>
+    <row r="833" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A833" s="10"/>
+      <c r="B833" s="10"/>
+    </row>
+    <row r="834" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A834" s="10"/>
+      <c r="B834" s="10"/>
+    </row>
+    <row r="835" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A835" s="10"/>
+      <c r="B835" s="10"/>
+    </row>
+    <row r="836" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A836" s="10"/>
+      <c r="B836" s="10"/>
+    </row>
+    <row r="837" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A837" s="10"/>
+      <c r="B837" s="10"/>
+    </row>
+    <row r="838" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A838" s="10"/>
+      <c r="B838" s="10"/>
+    </row>
+    <row r="839" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A839" s="10"/>
+      <c r="B839" s="10"/>
+    </row>
+    <row r="840" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A840" s="10"/>
+      <c r="B840" s="10"/>
+    </row>
+    <row r="841" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A841" s="10"/>
+      <c r="B841" s="10"/>
+    </row>
+    <row r="842" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A842" s="10"/>
+      <c r="B842" s="10"/>
+    </row>
+    <row r="843" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A843" s="10"/>
+      <c r="B843" s="10"/>
+    </row>
+    <row r="844" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A844" s="10"/>
+      <c r="B844" s="10"/>
+    </row>
+    <row r="845" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A845" s="10"/>
+      <c r="B845" s="10"/>
+    </row>
+    <row r="846" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A846" s="10"/>
+      <c r="B846" s="10"/>
+    </row>
+    <row r="847" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A847" s="10"/>
+      <c r="B847" s="10"/>
+    </row>
+    <row r="848" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A848" s="10"/>
+      <c r="B848" s="10"/>
+    </row>
+    <row r="849" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A849" s="10"/>
+      <c r="B849" s="10"/>
+    </row>
+    <row r="850" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A850" s="10"/>
+      <c r="B850" s="10"/>
+    </row>
+    <row r="851" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A851" s="10"/>
+      <c r="B851" s="10"/>
+    </row>
+    <row r="852" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A852" s="10"/>
+      <c r="B852" s="10"/>
+    </row>
+    <row r="853" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A853" s="10"/>
+      <c r="B853" s="10"/>
+    </row>
+    <row r="854" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A854" s="10"/>
+      <c r="B854" s="10"/>
+    </row>
+    <row r="855" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A855" s="10"/>
+      <c r="B855" s="10"/>
+    </row>
+    <row r="856" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A856" s="10"/>
+      <c r="B856" s="10"/>
+    </row>
+    <row r="857" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A857" s="10"/>
+      <c r="B857" s="10"/>
+    </row>
+    <row r="858" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A858" s="10"/>
+      <c r="B858" s="10"/>
+    </row>
+    <row r="859" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A859" s="10"/>
+      <c r="B859" s="10"/>
+    </row>
+    <row r="860" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A860" s="10"/>
+      <c r="B860" s="10"/>
+    </row>
+    <row r="861" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A861" s="10"/>
+      <c r="B861" s="10"/>
+    </row>
+    <row r="862" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A862" s="10"/>
+      <c r="B862" s="10"/>
+    </row>
+    <row r="863" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A863" s="10"/>
+      <c r="B863" s="10"/>
+    </row>
+    <row r="864" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A864" s="10"/>
+      <c r="B864" s="10"/>
+    </row>
+    <row r="865" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A865" s="10"/>
+      <c r="B865" s="10"/>
+    </row>
+    <row r="866" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A866" s="10"/>
+      <c r="B866" s="10"/>
+    </row>
+    <row r="867" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A867" s="10"/>
+      <c r="B867" s="10"/>
+    </row>
+    <row r="868" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A868" s="10"/>
+      <c r="B868" s="10"/>
+    </row>
+    <row r="869" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A869" s="10"/>
+      <c r="B869" s="10"/>
+    </row>
+    <row r="870" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A870" s="10"/>
+      <c r="B870" s="10"/>
+    </row>
+    <row r="871" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A871" s="10"/>
+      <c r="B871" s="10"/>
+    </row>
+    <row r="872" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A872" s="10"/>
+      <c r="B872" s="10"/>
+    </row>
+    <row r="873" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A873" s="10"/>
+      <c r="B873" s="10"/>
+    </row>
+    <row r="874" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A874" s="10"/>
+      <c r="B874" s="10"/>
+    </row>
+    <row r="875" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A875" s="10"/>
+      <c r="B875" s="10"/>
+    </row>
+    <row r="876" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A876" s="10"/>
+      <c r="B876" s="10"/>
+    </row>
+    <row r="877" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A877" s="10"/>
+      <c r="B877" s="10"/>
+    </row>
+    <row r="878" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A878" s="10"/>
+      <c r="B878" s="10"/>
+    </row>
+    <row r="879" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A879" s="10"/>
+      <c r="B879" s="10"/>
+    </row>
+    <row r="880" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A880" s="10"/>
+      <c r="B880" s="10"/>
+    </row>
+    <row r="881" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A881" s="10"/>
+      <c r="B881" s="10"/>
+    </row>
+    <row r="882" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A882" s="10"/>
+      <c r="B882" s="10"/>
+    </row>
+    <row r="883" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A883" s="10"/>
+      <c r="B883" s="10"/>
+    </row>
+    <row r="884" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A884" s="10"/>
+      <c r="B884" s="10"/>
+    </row>
+    <row r="885" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A885" s="10"/>
+      <c r="B885" s="10"/>
+    </row>
+    <row r="886" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A886" s="10"/>
+      <c r="B886" s="10"/>
+    </row>
+    <row r="887" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A887" s="10"/>
+      <c r="B887" s="10"/>
+    </row>
+    <row r="888" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A888" s="10"/>
+      <c r="B888" s="10"/>
+    </row>
+    <row r="889" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A889" s="10"/>
+      <c r="B889" s="10"/>
+    </row>
+    <row r="890" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A890" s="10"/>
+      <c r="B890" s="10"/>
+    </row>
+    <row r="891" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A891" s="10"/>
+      <c r="B891" s="10"/>
+    </row>
+    <row r="892" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A892" s="10"/>
+      <c r="B892" s="10"/>
+    </row>
+    <row r="893" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A893" s="10"/>
+      <c r="B893" s="10"/>
+    </row>
+    <row r="894" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A894" s="10"/>
+      <c r="B894" s="10"/>
+    </row>
+    <row r="895" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A895" s="10"/>
+      <c r="B895" s="10"/>
+    </row>
+    <row r="896" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A896" s="10"/>
+      <c r="B896" s="10"/>
+    </row>
+    <row r="897" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A897" s="10"/>
+      <c r="B897" s="10"/>
+    </row>
+    <row r="898" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A898" s="10"/>
+      <c r="B898" s="10"/>
+    </row>
+    <row r="899" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A899" s="10"/>
+      <c r="B899" s="10"/>
+    </row>
+    <row r="900" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A900" s="10"/>
+      <c r="B900" s="10"/>
+    </row>
+    <row r="901" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A901" s="10"/>
+      <c r="B901" s="10"/>
+    </row>
+    <row r="902" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A902" s="10"/>
+      <c r="B902" s="10"/>
+    </row>
+    <row r="903" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A903" s="10"/>
+      <c r="B903" s="10"/>
+    </row>
+    <row r="904" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A904" s="10"/>
+      <c r="B904" s="10"/>
+    </row>
+    <row r="905" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A905" s="10"/>
+      <c r="B905" s="10"/>
+    </row>
+    <row r="906" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A906" s="10"/>
+      <c r="B906" s="10"/>
+    </row>
+    <row r="907" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A907" s="10"/>
+      <c r="B907" s="10"/>
+    </row>
+    <row r="908" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A908" s="10"/>
+      <c r="B908" s="10"/>
+    </row>
+    <row r="909" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A909" s="10"/>
+      <c r="B909" s="10"/>
+    </row>
+    <row r="910" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A910" s="10"/>
+      <c r="B910" s="10"/>
+    </row>
+    <row r="911" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A911" s="10"/>
+      <c r="B911" s="10"/>
+    </row>
+    <row r="912" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A912" s="10"/>
+      <c r="B912" s="10"/>
+    </row>
+    <row r="913" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A913" s="10"/>
+      <c r="B913" s="10"/>
+    </row>
+    <row r="914" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A914" s="10"/>
+      <c r="B914" s="10"/>
+    </row>
+    <row r="915" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A915" s="10"/>
+      <c r="B915" s="10"/>
+    </row>
+    <row r="916" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A916" s="10"/>
+      <c r="B916" s="10"/>
+    </row>
+    <row r="917" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A917" s="10"/>
+      <c r="B917" s="10"/>
+    </row>
+    <row r="918" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A918" s="10"/>
+      <c r="B918" s="10"/>
+    </row>
+    <row r="919" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A919" s="10"/>
+      <c r="B919" s="10"/>
+    </row>
+    <row r="920" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A920" s="10"/>
+      <c r="B920" s="10"/>
+    </row>
+    <row r="921" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A921" s="10"/>
+      <c r="B921" s="10"/>
+    </row>
+    <row r="922" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A922" s="10"/>
+      <c r="B922" s="10"/>
+    </row>
+    <row r="923" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A923" s="10"/>
+      <c r="B923" s="10"/>
+    </row>
+    <row r="924" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A924" s="10"/>
+      <c r="B924" s="10"/>
+    </row>
+    <row r="925" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A925" s="10"/>
+      <c r="B925" s="10"/>
+    </row>
+    <row r="926" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A926" s="10"/>
+      <c r="B926" s="10"/>
+    </row>
+    <row r="927" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A927" s="10"/>
+      <c r="B927" s="10"/>
+    </row>
+    <row r="928" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A928" s="10"/>
+      <c r="B928" s="10"/>
+    </row>
+    <row r="929" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A929" s="10"/>
+      <c r="B929" s="10"/>
+    </row>
+    <row r="930" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A930" s="10"/>
+      <c r="B930" s="10"/>
+    </row>
+    <row r="931" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A931" s="10"/>
+      <c r="B931" s="10"/>
+    </row>
+    <row r="932" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A932" s="10"/>
+      <c r="B932" s="10"/>
+    </row>
+    <row r="933" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A933" s="10"/>
+      <c r="B933" s="10"/>
+    </row>
+    <row r="934" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A934" s="10"/>
+      <c r="B934" s="10"/>
+    </row>
+    <row r="935" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A935" s="10"/>
+      <c r="B935" s="10"/>
+    </row>
+    <row r="936" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A936" s="10"/>
+      <c r="B936" s="10"/>
+    </row>
+    <row r="937" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A937" s="10"/>
+      <c r="B937" s="10"/>
+    </row>
+    <row r="938" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A938" s="10"/>
+      <c r="B938" s="10"/>
+    </row>
+    <row r="939" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A939" s="10"/>
+      <c r="B939" s="10"/>
+    </row>
+    <row r="940" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A940" s="10"/>
+      <c r="B940" s="10"/>
+    </row>
+    <row r="941" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A941" s="10"/>
+      <c r="B941" s="10"/>
+    </row>
+    <row r="942" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A942" s="10"/>
+      <c r="B942" s="10"/>
+    </row>
+    <row r="943" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A943" s="10"/>
+      <c r="B943" s="10"/>
+    </row>
+    <row r="944" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A944" s="10"/>
+      <c r="B944" s="10"/>
+    </row>
+    <row r="945" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A945" s="10"/>
+      <c r="B945" s="10"/>
+    </row>
+    <row r="946" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A946" s="10"/>
+      <c r="B946" s="10"/>
+    </row>
+    <row r="947" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A947" s="10"/>
+      <c r="B947" s="10"/>
+    </row>
+    <row r="948" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A948" s="10"/>
+      <c r="B948" s="10"/>
+    </row>
+    <row r="949" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A949" s="10"/>
+      <c r="B949" s="10"/>
+    </row>
+    <row r="950" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A950" s="10"/>
+      <c r="B950" s="10"/>
+    </row>
+    <row r="951" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A951" s="10"/>
+      <c r="B951" s="10"/>
+    </row>
+    <row r="952" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A952" s="10"/>
+      <c r="B952" s="10"/>
+    </row>
+    <row r="953" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A953" s="10"/>
+      <c r="B953" s="10"/>
+    </row>
+    <row r="954" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A954" s="10"/>
+      <c r="B954" s="10"/>
+    </row>
+    <row r="955" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A955" s="10"/>
+      <c r="B955" s="10"/>
+    </row>
+    <row r="956" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A956" s="10"/>
+      <c r="B956" s="10"/>
+    </row>
+    <row r="957" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A957" s="10"/>
+      <c r="B957" s="10"/>
+    </row>
+    <row r="958" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A958" s="10"/>
+      <c r="B958" s="10"/>
+    </row>
+    <row r="959" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A959" s="10"/>
+      <c r="B959" s="10"/>
+    </row>
+    <row r="960" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A960" s="10"/>
+      <c r="B960" s="10"/>
+    </row>
+    <row r="961" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A961" s="10"/>
+      <c r="B961" s="10"/>
+    </row>
+    <row r="962" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A962" s="10"/>
+      <c r="B962" s="10"/>
+    </row>
+    <row r="963" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A963" s="10"/>
+      <c r="B963" s="10"/>
+    </row>
+    <row r="964" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A964" s="10"/>
+      <c r="B964" s="10"/>
+    </row>
+    <row r="965" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A965" s="10"/>
+      <c r="B965" s="10"/>
+    </row>
+    <row r="966" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A966" s="10"/>
+      <c r="B966" s="10"/>
+    </row>
+    <row r="967" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A967" s="10"/>
+      <c r="B967" s="10"/>
+    </row>
+    <row r="968" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A968" s="10"/>
+      <c r="B968" s="10"/>
+    </row>
+    <row r="969" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A969" s="10"/>
+      <c r="B969" s="10"/>
+    </row>
+    <row r="970" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A970" s="10"/>
+      <c r="B970" s="10"/>
+    </row>
+    <row r="971" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A971" s="10"/>
+      <c r="B971" s="10"/>
+    </row>
+    <row r="972" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A972" s="10"/>
+      <c r="B972" s="10"/>
+    </row>
+    <row r="973" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A973" s="10"/>
+      <c r="B973" s="10"/>
+    </row>
+    <row r="974" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A974" s="10"/>
+      <c r="B974" s="10"/>
+    </row>
+    <row r="975" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A975" s="10"/>
+      <c r="B975" s="10"/>
+    </row>
+    <row r="976" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A976" s="10"/>
+      <c r="B976" s="10"/>
+    </row>
+    <row r="977" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A977" s="10"/>
+      <c r="B977" s="10"/>
+    </row>
+    <row r="978" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A978" s="10"/>
+      <c r="B978" s="10"/>
+    </row>
+    <row r="979" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A979" s="10"/>
+      <c r="B979" s="10"/>
+    </row>
+    <row r="980" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A980" s="10"/>
+      <c r="B980" s="10"/>
+    </row>
+    <row r="981" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A981" s="10"/>
+      <c r="B981" s="10"/>
+    </row>
+    <row r="982" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A982" s="10"/>
+      <c r="B982" s="10"/>
+    </row>
+    <row r="983" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A983" s="10"/>
+      <c r="B983" s="10"/>
+    </row>
+    <row r="984" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A984" s="10"/>
+      <c r="B984" s="10"/>
+    </row>
+    <row r="985" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A985" s="10"/>
+      <c r="B985" s="10"/>
+    </row>
+    <row r="986" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A986" s="10"/>
+      <c r="B986" s="10"/>
+    </row>
+    <row r="987" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A987" s="10"/>
+      <c r="B987" s="10"/>
+    </row>
+    <row r="988" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A988" s="10"/>
+      <c r="B988" s="10"/>
+    </row>
+    <row r="989" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A989" s="10"/>
+      <c r="B989" s="10"/>
+    </row>
+    <row r="990" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A990" s="10"/>
+      <c r="B990" s="10"/>
+    </row>
+    <row r="991" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A991" s="10"/>
+      <c r="B991" s="10"/>
+    </row>
+    <row r="992" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A992" s="10"/>
+      <c r="B992" s="10"/>
+    </row>
+    <row r="993" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A993" s="10"/>
+      <c r="B993" s="10"/>
+    </row>
+    <row r="994" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A994" s="10"/>
+      <c r="B994" s="10"/>
+    </row>
+    <row r="995" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A995" s="10"/>
+      <c r="B995" s="10"/>
+    </row>
+    <row r="996" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A996" s="10"/>
+      <c r="B996" s="10"/>
+    </row>
+    <row r="997" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A997" s="10"/>
+      <c r="B997" s="10"/>
+    </row>
+    <row r="998" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A998" s="10"/>
+      <c r="B998" s="10"/>
+    </row>
+    <row r="999" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A999" s="10"/>
+      <c r="B999" s="10"/>
+    </row>
+    <row r="1000" ht="15.75" customHeight="1" spans="1:2">
+      <c r="A1000" s="10"/>
+      <c r="B1000" s="10"/>
     </row>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.699999988079071" right="0.699999988079071" top="0.75"/>
+  <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="15636" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -271,10 +271,10 @@
     <t>Painting</t>
   </si>
   <si>
-    <t>Painting_1,PaintingFrame_White,PaintingFrame_WoodHell</t>
+    <t>PaintingFrame_WoodHell,PaintingFrame_White,Painting_1</t>
   </si>
   <si>
-    <t>Painting_1[Painting_1]</t>
+    <t>Painting_1_Mesh[Painting_1]</t>
   </si>
   <si>
     <t>PaintingObject</t>
@@ -283,37 +283,37 @@
     <t>Item_Painting_02</t>
   </si>
   <si>
-    <t>Painting_6,PaintingFrame_White</t>
+    <t>PaintingFrame_White,Painting_6</t>
   </si>
   <si>
-    <t>Painting_2[Painting_2]</t>
+    <t>Painting_2_Mesh[Painting_2]</t>
   </si>
   <si>
     <t>Item_Painting_03</t>
   </si>
   <si>
-    <t>Painting_8,PaintingFrame_Gold,PaintingFrame_Black</t>
+    <t>PaintingFrame_Black,PaintingFrame_Gold,Painting_8</t>
   </si>
   <si>
-    <t>Painting_3[Painting_8]</t>
+    <t>Painting_3_Mesh[Painting_8]</t>
   </si>
   <si>
     <t>Item_Painting_04</t>
   </si>
   <si>
-    <t>Painting_3,PaintingFrame_White</t>
+    <t>PaintingFrame_White,Painting_3</t>
   </si>
   <si>
-    <t>Painting_4[Painting_4]</t>
+    <t>Painting_4_Mesh[Painting_4]</t>
   </si>
   <si>
     <t>Item_Painting_05</t>
   </si>
   <si>
-    <t>Painting_2,PaintingFrame_WoodHell</t>
+    <t>PaintingFrame_WoodHell,Painting_2</t>
   </si>
   <si>
-    <t>Painting_5[Painting_5]</t>
+    <t>Painting_5_Mesh[Painting_5]</t>
   </si>
 </sst>
 </file>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15636" windowHeight="8400"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="114">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -314,6 +314,326 @@
   </si>
   <si>
     <t>Painting_5_Mesh[Painting_5]</t>
+  </si>
+  <si>
+    <t>Item_Statue_Stone</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>돌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>투박한</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>돌로</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>만든</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상이다.</t>
+    </r>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>Statue_Stone</t>
+  </si>
+  <si>
+    <t>SeatedLion[Seated_Lion_LOD0]</t>
+  </si>
+  <si>
+    <t>StatueObject</t>
+  </si>
+  <si>
+    <t>Item_Statue_Copper</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>구리</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상</t>
+    </r>
+  </si>
+  <si>
+    <t>특이한 색의 조각상이다.</t>
+  </si>
+  <si>
+    <t>Statue_Copper</t>
+  </si>
+  <si>
+    <t>Item_Statue_Metal</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>금속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>광택이</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>나는</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>금속</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상이다.</t>
+    </r>
+  </si>
+  <si>
+    <t>Statue_Metal</t>
+  </si>
+  <si>
+    <t>Item_Statue_Marble</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>대리석</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>아름다운</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="바탕체"/>
+        <charset val="134"/>
+      </rPr>
+      <t>조각상이다</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Statue_Marble</t>
   </si>
 </sst>
 </file>
@@ -326,7 +646,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -370,6 +690,12 @@
       <name val="Arial"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="바탕체"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -853,31 +1179,28 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -886,119 +1209,122 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1013,6 +1339,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
@@ -2070,7 +2397,7 @@
         <v>43</v>
       </c>
       <c r="F13" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G13" s="4">
         <v>1200</v>
@@ -2115,7 +2442,7 @@
         <v>43</v>
       </c>
       <c r="F14" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G14" s="4">
         <v>1200</v>
@@ -2160,7 +2487,7 @@
         <v>43</v>
       </c>
       <c r="F15" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G15" s="4">
         <v>1200</v>
@@ -2205,7 +2532,7 @@
         <v>43</v>
       </c>
       <c r="F16" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G16" s="4">
         <v>1200</v>
@@ -2250,7 +2577,7 @@
         <v>43</v>
       </c>
       <c r="F17" s="4">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="G17" s="4">
         <v>1200</v>
@@ -2279,19 +2606,41 @@
       <c r="U17" s="4"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
+      <c r="A18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>800</v>
+      </c>
       <c r="H18" s="4"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="J18" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M18" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -2302,19 +2651,41 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
+      <c r="A19" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="4">
+        <v>10</v>
+      </c>
+      <c r="G19" s="4">
+        <v>1600</v>
+      </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
+      <c r="J19" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M19" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
@@ -2325,19 +2696,41 @@
       <c r="U19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
+      <c r="A20" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="4">
+        <v>15</v>
+      </c>
+      <c r="G20" s="4">
+        <v>3000</v>
+      </c>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
+      <c r="J20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M20" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
@@ -2348,19 +2741,41 @@
       <c r="U20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
+      <c r="A21" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="4">
+        <v>20</v>
+      </c>
+      <c r="G21" s="4">
+        <v>5000</v>
+      </c>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
+      <c r="J21" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
@@ -6948,3124 +7363,3124 @@
       <c r="U220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A221" s="10"/>
-      <c r="B221" s="10"/>
+      <c r="A221" s="11"/>
+      <c r="B221" s="11"/>
     </row>
     <row r="222" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A222" s="10"/>
-      <c r="B222" s="10"/>
+      <c r="A222" s="11"/>
+      <c r="B222" s="11"/>
     </row>
     <row r="223" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A223" s="10"/>
-      <c r="B223" s="10"/>
+      <c r="A223" s="11"/>
+      <c r="B223" s="11"/>
     </row>
     <row r="224" ht="15.75" customHeight="1" spans="1:21">
-      <c r="A224" s="10"/>
-      <c r="B224" s="10"/>
+      <c r="A224" s="11"/>
+      <c r="B224" s="11"/>
     </row>
     <row r="225" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A225" s="10"/>
-      <c r="B225" s="10"/>
+      <c r="A225" s="11"/>
+      <c r="B225" s="11"/>
     </row>
     <row r="226" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A226" s="10"/>
-      <c r="B226" s="10"/>
+      <c r="A226" s="11"/>
+      <c r="B226" s="11"/>
     </row>
     <row r="227" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A227" s="10"/>
-      <c r="B227" s="10"/>
+      <c r="A227" s="11"/>
+      <c r="B227" s="11"/>
     </row>
     <row r="228" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A228" s="10"/>
-      <c r="B228" s="10"/>
+      <c r="A228" s="11"/>
+      <c r="B228" s="11"/>
     </row>
     <row r="229" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A229" s="10"/>
-      <c r="B229" s="10"/>
+      <c r="A229" s="11"/>
+      <c r="B229" s="11"/>
     </row>
     <row r="230" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A230" s="10"/>
-      <c r="B230" s="10"/>
+      <c r="A230" s="11"/>
+      <c r="B230" s="11"/>
     </row>
     <row r="231" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A231" s="10"/>
-      <c r="B231" s="10"/>
+      <c r="A231" s="11"/>
+      <c r="B231" s="11"/>
     </row>
     <row r="232" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A232" s="10"/>
-      <c r="B232" s="10"/>
+      <c r="A232" s="11"/>
+      <c r="B232" s="11"/>
     </row>
     <row r="233" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A233" s="10"/>
-      <c r="B233" s="10"/>
+      <c r="A233" s="11"/>
+      <c r="B233" s="11"/>
     </row>
     <row r="234" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A234" s="10"/>
-      <c r="B234" s="10"/>
+      <c r="A234" s="11"/>
+      <c r="B234" s="11"/>
     </row>
     <row r="235" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A235" s="10"/>
-      <c r="B235" s="10"/>
+      <c r="A235" s="11"/>
+      <c r="B235" s="11"/>
     </row>
     <row r="236" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A236" s="10"/>
-      <c r="B236" s="10"/>
+      <c r="A236" s="11"/>
+      <c r="B236" s="11"/>
     </row>
     <row r="237" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A237" s="10"/>
-      <c r="B237" s="10"/>
+      <c r="A237" s="11"/>
+      <c r="B237" s="11"/>
     </row>
     <row r="238" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A238" s="10"/>
-      <c r="B238" s="10"/>
+      <c r="A238" s="11"/>
+      <c r="B238" s="11"/>
     </row>
     <row r="239" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A239" s="10"/>
-      <c r="B239" s="10"/>
+      <c r="A239" s="11"/>
+      <c r="B239" s="11"/>
     </row>
     <row r="240" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A240" s="10"/>
-      <c r="B240" s="10"/>
+      <c r="A240" s="11"/>
+      <c r="B240" s="11"/>
     </row>
     <row r="241" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A241" s="10"/>
-      <c r="B241" s="10"/>
+      <c r="A241" s="11"/>
+      <c r="B241" s="11"/>
     </row>
     <row r="242" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A242" s="10"/>
-      <c r="B242" s="10"/>
+      <c r="A242" s="11"/>
+      <c r="B242" s="11"/>
     </row>
     <row r="243" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A243" s="10"/>
-      <c r="B243" s="10"/>
+      <c r="A243" s="11"/>
+      <c r="B243" s="11"/>
     </row>
     <row r="244" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A244" s="10"/>
-      <c r="B244" s="10"/>
+      <c r="A244" s="11"/>
+      <c r="B244" s="11"/>
     </row>
     <row r="245" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A245" s="10"/>
-      <c r="B245" s="10"/>
+      <c r="A245" s="11"/>
+      <c r="B245" s="11"/>
     </row>
     <row r="246" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A246" s="10"/>
-      <c r="B246" s="10"/>
+      <c r="A246" s="11"/>
+      <c r="B246" s="11"/>
     </row>
     <row r="247" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A247" s="10"/>
-      <c r="B247" s="10"/>
+      <c r="A247" s="11"/>
+      <c r="B247" s="11"/>
     </row>
     <row r="248" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A248" s="10"/>
-      <c r="B248" s="10"/>
+      <c r="A248" s="11"/>
+      <c r="B248" s="11"/>
     </row>
     <row r="249" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A249" s="10"/>
-      <c r="B249" s="10"/>
+      <c r="A249" s="11"/>
+      <c r="B249" s="11"/>
     </row>
     <row r="250" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A250" s="10"/>
-      <c r="B250" s="10"/>
+      <c r="A250" s="11"/>
+      <c r="B250" s="11"/>
     </row>
     <row r="251" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A251" s="10"/>
-      <c r="B251" s="10"/>
+      <c r="A251" s="11"/>
+      <c r="B251" s="11"/>
     </row>
     <row r="252" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A252" s="10"/>
-      <c r="B252" s="10"/>
+      <c r="A252" s="11"/>
+      <c r="B252" s="11"/>
     </row>
     <row r="253" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A253" s="10"/>
-      <c r="B253" s="10"/>
+      <c r="A253" s="11"/>
+      <c r="B253" s="11"/>
     </row>
     <row r="254" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A254" s="10"/>
-      <c r="B254" s="10"/>
+      <c r="A254" s="11"/>
+      <c r="B254" s="11"/>
     </row>
     <row r="255" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A255" s="10"/>
-      <c r="B255" s="10"/>
+      <c r="A255" s="11"/>
+      <c r="B255" s="11"/>
     </row>
     <row r="256" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A256" s="10"/>
-      <c r="B256" s="10"/>
+      <c r="A256" s="11"/>
+      <c r="B256" s="11"/>
     </row>
     <row r="257" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A257" s="10"/>
-      <c r="B257" s="10"/>
+      <c r="A257" s="11"/>
+      <c r="B257" s="11"/>
     </row>
     <row r="258" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A258" s="10"/>
-      <c r="B258" s="10"/>
+      <c r="A258" s="11"/>
+      <c r="B258" s="11"/>
     </row>
     <row r="259" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A259" s="10"/>
-      <c r="B259" s="10"/>
+      <c r="A259" s="11"/>
+      <c r="B259" s="11"/>
     </row>
     <row r="260" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A260" s="10"/>
-      <c r="B260" s="10"/>
+      <c r="A260" s="11"/>
+      <c r="B260" s="11"/>
     </row>
     <row r="261" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A261" s="10"/>
-      <c r="B261" s="10"/>
+      <c r="A261" s="11"/>
+      <c r="B261" s="11"/>
     </row>
     <row r="262" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A262" s="10"/>
-      <c r="B262" s="10"/>
+      <c r="A262" s="11"/>
+      <c r="B262" s="11"/>
     </row>
     <row r="263" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A263" s="10"/>
-      <c r="B263" s="10"/>
+      <c r="A263" s="11"/>
+      <c r="B263" s="11"/>
     </row>
     <row r="264" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A264" s="10"/>
-      <c r="B264" s="10"/>
+      <c r="A264" s="11"/>
+      <c r="B264" s="11"/>
     </row>
     <row r="265" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A265" s="10"/>
-      <c r="B265" s="10"/>
+      <c r="A265" s="11"/>
+      <c r="B265" s="11"/>
     </row>
     <row r="266" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A266" s="10"/>
-      <c r="B266" s="10"/>
+      <c r="A266" s="11"/>
+      <c r="B266" s="11"/>
     </row>
     <row r="267" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A267" s="10"/>
-      <c r="B267" s="10"/>
+      <c r="A267" s="11"/>
+      <c r="B267" s="11"/>
     </row>
     <row r="268" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A268" s="10"/>
-      <c r="B268" s="10"/>
+      <c r="A268" s="11"/>
+      <c r="B268" s="11"/>
     </row>
     <row r="269" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A269" s="10"/>
-      <c r="B269" s="10"/>
+      <c r="A269" s="11"/>
+      <c r="B269" s="11"/>
     </row>
     <row r="270" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A270" s="10"/>
-      <c r="B270" s="10"/>
+      <c r="A270" s="11"/>
+      <c r="B270" s="11"/>
     </row>
     <row r="271" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A271" s="10"/>
-      <c r="B271" s="10"/>
+      <c r="A271" s="11"/>
+      <c r="B271" s="11"/>
     </row>
     <row r="272" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A272" s="10"/>
-      <c r="B272" s="10"/>
+      <c r="A272" s="11"/>
+      <c r="B272" s="11"/>
     </row>
     <row r="273" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A273" s="10"/>
-      <c r="B273" s="10"/>
+      <c r="A273" s="11"/>
+      <c r="B273" s="11"/>
     </row>
     <row r="274" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A274" s="10"/>
-      <c r="B274" s="10"/>
+      <c r="A274" s="11"/>
+      <c r="B274" s="11"/>
     </row>
     <row r="275" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A275" s="10"/>
-      <c r="B275" s="10"/>
+      <c r="A275" s="11"/>
+      <c r="B275" s="11"/>
     </row>
     <row r="276" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A276" s="10"/>
-      <c r="B276" s="10"/>
+      <c r="A276" s="11"/>
+      <c r="B276" s="11"/>
     </row>
     <row r="277" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A277" s="10"/>
-      <c r="B277" s="10"/>
+      <c r="A277" s="11"/>
+      <c r="B277" s="11"/>
     </row>
     <row r="278" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A278" s="10"/>
-      <c r="B278" s="10"/>
+      <c r="A278" s="11"/>
+      <c r="B278" s="11"/>
     </row>
     <row r="279" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A279" s="10"/>
-      <c r="B279" s="10"/>
+      <c r="A279" s="11"/>
+      <c r="B279" s="11"/>
     </row>
     <row r="280" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A280" s="10"/>
-      <c r="B280" s="10"/>
+      <c r="A280" s="11"/>
+      <c r="B280" s="11"/>
     </row>
     <row r="281" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A281" s="10"/>
-      <c r="B281" s="10"/>
+      <c r="A281" s="11"/>
+      <c r="B281" s="11"/>
     </row>
     <row r="282" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A282" s="10"/>
-      <c r="B282" s="10"/>
+      <c r="A282" s="11"/>
+      <c r="B282" s="11"/>
     </row>
     <row r="283" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A283" s="10"/>
-      <c r="B283" s="10"/>
+      <c r="A283" s="11"/>
+      <c r="B283" s="11"/>
     </row>
     <row r="284" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A284" s="10"/>
-      <c r="B284" s="10"/>
+      <c r="A284" s="11"/>
+      <c r="B284" s="11"/>
     </row>
     <row r="285" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A285" s="10"/>
-      <c r="B285" s="10"/>
+      <c r="A285" s="11"/>
+      <c r="B285" s="11"/>
     </row>
     <row r="286" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A286" s="10"/>
-      <c r="B286" s="10"/>
+      <c r="A286" s="11"/>
+      <c r="B286" s="11"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A287" s="10"/>
-      <c r="B287" s="10"/>
+      <c r="A287" s="11"/>
+      <c r="B287" s="11"/>
     </row>
     <row r="288" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A288" s="10"/>
-      <c r="B288" s="10"/>
+      <c r="A288" s="11"/>
+      <c r="B288" s="11"/>
     </row>
     <row r="289" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A289" s="10"/>
-      <c r="B289" s="10"/>
+      <c r="A289" s="11"/>
+      <c r="B289" s="11"/>
     </row>
     <row r="290" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A290" s="10"/>
-      <c r="B290" s="10"/>
+      <c r="A290" s="11"/>
+      <c r="B290" s="11"/>
     </row>
     <row r="291" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A291" s="10"/>
-      <c r="B291" s="10"/>
+      <c r="A291" s="11"/>
+      <c r="B291" s="11"/>
     </row>
     <row r="292" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A292" s="10"/>
-      <c r="B292" s="10"/>
+      <c r="A292" s="11"/>
+      <c r="B292" s="11"/>
     </row>
     <row r="293" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A293" s="10"/>
-      <c r="B293" s="10"/>
+      <c r="A293" s="11"/>
+      <c r="B293" s="11"/>
     </row>
     <row r="294" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A294" s="10"/>
-      <c r="B294" s="10"/>
+      <c r="A294" s="11"/>
+      <c r="B294" s="11"/>
     </row>
     <row r="295" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A295" s="10"/>
-      <c r="B295" s="10"/>
+      <c r="A295" s="11"/>
+      <c r="B295" s="11"/>
     </row>
     <row r="296" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A296" s="10"/>
-      <c r="B296" s="10"/>
+      <c r="A296" s="11"/>
+      <c r="B296" s="11"/>
     </row>
     <row r="297" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A297" s="10"/>
-      <c r="B297" s="10"/>
+      <c r="A297" s="11"/>
+      <c r="B297" s="11"/>
     </row>
     <row r="298" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A298" s="10"/>
-      <c r="B298" s="10"/>
+      <c r="A298" s="11"/>
+      <c r="B298" s="11"/>
     </row>
     <row r="299" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A299" s="10"/>
-      <c r="B299" s="10"/>
+      <c r="A299" s="11"/>
+      <c r="B299" s="11"/>
     </row>
     <row r="300" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A300" s="10"/>
-      <c r="B300" s="10"/>
+      <c r="A300" s="11"/>
+      <c r="B300" s="11"/>
     </row>
     <row r="301" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A301" s="10"/>
-      <c r="B301" s="10"/>
+      <c r="A301" s="11"/>
+      <c r="B301" s="11"/>
     </row>
     <row r="302" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A302" s="10"/>
-      <c r="B302" s="10"/>
+      <c r="A302" s="11"/>
+      <c r="B302" s="11"/>
     </row>
     <row r="303" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A303" s="10"/>
-      <c r="B303" s="10"/>
+      <c r="A303" s="11"/>
+      <c r="B303" s="11"/>
     </row>
     <row r="304" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A304" s="10"/>
-      <c r="B304" s="10"/>
+      <c r="A304" s="11"/>
+      <c r="B304" s="11"/>
     </row>
     <row r="305" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A305" s="10"/>
-      <c r="B305" s="10"/>
+      <c r="A305" s="11"/>
+      <c r="B305" s="11"/>
     </row>
     <row r="306" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A306" s="10"/>
-      <c r="B306" s="10"/>
+      <c r="A306" s="11"/>
+      <c r="B306" s="11"/>
     </row>
     <row r="307" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A307" s="10"/>
-      <c r="B307" s="10"/>
+      <c r="A307" s="11"/>
+      <c r="B307" s="11"/>
     </row>
     <row r="308" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A308" s="10"/>
-      <c r="B308" s="10"/>
+      <c r="A308" s="11"/>
+      <c r="B308" s="11"/>
     </row>
     <row r="309" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A309" s="10"/>
-      <c r="B309" s="10"/>
+      <c r="A309" s="11"/>
+      <c r="B309" s="11"/>
     </row>
     <row r="310" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A310" s="10"/>
-      <c r="B310" s="10"/>
+      <c r="A310" s="11"/>
+      <c r="B310" s="11"/>
     </row>
     <row r="311" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A311" s="10"/>
-      <c r="B311" s="10"/>
+      <c r="A311" s="11"/>
+      <c r="B311" s="11"/>
     </row>
     <row r="312" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A312" s="10"/>
-      <c r="B312" s="10"/>
+      <c r="A312" s="11"/>
+      <c r="B312" s="11"/>
     </row>
     <row r="313" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A313" s="10"/>
-      <c r="B313" s="10"/>
+      <c r="A313" s="11"/>
+      <c r="B313" s="11"/>
     </row>
     <row r="314" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A314" s="10"/>
-      <c r="B314" s="10"/>
+      <c r="A314" s="11"/>
+      <c r="B314" s="11"/>
     </row>
     <row r="315" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A315" s="10"/>
-      <c r="B315" s="10"/>
+      <c r="A315" s="11"/>
+      <c r="B315" s="11"/>
     </row>
     <row r="316" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A316" s="10"/>
-      <c r="B316" s="10"/>
+      <c r="A316" s="11"/>
+      <c r="B316" s="11"/>
     </row>
     <row r="317" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A317" s="10"/>
-      <c r="B317" s="10"/>
+      <c r="A317" s="11"/>
+      <c r="B317" s="11"/>
     </row>
     <row r="318" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A318" s="10"/>
-      <c r="B318" s="10"/>
+      <c r="A318" s="11"/>
+      <c r="B318" s="11"/>
     </row>
     <row r="319" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A319" s="10"/>
-      <c r="B319" s="10"/>
+      <c r="A319" s="11"/>
+      <c r="B319" s="11"/>
     </row>
     <row r="320" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A320" s="10"/>
-      <c r="B320" s="10"/>
+      <c r="A320" s="11"/>
+      <c r="B320" s="11"/>
     </row>
     <row r="321" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A321" s="10"/>
-      <c r="B321" s="10"/>
+      <c r="A321" s="11"/>
+      <c r="B321" s="11"/>
     </row>
     <row r="322" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A322" s="10"/>
-      <c r="B322" s="10"/>
+      <c r="A322" s="11"/>
+      <c r="B322" s="11"/>
     </row>
     <row r="323" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A323" s="10"/>
-      <c r="B323" s="10"/>
+      <c r="A323" s="11"/>
+      <c r="B323" s="11"/>
     </row>
     <row r="324" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A324" s="10"/>
-      <c r="B324" s="10"/>
+      <c r="A324" s="11"/>
+      <c r="B324" s="11"/>
     </row>
     <row r="325" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A325" s="10"/>
-      <c r="B325" s="10"/>
+      <c r="A325" s="11"/>
+      <c r="B325" s="11"/>
     </row>
     <row r="326" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A326" s="10"/>
-      <c r="B326" s="10"/>
+      <c r="A326" s="11"/>
+      <c r="B326" s="11"/>
     </row>
     <row r="327" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A327" s="10"/>
-      <c r="B327" s="10"/>
+      <c r="A327" s="11"/>
+      <c r="B327" s="11"/>
     </row>
     <row r="328" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A328" s="10"/>
-      <c r="B328" s="10"/>
+      <c r="A328" s="11"/>
+      <c r="B328" s="11"/>
     </row>
     <row r="329" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A329" s="10"/>
-      <c r="B329" s="10"/>
+      <c r="A329" s="11"/>
+      <c r="B329" s="11"/>
     </row>
     <row r="330" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A330" s="10"/>
-      <c r="B330" s="10"/>
+      <c r="A330" s="11"/>
+      <c r="B330" s="11"/>
     </row>
     <row r="331" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A331" s="10"/>
-      <c r="B331" s="10"/>
+      <c r="A331" s="11"/>
+      <c r="B331" s="11"/>
     </row>
     <row r="332" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A332" s="10"/>
-      <c r="B332" s="10"/>
+      <c r="A332" s="11"/>
+      <c r="B332" s="11"/>
     </row>
     <row r="333" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A333" s="10"/>
-      <c r="B333" s="10"/>
+      <c r="A333" s="11"/>
+      <c r="B333" s="11"/>
     </row>
     <row r="334" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A334" s="10"/>
-      <c r="B334" s="10"/>
+      <c r="A334" s="11"/>
+      <c r="B334" s="11"/>
     </row>
     <row r="335" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A335" s="10"/>
-      <c r="B335" s="10"/>
+      <c r="A335" s="11"/>
+      <c r="B335" s="11"/>
     </row>
     <row r="336" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A336" s="10"/>
-      <c r="B336" s="10"/>
+      <c r="A336" s="11"/>
+      <c r="B336" s="11"/>
     </row>
     <row r="337" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A337" s="10"/>
-      <c r="B337" s="10"/>
+      <c r="A337" s="11"/>
+      <c r="B337" s="11"/>
     </row>
     <row r="338" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A338" s="10"/>
-      <c r="B338" s="10"/>
+      <c r="A338" s="11"/>
+      <c r="B338" s="11"/>
     </row>
     <row r="339" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A339" s="10"/>
-      <c r="B339" s="10"/>
+      <c r="A339" s="11"/>
+      <c r="B339" s="11"/>
     </row>
     <row r="340" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A340" s="10"/>
-      <c r="B340" s="10"/>
+      <c r="A340" s="11"/>
+      <c r="B340" s="11"/>
     </row>
     <row r="341" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A341" s="10"/>
-      <c r="B341" s="10"/>
+      <c r="A341" s="11"/>
+      <c r="B341" s="11"/>
     </row>
     <row r="342" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A342" s="10"/>
-      <c r="B342" s="10"/>
+      <c r="A342" s="11"/>
+      <c r="B342" s="11"/>
     </row>
     <row r="343" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A343" s="10"/>
-      <c r="B343" s="10"/>
+      <c r="A343" s="11"/>
+      <c r="B343" s="11"/>
     </row>
     <row r="344" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A344" s="10"/>
-      <c r="B344" s="10"/>
+      <c r="A344" s="11"/>
+      <c r="B344" s="11"/>
     </row>
     <row r="345" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A345" s="10"/>
-      <c r="B345" s="10"/>
+      <c r="A345" s="11"/>
+      <c r="B345" s="11"/>
     </row>
     <row r="346" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A346" s="10"/>
-      <c r="B346" s="10"/>
+      <c r="A346" s="11"/>
+      <c r="B346" s="11"/>
     </row>
     <row r="347" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A347" s="10"/>
-      <c r="B347" s="10"/>
+      <c r="A347" s="11"/>
+      <c r="B347" s="11"/>
     </row>
     <row r="348" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A348" s="10"/>
-      <c r="B348" s="10"/>
+      <c r="A348" s="11"/>
+      <c r="B348" s="11"/>
     </row>
     <row r="349" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A349" s="10"/>
-      <c r="B349" s="10"/>
+      <c r="A349" s="11"/>
+      <c r="B349" s="11"/>
     </row>
     <row r="350" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A350" s="10"/>
-      <c r="B350" s="10"/>
+      <c r="A350" s="11"/>
+      <c r="B350" s="11"/>
     </row>
     <row r="351" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A351" s="10"/>
-      <c r="B351" s="10"/>
+      <c r="A351" s="11"/>
+      <c r="B351" s="11"/>
     </row>
     <row r="352" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A352" s="10"/>
-      <c r="B352" s="10"/>
+      <c r="A352" s="11"/>
+      <c r="B352" s="11"/>
     </row>
     <row r="353" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A353" s="10"/>
-      <c r="B353" s="10"/>
+      <c r="A353" s="11"/>
+      <c r="B353" s="11"/>
     </row>
     <row r="354" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A354" s="10"/>
-      <c r="B354" s="10"/>
+      <c r="A354" s="11"/>
+      <c r="B354" s="11"/>
     </row>
     <row r="355" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A355" s="10"/>
-      <c r="B355" s="10"/>
+      <c r="A355" s="11"/>
+      <c r="B355" s="11"/>
     </row>
     <row r="356" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A356" s="10"/>
-      <c r="B356" s="10"/>
+      <c r="A356" s="11"/>
+      <c r="B356" s="11"/>
     </row>
     <row r="357" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A357" s="10"/>
-      <c r="B357" s="10"/>
+      <c r="A357" s="11"/>
+      <c r="B357" s="11"/>
     </row>
     <row r="358" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A358" s="10"/>
-      <c r="B358" s="10"/>
+      <c r="A358" s="11"/>
+      <c r="B358" s="11"/>
     </row>
     <row r="359" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A359" s="10"/>
-      <c r="B359" s="10"/>
+      <c r="A359" s="11"/>
+      <c r="B359" s="11"/>
     </row>
     <row r="360" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A360" s="10"/>
-      <c r="B360" s="10"/>
+      <c r="A360" s="11"/>
+      <c r="B360" s="11"/>
     </row>
     <row r="361" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A361" s="10"/>
-      <c r="B361" s="10"/>
+      <c r="A361" s="11"/>
+      <c r="B361" s="11"/>
     </row>
     <row r="362" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A362" s="10"/>
-      <c r="B362" s="10"/>
+      <c r="A362" s="11"/>
+      <c r="B362" s="11"/>
     </row>
     <row r="363" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A363" s="10"/>
-      <c r="B363" s="10"/>
+      <c r="A363" s="11"/>
+      <c r="B363" s="11"/>
     </row>
     <row r="364" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A364" s="10"/>
-      <c r="B364" s="10"/>
+      <c r="A364" s="11"/>
+      <c r="B364" s="11"/>
     </row>
     <row r="365" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A365" s="10"/>
-      <c r="B365" s="10"/>
+      <c r="A365" s="11"/>
+      <c r="B365" s="11"/>
     </row>
     <row r="366" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A366" s="10"/>
-      <c r="B366" s="10"/>
+      <c r="A366" s="11"/>
+      <c r="B366" s="11"/>
     </row>
     <row r="367" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A367" s="10"/>
-      <c r="B367" s="10"/>
+      <c r="A367" s="11"/>
+      <c r="B367" s="11"/>
     </row>
     <row r="368" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A368" s="10"/>
-      <c r="B368" s="10"/>
+      <c r="A368" s="11"/>
+      <c r="B368" s="11"/>
     </row>
     <row r="369" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A369" s="10"/>
-      <c r="B369" s="10"/>
+      <c r="A369" s="11"/>
+      <c r="B369" s="11"/>
     </row>
     <row r="370" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A370" s="10"/>
-      <c r="B370" s="10"/>
+      <c r="A370" s="11"/>
+      <c r="B370" s="11"/>
     </row>
     <row r="371" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A371" s="10"/>
-      <c r="B371" s="10"/>
+      <c r="A371" s="11"/>
+      <c r="B371" s="11"/>
     </row>
     <row r="372" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A372" s="10"/>
-      <c r="B372" s="10"/>
+      <c r="A372" s="11"/>
+      <c r="B372" s="11"/>
     </row>
     <row r="373" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A373" s="10"/>
-      <c r="B373" s="10"/>
+      <c r="A373" s="11"/>
+      <c r="B373" s="11"/>
     </row>
     <row r="374" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A374" s="10"/>
-      <c r="B374" s="10"/>
+      <c r="A374" s="11"/>
+      <c r="B374" s="11"/>
     </row>
     <row r="375" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A375" s="10"/>
-      <c r="B375" s="10"/>
+      <c r="A375" s="11"/>
+      <c r="B375" s="11"/>
     </row>
     <row r="376" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A376" s="10"/>
-      <c r="B376" s="10"/>
+      <c r="A376" s="11"/>
+      <c r="B376" s="11"/>
     </row>
     <row r="377" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A377" s="10"/>
-      <c r="B377" s="10"/>
+      <c r="A377" s="11"/>
+      <c r="B377" s="11"/>
     </row>
     <row r="378" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A378" s="10"/>
-      <c r="B378" s="10"/>
+      <c r="A378" s="11"/>
+      <c r="B378" s="11"/>
     </row>
     <row r="379" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A379" s="10"/>
-      <c r="B379" s="10"/>
+      <c r="A379" s="11"/>
+      <c r="B379" s="11"/>
     </row>
     <row r="380" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A380" s="10"/>
-      <c r="B380" s="10"/>
+      <c r="A380" s="11"/>
+      <c r="B380" s="11"/>
     </row>
     <row r="381" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A381" s="10"/>
-      <c r="B381" s="10"/>
+      <c r="A381" s="11"/>
+      <c r="B381" s="11"/>
     </row>
     <row r="382" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A382" s="10"/>
-      <c r="B382" s="10"/>
+      <c r="A382" s="11"/>
+      <c r="B382" s="11"/>
     </row>
     <row r="383" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A383" s="10"/>
-      <c r="B383" s="10"/>
+      <c r="A383" s="11"/>
+      <c r="B383" s="11"/>
     </row>
     <row r="384" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A384" s="10"/>
-      <c r="B384" s="10"/>
+      <c r="A384" s="11"/>
+      <c r="B384" s="11"/>
     </row>
     <row r="385" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A385" s="10"/>
-      <c r="B385" s="10"/>
+      <c r="A385" s="11"/>
+      <c r="B385" s="11"/>
     </row>
     <row r="386" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A386" s="10"/>
-      <c r="B386" s="10"/>
+      <c r="A386" s="11"/>
+      <c r="B386" s="11"/>
     </row>
     <row r="387" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A387" s="10"/>
-      <c r="B387" s="10"/>
+      <c r="A387" s="11"/>
+      <c r="B387" s="11"/>
     </row>
     <row r="388" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A388" s="10"/>
-      <c r="B388" s="10"/>
+      <c r="A388" s="11"/>
+      <c r="B388" s="11"/>
     </row>
     <row r="389" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A389" s="10"/>
-      <c r="B389" s="10"/>
+      <c r="A389" s="11"/>
+      <c r="B389" s="11"/>
     </row>
     <row r="390" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A390" s="10"/>
-      <c r="B390" s="10"/>
+      <c r="A390" s="11"/>
+      <c r="B390" s="11"/>
     </row>
     <row r="391" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A391" s="10"/>
-      <c r="B391" s="10"/>
+      <c r="A391" s="11"/>
+      <c r="B391" s="11"/>
     </row>
     <row r="392" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A392" s="10"/>
-      <c r="B392" s="10"/>
+      <c r="A392" s="11"/>
+      <c r="B392" s="11"/>
     </row>
     <row r="393" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A393" s="10"/>
-      <c r="B393" s="10"/>
+      <c r="A393" s="11"/>
+      <c r="B393" s="11"/>
     </row>
     <row r="394" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A394" s="10"/>
-      <c r="B394" s="10"/>
+      <c r="A394" s="11"/>
+      <c r="B394" s="11"/>
     </row>
     <row r="395" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A395" s="10"/>
-      <c r="B395" s="10"/>
+      <c r="A395" s="11"/>
+      <c r="B395" s="11"/>
     </row>
     <row r="396" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A396" s="10"/>
-      <c r="B396" s="10"/>
+      <c r="A396" s="11"/>
+      <c r="B396" s="11"/>
     </row>
     <row r="397" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A397" s="10"/>
-      <c r="B397" s="10"/>
+      <c r="A397" s="11"/>
+      <c r="B397" s="11"/>
     </row>
     <row r="398" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A398" s="10"/>
-      <c r="B398" s="10"/>
+      <c r="A398" s="11"/>
+      <c r="B398" s="11"/>
     </row>
     <row r="399" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A399" s="10"/>
-      <c r="B399" s="10"/>
+      <c r="A399" s="11"/>
+      <c r="B399" s="11"/>
     </row>
     <row r="400" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A400" s="10"/>
-      <c r="B400" s="10"/>
+      <c r="A400" s="11"/>
+      <c r="B400" s="11"/>
     </row>
     <row r="401" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A401" s="10"/>
-      <c r="B401" s="10"/>
+      <c r="A401" s="11"/>
+      <c r="B401" s="11"/>
     </row>
     <row r="402" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A402" s="10"/>
-      <c r="B402" s="10"/>
+      <c r="A402" s="11"/>
+      <c r="B402" s="11"/>
     </row>
     <row r="403" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A403" s="10"/>
-      <c r="B403" s="10"/>
+      <c r="A403" s="11"/>
+      <c r="B403" s="11"/>
     </row>
     <row r="404" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A404" s="10"/>
-      <c r="B404" s="10"/>
+      <c r="A404" s="11"/>
+      <c r="B404" s="11"/>
     </row>
     <row r="405" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A405" s="10"/>
-      <c r="B405" s="10"/>
+      <c r="A405" s="11"/>
+      <c r="B405" s="11"/>
     </row>
     <row r="406" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A406" s="10"/>
-      <c r="B406" s="10"/>
+      <c r="A406" s="11"/>
+      <c r="B406" s="11"/>
     </row>
     <row r="407" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A407" s="10"/>
-      <c r="B407" s="10"/>
+      <c r="A407" s="11"/>
+      <c r="B407" s="11"/>
     </row>
     <row r="408" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A408" s="10"/>
-      <c r="B408" s="10"/>
+      <c r="A408" s="11"/>
+      <c r="B408" s="11"/>
     </row>
     <row r="409" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A409" s="10"/>
-      <c r="B409" s="10"/>
+      <c r="A409" s="11"/>
+      <c r="B409" s="11"/>
     </row>
     <row r="410" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A410" s="10"/>
-      <c r="B410" s="10"/>
+      <c r="A410" s="11"/>
+      <c r="B410" s="11"/>
     </row>
     <row r="411" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A411" s="10"/>
-      <c r="B411" s="10"/>
+      <c r="A411" s="11"/>
+      <c r="B411" s="11"/>
     </row>
     <row r="412" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A412" s="10"/>
-      <c r="B412" s="10"/>
+      <c r="A412" s="11"/>
+      <c r="B412" s="11"/>
     </row>
     <row r="413" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A413" s="10"/>
-      <c r="B413" s="10"/>
+      <c r="A413" s="11"/>
+      <c r="B413" s="11"/>
     </row>
     <row r="414" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A414" s="10"/>
-      <c r="B414" s="10"/>
+      <c r="A414" s="11"/>
+      <c r="B414" s="11"/>
     </row>
     <row r="415" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A415" s="10"/>
-      <c r="B415" s="10"/>
+      <c r="A415" s="11"/>
+      <c r="B415" s="11"/>
     </row>
     <row r="416" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A416" s="10"/>
-      <c r="B416" s="10"/>
+      <c r="A416" s="11"/>
+      <c r="B416" s="11"/>
     </row>
     <row r="417" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A417" s="10"/>
-      <c r="B417" s="10"/>
+      <c r="A417" s="11"/>
+      <c r="B417" s="11"/>
     </row>
     <row r="418" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A418" s="10"/>
-      <c r="B418" s="10"/>
+      <c r="A418" s="11"/>
+      <c r="B418" s="11"/>
     </row>
     <row r="419" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A419" s="10"/>
-      <c r="B419" s="10"/>
+      <c r="A419" s="11"/>
+      <c r="B419" s="11"/>
     </row>
     <row r="420" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A420" s="10"/>
-      <c r="B420" s="10"/>
+      <c r="A420" s="11"/>
+      <c r="B420" s="11"/>
     </row>
     <row r="421" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A421" s="10"/>
-      <c r="B421" s="10"/>
+      <c r="A421" s="11"/>
+      <c r="B421" s="11"/>
     </row>
     <row r="422" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A422" s="10"/>
-      <c r="B422" s="10"/>
+      <c r="A422" s="11"/>
+      <c r="B422" s="11"/>
     </row>
     <row r="423" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A423" s="10"/>
-      <c r="B423" s="10"/>
+      <c r="A423" s="11"/>
+      <c r="B423" s="11"/>
     </row>
     <row r="424" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A424" s="10"/>
-      <c r="B424" s="10"/>
+      <c r="A424" s="11"/>
+      <c r="B424" s="11"/>
     </row>
     <row r="425" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A425" s="10"/>
-      <c r="B425" s="10"/>
+      <c r="A425" s="11"/>
+      <c r="B425" s="11"/>
     </row>
     <row r="426" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A426" s="10"/>
-      <c r="B426" s="10"/>
+      <c r="A426" s="11"/>
+      <c r="B426" s="11"/>
     </row>
     <row r="427" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A427" s="10"/>
-      <c r="B427" s="10"/>
+      <c r="A427" s="11"/>
+      <c r="B427" s="11"/>
     </row>
     <row r="428" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A428" s="10"/>
-      <c r="B428" s="10"/>
+      <c r="A428" s="11"/>
+      <c r="B428" s="11"/>
     </row>
     <row r="429" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A429" s="10"/>
-      <c r="B429" s="10"/>
+      <c r="A429" s="11"/>
+      <c r="B429" s="11"/>
     </row>
     <row r="430" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A430" s="10"/>
-      <c r="B430" s="10"/>
+      <c r="A430" s="11"/>
+      <c r="B430" s="11"/>
     </row>
     <row r="431" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A431" s="10"/>
-      <c r="B431" s="10"/>
+      <c r="A431" s="11"/>
+      <c r="B431" s="11"/>
     </row>
     <row r="432" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A432" s="10"/>
-      <c r="B432" s="10"/>
+      <c r="A432" s="11"/>
+      <c r="B432" s="11"/>
     </row>
     <row r="433" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A433" s="10"/>
-      <c r="B433" s="10"/>
+      <c r="A433" s="11"/>
+      <c r="B433" s="11"/>
     </row>
     <row r="434" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A434" s="10"/>
-      <c r="B434" s="10"/>
+      <c r="A434" s="11"/>
+      <c r="B434" s="11"/>
     </row>
     <row r="435" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A435" s="10"/>
-      <c r="B435" s="10"/>
+      <c r="A435" s="11"/>
+      <c r="B435" s="11"/>
     </row>
     <row r="436" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A436" s="10"/>
-      <c r="B436" s="10"/>
+      <c r="A436" s="11"/>
+      <c r="B436" s="11"/>
     </row>
     <row r="437" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A437" s="10"/>
-      <c r="B437" s="10"/>
+      <c r="A437" s="11"/>
+      <c r="B437" s="11"/>
     </row>
     <row r="438" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A438" s="10"/>
-      <c r="B438" s="10"/>
+      <c r="A438" s="11"/>
+      <c r="B438" s="11"/>
     </row>
     <row r="439" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A439" s="10"/>
-      <c r="B439" s="10"/>
+      <c r="A439" s="11"/>
+      <c r="B439" s="11"/>
     </row>
     <row r="440" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A440" s="10"/>
-      <c r="B440" s="10"/>
+      <c r="A440" s="11"/>
+      <c r="B440" s="11"/>
     </row>
     <row r="441" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A441" s="10"/>
-      <c r="B441" s="10"/>
+      <c r="A441" s="11"/>
+      <c r="B441" s="11"/>
     </row>
     <row r="442" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A442" s="10"/>
-      <c r="B442" s="10"/>
+      <c r="A442" s="11"/>
+      <c r="B442" s="11"/>
     </row>
     <row r="443" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A443" s="10"/>
-      <c r="B443" s="10"/>
+      <c r="A443" s="11"/>
+      <c r="B443" s="11"/>
     </row>
     <row r="444" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A444" s="10"/>
-      <c r="B444" s="10"/>
+      <c r="A444" s="11"/>
+      <c r="B444" s="11"/>
     </row>
     <row r="445" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A445" s="10"/>
-      <c r="B445" s="10"/>
+      <c r="A445" s="11"/>
+      <c r="B445" s="11"/>
     </row>
     <row r="446" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A446" s="10"/>
-      <c r="B446" s="10"/>
+      <c r="A446" s="11"/>
+      <c r="B446" s="11"/>
     </row>
     <row r="447" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A447" s="10"/>
-      <c r="B447" s="10"/>
+      <c r="A447" s="11"/>
+      <c r="B447" s="11"/>
     </row>
     <row r="448" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A448" s="10"/>
-      <c r="B448" s="10"/>
+      <c r="A448" s="11"/>
+      <c r="B448" s="11"/>
     </row>
     <row r="449" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A449" s="10"/>
-      <c r="B449" s="10"/>
+      <c r="A449" s="11"/>
+      <c r="B449" s="11"/>
     </row>
     <row r="450" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A450" s="10"/>
-      <c r="B450" s="10"/>
+      <c r="A450" s="11"/>
+      <c r="B450" s="11"/>
     </row>
     <row r="451" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A451" s="10"/>
-      <c r="B451" s="10"/>
+      <c r="A451" s="11"/>
+      <c r="B451" s="11"/>
     </row>
     <row r="452" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A452" s="10"/>
-      <c r="B452" s="10"/>
+      <c r="A452" s="11"/>
+      <c r="B452" s="11"/>
     </row>
     <row r="453" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A453" s="10"/>
-      <c r="B453" s="10"/>
+      <c r="A453" s="11"/>
+      <c r="B453" s="11"/>
     </row>
     <row r="454" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A454" s="10"/>
-      <c r="B454" s="10"/>
+      <c r="A454" s="11"/>
+      <c r="B454" s="11"/>
     </row>
     <row r="455" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A455" s="10"/>
-      <c r="B455" s="10"/>
+      <c r="A455" s="11"/>
+      <c r="B455" s="11"/>
     </row>
     <row r="456" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A456" s="10"/>
-      <c r="B456" s="10"/>
+      <c r="A456" s="11"/>
+      <c r="B456" s="11"/>
     </row>
     <row r="457" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A457" s="10"/>
-      <c r="B457" s="10"/>
+      <c r="A457" s="11"/>
+      <c r="B457" s="11"/>
     </row>
     <row r="458" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A458" s="10"/>
-      <c r="B458" s="10"/>
+      <c r="A458" s="11"/>
+      <c r="B458" s="11"/>
     </row>
     <row r="459" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A459" s="10"/>
-      <c r="B459" s="10"/>
+      <c r="A459" s="11"/>
+      <c r="B459" s="11"/>
     </row>
     <row r="460" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A460" s="10"/>
-      <c r="B460" s="10"/>
+      <c r="A460" s="11"/>
+      <c r="B460" s="11"/>
     </row>
     <row r="461" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A461" s="10"/>
-      <c r="B461" s="10"/>
+      <c r="A461" s="11"/>
+      <c r="B461" s="11"/>
     </row>
     <row r="462" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A462" s="10"/>
-      <c r="B462" s="10"/>
+      <c r="A462" s="11"/>
+      <c r="B462" s="11"/>
     </row>
     <row r="463" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A463" s="10"/>
-      <c r="B463" s="10"/>
+      <c r="A463" s="11"/>
+      <c r="B463" s="11"/>
     </row>
     <row r="464" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A464" s="10"/>
-      <c r="B464" s="10"/>
+      <c r="A464" s="11"/>
+      <c r="B464" s="11"/>
     </row>
     <row r="465" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A465" s="10"/>
-      <c r="B465" s="10"/>
+      <c r="A465" s="11"/>
+      <c r="B465" s="11"/>
     </row>
     <row r="466" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A466" s="10"/>
-      <c r="B466" s="10"/>
+      <c r="A466" s="11"/>
+      <c r="B466" s="11"/>
     </row>
     <row r="467" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A467" s="10"/>
-      <c r="B467" s="10"/>
+      <c r="A467" s="11"/>
+      <c r="B467" s="11"/>
     </row>
     <row r="468" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A468" s="10"/>
-      <c r="B468" s="10"/>
+      <c r="A468" s="11"/>
+      <c r="B468" s="11"/>
     </row>
     <row r="469" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A469" s="10"/>
-      <c r="B469" s="10"/>
+      <c r="A469" s="11"/>
+      <c r="B469" s="11"/>
     </row>
     <row r="470" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A470" s="10"/>
-      <c r="B470" s="10"/>
+      <c r="A470" s="11"/>
+      <c r="B470" s="11"/>
     </row>
     <row r="471" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A471" s="10"/>
-      <c r="B471" s="10"/>
+      <c r="A471" s="11"/>
+      <c r="B471" s="11"/>
     </row>
     <row r="472" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A472" s="10"/>
-      <c r="B472" s="10"/>
+      <c r="A472" s="11"/>
+      <c r="B472" s="11"/>
     </row>
     <row r="473" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A473" s="10"/>
-      <c r="B473" s="10"/>
+      <c r="A473" s="11"/>
+      <c r="B473" s="11"/>
     </row>
     <row r="474" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A474" s="10"/>
-      <c r="B474" s="10"/>
+      <c r="A474" s="11"/>
+      <c r="B474" s="11"/>
     </row>
     <row r="475" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A475" s="10"/>
-      <c r="B475" s="10"/>
+      <c r="A475" s="11"/>
+      <c r="B475" s="11"/>
     </row>
     <row r="476" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A476" s="10"/>
-      <c r="B476" s="10"/>
+      <c r="A476" s="11"/>
+      <c r="B476" s="11"/>
     </row>
     <row r="477" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A477" s="10"/>
-      <c r="B477" s="10"/>
+      <c r="A477" s="11"/>
+      <c r="B477" s="11"/>
     </row>
     <row r="478" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A478" s="10"/>
-      <c r="B478" s="10"/>
+      <c r="A478" s="11"/>
+      <c r="B478" s="11"/>
     </row>
     <row r="479" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A479" s="10"/>
-      <c r="B479" s="10"/>
+      <c r="A479" s="11"/>
+      <c r="B479" s="11"/>
     </row>
     <row r="480" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A480" s="10"/>
-      <c r="B480" s="10"/>
+      <c r="A480" s="11"/>
+      <c r="B480" s="11"/>
     </row>
     <row r="481" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A481" s="10"/>
-      <c r="B481" s="10"/>
+      <c r="A481" s="11"/>
+      <c r="B481" s="11"/>
     </row>
     <row r="482" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A482" s="10"/>
-      <c r="B482" s="10"/>
+      <c r="A482" s="11"/>
+      <c r="B482" s="11"/>
     </row>
     <row r="483" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A483" s="10"/>
-      <c r="B483" s="10"/>
+      <c r="A483" s="11"/>
+      <c r="B483" s="11"/>
     </row>
     <row r="484" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A484" s="10"/>
-      <c r="B484" s="10"/>
+      <c r="A484" s="11"/>
+      <c r="B484" s="11"/>
     </row>
     <row r="485" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A485" s="10"/>
-      <c r="B485" s="10"/>
+      <c r="A485" s="11"/>
+      <c r="B485" s="11"/>
     </row>
     <row r="486" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A486" s="10"/>
-      <c r="B486" s="10"/>
+      <c r="A486" s="11"/>
+      <c r="B486" s="11"/>
     </row>
     <row r="487" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A487" s="10"/>
-      <c r="B487" s="10"/>
+      <c r="A487" s="11"/>
+      <c r="B487" s="11"/>
     </row>
     <row r="488" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A488" s="10"/>
-      <c r="B488" s="10"/>
+      <c r="A488" s="11"/>
+      <c r="B488" s="11"/>
     </row>
     <row r="489" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A489" s="10"/>
-      <c r="B489" s="10"/>
+      <c r="A489" s="11"/>
+      <c r="B489" s="11"/>
     </row>
     <row r="490" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A490" s="10"/>
-      <c r="B490" s="10"/>
+      <c r="A490" s="11"/>
+      <c r="B490" s="11"/>
     </row>
     <row r="491" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A491" s="10"/>
-      <c r="B491" s="10"/>
+      <c r="A491" s="11"/>
+      <c r="B491" s="11"/>
     </row>
     <row r="492" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A492" s="10"/>
-      <c r="B492" s="10"/>
+      <c r="A492" s="11"/>
+      <c r="B492" s="11"/>
     </row>
     <row r="493" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A493" s="10"/>
-      <c r="B493" s="10"/>
+      <c r="A493" s="11"/>
+      <c r="B493" s="11"/>
     </row>
     <row r="494" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A494" s="10"/>
-      <c r="B494" s="10"/>
+      <c r="A494" s="11"/>
+      <c r="B494" s="11"/>
     </row>
     <row r="495" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A495" s="10"/>
-      <c r="B495" s="10"/>
+      <c r="A495" s="11"/>
+      <c r="B495" s="11"/>
     </row>
     <row r="496" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A496" s="10"/>
-      <c r="B496" s="10"/>
+      <c r="A496" s="11"/>
+      <c r="B496" s="11"/>
     </row>
     <row r="497" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A497" s="10"/>
-      <c r="B497" s="10"/>
+      <c r="A497" s="11"/>
+      <c r="B497" s="11"/>
     </row>
     <row r="498" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A498" s="10"/>
-      <c r="B498" s="10"/>
+      <c r="A498" s="11"/>
+      <c r="B498" s="11"/>
     </row>
     <row r="499" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A499" s="10"/>
-      <c r="B499" s="10"/>
+      <c r="A499" s="11"/>
+      <c r="B499" s="11"/>
     </row>
     <row r="500" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A500" s="10"/>
-      <c r="B500" s="10"/>
+      <c r="A500" s="11"/>
+      <c r="B500" s="11"/>
     </row>
     <row r="501" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A501" s="10"/>
-      <c r="B501" s="10"/>
+      <c r="A501" s="11"/>
+      <c r="B501" s="11"/>
     </row>
     <row r="502" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A502" s="10"/>
-      <c r="B502" s="10"/>
+      <c r="A502" s="11"/>
+      <c r="B502" s="11"/>
     </row>
     <row r="503" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A503" s="10"/>
-      <c r="B503" s="10"/>
+      <c r="A503" s="11"/>
+      <c r="B503" s="11"/>
     </row>
     <row r="504" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A504" s="10"/>
-      <c r="B504" s="10"/>
+      <c r="A504" s="11"/>
+      <c r="B504" s="11"/>
     </row>
     <row r="505" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A505" s="10"/>
-      <c r="B505" s="10"/>
+      <c r="A505" s="11"/>
+      <c r="B505" s="11"/>
     </row>
     <row r="506" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A506" s="10"/>
-      <c r="B506" s="10"/>
+      <c r="A506" s="11"/>
+      <c r="B506" s="11"/>
     </row>
     <row r="507" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A507" s="10"/>
-      <c r="B507" s="10"/>
+      <c r="A507" s="11"/>
+      <c r="B507" s="11"/>
     </row>
     <row r="508" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A508" s="10"/>
-      <c r="B508" s="10"/>
+      <c r="A508" s="11"/>
+      <c r="B508" s="11"/>
     </row>
     <row r="509" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A509" s="10"/>
-      <c r="B509" s="10"/>
+      <c r="A509" s="11"/>
+      <c r="B509" s="11"/>
     </row>
     <row r="510" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A510" s="10"/>
-      <c r="B510" s="10"/>
+      <c r="A510" s="11"/>
+      <c r="B510" s="11"/>
     </row>
     <row r="511" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A511" s="10"/>
-      <c r="B511" s="10"/>
+      <c r="A511" s="11"/>
+      <c r="B511" s="11"/>
     </row>
     <row r="512" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A512" s="10"/>
-      <c r="B512" s="10"/>
+      <c r="A512" s="11"/>
+      <c r="B512" s="11"/>
     </row>
     <row r="513" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A513" s="10"/>
-      <c r="B513" s="10"/>
+      <c r="A513" s="11"/>
+      <c r="B513" s="11"/>
     </row>
     <row r="514" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A514" s="10"/>
-      <c r="B514" s="10"/>
+      <c r="A514" s="11"/>
+      <c r="B514" s="11"/>
     </row>
     <row r="515" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A515" s="10"/>
-      <c r="B515" s="10"/>
+      <c r="A515" s="11"/>
+      <c r="B515" s="11"/>
     </row>
     <row r="516" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A516" s="10"/>
-      <c r="B516" s="10"/>
+      <c r="A516" s="11"/>
+      <c r="B516" s="11"/>
     </row>
     <row r="517" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A517" s="10"/>
-      <c r="B517" s="10"/>
+      <c r="A517" s="11"/>
+      <c r="B517" s="11"/>
     </row>
     <row r="518" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A518" s="10"/>
-      <c r="B518" s="10"/>
+      <c r="A518" s="11"/>
+      <c r="B518" s="11"/>
     </row>
     <row r="519" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A519" s="10"/>
-      <c r="B519" s="10"/>
+      <c r="A519" s="11"/>
+      <c r="B519" s="11"/>
     </row>
     <row r="520" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A520" s="10"/>
-      <c r="B520" s="10"/>
+      <c r="A520" s="11"/>
+      <c r="B520" s="11"/>
     </row>
     <row r="521" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A521" s="10"/>
-      <c r="B521" s="10"/>
+      <c r="A521" s="11"/>
+      <c r="B521" s="11"/>
     </row>
     <row r="522" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A522" s="10"/>
-      <c r="B522" s="10"/>
+      <c r="A522" s="11"/>
+      <c r="B522" s="11"/>
     </row>
     <row r="523" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A523" s="10"/>
-      <c r="B523" s="10"/>
+      <c r="A523" s="11"/>
+      <c r="B523" s="11"/>
     </row>
     <row r="524" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A524" s="10"/>
-      <c r="B524" s="10"/>
+      <c r="A524" s="11"/>
+      <c r="B524" s="11"/>
     </row>
     <row r="525" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A525" s="10"/>
-      <c r="B525" s="10"/>
+      <c r="A525" s="11"/>
+      <c r="B525" s="11"/>
     </row>
     <row r="526" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A526" s="10"/>
-      <c r="B526" s="10"/>
+      <c r="A526" s="11"/>
+      <c r="B526" s="11"/>
     </row>
     <row r="527" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A527" s="10"/>
-      <c r="B527" s="10"/>
+      <c r="A527" s="11"/>
+      <c r="B527" s="11"/>
     </row>
     <row r="528" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A528" s="10"/>
-      <c r="B528" s="10"/>
+      <c r="A528" s="11"/>
+      <c r="B528" s="11"/>
     </row>
     <row r="529" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A529" s="10"/>
-      <c r="B529" s="10"/>
+      <c r="A529" s="11"/>
+      <c r="B529" s="11"/>
     </row>
     <row r="530" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A530" s="10"/>
-      <c r="B530" s="10"/>
+      <c r="A530" s="11"/>
+      <c r="B530" s="11"/>
     </row>
     <row r="531" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A531" s="10"/>
-      <c r="B531" s="10"/>
+      <c r="A531" s="11"/>
+      <c r="B531" s="11"/>
     </row>
     <row r="532" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A532" s="10"/>
-      <c r="B532" s="10"/>
+      <c r="A532" s="11"/>
+      <c r="B532" s="11"/>
     </row>
     <row r="533" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A533" s="10"/>
-      <c r="B533" s="10"/>
+      <c r="A533" s="11"/>
+      <c r="B533" s="11"/>
     </row>
     <row r="534" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A534" s="10"/>
-      <c r="B534" s="10"/>
+      <c r="A534" s="11"/>
+      <c r="B534" s="11"/>
     </row>
     <row r="535" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A535" s="10"/>
-      <c r="B535" s="10"/>
+      <c r="A535" s="11"/>
+      <c r="B535" s="11"/>
     </row>
     <row r="536" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A536" s="10"/>
-      <c r="B536" s="10"/>
+      <c r="A536" s="11"/>
+      <c r="B536" s="11"/>
     </row>
     <row r="537" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A537" s="10"/>
-      <c r="B537" s="10"/>
+      <c r="A537" s="11"/>
+      <c r="B537" s="11"/>
     </row>
     <row r="538" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A538" s="10"/>
-      <c r="B538" s="10"/>
+      <c r="A538" s="11"/>
+      <c r="B538" s="11"/>
     </row>
     <row r="539" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A539" s="10"/>
-      <c r="B539" s="10"/>
+      <c r="A539" s="11"/>
+      <c r="B539" s="11"/>
     </row>
     <row r="540" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A540" s="10"/>
-      <c r="B540" s="10"/>
+      <c r="A540" s="11"/>
+      <c r="B540" s="11"/>
     </row>
     <row r="541" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A541" s="10"/>
-      <c r="B541" s="10"/>
+      <c r="A541" s="11"/>
+      <c r="B541" s="11"/>
     </row>
     <row r="542" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A542" s="10"/>
-      <c r="B542" s="10"/>
+      <c r="A542" s="11"/>
+      <c r="B542" s="11"/>
     </row>
     <row r="543" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A543" s="10"/>
-      <c r="B543" s="10"/>
+      <c r="A543" s="11"/>
+      <c r="B543" s="11"/>
     </row>
     <row r="544" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A544" s="10"/>
-      <c r="B544" s="10"/>
+      <c r="A544" s="11"/>
+      <c r="B544" s="11"/>
     </row>
     <row r="545" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A545" s="10"/>
-      <c r="B545" s="10"/>
+      <c r="A545" s="11"/>
+      <c r="B545" s="11"/>
     </row>
     <row r="546" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A546" s="10"/>
-      <c r="B546" s="10"/>
+      <c r="A546" s="11"/>
+      <c r="B546" s="11"/>
     </row>
     <row r="547" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A547" s="10"/>
-      <c r="B547" s="10"/>
+      <c r="A547" s="11"/>
+      <c r="B547" s="11"/>
     </row>
     <row r="548" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A548" s="10"/>
-      <c r="B548" s="10"/>
+      <c r="A548" s="11"/>
+      <c r="B548" s="11"/>
     </row>
     <row r="549" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A549" s="10"/>
-      <c r="B549" s="10"/>
+      <c r="A549" s="11"/>
+      <c r="B549" s="11"/>
     </row>
     <row r="550" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A550" s="10"/>
-      <c r="B550" s="10"/>
+      <c r="A550" s="11"/>
+      <c r="B550" s="11"/>
     </row>
     <row r="551" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A551" s="10"/>
-      <c r="B551" s="10"/>
+      <c r="A551" s="11"/>
+      <c r="B551" s="11"/>
     </row>
     <row r="552" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A552" s="10"/>
-      <c r="B552" s="10"/>
+      <c r="A552" s="11"/>
+      <c r="B552" s="11"/>
     </row>
     <row r="553" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A553" s="10"/>
-      <c r="B553" s="10"/>
+      <c r="A553" s="11"/>
+      <c r="B553" s="11"/>
     </row>
     <row r="554" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A554" s="10"/>
-      <c r="B554" s="10"/>
+      <c r="A554" s="11"/>
+      <c r="B554" s="11"/>
     </row>
     <row r="555" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A555" s="10"/>
-      <c r="B555" s="10"/>
+      <c r="A555" s="11"/>
+      <c r="B555" s="11"/>
     </row>
     <row r="556" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A556" s="10"/>
-      <c r="B556" s="10"/>
+      <c r="A556" s="11"/>
+      <c r="B556" s="11"/>
     </row>
     <row r="557" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A557" s="10"/>
-      <c r="B557" s="10"/>
+      <c r="A557" s="11"/>
+      <c r="B557" s="11"/>
     </row>
     <row r="558" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A558" s="10"/>
-      <c r="B558" s="10"/>
+      <c r="A558" s="11"/>
+      <c r="B558" s="11"/>
     </row>
     <row r="559" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A559" s="10"/>
-      <c r="B559" s="10"/>
+      <c r="A559" s="11"/>
+      <c r="B559" s="11"/>
     </row>
     <row r="560" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A560" s="10"/>
-      <c r="B560" s="10"/>
+      <c r="A560" s="11"/>
+      <c r="B560" s="11"/>
     </row>
     <row r="561" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A561" s="10"/>
-      <c r="B561" s="10"/>
+      <c r="A561" s="11"/>
+      <c r="B561" s="11"/>
     </row>
     <row r="562" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A562" s="10"/>
-      <c r="B562" s="10"/>
+      <c r="A562" s="11"/>
+      <c r="B562" s="11"/>
     </row>
     <row r="563" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A563" s="10"/>
-      <c r="B563" s="10"/>
+      <c r="A563" s="11"/>
+      <c r="B563" s="11"/>
     </row>
     <row r="564" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A564" s="10"/>
-      <c r="B564" s="10"/>
+      <c r="A564" s="11"/>
+      <c r="B564" s="11"/>
     </row>
     <row r="565" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A565" s="10"/>
-      <c r="B565" s="10"/>
+      <c r="A565" s="11"/>
+      <c r="B565" s="11"/>
     </row>
     <row r="566" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A566" s="10"/>
-      <c r="B566" s="10"/>
+      <c r="A566" s="11"/>
+      <c r="B566" s="11"/>
     </row>
     <row r="567" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A567" s="10"/>
-      <c r="B567" s="10"/>
+      <c r="A567" s="11"/>
+      <c r="B567" s="11"/>
     </row>
     <row r="568" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A568" s="10"/>
-      <c r="B568" s="10"/>
+      <c r="A568" s="11"/>
+      <c r="B568" s="11"/>
     </row>
     <row r="569" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A569" s="10"/>
-      <c r="B569" s="10"/>
+      <c r="A569" s="11"/>
+      <c r="B569" s="11"/>
     </row>
     <row r="570" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A570" s="10"/>
-      <c r="B570" s="10"/>
+      <c r="A570" s="11"/>
+      <c r="B570" s="11"/>
     </row>
     <row r="571" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A571" s="10"/>
-      <c r="B571" s="10"/>
+      <c r="A571" s="11"/>
+      <c r="B571" s="11"/>
     </row>
     <row r="572" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A572" s="10"/>
-      <c r="B572" s="10"/>
+      <c r="A572" s="11"/>
+      <c r="B572" s="11"/>
     </row>
     <row r="573" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A573" s="10"/>
-      <c r="B573" s="10"/>
+      <c r="A573" s="11"/>
+      <c r="B573" s="11"/>
     </row>
     <row r="574" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A574" s="10"/>
-      <c r="B574" s="10"/>
+      <c r="A574" s="11"/>
+      <c r="B574" s="11"/>
     </row>
     <row r="575" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A575" s="10"/>
-      <c r="B575" s="10"/>
+      <c r="A575" s="11"/>
+      <c r="B575" s="11"/>
     </row>
     <row r="576" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A576" s="10"/>
-      <c r="B576" s="10"/>
+      <c r="A576" s="11"/>
+      <c r="B576" s="11"/>
     </row>
     <row r="577" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A577" s="10"/>
-      <c r="B577" s="10"/>
+      <c r="A577" s="11"/>
+      <c r="B577" s="11"/>
     </row>
     <row r="578" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A578" s="10"/>
-      <c r="B578" s="10"/>
+      <c r="A578" s="11"/>
+      <c r="B578" s="11"/>
     </row>
     <row r="579" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A579" s="10"/>
-      <c r="B579" s="10"/>
+      <c r="A579" s="11"/>
+      <c r="B579" s="11"/>
     </row>
     <row r="580" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A580" s="10"/>
-      <c r="B580" s="10"/>
+      <c r="A580" s="11"/>
+      <c r="B580" s="11"/>
     </row>
     <row r="581" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A581" s="10"/>
-      <c r="B581" s="10"/>
+      <c r="A581" s="11"/>
+      <c r="B581" s="11"/>
     </row>
     <row r="582" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A582" s="10"/>
-      <c r="B582" s="10"/>
+      <c r="A582" s="11"/>
+      <c r="B582" s="11"/>
     </row>
     <row r="583" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A583" s="10"/>
-      <c r="B583" s="10"/>
+      <c r="A583" s="11"/>
+      <c r="B583" s="11"/>
     </row>
     <row r="584" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A584" s="10"/>
-      <c r="B584" s="10"/>
+      <c r="A584" s="11"/>
+      <c r="B584" s="11"/>
     </row>
     <row r="585" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A585" s="10"/>
-      <c r="B585" s="10"/>
+      <c r="A585" s="11"/>
+      <c r="B585" s="11"/>
     </row>
     <row r="586" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A586" s="10"/>
-      <c r="B586" s="10"/>
+      <c r="A586" s="11"/>
+      <c r="B586" s="11"/>
     </row>
     <row r="587" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A587" s="10"/>
-      <c r="B587" s="10"/>
+      <c r="A587" s="11"/>
+      <c r="B587" s="11"/>
     </row>
     <row r="588" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A588" s="10"/>
-      <c r="B588" s="10"/>
+      <c r="A588" s="11"/>
+      <c r="B588" s="11"/>
     </row>
     <row r="589" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A589" s="10"/>
-      <c r="B589" s="10"/>
+      <c r="A589" s="11"/>
+      <c r="B589" s="11"/>
     </row>
     <row r="590" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A590" s="10"/>
-      <c r="B590" s="10"/>
+      <c r="A590" s="11"/>
+      <c r="B590" s="11"/>
     </row>
     <row r="591" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A591" s="10"/>
-      <c r="B591" s="10"/>
+      <c r="A591" s="11"/>
+      <c r="B591" s="11"/>
     </row>
     <row r="592" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A592" s="10"/>
-      <c r="B592" s="10"/>
+      <c r="A592" s="11"/>
+      <c r="B592" s="11"/>
     </row>
     <row r="593" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A593" s="10"/>
-      <c r="B593" s="10"/>
+      <c r="A593" s="11"/>
+      <c r="B593" s="11"/>
     </row>
     <row r="594" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A594" s="10"/>
-      <c r="B594" s="10"/>
+      <c r="A594" s="11"/>
+      <c r="B594" s="11"/>
     </row>
     <row r="595" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A595" s="10"/>
-      <c r="B595" s="10"/>
+      <c r="A595" s="11"/>
+      <c r="B595" s="11"/>
     </row>
     <row r="596" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A596" s="10"/>
-      <c r="B596" s="10"/>
+      <c r="A596" s="11"/>
+      <c r="B596" s="11"/>
     </row>
     <row r="597" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A597" s="10"/>
-      <c r="B597" s="10"/>
+      <c r="A597" s="11"/>
+      <c r="B597" s="11"/>
     </row>
     <row r="598" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A598" s="10"/>
-      <c r="B598" s="10"/>
+      <c r="A598" s="11"/>
+      <c r="B598" s="11"/>
     </row>
     <row r="599" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A599" s="10"/>
-      <c r="B599" s="10"/>
+      <c r="A599" s="11"/>
+      <c r="B599" s="11"/>
     </row>
     <row r="600" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A600" s="10"/>
-      <c r="B600" s="10"/>
+      <c r="A600" s="11"/>
+      <c r="B600" s="11"/>
     </row>
     <row r="601" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A601" s="10"/>
-      <c r="B601" s="10"/>
+      <c r="A601" s="11"/>
+      <c r="B601" s="11"/>
     </row>
     <row r="602" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A602" s="10"/>
-      <c r="B602" s="10"/>
+      <c r="A602" s="11"/>
+      <c r="B602" s="11"/>
     </row>
     <row r="603" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A603" s="10"/>
-      <c r="B603" s="10"/>
+      <c r="A603" s="11"/>
+      <c r="B603" s="11"/>
     </row>
     <row r="604" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A604" s="10"/>
-      <c r="B604" s="10"/>
+      <c r="A604" s="11"/>
+      <c r="B604" s="11"/>
     </row>
     <row r="605" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A605" s="10"/>
-      <c r="B605" s="10"/>
+      <c r="A605" s="11"/>
+      <c r="B605" s="11"/>
     </row>
     <row r="606" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A606" s="10"/>
-      <c r="B606" s="10"/>
+      <c r="A606" s="11"/>
+      <c r="B606" s="11"/>
     </row>
     <row r="607" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A607" s="10"/>
-      <c r="B607" s="10"/>
+      <c r="A607" s="11"/>
+      <c r="B607" s="11"/>
     </row>
     <row r="608" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A608" s="10"/>
-      <c r="B608" s="10"/>
+      <c r="A608" s="11"/>
+      <c r="B608" s="11"/>
     </row>
     <row r="609" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A609" s="10"/>
-      <c r="B609" s="10"/>
+      <c r="A609" s="11"/>
+      <c r="B609" s="11"/>
     </row>
     <row r="610" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A610" s="10"/>
-      <c r="B610" s="10"/>
+      <c r="A610" s="11"/>
+      <c r="B610" s="11"/>
     </row>
     <row r="611" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A611" s="10"/>
-      <c r="B611" s="10"/>
+      <c r="A611" s="11"/>
+      <c r="B611" s="11"/>
     </row>
     <row r="612" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A612" s="10"/>
-      <c r="B612" s="10"/>
+      <c r="A612" s="11"/>
+      <c r="B612" s="11"/>
     </row>
     <row r="613" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A613" s="10"/>
-      <c r="B613" s="10"/>
+      <c r="A613" s="11"/>
+      <c r="B613" s="11"/>
     </row>
     <row r="614" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A614" s="10"/>
-      <c r="B614" s="10"/>
+      <c r="A614" s="11"/>
+      <c r="B614" s="11"/>
     </row>
     <row r="615" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A615" s="10"/>
-      <c r="B615" s="10"/>
+      <c r="A615" s="11"/>
+      <c r="B615" s="11"/>
     </row>
     <row r="616" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A616" s="10"/>
-      <c r="B616" s="10"/>
+      <c r="A616" s="11"/>
+      <c r="B616" s="11"/>
     </row>
     <row r="617" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A617" s="10"/>
-      <c r="B617" s="10"/>
+      <c r="A617" s="11"/>
+      <c r="B617" s="11"/>
     </row>
     <row r="618" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A618" s="10"/>
-      <c r="B618" s="10"/>
+      <c r="A618" s="11"/>
+      <c r="B618" s="11"/>
     </row>
     <row r="619" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A619" s="10"/>
-      <c r="B619" s="10"/>
+      <c r="A619" s="11"/>
+      <c r="B619" s="11"/>
     </row>
     <row r="620" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A620" s="10"/>
-      <c r="B620" s="10"/>
+      <c r="A620" s="11"/>
+      <c r="B620" s="11"/>
     </row>
     <row r="621" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A621" s="10"/>
-      <c r="B621" s="10"/>
+      <c r="A621" s="11"/>
+      <c r="B621" s="11"/>
     </row>
     <row r="622" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A622" s="10"/>
-      <c r="B622" s="10"/>
+      <c r="A622" s="11"/>
+      <c r="B622" s="11"/>
     </row>
     <row r="623" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A623" s="10"/>
-      <c r="B623" s="10"/>
+      <c r="A623" s="11"/>
+      <c r="B623" s="11"/>
     </row>
     <row r="624" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A624" s="10"/>
-      <c r="B624" s="10"/>
+      <c r="A624" s="11"/>
+      <c r="B624" s="11"/>
     </row>
     <row r="625" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A625" s="10"/>
-      <c r="B625" s="10"/>
+      <c r="A625" s="11"/>
+      <c r="B625" s="11"/>
     </row>
     <row r="626" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A626" s="10"/>
-      <c r="B626" s="10"/>
+      <c r="A626" s="11"/>
+      <c r="B626" s="11"/>
     </row>
     <row r="627" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A627" s="10"/>
-      <c r="B627" s="10"/>
+      <c r="A627" s="11"/>
+      <c r="B627" s="11"/>
     </row>
     <row r="628" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A628" s="10"/>
-      <c r="B628" s="10"/>
+      <c r="A628" s="11"/>
+      <c r="B628" s="11"/>
     </row>
     <row r="629" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A629" s="10"/>
-      <c r="B629" s="10"/>
+      <c r="A629" s="11"/>
+      <c r="B629" s="11"/>
     </row>
     <row r="630" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A630" s="10"/>
-      <c r="B630" s="10"/>
+      <c r="A630" s="11"/>
+      <c r="B630" s="11"/>
     </row>
     <row r="631" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A631" s="10"/>
-      <c r="B631" s="10"/>
+      <c r="A631" s="11"/>
+      <c r="B631" s="11"/>
     </row>
     <row r="632" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A632" s="10"/>
-      <c r="B632" s="10"/>
+      <c r="A632" s="11"/>
+      <c r="B632" s="11"/>
     </row>
     <row r="633" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A633" s="10"/>
-      <c r="B633" s="10"/>
+      <c r="A633" s="11"/>
+      <c r="B633" s="11"/>
     </row>
     <row r="634" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A634" s="10"/>
-      <c r="B634" s="10"/>
+      <c r="A634" s="11"/>
+      <c r="B634" s="11"/>
     </row>
     <row r="635" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A635" s="10"/>
-      <c r="B635" s="10"/>
+      <c r="A635" s="11"/>
+      <c r="B635" s="11"/>
     </row>
     <row r="636" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A636" s="10"/>
-      <c r="B636" s="10"/>
+      <c r="A636" s="11"/>
+      <c r="B636" s="11"/>
     </row>
     <row r="637" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A637" s="10"/>
-      <c r="B637" s="10"/>
+      <c r="A637" s="11"/>
+      <c r="B637" s="11"/>
     </row>
     <row r="638" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A638" s="10"/>
-      <c r="B638" s="10"/>
+      <c r="A638" s="11"/>
+      <c r="B638" s="11"/>
     </row>
     <row r="639" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A639" s="10"/>
-      <c r="B639" s="10"/>
+      <c r="A639" s="11"/>
+      <c r="B639" s="11"/>
     </row>
     <row r="640" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A640" s="10"/>
-      <c r="B640" s="10"/>
+      <c r="A640" s="11"/>
+      <c r="B640" s="11"/>
     </row>
     <row r="641" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A641" s="10"/>
-      <c r="B641" s="10"/>
+      <c r="A641" s="11"/>
+      <c r="B641" s="11"/>
     </row>
     <row r="642" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A642" s="10"/>
-      <c r="B642" s="10"/>
+      <c r="A642" s="11"/>
+      <c r="B642" s="11"/>
     </row>
     <row r="643" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A643" s="10"/>
-      <c r="B643" s="10"/>
+      <c r="A643" s="11"/>
+      <c r="B643" s="11"/>
     </row>
     <row r="644" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A644" s="10"/>
-      <c r="B644" s="10"/>
+      <c r="A644" s="11"/>
+      <c r="B644" s="11"/>
     </row>
     <row r="645" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A645" s="10"/>
-      <c r="B645" s="10"/>
+      <c r="A645" s="11"/>
+      <c r="B645" s="11"/>
     </row>
     <row r="646" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A646" s="10"/>
-      <c r="B646" s="10"/>
+      <c r="A646" s="11"/>
+      <c r="B646" s="11"/>
     </row>
     <row r="647" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A647" s="10"/>
-      <c r="B647" s="10"/>
+      <c r="A647" s="11"/>
+      <c r="B647" s="11"/>
     </row>
     <row r="648" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A648" s="10"/>
-      <c r="B648" s="10"/>
+      <c r="A648" s="11"/>
+      <c r="B648" s="11"/>
     </row>
     <row r="649" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A649" s="10"/>
-      <c r="B649" s="10"/>
+      <c r="A649" s="11"/>
+      <c r="B649" s="11"/>
     </row>
     <row r="650" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A650" s="10"/>
-      <c r="B650" s="10"/>
+      <c r="A650" s="11"/>
+      <c r="B650" s="11"/>
     </row>
     <row r="651" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A651" s="10"/>
-      <c r="B651" s="10"/>
+      <c r="A651" s="11"/>
+      <c r="B651" s="11"/>
     </row>
     <row r="652" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A652" s="10"/>
-      <c r="B652" s="10"/>
+      <c r="A652" s="11"/>
+      <c r="B652" s="11"/>
     </row>
     <row r="653" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A653" s="10"/>
-      <c r="B653" s="10"/>
+      <c r="A653" s="11"/>
+      <c r="B653" s="11"/>
     </row>
     <row r="654" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A654" s="10"/>
-      <c r="B654" s="10"/>
+      <c r="A654" s="11"/>
+      <c r="B654" s="11"/>
     </row>
     <row r="655" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A655" s="10"/>
-      <c r="B655" s="10"/>
+      <c r="A655" s="11"/>
+      <c r="B655" s="11"/>
     </row>
     <row r="656" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A656" s="10"/>
-      <c r="B656" s="10"/>
+      <c r="A656" s="11"/>
+      <c r="B656" s="11"/>
     </row>
     <row r="657" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A657" s="10"/>
-      <c r="B657" s="10"/>
+      <c r="A657" s="11"/>
+      <c r="B657" s="11"/>
     </row>
     <row r="658" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A658" s="10"/>
-      <c r="B658" s="10"/>
+      <c r="A658" s="11"/>
+      <c r="B658" s="11"/>
     </row>
     <row r="659" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A659" s="10"/>
-      <c r="B659" s="10"/>
+      <c r="A659" s="11"/>
+      <c r="B659" s="11"/>
     </row>
     <row r="660" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A660" s="10"/>
-      <c r="B660" s="10"/>
+      <c r="A660" s="11"/>
+      <c r="B660" s="11"/>
     </row>
     <row r="661" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A661" s="10"/>
-      <c r="B661" s="10"/>
+      <c r="A661" s="11"/>
+      <c r="B661" s="11"/>
     </row>
     <row r="662" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A662" s="10"/>
-      <c r="B662" s="10"/>
+      <c r="A662" s="11"/>
+      <c r="B662" s="11"/>
     </row>
     <row r="663" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A663" s="10"/>
-      <c r="B663" s="10"/>
+      <c r="A663" s="11"/>
+      <c r="B663" s="11"/>
     </row>
     <row r="664" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A664" s="10"/>
-      <c r="B664" s="10"/>
+      <c r="A664" s="11"/>
+      <c r="B664" s="11"/>
     </row>
     <row r="665" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A665" s="10"/>
-      <c r="B665" s="10"/>
+      <c r="A665" s="11"/>
+      <c r="B665" s="11"/>
     </row>
     <row r="666" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A666" s="10"/>
-      <c r="B666" s="10"/>
+      <c r="A666" s="11"/>
+      <c r="B666" s="11"/>
     </row>
     <row r="667" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A667" s="10"/>
-      <c r="B667" s="10"/>
+      <c r="A667" s="11"/>
+      <c r="B667" s="11"/>
     </row>
     <row r="668" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A668" s="10"/>
-      <c r="B668" s="10"/>
+      <c r="A668" s="11"/>
+      <c r="B668" s="11"/>
     </row>
     <row r="669" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A669" s="10"/>
-      <c r="B669" s="10"/>
+      <c r="A669" s="11"/>
+      <c r="B669" s="11"/>
     </row>
     <row r="670" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A670" s="10"/>
-      <c r="B670" s="10"/>
+      <c r="A670" s="11"/>
+      <c r="B670" s="11"/>
     </row>
     <row r="671" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A671" s="10"/>
-      <c r="B671" s="10"/>
+      <c r="A671" s="11"/>
+      <c r="B671" s="11"/>
     </row>
     <row r="672" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A672" s="10"/>
-      <c r="B672" s="10"/>
+      <c r="A672" s="11"/>
+      <c r="B672" s="11"/>
     </row>
     <row r="673" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A673" s="10"/>
-      <c r="B673" s="10"/>
+      <c r="A673" s="11"/>
+      <c r="B673" s="11"/>
     </row>
     <row r="674" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A674" s="10"/>
-      <c r="B674" s="10"/>
+      <c r="A674" s="11"/>
+      <c r="B674" s="11"/>
     </row>
     <row r="675" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A675" s="10"/>
-      <c r="B675" s="10"/>
+      <c r="A675" s="11"/>
+      <c r="B675" s="11"/>
     </row>
     <row r="676" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A676" s="10"/>
-      <c r="B676" s="10"/>
+      <c r="A676" s="11"/>
+      <c r="B676" s="11"/>
     </row>
     <row r="677" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A677" s="10"/>
-      <c r="B677" s="10"/>
+      <c r="A677" s="11"/>
+      <c r="B677" s="11"/>
     </row>
     <row r="678" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A678" s="10"/>
-      <c r="B678" s="10"/>
+      <c r="A678" s="11"/>
+      <c r="B678" s="11"/>
     </row>
     <row r="679" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A679" s="10"/>
-      <c r="B679" s="10"/>
+      <c r="A679" s="11"/>
+      <c r="B679" s="11"/>
     </row>
     <row r="680" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A680" s="10"/>
-      <c r="B680" s="10"/>
+      <c r="A680" s="11"/>
+      <c r="B680" s="11"/>
     </row>
     <row r="681" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A681" s="10"/>
-      <c r="B681" s="10"/>
+      <c r="A681" s="11"/>
+      <c r="B681" s="11"/>
     </row>
     <row r="682" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A682" s="10"/>
-      <c r="B682" s="10"/>
+      <c r="A682" s="11"/>
+      <c r="B682" s="11"/>
     </row>
     <row r="683" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A683" s="10"/>
-      <c r="B683" s="10"/>
+      <c r="A683" s="11"/>
+      <c r="B683" s="11"/>
     </row>
     <row r="684" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A684" s="10"/>
-      <c r="B684" s="10"/>
+      <c r="A684" s="11"/>
+      <c r="B684" s="11"/>
     </row>
     <row r="685" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A685" s="10"/>
-      <c r="B685" s="10"/>
+      <c r="A685" s="11"/>
+      <c r="B685" s="11"/>
     </row>
     <row r="686" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A686" s="10"/>
-      <c r="B686" s="10"/>
+      <c r="A686" s="11"/>
+      <c r="B686" s="11"/>
     </row>
     <row r="687" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A687" s="10"/>
-      <c r="B687" s="10"/>
+      <c r="A687" s="11"/>
+      <c r="B687" s="11"/>
     </row>
     <row r="688" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A688" s="10"/>
-      <c r="B688" s="10"/>
+      <c r="A688" s="11"/>
+      <c r="B688" s="11"/>
     </row>
     <row r="689" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A689" s="10"/>
-      <c r="B689" s="10"/>
+      <c r="A689" s="11"/>
+      <c r="B689" s="11"/>
     </row>
     <row r="690" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A690" s="10"/>
-      <c r="B690" s="10"/>
+      <c r="A690" s="11"/>
+      <c r="B690" s="11"/>
     </row>
     <row r="691" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A691" s="10"/>
-      <c r="B691" s="10"/>
+      <c r="A691" s="11"/>
+      <c r="B691" s="11"/>
     </row>
     <row r="692" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A692" s="10"/>
-      <c r="B692" s="10"/>
+      <c r="A692" s="11"/>
+      <c r="B692" s="11"/>
     </row>
     <row r="693" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A693" s="10"/>
-      <c r="B693" s="10"/>
+      <c r="A693" s="11"/>
+      <c r="B693" s="11"/>
     </row>
     <row r="694" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A694" s="10"/>
-      <c r="B694" s="10"/>
+      <c r="A694" s="11"/>
+      <c r="B694" s="11"/>
     </row>
     <row r="695" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A695" s="10"/>
-      <c r="B695" s="10"/>
+      <c r="A695" s="11"/>
+      <c r="B695" s="11"/>
     </row>
     <row r="696" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A696" s="10"/>
-      <c r="B696" s="10"/>
+      <c r="A696" s="11"/>
+      <c r="B696" s="11"/>
     </row>
     <row r="697" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A697" s="10"/>
-      <c r="B697" s="10"/>
+      <c r="A697" s="11"/>
+      <c r="B697" s="11"/>
     </row>
     <row r="698" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A698" s="10"/>
-      <c r="B698" s="10"/>
+      <c r="A698" s="11"/>
+      <c r="B698" s="11"/>
     </row>
     <row r="699" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A699" s="10"/>
-      <c r="B699" s="10"/>
+      <c r="A699" s="11"/>
+      <c r="B699" s="11"/>
     </row>
     <row r="700" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A700" s="10"/>
-      <c r="B700" s="10"/>
+      <c r="A700" s="11"/>
+      <c r="B700" s="11"/>
     </row>
     <row r="701" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A701" s="10"/>
-      <c r="B701" s="10"/>
+      <c r="A701" s="11"/>
+      <c r="B701" s="11"/>
     </row>
     <row r="702" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A702" s="10"/>
-      <c r="B702" s="10"/>
+      <c r="A702" s="11"/>
+      <c r="B702" s="11"/>
     </row>
     <row r="703" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A703" s="10"/>
-      <c r="B703" s="10"/>
+      <c r="A703" s="11"/>
+      <c r="B703" s="11"/>
     </row>
     <row r="704" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A704" s="10"/>
-      <c r="B704" s="10"/>
+      <c r="A704" s="11"/>
+      <c r="B704" s="11"/>
     </row>
     <row r="705" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A705" s="10"/>
-      <c r="B705" s="10"/>
+      <c r="A705" s="11"/>
+      <c r="B705" s="11"/>
     </row>
     <row r="706" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A706" s="10"/>
-      <c r="B706" s="10"/>
+      <c r="A706" s="11"/>
+      <c r="B706" s="11"/>
     </row>
     <row r="707" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A707" s="10"/>
-      <c r="B707" s="10"/>
+      <c r="A707" s="11"/>
+      <c r="B707" s="11"/>
     </row>
     <row r="708" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A708" s="10"/>
-      <c r="B708" s="10"/>
+      <c r="A708" s="11"/>
+      <c r="B708" s="11"/>
     </row>
     <row r="709" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A709" s="10"/>
-      <c r="B709" s="10"/>
+      <c r="A709" s="11"/>
+      <c r="B709" s="11"/>
     </row>
     <row r="710" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A710" s="10"/>
-      <c r="B710" s="10"/>
+      <c r="A710" s="11"/>
+      <c r="B710" s="11"/>
     </row>
     <row r="711" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A711" s="10"/>
-      <c r="B711" s="10"/>
+      <c r="A711" s="11"/>
+      <c r="B711" s="11"/>
     </row>
     <row r="712" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A712" s="10"/>
-      <c r="B712" s="10"/>
+      <c r="A712" s="11"/>
+      <c r="B712" s="11"/>
     </row>
     <row r="713" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A713" s="10"/>
-      <c r="B713" s="10"/>
+      <c r="A713" s="11"/>
+      <c r="B713" s="11"/>
     </row>
     <row r="714" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A714" s="10"/>
-      <c r="B714" s="10"/>
+      <c r="A714" s="11"/>
+      <c r="B714" s="11"/>
     </row>
     <row r="715" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A715" s="10"/>
-      <c r="B715" s="10"/>
+      <c r="A715" s="11"/>
+      <c r="B715" s="11"/>
     </row>
     <row r="716" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A716" s="10"/>
-      <c r="B716" s="10"/>
+      <c r="A716" s="11"/>
+      <c r="B716" s="11"/>
     </row>
     <row r="717" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A717" s="10"/>
-      <c r="B717" s="10"/>
+      <c r="A717" s="11"/>
+      <c r="B717" s="11"/>
     </row>
     <row r="718" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A718" s="10"/>
-      <c r="B718" s="10"/>
+      <c r="A718" s="11"/>
+      <c r="B718" s="11"/>
     </row>
     <row r="719" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A719" s="10"/>
-      <c r="B719" s="10"/>
+      <c r="A719" s="11"/>
+      <c r="B719" s="11"/>
     </row>
     <row r="720" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A720" s="10"/>
-      <c r="B720" s="10"/>
+      <c r="A720" s="11"/>
+      <c r="B720" s="11"/>
     </row>
     <row r="721" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A721" s="10"/>
-      <c r="B721" s="10"/>
+      <c r="A721" s="11"/>
+      <c r="B721" s="11"/>
     </row>
     <row r="722" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A722" s="10"/>
-      <c r="B722" s="10"/>
+      <c r="A722" s="11"/>
+      <c r="B722" s="11"/>
     </row>
     <row r="723" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A723" s="10"/>
-      <c r="B723" s="10"/>
+      <c r="A723" s="11"/>
+      <c r="B723" s="11"/>
     </row>
     <row r="724" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A724" s="10"/>
-      <c r="B724" s="10"/>
+      <c r="A724" s="11"/>
+      <c r="B724" s="11"/>
     </row>
     <row r="725" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A725" s="10"/>
-      <c r="B725" s="10"/>
+      <c r="A725" s="11"/>
+      <c r="B725" s="11"/>
     </row>
     <row r="726" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A726" s="10"/>
-      <c r="B726" s="10"/>
+      <c r="A726" s="11"/>
+      <c r="B726" s="11"/>
     </row>
     <row r="727" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A727" s="10"/>
-      <c r="B727" s="10"/>
+      <c r="A727" s="11"/>
+      <c r="B727" s="11"/>
     </row>
     <row r="728" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A728" s="10"/>
-      <c r="B728" s="10"/>
+      <c r="A728" s="11"/>
+      <c r="B728" s="11"/>
     </row>
     <row r="729" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A729" s="10"/>
-      <c r="B729" s="10"/>
+      <c r="A729" s="11"/>
+      <c r="B729" s="11"/>
     </row>
     <row r="730" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A730" s="10"/>
-      <c r="B730" s="10"/>
+      <c r="A730" s="11"/>
+      <c r="B730" s="11"/>
     </row>
     <row r="731" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A731" s="10"/>
-      <c r="B731" s="10"/>
+      <c r="A731" s="11"/>
+      <c r="B731" s="11"/>
     </row>
     <row r="732" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A732" s="10"/>
-      <c r="B732" s="10"/>
+      <c r="A732" s="11"/>
+      <c r="B732" s="11"/>
     </row>
     <row r="733" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A733" s="10"/>
-      <c r="B733" s="10"/>
+      <c r="A733" s="11"/>
+      <c r="B733" s="11"/>
     </row>
     <row r="734" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A734" s="10"/>
-      <c r="B734" s="10"/>
+      <c r="A734" s="11"/>
+      <c r="B734" s="11"/>
     </row>
     <row r="735" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A735" s="10"/>
-      <c r="B735" s="10"/>
+      <c r="A735" s="11"/>
+      <c r="B735" s="11"/>
     </row>
     <row r="736" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A736" s="10"/>
-      <c r="B736" s="10"/>
+      <c r="A736" s="11"/>
+      <c r="B736" s="11"/>
     </row>
     <row r="737" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A737" s="10"/>
-      <c r="B737" s="10"/>
+      <c r="A737" s="11"/>
+      <c r="B737" s="11"/>
     </row>
     <row r="738" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A738" s="10"/>
-      <c r="B738" s="10"/>
+      <c r="A738" s="11"/>
+      <c r="B738" s="11"/>
     </row>
     <row r="739" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A739" s="10"/>
-      <c r="B739" s="10"/>
+      <c r="A739" s="11"/>
+      <c r="B739" s="11"/>
     </row>
     <row r="740" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A740" s="10"/>
-      <c r="B740" s="10"/>
+      <c r="A740" s="11"/>
+      <c r="B740" s="11"/>
     </row>
     <row r="741" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A741" s="10"/>
-      <c r="B741" s="10"/>
+      <c r="A741" s="11"/>
+      <c r="B741" s="11"/>
     </row>
     <row r="742" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A742" s="10"/>
-      <c r="B742" s="10"/>
+      <c r="A742" s="11"/>
+      <c r="B742" s="11"/>
     </row>
     <row r="743" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A743" s="10"/>
-      <c r="B743" s="10"/>
+      <c r="A743" s="11"/>
+      <c r="B743" s="11"/>
     </row>
     <row r="744" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A744" s="10"/>
-      <c r="B744" s="10"/>
+      <c r="A744" s="11"/>
+      <c r="B744" s="11"/>
     </row>
     <row r="745" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A745" s="10"/>
-      <c r="B745" s="10"/>
+      <c r="A745" s="11"/>
+      <c r="B745" s="11"/>
     </row>
     <row r="746" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A746" s="10"/>
-      <c r="B746" s="10"/>
+      <c r="A746" s="11"/>
+      <c r="B746" s="11"/>
     </row>
     <row r="747" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A747" s="10"/>
-      <c r="B747" s="10"/>
+      <c r="A747" s="11"/>
+      <c r="B747" s="11"/>
     </row>
     <row r="748" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A748" s="10"/>
-      <c r="B748" s="10"/>
+      <c r="A748" s="11"/>
+      <c r="B748" s="11"/>
     </row>
     <row r="749" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A749" s="10"/>
-      <c r="B749" s="10"/>
+      <c r="A749" s="11"/>
+      <c r="B749" s="11"/>
     </row>
     <row r="750" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A750" s="10"/>
-      <c r="B750" s="10"/>
+      <c r="A750" s="11"/>
+      <c r="B750" s="11"/>
     </row>
     <row r="751" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A751" s="10"/>
-      <c r="B751" s="10"/>
+      <c r="A751" s="11"/>
+      <c r="B751" s="11"/>
     </row>
     <row r="752" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A752" s="10"/>
-      <c r="B752" s="10"/>
+      <c r="A752" s="11"/>
+      <c r="B752" s="11"/>
     </row>
     <row r="753" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A753" s="10"/>
-      <c r="B753" s="10"/>
+      <c r="A753" s="11"/>
+      <c r="B753" s="11"/>
     </row>
     <row r="754" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A754" s="10"/>
-      <c r="B754" s="10"/>
+      <c r="A754" s="11"/>
+      <c r="B754" s="11"/>
     </row>
     <row r="755" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A755" s="10"/>
-      <c r="B755" s="10"/>
+      <c r="A755" s="11"/>
+      <c r="B755" s="11"/>
     </row>
     <row r="756" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A756" s="10"/>
-      <c r="B756" s="10"/>
+      <c r="A756" s="11"/>
+      <c r="B756" s="11"/>
     </row>
     <row r="757" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A757" s="10"/>
-      <c r="B757" s="10"/>
+      <c r="A757" s="11"/>
+      <c r="B757" s="11"/>
     </row>
     <row r="758" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A758" s="10"/>
-      <c r="B758" s="10"/>
+      <c r="A758" s="11"/>
+      <c r="B758" s="11"/>
     </row>
     <row r="759" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A759" s="10"/>
-      <c r="B759" s="10"/>
+      <c r="A759" s="11"/>
+      <c r="B759" s="11"/>
     </row>
     <row r="760" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A760" s="10"/>
-      <c r="B760" s="10"/>
+      <c r="A760" s="11"/>
+      <c r="B760" s="11"/>
     </row>
     <row r="761" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A761" s="10"/>
-      <c r="B761" s="10"/>
+      <c r="A761" s="11"/>
+      <c r="B761" s="11"/>
     </row>
     <row r="762" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A762" s="10"/>
-      <c r="B762" s="10"/>
+      <c r="A762" s="11"/>
+      <c r="B762" s="11"/>
     </row>
     <row r="763" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A763" s="10"/>
-      <c r="B763" s="10"/>
+      <c r="A763" s="11"/>
+      <c r="B763" s="11"/>
     </row>
     <row r="764" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A764" s="10"/>
-      <c r="B764" s="10"/>
+      <c r="A764" s="11"/>
+      <c r="B764" s="11"/>
     </row>
     <row r="765" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A765" s="10"/>
-      <c r="B765" s="10"/>
+      <c r="A765" s="11"/>
+      <c r="B765" s="11"/>
     </row>
     <row r="766" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A766" s="10"/>
-      <c r="B766" s="10"/>
+      <c r="A766" s="11"/>
+      <c r="B766" s="11"/>
     </row>
     <row r="767" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A767" s="10"/>
-      <c r="B767" s="10"/>
+      <c r="A767" s="11"/>
+      <c r="B767" s="11"/>
     </row>
     <row r="768" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A768" s="10"/>
-      <c r="B768" s="10"/>
+      <c r="A768" s="11"/>
+      <c r="B768" s="11"/>
     </row>
     <row r="769" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A769" s="10"/>
-      <c r="B769" s="10"/>
+      <c r="A769" s="11"/>
+      <c r="B769" s="11"/>
     </row>
     <row r="770" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A770" s="10"/>
-      <c r="B770" s="10"/>
+      <c r="A770" s="11"/>
+      <c r="B770" s="11"/>
     </row>
     <row r="771" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A771" s="10"/>
-      <c r="B771" s="10"/>
+      <c r="A771" s="11"/>
+      <c r="B771" s="11"/>
     </row>
     <row r="772" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A772" s="10"/>
-      <c r="B772" s="10"/>
+      <c r="A772" s="11"/>
+      <c r="B772" s="11"/>
     </row>
     <row r="773" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A773" s="10"/>
-      <c r="B773" s="10"/>
+      <c r="A773" s="11"/>
+      <c r="B773" s="11"/>
     </row>
     <row r="774" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A774" s="10"/>
-      <c r="B774" s="10"/>
+      <c r="A774" s="11"/>
+      <c r="B774" s="11"/>
     </row>
     <row r="775" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A775" s="10"/>
-      <c r="B775" s="10"/>
+      <c r="A775" s="11"/>
+      <c r="B775" s="11"/>
     </row>
     <row r="776" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A776" s="10"/>
-      <c r="B776" s="10"/>
+      <c r="A776" s="11"/>
+      <c r="B776" s="11"/>
     </row>
     <row r="777" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A777" s="10"/>
-      <c r="B777" s="10"/>
+      <c r="A777" s="11"/>
+      <c r="B777" s="11"/>
     </row>
     <row r="778" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A778" s="10"/>
-      <c r="B778" s="10"/>
+      <c r="A778" s="11"/>
+      <c r="B778" s="11"/>
     </row>
     <row r="779" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A779" s="10"/>
-      <c r="B779" s="10"/>
+      <c r="A779" s="11"/>
+      <c r="B779" s="11"/>
     </row>
     <row r="780" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A780" s="10"/>
-      <c r="B780" s="10"/>
+      <c r="A780" s="11"/>
+      <c r="B780" s="11"/>
     </row>
     <row r="781" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A781" s="10"/>
-      <c r="B781" s="10"/>
+      <c r="A781" s="11"/>
+      <c r="B781" s="11"/>
     </row>
     <row r="782" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A782" s="10"/>
-      <c r="B782" s="10"/>
+      <c r="A782" s="11"/>
+      <c r="B782" s="11"/>
     </row>
     <row r="783" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A783" s="10"/>
-      <c r="B783" s="10"/>
+      <c r="A783" s="11"/>
+      <c r="B783" s="11"/>
     </row>
     <row r="784" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A784" s="10"/>
-      <c r="B784" s="10"/>
+      <c r="A784" s="11"/>
+      <c r="B784" s="11"/>
     </row>
     <row r="785" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A785" s="10"/>
-      <c r="B785" s="10"/>
+      <c r="A785" s="11"/>
+      <c r="B785" s="11"/>
     </row>
     <row r="786" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A786" s="10"/>
-      <c r="B786" s="10"/>
+      <c r="A786" s="11"/>
+      <c r="B786" s="11"/>
     </row>
     <row r="787" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A787" s="10"/>
-      <c r="B787" s="10"/>
+      <c r="A787" s="11"/>
+      <c r="B787" s="11"/>
     </row>
     <row r="788" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A788" s="10"/>
-      <c r="B788" s="10"/>
+      <c r="A788" s="11"/>
+      <c r="B788" s="11"/>
     </row>
     <row r="789" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A789" s="10"/>
-      <c r="B789" s="10"/>
+      <c r="A789" s="11"/>
+      <c r="B789" s="11"/>
     </row>
     <row r="790" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A790" s="10"/>
-      <c r="B790" s="10"/>
+      <c r="A790" s="11"/>
+      <c r="B790" s="11"/>
     </row>
     <row r="791" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A791" s="10"/>
-      <c r="B791" s="10"/>
+      <c r="A791" s="11"/>
+      <c r="B791" s="11"/>
     </row>
     <row r="792" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A792" s="10"/>
-      <c r="B792" s="10"/>
+      <c r="A792" s="11"/>
+      <c r="B792" s="11"/>
     </row>
     <row r="793" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A793" s="10"/>
-      <c r="B793" s="10"/>
+      <c r="A793" s="11"/>
+      <c r="B793" s="11"/>
     </row>
     <row r="794" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A794" s="10"/>
-      <c r="B794" s="10"/>
+      <c r="A794" s="11"/>
+      <c r="B794" s="11"/>
     </row>
     <row r="795" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A795" s="10"/>
-      <c r="B795" s="10"/>
+      <c r="A795" s="11"/>
+      <c r="B795" s="11"/>
     </row>
     <row r="796" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A796" s="10"/>
-      <c r="B796" s="10"/>
+      <c r="A796" s="11"/>
+      <c r="B796" s="11"/>
     </row>
     <row r="797" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A797" s="10"/>
-      <c r="B797" s="10"/>
+      <c r="A797" s="11"/>
+      <c r="B797" s="11"/>
     </row>
     <row r="798" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A798" s="10"/>
-      <c r="B798" s="10"/>
+      <c r="A798" s="11"/>
+      <c r="B798" s="11"/>
     </row>
     <row r="799" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A799" s="10"/>
-      <c r="B799" s="10"/>
+      <c r="A799" s="11"/>
+      <c r="B799" s="11"/>
     </row>
     <row r="800" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A800" s="10"/>
-      <c r="B800" s="10"/>
+      <c r="A800" s="11"/>
+      <c r="B800" s="11"/>
     </row>
     <row r="801" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A801" s="10"/>
-      <c r="B801" s="10"/>
+      <c r="A801" s="11"/>
+      <c r="B801" s="11"/>
     </row>
     <row r="802" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A802" s="10"/>
-      <c r="B802" s="10"/>
+      <c r="A802" s="11"/>
+      <c r="B802" s="11"/>
     </row>
     <row r="803" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A803" s="10"/>
-      <c r="B803" s="10"/>
+      <c r="A803" s="11"/>
+      <c r="B803" s="11"/>
     </row>
     <row r="804" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A804" s="10"/>
-      <c r="B804" s="10"/>
+      <c r="A804" s="11"/>
+      <c r="B804" s="11"/>
     </row>
     <row r="805" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A805" s="10"/>
-      <c r="B805" s="10"/>
+      <c r="A805" s="11"/>
+      <c r="B805" s="11"/>
     </row>
     <row r="806" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A806" s="10"/>
-      <c r="B806" s="10"/>
+      <c r="A806" s="11"/>
+      <c r="B806" s="11"/>
     </row>
     <row r="807" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A807" s="10"/>
-      <c r="B807" s="10"/>
+      <c r="A807" s="11"/>
+      <c r="B807" s="11"/>
     </row>
     <row r="808" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A808" s="10"/>
-      <c r="B808" s="10"/>
+      <c r="A808" s="11"/>
+      <c r="B808" s="11"/>
     </row>
     <row r="809" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A809" s="10"/>
-      <c r="B809" s="10"/>
+      <c r="A809" s="11"/>
+      <c r="B809" s="11"/>
     </row>
     <row r="810" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A810" s="10"/>
-      <c r="B810" s="10"/>
+      <c r="A810" s="11"/>
+      <c r="B810" s="11"/>
     </row>
     <row r="811" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A811" s="10"/>
-      <c r="B811" s="10"/>
+      <c r="A811" s="11"/>
+      <c r="B811" s="11"/>
     </row>
     <row r="812" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A812" s="10"/>
-      <c r="B812" s="10"/>
+      <c r="A812" s="11"/>
+      <c r="B812" s="11"/>
     </row>
     <row r="813" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A813" s="10"/>
-      <c r="B813" s="10"/>
+      <c r="A813" s="11"/>
+      <c r="B813" s="11"/>
     </row>
     <row r="814" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A814" s="10"/>
-      <c r="B814" s="10"/>
+      <c r="A814" s="11"/>
+      <c r="B814" s="11"/>
     </row>
     <row r="815" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A815" s="10"/>
-      <c r="B815" s="10"/>
+      <c r="A815" s="11"/>
+      <c r="B815" s="11"/>
     </row>
     <row r="816" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A816" s="10"/>
-      <c r="B816" s="10"/>
+      <c r="A816" s="11"/>
+      <c r="B816" s="11"/>
     </row>
     <row r="817" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A817" s="10"/>
-      <c r="B817" s="10"/>
+      <c r="A817" s="11"/>
+      <c r="B817" s="11"/>
     </row>
     <row r="818" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A818" s="10"/>
-      <c r="B818" s="10"/>
+      <c r="A818" s="11"/>
+      <c r="B818" s="11"/>
     </row>
     <row r="819" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A819" s="10"/>
-      <c r="B819" s="10"/>
+      <c r="A819" s="11"/>
+      <c r="B819" s="11"/>
     </row>
     <row r="820" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A820" s="10"/>
-      <c r="B820" s="10"/>
+      <c r="A820" s="11"/>
+      <c r="B820" s="11"/>
     </row>
     <row r="821" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A821" s="10"/>
-      <c r="B821" s="10"/>
+      <c r="A821" s="11"/>
+      <c r="B821" s="11"/>
     </row>
     <row r="822" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A822" s="10"/>
-      <c r="B822" s="10"/>
+      <c r="A822" s="11"/>
+      <c r="B822" s="11"/>
     </row>
     <row r="823" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A823" s="10"/>
-      <c r="B823" s="10"/>
+      <c r="A823" s="11"/>
+      <c r="B823" s="11"/>
     </row>
     <row r="824" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A824" s="10"/>
-      <c r="B824" s="10"/>
+      <c r="A824" s="11"/>
+      <c r="B824" s="11"/>
     </row>
     <row r="825" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A825" s="10"/>
-      <c r="B825" s="10"/>
+      <c r="A825" s="11"/>
+      <c r="B825" s="11"/>
     </row>
     <row r="826" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A826" s="10"/>
-      <c r="B826" s="10"/>
+      <c r="A826" s="11"/>
+      <c r="B826" s="11"/>
     </row>
     <row r="827" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A827" s="10"/>
-      <c r="B827" s="10"/>
+      <c r="A827" s="11"/>
+      <c r="B827" s="11"/>
     </row>
     <row r="828" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A828" s="10"/>
-      <c r="B828" s="10"/>
+      <c r="A828" s="11"/>
+      <c r="B828" s="11"/>
     </row>
     <row r="829" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A829" s="10"/>
-      <c r="B829" s="10"/>
+      <c r="A829" s="11"/>
+      <c r="B829" s="11"/>
     </row>
     <row r="830" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A830" s="10"/>
-      <c r="B830" s="10"/>
+      <c r="A830" s="11"/>
+      <c r="B830" s="11"/>
     </row>
     <row r="831" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A831" s="10"/>
-      <c r="B831" s="10"/>
+      <c r="A831" s="11"/>
+      <c r="B831" s="11"/>
     </row>
     <row r="832" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A832" s="10"/>
-      <c r="B832" s="10"/>
+      <c r="A832" s="11"/>
+      <c r="B832" s="11"/>
     </row>
     <row r="833" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A833" s="10"/>
-      <c r="B833" s="10"/>
+      <c r="A833" s="11"/>
+      <c r="B833" s="11"/>
     </row>
     <row r="834" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A834" s="10"/>
-      <c r="B834" s="10"/>
+      <c r="A834" s="11"/>
+      <c r="B834" s="11"/>
     </row>
     <row r="835" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A835" s="10"/>
-      <c r="B835" s="10"/>
+      <c r="A835" s="11"/>
+      <c r="B835" s="11"/>
     </row>
     <row r="836" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A836" s="10"/>
-      <c r="B836" s="10"/>
+      <c r="A836" s="11"/>
+      <c r="B836" s="11"/>
     </row>
     <row r="837" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A837" s="10"/>
-      <c r="B837" s="10"/>
+      <c r="A837" s="11"/>
+      <c r="B837" s="11"/>
     </row>
     <row r="838" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A838" s="10"/>
-      <c r="B838" s="10"/>
+      <c r="A838" s="11"/>
+      <c r="B838" s="11"/>
     </row>
     <row r="839" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A839" s="10"/>
-      <c r="B839" s="10"/>
+      <c r="A839" s="11"/>
+      <c r="B839" s="11"/>
     </row>
     <row r="840" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A840" s="10"/>
-      <c r="B840" s="10"/>
+      <c r="A840" s="11"/>
+      <c r="B840" s="11"/>
     </row>
     <row r="841" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A841" s="10"/>
-      <c r="B841" s="10"/>
+      <c r="A841" s="11"/>
+      <c r="B841" s="11"/>
     </row>
     <row r="842" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A842" s="10"/>
-      <c r="B842" s="10"/>
+      <c r="A842" s="11"/>
+      <c r="B842" s="11"/>
     </row>
     <row r="843" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A843" s="10"/>
-      <c r="B843" s="10"/>
+      <c r="A843" s="11"/>
+      <c r="B843" s="11"/>
     </row>
     <row r="844" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A844" s="10"/>
-      <c r="B844" s="10"/>
+      <c r="A844" s="11"/>
+      <c r="B844" s="11"/>
     </row>
     <row r="845" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A845" s="10"/>
-      <c r="B845" s="10"/>
+      <c r="A845" s="11"/>
+      <c r="B845" s="11"/>
     </row>
     <row r="846" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A846" s="10"/>
-      <c r="B846" s="10"/>
+      <c r="A846" s="11"/>
+      <c r="B846" s="11"/>
     </row>
     <row r="847" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A847" s="10"/>
-      <c r="B847" s="10"/>
+      <c r="A847" s="11"/>
+      <c r="B847" s="11"/>
     </row>
     <row r="848" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A848" s="10"/>
-      <c r="B848" s="10"/>
+      <c r="A848" s="11"/>
+      <c r="B848" s="11"/>
     </row>
     <row r="849" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A849" s="10"/>
-      <c r="B849" s="10"/>
+      <c r="A849" s="11"/>
+      <c r="B849" s="11"/>
     </row>
     <row r="850" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A850" s="10"/>
-      <c r="B850" s="10"/>
+      <c r="A850" s="11"/>
+      <c r="B850" s="11"/>
     </row>
     <row r="851" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A851" s="10"/>
-      <c r="B851" s="10"/>
+      <c r="A851" s="11"/>
+      <c r="B851" s="11"/>
     </row>
     <row r="852" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A852" s="10"/>
-      <c r="B852" s="10"/>
+      <c r="A852" s="11"/>
+      <c r="B852" s="11"/>
     </row>
     <row r="853" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A853" s="10"/>
-      <c r="B853" s="10"/>
+      <c r="A853" s="11"/>
+      <c r="B853" s="11"/>
     </row>
     <row r="854" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A854" s="10"/>
-      <c r="B854" s="10"/>
+      <c r="A854" s="11"/>
+      <c r="B854" s="11"/>
     </row>
     <row r="855" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A855" s="10"/>
-      <c r="B855" s="10"/>
+      <c r="A855" s="11"/>
+      <c r="B855" s="11"/>
     </row>
     <row r="856" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A856" s="10"/>
-      <c r="B856" s="10"/>
+      <c r="A856" s="11"/>
+      <c r="B856" s="11"/>
     </row>
     <row r="857" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A857" s="10"/>
-      <c r="B857" s="10"/>
+      <c r="A857" s="11"/>
+      <c r="B857" s="11"/>
     </row>
     <row r="858" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A858" s="10"/>
-      <c r="B858" s="10"/>
+      <c r="A858" s="11"/>
+      <c r="B858" s="11"/>
     </row>
     <row r="859" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A859" s="10"/>
-      <c r="B859" s="10"/>
+      <c r="A859" s="11"/>
+      <c r="B859" s="11"/>
     </row>
     <row r="860" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A860" s="10"/>
-      <c r="B860" s="10"/>
+      <c r="A860" s="11"/>
+      <c r="B860" s="11"/>
     </row>
     <row r="861" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A861" s="10"/>
-      <c r="B861" s="10"/>
+      <c r="A861" s="11"/>
+      <c r="B861" s="11"/>
     </row>
     <row r="862" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A862" s="10"/>
-      <c r="B862" s="10"/>
+      <c r="A862" s="11"/>
+      <c r="B862" s="11"/>
     </row>
     <row r="863" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A863" s="10"/>
-      <c r="B863" s="10"/>
+      <c r="A863" s="11"/>
+      <c r="B863" s="11"/>
     </row>
     <row r="864" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A864" s="10"/>
-      <c r="B864" s="10"/>
+      <c r="A864" s="11"/>
+      <c r="B864" s="11"/>
     </row>
     <row r="865" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A865" s="10"/>
-      <c r="B865" s="10"/>
+      <c r="A865" s="11"/>
+      <c r="B865" s="11"/>
     </row>
     <row r="866" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A866" s="10"/>
-      <c r="B866" s="10"/>
+      <c r="A866" s="11"/>
+      <c r="B866" s="11"/>
     </row>
     <row r="867" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A867" s="10"/>
-      <c r="B867" s="10"/>
+      <c r="A867" s="11"/>
+      <c r="B867" s="11"/>
     </row>
     <row r="868" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A868" s="10"/>
-      <c r="B868" s="10"/>
+      <c r="A868" s="11"/>
+      <c r="B868" s="11"/>
     </row>
     <row r="869" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A869" s="10"/>
-      <c r="B869" s="10"/>
+      <c r="A869" s="11"/>
+      <c r="B869" s="11"/>
     </row>
     <row r="870" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A870" s="10"/>
-      <c r="B870" s="10"/>
+      <c r="A870" s="11"/>
+      <c r="B870" s="11"/>
     </row>
     <row r="871" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A871" s="10"/>
-      <c r="B871" s="10"/>
+      <c r="A871" s="11"/>
+      <c r="B871" s="11"/>
     </row>
     <row r="872" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A872" s="10"/>
-      <c r="B872" s="10"/>
+      <c r="A872" s="11"/>
+      <c r="B872" s="11"/>
     </row>
     <row r="873" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A873" s="10"/>
-      <c r="B873" s="10"/>
+      <c r="A873" s="11"/>
+      <c r="B873" s="11"/>
     </row>
     <row r="874" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A874" s="10"/>
-      <c r="B874" s="10"/>
+      <c r="A874" s="11"/>
+      <c r="B874" s="11"/>
     </row>
     <row r="875" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A875" s="10"/>
-      <c r="B875" s="10"/>
+      <c r="A875" s="11"/>
+      <c r="B875" s="11"/>
     </row>
     <row r="876" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A876" s="10"/>
-      <c r="B876" s="10"/>
+      <c r="A876" s="11"/>
+      <c r="B876" s="11"/>
     </row>
     <row r="877" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A877" s="10"/>
-      <c r="B877" s="10"/>
+      <c r="A877" s="11"/>
+      <c r="B877" s="11"/>
     </row>
     <row r="878" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A878" s="10"/>
-      <c r="B878" s="10"/>
+      <c r="A878" s="11"/>
+      <c r="B878" s="11"/>
     </row>
     <row r="879" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A879" s="10"/>
-      <c r="B879" s="10"/>
+      <c r="A879" s="11"/>
+      <c r="B879" s="11"/>
     </row>
     <row r="880" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A880" s="10"/>
-      <c r="B880" s="10"/>
+      <c r="A880" s="11"/>
+      <c r="B880" s="11"/>
     </row>
     <row r="881" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A881" s="10"/>
-      <c r="B881" s="10"/>
+      <c r="A881" s="11"/>
+      <c r="B881" s="11"/>
     </row>
     <row r="882" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A882" s="10"/>
-      <c r="B882" s="10"/>
+      <c r="A882" s="11"/>
+      <c r="B882" s="11"/>
     </row>
     <row r="883" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A883" s="10"/>
-      <c r="B883" s="10"/>
+      <c r="A883" s="11"/>
+      <c r="B883" s="11"/>
     </row>
     <row r="884" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A884" s="10"/>
-      <c r="B884" s="10"/>
+      <c r="A884" s="11"/>
+      <c r="B884" s="11"/>
     </row>
     <row r="885" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A885" s="10"/>
-      <c r="B885" s="10"/>
+      <c r="A885" s="11"/>
+      <c r="B885" s="11"/>
     </row>
     <row r="886" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A886" s="10"/>
-      <c r="B886" s="10"/>
+      <c r="A886" s="11"/>
+      <c r="B886" s="11"/>
     </row>
     <row r="887" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A887" s="10"/>
-      <c r="B887" s="10"/>
+      <c r="A887" s="11"/>
+      <c r="B887" s="11"/>
     </row>
     <row r="888" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A888" s="10"/>
-      <c r="B888" s="10"/>
+      <c r="A888" s="11"/>
+      <c r="B888" s="11"/>
     </row>
     <row r="889" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A889" s="10"/>
-      <c r="B889" s="10"/>
+      <c r="A889" s="11"/>
+      <c r="B889" s="11"/>
     </row>
     <row r="890" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A890" s="10"/>
-      <c r="B890" s="10"/>
+      <c r="A890" s="11"/>
+      <c r="B890" s="11"/>
     </row>
     <row r="891" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A891" s="10"/>
-      <c r="B891" s="10"/>
+      <c r="A891" s="11"/>
+      <c r="B891" s="11"/>
     </row>
     <row r="892" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A892" s="10"/>
-      <c r="B892" s="10"/>
+      <c r="A892" s="11"/>
+      <c r="B892" s="11"/>
     </row>
     <row r="893" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A893" s="10"/>
-      <c r="B893" s="10"/>
+      <c r="A893" s="11"/>
+      <c r="B893" s="11"/>
     </row>
     <row r="894" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A894" s="10"/>
-      <c r="B894" s="10"/>
+      <c r="A894" s="11"/>
+      <c r="B894" s="11"/>
     </row>
     <row r="895" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A895" s="10"/>
-      <c r="B895" s="10"/>
+      <c r="A895" s="11"/>
+      <c r="B895" s="11"/>
     </row>
     <row r="896" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A896" s="10"/>
-      <c r="B896" s="10"/>
+      <c r="A896" s="11"/>
+      <c r="B896" s="11"/>
     </row>
     <row r="897" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A897" s="10"/>
-      <c r="B897" s="10"/>
+      <c r="A897" s="11"/>
+      <c r="B897" s="11"/>
     </row>
     <row r="898" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A898" s="10"/>
-      <c r="B898" s="10"/>
+      <c r="A898" s="11"/>
+      <c r="B898" s="11"/>
     </row>
     <row r="899" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A899" s="10"/>
-      <c r="B899" s="10"/>
+      <c r="A899" s="11"/>
+      <c r="B899" s="11"/>
     </row>
     <row r="900" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A900" s="10"/>
-      <c r="B900" s="10"/>
+      <c r="A900" s="11"/>
+      <c r="B900" s="11"/>
     </row>
     <row r="901" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A901" s="10"/>
-      <c r="B901" s="10"/>
+      <c r="A901" s="11"/>
+      <c r="B901" s="11"/>
     </row>
     <row r="902" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A902" s="10"/>
-      <c r="B902" s="10"/>
+      <c r="A902" s="11"/>
+      <c r="B902" s="11"/>
     </row>
     <row r="903" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A903" s="10"/>
-      <c r="B903" s="10"/>
+      <c r="A903" s="11"/>
+      <c r="B903" s="11"/>
     </row>
     <row r="904" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A904" s="10"/>
-      <c r="B904" s="10"/>
+      <c r="A904" s="11"/>
+      <c r="B904" s="11"/>
     </row>
     <row r="905" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A905" s="10"/>
-      <c r="B905" s="10"/>
+      <c r="A905" s="11"/>
+      <c r="B905" s="11"/>
     </row>
     <row r="906" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A906" s="10"/>
-      <c r="B906" s="10"/>
+      <c r="A906" s="11"/>
+      <c r="B906" s="11"/>
     </row>
     <row r="907" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A907" s="10"/>
-      <c r="B907" s="10"/>
+      <c r="A907" s="11"/>
+      <c r="B907" s="11"/>
     </row>
     <row r="908" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A908" s="10"/>
-      <c r="B908" s="10"/>
+      <c r="A908" s="11"/>
+      <c r="B908" s="11"/>
     </row>
     <row r="909" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A909" s="10"/>
-      <c r="B909" s="10"/>
+      <c r="A909" s="11"/>
+      <c r="B909" s="11"/>
     </row>
     <row r="910" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A910" s="10"/>
-      <c r="B910" s="10"/>
+      <c r="A910" s="11"/>
+      <c r="B910" s="11"/>
     </row>
     <row r="911" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A911" s="10"/>
-      <c r="B911" s="10"/>
+      <c r="A911" s="11"/>
+      <c r="B911" s="11"/>
     </row>
     <row r="912" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A912" s="10"/>
-      <c r="B912" s="10"/>
+      <c r="A912" s="11"/>
+      <c r="B912" s="11"/>
     </row>
     <row r="913" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A913" s="10"/>
-      <c r="B913" s="10"/>
+      <c r="A913" s="11"/>
+      <c r="B913" s="11"/>
     </row>
     <row r="914" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A914" s="10"/>
-      <c r="B914" s="10"/>
+      <c r="A914" s="11"/>
+      <c r="B914" s="11"/>
     </row>
     <row r="915" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A915" s="10"/>
-      <c r="B915" s="10"/>
+      <c r="A915" s="11"/>
+      <c r="B915" s="11"/>
     </row>
     <row r="916" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A916" s="10"/>
-      <c r="B916" s="10"/>
+      <c r="A916" s="11"/>
+      <c r="B916" s="11"/>
     </row>
     <row r="917" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A917" s="10"/>
-      <c r="B917" s="10"/>
+      <c r="A917" s="11"/>
+      <c r="B917" s="11"/>
     </row>
     <row r="918" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A918" s="10"/>
-      <c r="B918" s="10"/>
+      <c r="A918" s="11"/>
+      <c r="B918" s="11"/>
     </row>
     <row r="919" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A919" s="10"/>
-      <c r="B919" s="10"/>
+      <c r="A919" s="11"/>
+      <c r="B919" s="11"/>
     </row>
     <row r="920" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A920" s="10"/>
-      <c r="B920" s="10"/>
+      <c r="A920" s="11"/>
+      <c r="B920" s="11"/>
     </row>
     <row r="921" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A921" s="10"/>
-      <c r="B921" s="10"/>
+      <c r="A921" s="11"/>
+      <c r="B921" s="11"/>
     </row>
     <row r="922" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A922" s="10"/>
-      <c r="B922" s="10"/>
+      <c r="A922" s="11"/>
+      <c r="B922" s="11"/>
     </row>
     <row r="923" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A923" s="10"/>
-      <c r="B923" s="10"/>
+      <c r="A923" s="11"/>
+      <c r="B923" s="11"/>
     </row>
     <row r="924" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A924" s="10"/>
-      <c r="B924" s="10"/>
+      <c r="A924" s="11"/>
+      <c r="B924" s="11"/>
     </row>
     <row r="925" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A925" s="10"/>
-      <c r="B925" s="10"/>
+      <c r="A925" s="11"/>
+      <c r="B925" s="11"/>
     </row>
     <row r="926" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A926" s="10"/>
-      <c r="B926" s="10"/>
+      <c r="A926" s="11"/>
+      <c r="B926" s="11"/>
     </row>
     <row r="927" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A927" s="10"/>
-      <c r="B927" s="10"/>
+      <c r="A927" s="11"/>
+      <c r="B927" s="11"/>
     </row>
     <row r="928" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A928" s="10"/>
-      <c r="B928" s="10"/>
+      <c r="A928" s="11"/>
+      <c r="B928" s="11"/>
     </row>
     <row r="929" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A929" s="10"/>
-      <c r="B929" s="10"/>
+      <c r="A929" s="11"/>
+      <c r="B929" s="11"/>
     </row>
     <row r="930" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A930" s="10"/>
-      <c r="B930" s="10"/>
+      <c r="A930" s="11"/>
+      <c r="B930" s="11"/>
     </row>
     <row r="931" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A931" s="10"/>
-      <c r="B931" s="10"/>
+      <c r="A931" s="11"/>
+      <c r="B931" s="11"/>
     </row>
     <row r="932" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A932" s="10"/>
-      <c r="B932" s="10"/>
+      <c r="A932" s="11"/>
+      <c r="B932" s="11"/>
     </row>
     <row r="933" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A933" s="10"/>
-      <c r="B933" s="10"/>
+      <c r="A933" s="11"/>
+      <c r="B933" s="11"/>
     </row>
     <row r="934" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A934" s="10"/>
-      <c r="B934" s="10"/>
+      <c r="A934" s="11"/>
+      <c r="B934" s="11"/>
     </row>
     <row r="935" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A935" s="10"/>
-      <c r="B935" s="10"/>
+      <c r="A935" s="11"/>
+      <c r="B935" s="11"/>
     </row>
     <row r="936" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A936" s="10"/>
-      <c r="B936" s="10"/>
+      <c r="A936" s="11"/>
+      <c r="B936" s="11"/>
     </row>
     <row r="937" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A937" s="10"/>
-      <c r="B937" s="10"/>
+      <c r="A937" s="11"/>
+      <c r="B937" s="11"/>
     </row>
     <row r="938" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A938" s="10"/>
-      <c r="B938" s="10"/>
+      <c r="A938" s="11"/>
+      <c r="B938" s="11"/>
     </row>
     <row r="939" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A939" s="10"/>
-      <c r="B939" s="10"/>
+      <c r="A939" s="11"/>
+      <c r="B939" s="11"/>
     </row>
     <row r="940" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A940" s="10"/>
-      <c r="B940" s="10"/>
+      <c r="A940" s="11"/>
+      <c r="B940" s="11"/>
     </row>
     <row r="941" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A941" s="10"/>
-      <c r="B941" s="10"/>
+      <c r="A941" s="11"/>
+      <c r="B941" s="11"/>
     </row>
     <row r="942" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A942" s="10"/>
-      <c r="B942" s="10"/>
+      <c r="A942" s="11"/>
+      <c r="B942" s="11"/>
     </row>
     <row r="943" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A943" s="10"/>
-      <c r="B943" s="10"/>
+      <c r="A943" s="11"/>
+      <c r="B943" s="11"/>
     </row>
     <row r="944" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A944" s="10"/>
-      <c r="B944" s="10"/>
+      <c r="A944" s="11"/>
+      <c r="B944" s="11"/>
     </row>
     <row r="945" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A945" s="10"/>
-      <c r="B945" s="10"/>
+      <c r="A945" s="11"/>
+      <c r="B945" s="11"/>
     </row>
     <row r="946" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A946" s="10"/>
-      <c r="B946" s="10"/>
+      <c r="A946" s="11"/>
+      <c r="B946" s="11"/>
     </row>
     <row r="947" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A947" s="10"/>
-      <c r="B947" s="10"/>
+      <c r="A947" s="11"/>
+      <c r="B947" s="11"/>
     </row>
     <row r="948" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A948" s="10"/>
-      <c r="B948" s="10"/>
+      <c r="A948" s="11"/>
+      <c r="B948" s="11"/>
     </row>
     <row r="949" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A949" s="10"/>
-      <c r="B949" s="10"/>
+      <c r="A949" s="11"/>
+      <c r="B949" s="11"/>
     </row>
     <row r="950" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A950" s="10"/>
-      <c r="B950" s="10"/>
+      <c r="A950" s="11"/>
+      <c r="B950" s="11"/>
     </row>
     <row r="951" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A951" s="10"/>
-      <c r="B951" s="10"/>
+      <c r="A951" s="11"/>
+      <c r="B951" s="11"/>
     </row>
     <row r="952" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A952" s="10"/>
-      <c r="B952" s="10"/>
+      <c r="A952" s="11"/>
+      <c r="B952" s="11"/>
     </row>
     <row r="953" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A953" s="10"/>
-      <c r="B953" s="10"/>
+      <c r="A953" s="11"/>
+      <c r="B953" s="11"/>
     </row>
     <row r="954" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A954" s="10"/>
-      <c r="B954" s="10"/>
+      <c r="A954" s="11"/>
+      <c r="B954" s="11"/>
     </row>
     <row r="955" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A955" s="10"/>
-      <c r="B955" s="10"/>
+      <c r="A955" s="11"/>
+      <c r="B955" s="11"/>
     </row>
     <row r="956" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A956" s="10"/>
-      <c r="B956" s="10"/>
+      <c r="A956" s="11"/>
+      <c r="B956" s="11"/>
     </row>
     <row r="957" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A957" s="10"/>
-      <c r="B957" s="10"/>
+      <c r="A957" s="11"/>
+      <c r="B957" s="11"/>
     </row>
     <row r="958" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A958" s="10"/>
-      <c r="B958" s="10"/>
+      <c r="A958" s="11"/>
+      <c r="B958" s="11"/>
     </row>
     <row r="959" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A959" s="10"/>
-      <c r="B959" s="10"/>
+      <c r="A959" s="11"/>
+      <c r="B959" s="11"/>
     </row>
     <row r="960" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A960" s="10"/>
-      <c r="B960" s="10"/>
+      <c r="A960" s="11"/>
+      <c r="B960" s="11"/>
     </row>
     <row r="961" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A961" s="10"/>
-      <c r="B961" s="10"/>
+      <c r="A961" s="11"/>
+      <c r="B961" s="11"/>
     </row>
     <row r="962" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A962" s="10"/>
-      <c r="B962" s="10"/>
+      <c r="A962" s="11"/>
+      <c r="B962" s="11"/>
     </row>
     <row r="963" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A963" s="10"/>
-      <c r="B963" s="10"/>
+      <c r="A963" s="11"/>
+      <c r="B963" s="11"/>
     </row>
     <row r="964" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A964" s="10"/>
-      <c r="B964" s="10"/>
+      <c r="A964" s="11"/>
+      <c r="B964" s="11"/>
     </row>
     <row r="965" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A965" s="10"/>
-      <c r="B965" s="10"/>
+      <c r="A965" s="11"/>
+      <c r="B965" s="11"/>
     </row>
     <row r="966" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A966" s="10"/>
-      <c r="B966" s="10"/>
+      <c r="A966" s="11"/>
+      <c r="B966" s="11"/>
     </row>
     <row r="967" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A967" s="10"/>
-      <c r="B967" s="10"/>
+      <c r="A967" s="11"/>
+      <c r="B967" s="11"/>
     </row>
     <row r="968" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A968" s="10"/>
-      <c r="B968" s="10"/>
+      <c r="A968" s="11"/>
+      <c r="B968" s="11"/>
     </row>
     <row r="969" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A969" s="10"/>
-      <c r="B969" s="10"/>
+      <c r="A969" s="11"/>
+      <c r="B969" s="11"/>
     </row>
     <row r="970" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A970" s="10"/>
-      <c r="B970" s="10"/>
+      <c r="A970" s="11"/>
+      <c r="B970" s="11"/>
     </row>
     <row r="971" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A971" s="10"/>
-      <c r="B971" s="10"/>
+      <c r="A971" s="11"/>
+      <c r="B971" s="11"/>
     </row>
     <row r="972" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A972" s="10"/>
-      <c r="B972" s="10"/>
+      <c r="A972" s="11"/>
+      <c r="B972" s="11"/>
     </row>
     <row r="973" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A973" s="10"/>
-      <c r="B973" s="10"/>
+      <c r="A973" s="11"/>
+      <c r="B973" s="11"/>
     </row>
     <row r="974" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A974" s="10"/>
-      <c r="B974" s="10"/>
+      <c r="A974" s="11"/>
+      <c r="B974" s="11"/>
     </row>
     <row r="975" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A975" s="10"/>
-      <c r="B975" s="10"/>
+      <c r="A975" s="11"/>
+      <c r="B975" s="11"/>
     </row>
     <row r="976" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A976" s="10"/>
-      <c r="B976" s="10"/>
+      <c r="A976" s="11"/>
+      <c r="B976" s="11"/>
     </row>
     <row r="977" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A977" s="10"/>
-      <c r="B977" s="10"/>
+      <c r="A977" s="11"/>
+      <c r="B977" s="11"/>
     </row>
     <row r="978" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A978" s="10"/>
-      <c r="B978" s="10"/>
+      <c r="A978" s="11"/>
+      <c r="B978" s="11"/>
     </row>
     <row r="979" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A979" s="10"/>
-      <c r="B979" s="10"/>
+      <c r="A979" s="11"/>
+      <c r="B979" s="11"/>
     </row>
     <row r="980" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A980" s="10"/>
-      <c r="B980" s="10"/>
+      <c r="A980" s="11"/>
+      <c r="B980" s="11"/>
     </row>
     <row r="981" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A981" s="10"/>
-      <c r="B981" s="10"/>
+      <c r="A981" s="11"/>
+      <c r="B981" s="11"/>
     </row>
     <row r="982" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A982" s="10"/>
-      <c r="B982" s="10"/>
+      <c r="A982" s="11"/>
+      <c r="B982" s="11"/>
     </row>
     <row r="983" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A983" s="10"/>
-      <c r="B983" s="10"/>
+      <c r="A983" s="11"/>
+      <c r="B983" s="11"/>
     </row>
     <row r="984" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A984" s="10"/>
-      <c r="B984" s="10"/>
+      <c r="A984" s="11"/>
+      <c r="B984" s="11"/>
     </row>
     <row r="985" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A985" s="10"/>
-      <c r="B985" s="10"/>
+      <c r="A985" s="11"/>
+      <c r="B985" s="11"/>
     </row>
     <row r="986" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A986" s="10"/>
-      <c r="B986" s="10"/>
+      <c r="A986" s="11"/>
+      <c r="B986" s="11"/>
     </row>
     <row r="987" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A987" s="10"/>
-      <c r="B987" s="10"/>
+      <c r="A987" s="11"/>
+      <c r="B987" s="11"/>
     </row>
     <row r="988" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A988" s="10"/>
-      <c r="B988" s="10"/>
+      <c r="A988" s="11"/>
+      <c r="B988" s="11"/>
     </row>
     <row r="989" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A989" s="10"/>
-      <c r="B989" s="10"/>
+      <c r="A989" s="11"/>
+      <c r="B989" s="11"/>
     </row>
     <row r="990" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A990" s="10"/>
-      <c r="B990" s="10"/>
+      <c r="A990" s="11"/>
+      <c r="B990" s="11"/>
     </row>
     <row r="991" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A991" s="10"/>
-      <c r="B991" s="10"/>
+      <c r="A991" s="11"/>
+      <c r="B991" s="11"/>
     </row>
     <row r="992" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A992" s="10"/>
-      <c r="B992" s="10"/>
+      <c r="A992" s="11"/>
+      <c r="B992" s="11"/>
     </row>
     <row r="993" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A993" s="10"/>
-      <c r="B993" s="10"/>
+      <c r="A993" s="11"/>
+      <c r="B993" s="11"/>
     </row>
     <row r="994" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A994" s="10"/>
-      <c r="B994" s="10"/>
+      <c r="A994" s="11"/>
+      <c r="B994" s="11"/>
     </row>
     <row r="995" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A995" s="10"/>
-      <c r="B995" s="10"/>
+      <c r="A995" s="11"/>
+      <c r="B995" s="11"/>
     </row>
     <row r="996" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A996" s="10"/>
-      <c r="B996" s="10"/>
+      <c r="A996" s="11"/>
+      <c r="B996" s="11"/>
     </row>
     <row r="997" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A997" s="10"/>
-      <c r="B997" s="10"/>
+      <c r="A997" s="11"/>
+      <c r="B997" s="11"/>
     </row>
     <row r="998" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A998" s="10"/>
-      <c r="B998" s="10"/>
+      <c r="A998" s="11"/>
+      <c r="B998" s="11"/>
     </row>
     <row r="999" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A999" s="10"/>
-      <c r="B999" s="10"/>
+      <c r="A999" s="11"/>
+      <c r="B999" s="11"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1" spans="1:2">
-      <c r="A1000" s="10"/>
-      <c r="B1000" s="10"/>
+      <c r="A1000" s="11"/>
+      <c r="B1000" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.699999988079071" right="0.699999988079071" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="114">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -246,13 +246,127 @@
   </si>
   <si>
     <t>M_Gemstone_Topaz</t>
+  </si>
+  <si>
+    <t>Item_Painting_01</t>
+  </si>
+  <si>
+    <t>명화</t>
+  </si>
+  <si>
+    <t>벽에 걸려있는 그림이다.</t>
+  </si>
+  <si>
+    <t>Painting</t>
+  </si>
+  <si>
+    <t>PaintingFrame_WoodHell,PaintingFrame_White,Painting_1</t>
+  </si>
+  <si>
+    <t>Painting_1_Mesh[Painting_1]</t>
+  </si>
+  <si>
+    <t>PaintingObject</t>
+  </si>
+  <si>
+    <t>Item_Painting_02</t>
+  </si>
+  <si>
+    <t>PaintingFrame_White,Painting_6</t>
+  </si>
+  <si>
+    <t>Painting_2_Mesh[Painting_2]</t>
+  </si>
+  <si>
+    <t>Item_Painting_03</t>
+  </si>
+  <si>
+    <t>PaintingFrame_Black,PaintingFrame_Gold,Painting_8</t>
+  </si>
+  <si>
+    <t>Painting_3_Mesh[Painting_8]</t>
+  </si>
+  <si>
+    <t>Item_Painting_04</t>
+  </si>
+  <si>
+    <t>PaintingFrame_White,Painting_3</t>
+  </si>
+  <si>
+    <t>Painting_4_Mesh[Painting_4]</t>
+  </si>
+  <si>
+    <t>Item_Painting_05</t>
+  </si>
+  <si>
+    <t>PaintingFrame_WoodHell,Painting_2</t>
+  </si>
+  <si>
+    <t>Painting_5_Mesh[Painting_5]</t>
+  </si>
+  <si>
+    <t>Item_Statue_Stone</t>
+  </si>
+  <si>
+    <t>돌 조각상</t>
+  </si>
+  <si>
+    <t>투박한 돌로 만든 조각상이다.</t>
+  </si>
+  <si>
+    <t>Statue</t>
+  </si>
+  <si>
+    <t>Statue_Stone</t>
+  </si>
+  <si>
+    <t>SeatedLion[Seated_Lion_LOD0]</t>
+  </si>
+  <si>
+    <t>StatueObject</t>
+  </si>
+  <si>
+    <t>Item_Statue_Copper</t>
+  </si>
+  <si>
+    <t>구리 조각상</t>
+  </si>
+  <si>
+    <t>특이한 색의 조각상이다.</t>
+  </si>
+  <si>
+    <t>Statue_Copper</t>
+  </si>
+  <si>
+    <t>Item_Statue_Metal</t>
+  </si>
+  <si>
+    <t>금속 조각상</t>
+  </si>
+  <si>
+    <t>광택이 나는 금속 조각상이다.</t>
+  </si>
+  <si>
+    <t>Statue_Metal</t>
+  </si>
+  <si>
+    <t>Item_Statue_Marble</t>
+  </si>
+  <si>
+    <t>대리석 조각상</t>
+  </si>
+  <si>
+    <t>아름다운 조각상이다.</t>
+  </si>
+  <si>
+    <t>Statue_Marble</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -287,6 +401,18 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="&quot;\0022맑은 고딕\0022&quot;"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <color rgb="FF000000"/>
+      <name val="바탕체"/>
     </font>
   </fonts>
   <fills count="4">
@@ -329,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="18">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -359,6 +485,21 @@
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -575,7 +716,7 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.63"/>
+    <col customWidth="1" min="1" max="1" width="25.38"/>
     <col customWidth="1" min="2" max="2" width="15.0"/>
     <col customWidth="1" min="3" max="3" width="24.25"/>
     <col customWidth="1" min="4" max="4" width="15.5"/>
@@ -1137,134 +1278,266 @@
       <c r="U12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
-      <c r="U13" s="4"/>
+      <c r="A13" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F13" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="G13" s="14">
+        <v>1200.0</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K13" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="L13" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
+      <c r="R13" s="15"/>
+      <c r="S13" s="15"/>
+      <c r="T13" s="15"/>
+      <c r="U13" s="15"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
-      <c r="U14" s="4"/>
+      <c r="A14" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="G14" s="14">
+        <v>1200.0</v>
+      </c>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="K14" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="L14" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
+      <c r="R14" s="15"/>
+      <c r="S14" s="15"/>
+      <c r="T14" s="15"/>
+      <c r="U14" s="15"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
-      <c r="U15" s="4"/>
+      <c r="A15" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="G15" s="14">
+        <v>1200.0</v>
+      </c>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="K15" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="L15" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="15"/>
+      <c r="T15" s="15"/>
+      <c r="U15" s="15"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
+      <c r="A16" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F16" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>1200.0</v>
+      </c>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="L16" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
+      <c r="R16" s="15"/>
+      <c r="S16" s="15"/>
+      <c r="T16" s="15"/>
+      <c r="U16" s="15"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
-      <c r="U17" s="4"/>
+      <c r="A17" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F17" s="14">
+        <v>12.0</v>
+      </c>
+      <c r="G17" s="14">
+        <v>1200.0</v>
+      </c>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
+      <c r="A18" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G18" s="14">
+        <v>800.0</v>
+      </c>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="K18" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -1275,19 +1548,41 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
+      <c r="A19" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="14">
+        <v>10.0</v>
+      </c>
+      <c r="G19" s="14">
+        <v>1600.0</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="K19" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L19" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
@@ -1298,19 +1593,41 @@
       <c r="U19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
+      <c r="A20" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="F20" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="G20" s="14">
+        <v>3000.0</v>
+      </c>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="K20" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L20" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
@@ -1321,19 +1638,41 @@
       <c r="U20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
+      <c r="A21" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D21" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="E21" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F21" s="14">
+        <v>20.0</v>
+      </c>
+      <c r="G21" s="14">
+        <v>5000.0</v>
+      </c>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K21" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="L21" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M21" s="13" t="s">
+        <v>52</v>
+      </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
@@ -5921,3124 +6260,3124 @@
       <c r="U220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="12"/>
-      <c r="B221" s="12"/>
+      <c r="A221" s="17"/>
+      <c r="B221" s="17"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="12"/>
-      <c r="B222" s="12"/>
+      <c r="A222" s="17"/>
+      <c r="B222" s="17"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="12"/>
-      <c r="B223" s="12"/>
+      <c r="A223" s="17"/>
+      <c r="B223" s="17"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="12"/>
-      <c r="B224" s="12"/>
+      <c r="A224" s="17"/>
+      <c r="B224" s="17"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="12"/>
-      <c r="B225" s="12"/>
+      <c r="A225" s="17"/>
+      <c r="B225" s="17"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="12"/>
-      <c r="B226" s="12"/>
+      <c r="A226" s="17"/>
+      <c r="B226" s="17"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="12"/>
-      <c r="B227" s="12"/>
+      <c r="A227" s="17"/>
+      <c r="B227" s="17"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="12"/>
-      <c r="B228" s="12"/>
+      <c r="A228" s="17"/>
+      <c r="B228" s="17"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="12"/>
-      <c r="B229" s="12"/>
+      <c r="A229" s="17"/>
+      <c r="B229" s="17"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="12"/>
-      <c r="B230" s="12"/>
+      <c r="A230" s="17"/>
+      <c r="B230" s="17"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="12"/>
-      <c r="B231" s="12"/>
+      <c r="A231" s="17"/>
+      <c r="B231" s="17"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="12"/>
-      <c r="B232" s="12"/>
+      <c r="A232" s="17"/>
+      <c r="B232" s="17"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="12"/>
-      <c r="B233" s="12"/>
+      <c r="A233" s="17"/>
+      <c r="B233" s="17"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="12"/>
-      <c r="B234" s="12"/>
+      <c r="A234" s="17"/>
+      <c r="B234" s="17"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="12"/>
-      <c r="B235" s="12"/>
+      <c r="A235" s="17"/>
+      <c r="B235" s="17"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="12"/>
-      <c r="B236" s="12"/>
+      <c r="A236" s="17"/>
+      <c r="B236" s="17"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="12"/>
-      <c r="B237" s="12"/>
+      <c r="A237" s="17"/>
+      <c r="B237" s="17"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="12"/>
-      <c r="B238" s="12"/>
+      <c r="A238" s="17"/>
+      <c r="B238" s="17"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="12"/>
-      <c r="B239" s="12"/>
+      <c r="A239" s="17"/>
+      <c r="B239" s="17"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="12"/>
-      <c r="B240" s="12"/>
+      <c r="A240" s="17"/>
+      <c r="B240" s="17"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="12"/>
-      <c r="B241" s="12"/>
+      <c r="A241" s="17"/>
+      <c r="B241" s="17"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="12"/>
-      <c r="B242" s="12"/>
+      <c r="A242" s="17"/>
+      <c r="B242" s="17"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="12"/>
-      <c r="B243" s="12"/>
+      <c r="A243" s="17"/>
+      <c r="B243" s="17"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="12"/>
-      <c r="B244" s="12"/>
+      <c r="A244" s="17"/>
+      <c r="B244" s="17"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="12"/>
-      <c r="B245" s="12"/>
+      <c r="A245" s="17"/>
+      <c r="B245" s="17"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="12"/>
-      <c r="B246" s="12"/>
+      <c r="A246" s="17"/>
+      <c r="B246" s="17"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="12"/>
-      <c r="B247" s="12"/>
+      <c r="A247" s="17"/>
+      <c r="B247" s="17"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="12"/>
-      <c r="B248" s="12"/>
+      <c r="A248" s="17"/>
+      <c r="B248" s="17"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="12"/>
-      <c r="B249" s="12"/>
+      <c r="A249" s="17"/>
+      <c r="B249" s="17"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="12"/>
-      <c r="B250" s="12"/>
+      <c r="A250" s="17"/>
+      <c r="B250" s="17"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="12"/>
-      <c r="B251" s="12"/>
+      <c r="A251" s="17"/>
+      <c r="B251" s="17"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="12"/>
-      <c r="B252" s="12"/>
+      <c r="A252" s="17"/>
+      <c r="B252" s="17"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="12"/>
-      <c r="B253" s="12"/>
+      <c r="A253" s="17"/>
+      <c r="B253" s="17"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="12"/>
-      <c r="B254" s="12"/>
+      <c r="A254" s="17"/>
+      <c r="B254" s="17"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="12"/>
-      <c r="B255" s="12"/>
+      <c r="A255" s="17"/>
+      <c r="B255" s="17"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="12"/>
-      <c r="B256" s="12"/>
+      <c r="A256" s="17"/>
+      <c r="B256" s="17"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="12"/>
-      <c r="B257" s="12"/>
+      <c r="A257" s="17"/>
+      <c r="B257" s="17"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="12"/>
-      <c r="B258" s="12"/>
+      <c r="A258" s="17"/>
+      <c r="B258" s="17"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="12"/>
-      <c r="B259" s="12"/>
+      <c r="A259" s="17"/>
+      <c r="B259" s="17"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="12"/>
-      <c r="B260" s="12"/>
+      <c r="A260" s="17"/>
+      <c r="B260" s="17"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="12"/>
-      <c r="B261" s="12"/>
+      <c r="A261" s="17"/>
+      <c r="B261" s="17"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="12"/>
-      <c r="B262" s="12"/>
+      <c r="A262" s="17"/>
+      <c r="B262" s="17"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="12"/>
-      <c r="B263" s="12"/>
+      <c r="A263" s="17"/>
+      <c r="B263" s="17"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="12"/>
-      <c r="B264" s="12"/>
+      <c r="A264" s="17"/>
+      <c r="B264" s="17"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="12"/>
-      <c r="B265" s="12"/>
+      <c r="A265" s="17"/>
+      <c r="B265" s="17"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="12"/>
-      <c r="B266" s="12"/>
+      <c r="A266" s="17"/>
+      <c r="B266" s="17"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="12"/>
-      <c r="B267" s="12"/>
+      <c r="A267" s="17"/>
+      <c r="B267" s="17"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="12"/>
-      <c r="B268" s="12"/>
+      <c r="A268" s="17"/>
+      <c r="B268" s="17"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="12"/>
-      <c r="B269" s="12"/>
+      <c r="A269" s="17"/>
+      <c r="B269" s="17"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="12"/>
-      <c r="B270" s="12"/>
+      <c r="A270" s="17"/>
+      <c r="B270" s="17"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="12"/>
-      <c r="B271" s="12"/>
+      <c r="A271" s="17"/>
+      <c r="B271" s="17"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="12"/>
-      <c r="B272" s="12"/>
+      <c r="A272" s="17"/>
+      <c r="B272" s="17"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="12"/>
-      <c r="B273" s="12"/>
+      <c r="A273" s="17"/>
+      <c r="B273" s="17"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="12"/>
-      <c r="B274" s="12"/>
+      <c r="A274" s="17"/>
+      <c r="B274" s="17"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="12"/>
-      <c r="B275" s="12"/>
+      <c r="A275" s="17"/>
+      <c r="B275" s="17"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="12"/>
-      <c r="B276" s="12"/>
+      <c r="A276" s="17"/>
+      <c r="B276" s="17"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="12"/>
-      <c r="B277" s="12"/>
+      <c r="A277" s="17"/>
+      <c r="B277" s="17"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="12"/>
-      <c r="B278" s="12"/>
+      <c r="A278" s="17"/>
+      <c r="B278" s="17"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="12"/>
-      <c r="B279" s="12"/>
+      <c r="A279" s="17"/>
+      <c r="B279" s="17"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="12"/>
-      <c r="B280" s="12"/>
+      <c r="A280" s="17"/>
+      <c r="B280" s="17"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="12"/>
-      <c r="B281" s="12"/>
+      <c r="A281" s="17"/>
+      <c r="B281" s="17"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="12"/>
-      <c r="B282" s="12"/>
+      <c r="A282" s="17"/>
+      <c r="B282" s="17"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="12"/>
-      <c r="B283" s="12"/>
+      <c r="A283" s="17"/>
+      <c r="B283" s="17"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="12"/>
-      <c r="B284" s="12"/>
+      <c r="A284" s="17"/>
+      <c r="B284" s="17"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="12"/>
-      <c r="B285" s="12"/>
+      <c r="A285" s="17"/>
+      <c r="B285" s="17"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="12"/>
-      <c r="B286" s="12"/>
+      <c r="A286" s="17"/>
+      <c r="B286" s="17"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="12"/>
-      <c r="B287" s="12"/>
+      <c r="A287" s="17"/>
+      <c r="B287" s="17"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="12"/>
-      <c r="B288" s="12"/>
+      <c r="A288" s="17"/>
+      <c r="B288" s="17"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="12"/>
-      <c r="B289" s="12"/>
+      <c r="A289" s="17"/>
+      <c r="B289" s="17"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="12"/>
-      <c r="B290" s="12"/>
+      <c r="A290" s="17"/>
+      <c r="B290" s="17"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="12"/>
-      <c r="B291" s="12"/>
+      <c r="A291" s="17"/>
+      <c r="B291" s="17"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="12"/>
-      <c r="B292" s="12"/>
+      <c r="A292" s="17"/>
+      <c r="B292" s="17"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="12"/>
-      <c r="B293" s="12"/>
+      <c r="A293" s="17"/>
+      <c r="B293" s="17"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="12"/>
-      <c r="B294" s="12"/>
+      <c r="A294" s="17"/>
+      <c r="B294" s="17"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="12"/>
-      <c r="B295" s="12"/>
+      <c r="A295" s="17"/>
+      <c r="B295" s="17"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="12"/>
-      <c r="B296" s="12"/>
+      <c r="A296" s="17"/>
+      <c r="B296" s="17"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="12"/>
-      <c r="B297" s="12"/>
+      <c r="A297" s="17"/>
+      <c r="B297" s="17"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="12"/>
-      <c r="B298" s="12"/>
+      <c r="A298" s="17"/>
+      <c r="B298" s="17"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="12"/>
-      <c r="B299" s="12"/>
+      <c r="A299" s="17"/>
+      <c r="B299" s="17"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="12"/>
-      <c r="B300" s="12"/>
+      <c r="A300" s="17"/>
+      <c r="B300" s="17"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="12"/>
-      <c r="B301" s="12"/>
+      <c r="A301" s="17"/>
+      <c r="B301" s="17"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="12"/>
-      <c r="B302" s="12"/>
+      <c r="A302" s="17"/>
+      <c r="B302" s="17"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="12"/>
-      <c r="B303" s="12"/>
+      <c r="A303" s="17"/>
+      <c r="B303" s="17"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="12"/>
-      <c r="B304" s="12"/>
+      <c r="A304" s="17"/>
+      <c r="B304" s="17"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="12"/>
-      <c r="B305" s="12"/>
+      <c r="A305" s="17"/>
+      <c r="B305" s="17"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="12"/>
-      <c r="B306" s="12"/>
+      <c r="A306" s="17"/>
+      <c r="B306" s="17"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="12"/>
-      <c r="B307" s="12"/>
+      <c r="A307" s="17"/>
+      <c r="B307" s="17"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="12"/>
-      <c r="B308" s="12"/>
+      <c r="A308" s="17"/>
+      <c r="B308" s="17"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="12"/>
-      <c r="B309" s="12"/>
+      <c r="A309" s="17"/>
+      <c r="B309" s="17"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="12"/>
-      <c r="B310" s="12"/>
+      <c r="A310" s="17"/>
+      <c r="B310" s="17"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="12"/>
-      <c r="B311" s="12"/>
+      <c r="A311" s="17"/>
+      <c r="B311" s="17"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="12"/>
-      <c r="B312" s="12"/>
+      <c r="A312" s="17"/>
+      <c r="B312" s="17"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="12"/>
-      <c r="B313" s="12"/>
+      <c r="A313" s="17"/>
+      <c r="B313" s="17"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="12"/>
-      <c r="B314" s="12"/>
+      <c r="A314" s="17"/>
+      <c r="B314" s="17"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="12"/>
-      <c r="B315" s="12"/>
+      <c r="A315" s="17"/>
+      <c r="B315" s="17"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="12"/>
-      <c r="B316" s="12"/>
+      <c r="A316" s="17"/>
+      <c r="B316" s="17"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="12"/>
-      <c r="B317" s="12"/>
+      <c r="A317" s="17"/>
+      <c r="B317" s="17"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="12"/>
-      <c r="B318" s="12"/>
+      <c r="A318" s="17"/>
+      <c r="B318" s="17"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="12"/>
-      <c r="B319" s="12"/>
+      <c r="A319" s="17"/>
+      <c r="B319" s="17"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="12"/>
-      <c r="B320" s="12"/>
+      <c r="A320" s="17"/>
+      <c r="B320" s="17"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="12"/>
-      <c r="B321" s="12"/>
+      <c r="A321" s="17"/>
+      <c r="B321" s="17"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="12"/>
-      <c r="B322" s="12"/>
+      <c r="A322" s="17"/>
+      <c r="B322" s="17"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="12"/>
-      <c r="B323" s="12"/>
+      <c r="A323" s="17"/>
+      <c r="B323" s="17"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="12"/>
-      <c r="B324" s="12"/>
+      <c r="A324" s="17"/>
+      <c r="B324" s="17"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="12"/>
-      <c r="B325" s="12"/>
+      <c r="A325" s="17"/>
+      <c r="B325" s="17"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="12"/>
-      <c r="B326" s="12"/>
+      <c r="A326" s="17"/>
+      <c r="B326" s="17"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="12"/>
-      <c r="B327" s="12"/>
+      <c r="A327" s="17"/>
+      <c r="B327" s="17"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="12"/>
-      <c r="B328" s="12"/>
+      <c r="A328" s="17"/>
+      <c r="B328" s="17"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="12"/>
-      <c r="B329" s="12"/>
+      <c r="A329" s="17"/>
+      <c r="B329" s="17"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="12"/>
-      <c r="B330" s="12"/>
+      <c r="A330" s="17"/>
+      <c r="B330" s="17"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="12"/>
-      <c r="B331" s="12"/>
+      <c r="A331" s="17"/>
+      <c r="B331" s="17"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="12"/>
-      <c r="B332" s="12"/>
+      <c r="A332" s="17"/>
+      <c r="B332" s="17"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="12"/>
-      <c r="B333" s="12"/>
+      <c r="A333" s="17"/>
+      <c r="B333" s="17"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="12"/>
-      <c r="B334" s="12"/>
+      <c r="A334" s="17"/>
+      <c r="B334" s="17"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="12"/>
-      <c r="B335" s="12"/>
+      <c r="A335" s="17"/>
+      <c r="B335" s="17"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="12"/>
-      <c r="B336" s="12"/>
+      <c r="A336" s="17"/>
+      <c r="B336" s="17"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="12"/>
-      <c r="B337" s="12"/>
+      <c r="A337" s="17"/>
+      <c r="B337" s="17"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="12"/>
-      <c r="B338" s="12"/>
+      <c r="A338" s="17"/>
+      <c r="B338" s="17"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="12"/>
-      <c r="B339" s="12"/>
+      <c r="A339" s="17"/>
+      <c r="B339" s="17"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="12"/>
-      <c r="B340" s="12"/>
+      <c r="A340" s="17"/>
+      <c r="B340" s="17"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="12"/>
-      <c r="B341" s="12"/>
+      <c r="A341" s="17"/>
+      <c r="B341" s="17"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="12"/>
-      <c r="B342" s="12"/>
+      <c r="A342" s="17"/>
+      <c r="B342" s="17"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="12"/>
-      <c r="B343" s="12"/>
+      <c r="A343" s="17"/>
+      <c r="B343" s="17"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="12"/>
-      <c r="B344" s="12"/>
+      <c r="A344" s="17"/>
+      <c r="B344" s="17"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="12"/>
-      <c r="B345" s="12"/>
+      <c r="A345" s="17"/>
+      <c r="B345" s="17"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="12"/>
-      <c r="B346" s="12"/>
+      <c r="A346" s="17"/>
+      <c r="B346" s="17"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="12"/>
-      <c r="B347" s="12"/>
+      <c r="A347" s="17"/>
+      <c r="B347" s="17"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="12"/>
-      <c r="B348" s="12"/>
+      <c r="A348" s="17"/>
+      <c r="B348" s="17"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="12"/>
-      <c r="B349" s="12"/>
+      <c r="A349" s="17"/>
+      <c r="B349" s="17"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="12"/>
-      <c r="B350" s="12"/>
+      <c r="A350" s="17"/>
+      <c r="B350" s="17"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="12"/>
-      <c r="B351" s="12"/>
+      <c r="A351" s="17"/>
+      <c r="B351" s="17"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="12"/>
-      <c r="B352" s="12"/>
+      <c r="A352" s="17"/>
+      <c r="B352" s="17"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="12"/>
-      <c r="B353" s="12"/>
+      <c r="A353" s="17"/>
+      <c r="B353" s="17"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="12"/>
-      <c r="B354" s="12"/>
+      <c r="A354" s="17"/>
+      <c r="B354" s="17"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="12"/>
-      <c r="B355" s="12"/>
+      <c r="A355" s="17"/>
+      <c r="B355" s="17"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="12"/>
-      <c r="B356" s="12"/>
+      <c r="A356" s="17"/>
+      <c r="B356" s="17"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="12"/>
-      <c r="B357" s="12"/>
+      <c r="A357" s="17"/>
+      <c r="B357" s="17"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="12"/>
-      <c r="B358" s="12"/>
+      <c r="A358" s="17"/>
+      <c r="B358" s="17"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="12"/>
-      <c r="B359" s="12"/>
+      <c r="A359" s="17"/>
+      <c r="B359" s="17"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="12"/>
-      <c r="B360" s="12"/>
+      <c r="A360" s="17"/>
+      <c r="B360" s="17"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="12"/>
-      <c r="B361" s="12"/>
+      <c r="A361" s="17"/>
+      <c r="B361" s="17"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="12"/>
-      <c r="B362" s="12"/>
+      <c r="A362" s="17"/>
+      <c r="B362" s="17"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="12"/>
-      <c r="B363" s="12"/>
+      <c r="A363" s="17"/>
+      <c r="B363" s="17"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="12"/>
-      <c r="B364" s="12"/>
+      <c r="A364" s="17"/>
+      <c r="B364" s="17"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="12"/>
-      <c r="B365" s="12"/>
+      <c r="A365" s="17"/>
+      <c r="B365" s="17"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="12"/>
-      <c r="B366" s="12"/>
+      <c r="A366" s="17"/>
+      <c r="B366" s="17"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="12"/>
-      <c r="B367" s="12"/>
+      <c r="A367" s="17"/>
+      <c r="B367" s="17"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="12"/>
-      <c r="B368" s="12"/>
+      <c r="A368" s="17"/>
+      <c r="B368" s="17"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="12"/>
-      <c r="B369" s="12"/>
+      <c r="A369" s="17"/>
+      <c r="B369" s="17"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="12"/>
-      <c r="B370" s="12"/>
+      <c r="A370" s="17"/>
+      <c r="B370" s="17"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="12"/>
-      <c r="B371" s="12"/>
+      <c r="A371" s="17"/>
+      <c r="B371" s="17"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="12"/>
-      <c r="B372" s="12"/>
+      <c r="A372" s="17"/>
+      <c r="B372" s="17"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="12"/>
-      <c r="B373" s="12"/>
+      <c r="A373" s="17"/>
+      <c r="B373" s="17"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="12"/>
-      <c r="B374" s="12"/>
+      <c r="A374" s="17"/>
+      <c r="B374" s="17"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="12"/>
-      <c r="B375" s="12"/>
+      <c r="A375" s="17"/>
+      <c r="B375" s="17"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="12"/>
-      <c r="B376" s="12"/>
+      <c r="A376" s="17"/>
+      <c r="B376" s="17"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="12"/>
-      <c r="B377" s="12"/>
+      <c r="A377" s="17"/>
+      <c r="B377" s="17"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="12"/>
-      <c r="B378" s="12"/>
+      <c r="A378" s="17"/>
+      <c r="B378" s="17"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="12"/>
-      <c r="B379" s="12"/>
+      <c r="A379" s="17"/>
+      <c r="B379" s="17"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="12"/>
-      <c r="B380" s="12"/>
+      <c r="A380" s="17"/>
+      <c r="B380" s="17"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="12"/>
-      <c r="B381" s="12"/>
+      <c r="A381" s="17"/>
+      <c r="B381" s="17"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="12"/>
-      <c r="B382" s="12"/>
+      <c r="A382" s="17"/>
+      <c r="B382" s="17"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="12"/>
-      <c r="B383" s="12"/>
+      <c r="A383" s="17"/>
+      <c r="B383" s="17"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="12"/>
-      <c r="B384" s="12"/>
+      <c r="A384" s="17"/>
+      <c r="B384" s="17"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="12"/>
-      <c r="B385" s="12"/>
+      <c r="A385" s="17"/>
+      <c r="B385" s="17"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="12"/>
-      <c r="B386" s="12"/>
+      <c r="A386" s="17"/>
+      <c r="B386" s="17"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="12"/>
-      <c r="B387" s="12"/>
+      <c r="A387" s="17"/>
+      <c r="B387" s="17"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="12"/>
-      <c r="B388" s="12"/>
+      <c r="A388" s="17"/>
+      <c r="B388" s="17"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="12"/>
-      <c r="B389" s="12"/>
+      <c r="A389" s="17"/>
+      <c r="B389" s="17"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="12"/>
-      <c r="B390" s="12"/>
+      <c r="A390" s="17"/>
+      <c r="B390" s="17"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="12"/>
-      <c r="B391" s="12"/>
+      <c r="A391" s="17"/>
+      <c r="B391" s="17"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="12"/>
-      <c r="B392" s="12"/>
+      <c r="A392" s="17"/>
+      <c r="B392" s="17"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="12"/>
-      <c r="B393" s="12"/>
+      <c r="A393" s="17"/>
+      <c r="B393" s="17"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="12"/>
-      <c r="B394" s="12"/>
+      <c r="A394" s="17"/>
+      <c r="B394" s="17"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="12"/>
-      <c r="B395" s="12"/>
+      <c r="A395" s="17"/>
+      <c r="B395" s="17"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="12"/>
-      <c r="B396" s="12"/>
+      <c r="A396" s="17"/>
+      <c r="B396" s="17"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="12"/>
-      <c r="B397" s="12"/>
+      <c r="A397" s="17"/>
+      <c r="B397" s="17"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="12"/>
-      <c r="B398" s="12"/>
+      <c r="A398" s="17"/>
+      <c r="B398" s="17"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="12"/>
-      <c r="B399" s="12"/>
+      <c r="A399" s="17"/>
+      <c r="B399" s="17"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="12"/>
-      <c r="B400" s="12"/>
+      <c r="A400" s="17"/>
+      <c r="B400" s="17"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="12"/>
-      <c r="B401" s="12"/>
+      <c r="A401" s="17"/>
+      <c r="B401" s="17"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="12"/>
-      <c r="B402" s="12"/>
+      <c r="A402" s="17"/>
+      <c r="B402" s="17"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="12"/>
-      <c r="B403" s="12"/>
+      <c r="A403" s="17"/>
+      <c r="B403" s="17"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="12"/>
-      <c r="B404" s="12"/>
+      <c r="A404" s="17"/>
+      <c r="B404" s="17"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="12"/>
-      <c r="B405" s="12"/>
+      <c r="A405" s="17"/>
+      <c r="B405" s="17"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="12"/>
-      <c r="B406" s="12"/>
+      <c r="A406" s="17"/>
+      <c r="B406" s="17"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="12"/>
-      <c r="B407" s="12"/>
+      <c r="A407" s="17"/>
+      <c r="B407" s="17"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="12"/>
-      <c r="B408" s="12"/>
+      <c r="A408" s="17"/>
+      <c r="B408" s="17"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="12"/>
-      <c r="B409" s="12"/>
+      <c r="A409" s="17"/>
+      <c r="B409" s="17"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="12"/>
-      <c r="B410" s="12"/>
+      <c r="A410" s="17"/>
+      <c r="B410" s="17"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="12"/>
-      <c r="B411" s="12"/>
+      <c r="A411" s="17"/>
+      <c r="B411" s="17"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="12"/>
-      <c r="B412" s="12"/>
+      <c r="A412" s="17"/>
+      <c r="B412" s="17"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="12"/>
-      <c r="B413" s="12"/>
+      <c r="A413" s="17"/>
+      <c r="B413" s="17"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="12"/>
-      <c r="B414" s="12"/>
+      <c r="A414" s="17"/>
+      <c r="B414" s="17"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="12"/>
-      <c r="B415" s="12"/>
+      <c r="A415" s="17"/>
+      <c r="B415" s="17"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="12"/>
-      <c r="B416" s="12"/>
+      <c r="A416" s="17"/>
+      <c r="B416" s="17"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="12"/>
-      <c r="B417" s="12"/>
+      <c r="A417" s="17"/>
+      <c r="B417" s="17"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="12"/>
-      <c r="B418" s="12"/>
+      <c r="A418" s="17"/>
+      <c r="B418" s="17"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="12"/>
-      <c r="B419" s="12"/>
+      <c r="A419" s="17"/>
+      <c r="B419" s="17"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="12"/>
-      <c r="B420" s="12"/>
+      <c r="A420" s="17"/>
+      <c r="B420" s="17"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="12"/>
-      <c r="B421" s="12"/>
+      <c r="A421" s="17"/>
+      <c r="B421" s="17"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="12"/>
-      <c r="B422" s="12"/>
+      <c r="A422" s="17"/>
+      <c r="B422" s="17"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="12"/>
-      <c r="B423" s="12"/>
+      <c r="A423" s="17"/>
+      <c r="B423" s="17"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="12"/>
-      <c r="B424" s="12"/>
+      <c r="A424" s="17"/>
+      <c r="B424" s="17"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="12"/>
-      <c r="B425" s="12"/>
+      <c r="A425" s="17"/>
+      <c r="B425" s="17"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="12"/>
-      <c r="B426" s="12"/>
+      <c r="A426" s="17"/>
+      <c r="B426" s="17"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="12"/>
-      <c r="B427" s="12"/>
+      <c r="A427" s="17"/>
+      <c r="B427" s="17"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="12"/>
-      <c r="B428" s="12"/>
+      <c r="A428" s="17"/>
+      <c r="B428" s="17"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="12"/>
-      <c r="B429" s="12"/>
+      <c r="A429" s="17"/>
+      <c r="B429" s="17"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="12"/>
-      <c r="B430" s="12"/>
+      <c r="A430" s="17"/>
+      <c r="B430" s="17"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="12"/>
-      <c r="B431" s="12"/>
+      <c r="A431" s="17"/>
+      <c r="B431" s="17"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="12"/>
-      <c r="B432" s="12"/>
+      <c r="A432" s="17"/>
+      <c r="B432" s="17"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="12"/>
-      <c r="B433" s="12"/>
+      <c r="A433" s="17"/>
+      <c r="B433" s="17"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="12"/>
-      <c r="B434" s="12"/>
+      <c r="A434" s="17"/>
+      <c r="B434" s="17"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="12"/>
-      <c r="B435" s="12"/>
+      <c r="A435" s="17"/>
+      <c r="B435" s="17"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="12"/>
-      <c r="B436" s="12"/>
+      <c r="A436" s="17"/>
+      <c r="B436" s="17"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="12"/>
-      <c r="B437" s="12"/>
+      <c r="A437" s="17"/>
+      <c r="B437" s="17"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="12"/>
-      <c r="B438" s="12"/>
+      <c r="A438" s="17"/>
+      <c r="B438" s="17"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="12"/>
-      <c r="B439" s="12"/>
+      <c r="A439" s="17"/>
+      <c r="B439" s="17"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="12"/>
-      <c r="B440" s="12"/>
+      <c r="A440" s="17"/>
+      <c r="B440" s="17"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="12"/>
-      <c r="B441" s="12"/>
+      <c r="A441" s="17"/>
+      <c r="B441" s="17"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="12"/>
-      <c r="B442" s="12"/>
+      <c r="A442" s="17"/>
+      <c r="B442" s="17"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="12"/>
-      <c r="B443" s="12"/>
+      <c r="A443" s="17"/>
+      <c r="B443" s="17"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="12"/>
-      <c r="B444" s="12"/>
+      <c r="A444" s="17"/>
+      <c r="B444" s="17"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="12"/>
-      <c r="B445" s="12"/>
+      <c r="A445" s="17"/>
+      <c r="B445" s="17"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="12"/>
-      <c r="B446" s="12"/>
+      <c r="A446" s="17"/>
+      <c r="B446" s="17"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="12"/>
-      <c r="B447" s="12"/>
+      <c r="A447" s="17"/>
+      <c r="B447" s="17"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="12"/>
-      <c r="B448" s="12"/>
+      <c r="A448" s="17"/>
+      <c r="B448" s="17"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="12"/>
-      <c r="B449" s="12"/>
+      <c r="A449" s="17"/>
+      <c r="B449" s="17"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="12"/>
-      <c r="B450" s="12"/>
+      <c r="A450" s="17"/>
+      <c r="B450" s="17"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="12"/>
-      <c r="B451" s="12"/>
+      <c r="A451" s="17"/>
+      <c r="B451" s="17"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="12"/>
-      <c r="B452" s="12"/>
+      <c r="A452" s="17"/>
+      <c r="B452" s="17"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="12"/>
-      <c r="B453" s="12"/>
+      <c r="A453" s="17"/>
+      <c r="B453" s="17"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="12"/>
-      <c r="B454" s="12"/>
+      <c r="A454" s="17"/>
+      <c r="B454" s="17"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="12"/>
-      <c r="B455" s="12"/>
+      <c r="A455" s="17"/>
+      <c r="B455" s="17"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="12"/>
-      <c r="B456" s="12"/>
+      <c r="A456" s="17"/>
+      <c r="B456" s="17"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="12"/>
-      <c r="B457" s="12"/>
+      <c r="A457" s="17"/>
+      <c r="B457" s="17"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="12"/>
-      <c r="B458" s="12"/>
+      <c r="A458" s="17"/>
+      <c r="B458" s="17"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="12"/>
-      <c r="B459" s="12"/>
+      <c r="A459" s="17"/>
+      <c r="B459" s="17"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="12"/>
-      <c r="B460" s="12"/>
+      <c r="A460" s="17"/>
+      <c r="B460" s="17"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="12"/>
-      <c r="B461" s="12"/>
+      <c r="A461" s="17"/>
+      <c r="B461" s="17"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="12"/>
-      <c r="B462" s="12"/>
+      <c r="A462" s="17"/>
+      <c r="B462" s="17"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="12"/>
-      <c r="B463" s="12"/>
+      <c r="A463" s="17"/>
+      <c r="B463" s="17"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="12"/>
-      <c r="B464" s="12"/>
+      <c r="A464" s="17"/>
+      <c r="B464" s="17"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="12"/>
-      <c r="B465" s="12"/>
+      <c r="A465" s="17"/>
+      <c r="B465" s="17"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="12"/>
-      <c r="B466" s="12"/>
+      <c r="A466" s="17"/>
+      <c r="B466" s="17"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="12"/>
-      <c r="B467" s="12"/>
+      <c r="A467" s="17"/>
+      <c r="B467" s="17"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="12"/>
-      <c r="B468" s="12"/>
+      <c r="A468" s="17"/>
+      <c r="B468" s="17"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="12"/>
-      <c r="B469" s="12"/>
+      <c r="A469" s="17"/>
+      <c r="B469" s="17"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="12"/>
-      <c r="B470" s="12"/>
+      <c r="A470" s="17"/>
+      <c r="B470" s="17"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="12"/>
-      <c r="B471" s="12"/>
+      <c r="A471" s="17"/>
+      <c r="B471" s="17"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="12"/>
-      <c r="B472" s="12"/>
+      <c r="A472" s="17"/>
+      <c r="B472" s="17"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="12"/>
-      <c r="B473" s="12"/>
+      <c r="A473" s="17"/>
+      <c r="B473" s="17"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="12"/>
-      <c r="B474" s="12"/>
+      <c r="A474" s="17"/>
+      <c r="B474" s="17"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="12"/>
-      <c r="B475" s="12"/>
+      <c r="A475" s="17"/>
+      <c r="B475" s="17"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="12"/>
-      <c r="B476" s="12"/>
+      <c r="A476" s="17"/>
+      <c r="B476" s="17"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="12"/>
-      <c r="B477" s="12"/>
+      <c r="A477" s="17"/>
+      <c r="B477" s="17"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="12"/>
-      <c r="B478" s="12"/>
+      <c r="A478" s="17"/>
+      <c r="B478" s="17"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="12"/>
-      <c r="B479" s="12"/>
+      <c r="A479" s="17"/>
+      <c r="B479" s="17"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="12"/>
-      <c r="B480" s="12"/>
+      <c r="A480" s="17"/>
+      <c r="B480" s="17"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="12"/>
-      <c r="B481" s="12"/>
+      <c r="A481" s="17"/>
+      <c r="B481" s="17"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="12"/>
-      <c r="B482" s="12"/>
+      <c r="A482" s="17"/>
+      <c r="B482" s="17"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="12"/>
-      <c r="B483" s="12"/>
+      <c r="A483" s="17"/>
+      <c r="B483" s="17"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="12"/>
-      <c r="B484" s="12"/>
+      <c r="A484" s="17"/>
+      <c r="B484" s="17"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="12"/>
-      <c r="B485" s="12"/>
+      <c r="A485" s="17"/>
+      <c r="B485" s="17"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="12"/>
-      <c r="B486" s="12"/>
+      <c r="A486" s="17"/>
+      <c r="B486" s="17"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="12"/>
-      <c r="B487" s="12"/>
+      <c r="A487" s="17"/>
+      <c r="B487" s="17"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="12"/>
-      <c r="B488" s="12"/>
+      <c r="A488" s="17"/>
+      <c r="B488" s="17"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="12"/>
-      <c r="B489" s="12"/>
+      <c r="A489" s="17"/>
+      <c r="B489" s="17"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="12"/>
-      <c r="B490" s="12"/>
+      <c r="A490" s="17"/>
+      <c r="B490" s="17"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="12"/>
-      <c r="B491" s="12"/>
+      <c r="A491" s="17"/>
+      <c r="B491" s="17"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="12"/>
-      <c r="B492" s="12"/>
+      <c r="A492" s="17"/>
+      <c r="B492" s="17"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="12"/>
-      <c r="B493" s="12"/>
+      <c r="A493" s="17"/>
+      <c r="B493" s="17"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="12"/>
-      <c r="B494" s="12"/>
+      <c r="A494" s="17"/>
+      <c r="B494" s="17"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="12"/>
-      <c r="B495" s="12"/>
+      <c r="A495" s="17"/>
+      <c r="B495" s="17"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="12"/>
-      <c r="B496" s="12"/>
+      <c r="A496" s="17"/>
+      <c r="B496" s="17"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="12"/>
-      <c r="B497" s="12"/>
+      <c r="A497" s="17"/>
+      <c r="B497" s="17"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="12"/>
-      <c r="B498" s="12"/>
+      <c r="A498" s="17"/>
+      <c r="B498" s="17"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="12"/>
-      <c r="B499" s="12"/>
+      <c r="A499" s="17"/>
+      <c r="B499" s="17"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="12"/>
-      <c r="B500" s="12"/>
+      <c r="A500" s="17"/>
+      <c r="B500" s="17"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="12"/>
-      <c r="B501" s="12"/>
+      <c r="A501" s="17"/>
+      <c r="B501" s="17"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="12"/>
-      <c r="B502" s="12"/>
+      <c r="A502" s="17"/>
+      <c r="B502" s="17"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="12"/>
-      <c r="B503" s="12"/>
+      <c r="A503" s="17"/>
+      <c r="B503" s="17"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="12"/>
-      <c r="B504" s="12"/>
+      <c r="A504" s="17"/>
+      <c r="B504" s="17"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="12"/>
-      <c r="B505" s="12"/>
+      <c r="A505" s="17"/>
+      <c r="B505" s="17"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="12"/>
-      <c r="B506" s="12"/>
+      <c r="A506" s="17"/>
+      <c r="B506" s="17"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="12"/>
-      <c r="B507" s="12"/>
+      <c r="A507" s="17"/>
+      <c r="B507" s="17"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="12"/>
-      <c r="B508" s="12"/>
+      <c r="A508" s="17"/>
+      <c r="B508" s="17"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="12"/>
-      <c r="B509" s="12"/>
+      <c r="A509" s="17"/>
+      <c r="B509" s="17"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="12"/>
-      <c r="B510" s="12"/>
+      <c r="A510" s="17"/>
+      <c r="B510" s="17"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="12"/>
-      <c r="B511" s="12"/>
+      <c r="A511" s="17"/>
+      <c r="B511" s="17"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="12"/>
-      <c r="B512" s="12"/>
+      <c r="A512" s="17"/>
+      <c r="B512" s="17"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="12"/>
-      <c r="B513" s="12"/>
+      <c r="A513" s="17"/>
+      <c r="B513" s="17"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="12"/>
-      <c r="B514" s="12"/>
+      <c r="A514" s="17"/>
+      <c r="B514" s="17"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="12"/>
-      <c r="B515" s="12"/>
+      <c r="A515" s="17"/>
+      <c r="B515" s="17"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="12"/>
-      <c r="B516" s="12"/>
+      <c r="A516" s="17"/>
+      <c r="B516" s="17"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="12"/>
-      <c r="B517" s="12"/>
+      <c r="A517" s="17"/>
+      <c r="B517" s="17"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="12"/>
-      <c r="B518" s="12"/>
+      <c r="A518" s="17"/>
+      <c r="B518" s="17"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="12"/>
-      <c r="B519" s="12"/>
+      <c r="A519" s="17"/>
+      <c r="B519" s="17"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="12"/>
-      <c r="B520" s="12"/>
+      <c r="A520" s="17"/>
+      <c r="B520" s="17"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="12"/>
-      <c r="B521" s="12"/>
+      <c r="A521" s="17"/>
+      <c r="B521" s="17"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="12"/>
-      <c r="B522" s="12"/>
+      <c r="A522" s="17"/>
+      <c r="B522" s="17"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="12"/>
-      <c r="B523" s="12"/>
+      <c r="A523" s="17"/>
+      <c r="B523" s="17"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="12"/>
-      <c r="B524" s="12"/>
+      <c r="A524" s="17"/>
+      <c r="B524" s="17"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="12"/>
-      <c r="B525" s="12"/>
+      <c r="A525" s="17"/>
+      <c r="B525" s="17"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="12"/>
-      <c r="B526" s="12"/>
+      <c r="A526" s="17"/>
+      <c r="B526" s="17"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="12"/>
-      <c r="B527" s="12"/>
+      <c r="A527" s="17"/>
+      <c r="B527" s="17"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="12"/>
-      <c r="B528" s="12"/>
+      <c r="A528" s="17"/>
+      <c r="B528" s="17"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="12"/>
-      <c r="B529" s="12"/>
+      <c r="A529" s="17"/>
+      <c r="B529" s="17"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="12"/>
-      <c r="B530" s="12"/>
+      <c r="A530" s="17"/>
+      <c r="B530" s="17"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="12"/>
-      <c r="B531" s="12"/>
+      <c r="A531" s="17"/>
+      <c r="B531" s="17"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="12"/>
-      <c r="B532" s="12"/>
+      <c r="A532" s="17"/>
+      <c r="B532" s="17"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="12"/>
-      <c r="B533" s="12"/>
+      <c r="A533" s="17"/>
+      <c r="B533" s="17"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="12"/>
-      <c r="B534" s="12"/>
+      <c r="A534" s="17"/>
+      <c r="B534" s="17"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="12"/>
-      <c r="B535" s="12"/>
+      <c r="A535" s="17"/>
+      <c r="B535" s="17"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="12"/>
-      <c r="B536" s="12"/>
+      <c r="A536" s="17"/>
+      <c r="B536" s="17"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="12"/>
-      <c r="B537" s="12"/>
+      <c r="A537" s="17"/>
+      <c r="B537" s="17"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="12"/>
-      <c r="B538" s="12"/>
+      <c r="A538" s="17"/>
+      <c r="B538" s="17"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="12"/>
-      <c r="B539" s="12"/>
+      <c r="A539" s="17"/>
+      <c r="B539" s="17"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="12"/>
-      <c r="B540" s="12"/>
+      <c r="A540" s="17"/>
+      <c r="B540" s="17"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="12"/>
-      <c r="B541" s="12"/>
+      <c r="A541" s="17"/>
+      <c r="B541" s="17"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="12"/>
-      <c r="B542" s="12"/>
+      <c r="A542" s="17"/>
+      <c r="B542" s="17"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="12"/>
-      <c r="B543" s="12"/>
+      <c r="A543" s="17"/>
+      <c r="B543" s="17"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="12"/>
-      <c r="B544" s="12"/>
+      <c r="A544" s="17"/>
+      <c r="B544" s="17"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="12"/>
-      <c r="B545" s="12"/>
+      <c r="A545" s="17"/>
+      <c r="B545" s="17"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="12"/>
-      <c r="B546" s="12"/>
+      <c r="A546" s="17"/>
+      <c r="B546" s="17"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="12"/>
-      <c r="B547" s="12"/>
+      <c r="A547" s="17"/>
+      <c r="B547" s="17"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="12"/>
-      <c r="B548" s="12"/>
+      <c r="A548" s="17"/>
+      <c r="B548" s="17"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="12"/>
-      <c r="B549" s="12"/>
+      <c r="A549" s="17"/>
+      <c r="B549" s="17"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="12"/>
-      <c r="B550" s="12"/>
+      <c r="A550" s="17"/>
+      <c r="B550" s="17"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="12"/>
-      <c r="B551" s="12"/>
+      <c r="A551" s="17"/>
+      <c r="B551" s="17"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="12"/>
-      <c r="B552" s="12"/>
+      <c r="A552" s="17"/>
+      <c r="B552" s="17"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="12"/>
-      <c r="B553" s="12"/>
+      <c r="A553" s="17"/>
+      <c r="B553" s="17"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="12"/>
-      <c r="B554" s="12"/>
+      <c r="A554" s="17"/>
+      <c r="B554" s="17"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="12"/>
-      <c r="B555" s="12"/>
+      <c r="A555" s="17"/>
+      <c r="B555" s="17"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="12"/>
-      <c r="B556" s="12"/>
+      <c r="A556" s="17"/>
+      <c r="B556" s="17"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="12"/>
-      <c r="B557" s="12"/>
+      <c r="A557" s="17"/>
+      <c r="B557" s="17"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="12"/>
-      <c r="B558" s="12"/>
+      <c r="A558" s="17"/>
+      <c r="B558" s="17"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="12"/>
-      <c r="B559" s="12"/>
+      <c r="A559" s="17"/>
+      <c r="B559" s="17"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="12"/>
-      <c r="B560" s="12"/>
+      <c r="A560" s="17"/>
+      <c r="B560" s="17"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="12"/>
-      <c r="B561" s="12"/>
+      <c r="A561" s="17"/>
+      <c r="B561" s="17"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="12"/>
-      <c r="B562" s="12"/>
+      <c r="A562" s="17"/>
+      <c r="B562" s="17"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="12"/>
-      <c r="B563" s="12"/>
+      <c r="A563" s="17"/>
+      <c r="B563" s="17"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="12"/>
-      <c r="B564" s="12"/>
+      <c r="A564" s="17"/>
+      <c r="B564" s="17"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="12"/>
-      <c r="B565" s="12"/>
+      <c r="A565" s="17"/>
+      <c r="B565" s="17"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="12"/>
-      <c r="B566" s="12"/>
+      <c r="A566" s="17"/>
+      <c r="B566" s="17"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="12"/>
-      <c r="B567" s="12"/>
+      <c r="A567" s="17"/>
+      <c r="B567" s="17"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="12"/>
-      <c r="B568" s="12"/>
+      <c r="A568" s="17"/>
+      <c r="B568" s="17"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="12"/>
-      <c r="B569" s="12"/>
+      <c r="A569" s="17"/>
+      <c r="B569" s="17"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="12"/>
-      <c r="B570" s="12"/>
+      <c r="A570" s="17"/>
+      <c r="B570" s="17"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="12"/>
-      <c r="B571" s="12"/>
+      <c r="A571" s="17"/>
+      <c r="B571" s="17"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="12"/>
-      <c r="B572" s="12"/>
+      <c r="A572" s="17"/>
+      <c r="B572" s="17"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="12"/>
-      <c r="B573" s="12"/>
+      <c r="A573" s="17"/>
+      <c r="B573" s="17"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="12"/>
-      <c r="B574" s="12"/>
+      <c r="A574" s="17"/>
+      <c r="B574" s="17"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="12"/>
-      <c r="B575" s="12"/>
+      <c r="A575" s="17"/>
+      <c r="B575" s="17"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="12"/>
-      <c r="B576" s="12"/>
+      <c r="A576" s="17"/>
+      <c r="B576" s="17"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="12"/>
-      <c r="B577" s="12"/>
+      <c r="A577" s="17"/>
+      <c r="B577" s="17"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="12"/>
-      <c r="B578" s="12"/>
+      <c r="A578" s="17"/>
+      <c r="B578" s="17"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="12"/>
-      <c r="B579" s="12"/>
+      <c r="A579" s="17"/>
+      <c r="B579" s="17"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="12"/>
-      <c r="B580" s="12"/>
+      <c r="A580" s="17"/>
+      <c r="B580" s="17"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="12"/>
-      <c r="B581" s="12"/>
+      <c r="A581" s="17"/>
+      <c r="B581" s="17"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="12"/>
-      <c r="B582" s="12"/>
+      <c r="A582" s="17"/>
+      <c r="B582" s="17"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="12"/>
-      <c r="B583" s="12"/>
+      <c r="A583" s="17"/>
+      <c r="B583" s="17"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="12"/>
-      <c r="B584" s="12"/>
+      <c r="A584" s="17"/>
+      <c r="B584" s="17"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="12"/>
-      <c r="B585" s="12"/>
+      <c r="A585" s="17"/>
+      <c r="B585" s="17"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="12"/>
-      <c r="B586" s="12"/>
+      <c r="A586" s="17"/>
+      <c r="B586" s="17"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="12"/>
-      <c r="B587" s="12"/>
+      <c r="A587" s="17"/>
+      <c r="B587" s="17"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="12"/>
-      <c r="B588" s="12"/>
+      <c r="A588" s="17"/>
+      <c r="B588" s="17"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="12"/>
-      <c r="B589" s="12"/>
+      <c r="A589" s="17"/>
+      <c r="B589" s="17"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="12"/>
-      <c r="B590" s="12"/>
+      <c r="A590" s="17"/>
+      <c r="B590" s="17"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="12"/>
-      <c r="B591" s="12"/>
+      <c r="A591" s="17"/>
+      <c r="B591" s="17"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="12"/>
-      <c r="B592" s="12"/>
+      <c r="A592" s="17"/>
+      <c r="B592" s="17"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="12"/>
-      <c r="B593" s="12"/>
+      <c r="A593" s="17"/>
+      <c r="B593" s="17"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="12"/>
-      <c r="B594" s="12"/>
+      <c r="A594" s="17"/>
+      <c r="B594" s="17"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="12"/>
-      <c r="B595" s="12"/>
+      <c r="A595" s="17"/>
+      <c r="B595" s="17"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="12"/>
-      <c r="B596" s="12"/>
+      <c r="A596" s="17"/>
+      <c r="B596" s="17"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="12"/>
-      <c r="B597" s="12"/>
+      <c r="A597" s="17"/>
+      <c r="B597" s="17"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="12"/>
-      <c r="B598" s="12"/>
+      <c r="A598" s="17"/>
+      <c r="B598" s="17"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="12"/>
-      <c r="B599" s="12"/>
+      <c r="A599" s="17"/>
+      <c r="B599" s="17"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="12"/>
-      <c r="B600" s="12"/>
+      <c r="A600" s="17"/>
+      <c r="B600" s="17"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="12"/>
-      <c r="B601" s="12"/>
+      <c r="A601" s="17"/>
+      <c r="B601" s="17"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="12"/>
-      <c r="B602" s="12"/>
+      <c r="A602" s="17"/>
+      <c r="B602" s="17"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="12"/>
-      <c r="B603" s="12"/>
+      <c r="A603" s="17"/>
+      <c r="B603" s="17"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="12"/>
-      <c r="B604" s="12"/>
+      <c r="A604" s="17"/>
+      <c r="B604" s="17"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="12"/>
-      <c r="B605" s="12"/>
+      <c r="A605" s="17"/>
+      <c r="B605" s="17"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="12"/>
-      <c r="B606" s="12"/>
+      <c r="A606" s="17"/>
+      <c r="B606" s="17"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="12"/>
-      <c r="B607" s="12"/>
+      <c r="A607" s="17"/>
+      <c r="B607" s="17"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="12"/>
-      <c r="B608" s="12"/>
+      <c r="A608" s="17"/>
+      <c r="B608" s="17"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="12"/>
-      <c r="B609" s="12"/>
+      <c r="A609" s="17"/>
+      <c r="B609" s="17"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="12"/>
-      <c r="B610" s="12"/>
+      <c r="A610" s="17"/>
+      <c r="B610" s="17"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="12"/>
-      <c r="B611" s="12"/>
+      <c r="A611" s="17"/>
+      <c r="B611" s="17"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="12"/>
-      <c r="B612" s="12"/>
+      <c r="A612" s="17"/>
+      <c r="B612" s="17"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="12"/>
-      <c r="B613" s="12"/>
+      <c r="A613" s="17"/>
+      <c r="B613" s="17"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="12"/>
-      <c r="B614" s="12"/>
+      <c r="A614" s="17"/>
+      <c r="B614" s="17"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="12"/>
-      <c r="B615" s="12"/>
+      <c r="A615" s="17"/>
+      <c r="B615" s="17"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="12"/>
-      <c r="B616" s="12"/>
+      <c r="A616" s="17"/>
+      <c r="B616" s="17"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="12"/>
-      <c r="B617" s="12"/>
+      <c r="A617" s="17"/>
+      <c r="B617" s="17"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="12"/>
-      <c r="B618" s="12"/>
+      <c r="A618" s="17"/>
+      <c r="B618" s="17"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="12"/>
-      <c r="B619" s="12"/>
+      <c r="A619" s="17"/>
+      <c r="B619" s="17"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="12"/>
-      <c r="B620" s="12"/>
+      <c r="A620" s="17"/>
+      <c r="B620" s="17"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="12"/>
-      <c r="B621" s="12"/>
+      <c r="A621" s="17"/>
+      <c r="B621" s="17"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="12"/>
-      <c r="B622" s="12"/>
+      <c r="A622" s="17"/>
+      <c r="B622" s="17"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="12"/>
-      <c r="B623" s="12"/>
+      <c r="A623" s="17"/>
+      <c r="B623" s="17"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="12"/>
-      <c r="B624" s="12"/>
+      <c r="A624" s="17"/>
+      <c r="B624" s="17"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="12"/>
-      <c r="B625" s="12"/>
+      <c r="A625" s="17"/>
+      <c r="B625" s="17"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="12"/>
-      <c r="B626" s="12"/>
+      <c r="A626" s="17"/>
+      <c r="B626" s="17"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="12"/>
-      <c r="B627" s="12"/>
+      <c r="A627" s="17"/>
+      <c r="B627" s="17"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="12"/>
-      <c r="B628" s="12"/>
+      <c r="A628" s="17"/>
+      <c r="B628" s="17"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="12"/>
-      <c r="B629" s="12"/>
+      <c r="A629" s="17"/>
+      <c r="B629" s="17"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="12"/>
-      <c r="B630" s="12"/>
+      <c r="A630" s="17"/>
+      <c r="B630" s="17"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="12"/>
-      <c r="B631" s="12"/>
+      <c r="A631" s="17"/>
+      <c r="B631" s="17"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="12"/>
-      <c r="B632" s="12"/>
+      <c r="A632" s="17"/>
+      <c r="B632" s="17"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="12"/>
-      <c r="B633" s="12"/>
+      <c r="A633" s="17"/>
+      <c r="B633" s="17"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="12"/>
-      <c r="B634" s="12"/>
+      <c r="A634" s="17"/>
+      <c r="B634" s="17"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="12"/>
-      <c r="B635" s="12"/>
+      <c r="A635" s="17"/>
+      <c r="B635" s="17"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="12"/>
-      <c r="B636" s="12"/>
+      <c r="A636" s="17"/>
+      <c r="B636" s="17"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="12"/>
-      <c r="B637" s="12"/>
+      <c r="A637" s="17"/>
+      <c r="B637" s="17"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="12"/>
-      <c r="B638" s="12"/>
+      <c r="A638" s="17"/>
+      <c r="B638" s="17"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="12"/>
-      <c r="B639" s="12"/>
+      <c r="A639" s="17"/>
+      <c r="B639" s="17"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="12"/>
-      <c r="B640" s="12"/>
+      <c r="A640" s="17"/>
+      <c r="B640" s="17"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="12"/>
-      <c r="B641" s="12"/>
+      <c r="A641" s="17"/>
+      <c r="B641" s="17"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="12"/>
-      <c r="B642" s="12"/>
+      <c r="A642" s="17"/>
+      <c r="B642" s="17"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="12"/>
-      <c r="B643" s="12"/>
+      <c r="A643" s="17"/>
+      <c r="B643" s="17"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="12"/>
-      <c r="B644" s="12"/>
+      <c r="A644" s="17"/>
+      <c r="B644" s="17"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="12"/>
-      <c r="B645" s="12"/>
+      <c r="A645" s="17"/>
+      <c r="B645" s="17"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="12"/>
-      <c r="B646" s="12"/>
+      <c r="A646" s="17"/>
+      <c r="B646" s="17"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="12"/>
-      <c r="B647" s="12"/>
+      <c r="A647" s="17"/>
+      <c r="B647" s="17"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="12"/>
-      <c r="B648" s="12"/>
+      <c r="A648" s="17"/>
+      <c r="B648" s="17"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="12"/>
-      <c r="B649" s="12"/>
+      <c r="A649" s="17"/>
+      <c r="B649" s="17"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="12"/>
-      <c r="B650" s="12"/>
+      <c r="A650" s="17"/>
+      <c r="B650" s="17"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="12"/>
-      <c r="B651" s="12"/>
+      <c r="A651" s="17"/>
+      <c r="B651" s="17"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="12"/>
-      <c r="B652" s="12"/>
+      <c r="A652" s="17"/>
+      <c r="B652" s="17"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="12"/>
-      <c r="B653" s="12"/>
+      <c r="A653" s="17"/>
+      <c r="B653" s="17"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="12"/>
-      <c r="B654" s="12"/>
+      <c r="A654" s="17"/>
+      <c r="B654" s="17"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="12"/>
-      <c r="B655" s="12"/>
+      <c r="A655" s="17"/>
+      <c r="B655" s="17"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="12"/>
-      <c r="B656" s="12"/>
+      <c r="A656" s="17"/>
+      <c r="B656" s="17"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="12"/>
-      <c r="B657" s="12"/>
+      <c r="A657" s="17"/>
+      <c r="B657" s="17"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="12"/>
-      <c r="B658" s="12"/>
+      <c r="A658" s="17"/>
+      <c r="B658" s="17"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="12"/>
-      <c r="B659" s="12"/>
+      <c r="A659" s="17"/>
+      <c r="B659" s="17"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="12"/>
-      <c r="B660" s="12"/>
+      <c r="A660" s="17"/>
+      <c r="B660" s="17"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="12"/>
-      <c r="B661" s="12"/>
+      <c r="A661" s="17"/>
+      <c r="B661" s="17"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="12"/>
-      <c r="B662" s="12"/>
+      <c r="A662" s="17"/>
+      <c r="B662" s="17"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="12"/>
-      <c r="B663" s="12"/>
+      <c r="A663" s="17"/>
+      <c r="B663" s="17"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="12"/>
-      <c r="B664" s="12"/>
+      <c r="A664" s="17"/>
+      <c r="B664" s="17"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="12"/>
-      <c r="B665" s="12"/>
+      <c r="A665" s="17"/>
+      <c r="B665" s="17"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="12"/>
-      <c r="B666" s="12"/>
+      <c r="A666" s="17"/>
+      <c r="B666" s="17"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="12"/>
-      <c r="B667" s="12"/>
+      <c r="A667" s="17"/>
+      <c r="B667" s="17"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="12"/>
-      <c r="B668" s="12"/>
+      <c r="A668" s="17"/>
+      <c r="B668" s="17"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="12"/>
-      <c r="B669" s="12"/>
+      <c r="A669" s="17"/>
+      <c r="B669" s="17"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="12"/>
-      <c r="B670" s="12"/>
+      <c r="A670" s="17"/>
+      <c r="B670" s="17"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="12"/>
-      <c r="B671" s="12"/>
+      <c r="A671" s="17"/>
+      <c r="B671" s="17"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="12"/>
-      <c r="B672" s="12"/>
+      <c r="A672" s="17"/>
+      <c r="B672" s="17"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="12"/>
-      <c r="B673" s="12"/>
+      <c r="A673" s="17"/>
+      <c r="B673" s="17"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="12"/>
-      <c r="B674" s="12"/>
+      <c r="A674" s="17"/>
+      <c r="B674" s="17"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="12"/>
-      <c r="B675" s="12"/>
+      <c r="A675" s="17"/>
+      <c r="B675" s="17"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="12"/>
-      <c r="B676" s="12"/>
+      <c r="A676" s="17"/>
+      <c r="B676" s="17"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="12"/>
-      <c r="B677" s="12"/>
+      <c r="A677" s="17"/>
+      <c r="B677" s="17"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="12"/>
-      <c r="B678" s="12"/>
+      <c r="A678" s="17"/>
+      <c r="B678" s="17"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="12"/>
-      <c r="B679" s="12"/>
+      <c r="A679" s="17"/>
+      <c r="B679" s="17"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="12"/>
-      <c r="B680" s="12"/>
+      <c r="A680" s="17"/>
+      <c r="B680" s="17"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="12"/>
-      <c r="B681" s="12"/>
+      <c r="A681" s="17"/>
+      <c r="B681" s="17"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="12"/>
-      <c r="B682" s="12"/>
+      <c r="A682" s="17"/>
+      <c r="B682" s="17"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="12"/>
-      <c r="B683" s="12"/>
+      <c r="A683" s="17"/>
+      <c r="B683" s="17"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="12"/>
-      <c r="B684" s="12"/>
+      <c r="A684" s="17"/>
+      <c r="B684" s="17"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="12"/>
-      <c r="B685" s="12"/>
+      <c r="A685" s="17"/>
+      <c r="B685" s="17"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="12"/>
-      <c r="B686" s="12"/>
+      <c r="A686" s="17"/>
+      <c r="B686" s="17"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="12"/>
-      <c r="B687" s="12"/>
+      <c r="A687" s="17"/>
+      <c r="B687" s="17"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="12"/>
-      <c r="B688" s="12"/>
+      <c r="A688" s="17"/>
+      <c r="B688" s="17"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="12"/>
-      <c r="B689" s="12"/>
+      <c r="A689" s="17"/>
+      <c r="B689" s="17"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="12"/>
-      <c r="B690" s="12"/>
+      <c r="A690" s="17"/>
+      <c r="B690" s="17"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="12"/>
-      <c r="B691" s="12"/>
+      <c r="A691" s="17"/>
+      <c r="B691" s="17"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="12"/>
-      <c r="B692" s="12"/>
+      <c r="A692" s="17"/>
+      <c r="B692" s="17"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="12"/>
-      <c r="B693" s="12"/>
+      <c r="A693" s="17"/>
+      <c r="B693" s="17"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="12"/>
-      <c r="B694" s="12"/>
+      <c r="A694" s="17"/>
+      <c r="B694" s="17"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="12"/>
-      <c r="B695" s="12"/>
+      <c r="A695" s="17"/>
+      <c r="B695" s="17"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="12"/>
-      <c r="B696" s="12"/>
+      <c r="A696" s="17"/>
+      <c r="B696" s="17"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="12"/>
-      <c r="B697" s="12"/>
+      <c r="A697" s="17"/>
+      <c r="B697" s="17"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="12"/>
-      <c r="B698" s="12"/>
+      <c r="A698" s="17"/>
+      <c r="B698" s="17"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="12"/>
-      <c r="B699" s="12"/>
+      <c r="A699" s="17"/>
+      <c r="B699" s="17"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="12"/>
-      <c r="B700" s="12"/>
+      <c r="A700" s="17"/>
+      <c r="B700" s="17"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="12"/>
-      <c r="B701" s="12"/>
+      <c r="A701" s="17"/>
+      <c r="B701" s="17"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="12"/>
-      <c r="B702" s="12"/>
+      <c r="A702" s="17"/>
+      <c r="B702" s="17"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="12"/>
-      <c r="B703" s="12"/>
+      <c r="A703" s="17"/>
+      <c r="B703" s="17"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="12"/>
-      <c r="B704" s="12"/>
+      <c r="A704" s="17"/>
+      <c r="B704" s="17"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="12"/>
-      <c r="B705" s="12"/>
+      <c r="A705" s="17"/>
+      <c r="B705" s="17"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="12"/>
-      <c r="B706" s="12"/>
+      <c r="A706" s="17"/>
+      <c r="B706" s="17"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="12"/>
-      <c r="B707" s="12"/>
+      <c r="A707" s="17"/>
+      <c r="B707" s="17"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="12"/>
-      <c r="B708" s="12"/>
+      <c r="A708" s="17"/>
+      <c r="B708" s="17"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="12"/>
-      <c r="B709" s="12"/>
+      <c r="A709" s="17"/>
+      <c r="B709" s="17"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="12"/>
-      <c r="B710" s="12"/>
+      <c r="A710" s="17"/>
+      <c r="B710" s="17"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="12"/>
-      <c r="B711" s="12"/>
+      <c r="A711" s="17"/>
+      <c r="B711" s="17"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="12"/>
-      <c r="B712" s="12"/>
+      <c r="A712" s="17"/>
+      <c r="B712" s="17"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="12"/>
-      <c r="B713" s="12"/>
+      <c r="A713" s="17"/>
+      <c r="B713" s="17"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="12"/>
-      <c r="B714" s="12"/>
+      <c r="A714" s="17"/>
+      <c r="B714" s="17"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="12"/>
-      <c r="B715" s="12"/>
+      <c r="A715" s="17"/>
+      <c r="B715" s="17"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="12"/>
-      <c r="B716" s="12"/>
+      <c r="A716" s="17"/>
+      <c r="B716" s="17"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="12"/>
-      <c r="B717" s="12"/>
+      <c r="A717" s="17"/>
+      <c r="B717" s="17"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="12"/>
-      <c r="B718" s="12"/>
+      <c r="A718" s="17"/>
+      <c r="B718" s="17"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="12"/>
-      <c r="B719" s="12"/>
+      <c r="A719" s="17"/>
+      <c r="B719" s="17"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="12"/>
-      <c r="B720" s="12"/>
+      <c r="A720" s="17"/>
+      <c r="B720" s="17"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="12"/>
-      <c r="B721" s="12"/>
+      <c r="A721" s="17"/>
+      <c r="B721" s="17"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="12"/>
-      <c r="B722" s="12"/>
+      <c r="A722" s="17"/>
+      <c r="B722" s="17"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="12"/>
-      <c r="B723" s="12"/>
+      <c r="A723" s="17"/>
+      <c r="B723" s="17"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="12"/>
-      <c r="B724" s="12"/>
+      <c r="A724" s="17"/>
+      <c r="B724" s="17"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="12"/>
-      <c r="B725" s="12"/>
+      <c r="A725" s="17"/>
+      <c r="B725" s="17"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="12"/>
-      <c r="B726" s="12"/>
+      <c r="A726" s="17"/>
+      <c r="B726" s="17"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="12"/>
-      <c r="B727" s="12"/>
+      <c r="A727" s="17"/>
+      <c r="B727" s="17"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="12"/>
-      <c r="B728" s="12"/>
+      <c r="A728" s="17"/>
+      <c r="B728" s="17"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="12"/>
-      <c r="B729" s="12"/>
+      <c r="A729" s="17"/>
+      <c r="B729" s="17"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="12"/>
-      <c r="B730" s="12"/>
+      <c r="A730" s="17"/>
+      <c r="B730" s="17"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="12"/>
-      <c r="B731" s="12"/>
+      <c r="A731" s="17"/>
+      <c r="B731" s="17"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="12"/>
-      <c r="B732" s="12"/>
+      <c r="A732" s="17"/>
+      <c r="B732" s="17"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="12"/>
-      <c r="B733" s="12"/>
+      <c r="A733" s="17"/>
+      <c r="B733" s="17"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="12"/>
-      <c r="B734" s="12"/>
+      <c r="A734" s="17"/>
+      <c r="B734" s="17"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="12"/>
-      <c r="B735" s="12"/>
+      <c r="A735" s="17"/>
+      <c r="B735" s="17"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="12"/>
-      <c r="B736" s="12"/>
+      <c r="A736" s="17"/>
+      <c r="B736" s="17"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="12"/>
-      <c r="B737" s="12"/>
+      <c r="A737" s="17"/>
+      <c r="B737" s="17"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="12"/>
-      <c r="B738" s="12"/>
+      <c r="A738" s="17"/>
+      <c r="B738" s="17"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="12"/>
-      <c r="B739" s="12"/>
+      <c r="A739" s="17"/>
+      <c r="B739" s="17"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="12"/>
-      <c r="B740" s="12"/>
+      <c r="A740" s="17"/>
+      <c r="B740" s="17"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="12"/>
-      <c r="B741" s="12"/>
+      <c r="A741" s="17"/>
+      <c r="B741" s="17"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="12"/>
-      <c r="B742" s="12"/>
+      <c r="A742" s="17"/>
+      <c r="B742" s="17"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="12"/>
-      <c r="B743" s="12"/>
+      <c r="A743" s="17"/>
+      <c r="B743" s="17"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="12"/>
-      <c r="B744" s="12"/>
+      <c r="A744" s="17"/>
+      <c r="B744" s="17"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="12"/>
-      <c r="B745" s="12"/>
+      <c r="A745" s="17"/>
+      <c r="B745" s="17"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="12"/>
-      <c r="B746" s="12"/>
+      <c r="A746" s="17"/>
+      <c r="B746" s="17"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="12"/>
-      <c r="B747" s="12"/>
+      <c r="A747" s="17"/>
+      <c r="B747" s="17"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="12"/>
-      <c r="B748" s="12"/>
+      <c r="A748" s="17"/>
+      <c r="B748" s="17"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="12"/>
-      <c r="B749" s="12"/>
+      <c r="A749" s="17"/>
+      <c r="B749" s="17"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="12"/>
-      <c r="B750" s="12"/>
+      <c r="A750" s="17"/>
+      <c r="B750" s="17"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="12"/>
-      <c r="B751" s="12"/>
+      <c r="A751" s="17"/>
+      <c r="B751" s="17"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="12"/>
-      <c r="B752" s="12"/>
+      <c r="A752" s="17"/>
+      <c r="B752" s="17"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="12"/>
-      <c r="B753" s="12"/>
+      <c r="A753" s="17"/>
+      <c r="B753" s="17"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="12"/>
-      <c r="B754" s="12"/>
+      <c r="A754" s="17"/>
+      <c r="B754" s="17"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="12"/>
-      <c r="B755" s="12"/>
+      <c r="A755" s="17"/>
+      <c r="B755" s="17"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="12"/>
-      <c r="B756" s="12"/>
+      <c r="A756" s="17"/>
+      <c r="B756" s="17"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="12"/>
-      <c r="B757" s="12"/>
+      <c r="A757" s="17"/>
+      <c r="B757" s="17"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="12"/>
-      <c r="B758" s="12"/>
+      <c r="A758" s="17"/>
+      <c r="B758" s="17"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="12"/>
-      <c r="B759" s="12"/>
+      <c r="A759" s="17"/>
+      <c r="B759" s="17"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="12"/>
-      <c r="B760" s="12"/>
+      <c r="A760" s="17"/>
+      <c r="B760" s="17"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="12"/>
-      <c r="B761" s="12"/>
+      <c r="A761" s="17"/>
+      <c r="B761" s="17"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="12"/>
-      <c r="B762" s="12"/>
+      <c r="A762" s="17"/>
+      <c r="B762" s="17"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="12"/>
-      <c r="B763" s="12"/>
+      <c r="A763" s="17"/>
+      <c r="B763" s="17"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="12"/>
-      <c r="B764" s="12"/>
+      <c r="A764" s="17"/>
+      <c r="B764" s="17"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="12"/>
-      <c r="B765" s="12"/>
+      <c r="A765" s="17"/>
+      <c r="B765" s="17"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="12"/>
-      <c r="B766" s="12"/>
+      <c r="A766" s="17"/>
+      <c r="B766" s="17"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="12"/>
-      <c r="B767" s="12"/>
+      <c r="A767" s="17"/>
+      <c r="B767" s="17"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="12"/>
-      <c r="B768" s="12"/>
+      <c r="A768" s="17"/>
+      <c r="B768" s="17"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="12"/>
-      <c r="B769" s="12"/>
+      <c r="A769" s="17"/>
+      <c r="B769" s="17"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="12"/>
-      <c r="B770" s="12"/>
+      <c r="A770" s="17"/>
+      <c r="B770" s="17"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="12"/>
-      <c r="B771" s="12"/>
+      <c r="A771" s="17"/>
+      <c r="B771" s="17"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="12"/>
-      <c r="B772" s="12"/>
+      <c r="A772" s="17"/>
+      <c r="B772" s="17"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="12"/>
-      <c r="B773" s="12"/>
+      <c r="A773" s="17"/>
+      <c r="B773" s="17"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="12"/>
-      <c r="B774" s="12"/>
+      <c r="A774" s="17"/>
+      <c r="B774" s="17"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="12"/>
-      <c r="B775" s="12"/>
+      <c r="A775" s="17"/>
+      <c r="B775" s="17"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="12"/>
-      <c r="B776" s="12"/>
+      <c r="A776" s="17"/>
+      <c r="B776" s="17"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="12"/>
-      <c r="B777" s="12"/>
+      <c r="A777" s="17"/>
+      <c r="B777" s="17"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="12"/>
-      <c r="B778" s="12"/>
+      <c r="A778" s="17"/>
+      <c r="B778" s="17"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="12"/>
-      <c r="B779" s="12"/>
+      <c r="A779" s="17"/>
+      <c r="B779" s="17"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="12"/>
-      <c r="B780" s="12"/>
+      <c r="A780" s="17"/>
+      <c r="B780" s="17"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="12"/>
-      <c r="B781" s="12"/>
+      <c r="A781" s="17"/>
+      <c r="B781" s="17"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="12"/>
-      <c r="B782" s="12"/>
+      <c r="A782" s="17"/>
+      <c r="B782" s="17"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="12"/>
-      <c r="B783" s="12"/>
+      <c r="A783" s="17"/>
+      <c r="B783" s="17"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="12"/>
-      <c r="B784" s="12"/>
+      <c r="A784" s="17"/>
+      <c r="B784" s="17"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="12"/>
-      <c r="B785" s="12"/>
+      <c r="A785" s="17"/>
+      <c r="B785" s="17"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="12"/>
-      <c r="B786" s="12"/>
+      <c r="A786" s="17"/>
+      <c r="B786" s="17"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="12"/>
-      <c r="B787" s="12"/>
+      <c r="A787" s="17"/>
+      <c r="B787" s="17"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="12"/>
-      <c r="B788" s="12"/>
+      <c r="A788" s="17"/>
+      <c r="B788" s="17"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="12"/>
-      <c r="B789" s="12"/>
+      <c r="A789" s="17"/>
+      <c r="B789" s="17"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="12"/>
-      <c r="B790" s="12"/>
+      <c r="A790" s="17"/>
+      <c r="B790" s="17"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="12"/>
-      <c r="B791" s="12"/>
+      <c r="A791" s="17"/>
+      <c r="B791" s="17"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="12"/>
-      <c r="B792" s="12"/>
+      <c r="A792" s="17"/>
+      <c r="B792" s="17"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="12"/>
-      <c r="B793" s="12"/>
+      <c r="A793" s="17"/>
+      <c r="B793" s="17"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="12"/>
-      <c r="B794" s="12"/>
+      <c r="A794" s="17"/>
+      <c r="B794" s="17"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="12"/>
-      <c r="B795" s="12"/>
+      <c r="A795" s="17"/>
+      <c r="B795" s="17"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="12"/>
-      <c r="B796" s="12"/>
+      <c r="A796" s="17"/>
+      <c r="B796" s="17"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="12"/>
-      <c r="B797" s="12"/>
+      <c r="A797" s="17"/>
+      <c r="B797" s="17"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="12"/>
-      <c r="B798" s="12"/>
+      <c r="A798" s="17"/>
+      <c r="B798" s="17"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="12"/>
-      <c r="B799" s="12"/>
+      <c r="A799" s="17"/>
+      <c r="B799" s="17"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="12"/>
-      <c r="B800" s="12"/>
+      <c r="A800" s="17"/>
+      <c r="B800" s="17"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="12"/>
-      <c r="B801" s="12"/>
+      <c r="A801" s="17"/>
+      <c r="B801" s="17"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="12"/>
-      <c r="B802" s="12"/>
+      <c r="A802" s="17"/>
+      <c r="B802" s="17"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="12"/>
-      <c r="B803" s="12"/>
+      <c r="A803" s="17"/>
+      <c r="B803" s="17"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="12"/>
-      <c r="B804" s="12"/>
+      <c r="A804" s="17"/>
+      <c r="B804" s="17"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="12"/>
-      <c r="B805" s="12"/>
+      <c r="A805" s="17"/>
+      <c r="B805" s="17"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="12"/>
-      <c r="B806" s="12"/>
+      <c r="A806" s="17"/>
+      <c r="B806" s="17"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="12"/>
-      <c r="B807" s="12"/>
+      <c r="A807" s="17"/>
+      <c r="B807" s="17"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="12"/>
-      <c r="B808" s="12"/>
+      <c r="A808" s="17"/>
+      <c r="B808" s="17"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="12"/>
-      <c r="B809" s="12"/>
+      <c r="A809" s="17"/>
+      <c r="B809" s="17"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="12"/>
-      <c r="B810" s="12"/>
+      <c r="A810" s="17"/>
+      <c r="B810" s="17"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="12"/>
-      <c r="B811" s="12"/>
+      <c r="A811" s="17"/>
+      <c r="B811" s="17"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="12"/>
-      <c r="B812" s="12"/>
+      <c r="A812" s="17"/>
+      <c r="B812" s="17"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="12"/>
-      <c r="B813" s="12"/>
+      <c r="A813" s="17"/>
+      <c r="B813" s="17"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="12"/>
-      <c r="B814" s="12"/>
+      <c r="A814" s="17"/>
+      <c r="B814" s="17"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="12"/>
-      <c r="B815" s="12"/>
+      <c r="A815" s="17"/>
+      <c r="B815" s="17"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="12"/>
-      <c r="B816" s="12"/>
+      <c r="A816" s="17"/>
+      <c r="B816" s="17"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="12"/>
-      <c r="B817" s="12"/>
+      <c r="A817" s="17"/>
+      <c r="B817" s="17"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="12"/>
-      <c r="B818" s="12"/>
+      <c r="A818" s="17"/>
+      <c r="B818" s="17"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="12"/>
-      <c r="B819" s="12"/>
+      <c r="A819" s="17"/>
+      <c r="B819" s="17"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="12"/>
-      <c r="B820" s="12"/>
+      <c r="A820" s="17"/>
+      <c r="B820" s="17"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="12"/>
-      <c r="B821" s="12"/>
+      <c r="A821" s="17"/>
+      <c r="B821" s="17"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="12"/>
-      <c r="B822" s="12"/>
+      <c r="A822" s="17"/>
+      <c r="B822" s="17"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="12"/>
-      <c r="B823" s="12"/>
+      <c r="A823" s="17"/>
+      <c r="B823" s="17"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="12"/>
-      <c r="B824" s="12"/>
+      <c r="A824" s="17"/>
+      <c r="B824" s="17"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="12"/>
-      <c r="B825" s="12"/>
+      <c r="A825" s="17"/>
+      <c r="B825" s="17"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="12"/>
-      <c r="B826" s="12"/>
+      <c r="A826" s="17"/>
+      <c r="B826" s="17"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="12"/>
-      <c r="B827" s="12"/>
+      <c r="A827" s="17"/>
+      <c r="B827" s="17"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="12"/>
-      <c r="B828" s="12"/>
+      <c r="A828" s="17"/>
+      <c r="B828" s="17"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="12"/>
-      <c r="B829" s="12"/>
+      <c r="A829" s="17"/>
+      <c r="B829" s="17"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="12"/>
-      <c r="B830" s="12"/>
+      <c r="A830" s="17"/>
+      <c r="B830" s="17"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="12"/>
-      <c r="B831" s="12"/>
+      <c r="A831" s="17"/>
+      <c r="B831" s="17"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="12"/>
-      <c r="B832" s="12"/>
+      <c r="A832" s="17"/>
+      <c r="B832" s="17"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="12"/>
-      <c r="B833" s="12"/>
+      <c r="A833" s="17"/>
+      <c r="B833" s="17"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="12"/>
-      <c r="B834" s="12"/>
+      <c r="A834" s="17"/>
+      <c r="B834" s="17"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="12"/>
-      <c r="B835" s="12"/>
+      <c r="A835" s="17"/>
+      <c r="B835" s="17"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="12"/>
-      <c r="B836" s="12"/>
+      <c r="A836" s="17"/>
+      <c r="B836" s="17"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="12"/>
-      <c r="B837" s="12"/>
+      <c r="A837" s="17"/>
+      <c r="B837" s="17"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="12"/>
-      <c r="B838" s="12"/>
+      <c r="A838" s="17"/>
+      <c r="B838" s="17"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="12"/>
-      <c r="B839" s="12"/>
+      <c r="A839" s="17"/>
+      <c r="B839" s="17"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="12"/>
-      <c r="B840" s="12"/>
+      <c r="A840" s="17"/>
+      <c r="B840" s="17"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="12"/>
-      <c r="B841" s="12"/>
+      <c r="A841" s="17"/>
+      <c r="B841" s="17"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="12"/>
-      <c r="B842" s="12"/>
+      <c r="A842" s="17"/>
+      <c r="B842" s="17"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="12"/>
-      <c r="B843" s="12"/>
+      <c r="A843" s="17"/>
+      <c r="B843" s="17"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="12"/>
-      <c r="B844" s="12"/>
+      <c r="A844" s="17"/>
+      <c r="B844" s="17"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="12"/>
-      <c r="B845" s="12"/>
+      <c r="A845" s="17"/>
+      <c r="B845" s="17"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="12"/>
-      <c r="B846" s="12"/>
+      <c r="A846" s="17"/>
+      <c r="B846" s="17"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="12"/>
-      <c r="B847" s="12"/>
+      <c r="A847" s="17"/>
+      <c r="B847" s="17"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="12"/>
-      <c r="B848" s="12"/>
+      <c r="A848" s="17"/>
+      <c r="B848" s="17"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="12"/>
-      <c r="B849" s="12"/>
+      <c r="A849" s="17"/>
+      <c r="B849" s="17"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="12"/>
-      <c r="B850" s="12"/>
+      <c r="A850" s="17"/>
+      <c r="B850" s="17"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="12"/>
-      <c r="B851" s="12"/>
+      <c r="A851" s="17"/>
+      <c r="B851" s="17"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="12"/>
-      <c r="B852" s="12"/>
+      <c r="A852" s="17"/>
+      <c r="B852" s="17"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="12"/>
-      <c r="B853" s="12"/>
+      <c r="A853" s="17"/>
+      <c r="B853" s="17"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="12"/>
-      <c r="B854" s="12"/>
+      <c r="A854" s="17"/>
+      <c r="B854" s="17"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="12"/>
-      <c r="B855" s="12"/>
+      <c r="A855" s="17"/>
+      <c r="B855" s="17"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="12"/>
-      <c r="B856" s="12"/>
+      <c r="A856" s="17"/>
+      <c r="B856" s="17"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="12"/>
-      <c r="B857" s="12"/>
+      <c r="A857" s="17"/>
+      <c r="B857" s="17"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="12"/>
-      <c r="B858" s="12"/>
+      <c r="A858" s="17"/>
+      <c r="B858" s="17"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="12"/>
-      <c r="B859" s="12"/>
+      <c r="A859" s="17"/>
+      <c r="B859" s="17"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="12"/>
-      <c r="B860" s="12"/>
+      <c r="A860" s="17"/>
+      <c r="B860" s="17"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="12"/>
-      <c r="B861" s="12"/>
+      <c r="A861" s="17"/>
+      <c r="B861" s="17"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="12"/>
-      <c r="B862" s="12"/>
+      <c r="A862" s="17"/>
+      <c r="B862" s="17"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="12"/>
-      <c r="B863" s="12"/>
+      <c r="A863" s="17"/>
+      <c r="B863" s="17"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="12"/>
-      <c r="B864" s="12"/>
+      <c r="A864" s="17"/>
+      <c r="B864" s="17"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="12"/>
-      <c r="B865" s="12"/>
+      <c r="A865" s="17"/>
+      <c r="B865" s="17"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="12"/>
-      <c r="B866" s="12"/>
+      <c r="A866" s="17"/>
+      <c r="B866" s="17"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="12"/>
-      <c r="B867" s="12"/>
+      <c r="A867" s="17"/>
+      <c r="B867" s="17"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="12"/>
-      <c r="B868" s="12"/>
+      <c r="A868" s="17"/>
+      <c r="B868" s="17"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="12"/>
-      <c r="B869" s="12"/>
+      <c r="A869" s="17"/>
+      <c r="B869" s="17"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="12"/>
-      <c r="B870" s="12"/>
+      <c r="A870" s="17"/>
+      <c r="B870" s="17"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="12"/>
-      <c r="B871" s="12"/>
+      <c r="A871" s="17"/>
+      <c r="B871" s="17"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="12"/>
-      <c r="B872" s="12"/>
+      <c r="A872" s="17"/>
+      <c r="B872" s="17"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="12"/>
-      <c r="B873" s="12"/>
+      <c r="A873" s="17"/>
+      <c r="B873" s="17"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="12"/>
-      <c r="B874" s="12"/>
+      <c r="A874" s="17"/>
+      <c r="B874" s="17"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="12"/>
-      <c r="B875" s="12"/>
+      <c r="A875" s="17"/>
+      <c r="B875" s="17"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="12"/>
-      <c r="B876" s="12"/>
+      <c r="A876" s="17"/>
+      <c r="B876" s="17"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="12"/>
-      <c r="B877" s="12"/>
+      <c r="A877" s="17"/>
+      <c r="B877" s="17"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="12"/>
-      <c r="B878" s="12"/>
+      <c r="A878" s="17"/>
+      <c r="B878" s="17"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="12"/>
-      <c r="B879" s="12"/>
+      <c r="A879" s="17"/>
+      <c r="B879" s="17"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="12"/>
-      <c r="B880" s="12"/>
+      <c r="A880" s="17"/>
+      <c r="B880" s="17"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="12"/>
-      <c r="B881" s="12"/>
+      <c r="A881" s="17"/>
+      <c r="B881" s="17"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="12"/>
-      <c r="B882" s="12"/>
+      <c r="A882" s="17"/>
+      <c r="B882" s="17"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="12"/>
-      <c r="B883" s="12"/>
+      <c r="A883" s="17"/>
+      <c r="B883" s="17"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="12"/>
-      <c r="B884" s="12"/>
+      <c r="A884" s="17"/>
+      <c r="B884" s="17"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="12"/>
-      <c r="B885" s="12"/>
+      <c r="A885" s="17"/>
+      <c r="B885" s="17"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="12"/>
-      <c r="B886" s="12"/>
+      <c r="A886" s="17"/>
+      <c r="B886" s="17"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="12"/>
-      <c r="B887" s="12"/>
+      <c r="A887" s="17"/>
+      <c r="B887" s="17"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="12"/>
-      <c r="B888" s="12"/>
+      <c r="A888" s="17"/>
+      <c r="B888" s="17"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="12"/>
-      <c r="B889" s="12"/>
+      <c r="A889" s="17"/>
+      <c r="B889" s="17"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="12"/>
-      <c r="B890" s="12"/>
+      <c r="A890" s="17"/>
+      <c r="B890" s="17"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="12"/>
-      <c r="B891" s="12"/>
+      <c r="A891" s="17"/>
+      <c r="B891" s="17"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="12"/>
-      <c r="B892" s="12"/>
+      <c r="A892" s="17"/>
+      <c r="B892" s="17"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="12"/>
-      <c r="B893" s="12"/>
+      <c r="A893" s="17"/>
+      <c r="B893" s="17"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="12"/>
-      <c r="B894" s="12"/>
+      <c r="A894" s="17"/>
+      <c r="B894" s="17"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="12"/>
-      <c r="B895" s="12"/>
+      <c r="A895" s="17"/>
+      <c r="B895" s="17"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="12"/>
-      <c r="B896" s="12"/>
+      <c r="A896" s="17"/>
+      <c r="B896" s="17"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="12"/>
-      <c r="B897" s="12"/>
+      <c r="A897" s="17"/>
+      <c r="B897" s="17"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="12"/>
-      <c r="B898" s="12"/>
+      <c r="A898" s="17"/>
+      <c r="B898" s="17"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="12"/>
-      <c r="B899" s="12"/>
+      <c r="A899" s="17"/>
+      <c r="B899" s="17"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="12"/>
-      <c r="B900" s="12"/>
+      <c r="A900" s="17"/>
+      <c r="B900" s="17"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="12"/>
-      <c r="B901" s="12"/>
+      <c r="A901" s="17"/>
+      <c r="B901" s="17"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="12"/>
-      <c r="B902" s="12"/>
+      <c r="A902" s="17"/>
+      <c r="B902" s="17"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="12"/>
-      <c r="B903" s="12"/>
+      <c r="A903" s="17"/>
+      <c r="B903" s="17"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="12"/>
-      <c r="B904" s="12"/>
+      <c r="A904" s="17"/>
+      <c r="B904" s="17"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="12"/>
-      <c r="B905" s="12"/>
+      <c r="A905" s="17"/>
+      <c r="B905" s="17"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="12"/>
-      <c r="B906" s="12"/>
+      <c r="A906" s="17"/>
+      <c r="B906" s="17"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="12"/>
-      <c r="B907" s="12"/>
+      <c r="A907" s="17"/>
+      <c r="B907" s="17"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="12"/>
-      <c r="B908" s="12"/>
+      <c r="A908" s="17"/>
+      <c r="B908" s="17"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="12"/>
-      <c r="B909" s="12"/>
+      <c r="A909" s="17"/>
+      <c r="B909" s="17"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="12"/>
-      <c r="B910" s="12"/>
+      <c r="A910" s="17"/>
+      <c r="B910" s="17"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="12"/>
-      <c r="B911" s="12"/>
+      <c r="A911" s="17"/>
+      <c r="B911" s="17"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="12"/>
-      <c r="B912" s="12"/>
+      <c r="A912" s="17"/>
+      <c r="B912" s="17"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="12"/>
-      <c r="B913" s="12"/>
+      <c r="A913" s="17"/>
+      <c r="B913" s="17"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="12"/>
-      <c r="B914" s="12"/>
+      <c r="A914" s="17"/>
+      <c r="B914" s="17"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="12"/>
-      <c r="B915" s="12"/>
+      <c r="A915" s="17"/>
+      <c r="B915" s="17"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="12"/>
-      <c r="B916" s="12"/>
+      <c r="A916" s="17"/>
+      <c r="B916" s="17"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="12"/>
-      <c r="B917" s="12"/>
+      <c r="A917" s="17"/>
+      <c r="B917" s="17"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="12"/>
-      <c r="B918" s="12"/>
+      <c r="A918" s="17"/>
+      <c r="B918" s="17"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="12"/>
-      <c r="B919" s="12"/>
+      <c r="A919" s="17"/>
+      <c r="B919" s="17"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="12"/>
-      <c r="B920" s="12"/>
+      <c r="A920" s="17"/>
+      <c r="B920" s="17"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="12"/>
-      <c r="B921" s="12"/>
+      <c r="A921" s="17"/>
+      <c r="B921" s="17"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="12"/>
-      <c r="B922" s="12"/>
+      <c r="A922" s="17"/>
+      <c r="B922" s="17"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="12"/>
-      <c r="B923" s="12"/>
+      <c r="A923" s="17"/>
+      <c r="B923" s="17"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="12"/>
-      <c r="B924" s="12"/>
+      <c r="A924" s="17"/>
+      <c r="B924" s="17"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="12"/>
-      <c r="B925" s="12"/>
+      <c r="A925" s="17"/>
+      <c r="B925" s="17"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="12"/>
-      <c r="B926" s="12"/>
+      <c r="A926" s="17"/>
+      <c r="B926" s="17"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="12"/>
-      <c r="B927" s="12"/>
+      <c r="A927" s="17"/>
+      <c r="B927" s="17"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="12"/>
-      <c r="B928" s="12"/>
+      <c r="A928" s="17"/>
+      <c r="B928" s="17"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="12"/>
-      <c r="B929" s="12"/>
+      <c r="A929" s="17"/>
+      <c r="B929" s="17"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="12"/>
-      <c r="B930" s="12"/>
+      <c r="A930" s="17"/>
+      <c r="B930" s="17"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="12"/>
-      <c r="B931" s="12"/>
+      <c r="A931" s="17"/>
+      <c r="B931" s="17"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="12"/>
-      <c r="B932" s="12"/>
+      <c r="A932" s="17"/>
+      <c r="B932" s="17"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="12"/>
-      <c r="B933" s="12"/>
+      <c r="A933" s="17"/>
+      <c r="B933" s="17"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="12"/>
-      <c r="B934" s="12"/>
+      <c r="A934" s="17"/>
+      <c r="B934" s="17"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="12"/>
-      <c r="B935" s="12"/>
+      <c r="A935" s="17"/>
+      <c r="B935" s="17"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="12"/>
-      <c r="B936" s="12"/>
+      <c r="A936" s="17"/>
+      <c r="B936" s="17"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="12"/>
-      <c r="B937" s="12"/>
+      <c r="A937" s="17"/>
+      <c r="B937" s="17"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="12"/>
-      <c r="B938" s="12"/>
+      <c r="A938" s="17"/>
+      <c r="B938" s="17"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="12"/>
-      <c r="B939" s="12"/>
+      <c r="A939" s="17"/>
+      <c r="B939" s="17"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="12"/>
-      <c r="B940" s="12"/>
+      <c r="A940" s="17"/>
+      <c r="B940" s="17"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="12"/>
-      <c r="B941" s="12"/>
+      <c r="A941" s="17"/>
+      <c r="B941" s="17"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="12"/>
-      <c r="B942" s="12"/>
+      <c r="A942" s="17"/>
+      <c r="B942" s="17"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="12"/>
-      <c r="B943" s="12"/>
+      <c r="A943" s="17"/>
+      <c r="B943" s="17"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="12"/>
-      <c r="B944" s="12"/>
+      <c r="A944" s="17"/>
+      <c r="B944" s="17"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="12"/>
-      <c r="B945" s="12"/>
+      <c r="A945" s="17"/>
+      <c r="B945" s="17"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="12"/>
-      <c r="B946" s="12"/>
+      <c r="A946" s="17"/>
+      <c r="B946" s="17"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="12"/>
-      <c r="B947" s="12"/>
+      <c r="A947" s="17"/>
+      <c r="B947" s="17"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="12"/>
-      <c r="B948" s="12"/>
+      <c r="A948" s="17"/>
+      <c r="B948" s="17"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="12"/>
-      <c r="B949" s="12"/>
+      <c r="A949" s="17"/>
+      <c r="B949" s="17"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="12"/>
-      <c r="B950" s="12"/>
+      <c r="A950" s="17"/>
+      <c r="B950" s="17"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="12"/>
-      <c r="B951" s="12"/>
+      <c r="A951" s="17"/>
+      <c r="B951" s="17"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="12"/>
-      <c r="B952" s="12"/>
+      <c r="A952" s="17"/>
+      <c r="B952" s="17"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="12"/>
-      <c r="B953" s="12"/>
+      <c r="A953" s="17"/>
+      <c r="B953" s="17"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="12"/>
-      <c r="B954" s="12"/>
+      <c r="A954" s="17"/>
+      <c r="B954" s="17"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="12"/>
-      <c r="B955" s="12"/>
+      <c r="A955" s="17"/>
+      <c r="B955" s="17"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="12"/>
-      <c r="B956" s="12"/>
+      <c r="A956" s="17"/>
+      <c r="B956" s="17"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="12"/>
-      <c r="B957" s="12"/>
+      <c r="A957" s="17"/>
+      <c r="B957" s="17"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="12"/>
-      <c r="B958" s="12"/>
+      <c r="A958" s="17"/>
+      <c r="B958" s="17"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="12"/>
-      <c r="B959" s="12"/>
+      <c r="A959" s="17"/>
+      <c r="B959" s="17"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="12"/>
-      <c r="B960" s="12"/>
+      <c r="A960" s="17"/>
+      <c r="B960" s="17"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="12"/>
-      <c r="B961" s="12"/>
+      <c r="A961" s="17"/>
+      <c r="B961" s="17"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="12"/>
-      <c r="B962" s="12"/>
+      <c r="A962" s="17"/>
+      <c r="B962" s="17"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="12"/>
-      <c r="B963" s="12"/>
+      <c r="A963" s="17"/>
+      <c r="B963" s="17"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="12"/>
-      <c r="B964" s="12"/>
+      <c r="A964" s="17"/>
+      <c r="B964" s="17"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="12"/>
-      <c r="B965" s="12"/>
+      <c r="A965" s="17"/>
+      <c r="B965" s="17"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="12"/>
-      <c r="B966" s="12"/>
+      <c r="A966" s="17"/>
+      <c r="B966" s="17"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="12"/>
-      <c r="B967" s="12"/>
+      <c r="A967" s="17"/>
+      <c r="B967" s="17"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="12"/>
-      <c r="B968" s="12"/>
+      <c r="A968" s="17"/>
+      <c r="B968" s="17"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="12"/>
-      <c r="B969" s="12"/>
+      <c r="A969" s="17"/>
+      <c r="B969" s="17"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="12"/>
-      <c r="B970" s="12"/>
+      <c r="A970" s="17"/>
+      <c r="B970" s="17"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="12"/>
-      <c r="B971" s="12"/>
+      <c r="A971" s="17"/>
+      <c r="B971" s="17"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="12"/>
-      <c r="B972" s="12"/>
+      <c r="A972" s="17"/>
+      <c r="B972" s="17"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="12"/>
-      <c r="B973" s="12"/>
+      <c r="A973" s="17"/>
+      <c r="B973" s="17"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="12"/>
-      <c r="B974" s="12"/>
+      <c r="A974" s="17"/>
+      <c r="B974" s="17"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="12"/>
-      <c r="B975" s="12"/>
+      <c r="A975" s="17"/>
+      <c r="B975" s="17"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="12"/>
-      <c r="B976" s="12"/>
+      <c r="A976" s="17"/>
+      <c r="B976" s="17"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="12"/>
-      <c r="B977" s="12"/>
+      <c r="A977" s="17"/>
+      <c r="B977" s="17"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="12"/>
-      <c r="B978" s="12"/>
+      <c r="A978" s="17"/>
+      <c r="B978" s="17"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="12"/>
-      <c r="B979" s="12"/>
+      <c r="A979" s="17"/>
+      <c r="B979" s="17"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="12"/>
-      <c r="B980" s="12"/>
+      <c r="A980" s="17"/>
+      <c r="B980" s="17"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="12"/>
-      <c r="B981" s="12"/>
+      <c r="A981" s="17"/>
+      <c r="B981" s="17"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="12"/>
-      <c r="B982" s="12"/>
+      <c r="A982" s="17"/>
+      <c r="B982" s="17"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="12"/>
-      <c r="B983" s="12"/>
+      <c r="A983" s="17"/>
+      <c r="B983" s="17"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="12"/>
-      <c r="B984" s="12"/>
+      <c r="A984" s="17"/>
+      <c r="B984" s="17"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="12"/>
-      <c r="B985" s="12"/>
+      <c r="A985" s="17"/>
+      <c r="B985" s="17"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="12"/>
-      <c r="B986" s="12"/>
+      <c r="A986" s="17"/>
+      <c r="B986" s="17"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="12"/>
-      <c r="B987" s="12"/>
+      <c r="A987" s="17"/>
+      <c r="B987" s="17"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="12"/>
-      <c r="B988" s="12"/>
+      <c r="A988" s="17"/>
+      <c r="B988" s="17"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="12"/>
-      <c r="B989" s="12"/>
+      <c r="A989" s="17"/>
+      <c r="B989" s="17"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="12"/>
-      <c r="B990" s="12"/>
+      <c r="A990" s="17"/>
+      <c r="B990" s="17"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="12"/>
-      <c r="B991" s="12"/>
+      <c r="A991" s="17"/>
+      <c r="B991" s="17"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="12"/>
-      <c r="B992" s="12"/>
+      <c r="A992" s="17"/>
+      <c r="B992" s="17"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="12"/>
-      <c r="B993" s="12"/>
+      <c r="A993" s="17"/>
+      <c r="B993" s="17"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="12"/>
-      <c r="B994" s="12"/>
+      <c r="A994" s="17"/>
+      <c r="B994" s="17"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="12"/>
-      <c r="B995" s="12"/>
+      <c r="A995" s="17"/>
+      <c r="B995" s="17"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="12"/>
-      <c r="B996" s="12"/>
+      <c r="A996" s="17"/>
+      <c r="B996" s="17"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="12"/>
-      <c r="B997" s="12"/>
+      <c r="A997" s="17"/>
+      <c r="B997" s="17"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="12"/>
-      <c r="B998" s="12"/>
+      <c r="A998" s="17"/>
+      <c r="B998" s="17"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="12"/>
-      <c r="B999" s="12"/>
+      <c r="A999" s="17"/>
+      <c r="B999" s="17"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="12"/>
-      <c r="B1000" s="12"/>
+      <c r="A1000" s="17"/>
+      <c r="B1000" s="17"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="149">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -97,6 +97,9 @@
   </si>
   <si>
     <t>HoldType</t>
+  </si>
+  <si>
+    <t>MeshCollider</t>
   </si>
   <si>
     <t>Item_Tool_MasterKey</t>
@@ -112,7 +115,7 @@
     <t>Tool</t>
   </si>
   <si>
-    <t>None</t>
+    <t>Epic</t>
   </si>
   <si>
     <t>Yellow</t>
@@ -122,6 +125,9 @@
   </si>
   <si>
     <t>ToolObject</t>
+  </si>
+  <si>
+    <t>Hold</t>
   </si>
   <si>
     <t>Item_Tool_Key</t>
@@ -134,6 +140,9 @@
 한 번만 사용 할 수 있다.</t>
   </si>
   <si>
+    <t>Rare</t>
+  </si>
+  <si>
     <t>Black</t>
   </si>
   <si>
@@ -149,9 +158,6 @@
     <t>Jewel</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
     <t>M_Gemstone_Diamond,Lit</t>
   </si>
   <si>
@@ -161,9 +167,6 @@
     <t>JewelObject</t>
   </si>
   <si>
-    <t>Hold</t>
-  </si>
-  <si>
     <t>Item_Jewel_Amethyst</t>
   </si>
   <si>
@@ -203,9 +206,6 @@
     <t>에메랄드다.</t>
   </si>
   <si>
-    <t>Rare</t>
-  </si>
-  <si>
     <t>M_Gemstone_Emerald</t>
   </si>
   <si>
@@ -360,6 +360,111 @@
   </si>
   <si>
     <t>Statue_Marble</t>
+  </si>
+  <si>
+    <t>Item_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>파란 병</t>
+  </si>
+  <si>
+    <t>평범한 파란 병이다.</t>
+  </si>
+  <si>
+    <t>Junk</t>
+  </si>
+  <si>
+    <t>PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
+  </si>
+  <si>
+    <t>JunkObject</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>Item_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>큰 핑크색 병</t>
+  </si>
+  <si>
+    <t>크기가 큰 핑크색 병이다.</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bar_Bottle_Lage_01]</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>Item_Junk_Can_Navy</t>
+  </si>
+  <si>
+    <t>남색 캔</t>
+  </si>
+  <si>
+    <t>누가 먹다남은 음료이다.</t>
+  </si>
+  <si>
+    <t>Junk_Can_Navy[SM_Prop_Can_01]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Fish</t>
+  </si>
+  <si>
+    <t>청새치</t>
+  </si>
+  <si>
+    <t>엄청 큰 청새치다. 맛있어 보인다.</t>
+  </si>
+  <si>
+    <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>썬글라스</t>
+  </si>
+  <si>
+    <t>화려한 썬글라스다.</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Item_Junk_Microphone</t>
+  </si>
+  <si>
+    <t>마이크</t>
+  </si>
+  <si>
+    <t>손 마이크이다.</t>
+  </si>
+  <si>
+    <t>Junk_Microphone[SM_Prop_Microphone_01]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Sculpture</t>
+  </si>
+  <si>
+    <t>조각품</t>
+  </si>
+  <si>
+    <t>예술가의 혼이 담긴 조각품이다.</t>
+  </si>
+  <si>
+    <t>PolygonNightclub_Mat_01_A_Metallic,PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>Junk_Sculpture[SM_Prop_Sculpture_01]</t>
   </si>
 </sst>
 </file>
@@ -719,14 +824,14 @@
     <col customWidth="1" min="1" max="1" width="25.38"/>
     <col customWidth="1" min="2" max="2" width="15.0"/>
     <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="15.5"/>
-    <col customWidth="1" min="5" max="5" width="14.5"/>
+    <col customWidth="1" min="4" max="4" width="12.75"/>
+    <col customWidth="1" min="5" max="5" width="13.25"/>
     <col customWidth="1" min="6" max="6" width="11.63"/>
     <col customWidth="1" min="7" max="7" width="9.63"/>
-    <col customWidth="1" min="8" max="8" width="23.75"/>
-    <col customWidth="1" min="9" max="9" width="14.13"/>
+    <col customWidth="1" min="8" max="8" width="9.38"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
     <col customWidth="1" min="10" max="10" width="21.25"/>
-    <col customWidth="1" min="11" max="11" width="27.38"/>
+    <col customWidth="1" min="11" max="11" width="28.38"/>
     <col customWidth="1" min="12" max="12" width="11.75"/>
     <col customWidth="1" min="13" max="21" width="9.63"/>
   </cols>
@@ -814,7 +919,9 @@
       <c r="M2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -863,7 +970,9 @@
       <c r="M3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="10"/>
+      <c r="N3" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -874,19 +983,19 @@
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4">
         <v>2.0</v>
@@ -899,15 +1008,17 @@
         <v>-1.0</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M4" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -919,19 +1030,19 @@
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4">
         <v>1.0</v>
@@ -944,15 +1055,17 @@
         <v>1.0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M5" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -964,19 +1077,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4">
         <v>10.0</v>
@@ -987,16 +1100,16 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
@@ -1009,19 +1122,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4">
         <v>8.0</v>
@@ -1032,16 +1145,16 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -1054,19 +1167,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4">
         <v>7.0</v>
@@ -1077,16 +1190,16 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -1099,19 +1212,19 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4">
         <v>6.0</v>
@@ -1125,13 +1238,13 @@
         <v>62</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -1153,10 +1266,10 @@
         <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4">
         <v>5.0</v>
@@ -1170,13 +1283,13 @@
         <v>66</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
@@ -1198,7 +1311,7 @@
         <v>69</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>70</v>
@@ -1215,13 +1328,13 @@
         <v>71</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -1243,7 +1356,7 @@
         <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>70</v>
@@ -1260,13 +1373,13 @@
         <v>75</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -1291,7 +1404,7 @@
         <v>79</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F13" s="14">
         <v>12.0</v>
@@ -1311,7 +1424,7 @@
         <v>82</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
@@ -1336,7 +1449,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F14" s="14">
         <v>12.0</v>
@@ -1356,7 +1469,7 @@
         <v>82</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
@@ -1381,7 +1494,7 @@
         <v>79</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F15" s="14">
         <v>12.0</v>
@@ -1401,7 +1514,7 @@
         <v>82</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -1426,7 +1539,7 @@
         <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F16" s="14">
         <v>12.0</v>
@@ -1446,7 +1559,7 @@
         <v>82</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -1471,7 +1584,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F17" s="14">
         <v>12.0</v>
@@ -1491,7 +1604,7 @@
         <v>82</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
@@ -1516,7 +1629,7 @@
         <v>98</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F18" s="14">
         <v>5.0</v>
@@ -1536,7 +1649,7 @@
         <v>101</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -1561,7 +1674,7 @@
         <v>98</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
         <v>10.0</v>
@@ -1581,7 +1694,7 @@
         <v>101</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -1606,7 +1719,7 @@
         <v>98</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="14">
         <v>15.0</v>
@@ -1626,7 +1739,7 @@
         <v>101</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
@@ -1671,7 +1784,7 @@
         <v>101</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -1683,20 +1796,42 @@
       <c r="U21" s="4"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="A22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
+      <c r="J22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
+      <c r="N22" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
@@ -1706,20 +1841,42 @@
       <c r="U22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="A23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="J23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
+      <c r="N23" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
@@ -1729,18 +1886,38 @@
       <c r="U23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="A24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="J24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -1752,18 +1929,38 @@
       <c r="U24" s="4"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="A25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4000.0</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
+      <c r="J25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
@@ -1775,20 +1972,42 @@
       <c r="U25" s="4"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="A26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="J26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="N26" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
@@ -1798,17 +2017,35 @@
       <c r="U26" s="4"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="A27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="J27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -1821,17 +2058,35 @@
       <c r="U27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="A28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="14">
+        <v>20.0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5000.0</v>
+      </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
+      <c r="J28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="149">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -96,7 +96,10 @@
     <t>Husks</t>
   </si>
   <si>
-    <t>HoldType</t>
+    <t>StringHoldType</t>
+  </si>
+  <si>
+    <t>MeshCollider</t>
   </si>
   <si>
     <t>Item_Tool_MasterKey</t>
@@ -112,7 +115,7 @@
     <t>Tool</t>
   </si>
   <si>
-    <t>None</t>
+    <t>Epic</t>
   </si>
   <si>
     <t>Yellow</t>
@@ -121,7 +124,10 @@
     <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
   </si>
   <si>
-    <t>ToolObject</t>
+    <t>Pool_Tool</t>
+  </si>
+  <si>
+    <t>Hold</t>
   </si>
   <si>
     <t>Item_Tool_Key</t>
@@ -134,6 +140,9 @@
 한 번만 사용 할 수 있다.</t>
   </si>
   <si>
+    <t>Rare</t>
+  </si>
+  <si>
     <t>Black</t>
   </si>
   <si>
@@ -149,19 +158,13 @@
     <t>Jewel</t>
   </si>
   <si>
-    <t>Epic</t>
-  </si>
-  <si>
     <t>M_Gemstone_Diamond,Lit</t>
   </si>
   <si>
     <t>Jewel_Cone[Cone]</t>
   </si>
   <si>
-    <t>JewelObject</t>
-  </si>
-  <si>
-    <t>Hold</t>
+    <t>Pool_Jewel</t>
   </si>
   <si>
     <t>Item_Jewel_Amethyst</t>
@@ -203,9 +206,6 @@
     <t>에메랄드다.</t>
   </si>
   <si>
-    <t>Rare</t>
-  </si>
-  <si>
     <t>M_Gemstone_Emerald</t>
   </si>
   <si>
@@ -360,6 +360,111 @@
   </si>
   <si>
     <t>Statue_Marble</t>
+  </si>
+  <si>
+    <t>Item_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>파란 병</t>
+  </si>
+  <si>
+    <t>평범한 파란 병이다.</t>
+  </si>
+  <si>
+    <t>Junk</t>
+  </si>
+  <si>
+    <t>PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
+  </si>
+  <si>
+    <t>JunkObject</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Blue</t>
+  </si>
+  <si>
+    <t>Item_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>큰 핑크색 병</t>
+  </si>
+  <si>
+    <t>크기가 큰 핑크색 병이다.</t>
+  </si>
+  <si>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
+  </si>
+  <si>
+    <t>Item_Junk_Can_Navy</t>
+  </si>
+  <si>
+    <t>남색 캔</t>
+  </si>
+  <si>
+    <t>누가 먹다남은 음료이다.</t>
+  </si>
+  <si>
+    <t>Junk_Can_Navy[SM_Prop_Can_01]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Fish</t>
+  </si>
+  <si>
+    <t>청새치</t>
+  </si>
+  <si>
+    <t>엄청 큰 청새치다. 맛있어 보인다.</t>
+  </si>
+  <si>
+    <t>Junk_Fish[SM_Prop_Display_Fish_02]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>썬글라스</t>
+  </si>
+  <si>
+    <t>화려한 썬글라스다.</t>
+  </si>
+  <si>
+    <t>Junk_Glasses[SM_Prop_Glasses_01]</t>
+  </si>
+  <si>
+    <t>MeshCollider_Junk_Glasses</t>
+  </si>
+  <si>
+    <t>Item_Junk_Microphone</t>
+  </si>
+  <si>
+    <t>마이크</t>
+  </si>
+  <si>
+    <t>손 마이크이다.</t>
+  </si>
+  <si>
+    <t>Junk_Microphone[SM_Prop_Microphone_01]</t>
+  </si>
+  <si>
+    <t>Item_Junk_Sculpture</t>
+  </si>
+  <si>
+    <t>조각품</t>
+  </si>
+  <si>
+    <t>예술가의 혼이 담긴 조각품이다.</t>
+  </si>
+  <si>
+    <t>PolygonNightclub_Mat_01_A_Metallic,PolygonNightclubs_01_A</t>
+  </si>
+  <si>
+    <t>Junk_Sculpture[SM_Prop_Sculpture_01]</t>
   </si>
 </sst>
 </file>
@@ -719,16 +824,17 @@
     <col customWidth="1" min="1" max="1" width="25.38"/>
     <col customWidth="1" min="2" max="2" width="15.0"/>
     <col customWidth="1" min="3" max="3" width="24.25"/>
-    <col customWidth="1" min="4" max="4" width="15.5"/>
-    <col customWidth="1" min="5" max="5" width="14.5"/>
+    <col customWidth="1" min="4" max="4" width="12.75"/>
+    <col customWidth="1" min="5" max="5" width="13.25"/>
     <col customWidth="1" min="6" max="6" width="11.63"/>
     <col customWidth="1" min="7" max="7" width="9.63"/>
-    <col customWidth="1" min="8" max="8" width="23.75"/>
-    <col customWidth="1" min="9" max="9" width="14.13"/>
+    <col customWidth="1" min="8" max="8" width="9.38"/>
+    <col customWidth="1" min="9" max="9" width="8.63"/>
     <col customWidth="1" min="10" max="10" width="21.25"/>
-    <col customWidth="1" min="11" max="11" width="27.38"/>
+    <col customWidth="1" min="11" max="11" width="28.38"/>
     <col customWidth="1" min="12" max="12" width="11.75"/>
-    <col customWidth="1" min="13" max="21" width="9.63"/>
+    <col customWidth="1" min="13" max="13" width="16.13"/>
+    <col customWidth="1" min="14" max="21" width="9.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -814,7 +920,9 @@
       <c r="M2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="4"/>
+      <c r="N2" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
@@ -863,7 +971,9 @@
       <c r="M3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="10"/>
+      <c r="N3" s="9" t="s">
+        <v>27</v>
+      </c>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
@@ -874,19 +984,19 @@
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4">
         <v>2.0</v>
@@ -899,15 +1009,17 @@
         <v>-1.0</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="4"/>
+      <c r="L4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -919,19 +1031,19 @@
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F5" s="4">
         <v>1.0</v>
@@ -944,15 +1056,17 @@
         <v>1.0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M5" s="4"/>
+      <c r="L5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>36</v>
+      </c>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -964,19 +1078,19 @@
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F6" s="4">
         <v>10.0</v>
@@ -987,16 +1101,16 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M6" s="11" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
@@ -1009,19 +1123,19 @@
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F7" s="4">
         <v>8.0</v>
@@ -1032,16 +1146,16 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M7" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
@@ -1054,19 +1168,19 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F8" s="4">
         <v>7.0</v>
@@ -1077,16 +1191,16 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M8" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
@@ -1099,19 +1213,19 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="F9" s="4">
         <v>6.0</v>
@@ -1125,13 +1239,13 @@
         <v>62</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M9" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
@@ -1153,10 +1267,10 @@
         <v>65</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F10" s="4">
         <v>5.0</v>
@@ -1170,13 +1284,13 @@
         <v>66</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M10" s="11" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
@@ -1198,7 +1312,7 @@
         <v>69</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>70</v>
@@ -1215,13 +1329,13 @@
         <v>71</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M11" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
@@ -1243,7 +1357,7 @@
         <v>74</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>70</v>
@@ -1260,13 +1374,13 @@
         <v>75</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>48</v>
       </c>
       <c r="M12" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
@@ -1291,7 +1405,7 @@
         <v>79</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F13" s="14">
         <v>12.0</v>
@@ -1311,7 +1425,7 @@
         <v>82</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
@@ -1336,7 +1450,7 @@
         <v>79</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F14" s="14">
         <v>12.0</v>
@@ -1356,7 +1470,7 @@
         <v>82</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
@@ -1381,7 +1495,7 @@
         <v>79</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F15" s="14">
         <v>12.0</v>
@@ -1401,7 +1515,7 @@
         <v>82</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
@@ -1426,7 +1540,7 @@
         <v>79</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F16" s="14">
         <v>12.0</v>
@@ -1446,7 +1560,7 @@
         <v>82</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
@@ -1471,7 +1585,7 @@
         <v>79</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F17" s="14">
         <v>12.0</v>
@@ -1491,7 +1605,7 @@
         <v>82</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
@@ -1516,7 +1630,7 @@
         <v>98</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="F18" s="14">
         <v>5.0</v>
@@ -1536,7 +1650,7 @@
         <v>101</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -1561,7 +1675,7 @@
         <v>98</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
         <v>10.0</v>
@@ -1581,7 +1695,7 @@
         <v>101</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
@@ -1606,7 +1720,7 @@
         <v>98</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F20" s="14">
         <v>15.0</v>
@@ -1626,7 +1740,7 @@
         <v>101</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
@@ -1671,7 +1785,7 @@
         <v>101</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
@@ -1683,20 +1797,42 @@
       <c r="U21" s="4"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
+      <c r="A22" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F22" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
+      <c r="J22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
+      <c r="N22" s="3" t="s">
+        <v>121</v>
+      </c>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
@@ -1706,20 +1842,42 @@
       <c r="U22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
+      <c r="A23" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F23" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G23" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="J23" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
+      <c r="N23" s="3" t="s">
+        <v>126</v>
+      </c>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
@@ -1729,18 +1887,38 @@
       <c r="U23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
+      <c r="A24" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F24" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G24" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="J24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -1752,19 +1930,41 @@
       <c r="U24" s="4"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
+      <c r="A25" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="F25" s="14">
+        <v>15.0</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4000.0</v>
+      </c>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
+      <c r="J25" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>36</v>
+      </c>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
       <c r="P25" s="4"/>
@@ -1775,20 +1975,42 @@
       <c r="U25" s="4"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
+      <c r="A26" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G26" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
+      <c r="J26" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
+      <c r="N26" s="3" t="s">
+        <v>139</v>
+      </c>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
@@ -1798,17 +2020,35 @@
       <c r="U26" s="4"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
+      <c r="A27" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F27" s="14">
+        <v>5.0</v>
+      </c>
+      <c r="G27" s="3">
+        <v>100.0</v>
+      </c>
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
+      <c r="J27" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>143</v>
+      </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
@@ -1821,17 +2061,35 @@
       <c r="U27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
+      <c r="A28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="F28" s="14">
+        <v>20.0</v>
+      </c>
+      <c r="G28" s="14">
+        <v>5000.0</v>
+      </c>
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
+      <c r="J28" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>148</v>
+      </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="149">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -124,7 +124,7 @@
     <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
   </si>
   <si>
-    <t>Pool_Tool</t>
+    <t>ToolObject</t>
   </si>
   <si>
     <t>Hold</t>
@@ -164,7 +164,7 @@
     <t>Jewel_Cone[Cone]</t>
   </si>
   <si>
-    <t>Pool_Jewel</t>
+    <t>JewelObject</t>
   </si>
   <si>
     <t>Item_Jewel_Amethyst</t>
@@ -503,6 +503,10 @@
       <name val="&quot;맑은 고딕&quot;"/>
     </font>
     <font>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -510,10 +514,6 @@
     <font>
       <color rgb="FF000000"/>
       <name val="&quot;\0022맑은 고딕\0022&quot;"/>
-    </font>
-    <font>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
     </font>
     <font>
       <color rgb="FF000000"/>
@@ -560,7 +560,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -588,19 +588,22 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -832,8 +835,7 @@
     <col customWidth="1" min="9" max="9" width="8.63"/>
     <col customWidth="1" min="10" max="10" width="21.25"/>
     <col customWidth="1" min="11" max="11" width="28.38"/>
-    <col customWidth="1" min="12" max="12" width="11.75"/>
-    <col customWidth="1" min="13" max="13" width="16.13"/>
+    <col customWidth="1" min="12" max="13" width="16.13"/>
     <col customWidth="1" min="14" max="21" width="9.63"/>
   </cols>
   <sheetData>
@@ -867,7 +869,7 @@
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="L1" s="5"/>
       <c r="M1" s="5" t="s">
         <v>9</v>
       </c>
@@ -914,7 +916,7 @@
       <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="7" t="s">
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
@@ -965,7 +967,7 @@
       <c r="K3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="7" t="s">
         <v>25</v>
       </c>
       <c r="M3" s="7" t="s">
@@ -1014,10 +1016,10 @@
       <c r="K4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M4" s="11" t="s">
+      <c r="M4" s="12" t="s">
         <v>36</v>
       </c>
       <c r="N4" s="4"/>
@@ -1061,10 +1063,10 @@
       <c r="K5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L5" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="M5" s="11" t="s">
+      <c r="M5" s="12" t="s">
         <v>36</v>
       </c>
       <c r="N5" s="4"/>
@@ -1106,10 +1108,10 @@
       <c r="K6" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="L6" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="M6" s="12" t="s">
         <v>36</v>
       </c>
       <c r="N6" s="4"/>
@@ -1151,10 +1153,10 @@
       <c r="K7" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M7" s="11" t="s">
+      <c r="M7" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N7" s="4"/>
@@ -1196,10 +1198,10 @@
       <c r="K8" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="L8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M8" s="11" t="s">
+      <c r="M8" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N8" s="4"/>
@@ -1241,10 +1243,10 @@
       <c r="K9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="L9" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="11" t="s">
+      <c r="M9" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N9" s="4"/>
@@ -1286,10 +1288,10 @@
       <c r="K10" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M10" s="11" t="s">
+      <c r="M10" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N10" s="4"/>
@@ -1331,10 +1333,10 @@
       <c r="K11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M11" s="11" t="s">
+      <c r="M11" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N11" s="4"/>
@@ -1376,10 +1378,10 @@
       <c r="K12" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="3" t="s">
+      <c r="L12" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="M12" s="11" t="s">
+      <c r="M12" s="12" t="s">
         <v>53</v>
       </c>
       <c r="N12" s="4"/>
@@ -1392,264 +1394,264 @@
       <c r="U12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="12" t="s">
+      <c r="A13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C13" s="12" t="s">
+      <c r="C13" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="15">
         <v>12.0</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="13" t="s">
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="L13" s="13" t="s">
+      <c r="L13" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M13" s="13" t="s">
+      <c r="M13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N13" s="15"/>
-      <c r="O13" s="15"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="15"/>
-      <c r="R13" s="15"/>
-      <c r="S13" s="15"/>
-      <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="12" t="s">
+      <c r="A14" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B14" s="12" t="s">
+      <c r="B14" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="13" t="s">
+      <c r="D14" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F14" s="15">
         <v>12.0</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H14" s="15"/>
-      <c r="I14" s="15"/>
-      <c r="J14" s="13" t="s">
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="K14" s="13" t="s">
+      <c r="K14" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="L14" s="13" t="s">
+      <c r="L14" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M14" s="13" t="s">
+      <c r="M14" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N14" s="15"/>
-      <c r="O14" s="15"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="15"/>
-      <c r="R14" s="15"/>
-      <c r="S14" s="15"/>
-      <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
+      <c r="N14" s="16"/>
+      <c r="O14" s="16"/>
+      <c r="P14" s="16"/>
+      <c r="Q14" s="16"/>
+      <c r="R14" s="16"/>
+      <c r="S14" s="16"/>
+      <c r="T14" s="16"/>
+      <c r="U14" s="16"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="B15" s="12" t="s">
+      <c r="B15" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="12" t="s">
+      <c r="C15" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="15">
         <v>12.0</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="13" t="s">
+      <c r="H15" s="16"/>
+      <c r="I15" s="16"/>
+      <c r="J15" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="L15" s="13" t="s">
+      <c r="L15" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M15" s="13" t="s">
+      <c r="M15" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="15"/>
-      <c r="R15" s="15"/>
-      <c r="S15" s="15"/>
-      <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
+      <c r="N15" s="16"/>
+      <c r="O15" s="16"/>
+      <c r="P15" s="16"/>
+      <c r="Q15" s="16"/>
+      <c r="R15" s="16"/>
+      <c r="S15" s="16"/>
+      <c r="T15" s="16"/>
+      <c r="U15" s="16"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="14">
+      <c r="F16" s="15">
         <v>12.0</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="13" t="s">
+      <c r="H16" s="16"/>
+      <c r="I16" s="16"/>
+      <c r="J16" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="L16" s="13" t="s">
+      <c r="L16" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M16" s="13" t="s">
+      <c r="M16" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
+      <c r="N16" s="16"/>
+      <c r="O16" s="16"/>
+      <c r="P16" s="16"/>
+      <c r="Q16" s="16"/>
+      <c r="R16" s="16"/>
+      <c r="S16" s="16"/>
+      <c r="T16" s="16"/>
+      <c r="U16" s="16"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="13" t="s">
+      <c r="A17" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F17" s="14">
+      <c r="F17" s="15">
         <v>12.0</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <v>1200.0</v>
       </c>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="13" t="s">
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="K17" s="13" t="s">
+      <c r="K17" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="L17" s="13" t="s">
+      <c r="L17" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="M17" s="13" t="s">
+      <c r="M17" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="N17" s="15"/>
-      <c r="O17" s="15"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="15"/>
-      <c r="R17" s="15"/>
-      <c r="S17" s="15"/>
-      <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F18" s="14">
+      <c r="F18" s="15">
         <v>5.0</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <v>800.0</v>
       </c>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="13" t="s">
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="K18" s="13" t="s">
+      <c r="K18" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="L18" s="13" t="s">
+      <c r="L18" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="M18" s="13" t="s">
+      <c r="M18" s="14" t="s">
         <v>36</v>
       </c>
       <c r="N18" s="4"/>
@@ -1662,39 +1664,39 @@
       <c r="U18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="13" t="s">
+      <c r="A19" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="17" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="14">
+      <c r="F19" s="15">
         <v>10.0</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <v>1600.0</v>
       </c>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="13" t="s">
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="K19" s="13" t="s">
+      <c r="K19" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="L19" s="13" t="s">
+      <c r="L19" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="M19" s="13" t="s">
+      <c r="M19" s="14" t="s">
         <v>36</v>
       </c>
       <c r="N19" s="4"/>
@@ -1707,39 +1709,39 @@
       <c r="U19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="17" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F20" s="14">
+      <c r="F20" s="15">
         <v>15.0</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <v>3000.0</v>
       </c>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="13" t="s">
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="13" t="s">
+      <c r="K20" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="L20" s="13" t="s">
+      <c r="L20" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="M20" s="13" t="s">
+      <c r="M20" s="14" t="s">
         <v>36</v>
       </c>
       <c r="N20" s="4"/>
@@ -1752,39 +1754,39 @@
       <c r="U20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
+      <c r="A21" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F21" s="14">
+      <c r="F21" s="15">
         <v>20.0</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <v>5000.0</v>
       </c>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="13" t="s">
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="K21" s="13" t="s">
+      <c r="K21" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="L21" s="13" t="s">
+      <c r="L21" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="M21" s="13" t="s">
+      <c r="M21" s="14" t="s">
         <v>36</v>
       </c>
       <c r="N21" s="4"/>
@@ -1812,7 +1814,7 @@
       <c r="E22" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F22" s="14">
+      <c r="F22" s="15">
         <v>5.0</v>
       </c>
       <c r="G22" s="3">
@@ -1857,7 +1859,7 @@
       <c r="E23" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F23" s="14">
+      <c r="F23" s="15">
         <v>5.0</v>
       </c>
       <c r="G23" s="3">
@@ -1902,7 +1904,7 @@
       <c r="E24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="14">
+      <c r="F24" s="15">
         <v>5.0</v>
       </c>
       <c r="G24" s="3">
@@ -1942,13 +1944,13 @@
       <c r="D25" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E25" s="13" t="s">
+      <c r="E25" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F25" s="14">
+      <c r="F25" s="15">
         <v>15.0</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <v>4000.0</v>
       </c>
       <c r="H25" s="4"/>
@@ -1962,7 +1964,7 @@
       <c r="L25" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M25" s="13" t="s">
+      <c r="M25" s="14" t="s">
         <v>36</v>
       </c>
       <c r="N25" s="4"/>
@@ -1990,7 +1992,7 @@
       <c r="E26" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="14">
+      <c r="F26" s="15">
         <v>5.0</v>
       </c>
       <c r="G26" s="3">
@@ -2035,7 +2037,7 @@
       <c r="E27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F27" s="14">
+      <c r="F27" s="15">
         <v>5.0</v>
       </c>
       <c r="G27" s="3">
@@ -2049,7 +2051,9 @@
       <c r="K27" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="L27" s="4"/>
+      <c r="L27" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
@@ -2073,13 +2077,13 @@
       <c r="D28" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E28" s="13" t="s">
+      <c r="E28" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="F28" s="14">
+      <c r="F28" s="15">
         <v>20.0</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <v>5000.0</v>
       </c>
       <c r="H28" s="4"/>
@@ -2090,7 +2094,9 @@
       <c r="K28" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="L28" s="4"/>
+      <c r="L28" s="3" t="s">
+        <v>120</v>
+      </c>
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
@@ -6518,3124 +6524,3124 @@
       <c r="U220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="17"/>
-      <c r="B221" s="17"/>
+      <c r="A221" s="18"/>
+      <c r="B221" s="18"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="A222" s="17"/>
-      <c r="B222" s="17"/>
+      <c r="A222" s="18"/>
+      <c r="B222" s="18"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="17"/>
-      <c r="B223" s="17"/>
+      <c r="A223" s="18"/>
+      <c r="B223" s="18"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="A224" s="17"/>
-      <c r="B224" s="17"/>
+      <c r="A224" s="18"/>
+      <c r="B224" s="18"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="A225" s="17"/>
-      <c r="B225" s="17"/>
+      <c r="A225" s="18"/>
+      <c r="B225" s="18"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="17"/>
-      <c r="B226" s="17"/>
+      <c r="A226" s="18"/>
+      <c r="B226" s="18"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="17"/>
-      <c r="B227" s="17"/>
+      <c r="A227" s="18"/>
+      <c r="B227" s="18"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="17"/>
-      <c r="B228" s="17"/>
+      <c r="A228" s="18"/>
+      <c r="B228" s="18"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="17"/>
-      <c r="B229" s="17"/>
+      <c r="A229" s="18"/>
+      <c r="B229" s="18"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="A230" s="17"/>
-      <c r="B230" s="17"/>
+      <c r="A230" s="18"/>
+      <c r="B230" s="18"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="17"/>
-      <c r="B231" s="17"/>
+      <c r="A231" s="18"/>
+      <c r="B231" s="18"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="17"/>
-      <c r="B232" s="17"/>
+      <c r="A232" s="18"/>
+      <c r="B232" s="18"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="17"/>
-      <c r="B233" s="17"/>
+      <c r="A233" s="18"/>
+      <c r="B233" s="18"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="17"/>
-      <c r="B234" s="17"/>
+      <c r="A234" s="18"/>
+      <c r="B234" s="18"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="17"/>
-      <c r="B235" s="17"/>
+      <c r="A235" s="18"/>
+      <c r="B235" s="18"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="17"/>
-      <c r="B236" s="17"/>
+      <c r="A236" s="18"/>
+      <c r="B236" s="18"/>
     </row>
     <row r="237" ht="15.75" customHeight="1">
-      <c r="A237" s="17"/>
-      <c r="B237" s="17"/>
+      <c r="A237" s="18"/>
+      <c r="B237" s="18"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="17"/>
-      <c r="B238" s="17"/>
+      <c r="A238" s="18"/>
+      <c r="B238" s="18"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="17"/>
-      <c r="B239" s="17"/>
+      <c r="A239" s="18"/>
+      <c r="B239" s="18"/>
     </row>
     <row r="240" ht="15.75" customHeight="1">
-      <c r="A240" s="17"/>
-      <c r="B240" s="17"/>
+      <c r="A240" s="18"/>
+      <c r="B240" s="18"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="17"/>
-      <c r="B241" s="17"/>
+      <c r="A241" s="18"/>
+      <c r="B241" s="18"/>
     </row>
     <row r="242" ht="15.75" customHeight="1">
-      <c r="A242" s="17"/>
-      <c r="B242" s="17"/>
+      <c r="A242" s="18"/>
+      <c r="B242" s="18"/>
     </row>
     <row r="243" ht="15.75" customHeight="1">
-      <c r="A243" s="17"/>
-      <c r="B243" s="17"/>
+      <c r="A243" s="18"/>
+      <c r="B243" s="18"/>
     </row>
     <row r="244" ht="15.75" customHeight="1">
-      <c r="A244" s="17"/>
-      <c r="B244" s="17"/>
+      <c r="A244" s="18"/>
+      <c r="B244" s="18"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="17"/>
-      <c r="B245" s="17"/>
+      <c r="A245" s="18"/>
+      <c r="B245" s="18"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="17"/>
-      <c r="B246" s="17"/>
+      <c r="A246" s="18"/>
+      <c r="B246" s="18"/>
     </row>
     <row r="247" ht="15.75" customHeight="1">
-      <c r="A247" s="17"/>
-      <c r="B247" s="17"/>
+      <c r="A247" s="18"/>
+      <c r="B247" s="18"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="17"/>
-      <c r="B248" s="17"/>
+      <c r="A248" s="18"/>
+      <c r="B248" s="18"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="17"/>
-      <c r="B249" s="17"/>
+      <c r="A249" s="18"/>
+      <c r="B249" s="18"/>
     </row>
     <row r="250" ht="15.75" customHeight="1">
-      <c r="A250" s="17"/>
-      <c r="B250" s="17"/>
+      <c r="A250" s="18"/>
+      <c r="B250" s="18"/>
     </row>
     <row r="251" ht="15.75" customHeight="1">
-      <c r="A251" s="17"/>
-      <c r="B251" s="17"/>
+      <c r="A251" s="18"/>
+      <c r="B251" s="18"/>
     </row>
     <row r="252" ht="15.75" customHeight="1">
-      <c r="A252" s="17"/>
-      <c r="B252" s="17"/>
+      <c r="A252" s="18"/>
+      <c r="B252" s="18"/>
     </row>
     <row r="253" ht="15.75" customHeight="1">
-      <c r="A253" s="17"/>
-      <c r="B253" s="17"/>
+      <c r="A253" s="18"/>
+      <c r="B253" s="18"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="17"/>
-      <c r="B254" s="17"/>
+      <c r="A254" s="18"/>
+      <c r="B254" s="18"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="17"/>
-      <c r="B255" s="17"/>
+      <c r="A255" s="18"/>
+      <c r="B255" s="18"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="17"/>
-      <c r="B256" s="17"/>
+      <c r="A256" s="18"/>
+      <c r="B256" s="18"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="17"/>
-      <c r="B257" s="17"/>
+      <c r="A257" s="18"/>
+      <c r="B257" s="18"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="17"/>
-      <c r="B258" s="17"/>
+      <c r="A258" s="18"/>
+      <c r="B258" s="18"/>
     </row>
     <row r="259" ht="15.75" customHeight="1">
-      <c r="A259" s="17"/>
-      <c r="B259" s="17"/>
+      <c r="A259" s="18"/>
+      <c r="B259" s="18"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="17"/>
-      <c r="B260" s="17"/>
+      <c r="A260" s="18"/>
+      <c r="B260" s="18"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="17"/>
-      <c r="B261" s="17"/>
+      <c r="A261" s="18"/>
+      <c r="B261" s="18"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="17"/>
-      <c r="B262" s="17"/>
+      <c r="A262" s="18"/>
+      <c r="B262" s="18"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="17"/>
-      <c r="B263" s="17"/>
+      <c r="A263" s="18"/>
+      <c r="B263" s="18"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="17"/>
-      <c r="B264" s="17"/>
+      <c r="A264" s="18"/>
+      <c r="B264" s="18"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="17"/>
-      <c r="B265" s="17"/>
+      <c r="A265" s="18"/>
+      <c r="B265" s="18"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="17"/>
-      <c r="B266" s="17"/>
+      <c r="A266" s="18"/>
+      <c r="B266" s="18"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="17"/>
-      <c r="B267" s="17"/>
+      <c r="A267" s="18"/>
+      <c r="B267" s="18"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="17"/>
-      <c r="B268" s="17"/>
+      <c r="A268" s="18"/>
+      <c r="B268" s="18"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="17"/>
-      <c r="B269" s="17"/>
+      <c r="A269" s="18"/>
+      <c r="B269" s="18"/>
     </row>
     <row r="270" ht="15.75" customHeight="1">
-      <c r="A270" s="17"/>
-      <c r="B270" s="17"/>
+      <c r="A270" s="18"/>
+      <c r="B270" s="18"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="17"/>
-      <c r="B271" s="17"/>
+      <c r="A271" s="18"/>
+      <c r="B271" s="18"/>
     </row>
     <row r="272" ht="15.75" customHeight="1">
-      <c r="A272" s="17"/>
-      <c r="B272" s="17"/>
+      <c r="A272" s="18"/>
+      <c r="B272" s="18"/>
     </row>
     <row r="273" ht="15.75" customHeight="1">
-      <c r="A273" s="17"/>
-      <c r="B273" s="17"/>
+      <c r="A273" s="18"/>
+      <c r="B273" s="18"/>
     </row>
     <row r="274" ht="15.75" customHeight="1">
-      <c r="A274" s="17"/>
-      <c r="B274" s="17"/>
+      <c r="A274" s="18"/>
+      <c r="B274" s="18"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="17"/>
-      <c r="B275" s="17"/>
+      <c r="A275" s="18"/>
+      <c r="B275" s="18"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="17"/>
-      <c r="B276" s="17"/>
+      <c r="A276" s="18"/>
+      <c r="B276" s="18"/>
     </row>
     <row r="277" ht="15.75" customHeight="1">
-      <c r="A277" s="17"/>
-      <c r="B277" s="17"/>
+      <c r="A277" s="18"/>
+      <c r="B277" s="18"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="17"/>
-      <c r="B278" s="17"/>
+      <c r="A278" s="18"/>
+      <c r="B278" s="18"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="17"/>
-      <c r="B279" s="17"/>
+      <c r="A279" s="18"/>
+      <c r="B279" s="18"/>
     </row>
     <row r="280" ht="15.75" customHeight="1">
-      <c r="A280" s="17"/>
-      <c r="B280" s="17"/>
+      <c r="A280" s="18"/>
+      <c r="B280" s="18"/>
     </row>
     <row r="281" ht="15.75" customHeight="1">
-      <c r="A281" s="17"/>
-      <c r="B281" s="17"/>
+      <c r="A281" s="18"/>
+      <c r="B281" s="18"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="17"/>
-      <c r="B282" s="17"/>
+      <c r="A282" s="18"/>
+      <c r="B282" s="18"/>
     </row>
     <row r="283" ht="15.75" customHeight="1">
-      <c r="A283" s="17"/>
-      <c r="B283" s="17"/>
+      <c r="A283" s="18"/>
+      <c r="B283" s="18"/>
     </row>
     <row r="284" ht="15.75" customHeight="1">
-      <c r="A284" s="17"/>
-      <c r="B284" s="17"/>
+      <c r="A284" s="18"/>
+      <c r="B284" s="18"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="17"/>
-      <c r="B285" s="17"/>
+      <c r="A285" s="18"/>
+      <c r="B285" s="18"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="17"/>
-      <c r="B286" s="17"/>
+      <c r="A286" s="18"/>
+      <c r="B286" s="18"/>
     </row>
     <row r="287" ht="15.75" customHeight="1">
-      <c r="A287" s="17"/>
-      <c r="B287" s="17"/>
+      <c r="A287" s="18"/>
+      <c r="B287" s="18"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="17"/>
-      <c r="B288" s="17"/>
+      <c r="A288" s="18"/>
+      <c r="B288" s="18"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="17"/>
-      <c r="B289" s="17"/>
+      <c r="A289" s="18"/>
+      <c r="B289" s="18"/>
     </row>
     <row r="290" ht="15.75" customHeight="1">
-      <c r="A290" s="17"/>
-      <c r="B290" s="17"/>
+      <c r="A290" s="18"/>
+      <c r="B290" s="18"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="17"/>
-      <c r="B291" s="17"/>
+      <c r="A291" s="18"/>
+      <c r="B291" s="18"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="17"/>
-      <c r="B292" s="17"/>
+      <c r="A292" s="18"/>
+      <c r="B292" s="18"/>
     </row>
     <row r="293" ht="15.75" customHeight="1">
-      <c r="A293" s="17"/>
-      <c r="B293" s="17"/>
+      <c r="A293" s="18"/>
+      <c r="B293" s="18"/>
     </row>
     <row r="294" ht="15.75" customHeight="1">
-      <c r="A294" s="17"/>
-      <c r="B294" s="17"/>
+      <c r="A294" s="18"/>
+      <c r="B294" s="18"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="17"/>
-      <c r="B295" s="17"/>
+      <c r="A295" s="18"/>
+      <c r="B295" s="18"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="17"/>
-      <c r="B296" s="17"/>
+      <c r="A296" s="18"/>
+      <c r="B296" s="18"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="17"/>
-      <c r="B297" s="17"/>
+      <c r="A297" s="18"/>
+      <c r="B297" s="18"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="17"/>
-      <c r="B298" s="17"/>
+      <c r="A298" s="18"/>
+      <c r="B298" s="18"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="17"/>
-      <c r="B299" s="17"/>
+      <c r="A299" s="18"/>
+      <c r="B299" s="18"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="17"/>
-      <c r="B300" s="17"/>
+      <c r="A300" s="18"/>
+      <c r="B300" s="18"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="17"/>
-      <c r="B301" s="17"/>
+      <c r="A301" s="18"/>
+      <c r="B301" s="18"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="17"/>
-      <c r="B302" s="17"/>
+      <c r="A302" s="18"/>
+      <c r="B302" s="18"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="17"/>
-      <c r="B303" s="17"/>
+      <c r="A303" s="18"/>
+      <c r="B303" s="18"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="17"/>
-      <c r="B304" s="17"/>
+      <c r="A304" s="18"/>
+      <c r="B304" s="18"/>
     </row>
     <row r="305" ht="15.75" customHeight="1">
-      <c r="A305" s="17"/>
-      <c r="B305" s="17"/>
+      <c r="A305" s="18"/>
+      <c r="B305" s="18"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="17"/>
-      <c r="B306" s="17"/>
+      <c r="A306" s="18"/>
+      <c r="B306" s="18"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="17"/>
-      <c r="B307" s="17"/>
+      <c r="A307" s="18"/>
+      <c r="B307" s="18"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="17"/>
-      <c r="B308" s="17"/>
+      <c r="A308" s="18"/>
+      <c r="B308" s="18"/>
     </row>
     <row r="309" ht="15.75" customHeight="1">
-      <c r="A309" s="17"/>
-      <c r="B309" s="17"/>
+      <c r="A309" s="18"/>
+      <c r="B309" s="18"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="17"/>
-      <c r="B310" s="17"/>
+      <c r="A310" s="18"/>
+      <c r="B310" s="18"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="17"/>
-      <c r="B311" s="17"/>
+      <c r="A311" s="18"/>
+      <c r="B311" s="18"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="17"/>
-      <c r="B312" s="17"/>
+      <c r="A312" s="18"/>
+      <c r="B312" s="18"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="17"/>
-      <c r="B313" s="17"/>
+      <c r="A313" s="18"/>
+      <c r="B313" s="18"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="17"/>
-      <c r="B314" s="17"/>
+      <c r="A314" s="18"/>
+      <c r="B314" s="18"/>
     </row>
     <row r="315" ht="15.75" customHeight="1">
-      <c r="A315" s="17"/>
-      <c r="B315" s="17"/>
+      <c r="A315" s="18"/>
+      <c r="B315" s="18"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="17"/>
-      <c r="B316" s="17"/>
+      <c r="A316" s="18"/>
+      <c r="B316" s="18"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="17"/>
-      <c r="B317" s="17"/>
+      <c r="A317" s="18"/>
+      <c r="B317" s="18"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="17"/>
-      <c r="B318" s="17"/>
+      <c r="A318" s="18"/>
+      <c r="B318" s="18"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="17"/>
-      <c r="B319" s="17"/>
+      <c r="A319" s="18"/>
+      <c r="B319" s="18"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="17"/>
-      <c r="B320" s="17"/>
+      <c r="A320" s="18"/>
+      <c r="B320" s="18"/>
     </row>
     <row r="321" ht="15.75" customHeight="1">
-      <c r="A321" s="17"/>
-      <c r="B321" s="17"/>
+      <c r="A321" s="18"/>
+      <c r="B321" s="18"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="17"/>
-      <c r="B322" s="17"/>
+      <c r="A322" s="18"/>
+      <c r="B322" s="18"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="17"/>
-      <c r="B323" s="17"/>
+      <c r="A323" s="18"/>
+      <c r="B323" s="18"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="17"/>
-      <c r="B324" s="17"/>
+      <c r="A324" s="18"/>
+      <c r="B324" s="18"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="17"/>
-      <c r="B325" s="17"/>
+      <c r="A325" s="18"/>
+      <c r="B325" s="18"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="17"/>
-      <c r="B326" s="17"/>
+      <c r="A326" s="18"/>
+      <c r="B326" s="18"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="17"/>
-      <c r="B327" s="17"/>
+      <c r="A327" s="18"/>
+      <c r="B327" s="18"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="17"/>
-      <c r="B328" s="17"/>
+      <c r="A328" s="18"/>
+      <c r="B328" s="18"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="17"/>
-      <c r="B329" s="17"/>
+      <c r="A329" s="18"/>
+      <c r="B329" s="18"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="17"/>
-      <c r="B330" s="17"/>
+      <c r="A330" s="18"/>
+      <c r="B330" s="18"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="17"/>
-      <c r="B331" s="17"/>
+      <c r="A331" s="18"/>
+      <c r="B331" s="18"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="17"/>
-      <c r="B332" s="17"/>
+      <c r="A332" s="18"/>
+      <c r="B332" s="18"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="17"/>
-      <c r="B333" s="17"/>
+      <c r="A333" s="18"/>
+      <c r="B333" s="18"/>
     </row>
     <row r="334" ht="15.75" customHeight="1">
-      <c r="A334" s="17"/>
-      <c r="B334" s="17"/>
+      <c r="A334" s="18"/>
+      <c r="B334" s="18"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="17"/>
-      <c r="B335" s="17"/>
+      <c r="A335" s="18"/>
+      <c r="B335" s="18"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="17"/>
-      <c r="B336" s="17"/>
+      <c r="A336" s="18"/>
+      <c r="B336" s="18"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="17"/>
-      <c r="B337" s="17"/>
+      <c r="A337" s="18"/>
+      <c r="B337" s="18"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="17"/>
-      <c r="B338" s="17"/>
+      <c r="A338" s="18"/>
+      <c r="B338" s="18"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="17"/>
-      <c r="B339" s="17"/>
+      <c r="A339" s="18"/>
+      <c r="B339" s="18"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="17"/>
-      <c r="B340" s="17"/>
+      <c r="A340" s="18"/>
+      <c r="B340" s="18"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="17"/>
-      <c r="B341" s="17"/>
+      <c r="A341" s="18"/>
+      <c r="B341" s="18"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="17"/>
-      <c r="B342" s="17"/>
+      <c r="A342" s="18"/>
+      <c r="B342" s="18"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="17"/>
-      <c r="B343" s="17"/>
+      <c r="A343" s="18"/>
+      <c r="B343" s="18"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="17"/>
-      <c r="B344" s="17"/>
+      <c r="A344" s="18"/>
+      <c r="B344" s="18"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="17"/>
-      <c r="B345" s="17"/>
+      <c r="A345" s="18"/>
+      <c r="B345" s="18"/>
     </row>
     <row r="346" ht="15.75" customHeight="1">
-      <c r="A346" s="17"/>
-      <c r="B346" s="17"/>
+      <c r="A346" s="18"/>
+      <c r="B346" s="18"/>
     </row>
     <row r="347" ht="15.75" customHeight="1">
-      <c r="A347" s="17"/>
-      <c r="B347" s="17"/>
+      <c r="A347" s="18"/>
+      <c r="B347" s="18"/>
     </row>
     <row r="348" ht="15.75" customHeight="1">
-      <c r="A348" s="17"/>
-      <c r="B348" s="17"/>
+      <c r="A348" s="18"/>
+      <c r="B348" s="18"/>
     </row>
     <row r="349" ht="15.75" customHeight="1">
-      <c r="A349" s="17"/>
-      <c r="B349" s="17"/>
+      <c r="A349" s="18"/>
+      <c r="B349" s="18"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="17"/>
-      <c r="B350" s="17"/>
+      <c r="A350" s="18"/>
+      <c r="B350" s="18"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="17"/>
-      <c r="B351" s="17"/>
+      <c r="A351" s="18"/>
+      <c r="B351" s="18"/>
     </row>
     <row r="352" ht="15.75" customHeight="1">
-      <c r="A352" s="17"/>
-      <c r="B352" s="17"/>
+      <c r="A352" s="18"/>
+      <c r="B352" s="18"/>
     </row>
     <row r="353" ht="15.75" customHeight="1">
-      <c r="A353" s="17"/>
-      <c r="B353" s="17"/>
+      <c r="A353" s="18"/>
+      <c r="B353" s="18"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="17"/>
-      <c r="B354" s="17"/>
+      <c r="A354" s="18"/>
+      <c r="B354" s="18"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="17"/>
-      <c r="B355" s="17"/>
+      <c r="A355" s="18"/>
+      <c r="B355" s="18"/>
     </row>
     <row r="356" ht="15.75" customHeight="1">
-      <c r="A356" s="17"/>
-      <c r="B356" s="17"/>
+      <c r="A356" s="18"/>
+      <c r="B356" s="18"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="17"/>
-      <c r="B357" s="17"/>
+      <c r="A357" s="18"/>
+      <c r="B357" s="18"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="17"/>
-      <c r="B358" s="17"/>
+      <c r="A358" s="18"/>
+      <c r="B358" s="18"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="17"/>
-      <c r="B359" s="17"/>
+      <c r="A359" s="18"/>
+      <c r="B359" s="18"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="17"/>
-      <c r="B360" s="17"/>
+      <c r="A360" s="18"/>
+      <c r="B360" s="18"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="17"/>
-      <c r="B361" s="17"/>
+      <c r="A361" s="18"/>
+      <c r="B361" s="18"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="17"/>
-      <c r="B362" s="17"/>
+      <c r="A362" s="18"/>
+      <c r="B362" s="18"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="17"/>
-      <c r="B363" s="17"/>
+      <c r="A363" s="18"/>
+      <c r="B363" s="18"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="17"/>
-      <c r="B364" s="17"/>
+      <c r="A364" s="18"/>
+      <c r="B364" s="18"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="17"/>
-      <c r="B365" s="17"/>
+      <c r="A365" s="18"/>
+      <c r="B365" s="18"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="17"/>
-      <c r="B366" s="17"/>
+      <c r="A366" s="18"/>
+      <c r="B366" s="18"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="17"/>
-      <c r="B367" s="17"/>
+      <c r="A367" s="18"/>
+      <c r="B367" s="18"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="17"/>
-      <c r="B368" s="17"/>
+      <c r="A368" s="18"/>
+      <c r="B368" s="18"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="17"/>
-      <c r="B369" s="17"/>
+      <c r="A369" s="18"/>
+      <c r="B369" s="18"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="17"/>
-      <c r="B370" s="17"/>
+      <c r="A370" s="18"/>
+      <c r="B370" s="18"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="17"/>
-      <c r="B371" s="17"/>
+      <c r="A371" s="18"/>
+      <c r="B371" s="18"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="17"/>
-      <c r="B372" s="17"/>
+      <c r="A372" s="18"/>
+      <c r="B372" s="18"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="17"/>
-      <c r="B373" s="17"/>
+      <c r="A373" s="18"/>
+      <c r="B373" s="18"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="17"/>
-      <c r="B374" s="17"/>
+      <c r="A374" s="18"/>
+      <c r="B374" s="18"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="17"/>
-      <c r="B375" s="17"/>
+      <c r="A375" s="18"/>
+      <c r="B375" s="18"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="17"/>
-      <c r="B376" s="17"/>
+      <c r="A376" s="18"/>
+      <c r="B376" s="18"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="17"/>
-      <c r="B377" s="17"/>
+      <c r="A377" s="18"/>
+      <c r="B377" s="18"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="17"/>
-      <c r="B378" s="17"/>
+      <c r="A378" s="18"/>
+      <c r="B378" s="18"/>
     </row>
     <row r="379" ht="15.75" customHeight="1">
-      <c r="A379" s="17"/>
-      <c r="B379" s="17"/>
+      <c r="A379" s="18"/>
+      <c r="B379" s="18"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="17"/>
-      <c r="B380" s="17"/>
+      <c r="A380" s="18"/>
+      <c r="B380" s="18"/>
     </row>
     <row r="381" ht="15.75" customHeight="1">
-      <c r="A381" s="17"/>
-      <c r="B381" s="17"/>
+      <c r="A381" s="18"/>
+      <c r="B381" s="18"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="17"/>
-      <c r="B382" s="17"/>
+      <c r="A382" s="18"/>
+      <c r="B382" s="18"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="17"/>
-      <c r="B383" s="17"/>
+      <c r="A383" s="18"/>
+      <c r="B383" s="18"/>
     </row>
     <row r="384" ht="15.75" customHeight="1">
-      <c r="A384" s="17"/>
-      <c r="B384" s="17"/>
+      <c r="A384" s="18"/>
+      <c r="B384" s="18"/>
     </row>
     <row r="385" ht="15.75" customHeight="1">
-      <c r="A385" s="17"/>
-      <c r="B385" s="17"/>
+      <c r="A385" s="18"/>
+      <c r="B385" s="18"/>
     </row>
     <row r="386" ht="15.75" customHeight="1">
-      <c r="A386" s="17"/>
-      <c r="B386" s="17"/>
+      <c r="A386" s="18"/>
+      <c r="B386" s="18"/>
     </row>
     <row r="387" ht="15.75" customHeight="1">
-      <c r="A387" s="17"/>
-      <c r="B387" s="17"/>
+      <c r="A387" s="18"/>
+      <c r="B387" s="18"/>
     </row>
     <row r="388" ht="15.75" customHeight="1">
-      <c r="A388" s="17"/>
-      <c r="B388" s="17"/>
+      <c r="A388" s="18"/>
+      <c r="B388" s="18"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="17"/>
-      <c r="B389" s="17"/>
+      <c r="A389" s="18"/>
+      <c r="B389" s="18"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="17"/>
-      <c r="B390" s="17"/>
+      <c r="A390" s="18"/>
+      <c r="B390" s="18"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="17"/>
-      <c r="B391" s="17"/>
+      <c r="A391" s="18"/>
+      <c r="B391" s="18"/>
     </row>
     <row r="392" ht="15.75" customHeight="1">
-      <c r="A392" s="17"/>
-      <c r="B392" s="17"/>
+      <c r="A392" s="18"/>
+      <c r="B392" s="18"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="17"/>
-      <c r="B393" s="17"/>
+      <c r="A393" s="18"/>
+      <c r="B393" s="18"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="17"/>
-      <c r="B394" s="17"/>
+      <c r="A394" s="18"/>
+      <c r="B394" s="18"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="17"/>
-      <c r="B395" s="17"/>
+      <c r="A395" s="18"/>
+      <c r="B395" s="18"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="17"/>
-      <c r="B396" s="17"/>
+      <c r="A396" s="18"/>
+      <c r="B396" s="18"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="17"/>
-      <c r="B397" s="17"/>
+      <c r="A397" s="18"/>
+      <c r="B397" s="18"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="17"/>
-      <c r="B398" s="17"/>
+      <c r="A398" s="18"/>
+      <c r="B398" s="18"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="17"/>
-      <c r="B399" s="17"/>
+      <c r="A399" s="18"/>
+      <c r="B399" s="18"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="17"/>
-      <c r="B400" s="17"/>
+      <c r="A400" s="18"/>
+      <c r="B400" s="18"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="17"/>
-      <c r="B401" s="17"/>
+      <c r="A401" s="18"/>
+      <c r="B401" s="18"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="17"/>
-      <c r="B402" s="17"/>
+      <c r="A402" s="18"/>
+      <c r="B402" s="18"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="17"/>
-      <c r="B403" s="17"/>
+      <c r="A403" s="18"/>
+      <c r="B403" s="18"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="17"/>
-      <c r="B404" s="17"/>
+      <c r="A404" s="18"/>
+      <c r="B404" s="18"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="17"/>
-      <c r="B405" s="17"/>
+      <c r="A405" s="18"/>
+      <c r="B405" s="18"/>
     </row>
     <row r="406" ht="15.75" customHeight="1">
-      <c r="A406" s="17"/>
-      <c r="B406" s="17"/>
+      <c r="A406" s="18"/>
+      <c r="B406" s="18"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="17"/>
-      <c r="B407" s="17"/>
+      <c r="A407" s="18"/>
+      <c r="B407" s="18"/>
     </row>
     <row r="408" ht="15.75" customHeight="1">
-      <c r="A408" s="17"/>
-      <c r="B408" s="17"/>
+      <c r="A408" s="18"/>
+      <c r="B408" s="18"/>
     </row>
     <row r="409" ht="15.75" customHeight="1">
-      <c r="A409" s="17"/>
-      <c r="B409" s="17"/>
+      <c r="A409" s="18"/>
+      <c r="B409" s="18"/>
     </row>
     <row r="410" ht="15.75" customHeight="1">
-      <c r="A410" s="17"/>
-      <c r="B410" s="17"/>
+      <c r="A410" s="18"/>
+      <c r="B410" s="18"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="17"/>
-      <c r="B411" s="17"/>
+      <c r="A411" s="18"/>
+      <c r="B411" s="18"/>
     </row>
     <row r="412" ht="15.75" customHeight="1">
-      <c r="A412" s="17"/>
-      <c r="B412" s="17"/>
+      <c r="A412" s="18"/>
+      <c r="B412" s="18"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="17"/>
-      <c r="B413" s="17"/>
+      <c r="A413" s="18"/>
+      <c r="B413" s="18"/>
     </row>
     <row r="414" ht="15.75" customHeight="1">
-      <c r="A414" s="17"/>
-      <c r="B414" s="17"/>
+      <c r="A414" s="18"/>
+      <c r="B414" s="18"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="17"/>
-      <c r="B415" s="17"/>
+      <c r="A415" s="18"/>
+      <c r="B415" s="18"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="17"/>
-      <c r="B416" s="17"/>
+      <c r="A416" s="18"/>
+      <c r="B416" s="18"/>
     </row>
     <row r="417" ht="15.75" customHeight="1">
-      <c r="A417" s="17"/>
-      <c r="B417" s="17"/>
+      <c r="A417" s="18"/>
+      <c r="B417" s="18"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="17"/>
-      <c r="B418" s="17"/>
+      <c r="A418" s="18"/>
+      <c r="B418" s="18"/>
     </row>
     <row r="419" ht="15.75" customHeight="1">
-      <c r="A419" s="17"/>
-      <c r="B419" s="17"/>
+      <c r="A419" s="18"/>
+      <c r="B419" s="18"/>
     </row>
     <row r="420" ht="15.75" customHeight="1">
-      <c r="A420" s="17"/>
-      <c r="B420" s="17"/>
+      <c r="A420" s="18"/>
+      <c r="B420" s="18"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="17"/>
-      <c r="B421" s="17"/>
+      <c r="A421" s="18"/>
+      <c r="B421" s="18"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="17"/>
-      <c r="B422" s="17"/>
+      <c r="A422" s="18"/>
+      <c r="B422" s="18"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="17"/>
-      <c r="B423" s="17"/>
+      <c r="A423" s="18"/>
+      <c r="B423" s="18"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="17"/>
-      <c r="B424" s="17"/>
+      <c r="A424" s="18"/>
+      <c r="B424" s="18"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="17"/>
-      <c r="B425" s="17"/>
+      <c r="A425" s="18"/>
+      <c r="B425" s="18"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="17"/>
-      <c r="B426" s="17"/>
+      <c r="A426" s="18"/>
+      <c r="B426" s="18"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="17"/>
-      <c r="B427" s="17"/>
+      <c r="A427" s="18"/>
+      <c r="B427" s="18"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="17"/>
-      <c r="B428" s="17"/>
+      <c r="A428" s="18"/>
+      <c r="B428" s="18"/>
     </row>
     <row r="429" ht="15.75" customHeight="1">
-      <c r="A429" s="17"/>
-      <c r="B429" s="17"/>
+      <c r="A429" s="18"/>
+      <c r="B429" s="18"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="17"/>
-      <c r="B430" s="17"/>
+      <c r="A430" s="18"/>
+      <c r="B430" s="18"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="17"/>
-      <c r="B431" s="17"/>
+      <c r="A431" s="18"/>
+      <c r="B431" s="18"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="17"/>
-      <c r="B432" s="17"/>
+      <c r="A432" s="18"/>
+      <c r="B432" s="18"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="17"/>
-      <c r="B433" s="17"/>
+      <c r="A433" s="18"/>
+      <c r="B433" s="18"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="17"/>
-      <c r="B434" s="17"/>
+      <c r="A434" s="18"/>
+      <c r="B434" s="18"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="17"/>
-      <c r="B435" s="17"/>
+      <c r="A435" s="18"/>
+      <c r="B435" s="18"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="17"/>
-      <c r="B436" s="17"/>
+      <c r="A436" s="18"/>
+      <c r="B436" s="18"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="17"/>
-      <c r="B437" s="17"/>
+      <c r="A437" s="18"/>
+      <c r="B437" s="18"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="17"/>
-      <c r="B438" s="17"/>
+      <c r="A438" s="18"/>
+      <c r="B438" s="18"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="17"/>
-      <c r="B439" s="17"/>
+      <c r="A439" s="18"/>
+      <c r="B439" s="18"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="17"/>
-      <c r="B440" s="17"/>
+      <c r="A440" s="18"/>
+      <c r="B440" s="18"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="17"/>
-      <c r="B441" s="17"/>
+      <c r="A441" s="18"/>
+      <c r="B441" s="18"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="17"/>
-      <c r="B442" s="17"/>
+      <c r="A442" s="18"/>
+      <c r="B442" s="18"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="17"/>
-      <c r="B443" s="17"/>
+      <c r="A443" s="18"/>
+      <c r="B443" s="18"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="17"/>
-      <c r="B444" s="17"/>
+      <c r="A444" s="18"/>
+      <c r="B444" s="18"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="17"/>
-      <c r="B445" s="17"/>
+      <c r="A445" s="18"/>
+      <c r="B445" s="18"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="17"/>
-      <c r="B446" s="17"/>
+      <c r="A446" s="18"/>
+      <c r="B446" s="18"/>
     </row>
     <row r="447" ht="15.75" customHeight="1">
-      <c r="A447" s="17"/>
-      <c r="B447" s="17"/>
+      <c r="A447" s="18"/>
+      <c r="B447" s="18"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="17"/>
-      <c r="B448" s="17"/>
+      <c r="A448" s="18"/>
+      <c r="B448" s="18"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="17"/>
-      <c r="B449" s="17"/>
+      <c r="A449" s="18"/>
+      <c r="B449" s="18"/>
     </row>
     <row r="450" ht="15.75" customHeight="1">
-      <c r="A450" s="17"/>
-      <c r="B450" s="17"/>
+      <c r="A450" s="18"/>
+      <c r="B450" s="18"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="17"/>
-      <c r="B451" s="17"/>
+      <c r="A451" s="18"/>
+      <c r="B451" s="18"/>
     </row>
     <row r="452" ht="15.75" customHeight="1">
-      <c r="A452" s="17"/>
-      <c r="B452" s="17"/>
+      <c r="A452" s="18"/>
+      <c r="B452" s="18"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="17"/>
-      <c r="B453" s="17"/>
+      <c r="A453" s="18"/>
+      <c r="B453" s="18"/>
     </row>
     <row r="454" ht="15.75" customHeight="1">
-      <c r="A454" s="17"/>
-      <c r="B454" s="17"/>
+      <c r="A454" s="18"/>
+      <c r="B454" s="18"/>
     </row>
     <row r="455" ht="15.75" customHeight="1">
-      <c r="A455" s="17"/>
-      <c r="B455" s="17"/>
+      <c r="A455" s="18"/>
+      <c r="B455" s="18"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="17"/>
-      <c r="B456" s="17"/>
+      <c r="A456" s="18"/>
+      <c r="B456" s="18"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="17"/>
-      <c r="B457" s="17"/>
+      <c r="A457" s="18"/>
+      <c r="B457" s="18"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="17"/>
-      <c r="B458" s="17"/>
+      <c r="A458" s="18"/>
+      <c r="B458" s="18"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="17"/>
-      <c r="B459" s="17"/>
+      <c r="A459" s="18"/>
+      <c r="B459" s="18"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="17"/>
-      <c r="B460" s="17"/>
+      <c r="A460" s="18"/>
+      <c r="B460" s="18"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="17"/>
-      <c r="B461" s="17"/>
+      <c r="A461" s="18"/>
+      <c r="B461" s="18"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="17"/>
-      <c r="B462" s="17"/>
+      <c r="A462" s="18"/>
+      <c r="B462" s="18"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="17"/>
-      <c r="B463" s="17"/>
+      <c r="A463" s="18"/>
+      <c r="B463" s="18"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="17"/>
-      <c r="B464" s="17"/>
+      <c r="A464" s="18"/>
+      <c r="B464" s="18"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="17"/>
-      <c r="B465" s="17"/>
+      <c r="A465" s="18"/>
+      <c r="B465" s="18"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="17"/>
-      <c r="B466" s="17"/>
+      <c r="A466" s="18"/>
+      <c r="B466" s="18"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="17"/>
-      <c r="B467" s="17"/>
+      <c r="A467" s="18"/>
+      <c r="B467" s="18"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="17"/>
-      <c r="B468" s="17"/>
+      <c r="A468" s="18"/>
+      <c r="B468" s="18"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="17"/>
-      <c r="B469" s="17"/>
+      <c r="A469" s="18"/>
+      <c r="B469" s="18"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="17"/>
-      <c r="B470" s="17"/>
+      <c r="A470" s="18"/>
+      <c r="B470" s="18"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="17"/>
-      <c r="B471" s="17"/>
+      <c r="A471" s="18"/>
+      <c r="B471" s="18"/>
     </row>
     <row r="472" ht="15.75" customHeight="1">
-      <c r="A472" s="17"/>
-      <c r="B472" s="17"/>
+      <c r="A472" s="18"/>
+      <c r="B472" s="18"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="17"/>
-      <c r="B473" s="17"/>
+      <c r="A473" s="18"/>
+      <c r="B473" s="18"/>
     </row>
     <row r="474" ht="15.75" customHeight="1">
-      <c r="A474" s="17"/>
-      <c r="B474" s="17"/>
+      <c r="A474" s="18"/>
+      <c r="B474" s="18"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="17"/>
-      <c r="B475" s="17"/>
+      <c r="A475" s="18"/>
+      <c r="B475" s="18"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="17"/>
-      <c r="B476" s="17"/>
+      <c r="A476" s="18"/>
+      <c r="B476" s="18"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="17"/>
-      <c r="B477" s="17"/>
+      <c r="A477" s="18"/>
+      <c r="B477" s="18"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="17"/>
-      <c r="B478" s="17"/>
+      <c r="A478" s="18"/>
+      <c r="B478" s="18"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="17"/>
-      <c r="B479" s="17"/>
+      <c r="A479" s="18"/>
+      <c r="B479" s="18"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="17"/>
-      <c r="B480" s="17"/>
+      <c r="A480" s="18"/>
+      <c r="B480" s="18"/>
     </row>
     <row r="481" ht="15.75" customHeight="1">
-      <c r="A481" s="17"/>
-      <c r="B481" s="17"/>
+      <c r="A481" s="18"/>
+      <c r="B481" s="18"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="17"/>
-      <c r="B482" s="17"/>
+      <c r="A482" s="18"/>
+      <c r="B482" s="18"/>
     </row>
     <row r="483" ht="15.75" customHeight="1">
-      <c r="A483" s="17"/>
-      <c r="B483" s="17"/>
+      <c r="A483" s="18"/>
+      <c r="B483" s="18"/>
     </row>
     <row r="484" ht="15.75" customHeight="1">
-      <c r="A484" s="17"/>
-      <c r="B484" s="17"/>
+      <c r="A484" s="18"/>
+      <c r="B484" s="18"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="17"/>
-      <c r="B485" s="17"/>
+      <c r="A485" s="18"/>
+      <c r="B485" s="18"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="17"/>
-      <c r="B486" s="17"/>
+      <c r="A486" s="18"/>
+      <c r="B486" s="18"/>
     </row>
     <row r="487" ht="15.75" customHeight="1">
-      <c r="A487" s="17"/>
-      <c r="B487" s="17"/>
+      <c r="A487" s="18"/>
+      <c r="B487" s="18"/>
     </row>
     <row r="488" ht="15.75" customHeight="1">
-      <c r="A488" s="17"/>
-      <c r="B488" s="17"/>
+      <c r="A488" s="18"/>
+      <c r="B488" s="18"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="17"/>
-      <c r="B489" s="17"/>
+      <c r="A489" s="18"/>
+      <c r="B489" s="18"/>
     </row>
     <row r="490" ht="15.75" customHeight="1">
-      <c r="A490" s="17"/>
-      <c r="B490" s="17"/>
+      <c r="A490" s="18"/>
+      <c r="B490" s="18"/>
     </row>
     <row r="491" ht="15.75" customHeight="1">
-      <c r="A491" s="17"/>
-      <c r="B491" s="17"/>
+      <c r="A491" s="18"/>
+      <c r="B491" s="18"/>
     </row>
     <row r="492" ht="15.75" customHeight="1">
-      <c r="A492" s="17"/>
-      <c r="B492" s="17"/>
+      <c r="A492" s="18"/>
+      <c r="B492" s="18"/>
     </row>
     <row r="493" ht="15.75" customHeight="1">
-      <c r="A493" s="17"/>
-      <c r="B493" s="17"/>
+      <c r="A493" s="18"/>
+      <c r="B493" s="18"/>
     </row>
     <row r="494" ht="15.75" customHeight="1">
-      <c r="A494" s="17"/>
-      <c r="B494" s="17"/>
+      <c r="A494" s="18"/>
+      <c r="B494" s="18"/>
     </row>
     <row r="495" ht="15.75" customHeight="1">
-      <c r="A495" s="17"/>
-      <c r="B495" s="17"/>
+      <c r="A495" s="18"/>
+      <c r="B495" s="18"/>
     </row>
     <row r="496" ht="15.75" customHeight="1">
-      <c r="A496" s="17"/>
-      <c r="B496" s="17"/>
+      <c r="A496" s="18"/>
+      <c r="B496" s="18"/>
     </row>
     <row r="497" ht="15.75" customHeight="1">
-      <c r="A497" s="17"/>
-      <c r="B497" s="17"/>
+      <c r="A497" s="18"/>
+      <c r="B497" s="18"/>
     </row>
     <row r="498" ht="15.75" customHeight="1">
-      <c r="A498" s="17"/>
-      <c r="B498" s="17"/>
+      <c r="A498" s="18"/>
+      <c r="B498" s="18"/>
     </row>
     <row r="499" ht="15.75" customHeight="1">
-      <c r="A499" s="17"/>
-      <c r="B499" s="17"/>
+      <c r="A499" s="18"/>
+      <c r="B499" s="18"/>
     </row>
     <row r="500" ht="15.75" customHeight="1">
-      <c r="A500" s="17"/>
-      <c r="B500" s="17"/>
+      <c r="A500" s="18"/>
+      <c r="B500" s="18"/>
     </row>
     <row r="501" ht="15.75" customHeight="1">
-      <c r="A501" s="17"/>
-      <c r="B501" s="17"/>
+      <c r="A501" s="18"/>
+      <c r="B501" s="18"/>
     </row>
     <row r="502" ht="15.75" customHeight="1">
-      <c r="A502" s="17"/>
-      <c r="B502" s="17"/>
+      <c r="A502" s="18"/>
+      <c r="B502" s="18"/>
     </row>
     <row r="503" ht="15.75" customHeight="1">
-      <c r="A503" s="17"/>
-      <c r="B503" s="17"/>
+      <c r="A503" s="18"/>
+      <c r="B503" s="18"/>
     </row>
     <row r="504" ht="15.75" customHeight="1">
-      <c r="A504" s="17"/>
-      <c r="B504" s="17"/>
+      <c r="A504" s="18"/>
+      <c r="B504" s="18"/>
     </row>
     <row r="505" ht="15.75" customHeight="1">
-      <c r="A505" s="17"/>
-      <c r="B505" s="17"/>
+      <c r="A505" s="18"/>
+      <c r="B505" s="18"/>
     </row>
     <row r="506" ht="15.75" customHeight="1">
-      <c r="A506" s="17"/>
-      <c r="B506" s="17"/>
+      <c r="A506" s="18"/>
+      <c r="B506" s="18"/>
     </row>
     <row r="507" ht="15.75" customHeight="1">
-      <c r="A507" s="17"/>
-      <c r="B507" s="17"/>
+      <c r="A507" s="18"/>
+      <c r="B507" s="18"/>
     </row>
     <row r="508" ht="15.75" customHeight="1">
-      <c r="A508" s="17"/>
-      <c r="B508" s="17"/>
+      <c r="A508" s="18"/>
+      <c r="B508" s="18"/>
     </row>
     <row r="509" ht="15.75" customHeight="1">
-      <c r="A509" s="17"/>
-      <c r="B509" s="17"/>
+      <c r="A509" s="18"/>
+      <c r="B509" s="18"/>
     </row>
     <row r="510" ht="15.75" customHeight="1">
-      <c r="A510" s="17"/>
-      <c r="B510" s="17"/>
+      <c r="A510" s="18"/>
+      <c r="B510" s="18"/>
     </row>
     <row r="511" ht="15.75" customHeight="1">
-      <c r="A511" s="17"/>
-      <c r="B511" s="17"/>
+      <c r="A511" s="18"/>
+      <c r="B511" s="18"/>
     </row>
     <row r="512" ht="15.75" customHeight="1">
-      <c r="A512" s="17"/>
-      <c r="B512" s="17"/>
+      <c r="A512" s="18"/>
+      <c r="B512" s="18"/>
     </row>
     <row r="513" ht="15.75" customHeight="1">
-      <c r="A513" s="17"/>
-      <c r="B513" s="17"/>
+      <c r="A513" s="18"/>
+      <c r="B513" s="18"/>
     </row>
     <row r="514" ht="15.75" customHeight="1">
-      <c r="A514" s="17"/>
-      <c r="B514" s="17"/>
+      <c r="A514" s="18"/>
+      <c r="B514" s="18"/>
     </row>
     <row r="515" ht="15.75" customHeight="1">
-      <c r="A515" s="17"/>
-      <c r="B515" s="17"/>
+      <c r="A515" s="18"/>
+      <c r="B515" s="18"/>
     </row>
     <row r="516" ht="15.75" customHeight="1">
-      <c r="A516" s="17"/>
-      <c r="B516" s="17"/>
+      <c r="A516" s="18"/>
+      <c r="B516" s="18"/>
     </row>
     <row r="517" ht="15.75" customHeight="1">
-      <c r="A517" s="17"/>
-      <c r="B517" s="17"/>
+      <c r="A517" s="18"/>
+      <c r="B517" s="18"/>
     </row>
     <row r="518" ht="15.75" customHeight="1">
-      <c r="A518" s="17"/>
-      <c r="B518" s="17"/>
+      <c r="A518" s="18"/>
+      <c r="B518" s="18"/>
     </row>
     <row r="519" ht="15.75" customHeight="1">
-      <c r="A519" s="17"/>
-      <c r="B519" s="17"/>
+      <c r="A519" s="18"/>
+      <c r="B519" s="18"/>
     </row>
     <row r="520" ht="15.75" customHeight="1">
-      <c r="A520" s="17"/>
-      <c r="B520" s="17"/>
+      <c r="A520" s="18"/>
+      <c r="B520" s="18"/>
     </row>
     <row r="521" ht="15.75" customHeight="1">
-      <c r="A521" s="17"/>
-      <c r="B521" s="17"/>
+      <c r="A521" s="18"/>
+      <c r="B521" s="18"/>
     </row>
     <row r="522" ht="15.75" customHeight="1">
-      <c r="A522" s="17"/>
-      <c r="B522" s="17"/>
+      <c r="A522" s="18"/>
+      <c r="B522" s="18"/>
     </row>
     <row r="523" ht="15.75" customHeight="1">
-      <c r="A523" s="17"/>
-      <c r="B523" s="17"/>
+      <c r="A523" s="18"/>
+      <c r="B523" s="18"/>
     </row>
     <row r="524" ht="15.75" customHeight="1">
-      <c r="A524" s="17"/>
-      <c r="B524" s="17"/>
+      <c r="A524" s="18"/>
+      <c r="B524" s="18"/>
     </row>
     <row r="525" ht="15.75" customHeight="1">
-      <c r="A525" s="17"/>
-      <c r="B525" s="17"/>
+      <c r="A525" s="18"/>
+      <c r="B525" s="18"/>
     </row>
     <row r="526" ht="15.75" customHeight="1">
-      <c r="A526" s="17"/>
-      <c r="B526" s="17"/>
+      <c r="A526" s="18"/>
+      <c r="B526" s="18"/>
     </row>
     <row r="527" ht="15.75" customHeight="1">
-      <c r="A527" s="17"/>
-      <c r="B527" s="17"/>
+      <c r="A527" s="18"/>
+      <c r="B527" s="18"/>
     </row>
     <row r="528" ht="15.75" customHeight="1">
-      <c r="A528" s="17"/>
-      <c r="B528" s="17"/>
+      <c r="A528" s="18"/>
+      <c r="B528" s="18"/>
     </row>
     <row r="529" ht="15.75" customHeight="1">
-      <c r="A529" s="17"/>
-      <c r="B529" s="17"/>
+      <c r="A529" s="18"/>
+      <c r="B529" s="18"/>
     </row>
     <row r="530" ht="15.75" customHeight="1">
-      <c r="A530" s="17"/>
-      <c r="B530" s="17"/>
+      <c r="A530" s="18"/>
+      <c r="B530" s="18"/>
     </row>
     <row r="531" ht="15.75" customHeight="1">
-      <c r="A531" s="17"/>
-      <c r="B531" s="17"/>
+      <c r="A531" s="18"/>
+      <c r="B531" s="18"/>
     </row>
     <row r="532" ht="15.75" customHeight="1">
-      <c r="A532" s="17"/>
-      <c r="B532" s="17"/>
+      <c r="A532" s="18"/>
+      <c r="B532" s="18"/>
     </row>
     <row r="533" ht="15.75" customHeight="1">
-      <c r="A533" s="17"/>
-      <c r="B533" s="17"/>
+      <c r="A533" s="18"/>
+      <c r="B533" s="18"/>
     </row>
     <row r="534" ht="15.75" customHeight="1">
-      <c r="A534" s="17"/>
-      <c r="B534" s="17"/>
+      <c r="A534" s="18"/>
+      <c r="B534" s="18"/>
     </row>
     <row r="535" ht="15.75" customHeight="1">
-      <c r="A535" s="17"/>
-      <c r="B535" s="17"/>
+      <c r="A535" s="18"/>
+      <c r="B535" s="18"/>
     </row>
     <row r="536" ht="15.75" customHeight="1">
-      <c r="A536" s="17"/>
-      <c r="B536" s="17"/>
+      <c r="A536" s="18"/>
+      <c r="B536" s="18"/>
     </row>
     <row r="537" ht="15.75" customHeight="1">
-      <c r="A537" s="17"/>
-      <c r="B537" s="17"/>
+      <c r="A537" s="18"/>
+      <c r="B537" s="18"/>
     </row>
     <row r="538" ht="15.75" customHeight="1">
-      <c r="A538" s="17"/>
-      <c r="B538" s="17"/>
+      <c r="A538" s="18"/>
+      <c r="B538" s="18"/>
     </row>
     <row r="539" ht="15.75" customHeight="1">
-      <c r="A539" s="17"/>
-      <c r="B539" s="17"/>
+      <c r="A539" s="18"/>
+      <c r="B539" s="18"/>
     </row>
     <row r="540" ht="15.75" customHeight="1">
-      <c r="A540" s="17"/>
-      <c r="B540" s="17"/>
+      <c r="A540" s="18"/>
+      <c r="B540" s="18"/>
     </row>
     <row r="541" ht="15.75" customHeight="1">
-      <c r="A541" s="17"/>
-      <c r="B541" s="17"/>
+      <c r="A541" s="18"/>
+      <c r="B541" s="18"/>
     </row>
     <row r="542" ht="15.75" customHeight="1">
-      <c r="A542" s="17"/>
-      <c r="B542" s="17"/>
+      <c r="A542" s="18"/>
+      <c r="B542" s="18"/>
     </row>
     <row r="543" ht="15.75" customHeight="1">
-      <c r="A543" s="17"/>
-      <c r="B543" s="17"/>
+      <c r="A543" s="18"/>
+      <c r="B543" s="18"/>
     </row>
     <row r="544" ht="15.75" customHeight="1">
-      <c r="A544" s="17"/>
-      <c r="B544" s="17"/>
+      <c r="A544" s="18"/>
+      <c r="B544" s="18"/>
     </row>
     <row r="545" ht="15.75" customHeight="1">
-      <c r="A545" s="17"/>
-      <c r="B545" s="17"/>
+      <c r="A545" s="18"/>
+      <c r="B545" s="18"/>
     </row>
     <row r="546" ht="15.75" customHeight="1">
-      <c r="A546" s="17"/>
-      <c r="B546" s="17"/>
+      <c r="A546" s="18"/>
+      <c r="B546" s="18"/>
     </row>
     <row r="547" ht="15.75" customHeight="1">
-      <c r="A547" s="17"/>
-      <c r="B547" s="17"/>
+      <c r="A547" s="18"/>
+      <c r="B547" s="18"/>
     </row>
     <row r="548" ht="15.75" customHeight="1">
-      <c r="A548" s="17"/>
-      <c r="B548" s="17"/>
+      <c r="A548" s="18"/>
+      <c r="B548" s="18"/>
     </row>
     <row r="549" ht="15.75" customHeight="1">
-      <c r="A549" s="17"/>
-      <c r="B549" s="17"/>
+      <c r="A549" s="18"/>
+      <c r="B549" s="18"/>
     </row>
     <row r="550" ht="15.75" customHeight="1">
-      <c r="A550" s="17"/>
-      <c r="B550" s="17"/>
+      <c r="A550" s="18"/>
+      <c r="B550" s="18"/>
     </row>
     <row r="551" ht="15.75" customHeight="1">
-      <c r="A551" s="17"/>
-      <c r="B551" s="17"/>
+      <c r="A551" s="18"/>
+      <c r="B551" s="18"/>
     </row>
     <row r="552" ht="15.75" customHeight="1">
-      <c r="A552" s="17"/>
-      <c r="B552" s="17"/>
+      <c r="A552" s="18"/>
+      <c r="B552" s="18"/>
     </row>
     <row r="553" ht="15.75" customHeight="1">
-      <c r="A553" s="17"/>
-      <c r="B553" s="17"/>
+      <c r="A553" s="18"/>
+      <c r="B553" s="18"/>
     </row>
     <row r="554" ht="15.75" customHeight="1">
-      <c r="A554" s="17"/>
-      <c r="B554" s="17"/>
+      <c r="A554" s="18"/>
+      <c r="B554" s="18"/>
     </row>
     <row r="555" ht="15.75" customHeight="1">
-      <c r="A555" s="17"/>
-      <c r="B555" s="17"/>
+      <c r="A555" s="18"/>
+      <c r="B555" s="18"/>
     </row>
     <row r="556" ht="15.75" customHeight="1">
-      <c r="A556" s="17"/>
-      <c r="B556" s="17"/>
+      <c r="A556" s="18"/>
+      <c r="B556" s="18"/>
     </row>
     <row r="557" ht="15.75" customHeight="1">
-      <c r="A557" s="17"/>
-      <c r="B557" s="17"/>
+      <c r="A557" s="18"/>
+      <c r="B557" s="18"/>
     </row>
     <row r="558" ht="15.75" customHeight="1">
-      <c r="A558" s="17"/>
-      <c r="B558" s="17"/>
+      <c r="A558" s="18"/>
+      <c r="B558" s="18"/>
     </row>
     <row r="559" ht="15.75" customHeight="1">
-      <c r="A559" s="17"/>
-      <c r="B559" s="17"/>
+      <c r="A559" s="18"/>
+      <c r="B559" s="18"/>
     </row>
     <row r="560" ht="15.75" customHeight="1">
-      <c r="A560" s="17"/>
-      <c r="B560" s="17"/>
+      <c r="A560" s="18"/>
+      <c r="B560" s="18"/>
     </row>
     <row r="561" ht="15.75" customHeight="1">
-      <c r="A561" s="17"/>
-      <c r="B561" s="17"/>
+      <c r="A561" s="18"/>
+      <c r="B561" s="18"/>
     </row>
     <row r="562" ht="15.75" customHeight="1">
-      <c r="A562" s="17"/>
-      <c r="B562" s="17"/>
+      <c r="A562" s="18"/>
+      <c r="B562" s="18"/>
     </row>
     <row r="563" ht="15.75" customHeight="1">
-      <c r="A563" s="17"/>
-      <c r="B563" s="17"/>
+      <c r="A563" s="18"/>
+      <c r="B563" s="18"/>
     </row>
     <row r="564" ht="15.75" customHeight="1">
-      <c r="A564" s="17"/>
-      <c r="B564" s="17"/>
+      <c r="A564" s="18"/>
+      <c r="B564" s="18"/>
     </row>
     <row r="565" ht="15.75" customHeight="1">
-      <c r="A565" s="17"/>
-      <c r="B565" s="17"/>
+      <c r="A565" s="18"/>
+      <c r="B565" s="18"/>
     </row>
     <row r="566" ht="15.75" customHeight="1">
-      <c r="A566" s="17"/>
-      <c r="B566" s="17"/>
+      <c r="A566" s="18"/>
+      <c r="B566" s="18"/>
     </row>
     <row r="567" ht="15.75" customHeight="1">
-      <c r="A567" s="17"/>
-      <c r="B567" s="17"/>
+      <c r="A567" s="18"/>
+      <c r="B567" s="18"/>
     </row>
     <row r="568" ht="15.75" customHeight="1">
-      <c r="A568" s="17"/>
-      <c r="B568" s="17"/>
+      <c r="A568" s="18"/>
+      <c r="B568" s="18"/>
     </row>
     <row r="569" ht="15.75" customHeight="1">
-      <c r="A569" s="17"/>
-      <c r="B569" s="17"/>
+      <c r="A569" s="18"/>
+      <c r="B569" s="18"/>
     </row>
     <row r="570" ht="15.75" customHeight="1">
-      <c r="A570" s="17"/>
-      <c r="B570" s="17"/>
+      <c r="A570" s="18"/>
+      <c r="B570" s="18"/>
     </row>
     <row r="571" ht="15.75" customHeight="1">
-      <c r="A571" s="17"/>
-      <c r="B571" s="17"/>
+      <c r="A571" s="18"/>
+      <c r="B571" s="18"/>
     </row>
     <row r="572" ht="15.75" customHeight="1">
-      <c r="A572" s="17"/>
-      <c r="B572" s="17"/>
+      <c r="A572" s="18"/>
+      <c r="B572" s="18"/>
     </row>
     <row r="573" ht="15.75" customHeight="1">
-      <c r="A573" s="17"/>
-      <c r="B573" s="17"/>
+      <c r="A573" s="18"/>
+      <c r="B573" s="18"/>
     </row>
     <row r="574" ht="15.75" customHeight="1">
-      <c r="A574" s="17"/>
-      <c r="B574" s="17"/>
+      <c r="A574" s="18"/>
+      <c r="B574" s="18"/>
     </row>
     <row r="575" ht="15.75" customHeight="1">
-      <c r="A575" s="17"/>
-      <c r="B575" s="17"/>
+      <c r="A575" s="18"/>
+      <c r="B575" s="18"/>
     </row>
     <row r="576" ht="15.75" customHeight="1">
-      <c r="A576" s="17"/>
-      <c r="B576" s="17"/>
+      <c r="A576" s="18"/>
+      <c r="B576" s="18"/>
     </row>
     <row r="577" ht="15.75" customHeight="1">
-      <c r="A577" s="17"/>
-      <c r="B577" s="17"/>
+      <c r="A577" s="18"/>
+      <c r="B577" s="18"/>
     </row>
     <row r="578" ht="15.75" customHeight="1">
-      <c r="A578" s="17"/>
-      <c r="B578" s="17"/>
+      <c r="A578" s="18"/>
+      <c r="B578" s="18"/>
     </row>
     <row r="579" ht="15.75" customHeight="1">
-      <c r="A579" s="17"/>
-      <c r="B579" s="17"/>
+      <c r="A579" s="18"/>
+      <c r="B579" s="18"/>
     </row>
     <row r="580" ht="15.75" customHeight="1">
-      <c r="A580" s="17"/>
-      <c r="B580" s="17"/>
+      <c r="A580" s="18"/>
+      <c r="B580" s="18"/>
     </row>
     <row r="581" ht="15.75" customHeight="1">
-      <c r="A581" s="17"/>
-      <c r="B581" s="17"/>
+      <c r="A581" s="18"/>
+      <c r="B581" s="18"/>
     </row>
     <row r="582" ht="15.75" customHeight="1">
-      <c r="A582" s="17"/>
-      <c r="B582" s="17"/>
+      <c r="A582" s="18"/>
+      <c r="B582" s="18"/>
     </row>
     <row r="583" ht="15.75" customHeight="1">
-      <c r="A583" s="17"/>
-      <c r="B583" s="17"/>
+      <c r="A583" s="18"/>
+      <c r="B583" s="18"/>
     </row>
     <row r="584" ht="15.75" customHeight="1">
-      <c r="A584" s="17"/>
-      <c r="B584" s="17"/>
+      <c r="A584" s="18"/>
+      <c r="B584" s="18"/>
     </row>
     <row r="585" ht="15.75" customHeight="1">
-      <c r="A585" s="17"/>
-      <c r="B585" s="17"/>
+      <c r="A585" s="18"/>
+      <c r="B585" s="18"/>
     </row>
     <row r="586" ht="15.75" customHeight="1">
-      <c r="A586" s="17"/>
-      <c r="B586" s="17"/>
+      <c r="A586" s="18"/>
+      <c r="B586" s="18"/>
     </row>
     <row r="587" ht="15.75" customHeight="1">
-      <c r="A587" s="17"/>
-      <c r="B587" s="17"/>
+      <c r="A587" s="18"/>
+      <c r="B587" s="18"/>
     </row>
     <row r="588" ht="15.75" customHeight="1">
-      <c r="A588" s="17"/>
-      <c r="B588" s="17"/>
+      <c r="A588" s="18"/>
+      <c r="B588" s="18"/>
     </row>
     <row r="589" ht="15.75" customHeight="1">
-      <c r="A589" s="17"/>
-      <c r="B589" s="17"/>
+      <c r="A589" s="18"/>
+      <c r="B589" s="18"/>
     </row>
     <row r="590" ht="15.75" customHeight="1">
-      <c r="A590" s="17"/>
-      <c r="B590" s="17"/>
+      <c r="A590" s="18"/>
+      <c r="B590" s="18"/>
     </row>
     <row r="591" ht="15.75" customHeight="1">
-      <c r="A591" s="17"/>
-      <c r="B591" s="17"/>
+      <c r="A591" s="18"/>
+      <c r="B591" s="18"/>
     </row>
     <row r="592" ht="15.75" customHeight="1">
-      <c r="A592" s="17"/>
-      <c r="B592" s="17"/>
+      <c r="A592" s="18"/>
+      <c r="B592" s="18"/>
     </row>
     <row r="593" ht="15.75" customHeight="1">
-      <c r="A593" s="17"/>
-      <c r="B593" s="17"/>
+      <c r="A593" s="18"/>
+      <c r="B593" s="18"/>
     </row>
     <row r="594" ht="15.75" customHeight="1">
-      <c r="A594" s="17"/>
-      <c r="B594" s="17"/>
+      <c r="A594" s="18"/>
+      <c r="B594" s="18"/>
     </row>
     <row r="595" ht="15.75" customHeight="1">
-      <c r="A595" s="17"/>
-      <c r="B595" s="17"/>
+      <c r="A595" s="18"/>
+      <c r="B595" s="18"/>
     </row>
     <row r="596" ht="15.75" customHeight="1">
-      <c r="A596" s="17"/>
-      <c r="B596" s="17"/>
+      <c r="A596" s="18"/>
+      <c r="B596" s="18"/>
     </row>
     <row r="597" ht="15.75" customHeight="1">
-      <c r="A597" s="17"/>
-      <c r="B597" s="17"/>
+      <c r="A597" s="18"/>
+      <c r="B597" s="18"/>
     </row>
     <row r="598" ht="15.75" customHeight="1">
-      <c r="A598" s="17"/>
-      <c r="B598" s="17"/>
+      <c r="A598" s="18"/>
+      <c r="B598" s="18"/>
     </row>
     <row r="599" ht="15.75" customHeight="1">
-      <c r="A599" s="17"/>
-      <c r="B599" s="17"/>
+      <c r="A599" s="18"/>
+      <c r="B599" s="18"/>
     </row>
     <row r="600" ht="15.75" customHeight="1">
-      <c r="A600" s="17"/>
-      <c r="B600" s="17"/>
+      <c r="A600" s="18"/>
+      <c r="B600" s="18"/>
     </row>
     <row r="601" ht="15.75" customHeight="1">
-      <c r="A601" s="17"/>
-      <c r="B601" s="17"/>
+      <c r="A601" s="18"/>
+      <c r="B601" s="18"/>
     </row>
     <row r="602" ht="15.75" customHeight="1">
-      <c r="A602" s="17"/>
-      <c r="B602" s="17"/>
+      <c r="A602" s="18"/>
+      <c r="B602" s="18"/>
     </row>
     <row r="603" ht="15.75" customHeight="1">
-      <c r="A603" s="17"/>
-      <c r="B603" s="17"/>
+      <c r="A603" s="18"/>
+      <c r="B603" s="18"/>
     </row>
     <row r="604" ht="15.75" customHeight="1">
-      <c r="A604" s="17"/>
-      <c r="B604" s="17"/>
+      <c r="A604" s="18"/>
+      <c r="B604" s="18"/>
     </row>
     <row r="605" ht="15.75" customHeight="1">
-      <c r="A605" s="17"/>
-      <c r="B605" s="17"/>
+      <c r="A605" s="18"/>
+      <c r="B605" s="18"/>
     </row>
     <row r="606" ht="15.75" customHeight="1">
-      <c r="A606" s="17"/>
-      <c r="B606" s="17"/>
+      <c r="A606" s="18"/>
+      <c r="B606" s="18"/>
     </row>
     <row r="607" ht="15.75" customHeight="1">
-      <c r="A607" s="17"/>
-      <c r="B607" s="17"/>
+      <c r="A607" s="18"/>
+      <c r="B607" s="18"/>
     </row>
     <row r="608" ht="15.75" customHeight="1">
-      <c r="A608" s="17"/>
-      <c r="B608" s="17"/>
+      <c r="A608" s="18"/>
+      <c r="B608" s="18"/>
     </row>
     <row r="609" ht="15.75" customHeight="1">
-      <c r="A609" s="17"/>
-      <c r="B609" s="17"/>
+      <c r="A609" s="18"/>
+      <c r="B609" s="18"/>
     </row>
     <row r="610" ht="15.75" customHeight="1">
-      <c r="A610" s="17"/>
-      <c r="B610" s="17"/>
+      <c r="A610" s="18"/>
+      <c r="B610" s="18"/>
     </row>
     <row r="611" ht="15.75" customHeight="1">
-      <c r="A611" s="17"/>
-      <c r="B611" s="17"/>
+      <c r="A611" s="18"/>
+      <c r="B611" s="18"/>
     </row>
     <row r="612" ht="15.75" customHeight="1">
-      <c r="A612" s="17"/>
-      <c r="B612" s="17"/>
+      <c r="A612" s="18"/>
+      <c r="B612" s="18"/>
     </row>
     <row r="613" ht="15.75" customHeight="1">
-      <c r="A613" s="17"/>
-      <c r="B613" s="17"/>
+      <c r="A613" s="18"/>
+      <c r="B613" s="18"/>
     </row>
     <row r="614" ht="15.75" customHeight="1">
-      <c r="A614" s="17"/>
-      <c r="B614" s="17"/>
+      <c r="A614" s="18"/>
+      <c r="B614" s="18"/>
     </row>
     <row r="615" ht="15.75" customHeight="1">
-      <c r="A615" s="17"/>
-      <c r="B615" s="17"/>
+      <c r="A615" s="18"/>
+      <c r="B615" s="18"/>
     </row>
     <row r="616" ht="15.75" customHeight="1">
-      <c r="A616" s="17"/>
-      <c r="B616" s="17"/>
+      <c r="A616" s="18"/>
+      <c r="B616" s="18"/>
     </row>
     <row r="617" ht="15.75" customHeight="1">
-      <c r="A617" s="17"/>
-      <c r="B617" s="17"/>
+      <c r="A617" s="18"/>
+      <c r="B617" s="18"/>
     </row>
     <row r="618" ht="15.75" customHeight="1">
-      <c r="A618" s="17"/>
-      <c r="B618" s="17"/>
+      <c r="A618" s="18"/>
+      <c r="B618" s="18"/>
     </row>
     <row r="619" ht="15.75" customHeight="1">
-      <c r="A619" s="17"/>
-      <c r="B619" s="17"/>
+      <c r="A619" s="18"/>
+      <c r="B619" s="18"/>
     </row>
     <row r="620" ht="15.75" customHeight="1">
-      <c r="A620" s="17"/>
-      <c r="B620" s="17"/>
+      <c r="A620" s="18"/>
+      <c r="B620" s="18"/>
     </row>
     <row r="621" ht="15.75" customHeight="1">
-      <c r="A621" s="17"/>
-      <c r="B621" s="17"/>
+      <c r="A621" s="18"/>
+      <c r="B621" s="18"/>
     </row>
     <row r="622" ht="15.75" customHeight="1">
-      <c r="A622" s="17"/>
-      <c r="B622" s="17"/>
+      <c r="A622" s="18"/>
+      <c r="B622" s="18"/>
     </row>
     <row r="623" ht="15.75" customHeight="1">
-      <c r="A623" s="17"/>
-      <c r="B623" s="17"/>
+      <c r="A623" s="18"/>
+      <c r="B623" s="18"/>
     </row>
     <row r="624" ht="15.75" customHeight="1">
-      <c r="A624" s="17"/>
-      <c r="B624" s="17"/>
+      <c r="A624" s="18"/>
+      <c r="B624" s="18"/>
     </row>
     <row r="625" ht="15.75" customHeight="1">
-      <c r="A625" s="17"/>
-      <c r="B625" s="17"/>
+      <c r="A625" s="18"/>
+      <c r="B625" s="18"/>
     </row>
     <row r="626" ht="15.75" customHeight="1">
-      <c r="A626" s="17"/>
-      <c r="B626" s="17"/>
+      <c r="A626" s="18"/>
+      <c r="B626" s="18"/>
     </row>
     <row r="627" ht="15.75" customHeight="1">
-      <c r="A627" s="17"/>
-      <c r="B627" s="17"/>
+      <c r="A627" s="18"/>
+      <c r="B627" s="18"/>
     </row>
     <row r="628" ht="15.75" customHeight="1">
-      <c r="A628" s="17"/>
-      <c r="B628" s="17"/>
+      <c r="A628" s="18"/>
+      <c r="B628" s="18"/>
     </row>
     <row r="629" ht="15.75" customHeight="1">
-      <c r="A629" s="17"/>
-      <c r="B629" s="17"/>
+      <c r="A629" s="18"/>
+      <c r="B629" s="18"/>
     </row>
     <row r="630" ht="15.75" customHeight="1">
-      <c r="A630" s="17"/>
-      <c r="B630" s="17"/>
+      <c r="A630" s="18"/>
+      <c r="B630" s="18"/>
     </row>
     <row r="631" ht="15.75" customHeight="1">
-      <c r="A631" s="17"/>
-      <c r="B631" s="17"/>
+      <c r="A631" s="18"/>
+      <c r="B631" s="18"/>
     </row>
     <row r="632" ht="15.75" customHeight="1">
-      <c r="A632" s="17"/>
-      <c r="B632" s="17"/>
+      <c r="A632" s="18"/>
+      <c r="B632" s="18"/>
     </row>
     <row r="633" ht="15.75" customHeight="1">
-      <c r="A633" s="17"/>
-      <c r="B633" s="17"/>
+      <c r="A633" s="18"/>
+      <c r="B633" s="18"/>
     </row>
     <row r="634" ht="15.75" customHeight="1">
-      <c r="A634" s="17"/>
-      <c r="B634" s="17"/>
+      <c r="A634" s="18"/>
+      <c r="B634" s="18"/>
     </row>
     <row r="635" ht="15.75" customHeight="1">
-      <c r="A635" s="17"/>
-      <c r="B635" s="17"/>
+      <c r="A635" s="18"/>
+      <c r="B635" s="18"/>
     </row>
     <row r="636" ht="15.75" customHeight="1">
-      <c r="A636" s="17"/>
-      <c r="B636" s="17"/>
+      <c r="A636" s="18"/>
+      <c r="B636" s="18"/>
     </row>
     <row r="637" ht="15.75" customHeight="1">
-      <c r="A637" s="17"/>
-      <c r="B637" s="17"/>
+      <c r="A637" s="18"/>
+      <c r="B637" s="18"/>
     </row>
     <row r="638" ht="15.75" customHeight="1">
-      <c r="A638" s="17"/>
-      <c r="B638" s="17"/>
+      <c r="A638" s="18"/>
+      <c r="B638" s="18"/>
     </row>
     <row r="639" ht="15.75" customHeight="1">
-      <c r="A639" s="17"/>
-      <c r="B639" s="17"/>
+      <c r="A639" s="18"/>
+      <c r="B639" s="18"/>
     </row>
     <row r="640" ht="15.75" customHeight="1">
-      <c r="A640" s="17"/>
-      <c r="B640" s="17"/>
+      <c r="A640" s="18"/>
+      <c r="B640" s="18"/>
     </row>
     <row r="641" ht="15.75" customHeight="1">
-      <c r="A641" s="17"/>
-      <c r="B641" s="17"/>
+      <c r="A641" s="18"/>
+      <c r="B641" s="18"/>
     </row>
     <row r="642" ht="15.75" customHeight="1">
-      <c r="A642" s="17"/>
-      <c r="B642" s="17"/>
+      <c r="A642" s="18"/>
+      <c r="B642" s="18"/>
     </row>
     <row r="643" ht="15.75" customHeight="1">
-      <c r="A643" s="17"/>
-      <c r="B643" s="17"/>
+      <c r="A643" s="18"/>
+      <c r="B643" s="18"/>
     </row>
     <row r="644" ht="15.75" customHeight="1">
-      <c r="A644" s="17"/>
-      <c r="B644" s="17"/>
+      <c r="A644" s="18"/>
+      <c r="B644" s="18"/>
     </row>
     <row r="645" ht="15.75" customHeight="1">
-      <c r="A645" s="17"/>
-      <c r="B645" s="17"/>
+      <c r="A645" s="18"/>
+      <c r="B645" s="18"/>
     </row>
     <row r="646" ht="15.75" customHeight="1">
-      <c r="A646" s="17"/>
-      <c r="B646" s="17"/>
+      <c r="A646" s="18"/>
+      <c r="B646" s="18"/>
     </row>
     <row r="647" ht="15.75" customHeight="1">
-      <c r="A647" s="17"/>
-      <c r="B647" s="17"/>
+      <c r="A647" s="18"/>
+      <c r="B647" s="18"/>
     </row>
     <row r="648" ht="15.75" customHeight="1">
-      <c r="A648" s="17"/>
-      <c r="B648" s="17"/>
+      <c r="A648" s="18"/>
+      <c r="B648" s="18"/>
     </row>
     <row r="649" ht="15.75" customHeight="1">
-      <c r="A649" s="17"/>
-      <c r="B649" s="17"/>
+      <c r="A649" s="18"/>
+      <c r="B649" s="18"/>
     </row>
     <row r="650" ht="15.75" customHeight="1">
-      <c r="A650" s="17"/>
-      <c r="B650" s="17"/>
+      <c r="A650" s="18"/>
+      <c r="B650" s="18"/>
     </row>
     <row r="651" ht="15.75" customHeight="1">
-      <c r="A651" s="17"/>
-      <c r="B651" s="17"/>
+      <c r="A651" s="18"/>
+      <c r="B651" s="18"/>
     </row>
     <row r="652" ht="15.75" customHeight="1">
-      <c r="A652" s="17"/>
-      <c r="B652" s="17"/>
+      <c r="A652" s="18"/>
+      <c r="B652" s="18"/>
     </row>
     <row r="653" ht="15.75" customHeight="1">
-      <c r="A653" s="17"/>
-      <c r="B653" s="17"/>
+      <c r="A653" s="18"/>
+      <c r="B653" s="18"/>
     </row>
     <row r="654" ht="15.75" customHeight="1">
-      <c r="A654" s="17"/>
-      <c r="B654" s="17"/>
+      <c r="A654" s="18"/>
+      <c r="B654" s="18"/>
     </row>
     <row r="655" ht="15.75" customHeight="1">
-      <c r="A655" s="17"/>
-      <c r="B655" s="17"/>
+      <c r="A655" s="18"/>
+      <c r="B655" s="18"/>
     </row>
     <row r="656" ht="15.75" customHeight="1">
-      <c r="A656" s="17"/>
-      <c r="B656" s="17"/>
+      <c r="A656" s="18"/>
+      <c r="B656" s="18"/>
     </row>
     <row r="657" ht="15.75" customHeight="1">
-      <c r="A657" s="17"/>
-      <c r="B657" s="17"/>
+      <c r="A657" s="18"/>
+      <c r="B657" s="18"/>
     </row>
     <row r="658" ht="15.75" customHeight="1">
-      <c r="A658" s="17"/>
-      <c r="B658" s="17"/>
+      <c r="A658" s="18"/>
+      <c r="B658" s="18"/>
     </row>
     <row r="659" ht="15.75" customHeight="1">
-      <c r="A659" s="17"/>
-      <c r="B659" s="17"/>
+      <c r="A659" s="18"/>
+      <c r="B659" s="18"/>
     </row>
     <row r="660" ht="15.75" customHeight="1">
-      <c r="A660" s="17"/>
-      <c r="B660" s="17"/>
+      <c r="A660" s="18"/>
+      <c r="B660" s="18"/>
     </row>
     <row r="661" ht="15.75" customHeight="1">
-      <c r="A661" s="17"/>
-      <c r="B661" s="17"/>
+      <c r="A661" s="18"/>
+      <c r="B661" s="18"/>
     </row>
     <row r="662" ht="15.75" customHeight="1">
-      <c r="A662" s="17"/>
-      <c r="B662" s="17"/>
+      <c r="A662" s="18"/>
+      <c r="B662" s="18"/>
     </row>
     <row r="663" ht="15.75" customHeight="1">
-      <c r="A663" s="17"/>
-      <c r="B663" s="17"/>
+      <c r="A663" s="18"/>
+      <c r="B663" s="18"/>
     </row>
     <row r="664" ht="15.75" customHeight="1">
-      <c r="A664" s="17"/>
-      <c r="B664" s="17"/>
+      <c r="A664" s="18"/>
+      <c r="B664" s="18"/>
     </row>
     <row r="665" ht="15.75" customHeight="1">
-      <c r="A665" s="17"/>
-      <c r="B665" s="17"/>
+      <c r="A665" s="18"/>
+      <c r="B665" s="18"/>
     </row>
     <row r="666" ht="15.75" customHeight="1">
-      <c r="A666" s="17"/>
-      <c r="B666" s="17"/>
+      <c r="A666" s="18"/>
+      <c r="B666" s="18"/>
     </row>
     <row r="667" ht="15.75" customHeight="1">
-      <c r="A667" s="17"/>
-      <c r="B667" s="17"/>
+      <c r="A667" s="18"/>
+      <c r="B667" s="18"/>
     </row>
     <row r="668" ht="15.75" customHeight="1">
-      <c r="A668" s="17"/>
-      <c r="B668" s="17"/>
+      <c r="A668" s="18"/>
+      <c r="B668" s="18"/>
     </row>
     <row r="669" ht="15.75" customHeight="1">
-      <c r="A669" s="17"/>
-      <c r="B669" s="17"/>
+      <c r="A669" s="18"/>
+      <c r="B669" s="18"/>
     </row>
     <row r="670" ht="15.75" customHeight="1">
-      <c r="A670" s="17"/>
-      <c r="B670" s="17"/>
+      <c r="A670" s="18"/>
+      <c r="B670" s="18"/>
     </row>
     <row r="671" ht="15.75" customHeight="1">
-      <c r="A671" s="17"/>
-      <c r="B671" s="17"/>
+      <c r="A671" s="18"/>
+      <c r="B671" s="18"/>
     </row>
     <row r="672" ht="15.75" customHeight="1">
-      <c r="A672" s="17"/>
-      <c r="B672" s="17"/>
+      <c r="A672" s="18"/>
+      <c r="B672" s="18"/>
     </row>
     <row r="673" ht="15.75" customHeight="1">
-      <c r="A673" s="17"/>
-      <c r="B673" s="17"/>
+      <c r="A673" s="18"/>
+      <c r="B673" s="18"/>
     </row>
     <row r="674" ht="15.75" customHeight="1">
-      <c r="A674" s="17"/>
-      <c r="B674" s="17"/>
+      <c r="A674" s="18"/>
+      <c r="B674" s="18"/>
     </row>
     <row r="675" ht="15.75" customHeight="1">
-      <c r="A675" s="17"/>
-      <c r="B675" s="17"/>
+      <c r="A675" s="18"/>
+      <c r="B675" s="18"/>
     </row>
     <row r="676" ht="15.75" customHeight="1">
-      <c r="A676" s="17"/>
-      <c r="B676" s="17"/>
+      <c r="A676" s="18"/>
+      <c r="B676" s="18"/>
     </row>
     <row r="677" ht="15.75" customHeight="1">
-      <c r="A677" s="17"/>
-      <c r="B677" s="17"/>
+      <c r="A677" s="18"/>
+      <c r="B677" s="18"/>
     </row>
     <row r="678" ht="15.75" customHeight="1">
-      <c r="A678" s="17"/>
-      <c r="B678" s="17"/>
+      <c r="A678" s="18"/>
+      <c r="B678" s="18"/>
     </row>
     <row r="679" ht="15.75" customHeight="1">
-      <c r="A679" s="17"/>
-      <c r="B679" s="17"/>
+      <c r="A679" s="18"/>
+      <c r="B679" s="18"/>
     </row>
     <row r="680" ht="15.75" customHeight="1">
-      <c r="A680" s="17"/>
-      <c r="B680" s="17"/>
+      <c r="A680" s="18"/>
+      <c r="B680" s="18"/>
     </row>
     <row r="681" ht="15.75" customHeight="1">
-      <c r="A681" s="17"/>
-      <c r="B681" s="17"/>
+      <c r="A681" s="18"/>
+      <c r="B681" s="18"/>
     </row>
     <row r="682" ht="15.75" customHeight="1">
-      <c r="A682" s="17"/>
-      <c r="B682" s="17"/>
+      <c r="A682" s="18"/>
+      <c r="B682" s="18"/>
     </row>
     <row r="683" ht="15.75" customHeight="1">
-      <c r="A683" s="17"/>
-      <c r="B683" s="17"/>
+      <c r="A683" s="18"/>
+      <c r="B683" s="18"/>
     </row>
     <row r="684" ht="15.75" customHeight="1">
-      <c r="A684" s="17"/>
-      <c r="B684" s="17"/>
+      <c r="A684" s="18"/>
+      <c r="B684" s="18"/>
     </row>
     <row r="685" ht="15.75" customHeight="1">
-      <c r="A685" s="17"/>
-      <c r="B685" s="17"/>
+      <c r="A685" s="18"/>
+      <c r="B685" s="18"/>
     </row>
     <row r="686" ht="15.75" customHeight="1">
-      <c r="A686" s="17"/>
-      <c r="B686" s="17"/>
+      <c r="A686" s="18"/>
+      <c r="B686" s="18"/>
     </row>
     <row r="687" ht="15.75" customHeight="1">
-      <c r="A687" s="17"/>
-      <c r="B687" s="17"/>
+      <c r="A687" s="18"/>
+      <c r="B687" s="18"/>
     </row>
     <row r="688" ht="15.75" customHeight="1">
-      <c r="A688" s="17"/>
-      <c r="B688" s="17"/>
+      <c r="A688" s="18"/>
+      <c r="B688" s="18"/>
     </row>
     <row r="689" ht="15.75" customHeight="1">
-      <c r="A689" s="17"/>
-      <c r="B689" s="17"/>
+      <c r="A689" s="18"/>
+      <c r="B689" s="18"/>
     </row>
     <row r="690" ht="15.75" customHeight="1">
-      <c r="A690" s="17"/>
-      <c r="B690" s="17"/>
+      <c r="A690" s="18"/>
+      <c r="B690" s="18"/>
     </row>
     <row r="691" ht="15.75" customHeight="1">
-      <c r="A691" s="17"/>
-      <c r="B691" s="17"/>
+      <c r="A691" s="18"/>
+      <c r="B691" s="18"/>
     </row>
     <row r="692" ht="15.75" customHeight="1">
-      <c r="A692" s="17"/>
-      <c r="B692" s="17"/>
+      <c r="A692" s="18"/>
+      <c r="B692" s="18"/>
     </row>
     <row r="693" ht="15.75" customHeight="1">
-      <c r="A693" s="17"/>
-      <c r="B693" s="17"/>
+      <c r="A693" s="18"/>
+      <c r="B693" s="18"/>
     </row>
     <row r="694" ht="15.75" customHeight="1">
-      <c r="A694" s="17"/>
-      <c r="B694" s="17"/>
+      <c r="A694" s="18"/>
+      <c r="B694" s="18"/>
     </row>
     <row r="695" ht="15.75" customHeight="1">
-      <c r="A695" s="17"/>
-      <c r="B695" s="17"/>
+      <c r="A695" s="18"/>
+      <c r="B695" s="18"/>
     </row>
     <row r="696" ht="15.75" customHeight="1">
-      <c r="A696" s="17"/>
-      <c r="B696" s="17"/>
+      <c r="A696" s="18"/>
+      <c r="B696" s="18"/>
     </row>
     <row r="697" ht="15.75" customHeight="1">
-      <c r="A697" s="17"/>
-      <c r="B697" s="17"/>
+      <c r="A697" s="18"/>
+      <c r="B697" s="18"/>
     </row>
     <row r="698" ht="15.75" customHeight="1">
-      <c r="A698" s="17"/>
-      <c r="B698" s="17"/>
+      <c r="A698" s="18"/>
+      <c r="B698" s="18"/>
     </row>
     <row r="699" ht="15.75" customHeight="1">
-      <c r="A699" s="17"/>
-      <c r="B699" s="17"/>
+      <c r="A699" s="18"/>
+      <c r="B699" s="18"/>
     </row>
     <row r="700" ht="15.75" customHeight="1">
-      <c r="A700" s="17"/>
-      <c r="B700" s="17"/>
+      <c r="A700" s="18"/>
+      <c r="B700" s="18"/>
     </row>
     <row r="701" ht="15.75" customHeight="1">
-      <c r="A701" s="17"/>
-      <c r="B701" s="17"/>
+      <c r="A701" s="18"/>
+      <c r="B701" s="18"/>
     </row>
     <row r="702" ht="15.75" customHeight="1">
-      <c r="A702" s="17"/>
-      <c r="B702" s="17"/>
+      <c r="A702" s="18"/>
+      <c r="B702" s="18"/>
     </row>
     <row r="703" ht="15.75" customHeight="1">
-      <c r="A703" s="17"/>
-      <c r="B703" s="17"/>
+      <c r="A703" s="18"/>
+      <c r="B703" s="18"/>
     </row>
     <row r="704" ht="15.75" customHeight="1">
-      <c r="A704" s="17"/>
-      <c r="B704" s="17"/>
+      <c r="A704" s="18"/>
+      <c r="B704" s="18"/>
     </row>
     <row r="705" ht="15.75" customHeight="1">
-      <c r="A705" s="17"/>
-      <c r="B705" s="17"/>
+      <c r="A705" s="18"/>
+      <c r="B705" s="18"/>
     </row>
     <row r="706" ht="15.75" customHeight="1">
-      <c r="A706" s="17"/>
-      <c r="B706" s="17"/>
+      <c r="A706" s="18"/>
+      <c r="B706" s="18"/>
     </row>
     <row r="707" ht="15.75" customHeight="1">
-      <c r="A707" s="17"/>
-      <c r="B707" s="17"/>
+      <c r="A707" s="18"/>
+      <c r="B707" s="18"/>
     </row>
     <row r="708" ht="15.75" customHeight="1">
-      <c r="A708" s="17"/>
-      <c r="B708" s="17"/>
+      <c r="A708" s="18"/>
+      <c r="B708" s="18"/>
     </row>
     <row r="709" ht="15.75" customHeight="1">
-      <c r="A709" s="17"/>
-      <c r="B709" s="17"/>
+      <c r="A709" s="18"/>
+      <c r="B709" s="18"/>
     </row>
     <row r="710" ht="15.75" customHeight="1">
-      <c r="A710" s="17"/>
-      <c r="B710" s="17"/>
+      <c r="A710" s="18"/>
+      <c r="B710" s="18"/>
     </row>
     <row r="711" ht="15.75" customHeight="1">
-      <c r="A711" s="17"/>
-      <c r="B711" s="17"/>
+      <c r="A711" s="18"/>
+      <c r="B711" s="18"/>
     </row>
     <row r="712" ht="15.75" customHeight="1">
-      <c r="A712" s="17"/>
-      <c r="B712" s="17"/>
+      <c r="A712" s="18"/>
+      <c r="B712" s="18"/>
     </row>
     <row r="713" ht="15.75" customHeight="1">
-      <c r="A713" s="17"/>
-      <c r="B713" s="17"/>
+      <c r="A713" s="18"/>
+      <c r="B713" s="18"/>
     </row>
     <row r="714" ht="15.75" customHeight="1">
-      <c r="A714" s="17"/>
-      <c r="B714" s="17"/>
+      <c r="A714" s="18"/>
+      <c r="B714" s="18"/>
     </row>
     <row r="715" ht="15.75" customHeight="1">
-      <c r="A715" s="17"/>
-      <c r="B715" s="17"/>
+      <c r="A715" s="18"/>
+      <c r="B715" s="18"/>
     </row>
     <row r="716" ht="15.75" customHeight="1">
-      <c r="A716" s="17"/>
-      <c r="B716" s="17"/>
+      <c r="A716" s="18"/>
+      <c r="B716" s="18"/>
     </row>
     <row r="717" ht="15.75" customHeight="1">
-      <c r="A717" s="17"/>
-      <c r="B717" s="17"/>
+      <c r="A717" s="18"/>
+      <c r="B717" s="18"/>
     </row>
     <row r="718" ht="15.75" customHeight="1">
-      <c r="A718" s="17"/>
-      <c r="B718" s="17"/>
+      <c r="A718" s="18"/>
+      <c r="B718" s="18"/>
     </row>
     <row r="719" ht="15.75" customHeight="1">
-      <c r="A719" s="17"/>
-      <c r="B719" s="17"/>
+      <c r="A719" s="18"/>
+      <c r="B719" s="18"/>
     </row>
     <row r="720" ht="15.75" customHeight="1">
-      <c r="A720" s="17"/>
-      <c r="B720" s="17"/>
+      <c r="A720" s="18"/>
+      <c r="B720" s="18"/>
     </row>
     <row r="721" ht="15.75" customHeight="1">
-      <c r="A721" s="17"/>
-      <c r="B721" s="17"/>
+      <c r="A721" s="18"/>
+      <c r="B721" s="18"/>
     </row>
     <row r="722" ht="15.75" customHeight="1">
-      <c r="A722" s="17"/>
-      <c r="B722" s="17"/>
+      <c r="A722" s="18"/>
+      <c r="B722" s="18"/>
     </row>
     <row r="723" ht="15.75" customHeight="1">
-      <c r="A723" s="17"/>
-      <c r="B723" s="17"/>
+      <c r="A723" s="18"/>
+      <c r="B723" s="18"/>
     </row>
     <row r="724" ht="15.75" customHeight="1">
-      <c r="A724" s="17"/>
-      <c r="B724" s="17"/>
+      <c r="A724" s="18"/>
+      <c r="B724" s="18"/>
     </row>
     <row r="725" ht="15.75" customHeight="1">
-      <c r="A725" s="17"/>
-      <c r="B725" s="17"/>
+      <c r="A725" s="18"/>
+      <c r="B725" s="18"/>
     </row>
     <row r="726" ht="15.75" customHeight="1">
-      <c r="A726" s="17"/>
-      <c r="B726" s="17"/>
+      <c r="A726" s="18"/>
+      <c r="B726" s="18"/>
     </row>
     <row r="727" ht="15.75" customHeight="1">
-      <c r="A727" s="17"/>
-      <c r="B727" s="17"/>
+      <c r="A727" s="18"/>
+      <c r="B727" s="18"/>
     </row>
     <row r="728" ht="15.75" customHeight="1">
-      <c r="A728" s="17"/>
-      <c r="B728" s="17"/>
+      <c r="A728" s="18"/>
+      <c r="B728" s="18"/>
     </row>
     <row r="729" ht="15.75" customHeight="1">
-      <c r="A729" s="17"/>
-      <c r="B729" s="17"/>
+      <c r="A729" s="18"/>
+      <c r="B729" s="18"/>
     </row>
     <row r="730" ht="15.75" customHeight="1">
-      <c r="A730" s="17"/>
-      <c r="B730" s="17"/>
+      <c r="A730" s="18"/>
+      <c r="B730" s="18"/>
     </row>
     <row r="731" ht="15.75" customHeight="1">
-      <c r="A731" s="17"/>
-      <c r="B731" s="17"/>
+      <c r="A731" s="18"/>
+      <c r="B731" s="18"/>
     </row>
     <row r="732" ht="15.75" customHeight="1">
-      <c r="A732" s="17"/>
-      <c r="B732" s="17"/>
+      <c r="A732" s="18"/>
+      <c r="B732" s="18"/>
     </row>
     <row r="733" ht="15.75" customHeight="1">
-      <c r="A733" s="17"/>
-      <c r="B733" s="17"/>
+      <c r="A733" s="18"/>
+      <c r="B733" s="18"/>
     </row>
     <row r="734" ht="15.75" customHeight="1">
-      <c r="A734" s="17"/>
-      <c r="B734" s="17"/>
+      <c r="A734" s="18"/>
+      <c r="B734" s="18"/>
     </row>
     <row r="735" ht="15.75" customHeight="1">
-      <c r="A735" s="17"/>
-      <c r="B735" s="17"/>
+      <c r="A735" s="18"/>
+      <c r="B735" s="18"/>
     </row>
     <row r="736" ht="15.75" customHeight="1">
-      <c r="A736" s="17"/>
-      <c r="B736" s="17"/>
+      <c r="A736" s="18"/>
+      <c r="B736" s="18"/>
     </row>
     <row r="737" ht="15.75" customHeight="1">
-      <c r="A737" s="17"/>
-      <c r="B737" s="17"/>
+      <c r="A737" s="18"/>
+      <c r="B737" s="18"/>
     </row>
     <row r="738" ht="15.75" customHeight="1">
-      <c r="A738" s="17"/>
-      <c r="B738" s="17"/>
+      <c r="A738" s="18"/>
+      <c r="B738" s="18"/>
     </row>
     <row r="739" ht="15.75" customHeight="1">
-      <c r="A739" s="17"/>
-      <c r="B739" s="17"/>
+      <c r="A739" s="18"/>
+      <c r="B739" s="18"/>
     </row>
     <row r="740" ht="15.75" customHeight="1">
-      <c r="A740" s="17"/>
-      <c r="B740" s="17"/>
+      <c r="A740" s="18"/>
+      <c r="B740" s="18"/>
     </row>
     <row r="741" ht="15.75" customHeight="1">
-      <c r="A741" s="17"/>
-      <c r="B741" s="17"/>
+      <c r="A741" s="18"/>
+      <c r="B741" s="18"/>
     </row>
     <row r="742" ht="15.75" customHeight="1">
-      <c r="A742" s="17"/>
-      <c r="B742" s="17"/>
+      <c r="A742" s="18"/>
+      <c r="B742" s="18"/>
     </row>
     <row r="743" ht="15.75" customHeight="1">
-      <c r="A743" s="17"/>
-      <c r="B743" s="17"/>
+      <c r="A743" s="18"/>
+      <c r="B743" s="18"/>
     </row>
     <row r="744" ht="15.75" customHeight="1">
-      <c r="A744" s="17"/>
-      <c r="B744" s="17"/>
+      <c r="A744" s="18"/>
+      <c r="B744" s="18"/>
     </row>
     <row r="745" ht="15.75" customHeight="1">
-      <c r="A745" s="17"/>
-      <c r="B745" s="17"/>
+      <c r="A745" s="18"/>
+      <c r="B745" s="18"/>
     </row>
     <row r="746" ht="15.75" customHeight="1">
-      <c r="A746" s="17"/>
-      <c r="B746" s="17"/>
+      <c r="A746" s="18"/>
+      <c r="B746" s="18"/>
     </row>
     <row r="747" ht="15.75" customHeight="1">
-      <c r="A747" s="17"/>
-      <c r="B747" s="17"/>
+      <c r="A747" s="18"/>
+      <c r="B747" s="18"/>
     </row>
     <row r="748" ht="15.75" customHeight="1">
-      <c r="A748" s="17"/>
-      <c r="B748" s="17"/>
+      <c r="A748" s="18"/>
+      <c r="B748" s="18"/>
     </row>
     <row r="749" ht="15.75" customHeight="1">
-      <c r="A749" s="17"/>
-      <c r="B749" s="17"/>
+      <c r="A749" s="18"/>
+      <c r="B749" s="18"/>
     </row>
     <row r="750" ht="15.75" customHeight="1">
-      <c r="A750" s="17"/>
-      <c r="B750" s="17"/>
+      <c r="A750" s="18"/>
+      <c r="B750" s="18"/>
     </row>
     <row r="751" ht="15.75" customHeight="1">
-      <c r="A751" s="17"/>
-      <c r="B751" s="17"/>
+      <c r="A751" s="18"/>
+      <c r="B751" s="18"/>
     </row>
     <row r="752" ht="15.75" customHeight="1">
-      <c r="A752" s="17"/>
-      <c r="B752" s="17"/>
+      <c r="A752" s="18"/>
+      <c r="B752" s="18"/>
     </row>
     <row r="753" ht="15.75" customHeight="1">
-      <c r="A753" s="17"/>
-      <c r="B753" s="17"/>
+      <c r="A753" s="18"/>
+      <c r="B753" s="18"/>
     </row>
     <row r="754" ht="15.75" customHeight="1">
-      <c r="A754" s="17"/>
-      <c r="B754" s="17"/>
+      <c r="A754" s="18"/>
+      <c r="B754" s="18"/>
     </row>
     <row r="755" ht="15.75" customHeight="1">
-      <c r="A755" s="17"/>
-      <c r="B755" s="17"/>
+      <c r="A755" s="18"/>
+      <c r="B755" s="18"/>
     </row>
     <row r="756" ht="15.75" customHeight="1">
-      <c r="A756" s="17"/>
-      <c r="B756" s="17"/>
+      <c r="A756" s="18"/>
+      <c r="B756" s="18"/>
     </row>
     <row r="757" ht="15.75" customHeight="1">
-      <c r="A757" s="17"/>
-      <c r="B757" s="17"/>
+      <c r="A757" s="18"/>
+      <c r="B757" s="18"/>
     </row>
     <row r="758" ht="15.75" customHeight="1">
-      <c r="A758" s="17"/>
-      <c r="B758" s="17"/>
+      <c r="A758" s="18"/>
+      <c r="B758" s="18"/>
     </row>
     <row r="759" ht="15.75" customHeight="1">
-      <c r="A759" s="17"/>
-      <c r="B759" s="17"/>
+      <c r="A759" s="18"/>
+      <c r="B759" s="18"/>
     </row>
     <row r="760" ht="15.75" customHeight="1">
-      <c r="A760" s="17"/>
-      <c r="B760" s="17"/>
+      <c r="A760" s="18"/>
+      <c r="B760" s="18"/>
     </row>
     <row r="761" ht="15.75" customHeight="1">
-      <c r="A761" s="17"/>
-      <c r="B761" s="17"/>
+      <c r="A761" s="18"/>
+      <c r="B761" s="18"/>
     </row>
     <row r="762" ht="15.75" customHeight="1">
-      <c r="A762" s="17"/>
-      <c r="B762" s="17"/>
+      <c r="A762" s="18"/>
+      <c r="B762" s="18"/>
     </row>
     <row r="763" ht="15.75" customHeight="1">
-      <c r="A763" s="17"/>
-      <c r="B763" s="17"/>
+      <c r="A763" s="18"/>
+      <c r="B763" s="18"/>
     </row>
     <row r="764" ht="15.75" customHeight="1">
-      <c r="A764" s="17"/>
-      <c r="B764" s="17"/>
+      <c r="A764" s="18"/>
+      <c r="B764" s="18"/>
     </row>
     <row r="765" ht="15.75" customHeight="1">
-      <c r="A765" s="17"/>
-      <c r="B765" s="17"/>
+      <c r="A765" s="18"/>
+      <c r="B765" s="18"/>
     </row>
     <row r="766" ht="15.75" customHeight="1">
-      <c r="A766" s="17"/>
-      <c r="B766" s="17"/>
+      <c r="A766" s="18"/>
+      <c r="B766" s="18"/>
     </row>
     <row r="767" ht="15.75" customHeight="1">
-      <c r="A767" s="17"/>
-      <c r="B767" s="17"/>
+      <c r="A767" s="18"/>
+      <c r="B767" s="18"/>
     </row>
     <row r="768" ht="15.75" customHeight="1">
-      <c r="A768" s="17"/>
-      <c r="B768" s="17"/>
+      <c r="A768" s="18"/>
+      <c r="B768" s="18"/>
     </row>
     <row r="769" ht="15.75" customHeight="1">
-      <c r="A769" s="17"/>
-      <c r="B769" s="17"/>
+      <c r="A769" s="18"/>
+      <c r="B769" s="18"/>
     </row>
     <row r="770" ht="15.75" customHeight="1">
-      <c r="A770" s="17"/>
-      <c r="B770" s="17"/>
+      <c r="A770" s="18"/>
+      <c r="B770" s="18"/>
     </row>
     <row r="771" ht="15.75" customHeight="1">
-      <c r="A771" s="17"/>
-      <c r="B771" s="17"/>
+      <c r="A771" s="18"/>
+      <c r="B771" s="18"/>
     </row>
     <row r="772" ht="15.75" customHeight="1">
-      <c r="A772" s="17"/>
-      <c r="B772" s="17"/>
+      <c r="A772" s="18"/>
+      <c r="B772" s="18"/>
     </row>
     <row r="773" ht="15.75" customHeight="1">
-      <c r="A773" s="17"/>
-      <c r="B773" s="17"/>
+      <c r="A773" s="18"/>
+      <c r="B773" s="18"/>
     </row>
     <row r="774" ht="15.75" customHeight="1">
-      <c r="A774" s="17"/>
-      <c r="B774" s="17"/>
+      <c r="A774" s="18"/>
+      <c r="B774" s="18"/>
     </row>
     <row r="775" ht="15.75" customHeight="1">
-      <c r="A775" s="17"/>
-      <c r="B775" s="17"/>
+      <c r="A775" s="18"/>
+      <c r="B775" s="18"/>
     </row>
     <row r="776" ht="15.75" customHeight="1">
-      <c r="A776" s="17"/>
-      <c r="B776" s="17"/>
+      <c r="A776" s="18"/>
+      <c r="B776" s="18"/>
     </row>
     <row r="777" ht="15.75" customHeight="1">
-      <c r="A777" s="17"/>
-      <c r="B777" s="17"/>
+      <c r="A777" s="18"/>
+      <c r="B777" s="18"/>
     </row>
     <row r="778" ht="15.75" customHeight="1">
-      <c r="A778" s="17"/>
-      <c r="B778" s="17"/>
+      <c r="A778" s="18"/>
+      <c r="B778" s="18"/>
     </row>
     <row r="779" ht="15.75" customHeight="1">
-      <c r="A779" s="17"/>
-      <c r="B779" s="17"/>
+      <c r="A779" s="18"/>
+      <c r="B779" s="18"/>
     </row>
     <row r="780" ht="15.75" customHeight="1">
-      <c r="A780" s="17"/>
-      <c r="B780" s="17"/>
+      <c r="A780" s="18"/>
+      <c r="B780" s="18"/>
     </row>
     <row r="781" ht="15.75" customHeight="1">
-      <c r="A781" s="17"/>
-      <c r="B781" s="17"/>
+      <c r="A781" s="18"/>
+      <c r="B781" s="18"/>
     </row>
     <row r="782" ht="15.75" customHeight="1">
-      <c r="A782" s="17"/>
-      <c r="B782" s="17"/>
+      <c r="A782" s="18"/>
+      <c r="B782" s="18"/>
     </row>
     <row r="783" ht="15.75" customHeight="1">
-      <c r="A783" s="17"/>
-      <c r="B783" s="17"/>
+      <c r="A783" s="18"/>
+      <c r="B783" s="18"/>
     </row>
     <row r="784" ht="15.75" customHeight="1">
-      <c r="A784" s="17"/>
-      <c r="B784" s="17"/>
+      <c r="A784" s="18"/>
+      <c r="B784" s="18"/>
     </row>
     <row r="785" ht="15.75" customHeight="1">
-      <c r="A785" s="17"/>
-      <c r="B785" s="17"/>
+      <c r="A785" s="18"/>
+      <c r="B785" s="18"/>
     </row>
     <row r="786" ht="15.75" customHeight="1">
-      <c r="A786" s="17"/>
-      <c r="B786" s="17"/>
+      <c r="A786" s="18"/>
+      <c r="B786" s="18"/>
     </row>
     <row r="787" ht="15.75" customHeight="1">
-      <c r="A787" s="17"/>
-      <c r="B787" s="17"/>
+      <c r="A787" s="18"/>
+      <c r="B787" s="18"/>
     </row>
     <row r="788" ht="15.75" customHeight="1">
-      <c r="A788" s="17"/>
-      <c r="B788" s="17"/>
+      <c r="A788" s="18"/>
+      <c r="B788" s="18"/>
     </row>
     <row r="789" ht="15.75" customHeight="1">
-      <c r="A789" s="17"/>
-      <c r="B789" s="17"/>
+      <c r="A789" s="18"/>
+      <c r="B789" s="18"/>
     </row>
     <row r="790" ht="15.75" customHeight="1">
-      <c r="A790" s="17"/>
-      <c r="B790" s="17"/>
+      <c r="A790" s="18"/>
+      <c r="B790" s="18"/>
     </row>
     <row r="791" ht="15.75" customHeight="1">
-      <c r="A791" s="17"/>
-      <c r="B791" s="17"/>
+      <c r="A791" s="18"/>
+      <c r="B791" s="18"/>
     </row>
     <row r="792" ht="15.75" customHeight="1">
-      <c r="A792" s="17"/>
-      <c r="B792" s="17"/>
+      <c r="A792" s="18"/>
+      <c r="B792" s="18"/>
     </row>
     <row r="793" ht="15.75" customHeight="1">
-      <c r="A793" s="17"/>
-      <c r="B793" s="17"/>
+      <c r="A793" s="18"/>
+      <c r="B793" s="18"/>
     </row>
     <row r="794" ht="15.75" customHeight="1">
-      <c r="A794" s="17"/>
-      <c r="B794" s="17"/>
+      <c r="A794" s="18"/>
+      <c r="B794" s="18"/>
     </row>
     <row r="795" ht="15.75" customHeight="1">
-      <c r="A795" s="17"/>
-      <c r="B795" s="17"/>
+      <c r="A795" s="18"/>
+      <c r="B795" s="18"/>
     </row>
     <row r="796" ht="15.75" customHeight="1">
-      <c r="A796" s="17"/>
-      <c r="B796" s="17"/>
+      <c r="A796" s="18"/>
+      <c r="B796" s="18"/>
     </row>
     <row r="797" ht="15.75" customHeight="1">
-      <c r="A797" s="17"/>
-      <c r="B797" s="17"/>
+      <c r="A797" s="18"/>
+      <c r="B797" s="18"/>
     </row>
     <row r="798" ht="15.75" customHeight="1">
-      <c r="A798" s="17"/>
-      <c r="B798" s="17"/>
+      <c r="A798" s="18"/>
+      <c r="B798" s="18"/>
     </row>
     <row r="799" ht="15.75" customHeight="1">
-      <c r="A799" s="17"/>
-      <c r="B799" s="17"/>
+      <c r="A799" s="18"/>
+      <c r="B799" s="18"/>
     </row>
     <row r="800" ht="15.75" customHeight="1">
-      <c r="A800" s="17"/>
-      <c r="B800" s="17"/>
+      <c r="A800" s="18"/>
+      <c r="B800" s="18"/>
     </row>
     <row r="801" ht="15.75" customHeight="1">
-      <c r="A801" s="17"/>
-      <c r="B801" s="17"/>
+      <c r="A801" s="18"/>
+      <c r="B801" s="18"/>
     </row>
     <row r="802" ht="15.75" customHeight="1">
-      <c r="A802" s="17"/>
-      <c r="B802" s="17"/>
+      <c r="A802" s="18"/>
+      <c r="B802" s="18"/>
     </row>
     <row r="803" ht="15.75" customHeight="1">
-      <c r="A803" s="17"/>
-      <c r="B803" s="17"/>
+      <c r="A803" s="18"/>
+      <c r="B803" s="18"/>
     </row>
     <row r="804" ht="15.75" customHeight="1">
-      <c r="A804" s="17"/>
-      <c r="B804" s="17"/>
+      <c r="A804" s="18"/>
+      <c r="B804" s="18"/>
     </row>
     <row r="805" ht="15.75" customHeight="1">
-      <c r="A805" s="17"/>
-      <c r="B805" s="17"/>
+      <c r="A805" s="18"/>
+      <c r="B805" s="18"/>
     </row>
     <row r="806" ht="15.75" customHeight="1">
-      <c r="A806" s="17"/>
-      <c r="B806" s="17"/>
+      <c r="A806" s="18"/>
+      <c r="B806" s="18"/>
     </row>
     <row r="807" ht="15.75" customHeight="1">
-      <c r="A807" s="17"/>
-      <c r="B807" s="17"/>
+      <c r="A807" s="18"/>
+      <c r="B807" s="18"/>
     </row>
     <row r="808" ht="15.75" customHeight="1">
-      <c r="A808" s="17"/>
-      <c r="B808" s="17"/>
+      <c r="A808" s="18"/>
+      <c r="B808" s="18"/>
     </row>
     <row r="809" ht="15.75" customHeight="1">
-      <c r="A809" s="17"/>
-      <c r="B809" s="17"/>
+      <c r="A809" s="18"/>
+      <c r="B809" s="18"/>
     </row>
     <row r="810" ht="15.75" customHeight="1">
-      <c r="A810" s="17"/>
-      <c r="B810" s="17"/>
+      <c r="A810" s="18"/>
+      <c r="B810" s="18"/>
     </row>
     <row r="811" ht="15.75" customHeight="1">
-      <c r="A811" s="17"/>
-      <c r="B811" s="17"/>
+      <c r="A811" s="18"/>
+      <c r="B811" s="18"/>
     </row>
     <row r="812" ht="15.75" customHeight="1">
-      <c r="A812" s="17"/>
-      <c r="B812" s="17"/>
+      <c r="A812" s="18"/>
+      <c r="B812" s="18"/>
     </row>
     <row r="813" ht="15.75" customHeight="1">
-      <c r="A813" s="17"/>
-      <c r="B813" s="17"/>
+      <c r="A813" s="18"/>
+      <c r="B813" s="18"/>
     </row>
     <row r="814" ht="15.75" customHeight="1">
-      <c r="A814" s="17"/>
-      <c r="B814" s="17"/>
+      <c r="A814" s="18"/>
+      <c r="B814" s="18"/>
     </row>
     <row r="815" ht="15.75" customHeight="1">
-      <c r="A815" s="17"/>
-      <c r="B815" s="17"/>
+      <c r="A815" s="18"/>
+      <c r="B815" s="18"/>
     </row>
     <row r="816" ht="15.75" customHeight="1">
-      <c r="A816" s="17"/>
-      <c r="B816" s="17"/>
+      <c r="A816" s="18"/>
+      <c r="B816" s="18"/>
     </row>
     <row r="817" ht="15.75" customHeight="1">
-      <c r="A817" s="17"/>
-      <c r="B817" s="17"/>
+      <c r="A817" s="18"/>
+      <c r="B817" s="18"/>
     </row>
     <row r="818" ht="15.75" customHeight="1">
-      <c r="A818" s="17"/>
-      <c r="B818" s="17"/>
+      <c r="A818" s="18"/>
+      <c r="B818" s="18"/>
     </row>
     <row r="819" ht="15.75" customHeight="1">
-      <c r="A819" s="17"/>
-      <c r="B819" s="17"/>
+      <c r="A819" s="18"/>
+      <c r="B819" s="18"/>
     </row>
     <row r="820" ht="15.75" customHeight="1">
-      <c r="A820" s="17"/>
-      <c r="B820" s="17"/>
+      <c r="A820" s="18"/>
+      <c r="B820" s="18"/>
     </row>
     <row r="821" ht="15.75" customHeight="1">
-      <c r="A821" s="17"/>
-      <c r="B821" s="17"/>
+      <c r="A821" s="18"/>
+      <c r="B821" s="18"/>
     </row>
     <row r="822" ht="15.75" customHeight="1">
-      <c r="A822" s="17"/>
-      <c r="B822" s="17"/>
+      <c r="A822" s="18"/>
+      <c r="B822" s="18"/>
     </row>
     <row r="823" ht="15.75" customHeight="1">
-      <c r="A823" s="17"/>
-      <c r="B823" s="17"/>
+      <c r="A823" s="18"/>
+      <c r="B823" s="18"/>
     </row>
     <row r="824" ht="15.75" customHeight="1">
-      <c r="A824" s="17"/>
-      <c r="B824" s="17"/>
+      <c r="A824" s="18"/>
+      <c r="B824" s="18"/>
     </row>
     <row r="825" ht="15.75" customHeight="1">
-      <c r="A825" s="17"/>
-      <c r="B825" s="17"/>
+      <c r="A825" s="18"/>
+      <c r="B825" s="18"/>
     </row>
     <row r="826" ht="15.75" customHeight="1">
-      <c r="A826" s="17"/>
-      <c r="B826" s="17"/>
+      <c r="A826" s="18"/>
+      <c r="B826" s="18"/>
     </row>
     <row r="827" ht="15.75" customHeight="1">
-      <c r="A827" s="17"/>
-      <c r="B827" s="17"/>
+      <c r="A827" s="18"/>
+      <c r="B827" s="18"/>
     </row>
     <row r="828" ht="15.75" customHeight="1">
-      <c r="A828" s="17"/>
-      <c r="B828" s="17"/>
+      <c r="A828" s="18"/>
+      <c r="B828" s="18"/>
     </row>
     <row r="829" ht="15.75" customHeight="1">
-      <c r="A829" s="17"/>
-      <c r="B829" s="17"/>
+      <c r="A829" s="18"/>
+      <c r="B829" s="18"/>
     </row>
     <row r="830" ht="15.75" customHeight="1">
-      <c r="A830" s="17"/>
-      <c r="B830" s="17"/>
+      <c r="A830" s="18"/>
+      <c r="B830" s="18"/>
     </row>
     <row r="831" ht="15.75" customHeight="1">
-      <c r="A831" s="17"/>
-      <c r="B831" s="17"/>
+      <c r="A831" s="18"/>
+      <c r="B831" s="18"/>
     </row>
     <row r="832" ht="15.75" customHeight="1">
-      <c r="A832" s="17"/>
-      <c r="B832" s="17"/>
+      <c r="A832" s="18"/>
+      <c r="B832" s="18"/>
     </row>
     <row r="833" ht="15.75" customHeight="1">
-      <c r="A833" s="17"/>
-      <c r="B833" s="17"/>
+      <c r="A833" s="18"/>
+      <c r="B833" s="18"/>
     </row>
     <row r="834" ht="15.75" customHeight="1">
-      <c r="A834" s="17"/>
-      <c r="B834" s="17"/>
+      <c r="A834" s="18"/>
+      <c r="B834" s="18"/>
     </row>
     <row r="835" ht="15.75" customHeight="1">
-      <c r="A835" s="17"/>
-      <c r="B835" s="17"/>
+      <c r="A835" s="18"/>
+      <c r="B835" s="18"/>
     </row>
     <row r="836" ht="15.75" customHeight="1">
-      <c r="A836" s="17"/>
-      <c r="B836" s="17"/>
+      <c r="A836" s="18"/>
+      <c r="B836" s="18"/>
     </row>
     <row r="837" ht="15.75" customHeight="1">
-      <c r="A837" s="17"/>
-      <c r="B837" s="17"/>
+      <c r="A837" s="18"/>
+      <c r="B837" s="18"/>
     </row>
     <row r="838" ht="15.75" customHeight="1">
-      <c r="A838" s="17"/>
-      <c r="B838" s="17"/>
+      <c r="A838" s="18"/>
+      <c r="B838" s="18"/>
     </row>
     <row r="839" ht="15.75" customHeight="1">
-      <c r="A839" s="17"/>
-      <c r="B839" s="17"/>
+      <c r="A839" s="18"/>
+      <c r="B839" s="18"/>
     </row>
     <row r="840" ht="15.75" customHeight="1">
-      <c r="A840" s="17"/>
-      <c r="B840" s="17"/>
+      <c r="A840" s="18"/>
+      <c r="B840" s="18"/>
     </row>
     <row r="841" ht="15.75" customHeight="1">
-      <c r="A841" s="17"/>
-      <c r="B841" s="17"/>
+      <c r="A841" s="18"/>
+      <c r="B841" s="18"/>
     </row>
     <row r="842" ht="15.75" customHeight="1">
-      <c r="A842" s="17"/>
-      <c r="B842" s="17"/>
+      <c r="A842" s="18"/>
+      <c r="B842" s="18"/>
     </row>
     <row r="843" ht="15.75" customHeight="1">
-      <c r="A843" s="17"/>
-      <c r="B843" s="17"/>
+      <c r="A843" s="18"/>
+      <c r="B843" s="18"/>
     </row>
     <row r="844" ht="15.75" customHeight="1">
-      <c r="A844" s="17"/>
-      <c r="B844" s="17"/>
+      <c r="A844" s="18"/>
+      <c r="B844" s="18"/>
     </row>
     <row r="845" ht="15.75" customHeight="1">
-      <c r="A845" s="17"/>
-      <c r="B845" s="17"/>
+      <c r="A845" s="18"/>
+      <c r="B845" s="18"/>
     </row>
     <row r="846" ht="15.75" customHeight="1">
-      <c r="A846" s="17"/>
-      <c r="B846" s="17"/>
+      <c r="A846" s="18"/>
+      <c r="B846" s="18"/>
     </row>
     <row r="847" ht="15.75" customHeight="1">
-      <c r="A847" s="17"/>
-      <c r="B847" s="17"/>
+      <c r="A847" s="18"/>
+      <c r="B847" s="18"/>
     </row>
     <row r="848" ht="15.75" customHeight="1">
-      <c r="A848" s="17"/>
-      <c r="B848" s="17"/>
+      <c r="A848" s="18"/>
+      <c r="B848" s="18"/>
     </row>
     <row r="849" ht="15.75" customHeight="1">
-      <c r="A849" s="17"/>
-      <c r="B849" s="17"/>
+      <c r="A849" s="18"/>
+      <c r="B849" s="18"/>
     </row>
     <row r="850" ht="15.75" customHeight="1">
-      <c r="A850" s="17"/>
-      <c r="B850" s="17"/>
+      <c r="A850" s="18"/>
+      <c r="B850" s="18"/>
     </row>
     <row r="851" ht="15.75" customHeight="1">
-      <c r="A851" s="17"/>
-      <c r="B851" s="17"/>
+      <c r="A851" s="18"/>
+      <c r="B851" s="18"/>
     </row>
     <row r="852" ht="15.75" customHeight="1">
-      <c r="A852" s="17"/>
-      <c r="B852" s="17"/>
+      <c r="A852" s="18"/>
+      <c r="B852" s="18"/>
     </row>
     <row r="853" ht="15.75" customHeight="1">
-      <c r="A853" s="17"/>
-      <c r="B853" s="17"/>
+      <c r="A853" s="18"/>
+      <c r="B853" s="18"/>
     </row>
     <row r="854" ht="15.75" customHeight="1">
-      <c r="A854" s="17"/>
-      <c r="B854" s="17"/>
+      <c r="A854" s="18"/>
+      <c r="B854" s="18"/>
     </row>
     <row r="855" ht="15.75" customHeight="1">
-      <c r="A855" s="17"/>
-      <c r="B855" s="17"/>
+      <c r="A855" s="18"/>
+      <c r="B855" s="18"/>
     </row>
     <row r="856" ht="15.75" customHeight="1">
-      <c r="A856" s="17"/>
-      <c r="B856" s="17"/>
+      <c r="A856" s="18"/>
+      <c r="B856" s="18"/>
     </row>
     <row r="857" ht="15.75" customHeight="1">
-      <c r="A857" s="17"/>
-      <c r="B857" s="17"/>
+      <c r="A857" s="18"/>
+      <c r="B857" s="18"/>
     </row>
     <row r="858" ht="15.75" customHeight="1">
-      <c r="A858" s="17"/>
-      <c r="B858" s="17"/>
+      <c r="A858" s="18"/>
+      <c r="B858" s="18"/>
     </row>
     <row r="859" ht="15.75" customHeight="1">
-      <c r="A859" s="17"/>
-      <c r="B859" s="17"/>
+      <c r="A859" s="18"/>
+      <c r="B859" s="18"/>
     </row>
     <row r="860" ht="15.75" customHeight="1">
-      <c r="A860" s="17"/>
-      <c r="B860" s="17"/>
+      <c r="A860" s="18"/>
+      <c r="B860" s="18"/>
     </row>
     <row r="861" ht="15.75" customHeight="1">
-      <c r="A861" s="17"/>
-      <c r="B861" s="17"/>
+      <c r="A861" s="18"/>
+      <c r="B861" s="18"/>
     </row>
     <row r="862" ht="15.75" customHeight="1">
-      <c r="A862" s="17"/>
-      <c r="B862" s="17"/>
+      <c r="A862" s="18"/>
+      <c r="B862" s="18"/>
     </row>
     <row r="863" ht="15.75" customHeight="1">
-      <c r="A863" s="17"/>
-      <c r="B863" s="17"/>
+      <c r="A863" s="18"/>
+      <c r="B863" s="18"/>
     </row>
     <row r="864" ht="15.75" customHeight="1">
-      <c r="A864" s="17"/>
-      <c r="B864" s="17"/>
+      <c r="A864" s="18"/>
+      <c r="B864" s="18"/>
     </row>
     <row r="865" ht="15.75" customHeight="1">
-      <c r="A865" s="17"/>
-      <c r="B865" s="17"/>
+      <c r="A865" s="18"/>
+      <c r="B865" s="18"/>
     </row>
     <row r="866" ht="15.75" customHeight="1">
-      <c r="A866" s="17"/>
-      <c r="B866" s="17"/>
+      <c r="A866" s="18"/>
+      <c r="B866" s="18"/>
     </row>
     <row r="867" ht="15.75" customHeight="1">
-      <c r="A867" s="17"/>
-      <c r="B867" s="17"/>
+      <c r="A867" s="18"/>
+      <c r="B867" s="18"/>
     </row>
     <row r="868" ht="15.75" customHeight="1">
-      <c r="A868" s="17"/>
-      <c r="B868" s="17"/>
+      <c r="A868" s="18"/>
+      <c r="B868" s="18"/>
     </row>
     <row r="869" ht="15.75" customHeight="1">
-      <c r="A869" s="17"/>
-      <c r="B869" s="17"/>
+      <c r="A869" s="18"/>
+      <c r="B869" s="18"/>
     </row>
     <row r="870" ht="15.75" customHeight="1">
-      <c r="A870" s="17"/>
-      <c r="B870" s="17"/>
+      <c r="A870" s="18"/>
+      <c r="B870" s="18"/>
     </row>
     <row r="871" ht="15.75" customHeight="1">
-      <c r="A871" s="17"/>
-      <c r="B871" s="17"/>
+      <c r="A871" s="18"/>
+      <c r="B871" s="18"/>
     </row>
     <row r="872" ht="15.75" customHeight="1">
-      <c r="A872" s="17"/>
-      <c r="B872" s="17"/>
+      <c r="A872" s="18"/>
+      <c r="B872" s="18"/>
     </row>
     <row r="873" ht="15.75" customHeight="1">
-      <c r="A873" s="17"/>
-      <c r="B873" s="17"/>
+      <c r="A873" s="18"/>
+      <c r="B873" s="18"/>
     </row>
     <row r="874" ht="15.75" customHeight="1">
-      <c r="A874" s="17"/>
-      <c r="B874" s="17"/>
+      <c r="A874" s="18"/>
+      <c r="B874" s="18"/>
     </row>
     <row r="875" ht="15.75" customHeight="1">
-      <c r="A875" s="17"/>
-      <c r="B875" s="17"/>
+      <c r="A875" s="18"/>
+      <c r="B875" s="18"/>
     </row>
     <row r="876" ht="15.75" customHeight="1">
-      <c r="A876" s="17"/>
-      <c r="B876" s="17"/>
+      <c r="A876" s="18"/>
+      <c r="B876" s="18"/>
     </row>
     <row r="877" ht="15.75" customHeight="1">
-      <c r="A877" s="17"/>
-      <c r="B877" s="17"/>
+      <c r="A877" s="18"/>
+      <c r="B877" s="18"/>
     </row>
     <row r="878" ht="15.75" customHeight="1">
-      <c r="A878" s="17"/>
-      <c r="B878" s="17"/>
+      <c r="A878" s="18"/>
+      <c r="B878" s="18"/>
     </row>
     <row r="879" ht="15.75" customHeight="1">
-      <c r="A879" s="17"/>
-      <c r="B879" s="17"/>
+      <c r="A879" s="18"/>
+      <c r="B879" s="18"/>
     </row>
     <row r="880" ht="15.75" customHeight="1">
-      <c r="A880" s="17"/>
-      <c r="B880" s="17"/>
+      <c r="A880" s="18"/>
+      <c r="B880" s="18"/>
     </row>
     <row r="881" ht="15.75" customHeight="1">
-      <c r="A881" s="17"/>
-      <c r="B881" s="17"/>
+      <c r="A881" s="18"/>
+      <c r="B881" s="18"/>
     </row>
     <row r="882" ht="15.75" customHeight="1">
-      <c r="A882" s="17"/>
-      <c r="B882" s="17"/>
+      <c r="A882" s="18"/>
+      <c r="B882" s="18"/>
     </row>
     <row r="883" ht="15.75" customHeight="1">
-      <c r="A883" s="17"/>
-      <c r="B883" s="17"/>
+      <c r="A883" s="18"/>
+      <c r="B883" s="18"/>
     </row>
     <row r="884" ht="15.75" customHeight="1">
-      <c r="A884" s="17"/>
-      <c r="B884" s="17"/>
+      <c r="A884" s="18"/>
+      <c r="B884" s="18"/>
     </row>
     <row r="885" ht="15.75" customHeight="1">
-      <c r="A885" s="17"/>
-      <c r="B885" s="17"/>
+      <c r="A885" s="18"/>
+      <c r="B885" s="18"/>
     </row>
     <row r="886" ht="15.75" customHeight="1">
-      <c r="A886" s="17"/>
-      <c r="B886" s="17"/>
+      <c r="A886" s="18"/>
+      <c r="B886" s="18"/>
     </row>
     <row r="887" ht="15.75" customHeight="1">
-      <c r="A887" s="17"/>
-      <c r="B887" s="17"/>
+      <c r="A887" s="18"/>
+      <c r="B887" s="18"/>
     </row>
     <row r="888" ht="15.75" customHeight="1">
-      <c r="A888" s="17"/>
-      <c r="B888" s="17"/>
+      <c r="A888" s="18"/>
+      <c r="B888" s="18"/>
     </row>
     <row r="889" ht="15.75" customHeight="1">
-      <c r="A889" s="17"/>
-      <c r="B889" s="17"/>
+      <c r="A889" s="18"/>
+      <c r="B889" s="18"/>
     </row>
     <row r="890" ht="15.75" customHeight="1">
-      <c r="A890" s="17"/>
-      <c r="B890" s="17"/>
+      <c r="A890" s="18"/>
+      <c r="B890" s="18"/>
     </row>
     <row r="891" ht="15.75" customHeight="1">
-      <c r="A891" s="17"/>
-      <c r="B891" s="17"/>
+      <c r="A891" s="18"/>
+      <c r="B891" s="18"/>
     </row>
     <row r="892" ht="15.75" customHeight="1">
-      <c r="A892" s="17"/>
-      <c r="B892" s="17"/>
+      <c r="A892" s="18"/>
+      <c r="B892" s="18"/>
     </row>
     <row r="893" ht="15.75" customHeight="1">
-      <c r="A893" s="17"/>
-      <c r="B893" s="17"/>
+      <c r="A893" s="18"/>
+      <c r="B893" s="18"/>
     </row>
     <row r="894" ht="15.75" customHeight="1">
-      <c r="A894" s="17"/>
-      <c r="B894" s="17"/>
+      <c r="A894" s="18"/>
+      <c r="B894" s="18"/>
     </row>
     <row r="895" ht="15.75" customHeight="1">
-      <c r="A895" s="17"/>
-      <c r="B895" s="17"/>
+      <c r="A895" s="18"/>
+      <c r="B895" s="18"/>
     </row>
     <row r="896" ht="15.75" customHeight="1">
-      <c r="A896" s="17"/>
-      <c r="B896" s="17"/>
+      <c r="A896" s="18"/>
+      <c r="B896" s="18"/>
     </row>
     <row r="897" ht="15.75" customHeight="1">
-      <c r="A897" s="17"/>
-      <c r="B897" s="17"/>
+      <c r="A897" s="18"/>
+      <c r="B897" s="18"/>
     </row>
     <row r="898" ht="15.75" customHeight="1">
-      <c r="A898" s="17"/>
-      <c r="B898" s="17"/>
+      <c r="A898" s="18"/>
+      <c r="B898" s="18"/>
     </row>
     <row r="899" ht="15.75" customHeight="1">
-      <c r="A899" s="17"/>
-      <c r="B899" s="17"/>
+      <c r="A899" s="18"/>
+      <c r="B899" s="18"/>
     </row>
     <row r="900" ht="15.75" customHeight="1">
-      <c r="A900" s="17"/>
-      <c r="B900" s="17"/>
+      <c r="A900" s="18"/>
+      <c r="B900" s="18"/>
     </row>
     <row r="901" ht="15.75" customHeight="1">
-      <c r="A901" s="17"/>
-      <c r="B901" s="17"/>
+      <c r="A901" s="18"/>
+      <c r="B901" s="18"/>
     </row>
     <row r="902" ht="15.75" customHeight="1">
-      <c r="A902" s="17"/>
-      <c r="B902" s="17"/>
+      <c r="A902" s="18"/>
+      <c r="B902" s="18"/>
     </row>
     <row r="903" ht="15.75" customHeight="1">
-      <c r="A903" s="17"/>
-      <c r="B903" s="17"/>
+      <c r="A903" s="18"/>
+      <c r="B903" s="18"/>
     </row>
     <row r="904" ht="15.75" customHeight="1">
-      <c r="A904" s="17"/>
-      <c r="B904" s="17"/>
+      <c r="A904" s="18"/>
+      <c r="B904" s="18"/>
     </row>
     <row r="905" ht="15.75" customHeight="1">
-      <c r="A905" s="17"/>
-      <c r="B905" s="17"/>
+      <c r="A905" s="18"/>
+      <c r="B905" s="18"/>
     </row>
     <row r="906" ht="15.75" customHeight="1">
-      <c r="A906" s="17"/>
-      <c r="B906" s="17"/>
+      <c r="A906" s="18"/>
+      <c r="B906" s="18"/>
     </row>
     <row r="907" ht="15.75" customHeight="1">
-      <c r="A907" s="17"/>
-      <c r="B907" s="17"/>
+      <c r="A907" s="18"/>
+      <c r="B907" s="18"/>
     </row>
     <row r="908" ht="15.75" customHeight="1">
-      <c r="A908" s="17"/>
-      <c r="B908" s="17"/>
+      <c r="A908" s="18"/>
+      <c r="B908" s="18"/>
     </row>
     <row r="909" ht="15.75" customHeight="1">
-      <c r="A909" s="17"/>
-      <c r="B909" s="17"/>
+      <c r="A909" s="18"/>
+      <c r="B909" s="18"/>
     </row>
     <row r="910" ht="15.75" customHeight="1">
-      <c r="A910" s="17"/>
-      <c r="B910" s="17"/>
+      <c r="A910" s="18"/>
+      <c r="B910" s="18"/>
     </row>
     <row r="911" ht="15.75" customHeight="1">
-      <c r="A911" s="17"/>
-      <c r="B911" s="17"/>
+      <c r="A911" s="18"/>
+      <c r="B911" s="18"/>
     </row>
     <row r="912" ht="15.75" customHeight="1">
-      <c r="A912" s="17"/>
-      <c r="B912" s="17"/>
+      <c r="A912" s="18"/>
+      <c r="B912" s="18"/>
     </row>
     <row r="913" ht="15.75" customHeight="1">
-      <c r="A913" s="17"/>
-      <c r="B913" s="17"/>
+      <c r="A913" s="18"/>
+      <c r="B913" s="18"/>
     </row>
     <row r="914" ht="15.75" customHeight="1">
-      <c r="A914" s="17"/>
-      <c r="B914" s="17"/>
+      <c r="A914" s="18"/>
+      <c r="B914" s="18"/>
     </row>
     <row r="915" ht="15.75" customHeight="1">
-      <c r="A915" s="17"/>
-      <c r="B915" s="17"/>
+      <c r="A915" s="18"/>
+      <c r="B915" s="18"/>
     </row>
     <row r="916" ht="15.75" customHeight="1">
-      <c r="A916" s="17"/>
-      <c r="B916" s="17"/>
+      <c r="A916" s="18"/>
+      <c r="B916" s="18"/>
     </row>
     <row r="917" ht="15.75" customHeight="1">
-      <c r="A917" s="17"/>
-      <c r="B917" s="17"/>
+      <c r="A917" s="18"/>
+      <c r="B917" s="18"/>
     </row>
     <row r="918" ht="15.75" customHeight="1">
-      <c r="A918" s="17"/>
-      <c r="B918" s="17"/>
+      <c r="A918" s="18"/>
+      <c r="B918" s="18"/>
     </row>
     <row r="919" ht="15.75" customHeight="1">
-      <c r="A919" s="17"/>
-      <c r="B919" s="17"/>
+      <c r="A919" s="18"/>
+      <c r="B919" s="18"/>
     </row>
     <row r="920" ht="15.75" customHeight="1">
-      <c r="A920" s="17"/>
-      <c r="B920" s="17"/>
+      <c r="A920" s="18"/>
+      <c r="B920" s="18"/>
     </row>
     <row r="921" ht="15.75" customHeight="1">
-      <c r="A921" s="17"/>
-      <c r="B921" s="17"/>
+      <c r="A921" s="18"/>
+      <c r="B921" s="18"/>
     </row>
     <row r="922" ht="15.75" customHeight="1">
-      <c r="A922" s="17"/>
-      <c r="B922" s="17"/>
+      <c r="A922" s="18"/>
+      <c r="B922" s="18"/>
     </row>
     <row r="923" ht="15.75" customHeight="1">
-      <c r="A923" s="17"/>
-      <c r="B923" s="17"/>
+      <c r="A923" s="18"/>
+      <c r="B923" s="18"/>
     </row>
     <row r="924" ht="15.75" customHeight="1">
-      <c r="A924" s="17"/>
-      <c r="B924" s="17"/>
+      <c r="A924" s="18"/>
+      <c r="B924" s="18"/>
     </row>
     <row r="925" ht="15.75" customHeight="1">
-      <c r="A925" s="17"/>
-      <c r="B925" s="17"/>
+      <c r="A925" s="18"/>
+      <c r="B925" s="18"/>
     </row>
     <row r="926" ht="15.75" customHeight="1">
-      <c r="A926" s="17"/>
-      <c r="B926" s="17"/>
+      <c r="A926" s="18"/>
+      <c r="B926" s="18"/>
     </row>
     <row r="927" ht="15.75" customHeight="1">
-      <c r="A927" s="17"/>
-      <c r="B927" s="17"/>
+      <c r="A927" s="18"/>
+      <c r="B927" s="18"/>
     </row>
     <row r="928" ht="15.75" customHeight="1">
-      <c r="A928" s="17"/>
-      <c r="B928" s="17"/>
+      <c r="A928" s="18"/>
+      <c r="B928" s="18"/>
     </row>
     <row r="929" ht="15.75" customHeight="1">
-      <c r="A929" s="17"/>
-      <c r="B929" s="17"/>
+      <c r="A929" s="18"/>
+      <c r="B929" s="18"/>
     </row>
     <row r="930" ht="15.75" customHeight="1">
-      <c r="A930" s="17"/>
-      <c r="B930" s="17"/>
+      <c r="A930" s="18"/>
+      <c r="B930" s="18"/>
     </row>
     <row r="931" ht="15.75" customHeight="1">
-      <c r="A931" s="17"/>
-      <c r="B931" s="17"/>
+      <c r="A931" s="18"/>
+      <c r="B931" s="18"/>
     </row>
     <row r="932" ht="15.75" customHeight="1">
-      <c r="A932" s="17"/>
-      <c r="B932" s="17"/>
+      <c r="A932" s="18"/>
+      <c r="B932" s="18"/>
     </row>
     <row r="933" ht="15.75" customHeight="1">
-      <c r="A933" s="17"/>
-      <c r="B933" s="17"/>
+      <c r="A933" s="18"/>
+      <c r="B933" s="18"/>
     </row>
     <row r="934" ht="15.75" customHeight="1">
-      <c r="A934" s="17"/>
-      <c r="B934" s="17"/>
+      <c r="A934" s="18"/>
+      <c r="B934" s="18"/>
     </row>
     <row r="935" ht="15.75" customHeight="1">
-      <c r="A935" s="17"/>
-      <c r="B935" s="17"/>
+      <c r="A935" s="18"/>
+      <c r="B935" s="18"/>
     </row>
     <row r="936" ht="15.75" customHeight="1">
-      <c r="A936" s="17"/>
-      <c r="B936" s="17"/>
+      <c r="A936" s="18"/>
+      <c r="B936" s="18"/>
     </row>
     <row r="937" ht="15.75" customHeight="1">
-      <c r="A937" s="17"/>
-      <c r="B937" s="17"/>
+      <c r="A937" s="18"/>
+      <c r="B937" s="18"/>
     </row>
     <row r="938" ht="15.75" customHeight="1">
-      <c r="A938" s="17"/>
-      <c r="B938" s="17"/>
+      <c r="A938" s="18"/>
+      <c r="B938" s="18"/>
     </row>
     <row r="939" ht="15.75" customHeight="1">
-      <c r="A939" s="17"/>
-      <c r="B939" s="17"/>
+      <c r="A939" s="18"/>
+      <c r="B939" s="18"/>
     </row>
     <row r="940" ht="15.75" customHeight="1">
-      <c r="A940" s="17"/>
-      <c r="B940" s="17"/>
+      <c r="A940" s="18"/>
+      <c r="B940" s="18"/>
     </row>
     <row r="941" ht="15.75" customHeight="1">
-      <c r="A941" s="17"/>
-      <c r="B941" s="17"/>
+      <c r="A941" s="18"/>
+      <c r="B941" s="18"/>
     </row>
     <row r="942" ht="15.75" customHeight="1">
-      <c r="A942" s="17"/>
-      <c r="B942" s="17"/>
+      <c r="A942" s="18"/>
+      <c r="B942" s="18"/>
     </row>
     <row r="943" ht="15.75" customHeight="1">
-      <c r="A943" s="17"/>
-      <c r="B943" s="17"/>
+      <c r="A943" s="18"/>
+      <c r="B943" s="18"/>
     </row>
     <row r="944" ht="15.75" customHeight="1">
-      <c r="A944" s="17"/>
-      <c r="B944" s="17"/>
+      <c r="A944" s="18"/>
+      <c r="B944" s="18"/>
     </row>
     <row r="945" ht="15.75" customHeight="1">
-      <c r="A945" s="17"/>
-      <c r="B945" s="17"/>
+      <c r="A945" s="18"/>
+      <c r="B945" s="18"/>
     </row>
     <row r="946" ht="15.75" customHeight="1">
-      <c r="A946" s="17"/>
-      <c r="B946" s="17"/>
+      <c r="A946" s="18"/>
+      <c r="B946" s="18"/>
     </row>
     <row r="947" ht="15.75" customHeight="1">
-      <c r="A947" s="17"/>
-      <c r="B947" s="17"/>
+      <c r="A947" s="18"/>
+      <c r="B947" s="18"/>
     </row>
     <row r="948" ht="15.75" customHeight="1">
-      <c r="A948" s="17"/>
-      <c r="B948" s="17"/>
+      <c r="A948" s="18"/>
+      <c r="B948" s="18"/>
     </row>
     <row r="949" ht="15.75" customHeight="1">
-      <c r="A949" s="17"/>
-      <c r="B949" s="17"/>
+      <c r="A949" s="18"/>
+      <c r="B949" s="18"/>
     </row>
     <row r="950" ht="15.75" customHeight="1">
-      <c r="A950" s="17"/>
-      <c r="B950" s="17"/>
+      <c r="A950" s="18"/>
+      <c r="B950" s="18"/>
     </row>
     <row r="951" ht="15.75" customHeight="1">
-      <c r="A951" s="17"/>
-      <c r="B951" s="17"/>
+      <c r="A951" s="18"/>
+      <c r="B951" s="18"/>
     </row>
     <row r="952" ht="15.75" customHeight="1">
-      <c r="A952" s="17"/>
-      <c r="B952" s="17"/>
+      <c r="A952" s="18"/>
+      <c r="B952" s="18"/>
     </row>
     <row r="953" ht="15.75" customHeight="1">
-      <c r="A953" s="17"/>
-      <c r="B953" s="17"/>
+      <c r="A953" s="18"/>
+      <c r="B953" s="18"/>
     </row>
     <row r="954" ht="15.75" customHeight="1">
-      <c r="A954" s="17"/>
-      <c r="B954" s="17"/>
+      <c r="A954" s="18"/>
+      <c r="B954" s="18"/>
     </row>
     <row r="955" ht="15.75" customHeight="1">
-      <c r="A955" s="17"/>
-      <c r="B955" s="17"/>
+      <c r="A955" s="18"/>
+      <c r="B955" s="18"/>
     </row>
     <row r="956" ht="15.75" customHeight="1">
-      <c r="A956" s="17"/>
-      <c r="B956" s="17"/>
+      <c r="A956" s="18"/>
+      <c r="B956" s="18"/>
     </row>
     <row r="957" ht="15.75" customHeight="1">
-      <c r="A957" s="17"/>
-      <c r="B957" s="17"/>
+      <c r="A957" s="18"/>
+      <c r="B957" s="18"/>
     </row>
     <row r="958" ht="15.75" customHeight="1">
-      <c r="A958" s="17"/>
-      <c r="B958" s="17"/>
+      <c r="A958" s="18"/>
+      <c r="B958" s="18"/>
     </row>
     <row r="959" ht="15.75" customHeight="1">
-      <c r="A959" s="17"/>
-      <c r="B959" s="17"/>
+      <c r="A959" s="18"/>
+      <c r="B959" s="18"/>
     </row>
     <row r="960" ht="15.75" customHeight="1">
-      <c r="A960" s="17"/>
-      <c r="B960" s="17"/>
+      <c r="A960" s="18"/>
+      <c r="B960" s="18"/>
     </row>
     <row r="961" ht="15.75" customHeight="1">
-      <c r="A961" s="17"/>
-      <c r="B961" s="17"/>
+      <c r="A961" s="18"/>
+      <c r="B961" s="18"/>
     </row>
     <row r="962" ht="15.75" customHeight="1">
-      <c r="A962" s="17"/>
-      <c r="B962" s="17"/>
+      <c r="A962" s="18"/>
+      <c r="B962" s="18"/>
     </row>
     <row r="963" ht="15.75" customHeight="1">
-      <c r="A963" s="17"/>
-      <c r="B963" s="17"/>
+      <c r="A963" s="18"/>
+      <c r="B963" s="18"/>
     </row>
     <row r="964" ht="15.75" customHeight="1">
-      <c r="A964" s="17"/>
-      <c r="B964" s="17"/>
+      <c r="A964" s="18"/>
+      <c r="B964" s="18"/>
     </row>
     <row r="965" ht="15.75" customHeight="1">
-      <c r="A965" s="17"/>
-      <c r="B965" s="17"/>
+      <c r="A965" s="18"/>
+      <c r="B965" s="18"/>
     </row>
     <row r="966" ht="15.75" customHeight="1">
-      <c r="A966" s="17"/>
-      <c r="B966" s="17"/>
+      <c r="A966" s="18"/>
+      <c r="B966" s="18"/>
     </row>
     <row r="967" ht="15.75" customHeight="1">
-      <c r="A967" s="17"/>
-      <c r="B967" s="17"/>
+      <c r="A967" s="18"/>
+      <c r="B967" s="18"/>
     </row>
     <row r="968" ht="15.75" customHeight="1">
-      <c r="A968" s="17"/>
-      <c r="B968" s="17"/>
+      <c r="A968" s="18"/>
+      <c r="B968" s="18"/>
     </row>
     <row r="969" ht="15.75" customHeight="1">
-      <c r="A969" s="17"/>
-      <c r="B969" s="17"/>
+      <c r="A969" s="18"/>
+      <c r="B969" s="18"/>
     </row>
     <row r="970" ht="15.75" customHeight="1">
-      <c r="A970" s="17"/>
-      <c r="B970" s="17"/>
+      <c r="A970" s="18"/>
+      <c r="B970" s="18"/>
     </row>
     <row r="971" ht="15.75" customHeight="1">
-      <c r="A971" s="17"/>
-      <c r="B971" s="17"/>
+      <c r="A971" s="18"/>
+      <c r="B971" s="18"/>
     </row>
     <row r="972" ht="15.75" customHeight="1">
-      <c r="A972" s="17"/>
-      <c r="B972" s="17"/>
+      <c r="A972" s="18"/>
+      <c r="B972" s="18"/>
     </row>
     <row r="973" ht="15.75" customHeight="1">
-      <c r="A973" s="17"/>
-      <c r="B973" s="17"/>
+      <c r="A973" s="18"/>
+      <c r="B973" s="18"/>
     </row>
     <row r="974" ht="15.75" customHeight="1">
-      <c r="A974" s="17"/>
-      <c r="B974" s="17"/>
+      <c r="A974" s="18"/>
+      <c r="B974" s="18"/>
     </row>
     <row r="975" ht="15.75" customHeight="1">
-      <c r="A975" s="17"/>
-      <c r="B975" s="17"/>
+      <c r="A975" s="18"/>
+      <c r="B975" s="18"/>
     </row>
     <row r="976" ht="15.75" customHeight="1">
-      <c r="A976" s="17"/>
-      <c r="B976" s="17"/>
+      <c r="A976" s="18"/>
+      <c r="B976" s="18"/>
     </row>
     <row r="977" ht="15.75" customHeight="1">
-      <c r="A977" s="17"/>
-      <c r="B977" s="17"/>
+      <c r="A977" s="18"/>
+      <c r="B977" s="18"/>
     </row>
     <row r="978" ht="15.75" customHeight="1">
-      <c r="A978" s="17"/>
-      <c r="B978" s="17"/>
+      <c r="A978" s="18"/>
+      <c r="B978" s="18"/>
     </row>
     <row r="979" ht="15.75" customHeight="1">
-      <c r="A979" s="17"/>
-      <c r="B979" s="17"/>
+      <c r="A979" s="18"/>
+      <c r="B979" s="18"/>
     </row>
     <row r="980" ht="15.75" customHeight="1">
-      <c r="A980" s="17"/>
-      <c r="B980" s="17"/>
+      <c r="A980" s="18"/>
+      <c r="B980" s="18"/>
     </row>
     <row r="981" ht="15.75" customHeight="1">
-      <c r="A981" s="17"/>
-      <c r="B981" s="17"/>
+      <c r="A981" s="18"/>
+      <c r="B981" s="18"/>
     </row>
     <row r="982" ht="15.75" customHeight="1">
-      <c r="A982" s="17"/>
-      <c r="B982" s="17"/>
+      <c r="A982" s="18"/>
+      <c r="B982" s="18"/>
     </row>
     <row r="983" ht="15.75" customHeight="1">
-      <c r="A983" s="17"/>
-      <c r="B983" s="17"/>
+      <c r="A983" s="18"/>
+      <c r="B983" s="18"/>
     </row>
     <row r="984" ht="15.75" customHeight="1">
-      <c r="A984" s="17"/>
-      <c r="B984" s="17"/>
+      <c r="A984" s="18"/>
+      <c r="B984" s="18"/>
     </row>
     <row r="985" ht="15.75" customHeight="1">
-      <c r="A985" s="17"/>
-      <c r="B985" s="17"/>
+      <c r="A985" s="18"/>
+      <c r="B985" s="18"/>
     </row>
     <row r="986" ht="15.75" customHeight="1">
-      <c r="A986" s="17"/>
-      <c r="B986" s="17"/>
+      <c r="A986" s="18"/>
+      <c r="B986" s="18"/>
     </row>
     <row r="987" ht="15.75" customHeight="1">
-      <c r="A987" s="17"/>
-      <c r="B987" s="17"/>
+      <c r="A987" s="18"/>
+      <c r="B987" s="18"/>
     </row>
     <row r="988" ht="15.75" customHeight="1">
-      <c r="A988" s="17"/>
-      <c r="B988" s="17"/>
+      <c r="A988" s="18"/>
+      <c r="B988" s="18"/>
     </row>
     <row r="989" ht="15.75" customHeight="1">
-      <c r="A989" s="17"/>
-      <c r="B989" s="17"/>
+      <c r="A989" s="18"/>
+      <c r="B989" s="18"/>
     </row>
     <row r="990" ht="15.75" customHeight="1">
-      <c r="A990" s="17"/>
-      <c r="B990" s="17"/>
+      <c r="A990" s="18"/>
+      <c r="B990" s="18"/>
     </row>
     <row r="991" ht="15.75" customHeight="1">
-      <c r="A991" s="17"/>
-      <c r="B991" s="17"/>
+      <c r="A991" s="18"/>
+      <c r="B991" s="18"/>
     </row>
     <row r="992" ht="15.75" customHeight="1">
-      <c r="A992" s="17"/>
-      <c r="B992" s="17"/>
+      <c r="A992" s="18"/>
+      <c r="B992" s="18"/>
     </row>
     <row r="993" ht="15.75" customHeight="1">
-      <c r="A993" s="17"/>
-      <c r="B993" s="17"/>
+      <c r="A993" s="18"/>
+      <c r="B993" s="18"/>
     </row>
     <row r="994" ht="15.75" customHeight="1">
-      <c r="A994" s="17"/>
-      <c r="B994" s="17"/>
+      <c r="A994" s="18"/>
+      <c r="B994" s="18"/>
     </row>
     <row r="995" ht="15.75" customHeight="1">
-      <c r="A995" s="17"/>
-      <c r="B995" s="17"/>
+      <c r="A995" s="18"/>
+      <c r="B995" s="18"/>
     </row>
     <row r="996" ht="15.75" customHeight="1">
-      <c r="A996" s="17"/>
-      <c r="B996" s="17"/>
+      <c r="A996" s="18"/>
+      <c r="B996" s="18"/>
     </row>
     <row r="997" ht="15.75" customHeight="1">
-      <c r="A997" s="17"/>
-      <c r="B997" s="17"/>
+      <c r="A997" s="18"/>
+      <c r="B997" s="18"/>
     </row>
     <row r="998" ht="15.75" customHeight="1">
-      <c r="A998" s="17"/>
-      <c r="B998" s="17"/>
+      <c r="A998" s="18"/>
+      <c r="B998" s="18"/>
     </row>
     <row r="999" ht="15.75" customHeight="1">
-      <c r="A999" s="17"/>
-      <c r="B999" s="17"/>
+      <c r="A999" s="18"/>
+      <c r="B999" s="18"/>
     </row>
     <row r="1000" ht="15.75" customHeight="1">
-      <c r="A1000" s="17"/>
-      <c r="B1000" s="17"/>
+      <c r="A1000" s="18"/>
+      <c r="B1000" s="18"/>
     </row>
   </sheetData>
   <printOptions/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -9,14 +9,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PSHgN1/kfcCjDd8eM0S9gC4F43mGfiTG0/AQb1lJB4c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1vHpoHAi14pJrWCrnqynttxKRttNcSH5KaN2SCCJsnE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="143">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -93,10 +93,7 @@
     <t>MeshPath</t>
   </si>
   <si>
-    <t>Husks</t>
-  </si>
-  <si>
-    <t>HoldType</t>
+    <t>StringHoldType</t>
   </si>
   <si>
     <t>MeshCollider</t>
@@ -124,9 +121,6 @@
     <t>KeyFBX[SM_Gen_Prop_Key_01]</t>
   </si>
   <si>
-    <t>ToolObject</t>
-  </si>
-  <si>
     <t>Hold</t>
   </si>
   <si>
@@ -164,9 +158,6 @@
     <t>Jewel_Cone[Cone]</t>
   </si>
   <si>
-    <t>JewelObject</t>
-  </si>
-  <si>
     <t>Item_Jewel_Amethyst</t>
   </si>
   <si>
@@ -266,9 +257,6 @@
     <t>Painting_1_Mesh[Painting_1]</t>
   </si>
   <si>
-    <t>PaintingObject</t>
-  </si>
-  <si>
     <t>Item_Painting_02</t>
   </si>
   <si>
@@ -323,9 +311,6 @@
     <t>SeatedLion[Seated_Lion_LOD0]</t>
   </si>
   <si>
-    <t>StatueObject</t>
-  </si>
-  <si>
     <t>Item_Statue_Copper</t>
   </si>
   <si>
@@ -380,9 +365,6 @@
     <t>Junk_Bottle_Blue[SM_Prop_Bar_Bottle_07]</t>
   </si>
   <si>
-    <t>JunkObject</t>
-  </si>
-  <si>
     <t>MeshCollider_Junk_Bottle_Blue</t>
   </si>
   <si>
@@ -395,7 +377,7 @@
     <t>크기가 큰 핑크색 병이다.</t>
   </si>
   <si>
-    <t>Junk_Bottle_Pink_Large[SM_Prop_Bar_Bottle_Lage_01]</t>
+    <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
   </si>
   <si>
     <t>MeshCollider_Junk_Bottle_Pink_Large</t>
@@ -832,8 +814,8 @@
     <col customWidth="1" min="9" max="9" width="8.63"/>
     <col customWidth="1" min="10" max="10" width="21.25"/>
     <col customWidth="1" min="11" max="11" width="28.38"/>
-    <col customWidth="1" min="12" max="12" width="11.75"/>
-    <col customWidth="1" min="13" max="21" width="9.63"/>
+    <col customWidth="1" min="12" max="12" width="16.13"/>
+    <col customWidth="1" min="13" max="20" width="9.63"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -866,10 +848,10 @@
       </c>
       <c r="J1" s="4"/>
       <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>9</v>
       </c>
+      <c r="M1" s="4"/>
       <c r="N1" s="4"/>
       <c r="O1" s="4"/>
       <c r="P1" s="4"/>
@@ -877,7 +859,6 @@
       <c r="R1" s="4"/>
       <c r="S1" s="4"/>
       <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -913,22 +894,19 @@
       <c r="K2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="3" t="s">
-        <v>10</v>
-      </c>
+      <c r="N2" s="4"/>
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
       <c r="R2" s="4"/>
       <c r="S2" s="4"/>
       <c r="T2" s="4"/>
-      <c r="U2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="8" t="s">
@@ -964,38 +942,35 @@
       <c r="K3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="9" t="s">
-        <v>27</v>
-      </c>
+      <c r="N3" s="10"/>
       <c r="O3" s="10"/>
       <c r="P3" s="10"/>
       <c r="Q3" s="10"/>
       <c r="R3" s="10"/>
       <c r="S3" s="10"/>
       <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
     </row>
     <row r="4" ht="15.0" customHeight="1">
       <c r="A4" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="F4" s="4">
         <v>2.0</v>
@@ -1008,17 +983,15 @@
         <v>-1.0</v>
       </c>
       <c r="J4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="L4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
@@ -1026,23 +999,22 @@
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
       <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
     </row>
     <row r="5" ht="15.0" customHeight="1">
       <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="D5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>40</v>
       </c>
       <c r="F5" s="4">
         <v>1.0</v>
@@ -1055,17 +1027,15 @@
         <v>1.0</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>36</v>
-      </c>
+      <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
       <c r="P5" s="4"/>
@@ -1073,23 +1043,22 @@
       <c r="R5" s="4"/>
       <c r="S5" s="4"/>
       <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
     </row>
     <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="D6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>45</v>
-      </c>
       <c r="E6" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F6" s="4">
         <v>10.0</v>
@@ -1100,17 +1069,15 @@
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
       <c r="J6" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>36</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
@@ -1118,23 +1085,22 @@
       <c r="R6" s="4"/>
       <c r="S6" s="4"/>
       <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
     </row>
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F7" s="4">
         <v>8.0</v>
@@ -1145,17 +1111,15 @@
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
       <c r="J7" s="4" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
@@ -1163,23 +1127,22 @@
       <c r="R7" s="4"/>
       <c r="S7" s="4"/>
       <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>54</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>57</v>
       </c>
       <c r="F8" s="4">
         <v>7.0</v>
@@ -1190,17 +1153,15 @@
       <c r="H8" s="4"/>
       <c r="I8" s="4"/>
       <c r="J8" s="4" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
@@ -1208,23 +1169,22 @@
       <c r="R8" s="4"/>
       <c r="S8" s="4"/>
       <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F9" s="4">
         <v>6.0</v>
@@ -1235,17 +1195,15 @@
       <c r="H9" s="4"/>
       <c r="I9" s="4"/>
       <c r="J9" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
@@ -1253,23 +1211,22 @@
       <c r="R9" s="4"/>
       <c r="S9" s="4"/>
       <c r="T9" s="4"/>
-      <c r="U9" s="4"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F10" s="4">
         <v>5.0</v>
@@ -1280,17 +1237,15 @@
       <c r="H10" s="4"/>
       <c r="I10" s="4"/>
       <c r="J10" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>36</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="4"/>
@@ -1298,23 +1253,22 @@
       <c r="R10" s="4"/>
       <c r="S10" s="4"/>
       <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>70</v>
       </c>
       <c r="F11" s="4">
         <v>4.0</v>
@@ -1325,17 +1279,15 @@
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
       <c r="J11" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="4"/>
@@ -1343,23 +1295,22 @@
       <c r="R11" s="4"/>
       <c r="S11" s="4"/>
       <c r="T11" s="4"/>
-      <c r="U11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F12" s="4">
         <v>3.0</v>
@@ -1370,17 +1321,15 @@
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
       <c r="J12" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>53</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="4"/>
@@ -1388,23 +1337,22 @@
       <c r="R12" s="4"/>
       <c r="S12" s="4"/>
       <c r="T12" s="4"/>
-      <c r="U12" s="4"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="B13" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>79</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F13" s="14">
         <v>12.0</v>
@@ -1415,17 +1363,15 @@
       <c r="H13" s="15"/>
       <c r="I13" s="15"/>
       <c r="J13" s="13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="L13" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M13" s="15"/>
       <c r="N13" s="15"/>
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
@@ -1433,23 +1379,22 @@
       <c r="R13" s="15"/>
       <c r="S13" s="15"/>
       <c r="T13" s="15"/>
-      <c r="U13" s="15"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F14" s="14">
         <v>12.0</v>
@@ -1460,17 +1405,15 @@
       <c r="H14" s="15"/>
       <c r="I14" s="15"/>
       <c r="J14" s="13" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="L14" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M14" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M14" s="15"/>
       <c r="N14" s="15"/>
       <c r="O14" s="15"/>
       <c r="P14" s="15"/>
@@ -1478,23 +1421,22 @@
       <c r="R14" s="15"/>
       <c r="S14" s="15"/>
       <c r="T14" s="15"/>
-      <c r="U14" s="15"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D15" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F15" s="14">
         <v>12.0</v>
@@ -1505,17 +1447,15 @@
       <c r="H15" s="15"/>
       <c r="I15" s="15"/>
       <c r="J15" s="13" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="L15" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M15" s="15"/>
       <c r="N15" s="15"/>
       <c r="O15" s="15"/>
       <c r="P15" s="15"/>
@@ -1523,23 +1463,22 @@
       <c r="R15" s="15"/>
       <c r="S15" s="15"/>
       <c r="T15" s="15"/>
-      <c r="U15" s="15"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F16" s="14">
         <v>12.0</v>
@@ -1550,17 +1489,15 @@
       <c r="H16" s="15"/>
       <c r="I16" s="15"/>
       <c r="J16" s="13" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M16" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M16" s="15"/>
       <c r="N16" s="15"/>
       <c r="O16" s="15"/>
       <c r="P16" s="15"/>
@@ -1568,23 +1505,22 @@
       <c r="R16" s="15"/>
       <c r="S16" s="15"/>
       <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D17" s="13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F17" s="14">
         <v>12.0</v>
@@ -1595,17 +1531,15 @@
       <c r="H17" s="15"/>
       <c r="I17" s="15"/>
       <c r="J17" s="13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M17" s="15"/>
       <c r="N17" s="15"/>
       <c r="O17" s="15"/>
       <c r="P17" s="15"/>
@@ -1613,23 +1547,22 @@
       <c r="R17" s="15"/>
       <c r="S17" s="15"/>
       <c r="T17" s="15"/>
-      <c r="U17" s="15"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="13" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D18" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F18" s="14">
         <v>5.0</v>
@@ -1640,17 +1573,15 @@
       <c r="H18" s="15"/>
       <c r="I18" s="15"/>
       <c r="J18" s="13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
       <c r="P18" s="4"/>
@@ -1658,23 +1589,22 @@
       <c r="R18" s="4"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
-      <c r="U18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D19" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F19" s="14">
         <v>10.0</v>
@@ -1685,17 +1615,15 @@
       <c r="H19" s="15"/>
       <c r="I19" s="15"/>
       <c r="J19" s="13" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M19" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
       <c r="P19" s="4"/>
@@ -1703,23 +1631,22 @@
       <c r="R19" s="4"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
-      <c r="U19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D20" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F20" s="14">
         <v>15.0</v>
@@ -1730,17 +1657,15 @@
       <c r="H20" s="15"/>
       <c r="I20" s="15"/>
       <c r="J20" s="13" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
@@ -1748,23 +1673,22 @@
       <c r="R20" s="4"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
-      <c r="U20" s="4"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F21" s="14">
         <v>20.0</v>
@@ -1775,17 +1699,15 @@
       <c r="H21" s="15"/>
       <c r="I21" s="15"/>
       <c r="J21" s="13" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="K21" s="13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L21" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="M21" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
@@ -1793,23 +1715,22 @@
       <c r="R21" s="4"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
-      <c r="U21" s="4"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F22" s="14">
         <v>5.0</v>
@@ -1820,41 +1741,38 @@
       <c r="H22" s="4"/>
       <c r="I22" s="4"/>
       <c r="J22" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M22" s="4"/>
-      <c r="N22" s="3" t="s">
-        <v>121</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="L22" s="4"/>
+      <c r="M22" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N22" s="4"/>
       <c r="O22" s="4"/>
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
       <c r="R22" s="4"/>
       <c r="S22" s="4"/>
       <c r="T22" s="4"/>
-      <c r="U22" s="4"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" s="14">
         <v>5.0</v>
@@ -1865,41 +1783,38 @@
       <c r="H23" s="4"/>
       <c r="I23" s="4"/>
       <c r="J23" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="L23" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="L23" s="4"/>
+      <c r="M23" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="M23" s="4"/>
-      <c r="N23" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="N23" s="4"/>
       <c r="O23" s="4"/>
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
       <c r="R23" s="4"/>
       <c r="S23" s="4"/>
       <c r="T23" s="4"/>
-      <c r="U23" s="4"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F24" s="14">
         <v>5.0</v>
@@ -1910,14 +1825,12 @@
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
       <c r="J24" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>120</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
@@ -1926,23 +1839,22 @@
       <c r="R24" s="4"/>
       <c r="S24" s="4"/>
       <c r="T24" s="4"/>
-      <c r="U24" s="4"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F25" s="14">
         <v>15.0</v>
@@ -1953,13 +1865,13 @@
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
       <c r="J25" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>120</v>
+        <v>128</v>
+      </c>
+      <c r="L25" s="13" t="s">
+        <v>34</v>
       </c>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
@@ -1969,23 +1881,22 @@
       <c r="R25" s="4"/>
       <c r="S25" s="4"/>
       <c r="T25" s="4"/>
-      <c r="U25" s="4"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F26" s="14">
         <v>5.0</v>
@@ -1996,41 +1907,38 @@
       <c r="H26" s="4"/>
       <c r="I26" s="4"/>
       <c r="J26" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="3" t="s">
-        <v>139</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="N26" s="4"/>
       <c r="O26" s="4"/>
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="4"/>
       <c r="T26" s="4"/>
-      <c r="U26" s="4"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F27" s="14">
         <v>5.0</v>
@@ -2041,10 +1949,10 @@
       <c r="H27" s="4"/>
       <c r="I27" s="4"/>
       <c r="J27" s="3" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
@@ -2055,23 +1963,22 @@
       <c r="R27" s="4"/>
       <c r="S27" s="4"/>
       <c r="T27" s="4"/>
-      <c r="U27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F28" s="14">
         <v>20.0</v>
@@ -2082,10 +1989,10 @@
       <c r="H28" s="4"/>
       <c r="I28" s="4"/>
       <c r="J28" s="3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
@@ -2096,7 +2003,6 @@
       <c r="R28" s="4"/>
       <c r="S28" s="4"/>
       <c r="T28" s="4"/>
-      <c r="U28" s="4"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4"/>
@@ -2119,7 +2025,6 @@
       <c r="R29" s="4"/>
       <c r="S29" s="4"/>
       <c r="T29" s="4"/>
-      <c r="U29" s="4"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4"/>
@@ -2142,7 +2047,6 @@
       <c r="R30" s="4"/>
       <c r="S30" s="4"/>
       <c r="T30" s="4"/>
-      <c r="U30" s="4"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4"/>
@@ -2165,7 +2069,6 @@
       <c r="R31" s="4"/>
       <c r="S31" s="4"/>
       <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4"/>
@@ -2188,7 +2091,6 @@
       <c r="R32" s="4"/>
       <c r="S32" s="4"/>
       <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4"/>
@@ -2211,7 +2113,6 @@
       <c r="R33" s="4"/>
       <c r="S33" s="4"/>
       <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4"/>
@@ -2234,7 +2135,6 @@
       <c r="R34" s="4"/>
       <c r="S34" s="4"/>
       <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="4"/>
@@ -2257,7 +2157,6 @@
       <c r="R35" s="4"/>
       <c r="S35" s="4"/>
       <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="4"/>
@@ -2280,7 +2179,6 @@
       <c r="R36" s="4"/>
       <c r="S36" s="4"/>
       <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="4"/>
@@ -2303,7 +2201,6 @@
       <c r="R37" s="4"/>
       <c r="S37" s="4"/>
       <c r="T37" s="4"/>
-      <c r="U37" s="4"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4"/>
@@ -2326,7 +2223,6 @@
       <c r="R38" s="4"/>
       <c r="S38" s="4"/>
       <c r="T38" s="4"/>
-      <c r="U38" s="4"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4"/>
@@ -2349,7 +2245,6 @@
       <c r="R39" s="4"/>
       <c r="S39" s="4"/>
       <c r="T39" s="4"/>
-      <c r="U39" s="4"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4"/>
@@ -2372,7 +2267,6 @@
       <c r="R40" s="4"/>
       <c r="S40" s="4"/>
       <c r="T40" s="4"/>
-      <c r="U40" s="4"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4"/>
@@ -2395,7 +2289,6 @@
       <c r="R41" s="4"/>
       <c r="S41" s="4"/>
       <c r="T41" s="4"/>
-      <c r="U41" s="4"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="4"/>
@@ -2418,7 +2311,6 @@
       <c r="R42" s="4"/>
       <c r="S42" s="4"/>
       <c r="T42" s="4"/>
-      <c r="U42" s="4"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="4"/>
@@ -2441,7 +2333,6 @@
       <c r="R43" s="4"/>
       <c r="S43" s="4"/>
       <c r="T43" s="4"/>
-      <c r="U43" s="4"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4"/>
@@ -2464,7 +2355,6 @@
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
-      <c r="U44" s="4"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4"/>
@@ -2487,7 +2377,6 @@
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
-      <c r="U45" s="4"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="4"/>
@@ -2510,7 +2399,6 @@
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
-      <c r="U46" s="4"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4"/>
@@ -2533,7 +2421,6 @@
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
-      <c r="U47" s="4"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4"/>
@@ -2556,7 +2443,6 @@
       <c r="R48" s="4"/>
       <c r="S48" s="4"/>
       <c r="T48" s="4"/>
-      <c r="U48" s="4"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4"/>
@@ -2579,7 +2465,6 @@
       <c r="R49" s="4"/>
       <c r="S49" s="4"/>
       <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4"/>
@@ -2602,7 +2487,6 @@
       <c r="R50" s="4"/>
       <c r="S50" s="4"/>
       <c r="T50" s="4"/>
-      <c r="U50" s="4"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4"/>
@@ -2625,7 +2509,6 @@
       <c r="R51" s="4"/>
       <c r="S51" s="4"/>
       <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4"/>
@@ -2648,7 +2531,6 @@
       <c r="R52" s="4"/>
       <c r="S52" s="4"/>
       <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4"/>
@@ -2671,7 +2553,6 @@
       <c r="R53" s="4"/>
       <c r="S53" s="4"/>
       <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4"/>
@@ -2694,7 +2575,6 @@
       <c r="R54" s="4"/>
       <c r="S54" s="4"/>
       <c r="T54" s="4"/>
-      <c r="U54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4"/>
@@ -2717,7 +2597,6 @@
       <c r="R55" s="4"/>
       <c r="S55" s="4"/>
       <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4"/>
@@ -2740,7 +2619,6 @@
       <c r="R56" s="4"/>
       <c r="S56" s="4"/>
       <c r="T56" s="4"/>
-      <c r="U56" s="4"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4"/>
@@ -2763,7 +2641,6 @@
       <c r="R57" s="4"/>
       <c r="S57" s="4"/>
       <c r="T57" s="4"/>
-      <c r="U57" s="4"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="4"/>
@@ -2786,7 +2663,6 @@
       <c r="R58" s="4"/>
       <c r="S58" s="4"/>
       <c r="T58" s="4"/>
-      <c r="U58" s="4"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="4"/>
@@ -2809,7 +2685,6 @@
       <c r="R59" s="4"/>
       <c r="S59" s="4"/>
       <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="4"/>
@@ -2832,7 +2707,6 @@
       <c r="R60" s="4"/>
       <c r="S60" s="4"/>
       <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="4"/>
@@ -2855,7 +2729,6 @@
       <c r="R61" s="4"/>
       <c r="S61" s="4"/>
       <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="4"/>
@@ -2878,7 +2751,6 @@
       <c r="R62" s="4"/>
       <c r="S62" s="4"/>
       <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="4"/>
@@ -2901,7 +2773,6 @@
       <c r="R63" s="4"/>
       <c r="S63" s="4"/>
       <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4"/>
@@ -2924,7 +2795,6 @@
       <c r="R64" s="4"/>
       <c r="S64" s="4"/>
       <c r="T64" s="4"/>
-      <c r="U64" s="4"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4"/>
@@ -2947,7 +2817,6 @@
       <c r="R65" s="4"/>
       <c r="S65" s="4"/>
       <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4"/>
@@ -2970,7 +2839,6 @@
       <c r="R66" s="4"/>
       <c r="S66" s="4"/>
       <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4"/>
@@ -2993,7 +2861,6 @@
       <c r="R67" s="4"/>
       <c r="S67" s="4"/>
       <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4"/>
@@ -3016,7 +2883,6 @@
       <c r="R68" s="4"/>
       <c r="S68" s="4"/>
       <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4"/>
@@ -3039,7 +2905,6 @@
       <c r="R69" s="4"/>
       <c r="S69" s="4"/>
       <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4"/>
@@ -3062,7 +2927,6 @@
       <c r="R70" s="4"/>
       <c r="S70" s="4"/>
       <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4"/>
@@ -3085,7 +2949,6 @@
       <c r="R71" s="4"/>
       <c r="S71" s="4"/>
       <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4"/>
@@ -3108,7 +2971,6 @@
       <c r="R72" s="4"/>
       <c r="S72" s="4"/>
       <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4"/>
@@ -3131,7 +2993,6 @@
       <c r="R73" s="4"/>
       <c r="S73" s="4"/>
       <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4"/>
@@ -3154,7 +3015,6 @@
       <c r="R74" s="4"/>
       <c r="S74" s="4"/>
       <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4"/>
@@ -3177,7 +3037,6 @@
       <c r="R75" s="4"/>
       <c r="S75" s="4"/>
       <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4"/>
@@ -3200,7 +3059,6 @@
       <c r="R76" s="4"/>
       <c r="S76" s="4"/>
       <c r="T76" s="4"/>
-      <c r="U76" s="4"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4"/>
@@ -3223,7 +3081,6 @@
       <c r="R77" s="4"/>
       <c r="S77" s="4"/>
       <c r="T77" s="4"/>
-      <c r="U77" s="4"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4"/>
@@ -3246,7 +3103,6 @@
       <c r="R78" s="4"/>
       <c r="S78" s="4"/>
       <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4"/>
@@ -3269,7 +3125,6 @@
       <c r="R79" s="4"/>
       <c r="S79" s="4"/>
       <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4"/>
@@ -3292,7 +3147,6 @@
       <c r="R80" s="4"/>
       <c r="S80" s="4"/>
       <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4"/>
@@ -3315,7 +3169,6 @@
       <c r="R81" s="4"/>
       <c r="S81" s="4"/>
       <c r="T81" s="4"/>
-      <c r="U81" s="4"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4"/>
@@ -3338,7 +3191,6 @@
       <c r="R82" s="4"/>
       <c r="S82" s="4"/>
       <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4"/>
@@ -3361,7 +3213,6 @@
       <c r="R83" s="4"/>
       <c r="S83" s="4"/>
       <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4"/>
@@ -3384,7 +3235,6 @@
       <c r="R84" s="4"/>
       <c r="S84" s="4"/>
       <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4"/>
@@ -3407,7 +3257,6 @@
       <c r="R85" s="4"/>
       <c r="S85" s="4"/>
       <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4"/>
@@ -3430,7 +3279,6 @@
       <c r="R86" s="4"/>
       <c r="S86" s="4"/>
       <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4"/>
@@ -3453,7 +3301,6 @@
       <c r="R87" s="4"/>
       <c r="S87" s="4"/>
       <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4"/>
@@ -3476,7 +3323,6 @@
       <c r="R88" s="4"/>
       <c r="S88" s="4"/>
       <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4"/>
@@ -3499,7 +3345,6 @@
       <c r="R89" s="4"/>
       <c r="S89" s="4"/>
       <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4"/>
@@ -3522,7 +3367,6 @@
       <c r="R90" s="4"/>
       <c r="S90" s="4"/>
       <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4"/>
@@ -3545,7 +3389,6 @@
       <c r="R91" s="4"/>
       <c r="S91" s="4"/>
       <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4"/>
@@ -3568,7 +3411,6 @@
       <c r="R92" s="4"/>
       <c r="S92" s="4"/>
       <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4"/>
@@ -3591,7 +3433,6 @@
       <c r="R93" s="4"/>
       <c r="S93" s="4"/>
       <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4"/>
@@ -3614,7 +3455,6 @@
       <c r="R94" s="4"/>
       <c r="S94" s="4"/>
       <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4"/>
@@ -3637,7 +3477,6 @@
       <c r="R95" s="4"/>
       <c r="S95" s="4"/>
       <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4"/>
@@ -3660,7 +3499,6 @@
       <c r="R96" s="4"/>
       <c r="S96" s="4"/>
       <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4"/>
@@ -3683,7 +3521,6 @@
       <c r="R97" s="4"/>
       <c r="S97" s="4"/>
       <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="4"/>
@@ -3706,7 +3543,6 @@
       <c r="R98" s="4"/>
       <c r="S98" s="4"/>
       <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4"/>
@@ -3729,7 +3565,6 @@
       <c r="R99" s="4"/>
       <c r="S99" s="4"/>
       <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4"/>
@@ -3752,7 +3587,6 @@
       <c r="R100" s="4"/>
       <c r="S100" s="4"/>
       <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4"/>
@@ -3775,7 +3609,6 @@
       <c r="R101" s="4"/>
       <c r="S101" s="4"/>
       <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4"/>
@@ -3798,7 +3631,6 @@
       <c r="R102" s="4"/>
       <c r="S102" s="4"/>
       <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4"/>
@@ -3821,7 +3653,6 @@
       <c r="R103" s="4"/>
       <c r="S103" s="4"/>
       <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4"/>
@@ -3844,7 +3675,6 @@
       <c r="R104" s="4"/>
       <c r="S104" s="4"/>
       <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4"/>
@@ -3867,7 +3697,6 @@
       <c r="R105" s="4"/>
       <c r="S105" s="4"/>
       <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4"/>
@@ -3890,7 +3719,6 @@
       <c r="R106" s="4"/>
       <c r="S106" s="4"/>
       <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4"/>
@@ -3913,7 +3741,6 @@
       <c r="R107" s="4"/>
       <c r="S107" s="4"/>
       <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4"/>
@@ -3936,7 +3763,6 @@
       <c r="R108" s="4"/>
       <c r="S108" s="4"/>
       <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4"/>
@@ -3959,7 +3785,6 @@
       <c r="R109" s="4"/>
       <c r="S109" s="4"/>
       <c r="T109" s="4"/>
-      <c r="U109" s="4"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="4"/>
@@ -3982,7 +3807,6 @@
       <c r="R110" s="4"/>
       <c r="S110" s="4"/>
       <c r="T110" s="4"/>
-      <c r="U110" s="4"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4"/>
@@ -4005,7 +3829,6 @@
       <c r="R111" s="4"/>
       <c r="S111" s="4"/>
       <c r="T111" s="4"/>
-      <c r="U111" s="4"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4"/>
@@ -4028,7 +3851,6 @@
       <c r="R112" s="4"/>
       <c r="S112" s="4"/>
       <c r="T112" s="4"/>
-      <c r="U112" s="4"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4"/>
@@ -4051,7 +3873,6 @@
       <c r="R113" s="4"/>
       <c r="S113" s="4"/>
       <c r="T113" s="4"/>
-      <c r="U113" s="4"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4"/>
@@ -4074,7 +3895,6 @@
       <c r="R114" s="4"/>
       <c r="S114" s="4"/>
       <c r="T114" s="4"/>
-      <c r="U114" s="4"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4"/>
@@ -4097,7 +3917,6 @@
       <c r="R115" s="4"/>
       <c r="S115" s="4"/>
       <c r="T115" s="4"/>
-      <c r="U115" s="4"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4"/>
@@ -4120,7 +3939,6 @@
       <c r="R116" s="4"/>
       <c r="S116" s="4"/>
       <c r="T116" s="4"/>
-      <c r="U116" s="4"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4"/>
@@ -4143,7 +3961,6 @@
       <c r="R117" s="4"/>
       <c r="S117" s="4"/>
       <c r="T117" s="4"/>
-      <c r="U117" s="4"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4"/>
@@ -4166,7 +3983,6 @@
       <c r="R118" s="4"/>
       <c r="S118" s="4"/>
       <c r="T118" s="4"/>
-      <c r="U118" s="4"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4"/>
@@ -4189,7 +4005,6 @@
       <c r="R119" s="4"/>
       <c r="S119" s="4"/>
       <c r="T119" s="4"/>
-      <c r="U119" s="4"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4"/>
@@ -4212,7 +4027,6 @@
       <c r="R120" s="4"/>
       <c r="S120" s="4"/>
       <c r="T120" s="4"/>
-      <c r="U120" s="4"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4"/>
@@ -4235,7 +4049,6 @@
       <c r="R121" s="4"/>
       <c r="S121" s="4"/>
       <c r="T121" s="4"/>
-      <c r="U121" s="4"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="4"/>
@@ -4258,7 +4071,6 @@
       <c r="R122" s="4"/>
       <c r="S122" s="4"/>
       <c r="T122" s="4"/>
-      <c r="U122" s="4"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="4"/>
@@ -4281,7 +4093,6 @@
       <c r="R123" s="4"/>
       <c r="S123" s="4"/>
       <c r="T123" s="4"/>
-      <c r="U123" s="4"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="4"/>
@@ -4304,7 +4115,6 @@
       <c r="R124" s="4"/>
       <c r="S124" s="4"/>
       <c r="T124" s="4"/>
-      <c r="U124" s="4"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="4"/>
@@ -4327,7 +4137,6 @@
       <c r="R125" s="4"/>
       <c r="S125" s="4"/>
       <c r="T125" s="4"/>
-      <c r="U125" s="4"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="4"/>
@@ -4350,7 +4159,6 @@
       <c r="R126" s="4"/>
       <c r="S126" s="4"/>
       <c r="T126" s="4"/>
-      <c r="U126" s="4"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="4"/>
@@ -4373,7 +4181,6 @@
       <c r="R127" s="4"/>
       <c r="S127" s="4"/>
       <c r="T127" s="4"/>
-      <c r="U127" s="4"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="4"/>
@@ -4396,7 +4203,6 @@
       <c r="R128" s="4"/>
       <c r="S128" s="4"/>
       <c r="T128" s="4"/>
-      <c r="U128" s="4"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="4"/>
@@ -4419,7 +4225,6 @@
       <c r="R129" s="4"/>
       <c r="S129" s="4"/>
       <c r="T129" s="4"/>
-      <c r="U129" s="4"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="4"/>
@@ -4442,7 +4247,6 @@
       <c r="R130" s="4"/>
       <c r="S130" s="4"/>
       <c r="T130" s="4"/>
-      <c r="U130" s="4"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="4"/>
@@ -4465,7 +4269,6 @@
       <c r="R131" s="4"/>
       <c r="S131" s="4"/>
       <c r="T131" s="4"/>
-      <c r="U131" s="4"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="4"/>
@@ -4488,7 +4291,6 @@
       <c r="R132" s="4"/>
       <c r="S132" s="4"/>
       <c r="T132" s="4"/>
-      <c r="U132" s="4"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="4"/>
@@ -4511,7 +4313,6 @@
       <c r="R133" s="4"/>
       <c r="S133" s="4"/>
       <c r="T133" s="4"/>
-      <c r="U133" s="4"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="4"/>
@@ -4534,7 +4335,6 @@
       <c r="R134" s="4"/>
       <c r="S134" s="4"/>
       <c r="T134" s="4"/>
-      <c r="U134" s="4"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
       <c r="A135" s="4"/>
@@ -4557,7 +4357,6 @@
       <c r="R135" s="4"/>
       <c r="S135" s="4"/>
       <c r="T135" s="4"/>
-      <c r="U135" s="4"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
       <c r="A136" s="4"/>
@@ -4580,7 +4379,6 @@
       <c r="R136" s="4"/>
       <c r="S136" s="4"/>
       <c r="T136" s="4"/>
-      <c r="U136" s="4"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
       <c r="A137" s="4"/>
@@ -4603,7 +4401,6 @@
       <c r="R137" s="4"/>
       <c r="S137" s="4"/>
       <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
       <c r="A138" s="4"/>
@@ -4626,7 +4423,6 @@
       <c r="R138" s="4"/>
       <c r="S138" s="4"/>
       <c r="T138" s="4"/>
-      <c r="U138" s="4"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
       <c r="A139" s="4"/>
@@ -4649,7 +4445,6 @@
       <c r="R139" s="4"/>
       <c r="S139" s="4"/>
       <c r="T139" s="4"/>
-      <c r="U139" s="4"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
       <c r="A140" s="4"/>
@@ -4672,7 +4467,6 @@
       <c r="R140" s="4"/>
       <c r="S140" s="4"/>
       <c r="T140" s="4"/>
-      <c r="U140" s="4"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
       <c r="A141" s="4"/>
@@ -4695,7 +4489,6 @@
       <c r="R141" s="4"/>
       <c r="S141" s="4"/>
       <c r="T141" s="4"/>
-      <c r="U141" s="4"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
       <c r="A142" s="4"/>
@@ -4718,7 +4511,6 @@
       <c r="R142" s="4"/>
       <c r="S142" s="4"/>
       <c r="T142" s="4"/>
-      <c r="U142" s="4"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
       <c r="A143" s="4"/>
@@ -4741,7 +4533,6 @@
       <c r="R143" s="4"/>
       <c r="S143" s="4"/>
       <c r="T143" s="4"/>
-      <c r="U143" s="4"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
       <c r="A144" s="4"/>
@@ -4764,7 +4555,6 @@
       <c r="R144" s="4"/>
       <c r="S144" s="4"/>
       <c r="T144" s="4"/>
-      <c r="U144" s="4"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
       <c r="A145" s="4"/>
@@ -4787,7 +4577,6 @@
       <c r="R145" s="4"/>
       <c r="S145" s="4"/>
       <c r="T145" s="4"/>
-      <c r="U145" s="4"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
       <c r="A146" s="4"/>
@@ -4810,7 +4599,6 @@
       <c r="R146" s="4"/>
       <c r="S146" s="4"/>
       <c r="T146" s="4"/>
-      <c r="U146" s="4"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
       <c r="A147" s="4"/>
@@ -4833,7 +4621,6 @@
       <c r="R147" s="4"/>
       <c r="S147" s="4"/>
       <c r="T147" s="4"/>
-      <c r="U147" s="4"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
       <c r="A148" s="4"/>
@@ -4856,7 +4643,6 @@
       <c r="R148" s="4"/>
       <c r="S148" s="4"/>
       <c r="T148" s="4"/>
-      <c r="U148" s="4"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
       <c r="A149" s="4"/>
@@ -4879,7 +4665,6 @@
       <c r="R149" s="4"/>
       <c r="S149" s="4"/>
       <c r="T149" s="4"/>
-      <c r="U149" s="4"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
       <c r="A150" s="4"/>
@@ -4902,7 +4687,6 @@
       <c r="R150" s="4"/>
       <c r="S150" s="4"/>
       <c r="T150" s="4"/>
-      <c r="U150" s="4"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
       <c r="A151" s="4"/>
@@ -4925,7 +4709,6 @@
       <c r="R151" s="4"/>
       <c r="S151" s="4"/>
       <c r="T151" s="4"/>
-      <c r="U151" s="4"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
       <c r="A152" s="4"/>
@@ -4948,7 +4731,6 @@
       <c r="R152" s="4"/>
       <c r="S152" s="4"/>
       <c r="T152" s="4"/>
-      <c r="U152" s="4"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="4"/>
@@ -4971,7 +4753,6 @@
       <c r="R153" s="4"/>
       <c r="S153" s="4"/>
       <c r="T153" s="4"/>
-      <c r="U153" s="4"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
       <c r="A154" s="4"/>
@@ -4994,7 +4775,6 @@
       <c r="R154" s="4"/>
       <c r="S154" s="4"/>
       <c r="T154" s="4"/>
-      <c r="U154" s="4"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
       <c r="A155" s="4"/>
@@ -5017,7 +4797,6 @@
       <c r="R155" s="4"/>
       <c r="S155" s="4"/>
       <c r="T155" s="4"/>
-      <c r="U155" s="4"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
       <c r="A156" s="4"/>
@@ -5040,7 +4819,6 @@
       <c r="R156" s="4"/>
       <c r="S156" s="4"/>
       <c r="T156" s="4"/>
-      <c r="U156" s="4"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
       <c r="A157" s="4"/>
@@ -5063,7 +4841,6 @@
       <c r="R157" s="4"/>
       <c r="S157" s="4"/>
       <c r="T157" s="4"/>
-      <c r="U157" s="4"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
       <c r="A158" s="4"/>
@@ -5086,7 +4863,6 @@
       <c r="R158" s="4"/>
       <c r="S158" s="4"/>
       <c r="T158" s="4"/>
-      <c r="U158" s="4"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
       <c r="A159" s="4"/>
@@ -5109,7 +4885,6 @@
       <c r="R159" s="4"/>
       <c r="S159" s="4"/>
       <c r="T159" s="4"/>
-      <c r="U159" s="4"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
       <c r="A160" s="4"/>
@@ -5132,7 +4907,6 @@
       <c r="R160" s="4"/>
       <c r="S160" s="4"/>
       <c r="T160" s="4"/>
-      <c r="U160" s="4"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
       <c r="A161" s="4"/>
@@ -5155,7 +4929,6 @@
       <c r="R161" s="4"/>
       <c r="S161" s="4"/>
       <c r="T161" s="4"/>
-      <c r="U161" s="4"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
       <c r="A162" s="4"/>
@@ -5178,7 +4951,6 @@
       <c r="R162" s="4"/>
       <c r="S162" s="4"/>
       <c r="T162" s="4"/>
-      <c r="U162" s="4"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
       <c r="A163" s="4"/>
@@ -5201,7 +4973,6 @@
       <c r="R163" s="4"/>
       <c r="S163" s="4"/>
       <c r="T163" s="4"/>
-      <c r="U163" s="4"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
       <c r="A164" s="4"/>
@@ -5224,7 +4995,6 @@
       <c r="R164" s="4"/>
       <c r="S164" s="4"/>
       <c r="T164" s="4"/>
-      <c r="U164" s="4"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
       <c r="A165" s="4"/>
@@ -5247,7 +5017,6 @@
       <c r="R165" s="4"/>
       <c r="S165" s="4"/>
       <c r="T165" s="4"/>
-      <c r="U165" s="4"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
       <c r="A166" s="4"/>
@@ -5270,7 +5039,6 @@
       <c r="R166" s="4"/>
       <c r="S166" s="4"/>
       <c r="T166" s="4"/>
-      <c r="U166" s="4"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
       <c r="A167" s="4"/>
@@ -5293,7 +5061,6 @@
       <c r="R167" s="4"/>
       <c r="S167" s="4"/>
       <c r="T167" s="4"/>
-      <c r="U167" s="4"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
       <c r="A168" s="4"/>
@@ -5316,7 +5083,6 @@
       <c r="R168" s="4"/>
       <c r="S168" s="4"/>
       <c r="T168" s="4"/>
-      <c r="U168" s="4"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="4"/>
@@ -5339,7 +5105,6 @@
       <c r="R169" s="4"/>
       <c r="S169" s="4"/>
       <c r="T169" s="4"/>
-      <c r="U169" s="4"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
       <c r="A170" s="4"/>
@@ -5362,7 +5127,6 @@
       <c r="R170" s="4"/>
       <c r="S170" s="4"/>
       <c r="T170" s="4"/>
-      <c r="U170" s="4"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
       <c r="A171" s="4"/>
@@ -5385,7 +5149,6 @@
       <c r="R171" s="4"/>
       <c r="S171" s="4"/>
       <c r="T171" s="4"/>
-      <c r="U171" s="4"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
       <c r="A172" s="4"/>
@@ -5408,7 +5171,6 @@
       <c r="R172" s="4"/>
       <c r="S172" s="4"/>
       <c r="T172" s="4"/>
-      <c r="U172" s="4"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
       <c r="A173" s="4"/>
@@ -5431,7 +5193,6 @@
       <c r="R173" s="4"/>
       <c r="S173" s="4"/>
       <c r="T173" s="4"/>
-      <c r="U173" s="4"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
       <c r="A174" s="4"/>
@@ -5454,7 +5215,6 @@
       <c r="R174" s="4"/>
       <c r="S174" s="4"/>
       <c r="T174" s="4"/>
-      <c r="U174" s="4"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
       <c r="A175" s="4"/>
@@ -5477,7 +5237,6 @@
       <c r="R175" s="4"/>
       <c r="S175" s="4"/>
       <c r="T175" s="4"/>
-      <c r="U175" s="4"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
       <c r="A176" s="4"/>
@@ -5500,7 +5259,6 @@
       <c r="R176" s="4"/>
       <c r="S176" s="4"/>
       <c r="T176" s="4"/>
-      <c r="U176" s="4"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
       <c r="A177" s="4"/>
@@ -5523,7 +5281,6 @@
       <c r="R177" s="4"/>
       <c r="S177" s="4"/>
       <c r="T177" s="4"/>
-      <c r="U177" s="4"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
       <c r="A178" s="4"/>
@@ -5546,7 +5303,6 @@
       <c r="R178" s="4"/>
       <c r="S178" s="4"/>
       <c r="T178" s="4"/>
-      <c r="U178" s="4"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
       <c r="A179" s="4"/>
@@ -5569,7 +5325,6 @@
       <c r="R179" s="4"/>
       <c r="S179" s="4"/>
       <c r="T179" s="4"/>
-      <c r="U179" s="4"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
       <c r="A180" s="4"/>
@@ -5592,7 +5347,6 @@
       <c r="R180" s="4"/>
       <c r="S180" s="4"/>
       <c r="T180" s="4"/>
-      <c r="U180" s="4"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
       <c r="A181" s="4"/>
@@ -5615,7 +5369,6 @@
       <c r="R181" s="4"/>
       <c r="S181" s="4"/>
       <c r="T181" s="4"/>
-      <c r="U181" s="4"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
       <c r="A182" s="4"/>
@@ -5638,7 +5391,6 @@
       <c r="R182" s="4"/>
       <c r="S182" s="4"/>
       <c r="T182" s="4"/>
-      <c r="U182" s="4"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
       <c r="A183" s="4"/>
@@ -5661,7 +5413,6 @@
       <c r="R183" s="4"/>
       <c r="S183" s="4"/>
       <c r="T183" s="4"/>
-      <c r="U183" s="4"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
       <c r="A184" s="4"/>
@@ -5684,7 +5435,6 @@
       <c r="R184" s="4"/>
       <c r="S184" s="4"/>
       <c r="T184" s="4"/>
-      <c r="U184" s="4"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
       <c r="A185" s="4"/>
@@ -5707,7 +5457,6 @@
       <c r="R185" s="4"/>
       <c r="S185" s="4"/>
       <c r="T185" s="4"/>
-      <c r="U185" s="4"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
       <c r="A186" s="4"/>
@@ -5730,7 +5479,6 @@
       <c r="R186" s="4"/>
       <c r="S186" s="4"/>
       <c r="T186" s="4"/>
-      <c r="U186" s="4"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
       <c r="A187" s="4"/>
@@ -5753,7 +5501,6 @@
       <c r="R187" s="4"/>
       <c r="S187" s="4"/>
       <c r="T187" s="4"/>
-      <c r="U187" s="4"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
       <c r="A188" s="4"/>
@@ -5776,7 +5523,6 @@
       <c r="R188" s="4"/>
       <c r="S188" s="4"/>
       <c r="T188" s="4"/>
-      <c r="U188" s="4"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
       <c r="A189" s="4"/>
@@ -5799,7 +5545,6 @@
       <c r="R189" s="4"/>
       <c r="S189" s="4"/>
       <c r="T189" s="4"/>
-      <c r="U189" s="4"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
       <c r="A190" s="4"/>
@@ -5822,7 +5567,6 @@
       <c r="R190" s="4"/>
       <c r="S190" s="4"/>
       <c r="T190" s="4"/>
-      <c r="U190" s="4"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
       <c r="A191" s="4"/>
@@ -5845,7 +5589,6 @@
       <c r="R191" s="4"/>
       <c r="S191" s="4"/>
       <c r="T191" s="4"/>
-      <c r="U191" s="4"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
       <c r="A192" s="4"/>
@@ -5868,7 +5611,6 @@
       <c r="R192" s="4"/>
       <c r="S192" s="4"/>
       <c r="T192" s="4"/>
-      <c r="U192" s="4"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
       <c r="A193" s="4"/>
@@ -5891,7 +5633,6 @@
       <c r="R193" s="4"/>
       <c r="S193" s="4"/>
       <c r="T193" s="4"/>
-      <c r="U193" s="4"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
       <c r="A194" s="4"/>
@@ -5914,7 +5655,6 @@
       <c r="R194" s="4"/>
       <c r="S194" s="4"/>
       <c r="T194" s="4"/>
-      <c r="U194" s="4"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
       <c r="A195" s="4"/>
@@ -5937,7 +5677,6 @@
       <c r="R195" s="4"/>
       <c r="S195" s="4"/>
       <c r="T195" s="4"/>
-      <c r="U195" s="4"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
       <c r="A196" s="4"/>
@@ -5960,7 +5699,6 @@
       <c r="R196" s="4"/>
       <c r="S196" s="4"/>
       <c r="T196" s="4"/>
-      <c r="U196" s="4"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
       <c r="A197" s="4"/>
@@ -5983,7 +5721,6 @@
       <c r="R197" s="4"/>
       <c r="S197" s="4"/>
       <c r="T197" s="4"/>
-      <c r="U197" s="4"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
       <c r="A198" s="4"/>
@@ -6006,7 +5743,6 @@
       <c r="R198" s="4"/>
       <c r="S198" s="4"/>
       <c r="T198" s="4"/>
-      <c r="U198" s="4"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
       <c r="A199" s="4"/>
@@ -6029,7 +5765,6 @@
       <c r="R199" s="4"/>
       <c r="S199" s="4"/>
       <c r="T199" s="4"/>
-      <c r="U199" s="4"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
       <c r="A200" s="4"/>
@@ -6052,7 +5787,6 @@
       <c r="R200" s="4"/>
       <c r="S200" s="4"/>
       <c r="T200" s="4"/>
-      <c r="U200" s="4"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
       <c r="A201" s="4"/>
@@ -6075,7 +5809,6 @@
       <c r="R201" s="4"/>
       <c r="S201" s="4"/>
       <c r="T201" s="4"/>
-      <c r="U201" s="4"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
       <c r="A202" s="4"/>
@@ -6098,7 +5831,6 @@
       <c r="R202" s="4"/>
       <c r="S202" s="4"/>
       <c r="T202" s="4"/>
-      <c r="U202" s="4"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
       <c r="A203" s="4"/>
@@ -6121,7 +5853,6 @@
       <c r="R203" s="4"/>
       <c r="S203" s="4"/>
       <c r="T203" s="4"/>
-      <c r="U203" s="4"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
       <c r="A204" s="4"/>
@@ -6144,7 +5875,6 @@
       <c r="R204" s="4"/>
       <c r="S204" s="4"/>
       <c r="T204" s="4"/>
-      <c r="U204" s="4"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
       <c r="A205" s="4"/>
@@ -6167,7 +5897,6 @@
       <c r="R205" s="4"/>
       <c r="S205" s="4"/>
       <c r="T205" s="4"/>
-      <c r="U205" s="4"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
       <c r="A206" s="4"/>
@@ -6190,7 +5919,6 @@
       <c r="R206" s="4"/>
       <c r="S206" s="4"/>
       <c r="T206" s="4"/>
-      <c r="U206" s="4"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
       <c r="A207" s="4"/>
@@ -6213,7 +5941,6 @@
       <c r="R207" s="4"/>
       <c r="S207" s="4"/>
       <c r="T207" s="4"/>
-      <c r="U207" s="4"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
       <c r="A208" s="4"/>
@@ -6236,7 +5963,6 @@
       <c r="R208" s="4"/>
       <c r="S208" s="4"/>
       <c r="T208" s="4"/>
-      <c r="U208" s="4"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
       <c r="A209" s="4"/>
@@ -6259,7 +5985,6 @@
       <c r="R209" s="4"/>
       <c r="S209" s="4"/>
       <c r="T209" s="4"/>
-      <c r="U209" s="4"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
       <c r="A210" s="4"/>
@@ -6282,7 +6007,6 @@
       <c r="R210" s="4"/>
       <c r="S210" s="4"/>
       <c r="T210" s="4"/>
-      <c r="U210" s="4"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
       <c r="A211" s="4"/>
@@ -6305,7 +6029,6 @@
       <c r="R211" s="4"/>
       <c r="S211" s="4"/>
       <c r="T211" s="4"/>
-      <c r="U211" s="4"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
       <c r="A212" s="4"/>
@@ -6328,7 +6051,6 @@
       <c r="R212" s="4"/>
       <c r="S212" s="4"/>
       <c r="T212" s="4"/>
-      <c r="U212" s="4"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
       <c r="A213" s="4"/>
@@ -6351,7 +6073,6 @@
       <c r="R213" s="4"/>
       <c r="S213" s="4"/>
       <c r="T213" s="4"/>
-      <c r="U213" s="4"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
       <c r="A214" s="4"/>
@@ -6374,7 +6095,6 @@
       <c r="R214" s="4"/>
       <c r="S214" s="4"/>
       <c r="T214" s="4"/>
-      <c r="U214" s="4"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
       <c r="A215" s="4"/>
@@ -6397,7 +6117,6 @@
       <c r="R215" s="4"/>
       <c r="S215" s="4"/>
       <c r="T215" s="4"/>
-      <c r="U215" s="4"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
       <c r="A216" s="4"/>
@@ -6420,7 +6139,6 @@
       <c r="R216" s="4"/>
       <c r="S216" s="4"/>
       <c r="T216" s="4"/>
-      <c r="U216" s="4"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
       <c r="A217" s="4"/>
@@ -6443,7 +6161,6 @@
       <c r="R217" s="4"/>
       <c r="S217" s="4"/>
       <c r="T217" s="4"/>
-      <c r="U217" s="4"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
       <c r="A218" s="4"/>
@@ -6466,7 +6183,6 @@
       <c r="R218" s="4"/>
       <c r="S218" s="4"/>
       <c r="T218" s="4"/>
-      <c r="U218" s="4"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
       <c r="A219" s="4"/>
@@ -6489,7 +6205,6 @@
       <c r="R219" s="4"/>
       <c r="S219" s="4"/>
       <c r="T219" s="4"/>
-      <c r="U219" s="4"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
       <c r="A220" s="4"/>
@@ -6512,7 +6227,6 @@
       <c r="R220" s="4"/>
       <c r="S220" s="4"/>
       <c r="T220" s="4"/>
-      <c r="U220" s="4"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
       <c r="A221" s="17"/>

--- a/JsonConverter/ExcelFiles/ItemData.xlsx
+++ b/JsonConverter/ExcelFiles/ItemData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\바탕화면\Project\JewelThief\JewelThief\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2CACD65-F25E-4CF2-A75E-099BEE2A2B05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C29822-C5D1-4F27-911F-8DF8483250BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1812" yWindow="1812" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="28080" windowHeight="14628" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ItemData" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
   <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="PSHgN1/kfcCjDd8eM0S9gC4F43mGfiTG0/AQb1lJB4c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="KVgJIt80mbyXwVPOfvEH4RqVzXD4ip2ThuePEi8DMaU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="157">
   <si>
     <t>아이템 ID</t>
   </si>
@@ -392,9 +392,6 @@
     <t>JunkObject</t>
   </si>
   <si>
-    <t>MeshCollider_Junk_Bottle_Blue</t>
-  </si>
-  <si>
     <t>Item_Junk_Bottle_Pink_Large</t>
   </si>
   <si>
@@ -407,9 +404,6 @@
     <t>Junk_Bottle_Pink_Large[SM_Prop_Bottle_Large_01]</t>
   </si>
   <si>
-    <t>MeshCollider_Junk_Bottle_Pink_Large</t>
-  </si>
-  <si>
     <t>Item_Junk_Can_Navy</t>
   </si>
   <si>
@@ -488,32 +482,31 @@
     <t>Jewel_Stone[Cube.058]</t>
   </si>
   <si>
-    <t>Item_Escape_Floor</t>
-  </si>
-  <si>
     <t>탈출구</t>
   </si>
   <si>
+    <t>탈출구.
+본부로 복귀합니다.</t>
+  </si>
+  <si>
     <t>Escape</t>
   </si>
   <si>
+    <t>Mesh_Escape[SM_Prop_Vent_01]</t>
+  </si>
+  <si>
     <t>MeshCollider_Escape</t>
   </si>
   <si>
-    <t>Item_Escape_Wall</t>
-  </si>
-  <si>
-    <t>Item_Escape_Ceiling</t>
-  </si>
-  <si>
-    <t>Mesh_Escape[SM_Prop_Vent_01]</t>
+    <t>Item_Escape</t>
+    <phoneticPr fontId="10" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -587,13 +580,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -648,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -672,7 +658,6 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -891,7 +876,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:U1000"/>
+  <dimension ref="A1:U998"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="25.33203125" customWidth="1"/>
@@ -1904,9 +1889,6 @@
       <c r="M22" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="O22" s="3"/>
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
@@ -1917,13 +1899,13 @@
     </row>
     <row r="23" spans="1:21" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>123</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>124</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>117</v>
@@ -1943,7 +1925,7 @@
         <v>118</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L23" s="3" t="s">
         <v>120</v>
@@ -1951,9 +1933,7 @@
       <c r="M23" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>126</v>
-      </c>
+      <c r="N23" s="3"/>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
       <c r="Q23" s="3"/>
@@ -1964,13 +1944,13 @@
     </row>
     <row r="24" spans="1:21" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>127</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>129</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>117</v>
@@ -1990,7 +1970,7 @@
         <v>118</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>120</v>
@@ -2009,13 +1989,13 @@
     </row>
     <row r="25" spans="1:21" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C25" s="3" t="s">
         <v>131</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>133</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>117</v>
@@ -2035,7 +2015,7 @@
         <v>118</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>120</v>
@@ -2054,13 +2034,13 @@
     </row>
     <row r="26" spans="1:21" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>135</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>137</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>117</v>
@@ -2080,7 +2060,7 @@
         <v>118</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>120</v>
@@ -2099,13 +2079,13 @@
     </row>
     <row r="27" spans="1:21" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>141</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>117</v>
@@ -2125,7 +2105,7 @@
         <v>118</v>
       </c>
       <c r="K27" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="L27" s="3" t="s">
         <v>120</v>
@@ -2144,13 +2124,13 @@
     </row>
     <row r="28" spans="1:21" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>145</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>117</v>
@@ -2167,10 +2147,10 @@
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
       <c r="J28" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>120</v>
@@ -2189,13 +2169,13 @@
     </row>
     <row r="29" spans="1:21" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>148</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>117</v>
@@ -2212,10 +2192,10 @@
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
       <c r="J29" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>120</v>
@@ -2234,16 +2214,16 @@
     </row>
     <row r="30" spans="1:21" ht="15.75" customHeight="1">
       <c r="A30" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D30" s="13" t="s">
         <v>153</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>155</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>40</v>
@@ -2259,15 +2239,15 @@
       <c r="J30" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="K30" s="15" t="s">
-        <v>159</v>
+      <c r="K30" s="3" t="s">
+        <v>154</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="M30" s="3"/>
       <c r="N30" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="O30" s="3"/>
       <c r="P30" s="3"/>
@@ -2278,42 +2258,20 @@
       <c r="U30" s="3"/>
     </row>
     <row r="31" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A31" s="12" t="s">
-        <v>157</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D31" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0</v>
-      </c>
-      <c r="G31" s="3">
-        <v>0</v>
-      </c>
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
-      <c r="J31" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K31" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="N31" s="3"/>
       <c r="O31" s="3"/>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
@@ -2323,42 +2281,20 @@
       <c r="U31" s="3"/>
     </row>
     <row r="32" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A32" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>0</v>
-      </c>
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
-      <c r="J32" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="K32" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>155</v>
-      </c>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
       <c r="M32" s="3"/>
-      <c r="N32" s="3" t="s">
-        <v>156</v>
-      </c>
+      <c r="N32" s="3"/>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
       <c r="Q32" s="3"/>
@@ -6646,50 +6582,12 @@
       <c r="U218" s="3"/>
     </row>
     <row r="219" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A219" s="3"/>
-      <c r="B219" s="3"/>
-      <c r="C219" s="3"/>
-      <c r="D219" s="3"/>
-      <c r="E219" s="3"/>
-      <c r="F219" s="3"/>
-      <c r="G219" s="3"/>
-      <c r="H219" s="3"/>
-      <c r="I219" s="3"/>
-      <c r="J219" s="3"/>
-      <c r="K219" s="3"/>
-      <c r="L219" s="3"/>
-      <c r="M219" s="3"/>
-      <c r="N219" s="3"/>
-      <c r="O219" s="3"/>
-      <c r="P219" s="3"/>
-      <c r="Q219" s="3"/>
-      <c r="R219" s="3"/>
-      <c r="S219" s="3"/>
-      <c r="T219" s="3"/>
-      <c r="U219" s="3"/>
+      <c r="A219" s="14"/>
+      <c r="B219" s="14"/>
     </row>
     <row r="220" spans="1:21" ht="15.75" customHeight="1">
-      <c r="A220" s="3"/>
-      <c r="B220" s="3"/>
-      <c r="C220" s="3"/>
-      <c r="D220" s="3"/>
-      <c r="E220" s="3"/>
-      <c r="F220" s="3"/>
-      <c r="G220" s="3"/>
-      <c r="H220" s="3"/>
-      <c r="I220" s="3"/>
-      <c r="J220" s="3"/>
-      <c r="K220" s="3"/>
-      <c r="L220" s="3"/>
-      <c r="M220" s="3"/>
-      <c r="N220" s="3"/>
-      <c r="O220" s="3"/>
-      <c r="P220" s="3"/>
-      <c r="Q220" s="3"/>
-      <c r="R220" s="3"/>
-      <c r="S220" s="3"/>
-      <c r="T220" s="3"/>
-      <c r="U220" s="3"/>
+      <c r="A220" s="14"/>
+      <c r="B220" s="14"/>
     </row>
     <row r="221" spans="1:21" ht="15.75" customHeight="1">
       <c r="A221" s="14"/>
@@ -9802,14 +9700,6 @@
     <row r="998" spans="1:2" ht="15.75" customHeight="1">
       <c r="A998" s="14"/>
       <c r="B998" s="14"/>
-    </row>
-    <row r="999" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A999" s="14"/>
-      <c r="B999" s="14"/>
-    </row>
-    <row r="1000" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A1000" s="14"/>
-      <c r="B1000" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="10" type="noConversion"/>
